--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -46252,7 +46252,7 @@
       <c r="C2" s="47" t="n"/>
       <c r="D2" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Login Non Employee</t>
+          <t>Membuka halaman Login</t>
         </is>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -46309,7 +46309,7 @@
       <c r="C3" s="47" t="n"/>
       <c r="D3" s="48" t="inlineStr">
         <is>
-          <t>Melakukan login Non Employee dengan email dan password valid</t>
+          <t>Melakukan login dengan email dan password valid</t>
         </is>
       </c>
       <c r="E3" s="46" t="inlineStr">
@@ -46374,7 +46374,7 @@
       <c r="C4" s="47" t="n"/>
       <c r="D4" s="48" t="inlineStr">
         <is>
-          <t>Melakukan login Non Employee dengan email tidak terdaftar</t>
+          <t>Melakukan login dengan email tidak terdaftar</t>
         </is>
       </c>
       <c r="E4" s="46" t="inlineStr">
@@ -46439,7 +46439,7 @@
       <c r="C5" s="47" t="n"/>
       <c r="D5" s="48" t="inlineStr">
         <is>
-          <t>Melakukan login Non Employee dengan password salah</t>
+          <t>Melakukan login dengan password salah</t>
         </is>
       </c>
       <c r="E5" s="46" t="inlineStr">

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -46111,7 +46111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA172"/>
+  <dimension ref="A1:AA171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48858,7 +48858,7 @@
       <c r="C46" s="47" t="n"/>
       <c r="D46" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail Versi Aplikasi</t>
+          <t>Logout dari aplikasi</t>
         </is>
       </c>
       <c r="E46" s="46" t="inlineStr">
@@ -48868,19 +48868,21 @@
       </c>
       <c r="F46" s="46" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G46" s="48" t="inlineStr">
         <is>
           <t>1. Klik menu Profile pada navigasi bawah.
-2. Lihat detail teks informasi Versi Aplikasi pada bagian Sistem.</t>
+2. Scroll ke bagian paling bawah dan klik button Logout.
+3. Klik konfirmasi pada dialog box logout.</t>
         </is>
       </c>
       <c r="H46" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil mengklik menu Profile.
-2. Berhasil menampilkan informasi nomor/versi aplikasi yang digunakan saat ini secara jelas.</t>
+2. Menampilkan dialog box konfirmasi logout akun.
+3. Berhasil memproses logout dan kembali ke halaman Login awal aplikasi.</t>
         </is>
       </c>
       <c r="I46" s="49" t="n"/>
@@ -48906,18 +48908,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B47" s="46" t="inlineStr">
         <is>
-          <t>Profile</t>
-        </is>
-      </c>
-      <c r="C47" s="47" t="n"/>
+          <t>Sales Tracking Activity</t>
+        </is>
+      </c>
+      <c r="C47" s="46" t="inlineStr">
+        <is>
+          <t>Visit In</t>
+        </is>
+      </c>
       <c r="D47" s="48" t="inlineStr">
         <is>
-          <t>Logout dari aplikasi</t>
+          <t>Melakukan Visit In untuk Sales Lending</t>
         </is>
       </c>
       <c r="E47" s="46" t="inlineStr">
@@ -48932,16 +48938,28 @@
       </c>
       <c r="G47" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu Profile pada navigasi bawah.
-2. Scroll ke bagian paling bawah dan klik button Logout.
-3. Klik konfirmasi pada dialog box logout.</t>
+          <t>1. Klik button Visit In 
+2. Pilih type Visit Lending pada popup.
+3. Pilih data pada field Tipe Kunjungan.
+4. Pilih data pada field Nasabah / Prospek (Opsional)
+5. Input data pada field Nama Nasabah.
+6. Input data pada field Alamat Nasabah.
+7. Input data pada field Catatan Kunjungan.
+8. Klik button Ambil Foto Kunjungan dan ambil foto.
+9. Klik button Mulai Kunjungan.</t>
         </is>
       </c>
       <c r="H47" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengklik menu Profile.
-2. Menampilkan dialog box konfirmasi logout akun.
-3. Berhasil memproses logout dan kembali ke halaman Login awal aplikasi.</t>
+          <t>1. Berhasil membuka halaman Kunjungan (Visit In)
+2. Berhasil memilih type Visit Lending.
+3. Berhasil memilih data pada field Tipe Kunjungan.
+4. Berhasil memilih data pada field Nasabah / Prospek (Opsional)
+5. Berhasil menginput data pada field Nama Nasabah.
+6. Berhasil menginput data pada field Alamat Nasabah.
+7. Berhasil menginput data pada field Catatan Kunjungan.
+8. Berhasil mengambil foto kunjungan.
+9. Berhasil melakukan Visit In.</t>
         </is>
       </c>
       <c r="I47" s="49" t="n"/>
@@ -48967,7 +48985,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B48" s="46" t="inlineStr">
@@ -48982,7 +49000,7 @@
       </c>
       <c r="D48" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Visit In untuk Sales Lending</t>
+          <t>Melakukan Visit In untuk Sales Funding</t>
         </is>
       </c>
       <c r="E48" s="46" t="inlineStr">
@@ -48998,9 +49016,9 @@
       <c r="G48" s="48" t="inlineStr">
         <is>
           <t>1. Klik button Visit In 
-2. Pilih type Visit Lending pada popup.
+2. Pilih type Visit Funding pada popup.
 3. Pilih data pada field Tipe Kunjungan.
-4. Pilih data pada field Nasabah / Prospek (Opsional)
+4. Pilih data pada field Nasabah / Prospek
 5. Input data pada field Nama Nasabah.
 6. Input data pada field Alamat Nasabah.
 7. Input data pada field Catatan Kunjungan.
@@ -49011,9 +49029,9 @@
       <c r="H48" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil membuka halaman Kunjungan (Visit In)
-2. Berhasil memilih type Visit Lending.
+2. Berhasil memilih type Visit Funding.
 3. Berhasil memilih data pada field Tipe Kunjungan.
-4. Berhasil memilih data pada field Nasabah / Prospek (Opsional)
+4. Berhasil memilih data pada field Nasabah / Prospek 
 5. Berhasil menginput data pada field Nama Nasabah.
 6. Berhasil menginput data pada field Alamat Nasabah.
 7. Berhasil menginput data pada field Catatan Kunjungan.
@@ -49044,7 +49062,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B49" s="46" t="inlineStr">
@@ -49059,12 +49077,12 @@
       </c>
       <c r="D49" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Visit In untuk Sales Funding</t>
+          <t>Melakukan Visit In tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E49" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F49" s="46" t="inlineStr">
@@ -49074,28 +49092,24 @@
       </c>
       <c r="G49" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Visit In 
-2. Pilih type Visit Funding pada popup.
-3. Pilih data pada field Tipe Kunjungan.
-4. Pilih data pada field Nasabah / Prospek
-5. Input data pada field Nama Nasabah.
-6. Input data pada field Alamat Nasabah.
-7. Input data pada field Catatan Kunjungan.
-8. Klik button Ambil Foto Kunjungan dan ambil foto.
-9. Klik button Mulai Kunjungan.</t>
+          <t>1. Klik button Visit In
+2. Pilih type Visit (Lending / Funding) pada popup.
+3. Biarkan kosong pada field Tipe Kunjungan.
+4. Biarkan kosong pada field Nama Nasabah.
+5. Biarkan kosong pada field Alamat Nasabah.
+6. Biarkan kosong pada field Catatan Kunjungan.
+7. Klik button Mulai Kunjungan.</t>
         </is>
       </c>
       <c r="H49" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil membuka halaman Kunjungan (Visit In)
-2. Berhasil memilih type Visit Funding.
-3. Berhasil memilih data pada field Tipe Kunjungan.
-4. Berhasil memilih data pada field Nasabah / Prospek 
-5. Berhasil menginput data pada field Nama Nasabah.
-6. Berhasil menginput data pada field Alamat Nasabah.
-7. Berhasil menginput data pada field Catatan Kunjungan.
-8. Berhasil mengambil foto kunjungan.
-9. Berhasil melakukan Visit In.</t>
+2. Berhasil memilih type Visit.
+3. Field Tipe Kunjungan tidak terisi.
+4. Field Nama Nasabah tidak terisi.
+5. Field Alamat Nasabah tidak terisi.
+6. Field Catatan Kunjungan tidak terisi.
+7. Sistem menampilkan pesan error validasi mandatory.</t>
         </is>
       </c>
       <c r="I49" s="49" t="n"/>
@@ -49121,7 +49135,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B50" s="46" t="inlineStr">
@@ -49131,17 +49145,17 @@
       </c>
       <c r="C50" s="46" t="inlineStr">
         <is>
-          <t>Visit In</t>
+          <t>Visit Out</t>
         </is>
       </c>
       <c r="D50" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Visit In tanpa mengisi field mandatory</t>
+          <t>Melakukan Visit Out</t>
         </is>
       </c>
       <c r="E50" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F50" s="46" t="inlineStr">
@@ -49151,24 +49165,18 @@
       </c>
       <c r="G50" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Visit In
-2. Pilih type Visit (Lending / Funding) pada popup.
-3. Biarkan kosong pada field Tipe Kunjungan.
-4. Biarkan kosong pada field Nama Nasabah.
-5. Biarkan kosong pada field Alamat Nasabah.
-6. Biarkan kosong pada field Catatan Kunjungan.
-7. Klik button Mulai Kunjungan.</t>
+          <t>1. Klik button Visit Out
+2. Input data pada field Catatan Kunjungan.
+3. Klik button Ambil Foto Kunjungan dan ambil foto.
+4. Klik button Selesai Kunjungan.</t>
         </is>
       </c>
       <c r="H50" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka halaman Kunjungan (Visit In)
-2. Berhasil memilih type Visit.
-3. Field Tipe Kunjungan tidak terisi.
-4. Field Nama Nasabah tidak terisi.
-5. Field Alamat Nasabah tidak terisi.
-6. Field Catatan Kunjungan tidak terisi.
-7. Sistem menampilkan pesan error validasi mandatory.</t>
+          <t>1. Berhasil menampilkan halaman Selesai Kunjungan (Visit Out)
+2. Berhasil menginput data pada field Catatan Kunjungan.
+3. Berhasil mengambil foto kunjungan.
+4. Berhasil melakukan Visit Out.</t>
         </is>
       </c>
       <c r="I50" s="49" t="n"/>
@@ -49194,7 +49202,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B51" s="46" t="inlineStr">
@@ -49209,12 +49217,12 @@
       </c>
       <c r="D51" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Visit Out</t>
+          <t>Melakukan Visit Out tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E51" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F51" s="46" t="inlineStr">
@@ -49225,17 +49233,15 @@
       <c r="G51" s="48" t="inlineStr">
         <is>
           <t>1. Klik button Visit Out
-2. Input data pada field Catatan Kunjungan.
-3. Klik button Ambil Foto Kunjungan dan ambil foto.
-4. Klik button Selesai Kunjungan.</t>
+2. Biarkan kosong pada field Catatan Kunjungan.
+3. Klik button Selesai Kunjungan.</t>
         </is>
       </c>
       <c r="H51" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan halaman Selesai Kunjungan (Visit Out)
-2. Berhasil menginput data pada field Catatan Kunjungan.
-3. Berhasil mengambil foto kunjungan.
-4. Berhasil melakukan Visit Out.</t>
+2. Field Catatan Kunjungan tidak terisi.
+3. Sistem menampilkan pesan error validasi mandatory.</t>
         </is>
       </c>
       <c r="I51" s="49" t="n"/>
@@ -49261,27 +49267,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B52" s="46" t="inlineStr">
         <is>
-          <t>Sales Tracking Activity</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="C52" s="46" t="inlineStr">
         <is>
-          <t>Visit Out</t>
+          <t>Clock In</t>
         </is>
       </c>
       <c r="D52" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Visit Out tanpa mengisi field mandatory</t>
+          <t>Melakukan Clock In di dalam jangkauan Attendance Spot</t>
         </is>
       </c>
       <c r="E52" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F52" s="46" t="inlineStr">
@@ -49291,16 +49297,16 @@
       </c>
       <c r="G52" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Visit Out
-2. Biarkan kosong pada field Catatan Kunjungan.
-3. Klik button Selesai Kunjungan.</t>
+          <t>1. Klik button Clock In.
+2. Mengupload foto dan mengisi field Keterangan.
+3. Klik button Rekam Kehadiran.</t>
         </is>
       </c>
       <c r="H52" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan halaman Selesai Kunjungan (Visit Out)
-2. Field Catatan Kunjungan tidak terisi.
-3. Sistem menampilkan pesan error validasi mandatory.</t>
+          <t>1. Berhasil mengklik button Clock In.
+2. Berhasil mengupload foto dan mengisi Keterangan.
+3. Berhasil melakukan Clock In dan status absensi tersimpan.</t>
         </is>
       </c>
       <c r="I52" s="49" t="n"/>
@@ -49326,7 +49332,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B53" s="46" t="inlineStr">
@@ -49341,7 +49347,7 @@
       </c>
       <c r="D53" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Clock In di dalam jangkauan Attendance Spot</t>
+          <t>Melakukan Clock In di luar jangkauan Attendance Spot</t>
         </is>
       </c>
       <c r="E53" s="46" t="inlineStr">
@@ -49365,7 +49371,7 @@
         <is>
           <t>1. Berhasil mengklik button Clock In.
 2. Berhasil mengupload foto dan mengisi Keterangan.
-3. Berhasil melakukan Clock In dan status absensi tersimpan.</t>
+3. Berhasil melakukan Clock In dan menunggu approval dari user Monitoring.</t>
         </is>
       </c>
       <c r="I53" s="49" t="n"/>
@@ -49391,7 +49397,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B54" s="46" t="inlineStr">
@@ -49401,12 +49407,12 @@
       </c>
       <c r="C54" s="46" t="inlineStr">
         <is>
-          <t>Clock In</t>
+          <t>Clock Out</t>
         </is>
       </c>
       <c r="D54" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Clock In di luar jangkauan Attendance Spot</t>
+          <t>Melakukan Clock Out di dalam jangkauan Attendance Spot</t>
         </is>
       </c>
       <c r="E54" s="46" t="inlineStr">
@@ -49421,16 +49427,16 @@
       </c>
       <c r="G54" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Clock In.
+          <t>1. Klik button Clock Out.
 2. Mengupload foto dan mengisi field Keterangan.
 3. Klik button Rekam Kehadiran.</t>
         </is>
       </c>
       <c r="H54" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengklik button Clock In.
+          <t>1. Berhasil mengklik button Clock Out.
 2. Berhasil mengupload foto dan mengisi Keterangan.
-3. Berhasil melakukan Clock In dan menunggu approval dari user Monitoring.</t>
+3. Berhasil melakukan Clock Out dan status absensi tersimpan.</t>
         </is>
       </c>
       <c r="I54" s="49" t="n"/>
@@ -49456,7 +49462,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B55" s="46" t="inlineStr">
@@ -49471,7 +49477,7 @@
       </c>
       <c r="D55" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Clock Out di dalam jangkauan Attendance Spot</t>
+          <t>Melakukan Clock Out di luar jangkauan Attendance Spot</t>
         </is>
       </c>
       <c r="E55" s="46" t="inlineStr">
@@ -49521,22 +49527,18 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B56" s="46" t="inlineStr">
         <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="C56" s="46" t="inlineStr">
-        <is>
-          <t>Clock Out</t>
-        </is>
-      </c>
+          <t>Log Absensi</t>
+        </is>
+      </c>
+      <c r="C56" s="47" t="n"/>
       <c r="D56" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Clock Out di luar jangkauan Attendance Spot</t>
+          <t>Membuka halaman Log Absensi</t>
         </is>
       </c>
       <c r="E56" s="46" t="inlineStr">
@@ -49551,16 +49553,14 @@
       </c>
       <c r="G56" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Clock Out.
-2. Mengupload foto dan mengisi field Keterangan.
-3. Klik button Rekam Kehadiran.</t>
+          <t>1. Klik menu Lainnya pada navigation bar.
+2. Klik menu Log Absensi.</t>
         </is>
       </c>
       <c r="H56" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengklik button Clock Out.
-2. Berhasil mengupload foto dan mengisi Keterangan.
-3. Berhasil melakukan Clock Out dan status absensi tersimpan.</t>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil membuka halaman Log Absensi.</t>
         </is>
       </c>
       <c r="I56" s="49" t="n"/>
@@ -49586,7 +49586,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B57" s="46" t="inlineStr">
@@ -49597,7 +49597,7 @@
       <c r="C57" s="47" t="n"/>
       <c r="D57" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Log Absensi</t>
+          <t>Menampilkan daftar data log absensi</t>
         </is>
       </c>
       <c r="E57" s="46" t="inlineStr">
@@ -49619,7 +49619,7 @@
       <c r="H57" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil membuka halaman Log Absensi.</t>
+2. Berhasil menampilkan daftar data log absensi beserta ringkasan Jam Kerja, Hadir, dan Terlambat.</t>
         </is>
       </c>
       <c r="I57" s="49" t="n"/>
@@ -49645,7 +49645,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B58" s="46" t="inlineStr">
@@ -49656,7 +49656,7 @@
       <c r="C58" s="47" t="n"/>
       <c r="D58" s="48" t="inlineStr">
         <is>
-          <t>Menampilkan daftar data log absensi</t>
+          <t>Melakukan filter data log absensi</t>
         </is>
       </c>
       <c r="E58" s="46" t="inlineStr">
@@ -49671,14 +49671,14 @@
       </c>
       <c r="G58" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu Lainnya pada navigation bar.
-2. Klik menu Log Absensi.</t>
+          <t>1. Pilih Tahun pada field Tahun.
+2. Pilih Bulan pada field Bulan.</t>
         </is>
       </c>
       <c r="H58" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan daftar data log absensi beserta ringkasan Jam Kerja, Hadir, dan Terlambat.</t>
+          <t>1. Berhasil memilih Tahun.
+2. Berhasil menampilkan daftar log absensi sesuai Bulan dan Tahun yang dipilih.</t>
         </is>
       </c>
       <c r="I58" s="49" t="n"/>
@@ -49704,7 +49704,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="B59" s="46" t="inlineStr">
@@ -49715,7 +49715,7 @@
       <c r="C59" s="47" t="n"/>
       <c r="D59" s="48" t="inlineStr">
         <is>
-          <t>Melakukan filter data log absensi</t>
+          <t>Melihat detail log absensi Clock In</t>
         </is>
       </c>
       <c r="E59" s="46" t="inlineStr">
@@ -49725,19 +49725,19 @@
       </c>
       <c r="F59" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G59" s="48" t="inlineStr">
         <is>
-          <t>1. Pilih Tahun pada field Tahun.
-2. Pilih Bulan pada field Bulan.</t>
+          <t>1. Klik salah satu item pada daftar log absensi.
+2. Klik tab Clock In.</t>
         </is>
       </c>
       <c r="H59" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil memilih Tahun.
-2. Berhasil menampilkan daftar log absensi sesuai Bulan dan Tahun yang dipilih.</t>
+          <t>1. Berhasil membuka halaman Log Absent Detail.
+2. Berhasil menampilkan informasi Clock In yang mencakup peta lokasi, tanggal, waktu Clock In, deskripsi, lokasi, dan akurasi.</t>
         </is>
       </c>
       <c r="I59" s="49" t="n"/>
@@ -49763,7 +49763,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="B60" s="46" t="inlineStr">
@@ -49774,7 +49774,7 @@
       <c r="C60" s="47" t="n"/>
       <c r="D60" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail log absensi Clock In</t>
+          <t>Melihat detail log absensi Clock Out</t>
         </is>
       </c>
       <c r="E60" s="46" t="inlineStr">
@@ -49790,13 +49790,13 @@
       <c r="G60" s="48" t="inlineStr">
         <is>
           <t>1. Klik salah satu item pada daftar log absensi.
-2. Klik tab Clock In.</t>
+2. Klik tab Clock Out.</t>
         </is>
       </c>
       <c r="H60" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil membuka halaman Log Absent Detail.
-2. Berhasil menampilkan informasi Clock In yang mencakup peta lokasi, tanggal, waktu Clock In, deskripsi, lokasi, dan akurasi.</t>
+2. Berhasil menampilkan detail log absensi Clock Out.</t>
         </is>
       </c>
       <c r="I60" s="49" t="n"/>
@@ -49822,18 +49822,18 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="B61" s="46" t="inlineStr">
         <is>
-          <t>Log Absensi</t>
+          <t>Personal Funnel</t>
         </is>
       </c>
       <c r="C61" s="47" t="n"/>
       <c r="D61" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail log absensi Clock Out</t>
+          <t>Membuka halaman Personal Funnel</t>
         </is>
       </c>
       <c r="E61" s="46" t="inlineStr">
@@ -49843,19 +49843,19 @@
       </c>
       <c r="F61" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G61" s="48" t="inlineStr">
         <is>
-          <t>1. Klik salah satu item pada daftar log absensi.
-2. Klik tab Clock Out.</t>
+          <t>1. Klik menu Laporan pada navigation bar.
+2. Klik menu Personal Funnel.</t>
         </is>
       </c>
       <c r="H61" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka halaman Log Absent Detail.
-2. Berhasil menampilkan detail log absensi Clock Out.</t>
+          <t>1. Berhasil membuka menu Laporan.
+2. Berhasil membuka halaman Personal Funnel.</t>
         </is>
       </c>
       <c r="I61" s="49" t="n"/>
@@ -49881,7 +49881,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="B62" s="46" t="inlineStr">
@@ -49892,7 +49892,7 @@
       <c r="C62" s="47" t="n"/>
       <c r="D62" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Personal Funnel</t>
+          <t>Melakukan filter data Personal Funnel</t>
         </is>
       </c>
       <c r="E62" s="46" t="inlineStr">
@@ -49907,14 +49907,22 @@
       </c>
       <c r="G62" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu Laporan pada navigation bar.
-2. Klik menu Personal Funnel.</t>
+          <t>1. Klik button Filter.
+2. Pilih Business Unit pada field Business Unit.
+3. Pilih Product pada field Product.
+4. Pilih Bulan pada field Bulan.
+5. Pilih Tahun pada field Tahun.
+6. Klik button Filter.</t>
         </is>
       </c>
       <c r="H62" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Laporan.
-2. Berhasil membuka halaman Personal Funnel.</t>
+          <t>1. Berhasil membuka panel Filter.
+2. Berhasil memilih Business Unit.
+3. Berhasil memilih Product.
+4. Berhasil memilih Bulan.
+5. Berhasil memilih Tahun.
+6. Berhasil menampilkan data grafik Personal Funnel sesuai filter yang dipilih.</t>
         </is>
       </c>
       <c r="I62" s="49" t="n"/>
@@ -49940,7 +49948,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="B63" s="46" t="inlineStr">
@@ -49951,37 +49959,31 @@
       <c r="C63" s="47" t="n"/>
       <c r="D63" s="48" t="inlineStr">
         <is>
-          <t>Melakukan filter data Personal Funnel</t>
+          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E63" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F63" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G63" s="48" t="inlineStr">
         <is>
           <t>1. Klik button Filter.
-2. Pilih Business Unit pada field Business Unit.
-3. Pilih Product pada field Product.
-4. Pilih Bulan pada field Bulan.
-5. Pilih Tahun pada field Tahun.
-6. Klik button Filter.</t>
+2. Mengosongkan field mandatory.
+3. Klik button Filter.</t>
         </is>
       </c>
       <c r="H63" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil membuka panel Filter.
-2. Berhasil memilih Business Unit.
-3. Berhasil memilih Product.
-4. Berhasil memilih Bulan.
-5. Berhasil memilih Tahun.
-6. Berhasil menampilkan data grafik Personal Funnel sesuai filter yang dipilih.</t>
+2. Berhasil mengosongkan field mandatory.
+3. Menampilkan pesan validasi field mandatory.</t>
         </is>
       </c>
       <c r="I63" s="49" t="n"/>
@@ -50007,7 +50009,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="B64" s="46" t="inlineStr">
@@ -50018,31 +50020,29 @@
       <c r="C64" s="47" t="n"/>
       <c r="D64" s="48" t="inlineStr">
         <is>
-          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
+          <t>Menampilkan grafik Prospek</t>
         </is>
       </c>
       <c r="E64" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F64" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G64" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Filter.
-2. Mengosongkan field mandatory.
-3. Klik button Filter.</t>
+          <t>1. Melakukan filter data Personal Funnel.
+2. Melihat grafik Prospek.</t>
         </is>
       </c>
       <c r="H64" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka panel Filter.
-2. Berhasil mengosongkan field mandatory.
-3. Menampilkan pesan validasi field mandatory.</t>
+          <t>1. Berhasil menerapkan filter.
+2. Berhasil menampilkan grafik batang Prospek dengan data Target dan Actual.</t>
         </is>
       </c>
       <c r="I64" s="49" t="n"/>
@@ -50068,7 +50068,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="B65" s="46" t="inlineStr">
@@ -50079,7 +50079,7 @@
       <c r="C65" s="47" t="n"/>
       <c r="D65" s="48" t="inlineStr">
         <is>
-          <t>Menampilkan grafik Prospek</t>
+          <t>Menampilkan grafik Call</t>
         </is>
       </c>
       <c r="E65" s="46" t="inlineStr">
@@ -50095,13 +50095,13 @@
       <c r="G65" s="48" t="inlineStr">
         <is>
           <t>1. Melakukan filter data Personal Funnel.
-2. Melihat grafik Prospek.</t>
+2. Melihat grafik Call.</t>
         </is>
       </c>
       <c r="H65" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menerapkan filter.
-2. Berhasil menampilkan grafik batang Prospek dengan data Target dan Actual.</t>
+2. Berhasil menampilkan grafik batang Call dengan data Target dan Actual.</t>
         </is>
       </c>
       <c r="I65" s="49" t="n"/>
@@ -50127,7 +50127,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="B66" s="46" t="inlineStr">
@@ -50138,7 +50138,7 @@
       <c r="C66" s="47" t="n"/>
       <c r="D66" s="48" t="inlineStr">
         <is>
-          <t>Menampilkan grafik Call</t>
+          <t>Menampilkan grafik Volume of Account</t>
         </is>
       </c>
       <c r="E66" s="46" t="inlineStr">
@@ -50154,13 +50154,13 @@
       <c r="G66" s="48" t="inlineStr">
         <is>
           <t>1. Melakukan filter data Personal Funnel.
-2. Melihat grafik Call.</t>
+2. Melihat grafik Volume of Account.</t>
         </is>
       </c>
       <c r="H66" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menerapkan filter.
-2. Berhasil menampilkan grafik batang Call dengan data Target dan Actual.</t>
+2. Berhasil menampilkan grafik batang Volume of Account dengan data Target dan Actual.</t>
         </is>
       </c>
       <c r="I66" s="49" t="n"/>
@@ -50186,7 +50186,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="B67" s="46" t="inlineStr">
@@ -50197,7 +50197,7 @@
       <c r="C67" s="47" t="n"/>
       <c r="D67" s="48" t="inlineStr">
         <is>
-          <t>Menampilkan grafik Volume of Account</t>
+          <t>Menampilkan grafik Pemberian Referral</t>
         </is>
       </c>
       <c r="E67" s="46" t="inlineStr">
@@ -50213,13 +50213,13 @@
       <c r="G67" s="48" t="inlineStr">
         <is>
           <t>1. Melakukan filter data Personal Funnel.
-2. Melihat grafik Volume of Account.</t>
+2. Melihat grafik Pemberian Referral.</t>
         </is>
       </c>
       <c r="H67" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menerapkan filter.
-2. Berhasil menampilkan grafik batang Volume of Account dengan data Target dan Actual.</t>
+2. Berhasil menampilkan grafik batang Pemberian Referral dengan data Target dan Actual.</t>
         </is>
       </c>
       <c r="I67" s="49" t="n"/>
@@ -50245,7 +50245,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="B68" s="46" t="inlineStr">
@@ -50256,7 +50256,7 @@
       <c r="C68" s="47" t="n"/>
       <c r="D68" s="48" t="inlineStr">
         <is>
-          <t>Menampilkan grafik Pemberian Referral</t>
+          <t>Menampilkan grafik Posisi</t>
         </is>
       </c>
       <c r="E68" s="46" t="inlineStr">
@@ -50272,13 +50272,13 @@
       <c r="G68" s="48" t="inlineStr">
         <is>
           <t>1. Melakukan filter data Personal Funnel.
-2. Melihat grafik Pemberian Referral.</t>
+2. Melihat grafik Posisi.</t>
         </is>
       </c>
       <c r="H68" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menerapkan filter.
-2. Berhasil menampilkan grafik batang Pemberian Referral dengan data Target dan Actual.</t>
+2. Berhasil menampilkan grafik batang Posisi dengan data Target dan Actual.</t>
         </is>
       </c>
       <c r="I68" s="49" t="n"/>
@@ -50304,7 +50304,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="B69" s="46" t="inlineStr">
@@ -50315,7 +50315,7 @@
       <c r="C69" s="47" t="n"/>
       <c r="D69" s="48" t="inlineStr">
         <is>
-          <t>Menampilkan grafik Posisi</t>
+          <t>Menampilkan grafik NOA Open Account</t>
         </is>
       </c>
       <c r="E69" s="46" t="inlineStr">
@@ -50331,13 +50331,13 @@
       <c r="G69" s="48" t="inlineStr">
         <is>
           <t>1. Melakukan filter data Personal Funnel.
-2. Melihat grafik Posisi.</t>
+2. Melihat grafik NOA Open Account.</t>
         </is>
       </c>
       <c r="H69" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menerapkan filter.
-2. Berhasil menampilkan grafik batang Posisi dengan data Target dan Actual.</t>
+2. Berhasil menampilkan grafik batang NOA Open Account dengan data Target dan Actual.</t>
         </is>
       </c>
       <c r="I69" s="49" t="n"/>
@@ -50363,7 +50363,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="B70" s="46" t="inlineStr">
@@ -50374,7 +50374,7 @@
       <c r="C70" s="47" t="n"/>
       <c r="D70" s="48" t="inlineStr">
         <is>
-          <t>Menampilkan grafik NOA Open Account</t>
+          <t>Menampilkan grafik NOA Top Up</t>
         </is>
       </c>
       <c r="E70" s="46" t="inlineStr">
@@ -50390,13 +50390,13 @@
       <c r="G70" s="48" t="inlineStr">
         <is>
           <t>1. Melakukan filter data Personal Funnel.
-2. Melihat grafik NOA Open Account.</t>
+2. Melihat grafik NOA Top Up.</t>
         </is>
       </c>
       <c r="H70" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menerapkan filter.
-2. Berhasil menampilkan grafik batang NOA Open Account dengan data Target dan Actual.</t>
+2. Berhasil menampilkan grafik batang NOA Top Up dengan data Target dan Actual.</t>
         </is>
       </c>
       <c r="I70" s="49" t="n"/>
@@ -50422,7 +50422,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="B71" s="46" t="inlineStr">
@@ -50433,7 +50433,7 @@
       <c r="C71" s="47" t="n"/>
       <c r="D71" s="48" t="inlineStr">
         <is>
-          <t>Menampilkan grafik NOA Top Up</t>
+          <t>Melihat detail tabel Prospek</t>
         </is>
       </c>
       <c r="E71" s="46" t="inlineStr">
@@ -50443,19 +50443,19 @@
       </c>
       <c r="F71" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G71" s="48" t="inlineStr">
         <is>
           <t>1. Melakukan filter data Personal Funnel.
-2. Melihat grafik NOA Top Up.</t>
+2. Klik icon tabel pada grafik Prospek.</t>
         </is>
       </c>
       <c r="H71" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menerapkan filter.
-2. Berhasil menampilkan grafik batang NOA Top Up dengan data Target dan Actual.</t>
+2. Berhasil membuka halaman detail tabel Prospek yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
         </is>
       </c>
       <c r="I71" s="49" t="n"/>
@@ -50481,7 +50481,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="B72" s="46" t="inlineStr">
@@ -50492,7 +50492,7 @@
       <c r="C72" s="47" t="n"/>
       <c r="D72" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail tabel Prospek</t>
+          <t>Melihat detail tabel Call</t>
         </is>
       </c>
       <c r="E72" s="46" t="inlineStr">
@@ -50508,13 +50508,13 @@
       <c r="G72" s="48" t="inlineStr">
         <is>
           <t>1. Melakukan filter data Personal Funnel.
-2. Klik icon tabel pada grafik Prospek.</t>
+2. Klik icon tabel pada grafik Call.</t>
         </is>
       </c>
       <c r="H72" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menerapkan filter.
-2. Berhasil membuka halaman detail tabel Prospek yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
+2. Berhasil membuka halaman detail tabel Call yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
         </is>
       </c>
       <c r="I72" s="49" t="n"/>
@@ -50540,7 +50540,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="B73" s="46" t="inlineStr">
@@ -50551,7 +50551,7 @@
       <c r="C73" s="47" t="n"/>
       <c r="D73" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail tabel Call</t>
+          <t>Melihat detail tabel Volume of Account</t>
         </is>
       </c>
       <c r="E73" s="46" t="inlineStr">
@@ -50567,13 +50567,13 @@
       <c r="G73" s="48" t="inlineStr">
         <is>
           <t>1. Melakukan filter data Personal Funnel.
-2. Klik icon tabel pada grafik Call.</t>
+2. Klik icon tabel pada grafik Volume of Account.</t>
         </is>
       </c>
       <c r="H73" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menerapkan filter.
-2. Berhasil membuka halaman detail tabel Call yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
+2. Berhasil membuka halaman detail tabel Volume of Account yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
         </is>
       </c>
       <c r="I73" s="49" t="n"/>
@@ -50599,7 +50599,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="B74" s="46" t="inlineStr">
@@ -50610,7 +50610,7 @@
       <c r="C74" s="47" t="n"/>
       <c r="D74" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail tabel Volume of Account</t>
+          <t>Melihat detail tabel Pemberian Referral</t>
         </is>
       </c>
       <c r="E74" s="46" t="inlineStr">
@@ -50626,13 +50626,13 @@
       <c r="G74" s="48" t="inlineStr">
         <is>
           <t>1. Melakukan filter data Personal Funnel.
-2. Klik icon tabel pada grafik Volume of Account.</t>
+2. Klik icon tabel pada grafik Pemberian Referral.</t>
         </is>
       </c>
       <c r="H74" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menerapkan filter.
-2. Berhasil membuka halaman detail tabel Volume of Account yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
+2. Berhasil membuka halaman detail tabel Pemberian Referral yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
         </is>
       </c>
       <c r="I74" s="49" t="n"/>
@@ -50658,7 +50658,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="B75" s="46" t="inlineStr">
@@ -50669,7 +50669,7 @@
       <c r="C75" s="47" t="n"/>
       <c r="D75" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail tabel Pemberian Referral</t>
+          <t>Melihat detail tabel Posisi</t>
         </is>
       </c>
       <c r="E75" s="46" t="inlineStr">
@@ -50685,13 +50685,13 @@
       <c r="G75" s="48" t="inlineStr">
         <is>
           <t>1. Melakukan filter data Personal Funnel.
-2. Klik icon tabel pada grafik Pemberian Referral.</t>
+2. Klik icon tabel pada grafik Posisi.</t>
         </is>
       </c>
       <c r="H75" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menerapkan filter.
-2. Berhasil membuka halaman detail tabel Pemberian Referral yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
+2. Berhasil membuka halaman detail tabel Posisi yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
         </is>
       </c>
       <c r="I75" s="49" t="n"/>
@@ -50717,7 +50717,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="B76" s="46" t="inlineStr">
@@ -50728,7 +50728,7 @@
       <c r="C76" s="47" t="n"/>
       <c r="D76" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail tabel Posisi</t>
+          <t>Melihat detail tabel NOA Open Account</t>
         </is>
       </c>
       <c r="E76" s="46" t="inlineStr">
@@ -50744,13 +50744,13 @@
       <c r="G76" s="48" t="inlineStr">
         <is>
           <t>1. Melakukan filter data Personal Funnel.
-2. Klik icon tabel pada grafik Posisi.</t>
+2. Klik icon tabel pada grafik NOA Open Account.</t>
         </is>
       </c>
       <c r="H76" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menerapkan filter.
-2. Berhasil membuka halaman detail tabel Posisi yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
+2. Berhasil membuka halaman detail tabel NOA Open Account yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
         </is>
       </c>
       <c r="I76" s="49" t="n"/>
@@ -50776,7 +50776,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="B77" s="46" t="inlineStr">
@@ -50787,7 +50787,7 @@
       <c r="C77" s="47" t="n"/>
       <c r="D77" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail tabel NOA Open Account</t>
+          <t>Melihat detail tabel NOA Top Up</t>
         </is>
       </c>
       <c r="E77" s="46" t="inlineStr">
@@ -50803,13 +50803,13 @@
       <c r="G77" s="48" t="inlineStr">
         <is>
           <t>1. Melakukan filter data Personal Funnel.
-2. Klik icon tabel pada grafik NOA Open Account.</t>
+2. Klik icon tabel pada grafik NOA Top Up.</t>
         </is>
       </c>
       <c r="H77" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menerapkan filter.
-2. Berhasil membuka halaman detail tabel NOA Open Account yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
+2. Berhasil membuka halaman detail tabel NOA Top Up yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
         </is>
       </c>
       <c r="I77" s="49" t="n"/>
@@ -50835,18 +50835,18 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B78" s="46" t="inlineStr">
         <is>
-          <t>Personal Funnel</t>
+          <t>Cuti &amp; Izin</t>
         </is>
       </c>
       <c r="C78" s="47" t="n"/>
       <c r="D78" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail tabel NOA Top Up</t>
+          <t>Membuka halaman Cuti &amp; Izin</t>
         </is>
       </c>
       <c r="E78" s="46" t="inlineStr">
@@ -50856,19 +50856,19 @@
       </c>
       <c r="F78" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G78" s="48" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data Personal Funnel.
-2. Klik icon tabel pada grafik NOA Top Up.</t>
+          <t>1. Klik menu Lainnya pada navigation bar.
+2. Klik menu Cuti &amp; Izin.</t>
         </is>
       </c>
       <c r="H78" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menerapkan filter.
-2. Berhasil membuka halaman detail tabel NOA Top Up yang menampilkan data Target (NTB &amp; ETB) dan Actual (NTB &amp; ETB).</t>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil membuka halaman Cuti &amp; Izin.</t>
         </is>
       </c>
       <c r="I78" s="49" t="n"/>
@@ -50894,7 +50894,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B79" s="46" t="inlineStr">
@@ -50905,7 +50905,7 @@
       <c r="C79" s="47" t="n"/>
       <c r="D79" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Cuti &amp; Izin</t>
+          <t>Menampilkan daftar data pengajuan cuti</t>
         </is>
       </c>
       <c r="E79" s="46" t="inlineStr">
@@ -50927,7 +50927,7 @@
       <c r="H79" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil membuka halaman Cuti &amp; Izin.</t>
+2. Berhasil menampilkan daftar data pengajuan cuti.</t>
         </is>
       </c>
       <c r="I79" s="49" t="n"/>
@@ -50953,7 +50953,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="B80" s="46" t="inlineStr">
@@ -50964,7 +50964,7 @@
       <c r="C80" s="47" t="n"/>
       <c r="D80" s="48" t="inlineStr">
         <is>
-          <t>Menampilkan daftar data pengajuan cuti</t>
+          <t>Mencari data pengajuan cuti dengan keyword valid</t>
         </is>
       </c>
       <c r="E80" s="46" t="inlineStr">
@@ -50979,14 +50979,14 @@
       </c>
       <c r="G80" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu Lainnya pada navigation bar.
-2. Klik menu Cuti &amp; Izin.</t>
+          <t>1. Masukkan keyword valid pada field Search.
+2. Klik button Search.</t>
         </is>
       </c>
       <c r="H80" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan daftar data pengajuan cuti.</t>
+          <t>1. Berhasil mengisi field Search.
+2. Berhasil menampilkan data pengajuan cuti sesuai keyword yang dicari.</t>
         </is>
       </c>
       <c r="I80" s="49" t="n"/>
@@ -51012,7 +51012,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="B81" s="46" t="inlineStr">
@@ -51023,12 +51023,12 @@
       <c r="C81" s="47" t="n"/>
       <c r="D81" s="48" t="inlineStr">
         <is>
-          <t>Mencari data pengajuan cuti dengan keyword valid</t>
+          <t>Mencari data pengajuan cuti dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E81" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F81" s="46" t="inlineStr">
@@ -51038,14 +51038,14 @@
       </c>
       <c r="G81" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan keyword valid pada field Search.
+          <t>1. Masukkan keyword tidak valid pada field Search.
 2. Klik button Search.</t>
         </is>
       </c>
       <c r="H81" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field Search.
-2. Berhasil menampilkan data pengajuan cuti sesuai keyword yang dicari.</t>
+2. Menampilkan pesan data tidak ditemukan.</t>
         </is>
       </c>
       <c r="I81" s="49" t="n"/>
@@ -51071,7 +51071,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="B82" s="46" t="inlineStr">
@@ -51082,29 +51082,33 @@
       <c r="C82" s="47" t="n"/>
       <c r="D82" s="48" t="inlineStr">
         <is>
-          <t>Mencari data pengajuan cuti dengan keyword tidak valid</t>
+          <t>Melakukan filter data pengajuan cuti</t>
         </is>
       </c>
       <c r="E82" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F82" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G82" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan keyword tidak valid pada field Search.
-2. Klik button Search.</t>
+          <t>1. Klik icon filter.
+2. Pilih rentang tanggal pada field Pilih Rentang Tanggal.
+3. Pilih urutan ASC atau DESC pada Urutkan Berdasarkan.
+4. Klik button Apply.</t>
         </is>
       </c>
       <c r="H82" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi field Search.
-2. Menampilkan pesan data tidak ditemukan.</t>
+          <t>1. Berhasil membuka panel filter.
+2. Berhasil memilih rentang tanggal.
+3. Berhasil memilih urutan.
+4. Berhasil menampilkan data pengajuan cuti sesuai filter yang dipilih.</t>
         </is>
       </c>
       <c r="I82" s="49" t="n"/>
@@ -51130,7 +51134,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="B83" s="46" t="inlineStr">
@@ -51141,7 +51145,7 @@
       <c r="C83" s="47" t="n"/>
       <c r="D83" s="48" t="inlineStr">
         <is>
-          <t>Melakukan filter data pengajuan cuti</t>
+          <t>Menampilkan data pengajuan cuti berdasarkan jenis cuti</t>
         </is>
       </c>
       <c r="E83" s="46" t="inlineStr">
@@ -51156,18 +51160,12 @@
       </c>
       <c r="G83" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon filter.
-2. Pilih rentang tanggal pada field Pilih Rentang Tanggal.
-3. Pilih urutan ASC atau DESC pada Urutkan Berdasarkan.
-4. Klik button Apply.</t>
+          <t>1. Klik salah satu card jenis cuti (Semua, Cuti Melahirkan, atau Cuti Menikah).</t>
         </is>
       </c>
       <c r="H83" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka panel filter.
-2. Berhasil memilih rentang tanggal.
-3. Berhasil memilih urutan.
-4. Berhasil menampilkan data pengajuan cuti sesuai filter yang dipilih.</t>
+          <t>1. Berhasil menampilkan data pengajuan cuti sesuai jenis cuti yang dipilih.</t>
         </is>
       </c>
       <c r="I83" s="49" t="n"/>
@@ -51193,7 +51191,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="B84" s="46" t="inlineStr">
@@ -51204,7 +51202,7 @@
       <c r="C84" s="47" t="n"/>
       <c r="D84" s="48" t="inlineStr">
         <is>
-          <t>Menampilkan data pengajuan cuti berdasarkan jenis cuti</t>
+          <t>Menampilkan data pengajuan cuti berdasarkan status</t>
         </is>
       </c>
       <c r="E84" s="46" t="inlineStr">
@@ -51219,12 +51217,12 @@
       </c>
       <c r="G84" s="48" t="inlineStr">
         <is>
-          <t>1. Klik salah satu card jenis cuti (Semua, Cuti Melahirkan, atau Cuti Menikah).</t>
+          <t>1. Klik salah satu tab status (Semua, Ditolak, Pending, atau Disetujui).</t>
         </is>
       </c>
       <c r="H84" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data pengajuan cuti sesuai jenis cuti yang dipilih.</t>
+          <t>1. Berhasil menampilkan data pengajuan cuti sesuai status yang dipilih.</t>
         </is>
       </c>
       <c r="I84" s="49" t="n"/>
@@ -51250,7 +51248,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="B85" s="46" t="inlineStr">
@@ -51261,7 +51259,7 @@
       <c r="C85" s="47" t="n"/>
       <c r="D85" s="48" t="inlineStr">
         <is>
-          <t>Menampilkan data pengajuan cuti berdasarkan status</t>
+          <t>Mengajukan cuti</t>
         </is>
       </c>
       <c r="E85" s="46" t="inlineStr">
@@ -51271,17 +51269,21 @@
       </c>
       <c r="F85" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G85" s="48" t="inlineStr">
         <is>
-          <t>1. Klik salah satu tab status (Semua, Ditolak, Pending, atau Disetujui).</t>
+          <t>1. Klik button Ajukan Cuti.
+2. Mengisi semua field mandatory.
+3. Klik button Ajukan Cuti.</t>
         </is>
       </c>
       <c r="H85" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data pengajuan cuti sesuai status yang dipilih.</t>
+          <t>1. Berhasil membuka halaman Ajukan Cuti.
+2. Berhasil mengisi semua field mandatory.
+3. Berhasil mengajukan cuti.</t>
         </is>
       </c>
       <c r="I85" s="49" t="n"/>
@@ -51307,7 +51309,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="B86" s="46" t="inlineStr">
@@ -51318,31 +51320,31 @@
       <c r="C86" s="47" t="n"/>
       <c r="D86" s="48" t="inlineStr">
         <is>
-          <t>Mengajukan cuti</t>
+          <t>Mengajukan cuti tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E86" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F86" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G86" s="48" t="inlineStr">
         <is>
           <t>1. Klik button Ajukan Cuti.
-2. Mengisi semua field mandatory.
+2. Mengosongkan field mandatory.
 3. Klik button Ajukan Cuti.</t>
         </is>
       </c>
       <c r="H86" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil membuka halaman Ajukan Cuti.
-2. Berhasil mengisi semua field mandatory.
-3. Berhasil mengajukan cuti.</t>
+2. Berhasil mengosongkan field mandatory.
+3. Menampilkan pesan validasi field mandatory.</t>
         </is>
       </c>
       <c r="I86" s="49" t="n"/>
@@ -51368,42 +51370,44 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="B87" s="46" t="inlineStr">
         <is>
-          <t>Cuti &amp; Izin</t>
-        </is>
-      </c>
-      <c r="C87" s="47" t="n"/>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C87" s="46" t="inlineStr">
+        <is>
+          <t>Aktifitas Prospek</t>
+        </is>
+      </c>
       <c r="D87" s="48" t="inlineStr">
         <is>
-          <t>Mengajukan cuti tanpa mengisi field mandatory</t>
+          <t>Membuka halaman Aktifitas Prospek</t>
         </is>
       </c>
       <c r="E87" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F87" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G87" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Ajukan Cuti.
-2. Mengosongkan field mandatory.
-3. Klik button Ajukan Cuti.</t>
+          <t>1. Buka menu Lainnya.
+2. Klik menu Aktifitas Prospek.</t>
         </is>
       </c>
       <c r="H87" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka halaman Ajukan Cuti.
-2. Berhasil mengosongkan field mandatory.
-3. Menampilkan pesan validasi field mandatory.</t>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman Aktifitas Prospek.</t>
         </is>
       </c>
       <c r="I87" s="49" t="n"/>
@@ -51429,7 +51433,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="B88" s="46" t="inlineStr">
@@ -51444,7 +51448,7 @@
       </c>
       <c r="D88" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Aktifitas Prospek</t>
+          <t>Mencari prospek menggunakan Search Bar</t>
         </is>
       </c>
       <c r="E88" s="46" t="inlineStr">
@@ -51459,14 +51463,12 @@
       </c>
       <c r="G88" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Aktifitas Prospek.</t>
+          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
         </is>
       </c>
       <c r="H88" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Aktifitas Prospek.</t>
+          <t>1. Berhasil menampilkan data prospek yang sesuai dengan kata kunci pencarian.</t>
         </is>
       </c>
       <c r="I88" s="49" t="n"/>
@@ -51492,7 +51494,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="B89" s="46" t="inlineStr">
@@ -51507,27 +51509,27 @@
       </c>
       <c r="D89" s="48" t="inlineStr">
         <is>
-          <t>Mencari prospek menggunakan Search Bar</t>
+          <t>Mencari prospek dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E89" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F89" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G89" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
         </is>
       </c>
       <c r="H89" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data prospek yang sesuai dengan kata kunci pencarian.</t>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
       <c r="I89" s="49" t="n"/>
@@ -51553,7 +51555,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="B90" s="46" t="inlineStr">
@@ -51568,27 +51570,31 @@
       </c>
       <c r="D90" s="48" t="inlineStr">
         <is>
-          <t>Mencari prospek dengan keyword tidak valid</t>
+          <t>Melakukan filter data prospek</t>
         </is>
       </c>
       <c r="E90" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F90" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G90" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+          <t>1. Klik button Filter di halaman Aktifitas Prospek.
+2. Pilih kriteria filter pada form Filter.
+3. Klik button Simpan.</t>
         </is>
       </c>
       <c r="H90" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+          <t>1. Berhasil membuka form Filter.
+2. Berhasil memilih kriteria filter.
+3. Berhasil menampilkan daftar prospek yang sesuai dengan kriteria filter.</t>
         </is>
       </c>
       <c r="I90" s="49" t="n"/>
@@ -51614,7 +51620,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="B91" s="46" t="inlineStr">
@@ -51629,7 +51635,7 @@
       </c>
       <c r="D91" s="48" t="inlineStr">
         <is>
-          <t>Melakukan filter data prospek</t>
+          <t>Melihat Detail Prospek</t>
         </is>
       </c>
       <c r="E91" s="46" t="inlineStr">
@@ -51644,16 +51650,14 @@
       </c>
       <c r="G91" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Filter di halaman Aktifitas Prospek.
-2. Pilih kriteria filter pada form Filter.
-3. Klik button Simpan.</t>
+          <t>1. Klik menu titik tiga pada salah satu card prospek.
+2. Pilih Detail Prospek.</t>
         </is>
       </c>
       <c r="H91" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka form Filter.
-2. Berhasil memilih kriteria filter.
-3. Berhasil menampilkan daftar prospek yang sesuai dengan kriteria filter.</t>
+          <t>1. Berhasil menampilkan menu pilihan.
+2. Berhasil menampilkan detail data prospek.</t>
         </is>
       </c>
       <c r="I91" s="49" t="n"/>
@@ -51679,7 +51683,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="B92" s="46" t="inlineStr">
@@ -51694,7 +51698,7 @@
       </c>
       <c r="D92" s="48" t="inlineStr">
         <is>
-          <t>Melihat Detail Prospek</t>
+          <t>Melihat Riwayat Prospek</t>
         </is>
       </c>
       <c r="E92" s="46" t="inlineStr">
@@ -51710,13 +51714,13 @@
       <c r="G92" s="48" t="inlineStr">
         <is>
           <t>1. Klik menu titik tiga pada salah satu card prospek.
-2. Pilih Detail Prospek.</t>
+2. Pilih Riwayat.</t>
         </is>
       </c>
       <c r="H92" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan menu pilihan.
-2. Berhasil menampilkan detail data prospek.</t>
+2. Berhasil membuka halaman Riwayat dan menampilkan daftar log riwayat.</t>
         </is>
       </c>
       <c r="I92" s="49" t="n"/>
@@ -51742,7 +51746,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="B93" s="46" t="inlineStr">
@@ -51757,7 +51761,7 @@
       </c>
       <c r="D93" s="48" t="inlineStr">
         <is>
-          <t>Melihat Riwayat Prospek</t>
+          <t>Mencari data pada halaman Riwayat</t>
         </is>
       </c>
       <c r="E93" s="46" t="inlineStr">
@@ -51767,19 +51771,17 @@
       </c>
       <c r="F93" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G93" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu titik tiga pada salah satu card prospek.
-2. Pilih Riwayat.</t>
+          <t>1. Masukkan kata kunci pada Search Bar global.</t>
         </is>
       </c>
       <c r="H93" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan menu pilihan.
-2. Berhasil membuka halaman Riwayat dan menampilkan daftar log riwayat.</t>
+          <t>1. Berhasil memfilter data riwayat sesuai kata kunci pencarian.</t>
         </is>
       </c>
       <c r="I93" s="49" t="n"/>
@@ -51805,7 +51807,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="B94" s="46" t="inlineStr">
@@ -51820,12 +51822,12 @@
       </c>
       <c r="D94" s="48" t="inlineStr">
         <is>
-          <t>Mencari data pada halaman Riwayat</t>
+          <t>Mencari data dengan keyword tidak valid pada halaman Riwayat</t>
         </is>
       </c>
       <c r="E94" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F94" s="46" t="inlineStr">
@@ -51835,12 +51837,12 @@
       </c>
       <c r="G94" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan kata kunci pada Search Bar global.</t>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
         </is>
       </c>
       <c r="H94" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil memfilter data riwayat sesuai kata kunci pencarian.</t>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
       <c r="I94" s="49" t="n"/>
@@ -51866,7 +51868,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="B95" s="46" t="inlineStr">
@@ -51881,27 +51883,27 @@
       </c>
       <c r="D95" s="48" t="inlineStr">
         <is>
-          <t>Mencari data dengan keyword tidak valid pada halaman Riwayat</t>
+          <t>Membuka form Input Aktifitas</t>
         </is>
       </c>
       <c r="E95" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F95" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G95" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+          <t>1. Klik button Aktifitas pada prospek yang berstatus aktif (belum closing).</t>
         </is>
       </c>
       <c r="H95" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+          <t>1. Berhasil membuka halaman Aktifitas Marketing dan menampilkan tab Prospek, Call, Visit, dan NOA Open Account.</t>
         </is>
       </c>
       <c r="I95" s="49" t="n"/>
@@ -51927,7 +51929,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="B96" s="46" t="inlineStr">
@@ -51942,7 +51944,7 @@
       </c>
       <c r="D96" s="48" t="inlineStr">
         <is>
-          <t>Membuka form Input Aktifitas</t>
+          <t>Membuka tab Prospek pada halaman Aktifitas Marketing</t>
         </is>
       </c>
       <c r="E96" s="46" t="inlineStr">
@@ -51952,17 +51954,17 @@
       </c>
       <c r="F96" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G96" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Aktifitas pada prospek yang berstatus aktif (belum closing).</t>
+          <t>1. Klik tab Prospek.</t>
         </is>
       </c>
       <c r="H96" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka halaman Aktifitas Marketing dan menampilkan tab Prospek, Call, Visit, dan NOA Open Account.</t>
+          <t>1. Berhasil berpindah ke tab Prospek dan menampilkan form informasi prospek.</t>
         </is>
       </c>
       <c r="I96" s="49" t="n"/>
@@ -51988,7 +51990,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="B97" s="46" t="inlineStr">
@@ -52003,7 +52005,7 @@
       </c>
       <c r="D97" s="48" t="inlineStr">
         <is>
-          <t>Membuka tab Prospek pada halaman Aktifitas Marketing</t>
+          <t>Mengedit data pada tab Prospek</t>
         </is>
       </c>
       <c r="E97" s="46" t="inlineStr">
@@ -52018,12 +52020,16 @@
       </c>
       <c r="G97" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Prospek.</t>
+          <t>1. Ubah data pada form informasi prospek.
+2. Klik button Edit.
+3. Klik button Next.</t>
         </is>
       </c>
       <c r="H97" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil berpindah ke tab Prospek dan menampilkan form informasi prospek.</t>
+          <t>1. Berhasil mengubah data pada form.
+2. Berhasil mengaktifkan mode edit form.
+3. Berhasil menyimpan perubahan dan melanjutkan ke tahap berikutnya.</t>
         </is>
       </c>
       <c r="I97" s="49" t="n"/>
@@ -52049,7 +52055,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="B98" s="46" t="inlineStr">
@@ -52064,7 +52070,7 @@
       </c>
       <c r="D98" s="48" t="inlineStr">
         <is>
-          <t>Mengedit data pada tab Prospek</t>
+          <t>Membuka tab Call pada halaman Aktifitas Marketing</t>
         </is>
       </c>
       <c r="E98" s="46" t="inlineStr">
@@ -52079,16 +52085,12 @@
       </c>
       <c r="G98" s="48" t="inlineStr">
         <is>
-          <t>1. Ubah data pada form informasi prospek.
-2. Klik button Edit.
-3. Klik button Next.</t>
+          <t>1. Klik tab Call.</t>
         </is>
       </c>
       <c r="H98" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengubah data pada form.
-2. Berhasil mengaktifkan mode edit form.
-3. Berhasil menyimpan perubahan dan melanjutkan ke tahap berikutnya.</t>
+          <t>1. Berhasil berpindah ke tab Call dan menampilkan form input Call serta Log Staging Call.</t>
         </is>
       </c>
       <c r="I98" s="49" t="n"/>
@@ -52114,7 +52116,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>10.13</t>
         </is>
       </c>
       <c r="B99" s="46" t="inlineStr">
@@ -52129,7 +52131,7 @@
       </c>
       <c r="D99" s="48" t="inlineStr">
         <is>
-          <t>Membuka tab Call pada halaman Aktifitas Marketing</t>
+          <t>Melakukan panggilan langsung melalui tombol Call</t>
         </is>
       </c>
       <c r="E99" s="46" t="inlineStr">
@@ -52144,12 +52146,12 @@
       </c>
       <c r="G99" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Call.</t>
+          <t>1. Klik button Call di samping nomor handphone.</t>
         </is>
       </c>
       <c r="H99" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil berpindah ke tab Call dan menampilkan form input Call serta Log Staging Call.</t>
+          <t>1. Berhasil mengarahkan ke aplikasi telepon bawaan perangkat (dialer).</t>
         </is>
       </c>
       <c r="I99" s="49" t="n"/>
@@ -52175,7 +52177,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="B100" s="46" t="inlineStr">
@@ -52190,7 +52192,7 @@
       </c>
       <c r="D100" s="48" t="inlineStr">
         <is>
-          <t>Melakukan panggilan langsung melalui tombol Call</t>
+          <t>Menyimpan log Call dengan data valid</t>
         </is>
       </c>
       <c r="E100" s="46" t="inlineStr">
@@ -52200,17 +52202,19 @@
       </c>
       <c r="F100" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G100" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Call di samping nomor handphone.</t>
+          <t>1. Isi field Status Call dan Keterangan dengan data valid.
+2. Klik button Simpan.</t>
         </is>
       </c>
       <c r="H100" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengarahkan ke aplikasi telepon bawaan perangkat (dialer).</t>
+          <t>1. Berhasil mengisi field Status Call dan Keterangan.
+2. Berhasil menyimpan aktifitas Call dan menambahkannya ke Log Staging Call.</t>
         </is>
       </c>
       <c r="I100" s="49" t="n"/>
@@ -52236,7 +52240,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="B101" s="46" t="inlineStr">
@@ -52251,29 +52255,29 @@
       </c>
       <c r="D101" s="48" t="inlineStr">
         <is>
-          <t>Menyimpan log Call dengan data valid</t>
+          <t>Menyimpan log Call tanpa field mandatory</t>
         </is>
       </c>
       <c r="E101" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F101" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G101" s="48" t="inlineStr">
         <is>
-          <t>1. Isi field Status Call dan Keterangan dengan data valid.
+          <t>1. Mengosongkan field Status Call dan Keterangan.
 2. Klik button Simpan.</t>
         </is>
       </c>
       <c r="H101" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi field Status Call dan Keterangan.
-2. Berhasil menyimpan aktifitas Call dan menambahkannya ke Log Staging Call.</t>
+          <t>1. Berhasil mengosongkan field mandatory.
+2. Menampilkan pesan validasi bahwa field Status Call dan Keterangan wajib diisi.</t>
         </is>
       </c>
       <c r="I101" s="49" t="n"/>
@@ -52299,7 +52303,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="B102" s="46" t="inlineStr">
@@ -52314,12 +52318,12 @@
       </c>
       <c r="D102" s="48" t="inlineStr">
         <is>
-          <t>Menyimpan log Call tanpa field mandatory</t>
+          <t>Membuka tab Visit pada halaman Aktifitas Marketing</t>
         </is>
       </c>
       <c r="E102" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F102" s="46" t="inlineStr">
@@ -52329,14 +52333,12 @@
       </c>
       <c r="G102" s="48" t="inlineStr">
         <is>
-          <t>1. Mengosongkan field Status Call dan Keterangan.
-2. Klik button Simpan.</t>
+          <t>1. Klik tab Visit.</t>
         </is>
       </c>
       <c r="H102" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan field mandatory.
-2. Menampilkan pesan validasi bahwa field Status Call dan Keterangan wajib diisi.</t>
+          <t>1. Berhasil berpindah ke tab Visit dan menampilkan button Visit In serta Log Staging Visit.</t>
         </is>
       </c>
       <c r="I102" s="49" t="n"/>
@@ -52362,7 +52364,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="B103" s="46" t="inlineStr">
@@ -52377,7 +52379,7 @@
       </c>
       <c r="D103" s="48" t="inlineStr">
         <is>
-          <t>Membuka tab Visit pada halaman Aktifitas Marketing</t>
+          <t>Melakukan Visit In</t>
         </is>
       </c>
       <c r="E103" s="46" t="inlineStr">
@@ -52387,17 +52389,17 @@
       </c>
       <c r="F103" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G103" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Visit.</t>
+          <t>1. Klik button Visit In.</t>
         </is>
       </c>
       <c r="H103" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil berpindah ke tab Visit dan menampilkan button Visit In serta Log Staging Visit.</t>
+          <t>1. Berhasil mengarahkan ke halaman Kunjungan dan menampilkan pop up pilihan tipe Visit.</t>
         </is>
       </c>
       <c r="I103" s="49" t="n"/>
@@ -52423,7 +52425,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="B104" s="46" t="inlineStr">
@@ -52438,7 +52440,7 @@
       </c>
       <c r="D104" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Visit In</t>
+          <t>Membuka tab NOA Open Account pada halaman Aktifitas Marketing</t>
         </is>
       </c>
       <c r="E104" s="46" t="inlineStr">
@@ -52448,17 +52450,17 @@
       </c>
       <c r="F104" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G104" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Visit In.</t>
+          <t>1. Klik tab NOA Open Account.</t>
         </is>
       </c>
       <c r="H104" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengarahkan ke halaman Kunjungan dan menampilkan pop up pilihan tipe Visit.</t>
+          <t>1. Berhasil berpindah ke tab NOA Open Account dan menampilkan form NOA Open Account.</t>
         </is>
       </c>
       <c r="I104" s="49" t="n"/>
@@ -52484,7 +52486,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="B105" s="46" t="inlineStr">
@@ -52499,7 +52501,7 @@
       </c>
       <c r="D105" s="48" t="inlineStr">
         <is>
-          <t>Membuka tab NOA Open Account pada halaman Aktifitas Marketing</t>
+          <t>Melakukan Submit NOA Open Account dengan data valid</t>
         </is>
       </c>
       <c r="E105" s="46" t="inlineStr">
@@ -52509,17 +52511,19 @@
       </c>
       <c r="F105" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G105" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab NOA Open Account.</t>
+          <t>1. Mengisi seluruh field pada form NOA Open Account dengan data valid.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H105" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil berpindah ke tab NOA Open Account dan menampilkan form NOA Open Account.</t>
+          <t>1. Berhasil mengisi data pada form NOA Open Account.
+2. Berhasil men-submit form dan menyimpan data Open Account.</t>
         </is>
       </c>
       <c r="I105" s="49" t="n"/>
@@ -52545,7 +52549,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="B106" s="46" t="inlineStr">
@@ -52560,29 +52564,29 @@
       </c>
       <c r="D106" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Submit NOA Open Account dengan data valid</t>
+          <t>Melakukan Submit NOA Open Account tanpa field mandatory</t>
         </is>
       </c>
       <c r="E106" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F106" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G106" s="48" t="inlineStr">
         <is>
-          <t>1. Mengisi seluruh field pada form NOA Open Account dengan data valid.
+          <t>1. Mengosongkan seluruh field mandatory pada form NOA Open Account.
 2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H106" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi data pada form NOA Open Account.
-2. Berhasil men-submit form dan menyimpan data Open Account.</t>
+          <t>1. Berhasil mengosongkan field mandatory.
+2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
         </is>
       </c>
       <c r="I106" s="49" t="n"/>
@@ -52608,7 +52612,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="B107" s="46" t="inlineStr">
@@ -52623,29 +52627,31 @@
       </c>
       <c r="D107" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Submit NOA Open Account tanpa field mandatory</t>
+          <t>Membatalkan prospek melalui menu titik tiga</t>
         </is>
       </c>
       <c r="E107" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F107" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G107" s="48" t="inlineStr">
         <is>
-          <t>1. Mengosongkan seluruh field mandatory pada form NOA Open Account.
-2. Klik button Submit.</t>
+          <t>1. Klik menu titik tiga pada pojok kanan atas.
+2. Pilih Batalkan Prospek.
+3. Klik button Batalkan pada pop-up konfirmasi.</t>
         </is>
       </c>
       <c r="H107" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan field mandatory.
-2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
+          <t>1. Berhasil membuka menu dropdown.
+2. Berhasil menampilkan pop-up konfirmasi pembatalan.
+3. Berhasil membatalkan prospek dan prospek tidak dapat dilanjutkan kembali.</t>
         </is>
       </c>
       <c r="I107" s="49" t="n"/>
@@ -52671,7 +52677,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="B108" s="46" t="inlineStr">
@@ -52681,12 +52687,12 @@
       </c>
       <c r="C108" s="46" t="inlineStr">
         <is>
-          <t>Aktifitas Prospek</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D108" s="48" t="inlineStr">
         <is>
-          <t>Membatalkan prospek melalui menu titik tiga</t>
+          <t>Membuka halaman Input Prospek melalui navigation bar bawah</t>
         </is>
       </c>
       <c r="E108" s="46" t="inlineStr">
@@ -52701,16 +52707,12 @@
       </c>
       <c r="G108" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu titik tiga pada pojok kanan atas.
-2. Pilih Batalkan Prospek.
-3. Klik button Batalkan pada pop-up konfirmasi.</t>
+          <t>1. Klik menu Input pada navigation bar bawah.</t>
         </is>
       </c>
       <c r="H108" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu dropdown.
-2. Berhasil menampilkan pop-up konfirmasi pembatalan.
-3. Berhasil membatalkan prospek dan prospek tidak dapat dilanjutkan kembali.</t>
+          <t>1. Berhasil membuka halaman Input Prospek dan menampilkan pop up tipe prospek.</t>
         </is>
       </c>
       <c r="I108" s="49" t="n"/>
@@ -52736,7 +52738,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="B109" s="46" t="inlineStr">
@@ -52751,7 +52753,7 @@
       </c>
       <c r="D109" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Input Prospek melalui navigation bar bawah</t>
+          <t>Membuka halaman Input Prospek melalui menu Lainnya</t>
         </is>
       </c>
       <c r="E109" s="46" t="inlineStr">
@@ -52766,12 +52768,14 @@
       </c>
       <c r="G109" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu Input pada navigation bar bawah.</t>
+          <t>1. Klik menu Lainnya pada navigation bar bawah.
+2. Klik menu Input Prospek.</t>
         </is>
       </c>
       <c r="H109" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka halaman Input Prospek dan menampilkan pop up tipe prospek.</t>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil membuka halaman Input Prospek dan menampilkan pop up tipe prospek.</t>
         </is>
       </c>
       <c r="I109" s="49" t="n"/>
@@ -52797,7 +52801,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="B110" s="46" t="inlineStr">
@@ -52812,7 +52816,7 @@
       </c>
       <c r="D110" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Input Prospek melalui menu Lainnya</t>
+          <t>Memilih tipe Prospek Individu</t>
         </is>
       </c>
       <c r="E110" s="46" t="inlineStr">
@@ -52827,14 +52831,14 @@
       </c>
       <c r="G110" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu Lainnya pada navigation bar bawah.
-2. Klik menu Input Prospek.</t>
+          <t>1. Buka halaman Input Prospek.
+2. Klik pilihan Individu.</t>
         </is>
       </c>
       <c r="H110" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil membuka halaman Input Prospek dan menampilkan pop up tipe prospek.</t>
+          <t>1. Berhasil membuka halaman Input Prospek.
+2. Berhasil menampilkan form Step 1 Informasi.</t>
         </is>
       </c>
       <c r="I110" s="49" t="n"/>
@@ -52860,7 +52864,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="B111" s="46" t="inlineStr">
@@ -52875,7 +52879,7 @@
       </c>
       <c r="D111" s="48" t="inlineStr">
         <is>
-          <t>Memilih tipe Prospek Individu</t>
+          <t>Mengisi form Step 1 (Informasi) dengan data valid</t>
         </is>
       </c>
       <c r="E111" s="46" t="inlineStr">
@@ -52890,14 +52894,16 @@
       </c>
       <c r="G111" s="48" t="inlineStr">
         <is>
-          <t>1. Buka halaman Input Prospek.
-2. Klik pilihan Individu.</t>
+          <t>1. Buka form Input Prospek Individu (Step 1 Informasi).
+2. Mengisi seluruh field pada Step 1 Informasi dengan data valid.
+3. Klik button Next.</t>
         </is>
       </c>
       <c r="H111" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka halaman Input Prospek.
-2. Berhasil menampilkan form Step 1 Informasi.</t>
+          <t>1. Berhasil menampilkan form Step 1 Informasi.
+2. Berhasil mengisi data pada Step 1 Informasi.
+3. Berhasil menyimpan data Step 1 dan berpindah ke Step 2 Data Pribadi.</t>
         </is>
       </c>
       <c r="I111" s="49" t="n"/>
@@ -52923,7 +52929,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="B112" s="46" t="inlineStr">
@@ -52938,31 +52944,31 @@
       </c>
       <c r="D112" s="48" t="inlineStr">
         <is>
-          <t>Mengisi form Step 1 (Informasi) dengan data valid</t>
+          <t>Mengisi form Step 1 (Informasi) tanpa field mandatory</t>
         </is>
       </c>
       <c r="E112" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F112" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G112" s="48" t="inlineStr">
         <is>
           <t>1. Buka form Input Prospek Individu (Step 1 Informasi).
-2. Mengisi seluruh field pada Step 1 Informasi dengan data valid.
+2. Mengosongkan field Nama Lengkap dan No. Telepon.
 3. Klik button Next.</t>
         </is>
       </c>
       <c r="H112" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan form Step 1 Informasi.
-2. Berhasil mengisi data pada Step 1 Informasi.
-3. Berhasil menyimpan data Step 1 dan berpindah ke Step 2 Data Pribadi.</t>
+2. Berhasil mengosongkan field mandatory.
+3. Menampilkan pesan validasi bahwa field Nama Lengkap dan No. Telepon wajib diisi.</t>
         </is>
       </c>
       <c r="I112" s="49" t="n"/>
@@ -52988,7 +52994,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="B113" s="46" t="inlineStr">
@@ -53003,12 +53009,12 @@
       </c>
       <c r="D113" s="48" t="inlineStr">
         <is>
-          <t>Mengisi form Step 1 (Informasi) tanpa field mandatory</t>
+          <t>Melakukan Check CIF pada form Step 1</t>
         </is>
       </c>
       <c r="E113" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F113" s="46" t="inlineStr">
@@ -53019,15 +53025,15 @@
       <c r="G113" s="48" t="inlineStr">
         <is>
           <t>1. Buka form Input Prospek Individu (Step 1 Informasi).
-2. Mengosongkan field Nama Lengkap dan No. Telepon.
-3. Klik button Next.</t>
+2. Isi field No KTP dengan nomor KTP valid.
+3. Klik button Check CIF.</t>
         </is>
       </c>
       <c r="H113" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan form Step 1 Informasi.
-2. Berhasil mengosongkan field mandatory.
-3. Menampilkan pesan validasi bahwa field Nama Lengkap dan No. Telepon wajib diisi.</t>
+2. Berhasil mengisi field No KTP.
+3. Berhasil menampilkan hasil Check CIF berdasarkan No KTP.</t>
         </is>
       </c>
       <c r="I113" s="49" t="n"/>
@@ -53053,7 +53059,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="B114" s="46" t="inlineStr">
@@ -53068,7 +53074,7 @@
       </c>
       <c r="D114" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Check CIF pada form Step 1</t>
+          <t>Mengisi form Step 2 (Data Pribadi) dengan data valid</t>
         </is>
       </c>
       <c r="E114" s="46" t="inlineStr">
@@ -53078,21 +53084,19 @@
       </c>
       <c r="F114" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G114" s="48" t="inlineStr">
         <is>
-          <t>1. Buka form Input Prospek Individu (Step 1 Informasi).
-2. Isi field No KTP dengan nomor KTP valid.
-3. Klik button Check CIF.</t>
+          <t>1. Mengisi seluruh field pada Step 2 Data Pribadi dengan data valid.
+2. Klik button Next.</t>
         </is>
       </c>
       <c r="H114" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan form Step 1 Informasi.
-2. Berhasil mengisi field No KTP.
-3. Berhasil menampilkan hasil Check CIF berdasarkan No KTP.</t>
+          <t>1. Berhasil mengisi data pada Step 2 Data Pribadi.
+2. Berhasil menyimpan data Step 2 dan berpindah ke Step 3 Pekerjaan.</t>
         </is>
       </c>
       <c r="I114" s="49" t="n"/>
@@ -53118,7 +53122,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="B115" s="46" t="inlineStr">
@@ -53133,7 +53137,7 @@
       </c>
       <c r="D115" s="48" t="inlineStr">
         <is>
-          <t>Mengisi form Step 2 (Data Pribadi) dengan data valid</t>
+          <t>Mengisi form Step 3 (Pekerjaan) dengan data valid</t>
         </is>
       </c>
       <c r="E115" s="46" t="inlineStr">
@@ -53148,14 +53152,14 @@
       </c>
       <c r="G115" s="48" t="inlineStr">
         <is>
-          <t>1. Mengisi seluruh field pada Step 2 Data Pribadi dengan data valid.
+          <t>1. Mengisi seluruh field pada Step 3 Pekerjaan dengan data valid.
 2. Klik button Next.</t>
         </is>
       </c>
       <c r="H115" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi data pada Step 2 Data Pribadi.
-2. Berhasil menyimpan data Step 2 dan berpindah ke Step 3 Pekerjaan.</t>
+          <t>1. Berhasil mengisi data pada Step 3 Pekerjaan.
+2. Berhasil menyimpan data Step 3 dan berpindah ke Step 4 Prospek.</t>
         </is>
       </c>
       <c r="I115" s="49" t="n"/>
@@ -53181,7 +53185,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="B116" s="46" t="inlineStr">
@@ -53196,7 +53200,7 @@
       </c>
       <c r="D116" s="48" t="inlineStr">
         <is>
-          <t>Mengisi form Step 3 (Pekerjaan) dengan data valid</t>
+          <t>Mengisi form Step 4 (Prospek) NTB dengan data valid</t>
         </is>
       </c>
       <c r="E116" s="46" t="inlineStr">
@@ -53211,14 +53215,14 @@
       </c>
       <c r="G116" s="48" t="inlineStr">
         <is>
-          <t>1. Mengisi seluruh field pada Step 3 Pekerjaan dengan data valid.
-2. Klik button Next.</t>
+          <t>1. Mengisi seluruh field pada Step 4 Prospek dengan data valid.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H116" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi data pada Step 3 Pekerjaan.
-2. Berhasil menyimpan data Step 3 dan berpindah ke Step 4 Prospek.</t>
+          <t>1. Berhasil mengisi data pada Step 4 Prospek.
+2. Berhasil menyimpan data prospek Individu NTB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
         </is>
       </c>
       <c r="I116" s="49" t="n"/>
@@ -53244,7 +53248,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.10</t>
         </is>
       </c>
       <c r="B117" s="46" t="inlineStr">
@@ -53259,7 +53263,7 @@
       </c>
       <c r="D117" s="48" t="inlineStr">
         <is>
-          <t>Mengisi form Step 4 (Prospek) NTB dengan data valid</t>
+          <t>Mengisi form Step 4 (Prospek) ETB dengan mengubah status NTB</t>
         </is>
       </c>
       <c r="E117" s="46" t="inlineStr">
@@ -53274,14 +53278,18 @@
       </c>
       <c r="G117" s="48" t="inlineStr">
         <is>
-          <t>1. Mengisi seluruh field pada Step 4 Prospek dengan data valid.
-2. Klik button Submit.</t>
+          <t>1. Aktifkan toggle Ubah NTB ke ETB.
+2. Isi field No CIF.
+3. Mengisi seluruh field pada Step 4 Prospek dengan data valid.
+4. Klik button Submit.</t>
         </is>
       </c>
       <c r="H117" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi data pada Step 4 Prospek.
-2. Berhasil menyimpan data prospek Individu NTB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
+          <t>1. Berhasil mengaktifkan toggle NTB ke ETB.
+2. Berhasil mengisi No CIF.
+3. Berhasil mengisi data pada Step 4 Prospek.
+4. Berhasil menyimpan data prospek Individu ETB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
         </is>
       </c>
       <c r="I117" s="49" t="n"/>
@@ -53307,7 +53315,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>11.10</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="B118" s="46" t="inlineStr">
@@ -53322,33 +53330,29 @@
       </c>
       <c r="D118" s="48" t="inlineStr">
         <is>
-          <t>Mengisi form Step 4 (Prospek) ETB dengan mengubah status NTB</t>
+          <t>Mengisi form Step 4 (Prospek) tanpa field mandatory</t>
         </is>
       </c>
       <c r="E118" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F118" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G118" s="48" t="inlineStr">
         <is>
-          <t>1. Aktifkan toggle Ubah NTB ke ETB.
-2. Isi field No CIF.
-3. Mengisi seluruh field pada Step 4 Prospek dengan data valid.
-4. Klik button Submit.</t>
+          <t>1. Mengosongkan seluruh field mandatory pada Step 4 Prospek.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H118" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengaktifkan toggle NTB ke ETB.
-2. Berhasil mengisi No CIF.
-3. Berhasil mengisi data pada Step 4 Prospek.
-4. Berhasil menyimpan data prospek Individu ETB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
+          <t>1. Berhasil mengosongkan field mandatory.
+2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
         </is>
       </c>
       <c r="I118" s="49" t="n"/>
@@ -53374,7 +53378,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="B119" s="46" t="inlineStr">
@@ -53389,29 +53393,27 @@
       </c>
       <c r="D119" s="48" t="inlineStr">
         <is>
-          <t>Mengisi form Step 4 (Prospek) tanpa field mandatory</t>
+          <t>Navigasi ke halaman Aktifitas dari layar konfirmasi Prospek Berhasil Dibuat</t>
         </is>
       </c>
       <c r="E119" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F119" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G119" s="48" t="inlineStr">
         <is>
-          <t>1. Mengosongkan seluruh field mandatory pada Step 4 Prospek.
-2. Klik button Submit.</t>
+          <t>1. Klik button Lihat Aktifitas.</t>
         </is>
       </c>
       <c r="H119" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan field mandatory.
-2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
+          <t>1. Berhasil mengarahkan pengguna ke halaman Lead Qualification Aktifitas.</t>
         </is>
       </c>
       <c r="I119" s="49" t="n"/>
@@ -53437,7 +53439,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>11.13</t>
         </is>
       </c>
       <c r="B120" s="46" t="inlineStr">
@@ -53452,7 +53454,7 @@
       </c>
       <c r="D120" s="48" t="inlineStr">
         <is>
-          <t>Navigasi ke halaman Aktifitas dari layar konfirmasi Prospek Berhasil Dibuat</t>
+          <t>Kembali ke halaman utama dari layar konfirmasi Prospek Berhasil Dibuat</t>
         </is>
       </c>
       <c r="E120" s="46" t="inlineStr">
@@ -53462,17 +53464,17 @@
       </c>
       <c r="F120" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G120" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Lihat Aktifitas.</t>
+          <t>1. Klik button Kembali.</t>
         </is>
       </c>
       <c r="H120" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengarahkan pengguna ke halaman Lead Qualification Aktifitas.</t>
+          <t>1. Berhasil mengarahkan pengguna kembali ke halaman utama / form input.</t>
         </is>
       </c>
       <c r="I120" s="49" t="n"/>
@@ -53498,7 +53500,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>11.13</t>
+          <t>11.14</t>
         </is>
       </c>
       <c r="B121" s="46" t="inlineStr">
@@ -53513,7 +53515,7 @@
       </c>
       <c r="D121" s="48" t="inlineStr">
         <is>
-          <t>Kembali ke halaman utama dari layar konfirmasi Prospek Berhasil Dibuat</t>
+          <t>Memilih tipe Prospek Lembaga</t>
         </is>
       </c>
       <c r="E121" s="46" t="inlineStr">
@@ -53523,17 +53525,19 @@
       </c>
       <c r="F121" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G121" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Kembali.</t>
+          <t>1. Buka halaman Input Prospek.
+2. Klik pilihan Lembaga.</t>
         </is>
       </c>
       <c r="H121" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengarahkan pengguna kembali ke halaman utama / form input.</t>
+          <t>1. Berhasil membuka halaman Input Prospek.
+2. Berhasil menampilkan form Step 1 Informasi Lembaga.</t>
         </is>
       </c>
       <c r="I121" s="49" t="n"/>
@@ -53559,7 +53563,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>11.14</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="B122" s="46" t="inlineStr">
@@ -53574,7 +53578,7 @@
       </c>
       <c r="D122" s="48" t="inlineStr">
         <is>
-          <t>Memilih tipe Prospek Lembaga</t>
+          <t>Mengisi form Step 1 (Informasi Lembaga) dengan data valid</t>
         </is>
       </c>
       <c r="E122" s="46" t="inlineStr">
@@ -53589,14 +53593,16 @@
       </c>
       <c r="G122" s="48" t="inlineStr">
         <is>
-          <t>1. Buka halaman Input Prospek.
-2. Klik pilihan Lembaga.</t>
+          <t>1. Buka form Input Prospek Lembaga (Step 1 Informasi Lembaga).
+2. Mengisi field NPWP dengan NPWP valid.
+3. Klik button Next.</t>
         </is>
       </c>
       <c r="H122" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka halaman Input Prospek.
-2. Berhasil menampilkan form Step 1 Informasi Lembaga.</t>
+          <t>1. Berhasil menampilkan form Step 1 Informasi Lembaga.
+2. Berhasil mengisi field NPWP.
+3. Berhasil menyimpan data Step 1 dan berpindah ke Step 2 Data Lembaga.</t>
         </is>
       </c>
       <c r="I122" s="49" t="n"/>
@@ -53622,7 +53628,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.16</t>
         </is>
       </c>
       <c r="B123" s="46" t="inlineStr">
@@ -53637,7 +53643,7 @@
       </c>
       <c r="D123" s="48" t="inlineStr">
         <is>
-          <t>Mengisi form Step 1 (Informasi Lembaga) dengan data valid</t>
+          <t>Mengisi form Step 2 (Data Lembaga) dengan data valid</t>
         </is>
       </c>
       <c r="E123" s="46" t="inlineStr">
@@ -53652,16 +53658,14 @@
       </c>
       <c r="G123" s="48" t="inlineStr">
         <is>
-          <t>1. Buka form Input Prospek Lembaga (Step 1 Informasi Lembaga).
-2. Mengisi field NPWP dengan NPWP valid.
-3. Klik button Next.</t>
+          <t>1. Mengisi seluruh field pada Step 2 Data Lembaga dengan data valid.
+2. Klik button Next.</t>
         </is>
       </c>
       <c r="H123" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan form Step 1 Informasi Lembaga.
-2. Berhasil mengisi field NPWP.
-3. Berhasil menyimpan data Step 1 dan berpindah ke Step 2 Data Lembaga.</t>
+          <t>1. Berhasil mengisi data pada Step 2 Data Lembaga.
+2. Berhasil menyimpan data Step 2 dan berpindah ke Step 3 Prospek.</t>
         </is>
       </c>
       <c r="I123" s="49" t="n"/>
@@ -53687,7 +53691,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="B124" s="46" t="inlineStr">
@@ -53702,29 +53706,29 @@
       </c>
       <c r="D124" s="48" t="inlineStr">
         <is>
-          <t>Mengisi form Step 2 (Data Lembaga) dengan data valid</t>
+          <t>Mengisi form Step 2 (Data Lembaga) tanpa field mandatory</t>
         </is>
       </c>
       <c r="E124" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F124" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G124" s="48" t="inlineStr">
         <is>
-          <t>1. Mengisi seluruh field pada Step 2 Data Lembaga dengan data valid.
+          <t>1. Mengosongkan field Nama Perusahaan dan Telepon Perusahaan.
 2. Klik button Next.</t>
         </is>
       </c>
       <c r="H124" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi data pada Step 2 Data Lembaga.
-2. Berhasil menyimpan data Step 2 dan berpindah ke Step 3 Prospek.</t>
+          <t>1. Berhasil mengosongkan field mandatory.
+2. Menampilkan pesan validasi bahwa field Nama Perusahaan dan Telepon Perusahaan wajib diisi.</t>
         </is>
       </c>
       <c r="I124" s="49" t="n"/>
@@ -53750,7 +53754,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="B125" s="46" t="inlineStr">
@@ -53765,29 +53769,29 @@
       </c>
       <c r="D125" s="48" t="inlineStr">
         <is>
-          <t>Mengisi form Step 2 (Data Lembaga) tanpa field mandatory</t>
+          <t>Mengisi form Step 3 (Prospek Lembaga) NTB dengan data valid</t>
         </is>
       </c>
       <c r="E125" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F125" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G125" s="48" t="inlineStr">
         <is>
-          <t>1. Mengosongkan field Nama Perusahaan dan Telepon Perusahaan.
-2. Klik button Next.</t>
+          <t>1. Mengisi seluruh field pada Step 3 Prospek Lembaga dengan data valid.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H125" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan field mandatory.
-2. Menampilkan pesan validasi bahwa field Nama Perusahaan dan Telepon Perusahaan wajib diisi.</t>
+          <t>1. Berhasil mengisi data pada Step 3 Prospek Lembaga.
+2. Berhasil menyimpan data prospek Lembaga NTB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
         </is>
       </c>
       <c r="I125" s="49" t="n"/>
@@ -53813,7 +53817,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="B126" s="46" t="inlineStr">
@@ -53828,7 +53832,7 @@
       </c>
       <c r="D126" s="48" t="inlineStr">
         <is>
-          <t>Mengisi form Step 3 (Prospek Lembaga) NTB dengan data valid</t>
+          <t>Mengisi form Step 3 (Prospek Lembaga) ETB dengan mengubah status NTB</t>
         </is>
       </c>
       <c r="E126" s="46" t="inlineStr">
@@ -53843,14 +53847,18 @@
       </c>
       <c r="G126" s="48" t="inlineStr">
         <is>
-          <t>1. Mengisi seluruh field pada Step 3 Prospek Lembaga dengan data valid.
-2. Klik button Submit.</t>
+          <t>1. Aktifkan toggle Ubah NTB ke ETB.
+2. Isi field No CIF.
+3. Mengisi seluruh field pada Step 3 Prospek Lembaga dengan data valid.
+4. Klik button Submit.</t>
         </is>
       </c>
       <c r="H126" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi data pada Step 3 Prospek Lembaga.
-2. Berhasil menyimpan data prospek Lembaga NTB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
+          <t>1. Berhasil mengaktifkan toggle NTB ke ETB.
+2. Berhasil mengisi No CIF.
+3. Berhasil mengisi data pada Step 3 Prospek Lembaga.
+4. Berhasil menyimpan data prospek Lembaga ETB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
         </is>
       </c>
       <c r="I126" s="49" t="n"/>
@@ -53876,7 +53884,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="B127" s="46" t="inlineStr">
@@ -53891,33 +53899,29 @@
       </c>
       <c r="D127" s="48" t="inlineStr">
         <is>
-          <t>Mengisi form Step 3 (Prospek Lembaga) ETB dengan mengubah status NTB</t>
+          <t>Mengisi form Step 3 (Prospek Lembaga) tanpa field mandatory</t>
         </is>
       </c>
       <c r="E127" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F127" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G127" s="48" t="inlineStr">
         <is>
-          <t>1. Aktifkan toggle Ubah NTB ke ETB.
-2. Isi field No CIF.
-3. Mengisi seluruh field pada Step 3 Prospek Lembaga dengan data valid.
-4. Klik button Submit.</t>
+          <t>1. Mengosongkan seluruh field mandatory pada Step 3 Prospek Lembaga.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H127" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengaktifkan toggle NTB ke ETB.
-2. Berhasil mengisi No CIF.
-3. Berhasil mengisi data pada Step 3 Prospek Lembaga.
-4. Berhasil menyimpan data prospek Lembaga ETB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
+          <t>1. Berhasil mengosongkan field mandatory.
+2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
         </is>
       </c>
       <c r="I127" s="49" t="n"/>
@@ -53943,7 +53947,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>11.20</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B128" s="46" t="inlineStr">
@@ -53953,34 +53957,34 @@
       </c>
       <c r="C128" s="46" t="inlineStr">
         <is>
-          <t>Input Prospek</t>
+          <t>List Nasabah ETB</t>
         </is>
       </c>
       <c r="D128" s="48" t="inlineStr">
         <is>
-          <t>Mengisi form Step 3 (Prospek Lembaga) tanpa field mandatory</t>
+          <t>Membuka halaman List Nasabah ETB</t>
         </is>
       </c>
       <c r="E128" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F128" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G128" s="48" t="inlineStr">
         <is>
-          <t>1. Mengosongkan seluruh field mandatory pada Step 3 Prospek Lembaga.
-2. Klik button Submit.</t>
+          <t>1. Buka menu Lainnya.
+2. Klik menu List Nasabah ETB.</t>
         </is>
       </c>
       <c r="H128" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan field mandatory.
-2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman List Nasabah ETB.</t>
         </is>
       </c>
       <c r="I128" s="49" t="n"/>
@@ -54006,7 +54010,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="B129" s="46" t="inlineStr">
@@ -54021,7 +54025,7 @@
       </c>
       <c r="D129" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman List Nasabah ETB</t>
+          <t>Mencari nasabah menggunakan Search Bar</t>
         </is>
       </c>
       <c r="E129" s="46" t="inlineStr">
@@ -54036,14 +54040,12 @@
       </c>
       <c r="G129" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu List Nasabah ETB.</t>
+          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
         </is>
       </c>
       <c r="H129" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman List Nasabah ETB.</t>
+          <t>1. Berhasil menampilkan data nasabah yang sesuai dengan kata kunci pencarian.</t>
         </is>
       </c>
       <c r="I129" s="49" t="n"/>
@@ -54069,7 +54071,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="B130" s="46" t="inlineStr">
@@ -54084,27 +54086,27 @@
       </c>
       <c r="D130" s="48" t="inlineStr">
         <is>
-          <t>Mencari nasabah menggunakan Search Bar</t>
+          <t>Mencari nasabah dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E130" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F130" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G130" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
         </is>
       </c>
       <c r="H130" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data nasabah yang sesuai dengan kata kunci pencarian.</t>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
       <c r="I130" s="49" t="n"/>
@@ -54130,7 +54132,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="B131" s="46" t="inlineStr">
@@ -54145,27 +54147,31 @@
       </c>
       <c r="D131" s="48" t="inlineStr">
         <is>
-          <t>Mencari nasabah dengan keyword tidak valid</t>
+          <t>Melakukan filter data nasabah</t>
         </is>
       </c>
       <c r="E131" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F131" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G131" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+          <t>1. Klik button Filter di halaman List Nasabah ETB.
+2. Pilih kriteria filter pada form Filter.
+3. Klik button Simpan.</t>
         </is>
       </c>
       <c r="H131" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+          <t>1. Berhasil membuka form Filter.
+2. Berhasil memilih kriteria filter.
+3. Berhasil menampilkan daftar nasabah yang sesuai dengan kriteria filter.</t>
         </is>
       </c>
       <c r="I131" s="49" t="n"/>
@@ -54191,7 +54197,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="B132" s="46" t="inlineStr">
@@ -54206,7 +54212,7 @@
       </c>
       <c r="D132" s="48" t="inlineStr">
         <is>
-          <t>Melakukan filter data nasabah</t>
+          <t>Melihat Detail Prospek Nasabah ETB</t>
         </is>
       </c>
       <c r="E132" s="46" t="inlineStr">
@@ -54221,16 +54227,14 @@
       </c>
       <c r="G132" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Filter di halaman List Nasabah ETB.
-2. Pilih kriteria filter pada form Filter.
-3. Klik button Simpan.</t>
+          <t>1. Klik menu titik tiga pada salah satu card nasabah.
+2. Pilih Detail Prospek.</t>
         </is>
       </c>
       <c r="H132" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka form Filter.
-2. Berhasil memilih kriteria filter.
-3. Berhasil menampilkan daftar nasabah yang sesuai dengan kriteria filter.</t>
+          <t>1. Berhasil menampilkan menu Lainnya.
+2. Berhasil membuka halaman Detail Prospek dan menampilkan informasi nasabah secara lengkap.</t>
         </is>
       </c>
       <c r="I132" s="49" t="n"/>
@@ -54256,7 +54260,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="B133" s="46" t="inlineStr">
@@ -54271,7 +54275,7 @@
       </c>
       <c r="D133" s="48" t="inlineStr">
         <is>
-          <t>Melihat Detail Prospek Nasabah ETB</t>
+          <t>Membuka form Prospek Ulang</t>
         </is>
       </c>
       <c r="E133" s="46" t="inlineStr">
@@ -54281,19 +54285,19 @@
       </c>
       <c r="F133" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G133" s="48" t="inlineStr">
         <is>
           <t>1. Klik menu titik tiga pada salah satu card nasabah.
-2. Pilih Detail Prospek.</t>
+2. Pilih Prospek Ulang.</t>
         </is>
       </c>
       <c r="H133" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan menu Lainnya.
-2. Berhasil membuka halaman Detail Prospek dan menampilkan informasi nasabah secara lengkap.</t>
+2. Berhasil membuka form Prospek Ulang.</t>
         </is>
       </c>
       <c r="I133" s="49" t="n"/>
@@ -54319,7 +54323,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="B134" s="46" t="inlineStr">
@@ -54334,7 +54338,7 @@
       </c>
       <c r="D134" s="48" t="inlineStr">
         <is>
-          <t>Membuka form Prospek Ulang</t>
+          <t>Melakukan Prospek Ulang dengan data valid</t>
         </is>
       </c>
       <c r="E134" s="46" t="inlineStr">
@@ -54344,19 +54348,19 @@
       </c>
       <c r="F134" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G134" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu titik tiga pada salah satu card nasabah.
-2. Pilih Prospek Ulang.</t>
+          <t>1. Mengisi seluruh field pada form Prospek Ulang dengan data valid.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H134" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan menu Lainnya.
-2. Berhasil membuka form Prospek Ulang.</t>
+          <t>1. Berhasil mengisi data pada form Prospek Ulang.
+2. Berhasil men-submit form dan memperbarui data prospek.</t>
         </is>
       </c>
       <c r="I134" s="49" t="n"/>
@@ -54382,7 +54386,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="B135" s="46" t="inlineStr">
@@ -54397,29 +54401,29 @@
       </c>
       <c r="D135" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Prospek Ulang dengan data valid</t>
+          <t>Melakukan Prospek Ulang tanpa field mandatory</t>
         </is>
       </c>
       <c r="E135" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F135" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G135" s="48" t="inlineStr">
         <is>
-          <t>1. Mengisi seluruh field pada form Prospek Ulang dengan data valid.
+          <t>1. Mengosongkan seluruh field mandatory pada form Prospek Ulang.
 2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H135" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi data pada form Prospek Ulang.
-2. Berhasil men-submit form dan memperbarui data prospek.</t>
+          <t>1. Berhasil mengosongkan field mandatory.
+2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
         </is>
       </c>
       <c r="I135" s="49" t="n"/>
@@ -54445,7 +54449,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="B136" s="46" t="inlineStr">
@@ -54460,29 +54464,29 @@
       </c>
       <c r="D136" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Prospek Ulang tanpa field mandatory</t>
+          <t>Melihat Informasi Rekening</t>
         </is>
       </c>
       <c r="E136" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F136" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G136" s="48" t="inlineStr">
         <is>
-          <t>1. Mengosongkan seluruh field mandatory pada form Prospek Ulang.
-2. Klik button Submit.</t>
+          <t>1. Klik menu titik tiga pada salah satu card nasabah.
+2. Pilih Informasi Rekening.</t>
         </is>
       </c>
       <c r="H136" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan field mandatory.
-2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
+          <t>1. Berhasil menampilkan menu Lainnya.
+2. Berhasil menampilkan detail rekening nasabah (nomor rekening dan saldo).</t>
         </is>
       </c>
       <c r="I136" s="49" t="n"/>
@@ -54508,7 +54512,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="B137" s="46" t="inlineStr">
@@ -54523,7 +54527,7 @@
       </c>
       <c r="D137" s="48" t="inlineStr">
         <is>
-          <t>Melihat Informasi Rekening</t>
+          <t>Menghapus data nasabah</t>
         </is>
       </c>
       <c r="E137" s="46" t="inlineStr">
@@ -54539,13 +54543,15 @@
       <c r="G137" s="48" t="inlineStr">
         <is>
           <t>1. Klik menu titik tiga pada salah satu card nasabah.
-2. Pilih Informasi Rekening.</t>
+2. Pilih Hapus.
+3. Klik button Ya pada pop-up konfirmasi.</t>
         </is>
       </c>
       <c r="H137" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan menu Lainnya.
-2. Berhasil menampilkan detail rekening nasabah (nomor rekening dan saldo).</t>
+2. Berhasil menampilkan pop-up konfirmasi hapus data.
+3. Berhasil menghapus data nasabah dari daftar List Nasabah ETB.</t>
         </is>
       </c>
       <c r="I137" s="49" t="n"/>
@@ -54571,7 +54577,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="B138" s="46" t="inlineStr">
@@ -54581,12 +54587,12 @@
       </c>
       <c r="C138" s="46" t="inlineStr">
         <is>
-          <t>List Nasabah ETB</t>
+          <t>Nasabah Referal</t>
         </is>
       </c>
       <c r="D138" s="48" t="inlineStr">
         <is>
-          <t>Menghapus data nasabah</t>
+          <t>Membuka halaman Nasabah Referal</t>
         </is>
       </c>
       <c r="E138" s="46" t="inlineStr">
@@ -54601,16 +54607,14 @@
       </c>
       <c r="G138" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu titik tiga pada salah satu card nasabah.
-2. Pilih Hapus.
-3. Klik button Ya pada pop-up konfirmasi.</t>
+          <t>1. Buka menu Lainnya.
+2. Klik menu Nasabah Referal.</t>
         </is>
       </c>
       <c r="H138" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan menu Lainnya.
-2. Berhasil menampilkan pop-up konfirmasi hapus data.
-3. Berhasil menghapus data nasabah dari daftar List Nasabah ETB.</t>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman Nasabah Referal.</t>
         </is>
       </c>
       <c r="I138" s="49" t="n"/>
@@ -54636,7 +54640,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="B139" s="46" t="inlineStr">
@@ -54651,7 +54655,7 @@
       </c>
       <c r="D139" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Nasabah Referal</t>
+          <t>Mencari nasabah referal menggunakan Search Bar</t>
         </is>
       </c>
       <c r="E139" s="46" t="inlineStr">
@@ -54666,14 +54670,12 @@
       </c>
       <c r="G139" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Nasabah Referal.</t>
+          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
         </is>
       </c>
       <c r="H139" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Nasabah Referal.</t>
+          <t>1. Berhasil menampilkan data nasabah referal yang sesuai dengan kata kunci pencarian.</t>
         </is>
       </c>
       <c r="I139" s="49" t="n"/>
@@ -54699,7 +54701,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="B140" s="46" t="inlineStr">
@@ -54714,27 +54716,27 @@
       </c>
       <c r="D140" s="48" t="inlineStr">
         <is>
-          <t>Mencari nasabah referal menggunakan Search Bar</t>
+          <t>Mencari nasabah referal dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E140" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F140" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G140" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
         </is>
       </c>
       <c r="H140" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data nasabah referal yang sesuai dengan kata kunci pencarian.</t>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
       <c r="I140" s="49" t="n"/>
@@ -54760,7 +54762,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="B141" s="46" t="inlineStr">
@@ -54775,27 +54777,27 @@
       </c>
       <c r="D141" s="48" t="inlineStr">
         <is>
-          <t>Mencari nasabah referal dengan keyword tidak valid</t>
+          <t>Melihat Detail Prospek nasabah referal</t>
         </is>
       </c>
       <c r="E141" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F141" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G141" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+          <t>1. Klik salah satu card nasabah referal.</t>
         </is>
       </c>
       <c r="H141" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+          <t>1. Berhasil menampilkan detail nasabah referal.</t>
         </is>
       </c>
       <c r="I141" s="49" t="n"/>
@@ -54821,22 +54823,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="B142" s="46" t="inlineStr">
         <is>
-          <t>Prospek &amp; Nasabah</t>
+          <t>Agenda</t>
         </is>
       </c>
       <c r="C142" s="46" t="inlineStr">
         <is>
-          <t>Nasabah Referal</t>
+          <t>Pengingat</t>
         </is>
       </c>
       <c r="D142" s="48" t="inlineStr">
         <is>
-          <t>Melihat Detail Prospek nasabah referal</t>
+          <t>Membuka halaman Pengingat</t>
         </is>
       </c>
       <c r="E142" s="46" t="inlineStr">
@@ -54851,12 +54853,14 @@
       </c>
       <c r="G142" s="48" t="inlineStr">
         <is>
-          <t>1. Klik salah satu card nasabah referal.</t>
+          <t>1. Buka menu Lainnya.
+2. Klik menu Pengingat.</t>
         </is>
       </c>
       <c r="H142" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail nasabah referal.</t>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman Pengingat.</t>
         </is>
       </c>
       <c r="I142" s="49" t="n"/>
@@ -54882,7 +54886,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="B143" s="46" t="inlineStr">
@@ -54897,7 +54901,7 @@
       </c>
       <c r="D143" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Pengingat</t>
+          <t>Melihat daftar pengingat pada tab Aktif</t>
         </is>
       </c>
       <c r="E143" s="46" t="inlineStr">
@@ -54907,19 +54911,17 @@
       </c>
       <c r="F143" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G143" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Pengingat.</t>
+          <t>1. Klik tab Aktif.</t>
         </is>
       </c>
       <c r="H143" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Pengingat.</t>
+          <t>1. Berhasil menampilkan daftar pengingat yang sedang aktif.</t>
         </is>
       </c>
       <c r="I143" s="49" t="n"/>
@@ -54945,7 +54947,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="B144" s="46" t="inlineStr">
@@ -54960,7 +54962,7 @@
       </c>
       <c r="D144" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar pengingat pada tab Aktif</t>
+          <t>Melihat daftar pengingat pada tab Selesai</t>
         </is>
       </c>
       <c r="E144" s="46" t="inlineStr">
@@ -54975,12 +54977,12 @@
       </c>
       <c r="G144" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Aktif.</t>
+          <t>1. Klik tab Selesai.</t>
         </is>
       </c>
       <c r="H144" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar pengingat yang sedang aktif.</t>
+          <t>1. Berhasil menampilkan daftar pengingat yang sudah selesai.</t>
         </is>
       </c>
       <c r="I144" s="49" t="n"/>
@@ -55006,7 +55008,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="B145" s="46" t="inlineStr">
@@ -55021,7 +55023,7 @@
       </c>
       <c r="D145" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar pengingat pada tab Selesai</t>
+          <t>Menambahkan pengingat baru dengan data valid</t>
         </is>
       </c>
       <c r="E145" s="46" t="inlineStr">
@@ -55031,17 +55033,21 @@
       </c>
       <c r="F145" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G145" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Selesai.</t>
+          <t>1. Klik button + Baru.
+2. Mengisi seluruh field mandatory pada form Tambah Pengingat dengan data valid.
+3. Klik button Simpan.</t>
         </is>
       </c>
       <c r="H145" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar pengingat yang sudah selesai.</t>
+          <t>1. Berhasil membuka form Tambah Pengingat.
+2. Berhasil mengisi seluruh field mandatory pada form Tambah Pengingat.
+3. Berhasil menyimpan pengingat dan menampilkan pengingat baru pada daftar.</t>
         </is>
       </c>
       <c r="I145" s="49" t="n"/>
@@ -55067,7 +55073,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="B146" s="46" t="inlineStr">
@@ -55082,31 +55088,31 @@
       </c>
       <c r="D146" s="48" t="inlineStr">
         <is>
-          <t>Menambahkan pengingat baru dengan data valid</t>
+          <t>Menambahkan pengingat baru tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E146" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F146" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G146" s="48" t="inlineStr">
         <is>
           <t>1. Klik button + Baru.
-2. Mengisi seluruh field mandatory pada form Tambah Pengingat dengan data valid.
+2. Mengosongkan seluruh field mandatory pada form Tambah Pengingat.
 3. Klik button Simpan.</t>
         </is>
       </c>
       <c r="H146" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil membuka form Tambah Pengingat.
-2. Berhasil mengisi seluruh field mandatory pada form Tambah Pengingat.
-3. Berhasil menyimpan pengingat dan menampilkan pengingat baru pada daftar.</t>
+2. Field mandatory berhasil dikosongkan.
+3. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
       <c r="I146" s="49" t="n"/>
@@ -55132,7 +55138,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="B147" s="46" t="inlineStr">
@@ -55147,31 +55153,29 @@
       </c>
       <c r="D147" s="48" t="inlineStr">
         <is>
-          <t>Menambahkan pengingat baru tanpa mengisi field mandatory</t>
+          <t>Menandai pengingat sebagai selesai</t>
         </is>
       </c>
       <c r="E147" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F147" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G147" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button + Baru.
-2. Mengosongkan seluruh field mandatory pada form Tambah Pengingat.
-3. Klik button Simpan.</t>
+          <t>1. Centang checkbox pada salah satu card pengingat aktif.
+2. Klik button Ya pada pop-up konfirmasi.</t>
         </is>
       </c>
       <c r="H147" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka form Tambah Pengingat.
-2. Field mandatory berhasil dikosongkan.
-3. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+          <t>1. Berhasil menampilkan pop-up konfirmasi selesai.
+2. Berhasil menandai pengingat sebagai selesai dan memindahkan pengingat ke tab Selesai.</t>
         </is>
       </c>
       <c r="I147" s="49" t="n"/>
@@ -55197,7 +55201,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="B148" s="46" t="inlineStr">
@@ -55207,12 +55211,12 @@
       </c>
       <c r="C148" s="46" t="inlineStr">
         <is>
-          <t>Pengingat</t>
+          <t>Daily Sales Agenda</t>
         </is>
       </c>
       <c r="D148" s="48" t="inlineStr">
         <is>
-          <t>Menandai pengingat sebagai selesai</t>
+          <t>Membuka halaman Daily Sales Agenda</t>
         </is>
       </c>
       <c r="E148" s="46" t="inlineStr">
@@ -55227,14 +55231,14 @@
       </c>
       <c r="G148" s="48" t="inlineStr">
         <is>
-          <t>1. Centang checkbox pada salah satu card pengingat aktif.
-2. Klik button Ya pada pop-up konfirmasi.</t>
+          <t>1. Buka menu Lainnya.
+2. Klik menu Daily Sales Agenda.</t>
         </is>
       </c>
       <c r="H148" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan pop-up konfirmasi selesai.
-2. Berhasil menandai pengingat sebagai selesai dan memindahkan pengingat ke tab Selesai.</t>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
         </is>
       </c>
       <c r="I148" s="49" t="n"/>
@@ -55260,7 +55264,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="B149" s="46" t="inlineStr">
@@ -55275,7 +55279,7 @@
       </c>
       <c r="D149" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Daily Sales Agenda</t>
+          <t>Melihat daftar agenda pada tab Masuk</t>
         </is>
       </c>
       <c r="E149" s="46" t="inlineStr">
@@ -55285,19 +55289,17 @@
       </c>
       <c r="F149" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G149" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Daily Sales Agenda.</t>
+          <t>1. Klik tab Masuk.</t>
         </is>
       </c>
       <c r="H149" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
+          <t>1. Berhasil menampilkan daftar nasabah yang masuk pada Daily Sales Agenda.</t>
         </is>
       </c>
       <c r="I149" s="49" t="n"/>
@@ -55323,7 +55325,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="B150" s="46" t="inlineStr">
@@ -55338,7 +55340,7 @@
       </c>
       <c r="D150" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar agenda pada tab Masuk</t>
+          <t>Melihat daftar agenda pada tab Closing</t>
         </is>
       </c>
       <c r="E150" s="46" t="inlineStr">
@@ -55353,12 +55355,12 @@
       </c>
       <c r="G150" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Masuk.</t>
+          <t>1. Klik tab Closing.</t>
         </is>
       </c>
       <c r="H150" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar nasabah yang masuk pada Daily Sales Agenda.</t>
+          <t>1. Berhasil menampilkan daftar nasabah yang closing pada Daily Sales Agenda.</t>
         </is>
       </c>
       <c r="I150" s="49" t="n"/>
@@ -55384,7 +55386,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="B151" s="46" t="inlineStr">
@@ -55399,7 +55401,7 @@
       </c>
       <c r="D151" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar agenda pada tab Closing</t>
+          <t>Melihat daftar agenda pada tab Referral</t>
         </is>
       </c>
       <c r="E151" s="46" t="inlineStr">
@@ -55414,12 +55416,12 @@
       </c>
       <c r="G151" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Closing.</t>
+          <t>1. Klik tab Referral.</t>
         </is>
       </c>
       <c r="H151" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar nasabah yang closing pada Daily Sales Agenda.</t>
+          <t>1. Berhasil menampilkan daftar nasabah referral pada Daily Sales Agenda.</t>
         </is>
       </c>
       <c r="I151" s="49" t="n"/>
@@ -55445,7 +55447,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="B152" s="46" t="inlineStr">
@@ -55460,7 +55462,7 @@
       </c>
       <c r="D152" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar agenda pada tab Referral</t>
+          <t>Melihat daftar agenda pada tab Ref. Closing</t>
         </is>
       </c>
       <c r="E152" s="46" t="inlineStr">
@@ -55475,12 +55477,12 @@
       </c>
       <c r="G152" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Referral.</t>
+          <t>1. Klik tab Ref. Closing.</t>
         </is>
       </c>
       <c r="H152" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar nasabah referral pada Daily Sales Agenda.</t>
+          <t>1. Berhasil menampilkan daftar nasabah referral yang closing pada Daily Sales Agenda.</t>
         </is>
       </c>
       <c r="I152" s="49" t="n"/>
@@ -55506,7 +55508,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="B153" s="46" t="inlineStr">
@@ -55521,7 +55523,7 @@
       </c>
       <c r="D153" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar agenda pada tab Ref. Closing</t>
+          <t>Mencari agenda menggunakan Search Bar</t>
         </is>
       </c>
       <c r="E153" s="46" t="inlineStr">
@@ -55531,17 +55533,17 @@
       </c>
       <c r="F153" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G153" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Ref. Closing.</t>
+          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
         </is>
       </c>
       <c r="H153" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar nasabah referral yang closing pada Daily Sales Agenda.</t>
+          <t>1. Berhasil menampilkan data agenda yang sesuai dengan kata kunci pencarian.</t>
         </is>
       </c>
       <c r="I153" s="49" t="n"/>
@@ -55567,7 +55569,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="B154" s="46" t="inlineStr">
@@ -55582,27 +55584,27 @@
       </c>
       <c r="D154" s="48" t="inlineStr">
         <is>
-          <t>Mencari agenda menggunakan Search Bar</t>
+          <t>Mencari agenda dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E154" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F154" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G154" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
         </is>
       </c>
       <c r="H154" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data agenda yang sesuai dengan kata kunci pencarian.</t>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
       <c r="I154" s="49" t="n"/>
@@ -55628,7 +55630,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="B155" s="46" t="inlineStr">
@@ -55643,27 +55645,31 @@
       </c>
       <c r="D155" s="48" t="inlineStr">
         <is>
-          <t>Mencari agenda dengan keyword tidak valid</t>
+          <t>Melakukan filter data Daily Sales Agenda</t>
         </is>
       </c>
       <c r="E155" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F155" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G155" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+          <t>1. Klik button Filter.
+2. Pilih kriteria filter pada form Filter (Product, Bulan, Tahun).
+3. Klik button Submit.</t>
         </is>
       </c>
       <c r="H155" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+          <t>1. Berhasil membuka form Filter.
+2. Berhasil memilih kriteria filter.
+3. Berhasil menampilkan data Daily Sales Agenda sesuai filter yang dipilih.</t>
         </is>
       </c>
       <c r="I155" s="49" t="n"/>
@@ -55689,22 +55695,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="B156" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Fitur</t>
         </is>
       </c>
       <c r="C156" s="46" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Marketing Toolkit</t>
         </is>
       </c>
       <c r="D156" s="48" t="inlineStr">
         <is>
-          <t>Melakukan filter data Daily Sales Agenda</t>
+          <t>Membuka halaman Marketing Toolkit</t>
         </is>
       </c>
       <c r="E156" s="46" t="inlineStr">
@@ -55719,16 +55725,14 @@
       </c>
       <c r="G156" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Filter.
-2. Pilih kriteria filter pada form Filter (Product, Bulan, Tahun).
-3. Klik button Submit.</t>
+          <t>1. Buka menu Lainnya.
+2. Klik menu Marketing Toolkit.</t>
         </is>
       </c>
       <c r="H156" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka form Filter.
-2. Berhasil memilih kriteria filter.
-3. Berhasil menampilkan data Daily Sales Agenda sesuai filter yang dipilih.</t>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman Marketing Toolkit.</t>
         </is>
       </c>
       <c r="I156" s="49" t="n"/>
@@ -55754,7 +55758,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="B157" s="46" t="inlineStr">
@@ -55769,7 +55773,7 @@
       </c>
       <c r="D157" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Marketing Toolkit</t>
+          <t>Mengubah tampilan folder menjadi List View</t>
         </is>
       </c>
       <c r="E157" s="46" t="inlineStr">
@@ -55779,19 +55783,17 @@
       </c>
       <c r="F157" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G157" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Marketing Toolkit.</t>
+          <t>1. Klik icon tampilan List pada halaman Marketing Toolkit.</t>
         </is>
       </c>
       <c r="H157" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Marketing Toolkit.</t>
+          <t>1. Berhasil mengubah tampilan folder menjadi List View.</t>
         </is>
       </c>
       <c r="I157" s="49" t="n"/>
@@ -55817,7 +55819,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="B158" s="46" t="inlineStr">
@@ -55832,7 +55834,7 @@
       </c>
       <c r="D158" s="48" t="inlineStr">
         <is>
-          <t>Mengubah tampilan folder menjadi List View</t>
+          <t>Mengubah tampilan folder menjadi Grid View</t>
         </is>
       </c>
       <c r="E158" s="46" t="inlineStr">
@@ -55847,12 +55849,12 @@
       </c>
       <c r="G158" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon tampilan List pada halaman Marketing Toolkit.</t>
+          <t>1. Klik icon tampilan Grid pada halaman Marketing Toolkit.</t>
         </is>
       </c>
       <c r="H158" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengubah tampilan folder menjadi List View.</t>
+          <t>1. Berhasil mengubah tampilan folder menjadi Grid View.</t>
         </is>
       </c>
       <c r="I158" s="49" t="n"/>
@@ -55878,7 +55880,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="B159" s="46" t="inlineStr">
@@ -55893,7 +55895,7 @@
       </c>
       <c r="D159" s="48" t="inlineStr">
         <is>
-          <t>Mengubah tampilan folder menjadi Grid View</t>
+          <t>Membuka folder pada Marketing Toolkit</t>
         </is>
       </c>
       <c r="E159" s="46" t="inlineStr">
@@ -55903,17 +55905,17 @@
       </c>
       <c r="F159" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G159" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon tampilan Grid pada halaman Marketing Toolkit.</t>
+          <t>1. Klik salah satu folder pada daftar Folder.</t>
         </is>
       </c>
       <c r="H159" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengubah tampilan folder menjadi Grid View.</t>
+          <t>1. Berhasil membuka folder Marketing Toolkit.</t>
         </is>
       </c>
       <c r="I159" s="49" t="n"/>
@@ -55939,7 +55941,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="B160" s="46" t="inlineStr">
@@ -55954,7 +55956,7 @@
       </c>
       <c r="D160" s="48" t="inlineStr">
         <is>
-          <t>Membuka folder pada Marketing Toolkit</t>
+          <t>Mencari konten di dalam folder menggunakan Search Bar</t>
         </is>
       </c>
       <c r="E160" s="46" t="inlineStr">
@@ -55969,12 +55971,12 @@
       </c>
       <c r="G160" s="48" t="inlineStr">
         <is>
-          <t>1. Klik salah satu folder pada daftar Folder.</t>
+          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
         </is>
       </c>
       <c r="H160" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka folder Marketing Toolkit.</t>
+          <t>1. Berhasil menampilkan data yang sesuai dengan kata kunci pencarian.</t>
         </is>
       </c>
       <c r="I160" s="49" t="n"/>
@@ -56000,7 +56002,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="B161" s="46" t="inlineStr">
@@ -56015,27 +56017,27 @@
       </c>
       <c r="D161" s="48" t="inlineStr">
         <is>
-          <t>Mencari konten di dalam folder menggunakan Search Bar</t>
+          <t>Mencari konten di dalam folder dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E161" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F161" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G161" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
         </is>
       </c>
       <c r="H161" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data yang sesuai dengan kata kunci pencarian.</t>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
       <c r="I161" s="49" t="n"/>
@@ -56061,7 +56063,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="B162" s="46" t="inlineStr">
@@ -56076,27 +56078,27 @@
       </c>
       <c r="D162" s="48" t="inlineStr">
         <is>
-          <t>Mencari konten di dalam folder dengan keyword tidak valid</t>
+          <t>Melihat detail konten Marketing Toolkit</t>
         </is>
       </c>
       <c r="E162" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F162" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G162" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+          <t>1. Klik salah satu sub-folder pada daftar folder.</t>
         </is>
       </c>
       <c r="H162" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+          <t>1. Berhasil menampilkan detail konten Marketing Toolkit.</t>
         </is>
       </c>
       <c r="I162" s="49" t="n"/>
@@ -56122,7 +56124,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="B163" s="46" t="inlineStr">
@@ -56137,7 +56139,7 @@
       </c>
       <c r="D163" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail konten Marketing Toolkit</t>
+          <t>Mengunduh lampiran pada konten Marketing Toolkit</t>
         </is>
       </c>
       <c r="E163" s="46" t="inlineStr">
@@ -56152,12 +56154,14 @@
       </c>
       <c r="G163" s="48" t="inlineStr">
         <is>
-          <t>1. Klik salah satu sub-folder pada daftar folder.</t>
+          <t>1. Klik icon titik tiga pada salah satu lampiran.
+2. Pilih Download.</t>
         </is>
       </c>
       <c r="H163" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail konten Marketing Toolkit.</t>
+          <t>1. Berhasil menampilkan opsi aksi pada lampiran.
+2. Berhasil mengunduh lampiran ke perangkat.</t>
         </is>
       </c>
       <c r="I163" s="49" t="n"/>
@@ -56183,7 +56187,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="B164" s="46" t="inlineStr">
@@ -56198,7 +56202,7 @@
       </c>
       <c r="D164" s="48" t="inlineStr">
         <is>
-          <t>Mengunduh lampiran pada konten Marketing Toolkit</t>
+          <t>Berbagi lampiran pada konten Marketing Toolkit</t>
         </is>
       </c>
       <c r="E164" s="46" t="inlineStr">
@@ -56208,19 +56212,19 @@
       </c>
       <c r="F164" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G164" s="48" t="inlineStr">
         <is>
           <t>1. Klik icon titik tiga pada salah satu lampiran.
-2. Pilih Download.</t>
+2. Pilih Share.</t>
         </is>
       </c>
       <c r="H164" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan opsi aksi pada lampiran.
-2. Berhasil mengunduh lampiran ke perangkat.</t>
+2. Berhasil menampilkan pilihan aplikasi berbagi.</t>
         </is>
       </c>
       <c r="I164" s="49" t="n"/>
@@ -56246,22 +56250,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="B165" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Sales Force</t>
         </is>
       </c>
       <c r="C165" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Dashboard Sales Code</t>
         </is>
       </c>
       <c r="D165" s="48" t="inlineStr">
         <is>
-          <t>Berbagi lampiran pada konten Marketing Toolkit</t>
+          <t>Membuka halaman Dashboard Sales Code</t>
         </is>
       </c>
       <c r="E165" s="46" t="inlineStr">
@@ -56271,19 +56275,19 @@
       </c>
       <c r="F165" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G165" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon titik tiga pada salah satu lampiran.
-2. Pilih Share.</t>
+          <t>1. Buka menu Lainnya.
+2. Klik menu Dashboard Sales Code.</t>
         </is>
       </c>
       <c r="H165" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan opsi aksi pada lampiran.
-2. Berhasil menampilkan pilihan aplikasi berbagi.</t>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman Dashboard Sales Code.</t>
         </is>
       </c>
       <c r="I165" s="49" t="n"/>
@@ -56309,7 +56313,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="B166" s="46" t="inlineStr">
@@ -56324,7 +56328,7 @@
       </c>
       <c r="D166" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Dashboard Sales Code</t>
+          <t>Melihat detail Voa Realization</t>
         </is>
       </c>
       <c r="E166" s="46" t="inlineStr">
@@ -56339,14 +56343,12 @@
       </c>
       <c r="G166" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Dashboard Sales Code.</t>
+          <t>1. Klik icon expand pada card Voa Realization.</t>
         </is>
       </c>
       <c r="H166" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Dashboard Sales Code.</t>
+          <t>1. Berhasil menampilkan detail Voa Realization.</t>
         </is>
       </c>
       <c r="I166" s="49" t="n"/>
@@ -56372,7 +56374,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="B167" s="46" t="inlineStr">
@@ -56387,7 +56389,7 @@
       </c>
       <c r="D167" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail Voa Realization</t>
+          <t>Melihat Daftar Pipeline pada Voa Realization</t>
         </is>
       </c>
       <c r="E167" s="46" t="inlineStr">
@@ -56402,12 +56404,14 @@
       </c>
       <c r="G167" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Voa Realization.</t>
+          <t>1. Klik icon expand pada card Voa Realization.
+2. Klik Lihat Daftar Pipeline.</t>
         </is>
       </c>
       <c r="H167" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Voa Realization.</t>
+          <t>1. Berhasil menampilkan detail Voa Realization.
+2. Berhasil menampilkan Daftar Pipeline.</t>
         </is>
       </c>
       <c r="I167" s="49" t="n"/>
@@ -56433,7 +56437,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="B168" s="46" t="inlineStr">
@@ -56448,7 +56452,7 @@
       </c>
       <c r="D168" s="48" t="inlineStr">
         <is>
-          <t>Melihat Daftar Pipeline pada Voa Realization</t>
+          <t>Melihat detail CIF Kelolaan</t>
         </is>
       </c>
       <c r="E168" s="46" t="inlineStr">
@@ -56458,19 +56462,17 @@
       </c>
       <c r="F168" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G168" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Voa Realization.
-2. Klik Lihat Daftar Pipeline.</t>
+          <t>1. Klik icon expand pada card CIF Kelolaan.</t>
         </is>
       </c>
       <c r="H168" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Voa Realization.
-2. Berhasil menampilkan Daftar Pipeline.</t>
+          <t>1. Berhasil menampilkan detail CIF Kelolaan.</t>
         </is>
       </c>
       <c r="I168" s="49" t="n"/>
@@ -56496,7 +56498,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="B169" s="46" t="inlineStr">
@@ -56511,7 +56513,7 @@
       </c>
       <c r="D169" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail CIF Kelolaan</t>
+          <t>Melihat detail Realisasi Konek E-Channel</t>
         </is>
       </c>
       <c r="E169" s="46" t="inlineStr">
@@ -56521,17 +56523,17 @@
       </c>
       <c r="F169" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G169" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card CIF Kelolaan.</t>
+          <t>1. Klik icon expand pada card Realisasi Konek E-Channel.</t>
         </is>
       </c>
       <c r="H169" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail CIF Kelolaan.</t>
+          <t>1. Berhasil menampilkan detail Realisasi Konek E-Channel.</t>
         </is>
       </c>
       <c r="I169" s="49" t="n"/>
@@ -56557,7 +56559,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="B170" s="46" t="inlineStr">
@@ -56572,7 +56574,7 @@
       </c>
       <c r="D170" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail Realisasi Konek E-Channel</t>
+          <t>Melihat detail Realisasi Akuisisi Merchant</t>
         </is>
       </c>
       <c r="E170" s="46" t="inlineStr">
@@ -56587,12 +56589,12 @@
       </c>
       <c r="G170" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Realisasi Konek E-Channel.</t>
+          <t>1. Klik icon expand pada card Realisasi Akuisisi Merchant.</t>
         </is>
       </c>
       <c r="H170" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Realisasi Konek E-Channel.</t>
+          <t>1. Berhasil menampilkan detail Realisasi Akuisisi Merchant.</t>
         </is>
       </c>
       <c r="I170" s="49" t="n"/>
@@ -56618,7 +56620,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="B171" s="46" t="inlineStr">
@@ -56633,7 +56635,7 @@
       </c>
       <c r="D171" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail Realisasi Akuisisi Merchant</t>
+          <t>Melihat detail Eligible Upgrade to Prospera/Prioritas</t>
         </is>
       </c>
       <c r="E171" s="46" t="inlineStr">
@@ -56648,12 +56650,12 @@
       </c>
       <c r="G171" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Realisasi Akuisisi Merchant.</t>
+          <t>1. Klik icon expand pada card Eligible Upgrade to Prospera/Prioritas.</t>
         </is>
       </c>
       <c r="H171" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Realisasi Akuisisi Merchant.</t>
+          <t>1. Berhasil menampilkan detail Eligible Upgrade to Prospera &amp; Prioritas.</t>
         </is>
       </c>
       <c r="I171" s="49" t="n"/>
@@ -56676,67 +56678,6 @@
       <c r="Z171" s="49" t="n"/>
       <c r="AA171" s="49" t="n"/>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>17.7</t>
-        </is>
-      </c>
-      <c r="B172" s="46" t="inlineStr">
-        <is>
-          <t>Sales Force</t>
-        </is>
-      </c>
-      <c r="C172" s="46" t="inlineStr">
-        <is>
-          <t>Dashboard Sales Code</t>
-        </is>
-      </c>
-      <c r="D172" s="48" t="inlineStr">
-        <is>
-          <t>Melihat detail Eligible Upgrade to Prospera/Prioritas</t>
-        </is>
-      </c>
-      <c r="E172" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F172" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G172" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik icon expand pada card Eligible Upgrade to Prospera/Prioritas.</t>
-        </is>
-      </c>
-      <c r="H172" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan detail Eligible Upgrade to Prospera &amp; Prioritas.</t>
-        </is>
-      </c>
-      <c r="I172" s="49" t="n"/>
-      <c r="J172" s="49" t="n"/>
-      <c r="K172" s="49" t="n"/>
-      <c r="L172" s="49" t="n"/>
-      <c r="M172" s="49" t="n"/>
-      <c r="N172" s="49" t="n"/>
-      <c r="O172" s="49" t="n"/>
-      <c r="P172" s="49" t="n"/>
-      <c r="Q172" s="49" t="n"/>
-      <c r="R172" s="49" t="n"/>
-      <c r="S172" s="49" t="n"/>
-      <c r="T172" s="49" t="n"/>
-      <c r="U172" s="49" t="n"/>
-      <c r="V172" s="49" t="n"/>
-      <c r="W172" s="49" t="n"/>
-      <c r="X172" s="49" t="n"/>
-      <c r="Y172" s="49" t="n"/>
-      <c r="Z172" s="49" t="n"/>
-      <c r="AA172" s="49" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -20745,7 +20745,7 @@
       </c>
       <c r="D458" s="4" t="inlineStr">
         <is>
-          <t>Membatalkan pembatalan approval</t>
+          <t>Membatalkan approval yang sudah di reject</t>
         </is>
       </c>
       <c r="E458" s="3" t="inlineStr">
@@ -20760,13 +20760,13 @@
       </c>
       <c r="G458" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Cancel Approval.
-2. Klik No.</t>
+          <t>1. Klik button Cancel Approval pada data yang berstatus Rejected.
+2. Klik Yes pada pop up konfirmasi.</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr">
         <is>
-          <t>Berhasil status approval tidak berubah.</t>
+          <t>Berhasil membatalkan status Rejected dan status approval kembali menjadi Pending.</t>
         </is>
       </c>
     </row>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z918"/>
+  <dimension ref="A1:Z916"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="12.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35995,7 +35995,7 @@
       </c>
       <c r="D807" s="4" t="inlineStr">
         <is>
-          <t>Menampilkan data Pengaturan Funnel Funding berdasarkan section</t>
+          <t>Mengubah data Pengaturan Funnel Funding</t>
         </is>
       </c>
       <c r="E807" s="3" t="inlineStr">
@@ -36005,17 +36005,19 @@
       </c>
       <c r="F807" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G807" s="4" t="inlineStr">
         <is>
-          <t>1. Klik salah satu daftar section pada tabel.</t>
+          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H807" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data pengaturan funnel Funding.</t>
+          <t>1. Berhasil mengisi field Performance Percentage.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
@@ -36037,7 +36039,7 @@
       </c>
       <c r="D808" s="4" t="inlineStr">
         <is>
-          <t>Mengubah data Pengaturan Funnel Funding</t>
+          <t>Mengubah data Pengaturan Funnel Funding tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E808" s="3" t="inlineStr">
@@ -36052,14 +36054,14 @@
       </c>
       <c r="G808" s="4" t="inlineStr">
         <is>
-          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
+          <t>1. Mengosongkan field mandatory Performance Percentage.
 2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H808" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi field Performance Percentage.
-2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
+          <t>1. Berhasil mengosongkan field Performance Percentage.
+2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
@@ -36081,7 +36083,7 @@
       </c>
       <c r="D809" s="4" t="inlineStr">
         <is>
-          <t>Mengubah data Pengaturan Funnel Funding tanpa mengisi field mandatory</t>
+          <t>Menambahkan Condition pada Performance Indicator</t>
         </is>
       </c>
       <c r="E809" s="3" t="inlineStr">
@@ -36095,57 +36097,13 @@
         </is>
       </c>
       <c r="G809" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field mandatory Performance Percentage.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H809" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field Performance Percentage.
-2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="810" ht="42" customHeight="1">
-      <c r="A810" s="43" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
-      <c r="B810" s="3" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C810" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D810" s="4" t="inlineStr">
-        <is>
-          <t>Menambahkan Condition pada Performance Indicator</t>
-        </is>
-      </c>
-      <c r="E810" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F810" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G810" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Add Condition pada bagian Performance Indicator.
 2. Mengisi semua field mandatory pada condition baru.
 3. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H810" s="4" t="inlineStr">
+      <c r="H809" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan form condition baru pada Performance Indicator.
 2. Berhasil mengisi field mandatory condition.
@@ -36153,45 +36111,1863 @@
         </is>
       </c>
     </row>
+    <row r="810" ht="42" customHeight="1">
+      <c r="A810" s="43" t="inlineStr">
+        <is>
+          <t>64.5</t>
+        </is>
+      </c>
+      <c r="B810" s="3" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C810" s="3" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D810" s="4" t="inlineStr">
+        <is>
+          <t>Menghapus Condition pada Performance Indicator</t>
+        </is>
+      </c>
+      <c r="E810" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F810" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G810" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Remove pada salah satu condition di Performance Indicator.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H810" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menghapus condition dari Performance Indicator.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
+        </is>
+      </c>
+    </row>
     <row r="811" ht="28" customHeight="1">
       <c r="A811" s="43" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="B811" s="3" t="inlineStr">
         <is>
-          <t>Report Funding</t>
+          <t>Report Lending</t>
         </is>
       </c>
       <c r="C811" s="3" t="inlineStr">
         <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D811" s="4" t="inlineStr">
+        <is>
+          <t>Membuka halaman Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="E811" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F811" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G811" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Daily Sales Agenda.</t>
+        </is>
+      </c>
+      <c r="H811" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="812" ht="42" customHeight="1">
+      <c r="A812" s="43" t="inlineStr">
+        <is>
+          <t>65.2</t>
+        </is>
+      </c>
+      <c r="B812" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C812" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D812" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="E812" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F812" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G812" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengisi semua field filter mandatory.
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H812" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi field filter mandatory.
+2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="813" ht="28" customHeight="1">
+      <c r="A813" s="43" t="inlineStr">
+        <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="B813" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C813" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D813" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E813" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F813" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G813" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengosongkan field filter mandatory.
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H813" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan field filter mandatory.
+2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="814" ht="28" customHeight="1">
+      <c r="A814" s="43" t="inlineStr">
+        <is>
+          <t>65.4</t>
+        </is>
+      </c>
+      <c r="B814" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C814" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D814" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data tab Prospek Masuk</t>
+        </is>
+      </c>
+      <c r="E814" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F814" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G814" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Masuk.</t>
+        </is>
+      </c>
+      <c r="H814" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data pada tab Prospek Masuk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="815" ht="56" customHeight="1">
+      <c r="A815" s="43" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="B815" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C815" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D815" s="4" t="inlineStr">
+        <is>
+          <t>Mencari data Prospek Masuk dengan keyword valid</t>
+        </is>
+      </c>
+      <c r="E815" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F815" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G815" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Masuk.
+2. Mengisi field Cari Data dengan keyword valid.
+3. Klik button Search.</t>
+        </is>
+      </c>
+      <c r="H815" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Masuk.
+2. Berhasil mengisi field Cari Data.
+3. Berhasil menampilkan data yang dicari.</t>
+        </is>
+      </c>
+    </row>
+    <row r="816" ht="56" customHeight="1">
+      <c r="A816" s="43" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="B816" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C816" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D816" s="4" t="inlineStr">
+        <is>
+          <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
+        </is>
+      </c>
+      <c r="E816" s="3" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F816" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G816" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Masuk.
+2. Mengisi field Cari Data dengan keyword tidak valid.
+3. Klik button Search.</t>
+        </is>
+      </c>
+      <c r="H816" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Masuk.
+2. Berhasil mengisi field Cari Data.
+3. Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="817" ht="28" customHeight="1">
+      <c r="A817" s="43" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="B817" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C817" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D817" s="4" t="inlineStr">
+        <is>
+          <t>Melihat detail Prospek Masuk</t>
+        </is>
+      </c>
+      <c r="E817" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F817" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G817" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Masuk.
+2. Klik salah satu nama prospek pada tabel.</t>
+        </is>
+      </c>
+      <c r="H817" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Masuk.
+2. Berhasil menampilkan halaman detail prospek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="818" ht="28" customHeight="1">
+      <c r="A818" s="43" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
+      </c>
+      <c r="B818" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C818" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D818" s="4" t="inlineStr">
+        <is>
+          <t>Mengekspor data tab Prospek Masuk</t>
+        </is>
+      </c>
+      <c r="E818" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F818" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G818" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Masuk.
+2. Klik button Export.
+3. Klik icon download pada panel Download Export.</t>
+        </is>
+      </c>
+      <c r="H818" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Masuk.
+2. Berhasil menampilkan panel Download Export.
+3. Berhasil mendownload file export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="819" ht="42" customHeight="1">
+      <c r="A819" s="43" t="inlineStr">
+        <is>
+          <t>65.9</t>
+        </is>
+      </c>
+      <c r="B819" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C819" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D819" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data tab Prospek Closing</t>
+        </is>
+      </c>
+      <c r="E819" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F819" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G819" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Closing.</t>
+        </is>
+      </c>
+      <c r="H819" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data pada tab Prospek Closing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="820" ht="14" customHeight="1">
+      <c r="A820" s="43" t="inlineStr">
+        <is>
+          <t>65.10</t>
+        </is>
+      </c>
+      <c r="B820" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C820" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D820" s="4" t="inlineStr">
+        <is>
+          <t>Mencari data Prospek Closing dengan keyword valid</t>
+        </is>
+      </c>
+      <c r="E820" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F820" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G820" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Closing.
+2. Mengisi field Cari Data dengan keyword valid.
+3. Klik button Search.</t>
+        </is>
+      </c>
+      <c r="H820" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Closing.
+2. Berhasil mengisi field Cari Data.
+3. Berhasil menampilkan data yang dicari.</t>
+        </is>
+      </c>
+    </row>
+    <row r="821" ht="56" customHeight="1">
+      <c r="A821" s="43" t="inlineStr">
+        <is>
+          <t>65.11</t>
+        </is>
+      </c>
+      <c r="B821" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C821" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D821" s="4" t="inlineStr">
+        <is>
+          <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
+        </is>
+      </c>
+      <c r="E821" s="3" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F821" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G821" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Closing.
+2. Mengisi field Cari Data dengan keyword tidak valid.
+3. Klik button Search.</t>
+        </is>
+      </c>
+      <c r="H821" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Closing.
+2. Berhasil mengisi field Cari Data.
+3. Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="822" ht="56" customHeight="1">
+      <c r="A822" s="43" t="inlineStr">
+        <is>
+          <t>65.12</t>
+        </is>
+      </c>
+      <c r="B822" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C822" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D822" s="4" t="inlineStr">
+        <is>
+          <t>Melihat detail Prospek Closing</t>
+        </is>
+      </c>
+      <c r="E822" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F822" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G822" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Closing.
+2. Klik salah satu nama prospek pada tabel.</t>
+        </is>
+      </c>
+      <c r="H822" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Closing.
+2. Berhasil menampilkan halaman detail prospek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="823" ht="56" customHeight="1">
+      <c r="A823" s="43" t="inlineStr">
+        <is>
+          <t>65.13</t>
+        </is>
+      </c>
+      <c r="B823" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C823" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D823" s="4" t="inlineStr">
+        <is>
+          <t>Mengekspor data tab Prospek Closing</t>
+        </is>
+      </c>
+      <c r="E823" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F823" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G823" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Closing.
+2. Klik button Export.
+3. Klik icon download pada panel Download Export.</t>
+        </is>
+      </c>
+      <c r="H823" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Closing.
+2. Berhasil menampilkan panel Download Export.
+3. Berhasil mendownload file export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="824" ht="14" customHeight="1">
+      <c r="A824" s="43" t="inlineStr">
+        <is>
+          <t>65.14</t>
+        </is>
+      </c>
+      <c r="B824" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C824" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D824" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data tab Prospek Referal</t>
+        </is>
+      </c>
+      <c r="E824" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F824" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G824" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal.</t>
+        </is>
+      </c>
+      <c r="H824" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data pada tab Prospek Referal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="825" ht="14" customHeight="1">
+      <c r="A825" s="43" t="inlineStr">
+        <is>
+          <t>65.15</t>
+        </is>
+      </c>
+      <c r="B825" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C825" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D825" s="4" t="inlineStr">
+        <is>
+          <t>Mencari data Prospek Referal dengan keyword valid</t>
+        </is>
+      </c>
+      <c r="E825" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F825" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G825" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal.
+2. Mengisi field Cari Data dengan keyword valid.
+3. Klik button Search.</t>
+        </is>
+      </c>
+      <c r="H825" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Referal.
+2. Berhasil mengisi field Cari Data.
+3. Berhasil menampilkan data yang dicari.</t>
+        </is>
+      </c>
+    </row>
+    <row r="826" ht="14" customHeight="1">
+      <c r="A826" s="43" t="inlineStr">
+        <is>
+          <t>65.16</t>
+        </is>
+      </c>
+      <c r="B826" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C826" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D826" s="4" t="inlineStr">
+        <is>
+          <t>Mencari data Prospek Referal dengan keyword tidak valid</t>
+        </is>
+      </c>
+      <c r="E826" s="3" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F826" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G826" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal.
+2. Mengisi field Cari Data dengan keyword tidak valid.
+3. Klik button Search.</t>
+        </is>
+      </c>
+      <c r="H826" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Referal.
+2. Berhasil mengisi field Cari Data.
+3. Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="827" ht="42" customHeight="1">
+      <c r="A827" s="43" t="inlineStr">
+        <is>
+          <t>65.17</t>
+        </is>
+      </c>
+      <c r="B827" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C827" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D827" s="4" t="inlineStr">
+        <is>
+          <t>Melihat detail Prospek Referal</t>
+        </is>
+      </c>
+      <c r="E827" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F827" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G827" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal.
+2. Klik salah satu nama prospek pada tabel.</t>
+        </is>
+      </c>
+      <c r="H827" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Referal.
+2. Berhasil menampilkan halaman detail prospek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="828" ht="14" customHeight="1">
+      <c r="A828" s="43" t="inlineStr">
+        <is>
+          <t>65.18</t>
+        </is>
+      </c>
+      <c r="B828" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C828" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D828" s="4" t="inlineStr">
+        <is>
+          <t>Mengekspor data tab Prospek Referal</t>
+        </is>
+      </c>
+      <c r="E828" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F828" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G828" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal.
+2. Klik button Export.
+3. Klik icon download pada panel Download Export.</t>
+        </is>
+      </c>
+      <c r="H828" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Referal.
+2. Berhasil menampilkan panel Download Export.
+3. Berhasil mendownload file export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="829" ht="56" customHeight="1">
+      <c r="A829" s="43" t="inlineStr">
+        <is>
+          <t>65.19</t>
+        </is>
+      </c>
+      <c r="B829" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C829" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D829" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data tab Prospek Referal Closing</t>
+        </is>
+      </c>
+      <c r="E829" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F829" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G829" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal Closing.</t>
+        </is>
+      </c>
+      <c r="H829" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="830" ht="28" customHeight="1">
+      <c r="A830" s="43" t="inlineStr">
+        <is>
+          <t>65.20</t>
+        </is>
+      </c>
+      <c r="B830" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C830" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D830" s="4" t="inlineStr">
+        <is>
+          <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
+        </is>
+      </c>
+      <c r="E830" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F830" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G830" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal Closing.
+2. Mengisi field Cari Data dengan keyword valid.
+3. Klik button Search.</t>
+        </is>
+      </c>
+      <c r="H830" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Referal Closing.
+2. Berhasil mengisi field Cari Data.
+3. Berhasil menampilkan data yang dicari.</t>
+        </is>
+      </c>
+    </row>
+    <row r="831" ht="42" customHeight="1">
+      <c r="A831" s="43" t="inlineStr">
+        <is>
+          <t>65.21</t>
+        </is>
+      </c>
+      <c r="B831" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C831" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D831" s="4" t="inlineStr">
+        <is>
+          <t>Mencari data Prospek Referal Closing dengan keyword tidak valid</t>
+        </is>
+      </c>
+      <c r="E831" s="3" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F831" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G831" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal Closing.
+2. Mengisi field Cari Data dengan keyword tidak valid.
+3. Klik button Search.</t>
+        </is>
+      </c>
+      <c r="H831" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Referal Closing.
+2. Berhasil mengisi field Cari Data.
+3. Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="832" ht="28" customHeight="1">
+      <c r="A832" s="43" t="inlineStr">
+        <is>
+          <t>65.22</t>
+        </is>
+      </c>
+      <c r="B832" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C832" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D832" s="4" t="inlineStr">
+        <is>
+          <t>Melihat detail Prospek Referal Closing</t>
+        </is>
+      </c>
+      <c r="E832" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F832" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G832" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal Closing.
+2. Klik salah satu nama prospek pada tabel.</t>
+        </is>
+      </c>
+      <c r="H832" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Referal Closing.
+2. Berhasil menampilkan halaman detail prospek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="833" ht="14" customHeight="1">
+      <c r="A833" s="43" t="inlineStr">
+        <is>
+          <t>65.23</t>
+        </is>
+      </c>
+      <c r="B833" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C833" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D833" s="4" t="inlineStr">
+        <is>
+          <t>Mengekspor data tab Prospek Referal Closing</t>
+        </is>
+      </c>
+      <c r="E833" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F833" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G833" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal Closing.
+2. Klik button Export.
+3. Klik icon download pada panel Download Export.</t>
+        </is>
+      </c>
+      <c r="H833" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Referal Closing.
+2. Berhasil menampilkan panel Download Export.
+3. Berhasil mendownload file export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="834" ht="14" customHeight="1">
+      <c r="A834" s="43" t="inlineStr">
+        <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="B834" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C834" s="3" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D834" s="4" t="inlineStr">
+        <is>
+          <t>Membuka halaman Personal Funnel</t>
+        </is>
+      </c>
+      <c r="E834" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F834" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G834" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Personal Funnel.</t>
+        </is>
+      </c>
+      <c r="H834" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Personal Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="835" ht="14" customHeight="1">
+      <c r="A835" s="43" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="B835" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C835" s="3" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D835" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Personal Funnel</t>
+        </is>
+      </c>
+      <c r="E835" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F835" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G835" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengisi semua field filter mandatory.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H835" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi field filter mandatory.
+2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="836" ht="42" customHeight="1">
+      <c r="A836" s="43" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="B836" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C836" s="3" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D836" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E836" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F836" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G836" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengosongkan field filter mandatory.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H836" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan field filter mandatory.
+2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="837" ht="28" customHeight="1">
+      <c r="A837" s="43" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="B837" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C837" s="3" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D837" s="4" t="inlineStr">
+        <is>
+          <t>Mengekspor data Personal Funnel</t>
+        </is>
+      </c>
+      <c r="E837" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F837" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G837" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Export.
+2. Klik icon download pada panel Download Export.</t>
+        </is>
+      </c>
+      <c r="H837" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan panel Download Export.
+2. Berhasil mendownload file export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="838" ht="28" customHeight="1">
+      <c r="A838" s="43" t="inlineStr">
+        <is>
+          <t>67.1</t>
+        </is>
+      </c>
+      <c r="B838" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C838" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D838" s="4" t="inlineStr">
+        <is>
+          <t>Membuka halaman Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E838" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F838" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G838" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Rekap Funnel.</t>
+        </is>
+      </c>
+      <c r="H838" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Rekap Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="839" ht="70" customHeight="1">
+      <c r="A839" s="43" t="inlineStr">
+        <is>
+          <t>67.2</t>
+        </is>
+      </c>
+      <c r="B839" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C839" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D839" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E839" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F839" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G839" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun).
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H839" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi field filter mandatory.
+2. Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="840" ht="28" customHeight="1">
+      <c r="A840" s="43" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="B840" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C840" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D840" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E840" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F840" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G840" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H840" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi kriteria filter.
+2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="841" ht="84" customHeight="1">
+      <c r="A841" s="43" t="inlineStr">
+        <is>
+          <t>67.4</t>
+        </is>
+      </c>
+      <c r="B841" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C841" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D841" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E841" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F841" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G841" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengosongkan field filter mandatory.
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H841" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan field filter mandatory.
+2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="842" ht="28" customHeight="1">
+      <c r="A842" s="43" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="B842" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C842" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D842" s="4" t="inlineStr">
+        <is>
+          <t>Mengunduh data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E842" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F842" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G842" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Download Excel.</t>
+        </is>
+      </c>
+      <c r="H842" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mendownload file Excel data Rekap Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="843" ht="28" customHeight="1">
+      <c r="A843" s="43" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="B843" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C843" s="3" t="inlineStr">
+        <is>
+          <t>Regional Funnel</t>
+        </is>
+      </c>
+      <c r="D843" s="4" t="inlineStr">
+        <is>
+          <t>Membuka halaman Regional Funnel</t>
+        </is>
+      </c>
+      <c r="E843" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F843" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G843" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Regional Funnel.</t>
+        </is>
+      </c>
+      <c r="H843" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Regional Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="844" ht="28" customHeight="1">
+      <c r="A844" s="43" t="inlineStr">
+        <is>
+          <t>68.2</t>
+        </is>
+      </c>
+      <c r="B844" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C844" s="3" t="inlineStr">
+        <is>
+          <t>Regional Funnel</t>
+        </is>
+      </c>
+      <c r="D844" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Regional Funnel</t>
+        </is>
+      </c>
+      <c r="E844" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F844" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G844" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengisi semua field filter mandatory.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H844" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi field filter mandatory.
+2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="845" ht="42" customHeight="1">
+      <c r="A845" s="43" t="inlineStr">
+        <is>
+          <t>68.3</t>
+        </is>
+      </c>
+      <c r="B845" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C845" s="3" t="inlineStr">
+        <is>
+          <t>Regional Funnel</t>
+        </is>
+      </c>
+      <c r="D845" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E845" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F845" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G845" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengosongkan field filter mandatory.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H845" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan field filter mandatory.
+2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="846" ht="28" customHeight="1">
+      <c r="A846" s="43" t="inlineStr">
+        <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="B846" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C846" s="3" t="inlineStr">
+        <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D811" s="4" t="inlineStr">
+      <c r="D846" s="4" t="inlineStr">
+        <is>
+          <t>Membuka halaman Pengaturan Funnel Lending</t>
+        </is>
+      </c>
+      <c r="E846" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F846" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G846" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Pengaturan Funnel.</t>
+        </is>
+      </c>
+      <c r="H846" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Pengaturan Funnel Lending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="847" ht="14" customHeight="1">
+      <c r="A847" s="43" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="B847" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C847" s="3" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D847" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data Pengaturan Funnel Lending berdasarkan section</t>
+        </is>
+      </c>
+      <c r="E847" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F847" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G847" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik salah satu daftar section pada tabel.</t>
+        </is>
+      </c>
+      <c r="H847" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data pengaturan funnel Lending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="848" ht="14" customHeight="1">
+      <c r="A848" s="43" t="inlineStr">
+        <is>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="B848" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C848" s="3" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D848" s="4" t="inlineStr">
+        <is>
+          <t>Mengubah data Pengaturan Funnel Lending</t>
+        </is>
+      </c>
+      <c r="E848" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F848" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G848" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H848" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi field Performance Percentage.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="849" ht="42" customHeight="1">
+      <c r="A849" s="43" t="inlineStr">
+        <is>
+          <t>69.4</t>
+        </is>
+      </c>
+      <c r="B849" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C849" s="3" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D849" s="4" t="inlineStr">
+        <is>
+          <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E849" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F849" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G849" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengosongkan field mandatory Performance Percentage.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H849" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan field Performance Percentage.
+2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="850" ht="28" customHeight="1">
+      <c r="A850" s="43" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="B850" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C850" s="3" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D850" s="4" t="inlineStr">
+        <is>
+          <t>Menambahkan Condition pada Performance Indicator</t>
+        </is>
+      </c>
+      <c r="E850" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F850" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G850" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Add Condition pada bagian Performance Indicator.
+2. Mengisi semua field mandatory pada condition baru.
+3. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H850" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan form condition baru pada Performance Indicator.
+2. Berhasil mengisi field mandatory condition.
+3. Berhasil menyimpan condition baru pada Performance Indicator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="851" ht="28" customHeight="1">
+      <c r="A851" s="43" t="inlineStr">
+        <is>
+          <t>69.6</t>
+        </is>
+      </c>
+      <c r="B851" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C851" s="3" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D851" s="4" t="inlineStr">
         <is>
           <t>Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E811" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F811" s="3" t="inlineStr">
+      <c r="E851" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F851" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G811" s="4" t="inlineStr">
+      <c r="G851" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Add Condition pada bagian Performance Indicator.
 2. Mengosongkan field mandatory pada condition baru.
 3. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H811" s="4" t="inlineStr">
+      <c r="H851" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan form condition baru pada Performance Indicator.
 2. Berhasil mengosongkan field mandatory condition.
@@ -36199,1843 +37975,69 @@
         </is>
       </c>
     </row>
-    <row r="812" ht="42" customHeight="1">
-      <c r="A812" s="43" t="inlineStr">
-        <is>
-          <t>64.7</t>
-        </is>
-      </c>
-      <c r="B812" s="3" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C812" s="3" t="inlineStr">
+    <row r="852" ht="28" customHeight="1">
+      <c r="A852" s="43" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="B852" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C852" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D812" s="4" t="inlineStr">
+      <c r="D852" s="4" t="inlineStr">
         <is>
           <t>Menghapus Condition pada Performance Indicator</t>
         </is>
       </c>
-      <c r="E812" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F812" s="3" t="inlineStr">
+      <c r="E852" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F852" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G812" s="4" t="inlineStr">
+      <c r="G852" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Remove pada salah satu condition di Performance Indicator.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H812" s="4" t="inlineStr">
+      <c r="H852" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menghapus condition dari Performance Indicator.
-2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="813" ht="28" customHeight="1">
-      <c r="A813" s="43" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
-      <c r="B813" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C813" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D813" s="4" t="inlineStr">
-        <is>
-          <t>Membuka halaman Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="E813" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F813" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G813" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Daily Sales Agenda.</t>
-        </is>
-      </c>
-      <c r="H813" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
-        </is>
-      </c>
-    </row>
-    <row r="814" ht="28" customHeight="1">
-      <c r="A814" s="43" t="inlineStr">
-        <is>
-          <t>65.2</t>
-        </is>
-      </c>
-      <c r="B814" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C814" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D814" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="E814" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F814" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G814" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi semua field filter mandatory.
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H814" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="815" ht="56" customHeight="1">
-      <c r="A815" s="43" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
-      <c r="B815" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C815" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D815" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E815" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F815" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G815" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H815" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="816" ht="56" customHeight="1">
-      <c r="A816" s="43" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
-      </c>
-      <c r="B816" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C816" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D816" s="4" t="inlineStr">
-        <is>
-          <t>Menampilkan data tab Prospek Masuk</t>
-        </is>
-      </c>
-      <c r="E816" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F816" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G816" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Masuk.</t>
-        </is>
-      </c>
-      <c r="H816" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data pada tab Prospek Masuk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="817" ht="28" customHeight="1">
-      <c r="A817" s="43" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="B817" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C817" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D817" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data Prospek Masuk dengan keyword valid</t>
-        </is>
-      </c>
-      <c r="E817" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F817" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G817" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Masuk.
-2. Mengisi field Cari Data dengan keyword valid.
-3. Klik button Search.</t>
-        </is>
-      </c>
-      <c r="H817" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Masuk.
-2. Berhasil mengisi field Cari Data.
-3. Berhasil menampilkan data yang dicari.</t>
-        </is>
-      </c>
-    </row>
-    <row r="818" ht="28" customHeight="1">
-      <c r="A818" s="43" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="B818" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C818" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D818" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
-        </is>
-      </c>
-      <c r="E818" s="3" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F818" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G818" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Masuk.
-2. Mengisi field Cari Data dengan keyword tidak valid.
-3. Klik button Search.</t>
-        </is>
-      </c>
-      <c r="H818" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Masuk.
-2. Berhasil mengisi field Cari Data.
-3. Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="819" ht="42" customHeight="1">
-      <c r="A819" s="43" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="B819" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C819" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D819" s="4" t="inlineStr">
-        <is>
-          <t>Melihat detail Prospek Masuk</t>
-        </is>
-      </c>
-      <c r="E819" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F819" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G819" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Masuk.
-2. Klik salah satu nama prospek pada tabel.</t>
-        </is>
-      </c>
-      <c r="H819" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Masuk.
-2. Berhasil menampilkan halaman detail prospek.</t>
-        </is>
-      </c>
-    </row>
-    <row r="820" ht="14" customHeight="1">
-      <c r="A820" s="43" t="inlineStr">
-        <is>
-          <t>65.8</t>
-        </is>
-      </c>
-      <c r="B820" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C820" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D820" s="4" t="inlineStr">
-        <is>
-          <t>Mengekspor data tab Prospek Masuk</t>
-        </is>
-      </c>
-      <c r="E820" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F820" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G820" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Masuk.
-2. Klik button Export.
-3. Klik icon download pada panel Download Export.</t>
-        </is>
-      </c>
-      <c r="H820" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Masuk.
-2. Berhasil menampilkan panel Download Export.
-3. Berhasil mendownload file export.</t>
-        </is>
-      </c>
-    </row>
-    <row r="821" ht="56" customHeight="1">
-      <c r="A821" s="43" t="inlineStr">
-        <is>
-          <t>65.9</t>
-        </is>
-      </c>
-      <c r="B821" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C821" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D821" s="4" t="inlineStr">
-        <is>
-          <t>Menampilkan data tab Prospek Closing</t>
-        </is>
-      </c>
-      <c r="E821" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F821" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G821" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Closing.</t>
-        </is>
-      </c>
-      <c r="H821" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data pada tab Prospek Closing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="822" ht="56" customHeight="1">
-      <c r="A822" s="43" t="inlineStr">
-        <is>
-          <t>65.10</t>
-        </is>
-      </c>
-      <c r="B822" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C822" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D822" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data Prospek Closing dengan keyword valid</t>
-        </is>
-      </c>
-      <c r="E822" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F822" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G822" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Closing.
-2. Mengisi field Cari Data dengan keyword valid.
-3. Klik button Search.</t>
-        </is>
-      </c>
-      <c r="H822" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Closing.
-2. Berhasil mengisi field Cari Data.
-3. Berhasil menampilkan data yang dicari.</t>
-        </is>
-      </c>
-    </row>
-    <row r="823" ht="56" customHeight="1">
-      <c r="A823" s="43" t="inlineStr">
-        <is>
-          <t>65.11</t>
-        </is>
-      </c>
-      <c r="B823" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C823" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D823" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
-        </is>
-      </c>
-      <c r="E823" s="3" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F823" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G823" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Closing.
-2. Mengisi field Cari Data dengan keyword tidak valid.
-3. Klik button Search.</t>
-        </is>
-      </c>
-      <c r="H823" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Closing.
-2. Berhasil mengisi field Cari Data.
-3. Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="824" ht="14" customHeight="1">
-      <c r="A824" s="43" t="inlineStr">
-        <is>
-          <t>65.12</t>
-        </is>
-      </c>
-      <c r="B824" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C824" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D824" s="4" t="inlineStr">
-        <is>
-          <t>Melihat detail Prospek Closing</t>
-        </is>
-      </c>
-      <c r="E824" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F824" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G824" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Closing.
-2. Klik salah satu nama prospek pada tabel.</t>
-        </is>
-      </c>
-      <c r="H824" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Closing.
-2. Berhasil menampilkan halaman detail prospek.</t>
-        </is>
-      </c>
-    </row>
-    <row r="825" ht="14" customHeight="1">
-      <c r="A825" s="43" t="inlineStr">
-        <is>
-          <t>65.13</t>
-        </is>
-      </c>
-      <c r="B825" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C825" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D825" s="4" t="inlineStr">
-        <is>
-          <t>Mengekspor data tab Prospek Closing</t>
-        </is>
-      </c>
-      <c r="E825" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F825" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G825" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Closing.
-2. Klik button Export.
-3. Klik icon download pada panel Download Export.</t>
-        </is>
-      </c>
-      <c r="H825" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Closing.
-2. Berhasil menampilkan panel Download Export.
-3. Berhasil mendownload file export.</t>
-        </is>
-      </c>
-    </row>
-    <row r="826" ht="14" customHeight="1">
-      <c r="A826" s="43" t="inlineStr">
-        <is>
-          <t>65.14</t>
-        </is>
-      </c>
-      <c r="B826" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C826" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D826" s="4" t="inlineStr">
-        <is>
-          <t>Menampilkan data tab Prospek Referal</t>
-        </is>
-      </c>
-      <c r="E826" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F826" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G826" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal.</t>
-        </is>
-      </c>
-      <c r="H826" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data pada tab Prospek Referal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="827" ht="42" customHeight="1">
-      <c r="A827" s="43" t="inlineStr">
-        <is>
-          <t>65.15</t>
-        </is>
-      </c>
-      <c r="B827" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C827" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D827" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data Prospek Referal dengan keyword valid</t>
-        </is>
-      </c>
-      <c r="E827" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F827" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G827" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal.
-2. Mengisi field Cari Data dengan keyword valid.
-3. Klik button Search.</t>
-        </is>
-      </c>
-      <c r="H827" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Referal.
-2. Berhasil mengisi field Cari Data.
-3. Berhasil menampilkan data yang dicari.</t>
-        </is>
-      </c>
-    </row>
-    <row r="828" ht="14" customHeight="1">
-      <c r="A828" s="43" t="inlineStr">
-        <is>
-          <t>65.16</t>
-        </is>
-      </c>
-      <c r="B828" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C828" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D828" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data Prospek Referal dengan keyword tidak valid</t>
-        </is>
-      </c>
-      <c r="E828" s="3" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F828" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G828" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal.
-2. Mengisi field Cari Data dengan keyword tidak valid.
-3. Klik button Search.</t>
-        </is>
-      </c>
-      <c r="H828" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Referal.
-2. Berhasil mengisi field Cari Data.
-3. Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="829" ht="56" customHeight="1">
-      <c r="A829" s="43" t="inlineStr">
-        <is>
-          <t>65.17</t>
-        </is>
-      </c>
-      <c r="B829" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C829" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D829" s="4" t="inlineStr">
-        <is>
-          <t>Melihat detail Prospek Referal</t>
-        </is>
-      </c>
-      <c r="E829" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F829" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G829" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal.
-2. Klik salah satu nama prospek pada tabel.</t>
-        </is>
-      </c>
-      <c r="H829" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Referal.
-2. Berhasil menampilkan halaman detail prospek.</t>
-        </is>
-      </c>
-    </row>
-    <row r="830" ht="28" customHeight="1">
-      <c r="A830" s="43" t="inlineStr">
-        <is>
-          <t>65.18</t>
-        </is>
-      </c>
-      <c r="B830" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C830" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D830" s="4" t="inlineStr">
-        <is>
-          <t>Mengekspor data tab Prospek Referal</t>
-        </is>
-      </c>
-      <c r="E830" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F830" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G830" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal.
-2. Klik button Export.
-3. Klik icon download pada panel Download Export.</t>
-        </is>
-      </c>
-      <c r="H830" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Referal.
-2. Berhasil menampilkan panel Download Export.
-3. Berhasil mendownload file export.</t>
-        </is>
-      </c>
-    </row>
-    <row r="831" ht="42" customHeight="1">
-      <c r="A831" s="43" t="inlineStr">
-        <is>
-          <t>65.19</t>
-        </is>
-      </c>
-      <c r="B831" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C831" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D831" s="4" t="inlineStr">
-        <is>
-          <t>Menampilkan data tab Prospek Referal Closing</t>
-        </is>
-      </c>
-      <c r="E831" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F831" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G831" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal Closing.</t>
-        </is>
-      </c>
-      <c r="H831" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="832" ht="28" customHeight="1">
-      <c r="A832" s="43" t="inlineStr">
-        <is>
-          <t>65.20</t>
-        </is>
-      </c>
-      <c r="B832" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C832" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D832" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
-        </is>
-      </c>
-      <c r="E832" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F832" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G832" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal Closing.
-2. Mengisi field Cari Data dengan keyword valid.
-3. Klik button Search.</t>
-        </is>
-      </c>
-      <c r="H832" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Referal Closing.
-2. Berhasil mengisi field Cari Data.
-3. Berhasil menampilkan data yang dicari.</t>
-        </is>
-      </c>
-    </row>
-    <row r="833" ht="14" customHeight="1">
-      <c r="A833" s="43" t="inlineStr">
-        <is>
-          <t>65.21</t>
-        </is>
-      </c>
-      <c r="B833" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C833" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D833" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data Prospek Referal Closing dengan keyword tidak valid</t>
-        </is>
-      </c>
-      <c r="E833" s="3" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F833" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G833" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal Closing.
-2. Mengisi field Cari Data dengan keyword tidak valid.
-3. Klik button Search.</t>
-        </is>
-      </c>
-      <c r="H833" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Referal Closing.
-2. Berhasil mengisi field Cari Data.
-3. Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="834" ht="14" customHeight="1">
-      <c r="A834" s="43" t="inlineStr">
-        <is>
-          <t>65.22</t>
-        </is>
-      </c>
-      <c r="B834" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C834" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D834" s="4" t="inlineStr">
-        <is>
-          <t>Melihat detail Prospek Referal Closing</t>
-        </is>
-      </c>
-      <c r="E834" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F834" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G834" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal Closing.
-2. Klik salah satu nama prospek pada tabel.</t>
-        </is>
-      </c>
-      <c r="H834" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Referal Closing.
-2. Berhasil menampilkan halaman detail prospek.</t>
-        </is>
-      </c>
-    </row>
-    <row r="835" ht="14" customHeight="1">
-      <c r="A835" s="43" t="inlineStr">
-        <is>
-          <t>65.23</t>
-        </is>
-      </c>
-      <c r="B835" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C835" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D835" s="4" t="inlineStr">
-        <is>
-          <t>Mengekspor data tab Prospek Referal Closing</t>
-        </is>
-      </c>
-      <c r="E835" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F835" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G835" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal Closing.
-2. Klik button Export.
-3. Klik icon download pada panel Download Export.</t>
-        </is>
-      </c>
-      <c r="H835" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Referal Closing.
-2. Berhasil menampilkan panel Download Export.
-3. Berhasil mendownload file export.</t>
-        </is>
-      </c>
-    </row>
-    <row r="836" ht="42" customHeight="1">
-      <c r="A836" s="43" t="inlineStr">
-        <is>
-          <t>66.1</t>
-        </is>
-      </c>
-      <c r="B836" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C836" s="3" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
-      <c r="D836" s="4" t="inlineStr">
-        <is>
-          <t>Membuka halaman Personal Funnel</t>
-        </is>
-      </c>
-      <c r="E836" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F836" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G836" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Personal Funnel.</t>
-        </is>
-      </c>
-      <c r="H836" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Personal Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="837" ht="28" customHeight="1">
-      <c r="A837" s="43" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="B837" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C837" s="3" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
-      <c r="D837" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Personal Funnel</t>
-        </is>
-      </c>
-      <c r="E837" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F837" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G837" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi semua field filter mandatory.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H837" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="838" ht="28" customHeight="1">
-      <c r="A838" s="43" t="inlineStr">
-        <is>
-          <t>66.3</t>
-        </is>
-      </c>
-      <c r="B838" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C838" s="3" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
-      <c r="D838" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E838" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F838" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G838" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H838" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="839" ht="70" customHeight="1">
-      <c r="A839" s="43" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="B839" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C839" s="3" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
-      <c r="D839" s="4" t="inlineStr">
-        <is>
-          <t>Mengekspor data Personal Funnel</t>
-        </is>
-      </c>
-      <c r="E839" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F839" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G839" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Export.
-2. Klik icon download pada panel Download Export.</t>
-        </is>
-      </c>
-      <c r="H839" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan panel Download Export.
-2. Berhasil mendownload file export.</t>
-        </is>
-      </c>
-    </row>
-    <row r="840" ht="28" customHeight="1">
-      <c r="A840" s="43" t="inlineStr">
-        <is>
-          <t>67.1</t>
-        </is>
-      </c>
-      <c r="B840" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C840" s="3" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D840" s="4" t="inlineStr">
-        <is>
-          <t>Membuka halaman Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E840" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F840" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G840" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Rekap Funnel.</t>
-        </is>
-      </c>
-      <c r="H840" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Rekap Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="841" ht="84" customHeight="1">
-      <c r="A841" s="43" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
-      </c>
-      <c r="B841" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C841" s="3" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D841" s="4" t="inlineStr">
-        <is>
-          <t>Menampilkan data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E841" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F841" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G841" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun).
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H841" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="842" ht="28" customHeight="1">
-      <c r="A842" s="43" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="B842" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C842" s="3" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D842" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E842" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F842" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G842" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H842" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi kriteria filter.
-2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="843" ht="28" customHeight="1">
-      <c r="A843" s="43" t="inlineStr">
-        <is>
-          <t>67.4</t>
-        </is>
-      </c>
-      <c r="B843" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C843" s="3" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D843" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E843" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F843" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G843" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H843" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="844" ht="28" customHeight="1">
-      <c r="A844" s="43" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
-      <c r="B844" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C844" s="3" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D844" s="4" t="inlineStr">
-        <is>
-          <t>Mengunduh data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E844" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F844" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G844" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Download Excel.</t>
-        </is>
-      </c>
-      <c r="H844" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mendownload file Excel data Rekap Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="845" ht="42" customHeight="1">
-      <c r="A845" s="43" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="B845" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C845" s="3" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D845" s="4" t="inlineStr">
-        <is>
-          <t>Membuka halaman Regional Funnel</t>
-        </is>
-      </c>
-      <c r="E845" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F845" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G845" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Regional Funnel.</t>
-        </is>
-      </c>
-      <c r="H845" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Regional Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="846" ht="28" customHeight="1">
-      <c r="A846" s="43" t="inlineStr">
-        <is>
-          <t>68.2</t>
-        </is>
-      </c>
-      <c r="B846" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C846" s="3" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D846" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Regional Funnel</t>
-        </is>
-      </c>
-      <c r="E846" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F846" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G846" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi semua field filter mandatory.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H846" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="847" ht="14" customHeight="1">
-      <c r="A847" s="43" t="inlineStr">
-        <is>
-          <t>68.3</t>
-        </is>
-      </c>
-      <c r="B847" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C847" s="3" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D847" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E847" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F847" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G847" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H847" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="848" ht="14" customHeight="1">
-      <c r="A848" s="43" t="inlineStr">
-        <is>
-          <t>69.1</t>
-        </is>
-      </c>
-      <c r="B848" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C848" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D848" s="4" t="inlineStr">
-        <is>
-          <t>Membuka halaman Pengaturan Funnel Lending</t>
-        </is>
-      </c>
-      <c r="E848" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F848" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G848" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Pengaturan Funnel.</t>
-        </is>
-      </c>
-      <c r="H848" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Pengaturan Funnel Lending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="849" ht="42" customHeight="1">
-      <c r="A849" s="43" t="inlineStr">
-        <is>
-          <t>69.2</t>
-        </is>
-      </c>
-      <c r="B849" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C849" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D849" s="4" t="inlineStr">
-        <is>
-          <t>Menampilkan data Pengaturan Funnel Lending berdasarkan section</t>
-        </is>
-      </c>
-      <c r="E849" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F849" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G849" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik salah satu daftar section pada tabel.</t>
-        </is>
-      </c>
-      <c r="H849" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data pengaturan funnel Lending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="850" ht="28" customHeight="1">
-      <c r="A850" s="43" t="inlineStr">
-        <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="B850" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C850" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D850" s="4" t="inlineStr">
-        <is>
-          <t>Mengubah data Pengaturan Funnel Lending</t>
-        </is>
-      </c>
-      <c r="E850" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F850" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G850" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H850" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field Performance Percentage.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="851" ht="28" customHeight="1">
-      <c r="A851" s="43" t="inlineStr">
-        <is>
-          <t>69.4</t>
-        </is>
-      </c>
-      <c r="B851" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C851" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D851" s="4" t="inlineStr">
-        <is>
-          <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E851" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F851" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G851" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field mandatory Performance Percentage.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H851" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field Performance Percentage.
-2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="852" ht="28" customHeight="1">
-      <c r="A852" s="43" t="inlineStr">
-        <is>
-          <t>69.5</t>
-        </is>
-      </c>
-      <c r="B852" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C852" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D852" s="4" t="inlineStr">
-        <is>
-          <t>Menambahkan Condition pada Performance Indicator</t>
-        </is>
-      </c>
-      <c r="E852" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F852" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G852" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Add Condition pada bagian Performance Indicator.
-2. Mengisi semua field mandatory pada condition baru.
-3. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H852" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan form condition baru pada Performance Indicator.
-2. Berhasil mengisi field mandatory condition.
-3. Berhasil menyimpan condition baru pada Performance Indicator.</t>
         </is>
       </c>
     </row>
     <row r="853" ht="28" customHeight="1">
       <c r="A853" s="43" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="B853" s="3" t="inlineStr">
         <is>
-          <t>Report Lending</t>
+          <t>Re-Assign dan Approval</t>
         </is>
       </c>
       <c r="C853" s="3" t="inlineStr">
         <is>
-          <t>Pengaturan Funnel</t>
+          <t>Approval Non Banking</t>
         </is>
       </c>
       <c r="D853" s="4" t="inlineStr">
         <is>
-          <t>Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory</t>
+          <t>Membuka halaman Approval non Banking</t>
         </is>
       </c>
       <c r="E853" s="3" t="inlineStr">
@@ -38050,38 +38052,36 @@
       </c>
       <c r="G853" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Add Condition pada bagian Performance Indicator.
-2. Mengosongkan field mandatory pada condition baru.
-3. Klik button Submit.</t>
+          <t>1. Klik menu Re-Assign &amp; Approval 
+2. Klik submenu Approval non banking</t>
         </is>
       </c>
       <c r="H853" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan form condition baru pada Performance Indicator.
-2. Berhasil mengosongkan field mandatory condition.
-3. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+          <t>1. Menampilkan submenu Re-Assign &amp; Approval 
+2. Menampilkan halaman Approval non banking</t>
         </is>
       </c>
     </row>
     <row r="854" ht="28" customHeight="1">
       <c r="A854" s="43" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="B854" s="3" t="inlineStr">
         <is>
-          <t>Report Lending</t>
+          <t>Re-Assign dan Approval</t>
         </is>
       </c>
       <c r="C854" s="3" t="inlineStr">
         <is>
-          <t>Pengaturan Funnel</t>
+          <t>Approval Non Banking</t>
         </is>
       </c>
       <c r="D854" s="4" t="inlineStr">
         <is>
-          <t>Menghapus Condition pada Performance Indicator</t>
+          <t>Melihat Detail data Approval non banking</t>
         </is>
       </c>
       <c r="E854" s="3" t="inlineStr">
@@ -38096,21 +38096,21 @@
       </c>
       <c r="G854" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Remove pada salah satu condition di Performance Indicator.
-2. Klik button Submit.</t>
+          <t>1. Klik titik tiga 
+2. Klik Detail</t>
         </is>
       </c>
       <c r="H854" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menghapus condition dari Performance Indicator.
-2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
+          <t>1. Menampilkan beberapa action (detail, setujui, tolak)
+2. Menampilkan halaman detail data approval non banking</t>
         </is>
       </c>
     </row>
     <row r="855" ht="28" customHeight="1">
       <c r="A855" s="43" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="B855" s="3" t="inlineStr">
@@ -38125,7 +38125,7 @@
       </c>
       <c r="D855" s="4" t="inlineStr">
         <is>
-          <t>Membuka halaman Approval non Banking</t>
+          <t>Menyetujui Prospek</t>
         </is>
       </c>
       <c r="E855" s="3" t="inlineStr">
@@ -38135,98 +38135,10 @@
       </c>
       <c r="F855" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G855" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Re-Assign &amp; Approval 
-2. Klik submenu Approval non banking</t>
-        </is>
-      </c>
-      <c r="H855" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan submenu Re-Assign &amp; Approval 
-2. Menampilkan halaman Approval non banking</t>
-        </is>
-      </c>
-    </row>
-    <row r="856" ht="28" customHeight="1">
-      <c r="A856" s="43" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="B856" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C856" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D856" s="4" t="inlineStr">
-        <is>
-          <t>Melihat Detail data Approval non banking</t>
-        </is>
-      </c>
-      <c r="E856" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F856" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G856" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik titik tiga 
-2. Klik Detail</t>
-        </is>
-      </c>
-      <c r="H856" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan beberapa action (detail, setujui, tolak)
-2. Menampilkan halaman detail data approval non banking</t>
-        </is>
-      </c>
-    </row>
-    <row r="857" ht="28" customHeight="1">
-      <c r="A857" s="43" t="inlineStr">
-        <is>
-          <t>70.3</t>
-        </is>
-      </c>
-      <c r="B857" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C857" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D857" s="4" t="inlineStr">
-        <is>
-          <t>Menyetujui Prospek</t>
-        </is>
-      </c>
-      <c r="E857" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F857" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G857" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Setujui 
@@ -38235,7 +38147,7 @@
 5. Klik button Setujui</t>
         </is>
       </c>
-      <c r="H857" s="4" t="inlineStr">
+      <c r="H855" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan modal approve 
@@ -38245,87 +38157,87 @@
         </is>
       </c>
     </row>
-    <row r="858" ht="28" customHeight="1">
-      <c r="A858" s="43" t="inlineStr">
+    <row r="856" ht="28" customHeight="1">
+      <c r="A856" s="43" t="inlineStr">
         <is>
           <t>70.4</t>
         </is>
       </c>
-      <c r="B858" s="3" t="inlineStr">
+      <c r="B856" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C858" s="3" t="inlineStr">
+      <c r="C856" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D858" s="4" t="inlineStr">
+      <c r="D856" s="4" t="inlineStr">
         <is>
           <t>Batal menyetujui Prospek</t>
         </is>
       </c>
-      <c r="E858" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F858" s="3" t="inlineStr">
+      <c r="E856" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F856" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G858" s="4" t="inlineStr">
+      <c r="G856" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Batalkan pada modal approve</t>
         </is>
       </c>
-      <c r="H858" s="4" t="inlineStr">
+      <c r="H856" s="4" t="inlineStr">
         <is>
           <t>1. Modal approve tertutup dan tetap di halaman approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="859" ht="28" customHeight="1">
-      <c r="A859" s="43" t="inlineStr">
+    <row r="857" ht="28" customHeight="1">
+      <c r="A857" s="43" t="inlineStr">
         <is>
           <t>70.5</t>
         </is>
       </c>
-      <c r="B859" s="3" t="inlineStr">
+      <c r="B857" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C859" s="3" t="inlineStr">
+      <c r="C857" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D859" s="4" t="inlineStr">
+      <c r="D857" s="4" t="inlineStr">
         <is>
           <t>Tidak menginput nilai realisasi pada modal approve</t>
         </is>
       </c>
-      <c r="E859" s="3" t="inlineStr">
+      <c r="E857" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F859" s="3" t="inlineStr">
+      <c r="F857" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G859" s="4" t="inlineStr">
+      <c r="G857" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan nilai realisasi 
 2. Input remark 
 3. Klik button Setujui</t>
         </is>
       </c>
-      <c r="H859" s="4" t="inlineStr">
+      <c r="H857" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field realisasi 
 2. Berhasil menginput remark 
@@ -38333,10 +38245,94 @@
         </is>
       </c>
     </row>
+    <row r="858" ht="28" customHeight="1">
+      <c r="A858" s="43" t="inlineStr">
+        <is>
+          <t>70.6</t>
+        </is>
+      </c>
+      <c r="B858" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C858" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D858" s="4" t="inlineStr">
+        <is>
+          <t>Tidak menginput remark pada modal approve</t>
+        </is>
+      </c>
+      <c r="E858" s="3" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F858" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G858" s="4" t="inlineStr">
+        <is>
+          <t>1. Kosongkan remark</t>
+        </is>
+      </c>
+      <c r="H858" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan alert 'Remark dibutuhkan!'</t>
+        </is>
+      </c>
+    </row>
+    <row r="859" ht="28" customHeight="1">
+      <c r="A859" s="43" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="B859" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C859" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D859" s="4" t="inlineStr">
+        <is>
+          <t>Menginput huruf pada field realisasi</t>
+        </is>
+      </c>
+      <c r="E859" s="3" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F859" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G859" s="4" t="inlineStr">
+        <is>
+          <t>1. Input huruf pada field realisasi kemudian pindah ke filed lain</t>
+        </is>
+      </c>
+      <c r="H859" s="4" t="inlineStr">
+        <is>
+          <t>1. Sistem menghapus input non-numerik secara otomatis saat field kehilangan fokus. Field Realiasi menjadi kosong</t>
+        </is>
+      </c>
+    </row>
     <row r="860" ht="28" customHeight="1">
       <c r="A860" s="43" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="B860" s="3" t="inlineStr">
@@ -38351,104 +38347,20 @@
       </c>
       <c r="D860" s="4" t="inlineStr">
         <is>
-          <t>Tidak menginput remark pada modal approve</t>
+          <t>Menolak Prospek</t>
         </is>
       </c>
       <c r="E860" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F860" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G860" s="4" t="inlineStr">
-        <is>
-          <t>1. Kosongkan remark</t>
-        </is>
-      </c>
-      <c r="H860" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan alert 'Remark dibutuhkan!'</t>
-        </is>
-      </c>
-    </row>
-    <row r="861" ht="28" customHeight="1">
-      <c r="A861" s="43" t="inlineStr">
-        <is>
-          <t>70.7</t>
-        </is>
-      </c>
-      <c r="B861" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C861" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D861" s="4" t="inlineStr">
-        <is>
-          <t>Menginput huruf pada field realisasi</t>
-        </is>
-      </c>
-      <c r="E861" s="3" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F861" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G861" s="4" t="inlineStr">
-        <is>
-          <t>1. Input huruf pada field realisasi kemudian pindah ke filed lain</t>
-        </is>
-      </c>
-      <c r="H861" s="4" t="inlineStr">
-        <is>
-          <t>1. Sistem menghapus input non-numerik secara otomatis saat field kehilangan fokus. Field Realiasi menjadi kosong</t>
-        </is>
-      </c>
-    </row>
-    <row r="862" ht="28" customHeight="1">
-      <c r="A862" s="43" t="inlineStr">
-        <is>
-          <t>70.8</t>
-        </is>
-      </c>
-      <c r="B862" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C862" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D862" s="4" t="inlineStr">
-        <is>
-          <t>Menolak Prospek</t>
-        </is>
-      </c>
-      <c r="E862" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F862" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G862" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Tolak 
@@ -38456,7 +38368,7 @@
 4. Klik button Tolak</t>
         </is>
       </c>
-      <c r="H862" s="4" t="inlineStr">
+      <c r="H860" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan modal tolak prospek
@@ -38465,10 +38377,96 @@
         </is>
       </c>
     </row>
+    <row r="861" ht="28" customHeight="1">
+      <c r="A861" s="43" t="inlineStr">
+        <is>
+          <t>70.9</t>
+        </is>
+      </c>
+      <c r="B861" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C861" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D861" s="4" t="inlineStr">
+        <is>
+          <t>Batal menolak prospek</t>
+        </is>
+      </c>
+      <c r="E861" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F861" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G861" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Batalkan pada moal tolak prospek</t>
+        </is>
+      </c>
+      <c r="H861" s="4" t="inlineStr">
+        <is>
+          <t>1. Modal tolak prospek tertutup dan tetap berada di halaman approval non banking</t>
+        </is>
+      </c>
+    </row>
+    <row r="862" ht="28" customHeight="1">
+      <c r="A862" s="43" t="inlineStr">
+        <is>
+          <t>70.10</t>
+        </is>
+      </c>
+      <c r="B862" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C862" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D862" s="4" t="inlineStr">
+        <is>
+          <t>Tidak menginput remark pada modal tolak prospek</t>
+        </is>
+      </c>
+      <c r="E862" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F862" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G862" s="4" t="inlineStr">
+        <is>
+          <t>1. Kosongkan remark 
+2. Klik button Tolak</t>
+        </is>
+      </c>
+      <c r="H862" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan remark 
+2. Menampilkan alert 'Remark dibutuhkan!'</t>
+        </is>
+      </c>
+    </row>
     <row r="863" ht="28" customHeight="1">
       <c r="A863" s="43" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="B863" s="3" t="inlineStr">
@@ -38483,7 +38481,7 @@
       </c>
       <c r="D863" s="4" t="inlineStr">
         <is>
-          <t>Batal menolak prospek</t>
+          <t>Filter kolom</t>
         </is>
       </c>
       <c r="E863" s="3" t="inlineStr">
@@ -38498,19 +38496,21 @@
       </c>
       <c r="G863" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Batalkan pada moal tolak prospek</t>
+          <t>1. Klik icon filter kolom 
+2. Checklist/unchecklist kolom</t>
         </is>
       </c>
       <c r="H863" s="4" t="inlineStr">
         <is>
-          <t>1. Modal tolak prospek tertutup dan tetap berada di halaman approval non banking</t>
+          <t>1. Menampilkan list kolom tabel 
+2. Menampilkan data tabel sesuai dengan kolom yang di ceklis</t>
         </is>
       </c>
     </row>
     <row r="864" ht="28" customHeight="1">
       <c r="A864" s="43" t="inlineStr">
         <is>
-          <t>70.10</t>
+          <t>70.12</t>
         </is>
       </c>
       <c r="B864" s="3" t="inlineStr">
@@ -38525,7 +38525,7 @@
       </c>
       <c r="D864" s="4" t="inlineStr">
         <is>
-          <t>Tidak menginput remark pada modal tolak prospek</t>
+          <t>Reset ke Default pada filter kolom</t>
         </is>
       </c>
       <c r="E864" s="3" t="inlineStr">
@@ -38535,26 +38535,24 @@
       </c>
       <c r="F864" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G864" s="4" t="inlineStr">
         <is>
-          <t>1. Kosongkan remark 
-2. Klik button Tolak</t>
+          <t>1. Klik Reset ke Default</t>
         </is>
       </c>
       <c r="H864" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan remark 
-2. Menampilkan alert 'Remark dibutuhkan!'</t>
+          <t>1. Berhasil menampilkan data tabel dengan kolom default</t>
         </is>
       </c>
     </row>
     <row r="865" ht="28" customHeight="1">
       <c r="A865" s="43" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="B865" s="3" t="inlineStr">
@@ -38564,12 +38562,12 @@
       </c>
       <c r="C865" s="3" t="inlineStr">
         <is>
-          <t>Approval Non Banking</t>
+          <t>Re-Assign Prospek</t>
         </is>
       </c>
       <c r="D865" s="4" t="inlineStr">
         <is>
-          <t>Filter kolom</t>
+          <t>Filter data</t>
         </is>
       </c>
       <c r="E865" s="3" t="inlineStr">
@@ -38583,92 +38581,6 @@
         </is>
       </c>
       <c r="G865" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik icon filter kolom 
-2. Checklist/unchecklist kolom</t>
-        </is>
-      </c>
-      <c r="H865" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan list kolom tabel 
-2. Menampilkan data tabel sesuai dengan kolom yang di ceklis</t>
-        </is>
-      </c>
-    </row>
-    <row r="866" ht="28" customHeight="1">
-      <c r="A866" s="43" t="inlineStr">
-        <is>
-          <t>70.12</t>
-        </is>
-      </c>
-      <c r="B866" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C866" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D866" s="4" t="inlineStr">
-        <is>
-          <t>Reset ke Default pada filter kolom</t>
-        </is>
-      </c>
-      <c r="E866" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F866" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G866" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik Reset ke Default</t>
-        </is>
-      </c>
-      <c r="H866" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data tabel dengan kolom default</t>
-        </is>
-      </c>
-    </row>
-    <row r="867" ht="28" customHeight="1">
-      <c r="A867" s="43" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
-      <c r="B867" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C867" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D867" s="4" t="inlineStr">
-        <is>
-          <t>Filter data</t>
-        </is>
-      </c>
-      <c r="E867" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F867" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G867" s="4" t="inlineStr">
         <is>
           <t>1. Pilih kantor wilayah
 2. Pilih kantor cabang 
@@ -38678,7 +38590,7 @@
 6. Klik button Filter</t>
         </is>
       </c>
-      <c r="H867" s="4" t="inlineStr">
+      <c r="H865" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list data filter kantor wilayah dan dapat di pilih
 2. Menampilkan dropdown list data filter kantor cabang dan dapat di pilih
@@ -38689,10 +38601,98 @@
         </is>
       </c>
     </row>
+    <row r="866" ht="28" customHeight="1">
+      <c r="A866" s="43" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="B866" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C866" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D866" s="4" t="inlineStr">
+        <is>
+          <t>Mencari data</t>
+        </is>
+      </c>
+      <c r="E866" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F866" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G866" s="4" t="inlineStr">
+        <is>
+          <t>1. Input keyword pada field search 
+2. Klik icon search yang ada di sebelah field</t>
+        </is>
+      </c>
+      <c r="H866" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menginput keyword 
+2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
+        </is>
+      </c>
+    </row>
+    <row r="867" ht="28" customHeight="1">
+      <c r="A867" s="43" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="B867" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C867" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D867" s="4" t="inlineStr">
+        <is>
+          <t>Membuka halaman Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="E867" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F867" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G867" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu Re-Assign &amp; Approval 
+2. Klik submenu Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="H867" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan submenu Re-Assign &amp; Approval 
+2. Menampilkan halaman Re-Assign Prospek</t>
+        </is>
+      </c>
+    </row>
     <row r="868" ht="28" customHeight="1">
       <c r="A868" s="43" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="B868" s="3" t="inlineStr">
@@ -38707,7 +38707,7 @@
       </c>
       <c r="D868" s="4" t="inlineStr">
         <is>
-          <t>Mencari data</t>
+          <t>Filter data</t>
         </is>
       </c>
       <c r="E868" s="3" t="inlineStr">
@@ -38717,98 +38717,10 @@
       </c>
       <c r="F868" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G868" s="4" t="inlineStr">
-        <is>
-          <t>1. Input keyword pada field search 
-2. Klik icon search yang ada di sebelah field</t>
-        </is>
-      </c>
-      <c r="H868" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menginput keyword 
-2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
-        </is>
-      </c>
-    </row>
-    <row r="869" ht="28" customHeight="1">
-      <c r="A869" s="43" t="inlineStr">
-        <is>
-          <t>71.3</t>
-        </is>
-      </c>
-      <c r="B869" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C869" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D869" s="4" t="inlineStr">
-        <is>
-          <t>Membuka halaman Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="E869" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F869" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G869" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Re-Assign &amp; Approval 
-2. Klik submenu Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="H869" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan submenu Re-Assign &amp; Approval 
-2. Menampilkan halaman Re-Assign Prospek</t>
-        </is>
-      </c>
-    </row>
-    <row r="870" ht="28" customHeight="1">
-      <c r="A870" s="43" t="inlineStr">
-        <is>
-          <t>71.4</t>
-        </is>
-      </c>
-      <c r="B870" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C870" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D870" s="4" t="inlineStr">
-        <is>
-          <t>Filter data</t>
-        </is>
-      </c>
-      <c r="E870" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F870" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G870" s="4" t="inlineStr">
         <is>
           <t>1. Pilih kantor wilayah
 2. Pilih kantor cabang 
@@ -38818,7 +38730,7 @@
 6. Klik button Filter</t>
         </is>
       </c>
-      <c r="H870" s="4" t="inlineStr">
+      <c r="H868" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list data filter kantor wilayah dan dapat di pilih
 2. Menampilkan dropdown list data filter kantor cabang dan dapat di pilih
@@ -38829,10 +38741,96 @@
         </is>
       </c>
     </row>
+    <row r="869" ht="28" customHeight="1">
+      <c r="A869" s="43" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="B869" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C869" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D869" s="4" t="inlineStr">
+        <is>
+          <t>Mencari data</t>
+        </is>
+      </c>
+      <c r="E869" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F869" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G869" s="4" t="inlineStr">
+        <is>
+          <t>1. Input keyword pada field search 
+2. Klik icon search yang ada di sebelah field</t>
+        </is>
+      </c>
+      <c r="H869" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menginput keyword 
+2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
+        </is>
+      </c>
+    </row>
+    <row r="870" ht="28" customHeight="1">
+      <c r="A870" s="43" t="inlineStr">
+        <is>
+          <t>71.6</t>
+        </is>
+      </c>
+      <c r="B870" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C870" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D870" s="4" t="inlineStr">
+        <is>
+          <t>Validasi count checklist data</t>
+        </is>
+      </c>
+      <c r="E870" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F870" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G870" s="4" t="inlineStr">
+        <is>
+          <t>1. Cek informasi yang ada pada button Reassign () data</t>
+        </is>
+      </c>
+      <c r="H870" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan count angka yang sesuai dengan data yang di checklist</t>
+        </is>
+      </c>
+    </row>
     <row r="871" ht="28" customHeight="1">
       <c r="A871" s="43" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="B871" s="3" t="inlineStr">
@@ -38847,7 +38845,7 @@
       </c>
       <c r="D871" s="4" t="inlineStr">
         <is>
-          <t>Mencari data</t>
+          <t>Validasi data yang sudah dii pilih</t>
         </is>
       </c>
       <c r="E871" s="3" t="inlineStr">
@@ -38857,26 +38855,24 @@
       </c>
       <c r="F871" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G871" s="4" t="inlineStr">
         <is>
-          <t>1. Input keyword pada field search 
-2. Klik icon search yang ada di sebelah field</t>
+          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi prospek yang di pilih</t>
         </is>
       </c>
       <c r="H871" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menginput keyword 
-2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
+          <t>1. Menampilkan data tabel prospek yang di pilih saja</t>
         </is>
       </c>
     </row>
     <row r="872" ht="70" customHeight="1">
       <c r="A872" s="43" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="B872" s="3" t="inlineStr">
@@ -38891,34 +38887,36 @@
       </c>
       <c r="D872" s="4" t="inlineStr">
         <is>
-          <t>Validasi count checklist data</t>
+          <t>Mengosongkan field inputan mandatory pada reassign prospek</t>
         </is>
       </c>
       <c r="E872" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F872" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G872" s="4" t="inlineStr">
         <is>
-          <t>1. Cek informasi yang ada pada button Reassign () data</t>
+          <t>1. Kosongkan salah satu atau semua field mandatory 
+2. Klik button Submit</t>
         </is>
       </c>
       <c r="H872" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan count angka yang sesuai dengan data yang di checklist</t>
+          <t>1. Berhasil tidak mengisi/mengosongkan field 
+2. Menampilkan alert pada setiap field mandatory bahwa field tersebut dibutuhkan / wajib diisi</t>
         </is>
       </c>
     </row>
     <row r="873" ht="42" customHeight="1">
       <c r="A873" s="43" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="B873" s="3" t="inlineStr">
@@ -38933,7 +38931,7 @@
       </c>
       <c r="D873" s="4" t="inlineStr">
         <is>
-          <t>Validasi data yang sudah dii pilih</t>
+          <t>Membatalkan Re-Assign Prospek</t>
         </is>
       </c>
       <c r="E873" s="3" t="inlineStr">
@@ -38943,24 +38941,24 @@
       </c>
       <c r="F873" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G873" s="4" t="inlineStr">
         <is>
-          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi prospek yang di pilih</t>
+          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
         </is>
       </c>
       <c r="H873" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data tabel prospek yang di pilih saja</t>
+          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
         </is>
       </c>
     </row>
     <row r="874" ht="42" customHeight="1">
       <c r="A874" s="43" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.10</t>
         </is>
       </c>
       <c r="B874" s="3" t="inlineStr">
@@ -38975,12 +38973,12 @@
       </c>
       <c r="D874" s="4" t="inlineStr">
         <is>
-          <t>Mengosongkan field inputan mandatory pada reassign prospek</t>
+          <t>Validasi data prospek yang di re-assign</t>
         </is>
       </c>
       <c r="E874" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F874" s="3" t="inlineStr">
@@ -38989,92 +38987,6 @@
         </is>
       </c>
       <c r="G874" s="4" t="inlineStr">
-        <is>
-          <t>1. Kosongkan salah satu atau semua field mandatory 
-2. Klik button Submit</t>
-        </is>
-      </c>
-      <c r="H874" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil tidak mengisi/mengosongkan field 
-2. Menampilkan alert pada setiap field mandatory bahwa field tersebut dibutuhkan / wajib diisi</t>
-        </is>
-      </c>
-    </row>
-    <row r="875" ht="70" customHeight="1">
-      <c r="A875" s="43" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
-      </c>
-      <c r="B875" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C875" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D875" s="4" t="inlineStr">
-        <is>
-          <t>Membatalkan Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="E875" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F875" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G875" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
-        </is>
-      </c>
-      <c r="H875" s="4" t="inlineStr">
-        <is>
-          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
-        </is>
-      </c>
-    </row>
-    <row r="876" ht="28" customHeight="1">
-      <c r="A876" s="43" t="inlineStr">
-        <is>
-          <t>71.10</t>
-        </is>
-      </c>
-      <c r="B876" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C876" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D876" s="4" t="inlineStr">
-        <is>
-          <t>Validasi data prospek yang di re-assign</t>
-        </is>
-      </c>
-      <c r="E876" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F876" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G876" s="4" t="inlineStr">
         <is>
           <t>1. Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek 
 2. Klik menu Lead Qualification 
@@ -39082,7 +38994,7 @@
 4. Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
-      <c r="H876" s="4" t="inlineStr">
+      <c r="H874" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login 
 2. Menampilkan dropdown submenu Lead Qualification 
@@ -39091,38 +39003,38 @@
         </is>
       </c>
     </row>
-    <row r="877" ht="42" customHeight="1">
-      <c r="A877" s="43" t="inlineStr">
+    <row r="875" ht="70" customHeight="1">
+      <c r="A875" s="43" t="inlineStr">
         <is>
           <t>71.11</t>
         </is>
       </c>
-      <c r="B877" s="3" t="inlineStr">
+      <c r="B875" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C877" s="3" t="inlineStr">
+      <c r="C875" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D877" s="4" t="inlineStr">
+      <c r="D875" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-assign prospek semua data</t>
         </is>
       </c>
-      <c r="E877" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F877" s="3" t="inlineStr">
+      <c r="E875" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F875" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G877" s="4" t="inlineStr">
+      <c r="G875" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Reassign semua data 
 2. Klik button Yes 
@@ -39133,7 +39045,7 @@
 7. Klik button Submit</t>
         </is>
       </c>
-      <c r="H877" s="4" t="inlineStr">
+      <c r="H875" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan popup konfirmasi 
 2. Menampilkan halaman pindah kelolaan 
@@ -39145,10 +39057,94 @@
         </is>
       </c>
     </row>
+    <row r="876" ht="28" customHeight="1">
+      <c r="A876" s="43" t="inlineStr">
+        <is>
+          <t>71.12</t>
+        </is>
+      </c>
+      <c r="B876" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C876" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D876" s="4" t="inlineStr">
+        <is>
+          <t>Validasi semua data</t>
+        </is>
+      </c>
+      <c r="E876" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F876" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G876" s="4" t="inlineStr">
+        <is>
+          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi semua prospek</t>
+        </is>
+      </c>
+      <c r="H876" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan data tabel yang berisi semua prospek</t>
+        </is>
+      </c>
+    </row>
+    <row r="877" ht="42" customHeight="1">
+      <c r="A877" s="43" t="inlineStr">
+        <is>
+          <t>71.13</t>
+        </is>
+      </c>
+      <c r="B877" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C877" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D877" s="4" t="inlineStr">
+        <is>
+          <t>Membatalkan Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="E877" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F877" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G877" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
+        </is>
+      </c>
+      <c r="H877" s="4" t="inlineStr">
+        <is>
+          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
+        </is>
+      </c>
+    </row>
     <row r="878" ht="28" customHeight="1">
       <c r="A878" s="43" t="inlineStr">
         <is>
-          <t>71.12</t>
+          <t>71.14</t>
         </is>
       </c>
       <c r="B878" s="3" t="inlineStr">
@@ -39163,7 +39159,7 @@
       </c>
       <c r="D878" s="4" t="inlineStr">
         <is>
-          <t>Validasi semua data</t>
+          <t>Validasi semua data prospek yang di re-assign</t>
         </is>
       </c>
       <c r="E878" s="3" t="inlineStr">
@@ -39177,90 +39173,6 @@
         </is>
       </c>
       <c r="G878" s="4" t="inlineStr">
-        <is>
-          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi semua prospek</t>
-        </is>
-      </c>
-      <c r="H878" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan data tabel yang berisi semua prospek</t>
-        </is>
-      </c>
-    </row>
-    <row r="879" ht="28" customHeight="1">
-      <c r="A879" s="43" t="inlineStr">
-        <is>
-          <t>71.13</t>
-        </is>
-      </c>
-      <c r="B879" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C879" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D879" s="4" t="inlineStr">
-        <is>
-          <t>Membatalkan Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="E879" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F879" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G879" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
-        </is>
-      </c>
-      <c r="H879" s="4" t="inlineStr">
-        <is>
-          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
-        </is>
-      </c>
-    </row>
-    <row r="880" ht="28" customHeight="1">
-      <c r="A880" s="43" t="inlineStr">
-        <is>
-          <t>71.14</t>
-        </is>
-      </c>
-      <c r="B880" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C880" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D880" s="4" t="inlineStr">
-        <is>
-          <t>Validasi semua data prospek yang di re-assign</t>
-        </is>
-      </c>
-      <c r="E880" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F880" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G880" s="4" t="inlineStr">
         <is>
           <t>1. Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek 
 2. Klik menu Lead Qualification 
@@ -39268,7 +39180,7 @@
 4. Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
-      <c r="H880" s="4" t="inlineStr">
+      <c r="H878" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login 
 2. Menampilkan dropdown submenu Lead Qualification 
@@ -39277,10 +39189,98 @@
         </is>
       </c>
     </row>
+    <row r="879" ht="28" customHeight="1">
+      <c r="A879" s="43" t="inlineStr">
+        <is>
+          <t>72.1</t>
+        </is>
+      </c>
+      <c r="B879" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C879" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D879" s="4" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="E879" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F879" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G879" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik pagination (10/halaman).
+2. Pilih berapa data yang ingin ditampilkan.</t>
+        </is>
+      </c>
+      <c r="H879" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengklik pagination.
+2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="880" ht="28" customHeight="1">
+      <c r="A880" s="43" t="inlineStr">
+        <is>
+          <t>72.2</t>
+        </is>
+      </c>
+      <c r="B880" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C880" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D880" s="4" t="inlineStr">
+        <is>
+          <t>Pindah Halaman</t>
+        </is>
+      </c>
+      <c r="E880" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F880" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G880" s="4" t="inlineStr">
+        <is>
+          <t>1. Input angka halaman di field pindah halaman.
+2. Klik Enter pada keyboard.</t>
+        </is>
+      </c>
+      <c r="H880" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menginput angka halaman.
+2. Berhasil berpindah ke halaman yang dituju.</t>
+        </is>
+      </c>
+    </row>
     <row r="881" ht="14" customHeight="1">
       <c r="A881" s="43" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="B881" s="3" t="inlineStr">
@@ -39295,7 +39295,7 @@
       </c>
       <c r="D881" s="4" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
       <c r="E881" s="3" t="inlineStr">
@@ -39305,98 +39305,10 @@
       </c>
       <c r="F881" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G881" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik pagination (10/halaman).
-2. Pilih berapa data yang ingin ditampilkan.</t>
-        </is>
-      </c>
-      <c r="H881" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengklik pagination.
-2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="882" ht="42" customHeight="1">
-      <c r="A882" s="43" t="inlineStr">
-        <is>
-          <t>72.2</t>
-        </is>
-      </c>
-      <c r="B882" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C882" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Management</t>
-        </is>
-      </c>
-      <c r="D882" s="4" t="inlineStr">
-        <is>
-          <t>Pindah Halaman</t>
-        </is>
-      </c>
-      <c r="E882" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F882" s="3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G882" s="4" t="inlineStr">
-        <is>
-          <t>1. Input angka halaman di field pindah halaman.
-2. Klik Enter pada keyboard.</t>
-        </is>
-      </c>
-      <c r="H882" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menginput angka halaman.
-2. Berhasil berpindah ke halaman yang dituju.</t>
-        </is>
-      </c>
-    </row>
-    <row r="883" ht="42" customHeight="1">
-      <c r="A883" s="43" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="B883" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C883" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Management</t>
-        </is>
-      </c>
-      <c r="D883" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="E883" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F883" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G883" s="4" t="inlineStr">
         <is>
           <t>1. Pilih prospek dengan klik checkbox yang ada di samping setiap data prospek 
 2. Klik button Reassign () data 
@@ -39405,7 +39317,7 @@
 5. Klik button Submit</t>
         </is>
       </c>
-      <c r="H883" s="4" t="inlineStr">
+      <c r="H881" s="4" t="inlineStr">
         <is>
           <t>1. Checkbox menjadi ceklis dan data berhasil di pilih 
 2. Menampilkan popup konfirmasi 
@@ -39415,10 +39327,98 @@
         </is>
       </c>
     </row>
+    <row r="882" ht="42" customHeight="1">
+      <c r="A882" s="43" t="inlineStr">
+        <is>
+          <t>72.4</t>
+        </is>
+      </c>
+      <c r="B882" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C882" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D882" s="4" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="E882" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F882" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G882" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik pagination (10/halaman).
+2. Pilih berapa data yang ingin ditampilkan.</t>
+        </is>
+      </c>
+      <c r="H882" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengklik pagination.
+2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="883" ht="42" customHeight="1">
+      <c r="A883" s="43" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="B883" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C883" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D883" s="4" t="inlineStr">
+        <is>
+          <t>Pindah Halaman</t>
+        </is>
+      </c>
+      <c r="E883" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F883" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G883" s="4" t="inlineStr">
+        <is>
+          <t>1. Input angka halaman di field pindah halaman.
+2. Klik Enter pada keyboard.</t>
+        </is>
+      </c>
+      <c r="H883" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menginput angka halaman.
+2. Berhasil berpindah ke halaman yang dituju.</t>
+        </is>
+      </c>
+    </row>
     <row r="884" ht="28" customHeight="1">
       <c r="A884" s="43" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="B884" s="3" t="inlineStr">
@@ -39433,7 +39433,7 @@
       </c>
       <c r="D884" s="4" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Membuka halaman Re-Assign Management</t>
         </is>
       </c>
       <c r="E884" s="3" t="inlineStr">
@@ -39443,26 +39443,26 @@
       </c>
       <c r="F884" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G884" s="4" t="inlineStr">
         <is>
-          <t>1. Klik pagination (10/halaman).
-2. Pilih berapa data yang ingin ditampilkan.</t>
+          <t>1. Klik menu Re-Assign &amp; Approval 
+2. Klik submenu Re-Assign Management</t>
         </is>
       </c>
       <c r="H884" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengklik pagination.
-2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+          <t>1. Menampilkan dropdown list submenu Re-Assign &amp; Approval 
+2. Menampilkan halaman Re-Assign Management</t>
         </is>
       </c>
     </row>
     <row r="885" ht="42" customHeight="1">
       <c r="A885" s="43" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="B885" s="3" t="inlineStr">
@@ -39477,7 +39477,7 @@
       </c>
       <c r="D885" s="4" t="inlineStr">
         <is>
-          <t>Pindah Halaman</t>
+          <t>Mencari data prospek pada halaman Re-Assign Management</t>
         </is>
       </c>
       <c r="E885" s="3" t="inlineStr">
@@ -39487,26 +39487,26 @@
       </c>
       <c r="F885" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G885" s="4" t="inlineStr">
         <is>
-          <t>1. Input angka halaman di field pindah halaman.
-2. Klik Enter pada keyboard.</t>
+          <t>1. Input nama nasabah pada field search 
+2. Klik icon search atau klik Enter</t>
         </is>
       </c>
       <c r="H885" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menginput angka halaman.
-2. Berhasil berpindah ke halaman yang dituju.</t>
+          <t>1. Berhasil menginput nama nasabah
+2. Menampilkan data prospek Re-Assign Management sesuai dengan nama yang di cari</t>
         </is>
       </c>
     </row>
     <row r="886" ht="14" customHeight="1">
       <c r="A886" s="43" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="B886" s="3" t="inlineStr">
@@ -39521,7 +39521,7 @@
       </c>
       <c r="D886" s="4" t="inlineStr">
         <is>
-          <t>Membuka halaman Re-Assign Management</t>
+          <t>Mencari data prospek yang tidak ada pada halaman Re-Assign Management</t>
         </is>
       </c>
       <c r="E886" s="3" t="inlineStr">
@@ -39536,21 +39536,21 @@
       </c>
       <c r="G886" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu Re-Assign &amp; Approval 
-2. Klik submenu Re-Assign Management</t>
+          <t>1. Input nama nasabah yang datanya tidak ada 
+2. Klik icon search atau klik Enter</t>
         </is>
       </c>
       <c r="H886" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan dropdown list submenu Re-Assign &amp; Approval 
-2. Menampilkan halaman Re-Assign Management</t>
+          <t>1. Berhasil menginput nama nasabah
+2. Menampilkan tabel kosong dengan keterangan no data</t>
         </is>
       </c>
     </row>
     <row r="887" ht="42" customHeight="1">
       <c r="A887" s="43" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="B887" s="3" t="inlineStr">
@@ -39565,7 +39565,7 @@
       </c>
       <c r="D887" s="4" t="inlineStr">
         <is>
-          <t>Mencari data prospek pada halaman Re-Assign Management</t>
+          <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
       <c r="E887" s="3" t="inlineStr">
@@ -39579,94 +39579,6 @@
         </is>
       </c>
       <c r="G887" s="4" t="inlineStr">
-        <is>
-          <t>1. Input nama nasabah pada field search 
-2. Klik icon search atau klik Enter</t>
-        </is>
-      </c>
-      <c r="H887" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menginput nama nasabah
-2. Menampilkan data prospek Re-Assign Management sesuai dengan nama yang di cari</t>
-        </is>
-      </c>
-    </row>
-    <row r="888" ht="42" customHeight="1">
-      <c r="A888" s="43" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
-      <c r="B888" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C888" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Management</t>
-        </is>
-      </c>
-      <c r="D888" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data prospek yang tidak ada pada halaman Re-Assign Management</t>
-        </is>
-      </c>
-      <c r="E888" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F888" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G888" s="4" t="inlineStr">
-        <is>
-          <t>1. Input nama nasabah yang datanya tidak ada 
-2. Klik icon search atau klik Enter</t>
-        </is>
-      </c>
-      <c r="H888" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menginput nama nasabah
-2. Menampilkan tabel kosong dengan keterangan no data</t>
-        </is>
-      </c>
-    </row>
-    <row r="889" ht="28" customHeight="1">
-      <c r="A889" s="43" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
-      </c>
-      <c r="B889" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C889" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Management</t>
-        </is>
-      </c>
-      <c r="D889" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="E889" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F889" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G889" s="4" t="inlineStr">
         <is>
           <t>1. Pilih prospek dengan klik checkbox yang ada di samping setiap data prospek 
 2. Klik button Reassign () data 
@@ -39675,7 +39587,7 @@
 5. Klik button Submit</t>
         </is>
       </c>
-      <c r="H889" s="4" t="inlineStr">
+      <c r="H887" s="4" t="inlineStr">
         <is>
           <t>1. Checkbox menjadi ceklis dan data berhasil di pilih 
 2. Menampilkan popup konfirmasi 
@@ -39685,80 +39597,80 @@
         </is>
       </c>
     </row>
-    <row r="890" ht="42" customHeight="1">
-      <c r="A890" s="43" t="inlineStr">
+    <row r="888" ht="42" customHeight="1">
+      <c r="A888" s="43" t="inlineStr">
         <is>
           <t>72.10</t>
         </is>
       </c>
-      <c r="B890" s="3" t="inlineStr">
+      <c r="B888" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C890" s="3" t="inlineStr">
+      <c r="C888" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D890" s="4" t="inlineStr">
+      <c r="D888" s="4" t="inlineStr">
         <is>
           <t>Validasi jumlah data yang di pilih untuk reassign</t>
         </is>
       </c>
-      <c r="E890" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F890" s="3" t="inlineStr">
+      <c r="E888" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F888" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G890" s="4" t="inlineStr">
+      <c r="G888" s="4" t="inlineStr">
         <is>
           <t>1. cek jumlah data yang muncul pada button Reassign () data</t>
         </is>
       </c>
-      <c r="H890" s="4" t="inlineStr">
+      <c r="H888" s="4" t="inlineStr">
         <is>
           <t>1. Angka yang muncul pada button sesuai dengan jumlah data yang di pilih</t>
         </is>
       </c>
     </row>
-    <row r="891" ht="14" customHeight="1">
-      <c r="A891" s="43" t="inlineStr">
+    <row r="889" ht="28" customHeight="1">
+      <c r="A889" s="43" t="inlineStr">
         <is>
           <t>72.11</t>
         </is>
       </c>
-      <c r="B891" s="3" t="inlineStr">
+      <c r="B889" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C891" s="3" t="inlineStr">
+      <c r="C889" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D891" s="4" t="inlineStr">
+      <c r="D889" s="4" t="inlineStr">
         <is>
           <t>Validasi data prospek yang di re-assign ke sales</t>
         </is>
       </c>
-      <c r="E891" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F891" s="3" t="inlineStr">
+      <c r="E889" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F889" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G891" s="4" t="inlineStr">
+      <c r="G889" s="4" t="inlineStr">
         <is>
           <t>1. Login dengan akun sales yang sebelumnya sudah di pilih reassign management
 2. Klik menu Lead Qualification
@@ -39766,7 +39678,7 @@
 4. Cek data prospek yang sudah di reassign</t>
         </is>
       </c>
-      <c r="H891" s="4" t="inlineStr">
+      <c r="H889" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login akun sales
 2. Menampilkan dropdown submenu Lead Qualification
@@ -39775,25 +39687,113 @@
         </is>
       </c>
     </row>
+    <row r="890" ht="42" customHeight="1">
+      <c r="A890" s="43" t="inlineStr">
+        <is>
+          <t>72.12</t>
+        </is>
+      </c>
+      <c r="B890" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C890" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D890" s="4" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="E890" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F890" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G890" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik pagination (10/halaman).
+2. Pilih berapa data yang ingin ditampilkan.</t>
+        </is>
+      </c>
+      <c r="H890" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengklik pagination.
+2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="891" ht="14" customHeight="1">
+      <c r="A891" s="43" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="B891" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C891" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D891" s="4" t="inlineStr">
+        <is>
+          <t>Pindah Halaman</t>
+        </is>
+      </c>
+      <c r="E891" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F891" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G891" s="4" t="inlineStr">
+        <is>
+          <t>1. Input angka halaman di field pindah halaman.
+2. Klik Enter pada keyboard.</t>
+        </is>
+      </c>
+      <c r="H891" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menginput angka halaman.
+2. Berhasil berpindah ke halaman yang dituju.</t>
+        </is>
+      </c>
+    </row>
     <row r="892" ht="42" customHeight="1">
       <c r="A892" s="43" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="B892" s="3" t="inlineStr">
         <is>
-          <t>Re-Assign dan Approval</t>
+          <t>Export data management</t>
         </is>
       </c>
       <c r="C892" s="3" t="inlineStr">
         <is>
-          <t>Re-Assign Management</t>
+          <t>Riwayat export saya</t>
         </is>
       </c>
       <c r="D892" s="4" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Membuka menu riwayat export saya</t>
         </is>
       </c>
       <c r="E892" s="3" t="inlineStr">
@@ -39803,41 +39803,39 @@
       </c>
       <c r="F892" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G892" s="4" t="inlineStr">
         <is>
-          <t>1. Klik pagination (10/halaman).
-2. Pilih berapa data yang ingin ditampilkan.</t>
+          <t>1. Klik menu exported data management, klik submenu riwayat export saya</t>
         </is>
       </c>
       <c r="H892" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengklik pagination.
-2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+          <t>1. Menampilkan halaman riwayat export saya</t>
         </is>
       </c>
     </row>
     <row r="893" ht="42" customHeight="1">
       <c r="A893" s="43" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="B893" s="3" t="inlineStr">
         <is>
-          <t>Re-Assign dan Approval</t>
+          <t>Export data management</t>
         </is>
       </c>
       <c r="C893" s="3" t="inlineStr">
         <is>
-          <t>Re-Assign Management</t>
+          <t>Riwayat export saya</t>
         </is>
       </c>
       <c r="D893" s="4" t="inlineStr">
         <is>
-          <t>Pindah Halaman</t>
+          <t>Validasi card disetujui dengan data table</t>
         </is>
       </c>
       <c r="E893" s="3" t="inlineStr">
@@ -39847,26 +39845,24 @@
       </c>
       <c r="F893" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G893" s="4" t="inlineStr">
         <is>
-          <t>1. Input angka halaman di field pindah halaman.
-2. Klik Enter pada keyboard.</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Approved”</t>
         </is>
       </c>
       <c r="H893" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menginput angka halaman.
-2. Berhasil berpindah ke halaman yang dituju.</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="894" ht="28" customHeight="1">
       <c r="A894" s="43" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="B894" s="3" t="inlineStr">
@@ -39881,7 +39877,7 @@
       </c>
       <c r="D894" s="4" t="inlineStr">
         <is>
-          <t>Membuka menu riwayat export saya</t>
+          <t>Validasi card ditolak dengan data table</t>
         </is>
       </c>
       <c r="E894" s="3" t="inlineStr">
@@ -39896,19 +39892,19 @@
       </c>
       <c r="G894" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu exported data management, klik submenu riwayat export saya</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Rejected”</t>
         </is>
       </c>
       <c r="H894" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan halaman riwayat export saya</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="895" ht="42" customHeight="1">
       <c r="A895" s="43" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="B895" s="3" t="inlineStr">
@@ -39923,7 +39919,7 @@
       </c>
       <c r="D895" s="4" t="inlineStr">
         <is>
-          <t>Validasi card disetujui dengan data table</t>
+          <t>Validasi card kadaluwarsa dengan data table</t>
         </is>
       </c>
       <c r="E895" s="3" t="inlineStr">
@@ -39933,12 +39929,12 @@
       </c>
       <c r="F895" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G895" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Approved”</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Expired”</t>
         </is>
       </c>
       <c r="H895" s="4" t="inlineStr">
@@ -39950,7 +39946,7 @@
     <row r="896" ht="14" customHeight="1">
       <c r="A896" s="43" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="B896" s="3" t="inlineStr">
@@ -39965,7 +39961,7 @@
       </c>
       <c r="D896" s="4" t="inlineStr">
         <is>
-          <t>Validasi card ditolak dengan data table</t>
+          <t>Mengunduh data yang sudah di approve</t>
         </is>
       </c>
       <c r="E896" s="3" t="inlineStr">
@@ -39980,19 +39976,19 @@
       </c>
       <c r="G896" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Rejected”</t>
+          <t>1. Klik button download</t>
         </is>
       </c>
       <c r="H896" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Berhasil mengunduh data</t>
         </is>
       </c>
     </row>
     <row r="897" ht="42" customHeight="1">
       <c r="A897" s="43" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="B897" s="3" t="inlineStr">
@@ -40007,7 +40003,7 @@
       </c>
       <c r="D897" s="4" t="inlineStr">
         <is>
-          <t>Validasi card kadaluwarsa dengan data table</t>
+          <t>Membuka dokumen hasil download</t>
         </is>
       </c>
       <c r="E897" s="3" t="inlineStr">
@@ -40017,24 +40013,24 @@
       </c>
       <c r="F897" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G897" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Expired”</t>
+          <t>1. Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
         </is>
       </c>
       <c r="H897" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Berhasil membuka file hasil download</t>
         </is>
       </c>
     </row>
     <row r="898" ht="42" customHeight="1">
       <c r="A898" s="43" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="B898" s="3" t="inlineStr">
@@ -40044,12 +40040,12 @@
       </c>
       <c r="C898" s="3" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D898" s="4" t="inlineStr">
         <is>
-          <t>Mengunduh data yang sudah di approve</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E898" s="3" t="inlineStr">
@@ -40059,24 +40055,24 @@
       </c>
       <c r="F898" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G898" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button download</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H898" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengunduh data</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="899" ht="28" customHeight="1">
       <c r="A899" s="43" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="B899" s="3" t="inlineStr">
@@ -40086,12 +40082,12 @@
       </c>
       <c r="C899" s="3" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D899" s="4" t="inlineStr">
         <is>
-          <t>Membuka dokumen hasil download</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E899" s="3" t="inlineStr">
@@ -40106,19 +40102,19 @@
       </c>
       <c r="G899" s="4" t="inlineStr">
         <is>
-          <t>1. Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
         </is>
       </c>
       <c r="H899" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka file hasil download</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="900" ht="42" customHeight="1">
       <c r="A900" s="43" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="B900" s="3" t="inlineStr">
@@ -40133,7 +40129,7 @@
       </c>
       <c r="D900" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E900" s="3" t="inlineStr">
@@ -40143,24 +40139,24 @@
       </c>
       <c r="F900" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G900" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H900" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="901" ht="28" customHeight="1">
       <c r="A901" s="43" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="B901" s="3" t="inlineStr">
@@ -40175,12 +40171,12 @@
       </c>
       <c r="D901" s="4" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E901" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F901" s="3" t="inlineStr">
@@ -40190,19 +40186,19 @@
       </c>
       <c r="G901" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H901" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="902" ht="28" customHeight="1">
       <c r="A902" s="43" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="B902" s="3" t="inlineStr">
@@ -40217,7 +40213,7 @@
       </c>
       <c r="D902" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E902" s="3" t="inlineStr">
@@ -40227,24 +40223,24 @@
       </c>
       <c r="F902" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G902" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H902" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="903" ht="28" customHeight="1">
       <c r="A903" s="43" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="B903" s="3" t="inlineStr">
@@ -40259,12 +40255,12 @@
       </c>
       <c r="D903" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E903" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F903" s="3" t="inlineStr">
@@ -40274,19 +40270,19 @@
       </c>
       <c r="G903" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H903" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="904" ht="28" customHeight="1">
       <c r="A904" s="43" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="B904" s="3" t="inlineStr">
@@ -40301,34 +40297,34 @@
       </c>
       <c r="D904" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E904" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F904" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G904" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H904" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="905" ht="28" customHeight="1">
       <c r="A905" s="43" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="B905" s="3" t="inlineStr">
@@ -40343,7 +40339,7 @@
       </c>
       <c r="D905" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Membuka menu Management Export</t>
         </is>
       </c>
       <c r="E905" s="3" t="inlineStr">
@@ -40358,19 +40354,19 @@
       </c>
       <c r="G905" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Klik menu exported data management, klik submenu management export</t>
         </is>
       </c>
       <c r="H905" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Menampilkan halaman management export</t>
         </is>
       </c>
     </row>
     <row r="906" ht="42" customHeight="1">
       <c r="A906" s="43" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="B906" s="3" t="inlineStr">
@@ -40385,34 +40381,34 @@
       </c>
       <c r="D906" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E906" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F906" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G906" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H906" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="907" ht="42" customHeight="1">
       <c r="A907" s="43" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.10</t>
         </is>
       </c>
       <c r="B907" s="3" t="inlineStr">
@@ -40427,7 +40423,7 @@
       </c>
       <c r="D907" s="4" t="inlineStr">
         <is>
-          <t>Membuka menu Management Export</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E907" s="3" t="inlineStr">
@@ -40442,19 +40438,19 @@
       </c>
       <c r="G907" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu exported data management, klik submenu management export</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H907" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan halaman management export</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="908" ht="28" customHeight="1">
       <c r="A908" s="43" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>74.11</t>
         </is>
       </c>
       <c r="B908" s="3" t="inlineStr">
@@ -40469,34 +40465,34 @@
       </c>
       <c r="D908" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E908" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F908" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G908" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H908" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="909" ht="14" customHeight="1">
       <c r="A909" s="43" t="inlineStr">
         <is>
-          <t>74.10</t>
+          <t>74.12</t>
         </is>
       </c>
       <c r="B909" s="3" t="inlineStr">
@@ -40511,7 +40507,7 @@
       </c>
       <c r="D909" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E909" s="3" t="inlineStr">
@@ -40526,19 +40522,19 @@
       </c>
       <c r="G909" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
         </is>
       </c>
       <c r="H909" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="910" ht="28" customHeight="1">
       <c r="A910" s="43" t="inlineStr">
         <is>
-          <t>74.11</t>
+          <t>74.13</t>
         </is>
       </c>
       <c r="B910" s="3" t="inlineStr">
@@ -40553,34 +40549,34 @@
       </c>
       <c r="D910" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Validasi card data file aktif dengan data table</t>
         </is>
       </c>
       <c r="E910" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F910" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G910" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
         </is>
       </c>
       <c r="H910" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="911" ht="28" customHeight="1">
       <c r="A911" s="43" t="inlineStr">
         <is>
-          <t>74.12</t>
+          <t>74.14</t>
         </is>
       </c>
       <c r="B911" s="3" t="inlineStr">
@@ -40595,7 +40591,7 @@
       </c>
       <c r="D911" s="4" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Validasi card file kadaluwarsa dengan data table</t>
         </is>
       </c>
       <c r="E911" s="3" t="inlineStr">
@@ -40605,12 +40601,12 @@
       </c>
       <c r="F911" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G911" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
         </is>
       </c>
       <c r="H911" s="4" t="inlineStr">
@@ -40622,7 +40618,7 @@
     <row r="912" ht="28" customHeight="1">
       <c r="A912" s="43" t="inlineStr">
         <is>
-          <t>74.13</t>
+          <t>74.15</t>
         </is>
       </c>
       <c r="B912" s="3" t="inlineStr">
@@ -40637,7 +40633,7 @@
       </c>
       <c r="D912" s="4" t="inlineStr">
         <is>
-          <t>Validasi card data file aktif dengan data table</t>
+          <t>Validasi card reject dengan data table</t>
         </is>
       </c>
       <c r="E912" s="3" t="inlineStr">
@@ -40647,12 +40643,12 @@
       </c>
       <c r="F912" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G912" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
         </is>
       </c>
       <c r="H912" s="4" t="inlineStr">
@@ -40664,7 +40660,7 @@
     <row r="913" ht="28" customHeight="1">
       <c r="A913" s="43" t="inlineStr">
         <is>
-          <t>74.14</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="B913" s="3" t="inlineStr">
@@ -40674,12 +40670,12 @@
       </c>
       <c r="C913" s="3" t="inlineStr">
         <is>
-          <t>Management export</t>
+          <t>Persetujuan export</t>
         </is>
       </c>
       <c r="D913" s="4" t="inlineStr">
         <is>
-          <t>Validasi card file kadaluwarsa dengan data table</t>
+          <t>Lakukan login menggunakan user monitoring</t>
         </is>
       </c>
       <c r="E913" s="3" t="inlineStr">
@@ -40694,19 +40690,19 @@
       </c>
       <c r="G913" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
+          <t>1. Login menggunakan user monitoring</t>
         </is>
       </c>
       <c r="H913" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Berhasil melakukan login</t>
         </is>
       </c>
     </row>
     <row r="914" ht="28" customHeight="1">
       <c r="A914" s="43" t="inlineStr">
         <is>
-          <t>74.15</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="B914" s="3" t="inlineStr">
@@ -40716,12 +40712,12 @@
       </c>
       <c r="C914" s="3" t="inlineStr">
         <is>
-          <t>Management export</t>
+          <t>Persetujuan export</t>
         </is>
       </c>
       <c r="D914" s="4" t="inlineStr">
         <is>
-          <t>Validasi card reject dengan data table</t>
+          <t>Membuka menu Persetujuan Export</t>
         </is>
       </c>
       <c r="E914" s="3" t="inlineStr">
@@ -40736,19 +40732,19 @@
       </c>
       <c r="G914" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
+          <t>1. Klik menu exported data management, klik submenu persetujuan export</t>
         </is>
       </c>
       <c r="H914" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Menampilkan halaman persetujuan export</t>
         </is>
       </c>
     </row>
     <row r="915" ht="14" customHeight="1">
       <c r="A915" s="43" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="B915" s="3" t="inlineStr">
@@ -40763,7 +40759,7 @@
       </c>
       <c r="D915" s="4" t="inlineStr">
         <is>
-          <t>Lakukan login menggunakan user monitoring</t>
+          <t>Melakukan approval data pengajuan export</t>
         </is>
       </c>
       <c r="E915" s="3" t="inlineStr">
@@ -40773,101 +40769,17 @@
       </c>
       <c r="F915" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G915" s="4" t="inlineStr">
-        <is>
-          <t>1. Login menggunakan user monitoring</t>
-        </is>
-      </c>
-      <c r="H915" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil melakukan login</t>
-        </is>
-      </c>
-    </row>
-    <row r="916" ht="28" customHeight="1">
-      <c r="A916" s="43" t="inlineStr">
-        <is>
-          <t>75.2</t>
-        </is>
-      </c>
-      <c r="B916" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C916" s="3" t="inlineStr">
-        <is>
-          <t>Persetujuan export</t>
-        </is>
-      </c>
-      <c r="D916" s="4" t="inlineStr">
-        <is>
-          <t>Membuka menu Persetujuan Export</t>
-        </is>
-      </c>
-      <c r="E916" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F916" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G916" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu exported data management, klik submenu persetujuan export</t>
-        </is>
-      </c>
-      <c r="H916" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan halaman persetujuan export</t>
-        </is>
-      </c>
-    </row>
-    <row r="917" ht="14" customHeight="1">
-      <c r="A917" s="43" t="inlineStr">
-        <is>
-          <t>75.3</t>
-        </is>
-      </c>
-      <c r="B917" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C917" s="3" t="inlineStr">
-        <is>
-          <t>Persetujuan export</t>
-        </is>
-      </c>
-      <c r="D917" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan approval data pengajuan export</t>
-        </is>
-      </c>
-      <c r="E917" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F917" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G917" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon titik tiga pada data pengajuan.
 2. Klik menu Setuju.
 3. Klik button YA pada popup konfirmasi.</t>
         </is>
       </c>
-      <c r="H917" s="4" t="inlineStr">
+      <c r="H915" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan menu opsi.
 2. Berhasil menampilkan popup konfirmasi.
@@ -40875,48 +40787,50 @@
         </is>
       </c>
     </row>
-    <row r="918" ht="28" customHeight="1">
-      <c r="A918" s="43" t="inlineStr">
+    <row r="916" ht="28" customHeight="1">
+      <c r="A916" s="43" t="inlineStr">
         <is>
           <t>75.4</t>
         </is>
       </c>
-      <c r="B918" s="3" t="inlineStr">
+      <c r="B916" s="3" t="inlineStr">
         <is>
           <t>Export data management</t>
         </is>
       </c>
-      <c r="C918" s="3" t="inlineStr">
+      <c r="C916" s="3" t="inlineStr">
         <is>
           <t>Persetujuan export</t>
         </is>
       </c>
-      <c r="D918" s="4" t="inlineStr">
+      <c r="D916" s="4" t="inlineStr">
         <is>
           <t>Melakukan reject data pengajuan export</t>
         </is>
       </c>
-      <c r="E918" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F918" s="3" t="inlineStr">
+      <c r="E916" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F916" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G918" s="4" t="inlineStr">
+      <c r="G916" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon (titik tiga) klik tolak, input alasan, klik submit</t>
         </is>
       </c>
-      <c r="H918" s="4" t="inlineStr">
+      <c r="H916" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil melakukan reject data</t>
         </is>
       </c>
     </row>
+    <row r="917" ht="14" customHeight="1"/>
+    <row r="918" ht="28" customHeight="1"/>
     <row r="919" ht="28" customHeight="1"/>
     <row r="920" ht="42" customHeight="1"/>
     <row r="921" ht="42" customHeight="1"/>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z916"/>
+  <dimension ref="A1:Z918"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="12.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -36158,216 +36158,306 @@
     <row r="811" ht="28" customHeight="1">
       <c r="A811" s="43" t="inlineStr">
         <is>
+          <t>64.6</t>
+        </is>
+      </c>
+      <c r="B811" s="3" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C811" s="3" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D811" s="4" t="inlineStr">
+        <is>
+          <t>Menambahkan Operator pada Condition di Performance Indicator</t>
+        </is>
+      </c>
+      <c r="E811" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F811" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G811" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik link tambah operator pada salah satu condition di Performance Indicator.
+2. Mengisi field operator baru.
+3. Klik button Simpan Pengaturan.</t>
+        </is>
+      </c>
+      <c r="H811" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan baris operator baru pada condition.
+2. Berhasil mengisi data operator.
+3. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="812" ht="42" customHeight="1">
+      <c r="A812" s="43" t="inlineStr">
+        <is>
+          <t>64.7</t>
+        </is>
+      </c>
+      <c r="B812" s="3" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C812" s="3" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D812" s="4" t="inlineStr">
+        <is>
+          <t>Menghapus Operator pada Condition di Performance Indicator</t>
+        </is>
+      </c>
+      <c r="E812" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F812" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G812" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button x pada salah satu operator di Performance Indicator.
+2. Klik button Simpan Pengaturan.</t>
+        </is>
+      </c>
+      <c r="H812" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menghapus operator dari condition di Performance Indicator.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="813" ht="28" customHeight="1">
+      <c r="A813" s="43" t="inlineStr">
+        <is>
           <t>65.1</t>
         </is>
       </c>
-      <c r="B811" s="3" t="inlineStr">
+      <c r="B813" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C811" s="3" t="inlineStr">
+      <c r="C813" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D811" s="4" t="inlineStr">
+      <c r="D813" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="E811" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F811" s="3" t="inlineStr">
+      <c r="E813" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F813" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G811" s="4" t="inlineStr">
+      <c r="G813" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Lending.
 2. Klik sub menu Daily Sales Agenda.</t>
         </is>
       </c>
-      <c r="H811" s="4" t="inlineStr">
+      <c r="H813" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Lending.
 2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
         </is>
       </c>
     </row>
-    <row r="812" ht="42" customHeight="1">
-      <c r="A812" s="43" t="inlineStr">
+    <row r="814" ht="28" customHeight="1">
+      <c r="A814" s="43" t="inlineStr">
         <is>
           <t>65.2</t>
         </is>
       </c>
-      <c r="B812" s="3" t="inlineStr">
+      <c r="B814" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C812" s="3" t="inlineStr">
+      <c r="C814" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D812" s="4" t="inlineStr">
+      <c r="D814" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="E812" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F812" s="3" t="inlineStr">
+      <c r="E814" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F814" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G812" s="4" t="inlineStr">
+      <c r="G814" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi semua field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H812" s="4" t="inlineStr">
+      <c r="H814" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field filter mandatory.
 2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="813" ht="28" customHeight="1">
-      <c r="A813" s="43" t="inlineStr">
+    <row r="815" ht="56" customHeight="1">
+      <c r="A815" s="43" t="inlineStr">
         <is>
           <t>65.3</t>
         </is>
       </c>
-      <c r="B813" s="3" t="inlineStr">
+      <c r="B815" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C813" s="3" t="inlineStr">
+      <c r="C815" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D813" s="4" t="inlineStr">
+      <c r="D815" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E813" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F813" s="3" t="inlineStr">
+      <c r="E815" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F815" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G813" s="4" t="inlineStr">
+      <c r="G815" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H813" s="4" t="inlineStr">
+      <c r="H815" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
-    <row r="814" ht="28" customHeight="1">
-      <c r="A814" s="43" t="inlineStr">
+    <row r="816" ht="56" customHeight="1">
+      <c r="A816" s="43" t="inlineStr">
         <is>
           <t>65.4</t>
         </is>
       </c>
-      <c r="B814" s="3" t="inlineStr">
+      <c r="B816" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C814" s="3" t="inlineStr">
+      <c r="C816" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D814" s="4" t="inlineStr">
+      <c r="D816" s="4" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Masuk</t>
         </is>
       </c>
-      <c r="E814" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F814" s="3" t="inlineStr">
+      <c r="E816" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F816" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G814" s="4" t="inlineStr">
+      <c r="G816" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.</t>
         </is>
       </c>
-      <c r="H814" s="4" t="inlineStr">
+      <c r="H816" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Masuk.</t>
         </is>
       </c>
     </row>
-    <row r="815" ht="56" customHeight="1">
-      <c r="A815" s="43" t="inlineStr">
+    <row r="817" ht="28" customHeight="1">
+      <c r="A817" s="43" t="inlineStr">
         <is>
           <t>65.5</t>
         </is>
       </c>
-      <c r="B815" s="3" t="inlineStr">
+      <c r="B817" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C815" s="3" t="inlineStr">
+      <c r="C817" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D815" s="4" t="inlineStr">
+      <c r="D817" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Masuk dengan keyword valid</t>
         </is>
       </c>
-      <c r="E815" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F815" s="3" t="inlineStr">
+      <c r="E817" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F817" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G815" s="4" t="inlineStr">
+      <c r="G817" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H815" s="4" t="inlineStr">
+      <c r="H817" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil mengisi field Cari Data.
@@ -36375,45 +36465,45 @@
         </is>
       </c>
     </row>
-    <row r="816" ht="56" customHeight="1">
-      <c r="A816" s="43" t="inlineStr">
+    <row r="818" ht="28" customHeight="1">
+      <c r="A818" s="43" t="inlineStr">
         <is>
           <t>65.6</t>
         </is>
       </c>
-      <c r="B816" s="3" t="inlineStr">
+      <c r="B818" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C816" s="3" t="inlineStr">
+      <c r="C818" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D816" s="4" t="inlineStr">
+      <c r="D818" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E816" s="3" t="inlineStr">
+      <c r="E818" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F816" s="3" t="inlineStr">
+      <c r="F818" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G816" s="4" t="inlineStr">
+      <c r="G818" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H816" s="4" t="inlineStr">
+      <c r="H818" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil mengisi field Cari Data.
@@ -36421,89 +36511,89 @@
         </is>
       </c>
     </row>
-    <row r="817" ht="28" customHeight="1">
-      <c r="A817" s="43" t="inlineStr">
+    <row r="819" ht="42" customHeight="1">
+      <c r="A819" s="43" t="inlineStr">
         <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="B817" s="3" t="inlineStr">
+      <c r="B819" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C817" s="3" t="inlineStr">
+      <c r="C819" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D817" s="4" t="inlineStr">
+      <c r="D819" s="4" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Masuk</t>
         </is>
       </c>
-      <c r="E817" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F817" s="3" t="inlineStr">
+      <c r="E819" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F819" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G817" s="4" t="inlineStr">
+      <c r="G819" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H817" s="4" t="inlineStr">
+      <c r="H819" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="818" ht="28" customHeight="1">
-      <c r="A818" s="43" t="inlineStr">
+    <row r="820" ht="14" customHeight="1">
+      <c r="A820" s="43" t="inlineStr">
         <is>
           <t>65.8</t>
         </is>
       </c>
-      <c r="B818" s="3" t="inlineStr">
+      <c r="B820" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C818" s="3" t="inlineStr">
+      <c r="C820" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D818" s="4" t="inlineStr">
+      <c r="D820" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Masuk</t>
         </is>
       </c>
-      <c r="E818" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F818" s="3" t="inlineStr">
+      <c r="E820" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F820" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G818" s="4" t="inlineStr">
+      <c r="G820" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H818" s="4" t="inlineStr">
+      <c r="H820" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil menampilkan panel Download Export.
@@ -36511,87 +36601,87 @@
         </is>
       </c>
     </row>
-    <row r="819" ht="42" customHeight="1">
-      <c r="A819" s="43" t="inlineStr">
+    <row r="821" ht="56" customHeight="1">
+      <c r="A821" s="43" t="inlineStr">
         <is>
           <t>65.9</t>
         </is>
       </c>
-      <c r="B819" s="3" t="inlineStr">
+      <c r="B821" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C819" s="3" t="inlineStr">
+      <c r="C821" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D819" s="4" t="inlineStr">
+      <c r="D821" s="4" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Closing</t>
         </is>
       </c>
-      <c r="E819" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F819" s="3" t="inlineStr">
+      <c r="E821" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F821" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G819" s="4" t="inlineStr">
+      <c r="G821" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.</t>
         </is>
       </c>
-      <c r="H819" s="4" t="inlineStr">
+      <c r="H821" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Closing.</t>
         </is>
       </c>
     </row>
-    <row r="820" ht="14" customHeight="1">
-      <c r="A820" s="43" t="inlineStr">
+    <row r="822" ht="56" customHeight="1">
+      <c r="A822" s="43" t="inlineStr">
         <is>
           <t>65.10</t>
         </is>
       </c>
-      <c r="B820" s="3" t="inlineStr">
+      <c r="B822" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C820" s="3" t="inlineStr">
+      <c r="C822" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D820" s="4" t="inlineStr">
+      <c r="D822" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Closing dengan keyword valid</t>
         </is>
       </c>
-      <c r="E820" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F820" s="3" t="inlineStr">
+      <c r="E822" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F822" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G820" s="4" t="inlineStr">
+      <c r="G822" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H820" s="4" t="inlineStr">
+      <c r="H822" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil mengisi field Cari Data.
@@ -36599,45 +36689,45 @@
         </is>
       </c>
     </row>
-    <row r="821" ht="56" customHeight="1">
-      <c r="A821" s="43" t="inlineStr">
+    <row r="823" ht="56" customHeight="1">
+      <c r="A823" s="43" t="inlineStr">
         <is>
           <t>65.11</t>
         </is>
       </c>
-      <c r="B821" s="3" t="inlineStr">
+      <c r="B823" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C821" s="3" t="inlineStr">
+      <c r="C823" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D821" s="4" t="inlineStr">
+      <c r="D823" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E821" s="3" t="inlineStr">
+      <c r="E823" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F821" s="3" t="inlineStr">
+      <c r="F823" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G821" s="4" t="inlineStr">
+      <c r="G823" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H821" s="4" t="inlineStr">
+      <c r="H823" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil mengisi field Cari Data.
@@ -36645,89 +36735,89 @@
         </is>
       </c>
     </row>
-    <row r="822" ht="56" customHeight="1">
-      <c r="A822" s="43" t="inlineStr">
+    <row r="824" ht="14" customHeight="1">
+      <c r="A824" s="43" t="inlineStr">
         <is>
           <t>65.12</t>
         </is>
       </c>
-      <c r="B822" s="3" t="inlineStr">
+      <c r="B824" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C822" s="3" t="inlineStr">
+      <c r="C824" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D822" s="4" t="inlineStr">
+      <c r="D824" s="4" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Closing</t>
         </is>
       </c>
-      <c r="E822" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F822" s="3" t="inlineStr">
+      <c r="E824" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F824" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G822" s="4" t="inlineStr">
+      <c r="G824" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H822" s="4" t="inlineStr">
+      <c r="H824" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="823" ht="56" customHeight="1">
-      <c r="A823" s="43" t="inlineStr">
+    <row r="825" ht="14" customHeight="1">
+      <c r="A825" s="43" t="inlineStr">
         <is>
           <t>65.13</t>
         </is>
       </c>
-      <c r="B823" s="3" t="inlineStr">
+      <c r="B825" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C823" s="3" t="inlineStr">
+      <c r="C825" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D823" s="4" t="inlineStr">
+      <c r="D825" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Closing</t>
         </is>
       </c>
-      <c r="E823" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F823" s="3" t="inlineStr">
+      <c r="E825" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F825" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G823" s="4" t="inlineStr">
+      <c r="G825" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H823" s="4" t="inlineStr">
+      <c r="H825" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil menampilkan panel Download Export.
@@ -36735,87 +36825,87 @@
         </is>
       </c>
     </row>
-    <row r="824" ht="14" customHeight="1">
-      <c r="A824" s="43" t="inlineStr">
+    <row r="826" ht="14" customHeight="1">
+      <c r="A826" s="43" t="inlineStr">
         <is>
           <t>65.14</t>
         </is>
       </c>
-      <c r="B824" s="3" t="inlineStr">
+      <c r="B826" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C824" s="3" t="inlineStr">
+      <c r="C826" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D824" s="4" t="inlineStr">
+      <c r="D826" s="4" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Referal</t>
         </is>
       </c>
-      <c r="E824" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F824" s="3" t="inlineStr">
+      <c r="E826" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F826" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G824" s="4" t="inlineStr">
+      <c r="G826" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.</t>
         </is>
       </c>
-      <c r="H824" s="4" t="inlineStr">
+      <c r="H826" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Referal.</t>
         </is>
       </c>
     </row>
-    <row r="825" ht="14" customHeight="1">
-      <c r="A825" s="43" t="inlineStr">
+    <row r="827" ht="42" customHeight="1">
+      <c r="A827" s="43" t="inlineStr">
         <is>
           <t>65.15</t>
         </is>
       </c>
-      <c r="B825" s="3" t="inlineStr">
+      <c r="B827" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C825" s="3" t="inlineStr">
+      <c r="C827" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D825" s="4" t="inlineStr">
+      <c r="D827" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal dengan keyword valid</t>
         </is>
       </c>
-      <c r="E825" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F825" s="3" t="inlineStr">
+      <c r="E827" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F827" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G825" s="4" t="inlineStr">
+      <c r="G827" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H825" s="4" t="inlineStr">
+      <c r="H827" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil mengisi field Cari Data.
@@ -36823,45 +36913,45 @@
         </is>
       </c>
     </row>
-    <row r="826" ht="14" customHeight="1">
-      <c r="A826" s="43" t="inlineStr">
+    <row r="828" ht="14" customHeight="1">
+      <c r="A828" s="43" t="inlineStr">
         <is>
           <t>65.16</t>
         </is>
       </c>
-      <c r="B826" s="3" t="inlineStr">
+      <c r="B828" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C826" s="3" t="inlineStr">
+      <c r="C828" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D826" s="4" t="inlineStr">
+      <c r="D828" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E826" s="3" t="inlineStr">
+      <c r="E828" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F826" s="3" t="inlineStr">
+      <c r="F828" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G826" s="4" t="inlineStr">
+      <c r="G828" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H826" s="4" t="inlineStr">
+      <c r="H828" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil mengisi field Cari Data.
@@ -36869,89 +36959,89 @@
         </is>
       </c>
     </row>
-    <row r="827" ht="42" customHeight="1">
-      <c r="A827" s="43" t="inlineStr">
+    <row r="829" ht="56" customHeight="1">
+      <c r="A829" s="43" t="inlineStr">
         <is>
           <t>65.17</t>
         </is>
       </c>
-      <c r="B827" s="3" t="inlineStr">
+      <c r="B829" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C827" s="3" t="inlineStr">
+      <c r="C829" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D827" s="4" t="inlineStr">
+      <c r="D829" s="4" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Referal</t>
         </is>
       </c>
-      <c r="E827" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F827" s="3" t="inlineStr">
+      <c r="E829" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F829" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G827" s="4" t="inlineStr">
+      <c r="G829" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H827" s="4" t="inlineStr">
+      <c r="H829" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="828" ht="14" customHeight="1">
-      <c r="A828" s="43" t="inlineStr">
+    <row r="830" ht="28" customHeight="1">
+      <c r="A830" s="43" t="inlineStr">
         <is>
           <t>65.18</t>
         </is>
       </c>
-      <c r="B828" s="3" t="inlineStr">
+      <c r="B830" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C828" s="3" t="inlineStr">
+      <c r="C830" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D828" s="4" t="inlineStr">
+      <c r="D830" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Referal</t>
         </is>
       </c>
-      <c r="E828" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F828" s="3" t="inlineStr">
+      <c r="E830" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F830" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G828" s="4" t="inlineStr">
+      <c r="G830" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H828" s="4" t="inlineStr">
+      <c r="H830" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil menampilkan panel Download Export.
@@ -36959,87 +37049,87 @@
         </is>
       </c>
     </row>
-    <row r="829" ht="56" customHeight="1">
-      <c r="A829" s="43" t="inlineStr">
+    <row r="831" ht="42" customHeight="1">
+      <c r="A831" s="43" t="inlineStr">
         <is>
           <t>65.19</t>
         </is>
       </c>
-      <c r="B829" s="3" t="inlineStr">
+      <c r="B831" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C829" s="3" t="inlineStr">
+      <c r="C831" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D829" s="4" t="inlineStr">
+      <c r="D831" s="4" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E829" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F829" s="3" t="inlineStr">
+      <c r="E831" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F831" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G829" s="4" t="inlineStr">
+      <c r="G831" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.</t>
         </is>
       </c>
-      <c r="H829" s="4" t="inlineStr">
+      <c r="H831" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
         </is>
       </c>
     </row>
-    <row r="830" ht="28" customHeight="1">
-      <c r="A830" s="43" t="inlineStr">
+    <row r="832" ht="28" customHeight="1">
+      <c r="A832" s="43" t="inlineStr">
         <is>
           <t>65.20</t>
         </is>
       </c>
-      <c r="B830" s="3" t="inlineStr">
+      <c r="B832" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C830" s="3" t="inlineStr">
+      <c r="C832" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D830" s="4" t="inlineStr">
+      <c r="D832" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
         </is>
       </c>
-      <c r="E830" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F830" s="3" t="inlineStr">
+      <c r="E832" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F832" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G830" s="4" t="inlineStr">
+      <c r="G832" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H830" s="4" t="inlineStr">
+      <c r="H832" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil mengisi field Cari Data.
@@ -37047,45 +37137,45 @@
         </is>
       </c>
     </row>
-    <row r="831" ht="42" customHeight="1">
-      <c r="A831" s="43" t="inlineStr">
+    <row r="833" ht="14" customHeight="1">
+      <c r="A833" s="43" t="inlineStr">
         <is>
           <t>65.21</t>
         </is>
       </c>
-      <c r="B831" s="3" t="inlineStr">
+      <c r="B833" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C831" s="3" t="inlineStr">
+      <c r="C833" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D831" s="4" t="inlineStr">
+      <c r="D833" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal Closing dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E831" s="3" t="inlineStr">
+      <c r="E833" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F831" s="3" t="inlineStr">
+      <c r="F833" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G831" s="4" t="inlineStr">
+      <c r="G833" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H831" s="4" t="inlineStr">
+      <c r="H833" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil mengisi field Cari Data.
@@ -37093,89 +37183,89 @@
         </is>
       </c>
     </row>
-    <row r="832" ht="28" customHeight="1">
-      <c r="A832" s="43" t="inlineStr">
+    <row r="834" ht="14" customHeight="1">
+      <c r="A834" s="43" t="inlineStr">
         <is>
           <t>65.22</t>
         </is>
       </c>
-      <c r="B832" s="3" t="inlineStr">
+      <c r="B834" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C832" s="3" t="inlineStr">
+      <c r="C834" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D832" s="4" t="inlineStr">
+      <c r="D834" s="4" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E832" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F832" s="3" t="inlineStr">
+      <c r="E834" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F834" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G832" s="4" t="inlineStr">
+      <c r="G834" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H832" s="4" t="inlineStr">
+      <c r="H834" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="833" ht="14" customHeight="1">
-      <c r="A833" s="43" t="inlineStr">
+    <row r="835" ht="14" customHeight="1">
+      <c r="A835" s="43" t="inlineStr">
         <is>
           <t>65.23</t>
         </is>
       </c>
-      <c r="B833" s="3" t="inlineStr">
+      <c r="B835" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C833" s="3" t="inlineStr">
+      <c r="C835" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D833" s="4" t="inlineStr">
+      <c r="D835" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E833" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F833" s="3" t="inlineStr">
+      <c r="E835" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F835" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G833" s="4" t="inlineStr">
+      <c r="G835" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H833" s="4" t="inlineStr">
+      <c r="H835" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil menampilkan panel Download Export.
@@ -37183,745 +37273,745 @@
         </is>
       </c>
     </row>
-    <row r="834" ht="14" customHeight="1">
-      <c r="A834" s="43" t="inlineStr">
+    <row r="836" ht="42" customHeight="1">
+      <c r="A836" s="43" t="inlineStr">
         <is>
           <t>66.1</t>
         </is>
       </c>
-      <c r="B834" s="3" t="inlineStr">
+      <c r="B836" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C834" s="3" t="inlineStr">
+      <c r="C836" s="3" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D834" s="4" t="inlineStr">
+      <c r="D836" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Personal Funnel</t>
         </is>
       </c>
-      <c r="E834" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F834" s="3" t="inlineStr">
+      <c r="E836" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F836" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G834" s="4" t="inlineStr">
+      <c r="G836" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Lending.
 2. Klik sub menu Personal Funnel.</t>
         </is>
       </c>
-      <c r="H834" s="4" t="inlineStr">
+      <c r="H836" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Lending.
 2. Berhasil menampilkan halaman Personal Funnel.</t>
         </is>
       </c>
     </row>
-    <row r="835" ht="14" customHeight="1">
-      <c r="A835" s="43" t="inlineStr">
+    <row r="837" ht="28" customHeight="1">
+      <c r="A837" s="43" t="inlineStr">
         <is>
           <t>66.2</t>
         </is>
       </c>
-      <c r="B835" s="3" t="inlineStr">
+      <c r="B837" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C835" s="3" t="inlineStr">
+      <c r="C837" s="3" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D835" s="4" t="inlineStr">
+      <c r="D837" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Personal Funnel</t>
         </is>
       </c>
-      <c r="E835" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F835" s="3" t="inlineStr">
+      <c r="E837" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F837" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G835" s="4" t="inlineStr">
+      <c r="G837" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi semua field filter mandatory.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H835" s="4" t="inlineStr">
+      <c r="H837" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field filter mandatory.
 2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="836" ht="42" customHeight="1">
-      <c r="A836" s="43" t="inlineStr">
+    <row r="838" ht="28" customHeight="1">
+      <c r="A838" s="43" t="inlineStr">
         <is>
           <t>66.3</t>
         </is>
       </c>
-      <c r="B836" s="3" t="inlineStr">
+      <c r="B838" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C836" s="3" t="inlineStr">
+      <c r="C838" s="3" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D836" s="4" t="inlineStr">
+      <c r="D838" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E836" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F836" s="3" t="inlineStr">
+      <c r="E838" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F838" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G836" s="4" t="inlineStr">
+      <c r="G838" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H836" s="4" t="inlineStr">
+      <c r="H838" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
-    <row r="837" ht="28" customHeight="1">
-      <c r="A837" s="43" t="inlineStr">
+    <row r="839" ht="70" customHeight="1">
+      <c r="A839" s="43" t="inlineStr">
         <is>
           <t>66.4</t>
         </is>
       </c>
-      <c r="B837" s="3" t="inlineStr">
+      <c r="B839" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C837" s="3" t="inlineStr">
+      <c r="C839" s="3" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D837" s="4" t="inlineStr">
+      <c r="D839" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data Personal Funnel</t>
         </is>
       </c>
-      <c r="E837" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F837" s="3" t="inlineStr">
+      <c r="E839" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F839" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G837" s="4" t="inlineStr">
+      <c r="G839" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Export.
 2. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H837" s="4" t="inlineStr">
+      <c r="H839" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan panel Download Export.
 2. Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
-    <row r="838" ht="28" customHeight="1">
-      <c r="A838" s="43" t="inlineStr">
+    <row r="840" ht="28" customHeight="1">
+      <c r="A840" s="43" t="inlineStr">
         <is>
           <t>67.1</t>
         </is>
       </c>
-      <c r="B838" s="3" t="inlineStr">
+      <c r="B840" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C838" s="3" t="inlineStr">
+      <c r="C840" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D838" s="4" t="inlineStr">
+      <c r="D840" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Rekap Funnel</t>
         </is>
       </c>
-      <c r="E838" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F838" s="3" t="inlineStr">
+      <c r="E840" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F840" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G838" s="4" t="inlineStr">
+      <c r="G840" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Lending.
 2. Klik sub menu Rekap Funnel.</t>
         </is>
       </c>
-      <c r="H838" s="4" t="inlineStr">
+      <c r="H840" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Lending.
 2. Berhasil menampilkan halaman Rekap Funnel.</t>
         </is>
       </c>
     </row>
-    <row r="839" ht="70" customHeight="1">
-      <c r="A839" s="43" t="inlineStr">
+    <row r="841" ht="84" customHeight="1">
+      <c r="A841" s="43" t="inlineStr">
         <is>
           <t>67.2</t>
         </is>
       </c>
-      <c r="B839" s="3" t="inlineStr">
+      <c r="B841" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C839" s="3" t="inlineStr">
+      <c r="C841" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D839" s="4" t="inlineStr">
+      <c r="D841" s="4" t="inlineStr">
         <is>
           <t>Menampilkan data Rekap Funnel</t>
         </is>
       </c>
-      <c r="E839" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F839" s="3" t="inlineStr">
+      <c r="E841" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F841" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G839" s="4" t="inlineStr">
+      <c r="G841" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun).
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H839" s="4" t="inlineStr">
+      <c r="H841" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field filter mandatory.
 2. Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
         </is>
       </c>
     </row>
-    <row r="840" ht="28" customHeight="1">
-      <c r="A840" s="43" t="inlineStr">
+    <row r="842" ht="28" customHeight="1">
+      <c r="A842" s="43" t="inlineStr">
         <is>
           <t>67.3</t>
         </is>
       </c>
-      <c r="B840" s="3" t="inlineStr">
+      <c r="B842" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C840" s="3" t="inlineStr">
+      <c r="C842" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D840" s="4" t="inlineStr">
+      <c r="D842" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Rekap Funnel</t>
         </is>
       </c>
-      <c r="E840" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F840" s="3" t="inlineStr">
+      <c r="E842" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F842" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G840" s="4" t="inlineStr">
+      <c r="G842" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H840" s="4" t="inlineStr">
+      <c r="H842" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi kriteria filter.
 2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="841" ht="84" customHeight="1">
-      <c r="A841" s="43" t="inlineStr">
+    <row r="843" ht="28" customHeight="1">
+      <c r="A843" s="43" t="inlineStr">
         <is>
           <t>67.4</t>
         </is>
       </c>
-      <c r="B841" s="3" t="inlineStr">
+      <c r="B843" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C841" s="3" t="inlineStr">
+      <c r="C843" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D841" s="4" t="inlineStr">
+      <c r="D843" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E841" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F841" s="3" t="inlineStr">
+      <c r="E843" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F843" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G841" s="4" t="inlineStr">
+      <c r="G843" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H841" s="4" t="inlineStr">
+      <c r="H843" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
-    <row r="842" ht="28" customHeight="1">
-      <c r="A842" s="43" t="inlineStr">
+    <row r="844" ht="28" customHeight="1">
+      <c r="A844" s="43" t="inlineStr">
         <is>
           <t>67.5</t>
         </is>
       </c>
-      <c r="B842" s="3" t="inlineStr">
+      <c r="B844" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C842" s="3" t="inlineStr">
+      <c r="C844" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D842" s="4" t="inlineStr">
+      <c r="D844" s="4" t="inlineStr">
         <is>
           <t>Mengunduh data Rekap Funnel</t>
         </is>
       </c>
-      <c r="E842" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F842" s="3" t="inlineStr">
+      <c r="E844" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F844" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G842" s="4" t="inlineStr">
+      <c r="G844" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Download Excel.</t>
         </is>
       </c>
-      <c r="H842" s="4" t="inlineStr">
+      <c r="H844" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mendownload file Excel data Rekap Funnel.</t>
         </is>
       </c>
     </row>
-    <row r="843" ht="28" customHeight="1">
-      <c r="A843" s="43" t="inlineStr">
+    <row r="845" ht="42" customHeight="1">
+      <c r="A845" s="43" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="B843" s="3" t="inlineStr">
+      <c r="B845" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C843" s="3" t="inlineStr">
+      <c r="C845" s="3" t="inlineStr">
         <is>
           <t>Regional Funnel</t>
         </is>
       </c>
-      <c r="D843" s="4" t="inlineStr">
+      <c r="D845" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Regional Funnel</t>
         </is>
       </c>
-      <c r="E843" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F843" s="3" t="inlineStr">
+      <c r="E845" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F845" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G843" s="4" t="inlineStr">
+      <c r="G845" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Lending.
 2. Klik sub menu Regional Funnel.</t>
         </is>
       </c>
-      <c r="H843" s="4" t="inlineStr">
+      <c r="H845" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Lending.
 2. Berhasil menampilkan halaman Regional Funnel.</t>
         </is>
       </c>
     </row>
-    <row r="844" ht="28" customHeight="1">
-      <c r="A844" s="43" t="inlineStr">
+    <row r="846" ht="28" customHeight="1">
+      <c r="A846" s="43" t="inlineStr">
         <is>
           <t>68.2</t>
         </is>
       </c>
-      <c r="B844" s="3" t="inlineStr">
+      <c r="B846" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C844" s="3" t="inlineStr">
+      <c r="C846" s="3" t="inlineStr">
         <is>
           <t>Regional Funnel</t>
         </is>
       </c>
-      <c r="D844" s="4" t="inlineStr">
+      <c r="D846" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Regional Funnel</t>
         </is>
       </c>
-      <c r="E844" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F844" s="3" t="inlineStr">
+      <c r="E846" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F846" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G844" s="4" t="inlineStr">
+      <c r="G846" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi semua field filter mandatory.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H844" s="4" t="inlineStr">
+      <c r="H846" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field filter mandatory.
 2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="845" ht="42" customHeight="1">
-      <c r="A845" s="43" t="inlineStr">
+    <row r="847" ht="14" customHeight="1">
+      <c r="A847" s="43" t="inlineStr">
         <is>
           <t>68.3</t>
         </is>
       </c>
-      <c r="B845" s="3" t="inlineStr">
+      <c r="B847" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C845" s="3" t="inlineStr">
+      <c r="C847" s="3" t="inlineStr">
         <is>
           <t>Regional Funnel</t>
         </is>
       </c>
-      <c r="D845" s="4" t="inlineStr">
+      <c r="D847" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E845" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F845" s="3" t="inlineStr">
+      <c r="E847" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F847" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G845" s="4" t="inlineStr">
+      <c r="G847" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H845" s="4" t="inlineStr">
+      <c r="H847" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
-    <row r="846" ht="28" customHeight="1">
-      <c r="A846" s="43" t="inlineStr">
+    <row r="848" ht="14" customHeight="1">
+      <c r="A848" s="43" t="inlineStr">
         <is>
           <t>69.1</t>
         </is>
       </c>
-      <c r="B846" s="3" t="inlineStr">
+      <c r="B848" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C846" s="3" t="inlineStr">
+      <c r="C848" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D846" s="4" t="inlineStr">
+      <c r="D848" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Pengaturan Funnel Lending</t>
         </is>
       </c>
-      <c r="E846" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F846" s="3" t="inlineStr">
+      <c r="E848" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F848" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G846" s="4" t="inlineStr">
+      <c r="G848" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Lending.
 2. Klik sub menu Pengaturan Funnel.</t>
         </is>
       </c>
-      <c r="H846" s="4" t="inlineStr">
+      <c r="H848" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Lending.
 2. Berhasil menampilkan halaman Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="847" ht="14" customHeight="1">
-      <c r="A847" s="43" t="inlineStr">
+    <row r="849" ht="42" customHeight="1">
+      <c r="A849" s="43" t="inlineStr">
         <is>
           <t>69.2</t>
         </is>
       </c>
-      <c r="B847" s="3" t="inlineStr">
+      <c r="B849" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C847" s="3" t="inlineStr">
+      <c r="C849" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D847" s="4" t="inlineStr">
+      <c r="D849" s="4" t="inlineStr">
         <is>
           <t>Menampilkan data Pengaturan Funnel Lending berdasarkan section</t>
         </is>
       </c>
-      <c r="E847" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F847" s="3" t="inlineStr">
+      <c r="E849" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F849" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G847" s="4" t="inlineStr">
+      <c r="G849" s="4" t="inlineStr">
         <is>
           <t>1. Klik salah satu daftar section pada tabel.</t>
         </is>
       </c>
-      <c r="H847" s="4" t="inlineStr">
+      <c r="H849" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pengaturan funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="848" ht="14" customHeight="1">
-      <c r="A848" s="43" t="inlineStr">
+    <row r="850" ht="28" customHeight="1">
+      <c r="A850" s="43" t="inlineStr">
         <is>
           <t>69.3</t>
         </is>
       </c>
-      <c r="B848" s="3" t="inlineStr">
+      <c r="B850" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C848" s="3" t="inlineStr">
+      <c r="C850" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D848" s="4" t="inlineStr">
+      <c r="D850" s="4" t="inlineStr">
         <is>
           <t>Mengubah data Pengaturan Funnel Lending</t>
         </is>
       </c>
-      <c r="E848" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F848" s="3" t="inlineStr">
+      <c r="E850" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F850" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G848" s="4" t="inlineStr">
+      <c r="G850" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H848" s="4" t="inlineStr">
+      <c r="H850" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field Performance Percentage.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="849" ht="42" customHeight="1">
-      <c r="A849" s="43" t="inlineStr">
+    <row r="851" ht="28" customHeight="1">
+      <c r="A851" s="43" t="inlineStr">
         <is>
           <t>69.4</t>
         </is>
       </c>
-      <c r="B849" s="3" t="inlineStr">
+      <c r="B851" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C849" s="3" t="inlineStr">
+      <c r="C851" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D849" s="4" t="inlineStr">
+      <c r="D851" s="4" t="inlineStr">
         <is>
           <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E849" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F849" s="3" t="inlineStr">
+      <c r="E851" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F851" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G849" s="4" t="inlineStr">
+      <c r="G851" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field mandatory Performance Percentage.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H849" s="4" t="inlineStr">
+      <c r="H851" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field Performance Percentage.
 2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
-    <row r="850" ht="28" customHeight="1">
-      <c r="A850" s="43" t="inlineStr">
+    <row r="852" ht="28" customHeight="1">
+      <c r="A852" s="43" t="inlineStr">
         <is>
           <t>69.5</t>
         </is>
       </c>
-      <c r="B850" s="3" t="inlineStr">
+      <c r="B852" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C850" s="3" t="inlineStr">
+      <c r="C852" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D850" s="4" t="inlineStr">
+      <c r="D852" s="4" t="inlineStr">
         <is>
           <t>Menambahkan Condition pada Performance Indicator</t>
         </is>
       </c>
-      <c r="E850" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F850" s="3" t="inlineStr">
+      <c r="E852" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F852" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G850" s="4" t="inlineStr">
+      <c r="G852" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Add Condition pada bagian Performance Indicator.
 2. Mengisi semua field mandatory pada condition baru.
 3. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H850" s="4" t="inlineStr">
+      <c r="H852" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan form condition baru pada Performance Indicator.
 2. Berhasil mengisi field mandatory condition.
@@ -37929,45 +38019,45 @@
         </is>
       </c>
     </row>
-    <row r="851" ht="28" customHeight="1">
-      <c r="A851" s="43" t="inlineStr">
+    <row r="853" ht="28" customHeight="1">
+      <c r="A853" s="43" t="inlineStr">
         <is>
           <t>69.6</t>
         </is>
       </c>
-      <c r="B851" s="3" t="inlineStr">
+      <c r="B853" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C851" s="3" t="inlineStr">
+      <c r="C853" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D851" s="4" t="inlineStr">
+      <c r="D853" s="4" t="inlineStr">
         <is>
           <t>Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E851" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F851" s="3" t="inlineStr">
+      <c r="E853" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F853" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G851" s="4" t="inlineStr">
+      <c r="G853" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Add Condition pada bagian Performance Indicator.
 2. Mengosongkan field mandatory pada condition baru.
 3. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H851" s="4" t="inlineStr">
+      <c r="H853" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan form condition baru pada Performance Indicator.
 2. Berhasil mengosongkan field mandatory condition.
@@ -37975,170 +38065,170 @@
         </is>
       </c>
     </row>
-    <row r="852" ht="28" customHeight="1">
-      <c r="A852" s="43" t="inlineStr">
+    <row r="854" ht="28" customHeight="1">
+      <c r="A854" s="43" t="inlineStr">
         <is>
           <t>69.7</t>
         </is>
       </c>
-      <c r="B852" s="3" t="inlineStr">
+      <c r="B854" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C852" s="3" t="inlineStr">
+      <c r="C854" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D852" s="4" t="inlineStr">
+      <c r="D854" s="4" t="inlineStr">
         <is>
           <t>Menghapus Condition pada Performance Indicator</t>
         </is>
       </c>
-      <c r="E852" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F852" s="3" t="inlineStr">
+      <c r="E854" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F854" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G852" s="4" t="inlineStr">
+      <c r="G854" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Remove pada salah satu condition di Performance Indicator.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H852" s="4" t="inlineStr">
+      <c r="H854" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menghapus condition dari Performance Indicator.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="853" ht="28" customHeight="1">
-      <c r="A853" s="43" t="inlineStr">
+    <row r="855" ht="28" customHeight="1">
+      <c r="A855" s="43" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="B853" s="3" t="inlineStr">
+      <c r="B855" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C853" s="3" t="inlineStr">
+      <c r="C855" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D853" s="4" t="inlineStr">
+      <c r="D855" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Approval non Banking</t>
         </is>
       </c>
-      <c r="E853" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F853" s="3" t="inlineStr">
+      <c r="E855" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F855" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G853" s="4" t="inlineStr">
+      <c r="G855" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Re-Assign &amp; Approval 
 2. Klik submenu Approval non banking</t>
         </is>
       </c>
-      <c r="H853" s="4" t="inlineStr">
+      <c r="H855" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan submenu Re-Assign &amp; Approval 
 2. Menampilkan halaman Approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="854" ht="28" customHeight="1">
-      <c r="A854" s="43" t="inlineStr">
+    <row r="856" ht="28" customHeight="1">
+      <c r="A856" s="43" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="B854" s="3" t="inlineStr">
+      <c r="B856" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C854" s="3" t="inlineStr">
+      <c r="C856" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D854" s="4" t="inlineStr">
+      <c r="D856" s="4" t="inlineStr">
         <is>
           <t>Melihat Detail data Approval non banking</t>
         </is>
       </c>
-      <c r="E854" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F854" s="3" t="inlineStr">
+      <c r="E856" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F856" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G854" s="4" t="inlineStr">
+      <c r="G856" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Detail</t>
         </is>
       </c>
-      <c r="H854" s="4" t="inlineStr">
+      <c r="H856" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan halaman detail data approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="855" ht="28" customHeight="1">
-      <c r="A855" s="43" t="inlineStr">
+    <row r="857" ht="28" customHeight="1">
+      <c r="A857" s="43" t="inlineStr">
         <is>
           <t>70.3</t>
         </is>
       </c>
-      <c r="B855" s="3" t="inlineStr">
+      <c r="B857" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C855" s="3" t="inlineStr">
+      <c r="C857" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D855" s="4" t="inlineStr">
+      <c r="D857" s="4" t="inlineStr">
         <is>
           <t>Menyetujui Prospek</t>
         </is>
       </c>
-      <c r="E855" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F855" s="3" t="inlineStr">
+      <c r="E857" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F857" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G855" s="4" t="inlineStr">
+      <c r="G857" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Setujui 
@@ -38147,7 +38237,7 @@
 5. Klik button Setujui</t>
         </is>
       </c>
-      <c r="H855" s="4" t="inlineStr">
+      <c r="H857" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan modal approve 
@@ -38157,87 +38247,87 @@
         </is>
       </c>
     </row>
-    <row r="856" ht="28" customHeight="1">
-      <c r="A856" s="43" t="inlineStr">
+    <row r="858" ht="28" customHeight="1">
+      <c r="A858" s="43" t="inlineStr">
         <is>
           <t>70.4</t>
         </is>
       </c>
-      <c r="B856" s="3" t="inlineStr">
+      <c r="B858" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C856" s="3" t="inlineStr">
+      <c r="C858" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D856" s="4" t="inlineStr">
+      <c r="D858" s="4" t="inlineStr">
         <is>
           <t>Batal menyetujui Prospek</t>
         </is>
       </c>
-      <c r="E856" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F856" s="3" t="inlineStr">
+      <c r="E858" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F858" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G856" s="4" t="inlineStr">
+      <c r="G858" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Batalkan pada modal approve</t>
         </is>
       </c>
-      <c r="H856" s="4" t="inlineStr">
+      <c r="H858" s="4" t="inlineStr">
         <is>
           <t>1. Modal approve tertutup dan tetap di halaman approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="857" ht="28" customHeight="1">
-      <c r="A857" s="43" t="inlineStr">
+    <row r="859" ht="28" customHeight="1">
+      <c r="A859" s="43" t="inlineStr">
         <is>
           <t>70.5</t>
         </is>
       </c>
-      <c r="B857" s="3" t="inlineStr">
+      <c r="B859" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C857" s="3" t="inlineStr">
+      <c r="C859" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D857" s="4" t="inlineStr">
+      <c r="D859" s="4" t="inlineStr">
         <is>
           <t>Tidak menginput nilai realisasi pada modal approve</t>
         </is>
       </c>
-      <c r="E857" s="3" t="inlineStr">
+      <c r="E859" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F857" s="3" t="inlineStr">
+      <c r="F859" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G857" s="4" t="inlineStr">
+      <c r="G859" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan nilai realisasi 
 2. Input remark 
 3. Klik button Setujui</t>
         </is>
       </c>
-      <c r="H857" s="4" t="inlineStr">
+      <c r="H859" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field realisasi 
 2. Berhasil menginput remark 
@@ -38245,122 +38335,122 @@
         </is>
       </c>
     </row>
-    <row r="858" ht="28" customHeight="1">
-      <c r="A858" s="43" t="inlineStr">
-        <is>
-          <t>70.6</t>
-        </is>
-      </c>
-      <c r="B858" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C858" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D858" s="4" t="inlineStr">
-        <is>
-          <t>Tidak menginput remark pada modal approve</t>
-        </is>
-      </c>
-      <c r="E858" s="3" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F858" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G858" s="4" t="inlineStr">
-        <is>
-          <t>1. Kosongkan remark</t>
-        </is>
-      </c>
-      <c r="H858" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan alert 'Remark dibutuhkan!'</t>
-        </is>
-      </c>
-    </row>
-    <row r="859" ht="28" customHeight="1">
-      <c r="A859" s="43" t="inlineStr">
-        <is>
-          <t>70.7</t>
-        </is>
-      </c>
-      <c r="B859" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C859" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D859" s="4" t="inlineStr">
-        <is>
-          <t>Menginput huruf pada field realisasi</t>
-        </is>
-      </c>
-      <c r="E859" s="3" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F859" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G859" s="4" t="inlineStr">
-        <is>
-          <t>1. Input huruf pada field realisasi kemudian pindah ke filed lain</t>
-        </is>
-      </c>
-      <c r="H859" s="4" t="inlineStr">
-        <is>
-          <t>1. Sistem menghapus input non-numerik secara otomatis saat field kehilangan fokus. Field Realiasi menjadi kosong</t>
-        </is>
-      </c>
-    </row>
     <row r="860" ht="28" customHeight="1">
       <c r="A860" s="43" t="inlineStr">
         <is>
+          <t>70.6</t>
+        </is>
+      </c>
+      <c r="B860" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C860" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D860" s="4" t="inlineStr">
+        <is>
+          <t>Tidak menginput remark pada modal approve</t>
+        </is>
+      </c>
+      <c r="E860" s="3" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F860" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G860" s="4" t="inlineStr">
+        <is>
+          <t>1. Kosongkan remark</t>
+        </is>
+      </c>
+      <c r="H860" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan alert 'Remark dibutuhkan!'</t>
+        </is>
+      </c>
+    </row>
+    <row r="861" ht="28" customHeight="1">
+      <c r="A861" s="43" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="B861" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C861" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D861" s="4" t="inlineStr">
+        <is>
+          <t>Menginput huruf pada field realisasi</t>
+        </is>
+      </c>
+      <c r="E861" s="3" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F861" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G861" s="4" t="inlineStr">
+        <is>
+          <t>1. Input huruf pada field realisasi kemudian pindah ke filed lain</t>
+        </is>
+      </c>
+      <c r="H861" s="4" t="inlineStr">
+        <is>
+          <t>1. Sistem menghapus input non-numerik secara otomatis saat field kehilangan fokus. Field Realiasi menjadi kosong</t>
+        </is>
+      </c>
+    </row>
+    <row r="862" ht="28" customHeight="1">
+      <c r="A862" s="43" t="inlineStr">
+        <is>
           <t>70.8</t>
         </is>
       </c>
-      <c r="B860" s="3" t="inlineStr">
+      <c r="B862" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C860" s="3" t="inlineStr">
+      <c r="C862" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D860" s="4" t="inlineStr">
+      <c r="D862" s="4" t="inlineStr">
         <is>
           <t>Menolak Prospek</t>
         </is>
       </c>
-      <c r="E860" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F860" s="3" t="inlineStr">
+      <c r="E862" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F862" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G860" s="4" t="inlineStr">
+      <c r="G862" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Tolak 
@@ -38368,7 +38458,7 @@
 4. Klik button Tolak</t>
         </is>
       </c>
-      <c r="H860" s="4" t="inlineStr">
+      <c r="H862" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan modal tolak prospek
@@ -38377,210 +38467,210 @@
         </is>
       </c>
     </row>
-    <row r="861" ht="28" customHeight="1">
-      <c r="A861" s="43" t="inlineStr">
+    <row r="863" ht="28" customHeight="1">
+      <c r="A863" s="43" t="inlineStr">
         <is>
           <t>70.9</t>
         </is>
       </c>
-      <c r="B861" s="3" t="inlineStr">
+      <c r="B863" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C861" s="3" t="inlineStr">
+      <c r="C863" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D861" s="4" t="inlineStr">
+      <c r="D863" s="4" t="inlineStr">
         <is>
           <t>Batal menolak prospek</t>
         </is>
       </c>
-      <c r="E861" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F861" s="3" t="inlineStr">
+      <c r="E863" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F863" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G861" s="4" t="inlineStr">
+      <c r="G863" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Batalkan pada moal tolak prospek</t>
         </is>
       </c>
-      <c r="H861" s="4" t="inlineStr">
+      <c r="H863" s="4" t="inlineStr">
         <is>
           <t>1. Modal tolak prospek tertutup dan tetap berada di halaman approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="862" ht="28" customHeight="1">
-      <c r="A862" s="43" t="inlineStr">
+    <row r="864" ht="28" customHeight="1">
+      <c r="A864" s="43" t="inlineStr">
         <is>
           <t>70.10</t>
         </is>
       </c>
-      <c r="B862" s="3" t="inlineStr">
+      <c r="B864" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C862" s="3" t="inlineStr">
+      <c r="C864" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D862" s="4" t="inlineStr">
+      <c r="D864" s="4" t="inlineStr">
         <is>
           <t>Tidak menginput remark pada modal tolak prospek</t>
         </is>
       </c>
-      <c r="E862" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F862" s="3" t="inlineStr">
+      <c r="E864" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F864" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G862" s="4" t="inlineStr">
+      <c r="G864" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan remark 
 2. Klik button Tolak</t>
         </is>
       </c>
-      <c r="H862" s="4" t="inlineStr">
+      <c r="H864" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan remark 
 2. Menampilkan alert 'Remark dibutuhkan!'</t>
         </is>
       </c>
     </row>
-    <row r="863" ht="28" customHeight="1">
-      <c r="A863" s="43" t="inlineStr">
+    <row r="865" ht="28" customHeight="1">
+      <c r="A865" s="43" t="inlineStr">
         <is>
           <t>70.11</t>
         </is>
       </c>
-      <c r="B863" s="3" t="inlineStr">
+      <c r="B865" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C863" s="3" t="inlineStr">
+      <c r="C865" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D863" s="4" t="inlineStr">
+      <c r="D865" s="4" t="inlineStr">
         <is>
           <t>Filter kolom</t>
         </is>
       </c>
-      <c r="E863" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F863" s="3" t="inlineStr">
+      <c r="E865" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F865" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G863" s="4" t="inlineStr">
+      <c r="G865" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon filter kolom 
 2. Checklist/unchecklist kolom</t>
         </is>
       </c>
-      <c r="H863" s="4" t="inlineStr">
+      <c r="H865" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan list kolom tabel 
 2. Menampilkan data tabel sesuai dengan kolom yang di ceklis</t>
         </is>
       </c>
     </row>
-    <row r="864" ht="28" customHeight="1">
-      <c r="A864" s="43" t="inlineStr">
+    <row r="866" ht="28" customHeight="1">
+      <c r="A866" s="43" t="inlineStr">
         <is>
           <t>70.12</t>
         </is>
       </c>
-      <c r="B864" s="3" t="inlineStr">
+      <c r="B866" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C864" s="3" t="inlineStr">
+      <c r="C866" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D864" s="4" t="inlineStr">
+      <c r="D866" s="4" t="inlineStr">
         <is>
           <t>Reset ke Default pada filter kolom</t>
         </is>
       </c>
-      <c r="E864" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F864" s="3" t="inlineStr">
+      <c r="E866" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F866" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G864" s="4" t="inlineStr">
+      <c r="G866" s="4" t="inlineStr">
         <is>
           <t>1. Klik Reset ke Default</t>
         </is>
       </c>
-      <c r="H864" s="4" t="inlineStr">
+      <c r="H866" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data tabel dengan kolom default</t>
         </is>
       </c>
     </row>
-    <row r="865" ht="28" customHeight="1">
-      <c r="A865" s="43" t="inlineStr">
+    <row r="867" ht="28" customHeight="1">
+      <c r="A867" s="43" t="inlineStr">
         <is>
           <t>71.1</t>
         </is>
       </c>
-      <c r="B865" s="3" t="inlineStr">
+      <c r="B867" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C865" s="3" t="inlineStr">
+      <c r="C867" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D865" s="4" t="inlineStr">
+      <c r="D867" s="4" t="inlineStr">
         <is>
           <t>Filter data</t>
         </is>
       </c>
-      <c r="E865" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F865" s="3" t="inlineStr">
+      <c r="E867" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F867" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G865" s="4" t="inlineStr">
+      <c r="G867" s="4" t="inlineStr">
         <is>
           <t>1. Pilih kantor wilayah
 2. Pilih kantor cabang 
@@ -38590,7 +38680,7 @@
 6. Klik button Filter</t>
         </is>
       </c>
-      <c r="H865" s="4" t="inlineStr">
+      <c r="H867" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list data filter kantor wilayah dan dapat di pilih
 2. Menampilkan dropdown list data filter kantor cabang dan dapat di pilih
@@ -38601,126 +38691,126 @@
         </is>
       </c>
     </row>
-    <row r="866" ht="28" customHeight="1">
-      <c r="A866" s="43" t="inlineStr">
+    <row r="868" ht="28" customHeight="1">
+      <c r="A868" s="43" t="inlineStr">
         <is>
           <t>71.2</t>
         </is>
       </c>
-      <c r="B866" s="3" t="inlineStr">
+      <c r="B868" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C866" s="3" t="inlineStr">
+      <c r="C868" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D866" s="4" t="inlineStr">
+      <c r="D868" s="4" t="inlineStr">
         <is>
           <t>Mencari data</t>
         </is>
       </c>
-      <c r="E866" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F866" s="3" t="inlineStr">
+      <c r="E868" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F868" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G866" s="4" t="inlineStr">
+      <c r="G868" s="4" t="inlineStr">
         <is>
           <t>1. Input keyword pada field search 
 2. Klik icon search yang ada di sebelah field</t>
         </is>
       </c>
-      <c r="H866" s="4" t="inlineStr">
+      <c r="H868" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput keyword 
 2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
         </is>
       </c>
     </row>
-    <row r="867" ht="28" customHeight="1">
-      <c r="A867" s="43" t="inlineStr">
+    <row r="869" ht="28" customHeight="1">
+      <c r="A869" s="43" t="inlineStr">
         <is>
           <t>71.3</t>
         </is>
       </c>
-      <c r="B867" s="3" t="inlineStr">
+      <c r="B869" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C867" s="3" t="inlineStr">
+      <c r="C869" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D867" s="4" t="inlineStr">
+      <c r="D869" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E867" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F867" s="3" t="inlineStr">
+      <c r="E869" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F869" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G867" s="4" t="inlineStr">
+      <c r="G869" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Re-Assign &amp; Approval 
 2. Klik submenu Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="H867" s="4" t="inlineStr">
+      <c r="H869" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan submenu Re-Assign &amp; Approval 
 2. Menampilkan halaman Re-Assign Prospek</t>
         </is>
       </c>
     </row>
-    <row r="868" ht="28" customHeight="1">
-      <c r="A868" s="43" t="inlineStr">
+    <row r="870" ht="28" customHeight="1">
+      <c r="A870" s="43" t="inlineStr">
         <is>
           <t>71.4</t>
         </is>
       </c>
-      <c r="B868" s="3" t="inlineStr">
+      <c r="B870" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C868" s="3" t="inlineStr">
+      <c r="C870" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D868" s="4" t="inlineStr">
+      <c r="D870" s="4" t="inlineStr">
         <is>
           <t>Filter data</t>
         </is>
       </c>
-      <c r="E868" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F868" s="3" t="inlineStr">
+      <c r="E870" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F870" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G868" s="4" t="inlineStr">
+      <c r="G870" s="4" t="inlineStr">
         <is>
           <t>1. Pilih kantor wilayah
 2. Pilih kantor cabang 
@@ -38730,7 +38820,7 @@
 6. Klik button Filter</t>
         </is>
       </c>
-      <c r="H868" s="4" t="inlineStr">
+      <c r="H870" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list data filter kantor wilayah dan dapat di pilih
 2. Menampilkan dropdown list data filter kantor cabang dan dapat di pilih
@@ -38741,252 +38831,252 @@
         </is>
       </c>
     </row>
-    <row r="869" ht="28" customHeight="1">
-      <c r="A869" s="43" t="inlineStr">
+    <row r="871" ht="28" customHeight="1">
+      <c r="A871" s="43" t="inlineStr">
         <is>
           <t>71.5</t>
         </is>
       </c>
-      <c r="B869" s="3" t="inlineStr">
+      <c r="B871" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C869" s="3" t="inlineStr">
+      <c r="C871" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D869" s="4" t="inlineStr">
+      <c r="D871" s="4" t="inlineStr">
         <is>
           <t>Mencari data</t>
         </is>
       </c>
-      <c r="E869" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F869" s="3" t="inlineStr">
+      <c r="E871" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F871" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G869" s="4" t="inlineStr">
+      <c r="G871" s="4" t="inlineStr">
         <is>
           <t>1. Input keyword pada field search 
 2. Klik icon search yang ada di sebelah field</t>
         </is>
       </c>
-      <c r="H869" s="4" t="inlineStr">
+      <c r="H871" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput keyword 
 2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
         </is>
       </c>
     </row>
-    <row r="870" ht="28" customHeight="1">
-      <c r="A870" s="43" t="inlineStr">
-        <is>
-          <t>71.6</t>
-        </is>
-      </c>
-      <c r="B870" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C870" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D870" s="4" t="inlineStr">
-        <is>
-          <t>Validasi count checklist data</t>
-        </is>
-      </c>
-      <c r="E870" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F870" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G870" s="4" t="inlineStr">
-        <is>
-          <t>1. Cek informasi yang ada pada button Reassign () data</t>
-        </is>
-      </c>
-      <c r="H870" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan count angka yang sesuai dengan data yang di checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="871" ht="28" customHeight="1">
-      <c r="A871" s="43" t="inlineStr">
-        <is>
-          <t>71.7</t>
-        </is>
-      </c>
-      <c r="B871" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C871" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D871" s="4" t="inlineStr">
-        <is>
-          <t>Validasi data yang sudah dii pilih</t>
-        </is>
-      </c>
-      <c r="E871" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F871" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G871" s="4" t="inlineStr">
-        <is>
-          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi prospek yang di pilih</t>
-        </is>
-      </c>
-      <c r="H871" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan data tabel prospek yang di pilih saja</t>
-        </is>
-      </c>
-    </row>
     <row r="872" ht="70" customHeight="1">
       <c r="A872" s="43" t="inlineStr">
         <is>
+          <t>71.6</t>
+        </is>
+      </c>
+      <c r="B872" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C872" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D872" s="4" t="inlineStr">
+        <is>
+          <t>Validasi count checklist data</t>
+        </is>
+      </c>
+      <c r="E872" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F872" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G872" s="4" t="inlineStr">
+        <is>
+          <t>1. Cek informasi yang ada pada button Reassign () data</t>
+        </is>
+      </c>
+      <c r="H872" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan count angka yang sesuai dengan data yang di checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="873" ht="42" customHeight="1">
+      <c r="A873" s="43" t="inlineStr">
+        <is>
+          <t>71.7</t>
+        </is>
+      </c>
+      <c r="B873" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C873" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D873" s="4" t="inlineStr">
+        <is>
+          <t>Validasi data yang sudah dii pilih</t>
+        </is>
+      </c>
+      <c r="E873" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F873" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G873" s="4" t="inlineStr">
+        <is>
+          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi prospek yang di pilih</t>
+        </is>
+      </c>
+      <c r="H873" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan data tabel prospek yang di pilih saja</t>
+        </is>
+      </c>
+    </row>
+    <row r="874" ht="42" customHeight="1">
+      <c r="A874" s="43" t="inlineStr">
+        <is>
           <t>71.8</t>
         </is>
       </c>
-      <c r="B872" s="3" t="inlineStr">
+      <c r="B874" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C872" s="3" t="inlineStr">
+      <c r="C874" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D872" s="4" t="inlineStr">
+      <c r="D874" s="4" t="inlineStr">
         <is>
           <t>Mengosongkan field inputan mandatory pada reassign prospek</t>
         </is>
       </c>
-      <c r="E872" s="3" t="inlineStr">
+      <c r="E874" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F872" s="3" t="inlineStr">
+      <c r="F874" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G872" s="4" t="inlineStr">
+      <c r="G874" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan salah satu atau semua field mandatory 
 2. Klik button Submit</t>
         </is>
       </c>
-      <c r="H872" s="4" t="inlineStr">
+      <c r="H874" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil tidak mengisi/mengosongkan field 
 2. Menampilkan alert pada setiap field mandatory bahwa field tersebut dibutuhkan / wajib diisi</t>
         </is>
       </c>
     </row>
-    <row r="873" ht="42" customHeight="1">
-      <c r="A873" s="43" t="inlineStr">
+    <row r="875" ht="70" customHeight="1">
+      <c r="A875" s="43" t="inlineStr">
         <is>
           <t>71.9</t>
         </is>
       </c>
-      <c r="B873" s="3" t="inlineStr">
+      <c r="B875" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C873" s="3" t="inlineStr">
+      <c r="C875" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D873" s="4" t="inlineStr">
+      <c r="D875" s="4" t="inlineStr">
         <is>
           <t>Membatalkan Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E873" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F873" s="3" t="inlineStr">
+      <c r="E875" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F875" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G873" s="4" t="inlineStr">
+      <c r="G875" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
         </is>
       </c>
-      <c r="H873" s="4" t="inlineStr">
+      <c r="H875" s="4" t="inlineStr">
         <is>
           <t>1. Kembali ke halaman utama Re-assign Prospek</t>
         </is>
       </c>
     </row>
-    <row r="874" ht="42" customHeight="1">
-      <c r="A874" s="43" t="inlineStr">
+    <row r="876" ht="28" customHeight="1">
+      <c r="A876" s="43" t="inlineStr">
         <is>
           <t>71.10</t>
         </is>
       </c>
-      <c r="B874" s="3" t="inlineStr">
+      <c r="B876" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C874" s="3" t="inlineStr">
+      <c r="C876" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D874" s="4" t="inlineStr">
+      <c r="D876" s="4" t="inlineStr">
         <is>
           <t>Validasi data prospek yang di re-assign</t>
         </is>
       </c>
-      <c r="E874" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F874" s="3" t="inlineStr">
+      <c r="E876" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F876" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G874" s="4" t="inlineStr">
+      <c r="G876" s="4" t="inlineStr">
         <is>
           <t>1. Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek 
 2. Klik menu Lead Qualification 
@@ -38994,7 +39084,7 @@
 4. Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
-      <c r="H874" s="4" t="inlineStr">
+      <c r="H876" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login 
 2. Menampilkan dropdown submenu Lead Qualification 
@@ -39003,38 +39093,38 @@
         </is>
       </c>
     </row>
-    <row r="875" ht="70" customHeight="1">
-      <c r="A875" s="43" t="inlineStr">
+    <row r="877" ht="42" customHeight="1">
+      <c r="A877" s="43" t="inlineStr">
         <is>
           <t>71.11</t>
         </is>
       </c>
-      <c r="B875" s="3" t="inlineStr">
+      <c r="B877" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C875" s="3" t="inlineStr">
+      <c r="C877" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D875" s="4" t="inlineStr">
+      <c r="D877" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-assign prospek semua data</t>
         </is>
       </c>
-      <c r="E875" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F875" s="3" t="inlineStr">
+      <c r="E877" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F877" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G875" s="4" t="inlineStr">
+      <c r="G877" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Reassign semua data 
 2. Klik button Yes 
@@ -39045,7 +39135,7 @@
 7. Klik button Submit</t>
         </is>
       </c>
-      <c r="H875" s="4" t="inlineStr">
+      <c r="H877" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan popup konfirmasi 
 2. Menampilkan halaman pindah kelolaan 
@@ -39057,122 +39147,122 @@
         </is>
       </c>
     </row>
-    <row r="876" ht="28" customHeight="1">
-      <c r="A876" s="43" t="inlineStr">
-        <is>
-          <t>71.12</t>
-        </is>
-      </c>
-      <c r="B876" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C876" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D876" s="4" t="inlineStr">
-        <is>
-          <t>Validasi semua data</t>
-        </is>
-      </c>
-      <c r="E876" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F876" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G876" s="4" t="inlineStr">
-        <is>
-          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi semua prospek</t>
-        </is>
-      </c>
-      <c r="H876" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan data tabel yang berisi semua prospek</t>
-        </is>
-      </c>
-    </row>
-    <row r="877" ht="42" customHeight="1">
-      <c r="A877" s="43" t="inlineStr">
-        <is>
-          <t>71.13</t>
-        </is>
-      </c>
-      <c r="B877" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C877" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D877" s="4" t="inlineStr">
-        <is>
-          <t>Membatalkan Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="E877" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F877" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G877" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
-        </is>
-      </c>
-      <c r="H877" s="4" t="inlineStr">
-        <is>
-          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
-        </is>
-      </c>
-    </row>
     <row r="878" ht="28" customHeight="1">
       <c r="A878" s="43" t="inlineStr">
         <is>
+          <t>71.12</t>
+        </is>
+      </c>
+      <c r="B878" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C878" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D878" s="4" t="inlineStr">
+        <is>
+          <t>Validasi semua data</t>
+        </is>
+      </c>
+      <c r="E878" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F878" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G878" s="4" t="inlineStr">
+        <is>
+          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi semua prospek</t>
+        </is>
+      </c>
+      <c r="H878" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan data tabel yang berisi semua prospek</t>
+        </is>
+      </c>
+    </row>
+    <row r="879" ht="28" customHeight="1">
+      <c r="A879" s="43" t="inlineStr">
+        <is>
+          <t>71.13</t>
+        </is>
+      </c>
+      <c r="B879" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C879" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D879" s="4" t="inlineStr">
+        <is>
+          <t>Membatalkan Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="E879" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F879" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G879" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
+        </is>
+      </c>
+      <c r="H879" s="4" t="inlineStr">
+        <is>
+          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
+        </is>
+      </c>
+    </row>
+    <row r="880" ht="28" customHeight="1">
+      <c r="A880" s="43" t="inlineStr">
+        <is>
           <t>71.14</t>
         </is>
       </c>
-      <c r="B878" s="3" t="inlineStr">
+      <c r="B880" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C878" s="3" t="inlineStr">
+      <c r="C880" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D878" s="4" t="inlineStr">
+      <c r="D880" s="4" t="inlineStr">
         <is>
           <t>Validasi semua data prospek yang di re-assign</t>
         </is>
       </c>
-      <c r="E878" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F878" s="3" t="inlineStr">
+      <c r="E880" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F880" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G878" s="4" t="inlineStr">
+      <c r="G880" s="4" t="inlineStr">
         <is>
           <t>1. Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek 
 2. Klik menu Lead Qualification 
@@ -39180,7 +39270,7 @@
 4. Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
-      <c r="H878" s="4" t="inlineStr">
+      <c r="H880" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login 
 2. Menampilkan dropdown submenu Lead Qualification 
@@ -39189,126 +39279,126 @@
         </is>
       </c>
     </row>
-    <row r="879" ht="28" customHeight="1">
-      <c r="A879" s="43" t="inlineStr">
+    <row r="881" ht="14" customHeight="1">
+      <c r="A881" s="43" t="inlineStr">
         <is>
           <t>72.1</t>
         </is>
       </c>
-      <c r="B879" s="3" t="inlineStr">
+      <c r="B881" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C879" s="3" t="inlineStr">
+      <c r="C881" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D879" s="4" t="inlineStr">
+      <c r="D881" s="4" t="inlineStr">
         <is>
           <t>Pagination</t>
         </is>
       </c>
-      <c r="E879" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F879" s="3" t="inlineStr">
+      <c r="E881" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F881" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G879" s="4" t="inlineStr">
+      <c r="G881" s="4" t="inlineStr">
         <is>
           <t>1. Klik pagination (10/halaman).
 2. Pilih berapa data yang ingin ditampilkan.</t>
         </is>
       </c>
-      <c r="H879" s="4" t="inlineStr">
+      <c r="H881" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengklik pagination.
 2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="880" ht="28" customHeight="1">
-      <c r="A880" s="43" t="inlineStr">
+    <row r="882" ht="42" customHeight="1">
+      <c r="A882" s="43" t="inlineStr">
         <is>
           <t>72.2</t>
         </is>
       </c>
-      <c r="B880" s="3" t="inlineStr">
+      <c r="B882" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C880" s="3" t="inlineStr">
+      <c r="C882" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D880" s="4" t="inlineStr">
+      <c r="D882" s="4" t="inlineStr">
         <is>
           <t>Pindah Halaman</t>
         </is>
       </c>
-      <c r="E880" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F880" s="3" t="inlineStr">
+      <c r="E882" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F882" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G880" s="4" t="inlineStr">
+      <c r="G882" s="4" t="inlineStr">
         <is>
           <t>1. Input angka halaman di field pindah halaman.
 2. Klik Enter pada keyboard.</t>
         </is>
       </c>
-      <c r="H880" s="4" t="inlineStr">
+      <c r="H882" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput angka halaman.
 2. Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
-    <row r="881" ht="14" customHeight="1">
-      <c r="A881" s="43" t="inlineStr">
+    <row r="883" ht="42" customHeight="1">
+      <c r="A883" s="43" t="inlineStr">
         <is>
           <t>72.3</t>
         </is>
       </c>
-      <c r="B881" s="3" t="inlineStr">
+      <c r="B883" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C881" s="3" t="inlineStr">
+      <c r="C883" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D881" s="4" t="inlineStr">
+      <c r="D883" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E881" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F881" s="3" t="inlineStr">
+      <c r="E883" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F883" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G881" s="4" t="inlineStr">
+      <c r="G883" s="4" t="inlineStr">
         <is>
           <t>1. Pilih prospek dengan klik checkbox yang ada di samping setiap data prospek 
 2. Klik button Reassign () data 
@@ -39317,7 +39407,7 @@
 5. Klik button Submit</t>
         </is>
       </c>
-      <c r="H881" s="4" t="inlineStr">
+      <c r="H883" s="4" t="inlineStr">
         <is>
           <t>1. Checkbox menjadi ceklis dan data berhasil di pilih 
 2. Menampilkan popup konfirmasi 
@@ -39327,258 +39417,258 @@
         </is>
       </c>
     </row>
-    <row r="882" ht="42" customHeight="1">
-      <c r="A882" s="43" t="inlineStr">
+    <row r="884" ht="28" customHeight="1">
+      <c r="A884" s="43" t="inlineStr">
         <is>
           <t>72.4</t>
         </is>
       </c>
-      <c r="B882" s="3" t="inlineStr">
+      <c r="B884" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C882" s="3" t="inlineStr">
+      <c r="C884" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D882" s="4" t="inlineStr">
+      <c r="D884" s="4" t="inlineStr">
         <is>
           <t>Pagination</t>
         </is>
       </c>
-      <c r="E882" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F882" s="3" t="inlineStr">
+      <c r="E884" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F884" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G882" s="4" t="inlineStr">
+      <c r="G884" s="4" t="inlineStr">
         <is>
           <t>1. Klik pagination (10/halaman).
 2. Pilih berapa data yang ingin ditampilkan.</t>
         </is>
       </c>
-      <c r="H882" s="4" t="inlineStr">
+      <c r="H884" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengklik pagination.
 2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="883" ht="42" customHeight="1">
-      <c r="A883" s="43" t="inlineStr">
+    <row r="885" ht="42" customHeight="1">
+      <c r="A885" s="43" t="inlineStr">
         <is>
           <t>72.5</t>
         </is>
       </c>
-      <c r="B883" s="3" t="inlineStr">
+      <c r="B885" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C883" s="3" t="inlineStr">
+      <c r="C885" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D883" s="4" t="inlineStr">
+      <c r="D885" s="4" t="inlineStr">
         <is>
           <t>Pindah Halaman</t>
         </is>
       </c>
-      <c r="E883" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F883" s="3" t="inlineStr">
+      <c r="E885" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F885" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G883" s="4" t="inlineStr">
+      <c r="G885" s="4" t="inlineStr">
         <is>
           <t>1. Input angka halaman di field pindah halaman.
 2. Klik Enter pada keyboard.</t>
         </is>
       </c>
-      <c r="H883" s="4" t="inlineStr">
+      <c r="H885" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput angka halaman.
 2. Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
-    <row r="884" ht="28" customHeight="1">
-      <c r="A884" s="43" t="inlineStr">
+    <row r="886" ht="14" customHeight="1">
+      <c r="A886" s="43" t="inlineStr">
         <is>
           <t>72.6</t>
         </is>
       </c>
-      <c r="B884" s="3" t="inlineStr">
+      <c r="B886" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C884" s="3" t="inlineStr">
+      <c r="C886" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D884" s="4" t="inlineStr">
+      <c r="D886" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Re-Assign Management</t>
         </is>
       </c>
-      <c r="E884" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F884" s="3" t="inlineStr">
+      <c r="E886" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F886" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G884" s="4" t="inlineStr">
+      <c r="G886" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Re-Assign &amp; Approval 
 2. Klik submenu Re-Assign Management</t>
         </is>
       </c>
-      <c r="H884" s="4" t="inlineStr">
+      <c r="H886" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list submenu Re-Assign &amp; Approval 
 2. Menampilkan halaman Re-Assign Management</t>
         </is>
       </c>
     </row>
-    <row r="885" ht="42" customHeight="1">
-      <c r="A885" s="43" t="inlineStr">
+    <row r="887" ht="42" customHeight="1">
+      <c r="A887" s="43" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="B885" s="3" t="inlineStr">
+      <c r="B887" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C885" s="3" t="inlineStr">
+      <c r="C887" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D885" s="4" t="inlineStr">
+      <c r="D887" s="4" t="inlineStr">
         <is>
           <t>Mencari data prospek pada halaman Re-Assign Management</t>
         </is>
       </c>
-      <c r="E885" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F885" s="3" t="inlineStr">
+      <c r="E887" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F887" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G885" s="4" t="inlineStr">
+      <c r="G887" s="4" t="inlineStr">
         <is>
           <t>1. Input nama nasabah pada field search 
 2. Klik icon search atau klik Enter</t>
         </is>
       </c>
-      <c r="H885" s="4" t="inlineStr">
+      <c r="H887" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput nama nasabah
 2. Menampilkan data prospek Re-Assign Management sesuai dengan nama yang di cari</t>
         </is>
       </c>
     </row>
-    <row r="886" ht="14" customHeight="1">
-      <c r="A886" s="43" t="inlineStr">
+    <row r="888" ht="42" customHeight="1">
+      <c r="A888" s="43" t="inlineStr">
         <is>
           <t>72.8</t>
         </is>
       </c>
-      <c r="B886" s="3" t="inlineStr">
+      <c r="B888" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C886" s="3" t="inlineStr">
+      <c r="C888" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D886" s="4" t="inlineStr">
+      <c r="D888" s="4" t="inlineStr">
         <is>
           <t>Mencari data prospek yang tidak ada pada halaman Re-Assign Management</t>
         </is>
       </c>
-      <c r="E886" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F886" s="3" t="inlineStr">
+      <c r="E888" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F888" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G886" s="4" t="inlineStr">
+      <c r="G888" s="4" t="inlineStr">
         <is>
           <t>1. Input nama nasabah yang datanya tidak ada 
 2. Klik icon search atau klik Enter</t>
         </is>
       </c>
-      <c r="H886" s="4" t="inlineStr">
+      <c r="H888" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput nama nasabah
 2. Menampilkan tabel kosong dengan keterangan no data</t>
         </is>
       </c>
     </row>
-    <row r="887" ht="42" customHeight="1">
-      <c r="A887" s="43" t="inlineStr">
+    <row r="889" ht="28" customHeight="1">
+      <c r="A889" s="43" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="B887" s="3" t="inlineStr">
+      <c r="B889" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C887" s="3" t="inlineStr">
+      <c r="C889" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D887" s="4" t="inlineStr">
+      <c r="D889" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E887" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F887" s="3" t="inlineStr">
+      <c r="E889" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F889" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G887" s="4" t="inlineStr">
+      <c r="G889" s="4" t="inlineStr">
         <is>
           <t>1. Pilih prospek dengan klik checkbox yang ada di samping setiap data prospek 
 2. Klik button Reassign () data 
@@ -39587,7 +39677,7 @@
 5. Klik button Submit</t>
         </is>
       </c>
-      <c r="H887" s="4" t="inlineStr">
+      <c r="H889" s="4" t="inlineStr">
         <is>
           <t>1. Checkbox menjadi ceklis dan data berhasil di pilih 
 2. Menampilkan popup konfirmasi 
@@ -39597,80 +39687,80 @@
         </is>
       </c>
     </row>
-    <row r="888" ht="42" customHeight="1">
-      <c r="A888" s="43" t="inlineStr">
+    <row r="890" ht="42" customHeight="1">
+      <c r="A890" s="43" t="inlineStr">
         <is>
           <t>72.10</t>
         </is>
       </c>
-      <c r="B888" s="3" t="inlineStr">
+      <c r="B890" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C888" s="3" t="inlineStr">
+      <c r="C890" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D888" s="4" t="inlineStr">
+      <c r="D890" s="4" t="inlineStr">
         <is>
           <t>Validasi jumlah data yang di pilih untuk reassign</t>
         </is>
       </c>
-      <c r="E888" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F888" s="3" t="inlineStr">
+      <c r="E890" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F890" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G888" s="4" t="inlineStr">
+      <c r="G890" s="4" t="inlineStr">
         <is>
           <t>1. cek jumlah data yang muncul pada button Reassign () data</t>
         </is>
       </c>
-      <c r="H888" s="4" t="inlineStr">
+      <c r="H890" s="4" t="inlineStr">
         <is>
           <t>1. Angka yang muncul pada button sesuai dengan jumlah data yang di pilih</t>
         </is>
       </c>
     </row>
-    <row r="889" ht="28" customHeight="1">
-      <c r="A889" s="43" t="inlineStr">
+    <row r="891" ht="14" customHeight="1">
+      <c r="A891" s="43" t="inlineStr">
         <is>
           <t>72.11</t>
         </is>
       </c>
-      <c r="B889" s="3" t="inlineStr">
+      <c r="B891" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C889" s="3" t="inlineStr">
+      <c r="C891" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D889" s="4" t="inlineStr">
+      <c r="D891" s="4" t="inlineStr">
         <is>
           <t>Validasi data prospek yang di re-assign ke sales</t>
         </is>
       </c>
-      <c r="E889" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F889" s="3" t="inlineStr">
+      <c r="E891" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F891" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G889" s="4" t="inlineStr">
+      <c r="G891" s="4" t="inlineStr">
         <is>
           <t>1. Login dengan akun sales yang sebelumnya sudah di pilih reassign management
 2. Klik menu Lead Qualification
@@ -39678,7 +39768,7 @@
 4. Cek data prospek yang sudah di reassign</t>
         </is>
       </c>
-      <c r="H889" s="4" t="inlineStr">
+      <c r="H891" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login akun sales
 2. Menampilkan dropdown submenu Lead Qualification
@@ -39687,182 +39777,98 @@
         </is>
       </c>
     </row>
-    <row r="890" ht="42" customHeight="1">
-      <c r="A890" s="43" t="inlineStr">
+    <row r="892" ht="42" customHeight="1">
+      <c r="A892" s="43" t="inlineStr">
         <is>
           <t>72.12</t>
         </is>
       </c>
-      <c r="B890" s="3" t="inlineStr">
+      <c r="B892" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C890" s="3" t="inlineStr">
+      <c r="C892" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D890" s="4" t="inlineStr">
+      <c r="D892" s="4" t="inlineStr">
         <is>
           <t>Pagination</t>
         </is>
       </c>
-      <c r="E890" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F890" s="3" t="inlineStr">
+      <c r="E892" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F892" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G890" s="4" t="inlineStr">
+      <c r="G892" s="4" t="inlineStr">
         <is>
           <t>1. Klik pagination (10/halaman).
 2. Pilih berapa data yang ingin ditampilkan.</t>
         </is>
       </c>
-      <c r="H890" s="4" t="inlineStr">
+      <c r="H892" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengklik pagination.
 2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="891" ht="14" customHeight="1">
-      <c r="A891" s="43" t="inlineStr">
+    <row r="893" ht="42" customHeight="1">
+      <c r="A893" s="43" t="inlineStr">
         <is>
           <t>72.13</t>
         </is>
       </c>
-      <c r="B891" s="3" t="inlineStr">
+      <c r="B893" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C891" s="3" t="inlineStr">
+      <c r="C893" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D891" s="4" t="inlineStr">
+      <c r="D893" s="4" t="inlineStr">
         <is>
           <t>Pindah Halaman</t>
         </is>
       </c>
-      <c r="E891" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F891" s="3" t="inlineStr">
+      <c r="E893" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F893" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G891" s="4" t="inlineStr">
+      <c r="G893" s="4" t="inlineStr">
         <is>
           <t>1. Input angka halaman di field pindah halaman.
 2. Klik Enter pada keyboard.</t>
         </is>
       </c>
-      <c r="H891" s="4" t="inlineStr">
+      <c r="H893" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput angka halaman.
 2. Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
-    <row r="892" ht="42" customHeight="1">
-      <c r="A892" s="43" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="B892" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C892" s="3" t="inlineStr">
-        <is>
-          <t>Riwayat export saya</t>
-        </is>
-      </c>
-      <c r="D892" s="4" t="inlineStr">
-        <is>
-          <t>Membuka menu riwayat export saya</t>
-        </is>
-      </c>
-      <c r="E892" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F892" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G892" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu exported data management, klik submenu riwayat export saya</t>
-        </is>
-      </c>
-      <c r="H892" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan halaman riwayat export saya</t>
-        </is>
-      </c>
-    </row>
-    <row r="893" ht="42" customHeight="1">
-      <c r="A893" s="43" t="inlineStr">
-        <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="B893" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C893" s="3" t="inlineStr">
-        <is>
-          <t>Riwayat export saya</t>
-        </is>
-      </c>
-      <c r="D893" s="4" t="inlineStr">
-        <is>
-          <t>Validasi card disetujui dengan data table</t>
-        </is>
-      </c>
-      <c r="E893" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F893" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G893" s="4" t="inlineStr">
-        <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Approved”</t>
-        </is>
-      </c>
-      <c r="H893" s="4" t="inlineStr">
-        <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
-        </is>
-      </c>
-    </row>
     <row r="894" ht="28" customHeight="1">
       <c r="A894" s="43" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="B894" s="3" t="inlineStr">
@@ -39877,7 +39883,7 @@
       </c>
       <c r="D894" s="4" t="inlineStr">
         <is>
-          <t>Validasi card ditolak dengan data table</t>
+          <t>Membuka menu riwayat export saya</t>
         </is>
       </c>
       <c r="E894" s="3" t="inlineStr">
@@ -39892,19 +39898,19 @@
       </c>
       <c r="G894" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Rejected”</t>
+          <t>1. Klik menu exported data management, klik submenu riwayat export saya</t>
         </is>
       </c>
       <c r="H894" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Menampilkan halaman riwayat export saya</t>
         </is>
       </c>
     </row>
     <row r="895" ht="42" customHeight="1">
       <c r="A895" s="43" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="B895" s="3" t="inlineStr">
@@ -39919,7 +39925,7 @@
       </c>
       <c r="D895" s="4" t="inlineStr">
         <is>
-          <t>Validasi card kadaluwarsa dengan data table</t>
+          <t>Validasi card disetujui dengan data table</t>
         </is>
       </c>
       <c r="E895" s="3" t="inlineStr">
@@ -39929,12 +39935,12 @@
       </c>
       <c r="F895" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G895" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Expired”</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Approved”</t>
         </is>
       </c>
       <c r="H895" s="4" t="inlineStr">
@@ -39946,7 +39952,7 @@
     <row r="896" ht="14" customHeight="1">
       <c r="A896" s="43" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="B896" s="3" t="inlineStr">
@@ -39961,7 +39967,7 @@
       </c>
       <c r="D896" s="4" t="inlineStr">
         <is>
-          <t>Mengunduh data yang sudah di approve</t>
+          <t>Validasi card ditolak dengan data table</t>
         </is>
       </c>
       <c r="E896" s="3" t="inlineStr">
@@ -39976,19 +39982,19 @@
       </c>
       <c r="G896" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button download</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Rejected”</t>
         </is>
       </c>
       <c r="H896" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengunduh data</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="897" ht="42" customHeight="1">
       <c r="A897" s="43" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="B897" s="3" t="inlineStr">
@@ -40003,7 +40009,7 @@
       </c>
       <c r="D897" s="4" t="inlineStr">
         <is>
-          <t>Membuka dokumen hasil download</t>
+          <t>Validasi card kadaluwarsa dengan data table</t>
         </is>
       </c>
       <c r="E897" s="3" t="inlineStr">
@@ -40013,24 +40019,24 @@
       </c>
       <c r="F897" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G897" s="4" t="inlineStr">
         <is>
-          <t>1. Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Expired”</t>
         </is>
       </c>
       <c r="H897" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka file hasil download</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="898" ht="42" customHeight="1">
       <c r="A898" s="43" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="B898" s="3" t="inlineStr">
@@ -40040,12 +40046,12 @@
       </c>
       <c r="C898" s="3" t="inlineStr">
         <is>
-          <t>Management export</t>
+          <t>Riwayat export saya</t>
         </is>
       </c>
       <c r="D898" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mengunduh data yang sudah di approve</t>
         </is>
       </c>
       <c r="E898" s="3" t="inlineStr">
@@ -40055,24 +40061,24 @@
       </c>
       <c r="F898" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G898" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Klik button download</t>
         </is>
       </c>
       <c r="H898" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Berhasil mengunduh data</t>
         </is>
       </c>
     </row>
     <row r="899" ht="28" customHeight="1">
       <c r="A899" s="43" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="B899" s="3" t="inlineStr">
@@ -40082,12 +40088,12 @@
       </c>
       <c r="C899" s="3" t="inlineStr">
         <is>
-          <t>Management export</t>
+          <t>Riwayat export saya</t>
         </is>
       </c>
       <c r="D899" s="4" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Membuka dokumen hasil download</t>
         </is>
       </c>
       <c r="E899" s="3" t="inlineStr">
@@ -40102,19 +40108,19 @@
       </c>
       <c r="G899" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
+          <t>1. Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
         </is>
       </c>
       <c r="H899" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Berhasil membuka file hasil download</t>
         </is>
       </c>
     </row>
     <row r="900" ht="42" customHeight="1">
       <c r="A900" s="43" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="B900" s="3" t="inlineStr">
@@ -40129,7 +40135,7 @@
       </c>
       <c r="D900" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E900" s="3" t="inlineStr">
@@ -40139,24 +40145,24 @@
       </c>
       <c r="F900" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G900" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H900" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="901" ht="28" customHeight="1">
       <c r="A901" s="43" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="B901" s="3" t="inlineStr">
@@ -40171,12 +40177,12 @@
       </c>
       <c r="D901" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E901" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F901" s="3" t="inlineStr">
@@ -40186,19 +40192,19 @@
       </c>
       <c r="G901" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
         </is>
       </c>
       <c r="H901" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="902" ht="28" customHeight="1">
       <c r="A902" s="43" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="B902" s="3" t="inlineStr">
@@ -40213,7 +40219,7 @@
       </c>
       <c r="D902" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E902" s="3" t="inlineStr">
@@ -40223,24 +40229,24 @@
       </c>
       <c r="F902" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G902" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H902" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="903" ht="28" customHeight="1">
       <c r="A903" s="43" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="B903" s="3" t="inlineStr">
@@ -40255,12 +40261,12 @@
       </c>
       <c r="D903" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E903" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F903" s="3" t="inlineStr">
@@ -40270,19 +40276,19 @@
       </c>
       <c r="G903" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H903" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="904" ht="28" customHeight="1">
       <c r="A904" s="43" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="B904" s="3" t="inlineStr">
@@ -40297,34 +40303,34 @@
       </c>
       <c r="D904" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E904" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F904" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G904" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H904" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="905" ht="28" customHeight="1">
       <c r="A905" s="43" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="B905" s="3" t="inlineStr">
@@ -40339,7 +40345,7 @@
       </c>
       <c r="D905" s="4" t="inlineStr">
         <is>
-          <t>Membuka menu Management Export</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E905" s="3" t="inlineStr">
@@ -40354,19 +40360,19 @@
       </c>
       <c r="G905" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu exported data management, klik submenu management export</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H905" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan halaman management export</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="906" ht="42" customHeight="1">
       <c r="A906" s="43" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="B906" s="3" t="inlineStr">
@@ -40381,34 +40387,34 @@
       </c>
       <c r="D906" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E906" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F906" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G906" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H906" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="907" ht="42" customHeight="1">
       <c r="A907" s="43" t="inlineStr">
         <is>
-          <t>74.10</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="B907" s="3" t="inlineStr">
@@ -40423,7 +40429,7 @@
       </c>
       <c r="D907" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Membuka menu Management Export</t>
         </is>
       </c>
       <c r="E907" s="3" t="inlineStr">
@@ -40438,19 +40444,19 @@
       </c>
       <c r="G907" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Klik menu exported data management, klik submenu management export</t>
         </is>
       </c>
       <c r="H907" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Menampilkan halaman management export</t>
         </is>
       </c>
     </row>
     <row r="908" ht="28" customHeight="1">
       <c r="A908" s="43" t="inlineStr">
         <is>
-          <t>74.11</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="B908" s="3" t="inlineStr">
@@ -40465,34 +40471,34 @@
       </c>
       <c r="D908" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E908" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F908" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G908" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H908" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="909" ht="14" customHeight="1">
       <c r="A909" s="43" t="inlineStr">
         <is>
-          <t>74.12</t>
+          <t>74.10</t>
         </is>
       </c>
       <c r="B909" s="3" t="inlineStr">
@@ -40507,7 +40513,7 @@
       </c>
       <c r="D909" s="4" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E909" s="3" t="inlineStr">
@@ -40522,19 +40528,19 @@
       </c>
       <c r="G909" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H909" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="910" ht="28" customHeight="1">
       <c r="A910" s="43" t="inlineStr">
         <is>
-          <t>74.13</t>
+          <t>74.11</t>
         </is>
       </c>
       <c r="B910" s="3" t="inlineStr">
@@ -40549,34 +40555,34 @@
       </c>
       <c r="D910" s="4" t="inlineStr">
         <is>
-          <t>Validasi card data file aktif dengan data table</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E910" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F910" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G910" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H910" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="911" ht="28" customHeight="1">
       <c r="A911" s="43" t="inlineStr">
         <is>
-          <t>74.14</t>
+          <t>74.12</t>
         </is>
       </c>
       <c r="B911" s="3" t="inlineStr">
@@ -40591,7 +40597,7 @@
       </c>
       <c r="D911" s="4" t="inlineStr">
         <is>
-          <t>Validasi card file kadaluwarsa dengan data table</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E911" s="3" t="inlineStr">
@@ -40601,12 +40607,12 @@
       </c>
       <c r="F911" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G911" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
         </is>
       </c>
       <c r="H911" s="4" t="inlineStr">
@@ -40618,7 +40624,7 @@
     <row r="912" ht="28" customHeight="1">
       <c r="A912" s="43" t="inlineStr">
         <is>
-          <t>74.15</t>
+          <t>74.13</t>
         </is>
       </c>
       <c r="B912" s="3" t="inlineStr">
@@ -40633,7 +40639,7 @@
       </c>
       <c r="D912" s="4" t="inlineStr">
         <is>
-          <t>Validasi card reject dengan data table</t>
+          <t>Validasi card data file aktif dengan data table</t>
         </is>
       </c>
       <c r="E912" s="3" t="inlineStr">
@@ -40643,12 +40649,12 @@
       </c>
       <c r="F912" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G912" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
         </is>
       </c>
       <c r="H912" s="4" t="inlineStr">
@@ -40660,7 +40666,7 @@
     <row r="913" ht="28" customHeight="1">
       <c r="A913" s="43" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.14</t>
         </is>
       </c>
       <c r="B913" s="3" t="inlineStr">
@@ -40670,12 +40676,12 @@
       </c>
       <c r="C913" s="3" t="inlineStr">
         <is>
-          <t>Persetujuan export</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D913" s="4" t="inlineStr">
         <is>
-          <t>Lakukan login menggunakan user monitoring</t>
+          <t>Validasi card file kadaluwarsa dengan data table</t>
         </is>
       </c>
       <c r="E913" s="3" t="inlineStr">
@@ -40690,19 +40696,19 @@
       </c>
       <c r="G913" s="4" t="inlineStr">
         <is>
-          <t>1. Login menggunakan user monitoring</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
         </is>
       </c>
       <c r="H913" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil melakukan login</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="914" ht="28" customHeight="1">
       <c r="A914" s="43" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.15</t>
         </is>
       </c>
       <c r="B914" s="3" t="inlineStr">
@@ -40712,12 +40718,12 @@
       </c>
       <c r="C914" s="3" t="inlineStr">
         <is>
-          <t>Persetujuan export</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D914" s="4" t="inlineStr">
         <is>
-          <t>Membuka menu Persetujuan Export</t>
+          <t>Validasi card reject dengan data table</t>
         </is>
       </c>
       <c r="E914" s="3" t="inlineStr">
@@ -40732,54 +40738,138 @@
       </c>
       <c r="G914" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu exported data management, klik submenu persetujuan export</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
         </is>
       </c>
       <c r="H914" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan halaman persetujuan export</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="915" ht="14" customHeight="1">
       <c r="A915" s="43" t="inlineStr">
         <is>
+          <t>75.1</t>
+        </is>
+      </c>
+      <c r="B915" s="3" t="inlineStr">
+        <is>
+          <t>Export data management</t>
+        </is>
+      </c>
+      <c r="C915" s="3" t="inlineStr">
+        <is>
+          <t>Persetujuan export</t>
+        </is>
+      </c>
+      <c r="D915" s="4" t="inlineStr">
+        <is>
+          <t>Lakukan login menggunakan user monitoring</t>
+        </is>
+      </c>
+      <c r="E915" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F915" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G915" s="4" t="inlineStr">
+        <is>
+          <t>1. Login menggunakan user monitoring</t>
+        </is>
+      </c>
+      <c r="H915" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil melakukan login</t>
+        </is>
+      </c>
+    </row>
+    <row r="916" ht="28" customHeight="1">
+      <c r="A916" s="43" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="B916" s="3" t="inlineStr">
+        <is>
+          <t>Export data management</t>
+        </is>
+      </c>
+      <c r="C916" s="3" t="inlineStr">
+        <is>
+          <t>Persetujuan export</t>
+        </is>
+      </c>
+      <c r="D916" s="4" t="inlineStr">
+        <is>
+          <t>Membuka menu Persetujuan Export</t>
+        </is>
+      </c>
+      <c r="E916" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F916" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G916" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu exported data management, klik submenu persetujuan export</t>
+        </is>
+      </c>
+      <c r="H916" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan halaman persetujuan export</t>
+        </is>
+      </c>
+    </row>
+    <row r="917" ht="14" customHeight="1">
+      <c r="A917" s="43" t="inlineStr">
+        <is>
           <t>75.3</t>
         </is>
       </c>
-      <c r="B915" s="3" t="inlineStr">
+      <c r="B917" s="3" t="inlineStr">
         <is>
           <t>Export data management</t>
         </is>
       </c>
-      <c r="C915" s="3" t="inlineStr">
+      <c r="C917" s="3" t="inlineStr">
         <is>
           <t>Persetujuan export</t>
         </is>
       </c>
-      <c r="D915" s="4" t="inlineStr">
+      <c r="D917" s="4" t="inlineStr">
         <is>
           <t>Melakukan approval data pengajuan export</t>
         </is>
       </c>
-      <c r="E915" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F915" s="3" t="inlineStr">
+      <c r="E917" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F917" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G915" s="4" t="inlineStr">
+      <c r="G917" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon titik tiga pada data pengajuan.
 2. Klik menu Setuju.
 3. Klik button YA pada popup konfirmasi.</t>
         </is>
       </c>
-      <c r="H915" s="4" t="inlineStr">
+      <c r="H917" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan menu opsi.
 2. Berhasil menampilkan popup konfirmasi.
@@ -40787,50 +40877,48 @@
         </is>
       </c>
     </row>
-    <row r="916" ht="28" customHeight="1">
-      <c r="A916" s="43" t="inlineStr">
+    <row r="918" ht="28" customHeight="1">
+      <c r="A918" s="43" t="inlineStr">
         <is>
           <t>75.4</t>
         </is>
       </c>
-      <c r="B916" s="3" t="inlineStr">
+      <c r="B918" s="3" t="inlineStr">
         <is>
           <t>Export data management</t>
         </is>
       </c>
-      <c r="C916" s="3" t="inlineStr">
+      <c r="C918" s="3" t="inlineStr">
         <is>
           <t>Persetujuan export</t>
         </is>
       </c>
-      <c r="D916" s="4" t="inlineStr">
+      <c r="D918" s="4" t="inlineStr">
         <is>
           <t>Melakukan reject data pengajuan export</t>
         </is>
       </c>
-      <c r="E916" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F916" s="3" t="inlineStr">
+      <c r="E918" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F918" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G916" s="4" t="inlineStr">
+      <c r="G918" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon (titik tiga) klik tolak, input alasan, klik submit</t>
         </is>
       </c>
-      <c r="H916" s="4" t="inlineStr">
+      <c r="H918" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil melakukan reject data</t>
         </is>
       </c>
     </row>
-    <row r="917" ht="14" customHeight="1"/>
-    <row r="918" ht="28" customHeight="1"/>
     <row r="919" ht="28" customHeight="1"/>
     <row r="920" ht="42" customHeight="1"/>
     <row r="921" ht="42" customHeight="1"/>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -36083,7 +36083,7 @@
       </c>
       <c r="D809" s="4" t="inlineStr">
         <is>
-          <t>Menambahkan Condition pada Performance Indicator</t>
+          <t>Menambahkan Kondisi pada Indikator Performa</t>
         </is>
       </c>
       <c r="E809" s="3" t="inlineStr">
@@ -36098,16 +36098,16 @@
       </c>
       <c r="G809" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Add Condition pada bagian Performance Indicator.
-2. Mengisi semua field mandatory pada condition baru.
-3. Klik button Submit.</t>
+          <t>1. Klik button + Tambah Kondisi pada bagian Indikator Performa.
+2. Mengisi semua field mandatory pada kondisi baru.
+3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H809" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan form condition baru pada Performance Indicator.
-2. Berhasil mengisi field mandatory condition.
-3. Berhasil menyimpan condition baru pada Performance Indicator.</t>
+          <t>1. Berhasil menampilkan form kondisi baru pada Indikator Performa.
+2. Berhasil mengisi field mandatory kondisi.
+3. Berhasil menyimpan kondisi baru pada Indikator Performa.</t>
         </is>
       </c>
     </row>
@@ -36129,7 +36129,7 @@
       </c>
       <c r="D810" s="4" t="inlineStr">
         <is>
-          <t>Menghapus Condition pada Performance Indicator</t>
+          <t>Menghapus Kondisi pada Indikator Performa</t>
         </is>
       </c>
       <c r="E810" s="3" t="inlineStr">
@@ -36144,13 +36144,13 @@
       </c>
       <c r="G810" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Remove pada salah satu condition di Performance Indicator.
-2. Klik button Submit.</t>
+          <t>1. Klik button Hapus pada salah satu kondisi di Indikator Performa.
+2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H810" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menghapus condition dari Performance Indicator.
+          <t>1. Berhasil menghapus kondisi dari Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
@@ -36173,7 +36173,7 @@
       </c>
       <c r="D811" s="4" t="inlineStr">
         <is>
-          <t>Menambahkan Operator pada Condition di Performance Indicator</t>
+          <t>Menambahkan Operator pada Kondisi</t>
         </is>
       </c>
       <c r="E811" s="3" t="inlineStr">
@@ -36188,14 +36188,14 @@
       </c>
       <c r="G811" s="4" t="inlineStr">
         <is>
-          <t>1. Klik link tambah operator pada salah satu condition di Performance Indicator.
+          <t>1. Klik link tambah operator pada salah satu kondisi di Indikator Performa.
 2. Mengisi field operator baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H811" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan baris operator baru pada condition.
+          <t>1. Berhasil menampilkan baris operator baru pada kondisi.
 2. Berhasil mengisi data operator.
 3. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
@@ -36219,7 +36219,7 @@
       </c>
       <c r="D812" s="4" t="inlineStr">
         <is>
-          <t>Menghapus Operator pada Condition di Performance Indicator</t>
+          <t>Menghapus Operator pada Kondisi</t>
         </is>
       </c>
       <c r="E812" s="3" t="inlineStr">
@@ -36234,13 +36234,13 @@
       </c>
       <c r="G812" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button x pada salah satu operator di Performance Indicator.
+          <t>1. Klik button x pada salah satu operator di Indikator Performa.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H812" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menghapus operator dari condition di Performance Indicator.
+          <t>1. Berhasil menghapus operator dari kondisi di Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
@@ -37861,7 +37861,7 @@
       </c>
       <c r="D849" s="4" t="inlineStr">
         <is>
-          <t>Menampilkan data Pengaturan Funnel Lending berdasarkan section</t>
+          <t>Mengubah data Pengaturan Funnel Lending</t>
         </is>
       </c>
       <c r="E849" s="3" t="inlineStr">
@@ -37871,17 +37871,19 @@
       </c>
       <c r="F849" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G849" s="4" t="inlineStr">
         <is>
-          <t>1. Klik salah satu daftar section pada tabel.</t>
+          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
+2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H849" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data pengaturan funnel Lending.</t>
+          <t>1. Berhasil mengisi field Performance Percentage.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
@@ -37903,7 +37905,7 @@
       </c>
       <c r="D850" s="4" t="inlineStr">
         <is>
-          <t>Mengubah data Pengaturan Funnel Lending</t>
+          <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E850" s="3" t="inlineStr">
@@ -37918,14 +37920,14 @@
       </c>
       <c r="G850" s="4" t="inlineStr">
         <is>
-          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
-2. Klik button Submit.</t>
+          <t>1. Mengosongkan field mandatory Performance Percentage.
+2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H850" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi field Performance Percentage.
-2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
+          <t>1. Berhasil mengosongkan field Performance Percentage.
+2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
@@ -37947,7 +37949,7 @@
       </c>
       <c r="D851" s="4" t="inlineStr">
         <is>
-          <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
+          <t>Menambahkan Kondisi pada Indikator Performa</t>
         </is>
       </c>
       <c r="E851" s="3" t="inlineStr">
@@ -37962,14 +37964,16 @@
       </c>
       <c r="G851" s="4" t="inlineStr">
         <is>
-          <t>1. Mengosongkan field mandatory Performance Percentage.
-2. Klik button Submit.</t>
+          <t>1. Klik button + Tambah Kondisi pada bagian Indikator Performa.
+2. Mengisi semua field mandatory pada kondisi baru.
+3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H851" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan field Performance Percentage.
-2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+          <t>1. Berhasil menampilkan form kondisi baru pada Indikator Performa.
+2. Berhasil mengisi field mandatory kondisi.
+3. Berhasil menyimpan kondisi baru pada Indikator Performa.</t>
         </is>
       </c>
     </row>
@@ -37991,7 +37995,7 @@
       </c>
       <c r="D852" s="4" t="inlineStr">
         <is>
-          <t>Menambahkan Condition pada Performance Indicator</t>
+          <t>Menghapus Kondisi pada Indikator Performa</t>
         </is>
       </c>
       <c r="E852" s="3" t="inlineStr">
@@ -38006,16 +38010,14 @@
       </c>
       <c r="G852" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Add Condition pada bagian Performance Indicator.
-2. Mengisi semua field mandatory pada condition baru.
-3. Klik button Submit.</t>
+          <t>1. Klik button Hapus pada salah satu kondisi di Indikator Performa.
+2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H852" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan form condition baru pada Performance Indicator.
-2. Berhasil mengisi field mandatory condition.
-3. Berhasil menyimpan condition baru pada Performance Indicator.</t>
+          <t>1. Berhasil menghapus kondisi dari Indikator Performa.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
@@ -38037,7 +38039,7 @@
       </c>
       <c r="D853" s="4" t="inlineStr">
         <is>
-          <t>Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory</t>
+          <t>Menambahkan Operator pada Kondisi</t>
         </is>
       </c>
       <c r="E853" s="3" t="inlineStr">
@@ -38052,16 +38054,16 @@
       </c>
       <c r="G853" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Add Condition pada bagian Performance Indicator.
-2. Mengosongkan field mandatory pada condition baru.
-3. Klik button Submit.</t>
+          <t>1. Klik link tambah operator pada salah satu kondisi di Indikator Performa.
+2. Mengisi field operator baru.
+3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H853" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan form condition baru pada Performance Indicator.
-2. Berhasil mengosongkan field mandatory condition.
-3. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+          <t>1. Berhasil menampilkan baris operator baru pada kondisi.
+2. Berhasil mengisi data operator.
+3. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
@@ -38083,7 +38085,7 @@
       </c>
       <c r="D854" s="4" t="inlineStr">
         <is>
-          <t>Menghapus Condition pada Performance Indicator</t>
+          <t>Menghapus Operator pada Kondisi</t>
         </is>
       </c>
       <c r="E854" s="3" t="inlineStr">
@@ -38098,13 +38100,13 @@
       </c>
       <c r="G854" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Remove pada salah satu condition di Performance Indicator.
-2. Klik button Submit.</t>
+          <t>1. Klik button x pada salah satu operator di Indikator Performa.
+2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H854" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menghapus condition dari Performance Indicator.
+          <t>1. Berhasil menghapus operator dari kondisi di Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z918"/>
+  <dimension ref="A1:Z909"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="12.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35684,12 +35684,12 @@
       </c>
       <c r="C800" s="3" t="inlineStr">
         <is>
-          <t>Regional Funnel</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D800" s="4" t="inlineStr">
         <is>
-          <t>Membuka halaman Regional Funnel</t>
+          <t>Membuka halaman Pengaturan Funnel Funding</t>
         </is>
       </c>
       <c r="E800" s="3" t="inlineStr">
@@ -35705,13 +35705,13 @@
       <c r="G800" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Funding.
-2. Klik sub menu Regional Funnel.</t>
+2. Klik sub menu Pengaturan Funnel.</t>
         </is>
       </c>
       <c r="H800" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Funding.
-2. Berhasil menampilkan halaman Regional Funnel.</t>
+2. Berhasil menampilkan halaman Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
@@ -35728,12 +35728,12 @@
       </c>
       <c r="C801" s="3" t="inlineStr">
         <is>
-          <t>Regional Funnel</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D801" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data Regional Funnel</t>
+          <t>Mengubah data Pengaturan Funnel Funding</t>
         </is>
       </c>
       <c r="E801" s="3" t="inlineStr">
@@ -35743,19 +35743,19 @@
       </c>
       <c r="F801" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G801" s="4" t="inlineStr">
         <is>
-          <t>1. Mengisi semua field filter mandatory.
+          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
 2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H801" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+          <t>1. Berhasil mengisi field Performance Percentage.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
@@ -35772,12 +35772,12 @@
       </c>
       <c r="C802" s="3" t="inlineStr">
         <is>
-          <t>Regional Funnel</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D802" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
+          <t>Mengubah data Pengaturan Funnel Funding tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E802" s="3" t="inlineStr">
@@ -35787,19 +35787,19 @@
       </c>
       <c r="F802" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G802" s="4" t="inlineStr">
         <is>
-          <t>1. Mengosongkan field filter mandatory.
+          <t>1. Mengosongkan field mandatory Performance Percentage.
 2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H802" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>1. Berhasil mengosongkan field Performance Percentage.
+2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
@@ -35816,12 +35816,12 @@
       </c>
       <c r="C803" s="3" t="inlineStr">
         <is>
-          <t>Regional Funnel</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D803" s="4" t="inlineStr">
         <is>
-          <t>Mencari data Regional Funnel dengan keyword valid</t>
+          <t>Menambahkan Kondisi pada Indikator Performa</t>
         </is>
       </c>
       <c r="E803" s="3" t="inlineStr">
@@ -35835,275 +35835,13 @@
         </is>
       </c>
       <c r="G803" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi field Cari Data dengan keyword valid.
-2. Klik button Search.</t>
-        </is>
-      </c>
-      <c r="H803" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field Cari Data.
-2. Berhasil menampilkan data yang dicari.</t>
-        </is>
-      </c>
-    </row>
-    <row r="804" ht="14" customHeight="1">
-      <c r="A804" s="43" t="inlineStr">
-        <is>
-          <t>63.5</t>
-        </is>
-      </c>
-      <c r="B804" s="3" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C804" s="3" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D804" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data Regional Funnel dengan keyword tidak valid</t>
-        </is>
-      </c>
-      <c r="E804" s="3" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F804" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G804" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi field Cari Data dengan keyword tidak valid.
-2. Klik button Search.</t>
-        </is>
-      </c>
-      <c r="H804" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field Cari Data.
-2. Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="805" ht="14" customHeight="1">
-      <c r="A805" s="43" t="inlineStr">
-        <is>
-          <t>63.6</t>
-        </is>
-      </c>
-      <c r="B805" s="3" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C805" s="3" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D805" s="4" t="inlineStr">
-        <is>
-          <t>Menampilkan data prospek berdasarkan kantor cabang</t>
-        </is>
-      </c>
-      <c r="E805" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F805" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G805" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik salah satu daftar kantor cabang pada tabel.</t>
-        </is>
-      </c>
-      <c r="H805" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data prospek pada kantor cabang yang dipilih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="806" ht="14" customHeight="1">
-      <c r="A806" s="43" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="B806" s="3" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C806" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D806" s="4" t="inlineStr">
-        <is>
-          <t>Membuka halaman Pengaturan Funnel Funding</t>
-        </is>
-      </c>
-      <c r="E806" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F806" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G806" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Funding.
-2. Klik sub menu Pengaturan Funnel.</t>
-        </is>
-      </c>
-      <c r="H806" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Funding.
-2. Berhasil menampilkan halaman Pengaturan Funnel Funding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="807" ht="14" customHeight="1">
-      <c r="A807" s="43" t="inlineStr">
-        <is>
-          <t>64.2</t>
-        </is>
-      </c>
-      <c r="B807" s="3" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C807" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D807" s="4" t="inlineStr">
-        <is>
-          <t>Mengubah data Pengaturan Funnel Funding</t>
-        </is>
-      </c>
-      <c r="E807" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F807" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G807" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H807" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field Performance Percentage.
-2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="808" ht="14" customHeight="1">
-      <c r="A808" s="43" t="inlineStr">
-        <is>
-          <t>64.3</t>
-        </is>
-      </c>
-      <c r="B808" s="3" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C808" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D808" s="4" t="inlineStr">
-        <is>
-          <t>Mengubah data Pengaturan Funnel Funding tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E808" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F808" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G808" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field mandatory Performance Percentage.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H808" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field Performance Percentage.
-2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="809" ht="14" customHeight="1">
-      <c r="A809" s="43" t="inlineStr">
-        <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="B809" s="3" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C809" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D809" s="4" t="inlineStr">
-        <is>
-          <t>Menambahkan Kondisi pada Indikator Performa</t>
-        </is>
-      </c>
-      <c r="E809" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F809" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G809" s="4" t="inlineStr">
         <is>
           <t>1. Klik button + Tambah Kondisi pada bagian Indikator Performa.
 2. Mengisi semua field mandatory pada kondisi baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H809" s="4" t="inlineStr">
+      <c r="H803" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan form kondisi baru pada Indikator Performa.
 2. Berhasil mengisi field mandatory kondisi.
@@ -36111,89 +35849,89 @@
         </is>
       </c>
     </row>
-    <row r="810" ht="42" customHeight="1">
-      <c r="A810" s="43" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
-      <c r="B810" s="3" t="inlineStr">
+    <row r="804" ht="14" customHeight="1">
+      <c r="A804" s="43" t="inlineStr">
+        <is>
+          <t>63.5</t>
+        </is>
+      </c>
+      <c r="B804" s="3" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C810" s="3" t="inlineStr">
+      <c r="C804" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D810" s="4" t="inlineStr">
+      <c r="D804" s="4" t="inlineStr">
         <is>
           <t>Menghapus Kondisi pada Indikator Performa</t>
         </is>
       </c>
-      <c r="E810" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F810" s="3" t="inlineStr">
+      <c r="E804" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F804" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G810" s="4" t="inlineStr">
+      <c r="G804" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Hapus pada salah satu kondisi di Indikator Performa.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H810" s="4" t="inlineStr">
+      <c r="H804" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menghapus kondisi dari Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
-    <row r="811" ht="28" customHeight="1">
-      <c r="A811" s="43" t="inlineStr">
-        <is>
-          <t>64.6</t>
-        </is>
-      </c>
-      <c r="B811" s="3" t="inlineStr">
+    <row r="805" ht="14" customHeight="1">
+      <c r="A805" s="43" t="inlineStr">
+        <is>
+          <t>63.6</t>
+        </is>
+      </c>
+      <c r="B805" s="3" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C811" s="3" t="inlineStr">
+      <c r="C805" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D811" s="4" t="inlineStr">
+      <c r="D805" s="4" t="inlineStr">
         <is>
           <t>Menambahkan Operator pada Kondisi</t>
         </is>
       </c>
-      <c r="E811" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F811" s="3" t="inlineStr">
+      <c r="E805" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F805" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G811" s="4" t="inlineStr">
+      <c r="G805" s="4" t="inlineStr">
         <is>
           <t>1. Klik link tambah operator pada salah satu kondisi di Indikator Performa.
 2. Mengisi field operator baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H811" s="4" t="inlineStr">
+      <c r="H805" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan baris operator baru pada kondisi.
 2. Berhasil mengisi data operator.
@@ -36201,263 +35939,263 @@
         </is>
       </c>
     </row>
-    <row r="812" ht="42" customHeight="1">
-      <c r="A812" s="43" t="inlineStr">
-        <is>
-          <t>64.7</t>
-        </is>
-      </c>
-      <c r="B812" s="3" t="inlineStr">
+    <row r="806" ht="14" customHeight="1">
+      <c r="A806" s="43" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="B806" s="3" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C812" s="3" t="inlineStr">
+      <c r="C806" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D812" s="4" t="inlineStr">
+      <c r="D806" s="4" t="inlineStr">
         <is>
           <t>Menghapus Operator pada Kondisi</t>
         </is>
       </c>
-      <c r="E812" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F812" s="3" t="inlineStr">
+      <c r="E806" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F806" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G812" s="4" t="inlineStr">
+      <c r="G806" s="4" t="inlineStr">
         <is>
           <t>1. Klik button x pada salah satu operator di Indikator Performa.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H812" s="4" t="inlineStr">
+      <c r="H806" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menghapus operator dari kondisi di Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
-    <row r="813" ht="28" customHeight="1">
-      <c r="A813" s="43" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
-      <c r="B813" s="3" t="inlineStr">
+    <row r="807" ht="14" customHeight="1">
+      <c r="A807" s="43" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="B807" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C813" s="3" t="inlineStr">
+      <c r="C807" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D813" s="4" t="inlineStr">
+      <c r="D807" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="E813" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F813" s="3" t="inlineStr">
+      <c r="E807" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F807" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G813" s="4" t="inlineStr">
+      <c r="G807" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Lending.
 2. Klik sub menu Daily Sales Agenda.</t>
         </is>
       </c>
-      <c r="H813" s="4" t="inlineStr">
+      <c r="H807" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Lending.
 2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
         </is>
       </c>
     </row>
-    <row r="814" ht="28" customHeight="1">
-      <c r="A814" s="43" t="inlineStr">
-        <is>
-          <t>65.2</t>
-        </is>
-      </c>
-      <c r="B814" s="3" t="inlineStr">
+    <row r="808" ht="14" customHeight="1">
+      <c r="A808" s="43" t="inlineStr">
+        <is>
+          <t>64.2</t>
+        </is>
+      </c>
+      <c r="B808" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C814" s="3" t="inlineStr">
+      <c r="C808" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D814" s="4" t="inlineStr">
+      <c r="D808" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="E814" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F814" s="3" t="inlineStr">
+      <c r="E808" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F808" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G814" s="4" t="inlineStr">
+      <c r="G808" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi semua field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H814" s="4" t="inlineStr">
+      <c r="H808" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field filter mandatory.
 2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="815" ht="56" customHeight="1">
-      <c r="A815" s="43" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
-      <c r="B815" s="3" t="inlineStr">
+    <row r="809" ht="14" customHeight="1">
+      <c r="A809" s="43" t="inlineStr">
+        <is>
+          <t>64.3</t>
+        </is>
+      </c>
+      <c r="B809" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C815" s="3" t="inlineStr">
+      <c r="C809" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D815" s="4" t="inlineStr">
+      <c r="D809" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E815" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F815" s="3" t="inlineStr">
+      <c r="E809" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F809" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G815" s="4" t="inlineStr">
+      <c r="G809" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H815" s="4" t="inlineStr">
+      <c r="H809" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
-    <row r="816" ht="56" customHeight="1">
-      <c r="A816" s="43" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
-      </c>
-      <c r="B816" s="3" t="inlineStr">
+    <row r="810" ht="42" customHeight="1">
+      <c r="A810" s="43" t="inlineStr">
+        <is>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="B810" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C816" s="3" t="inlineStr">
+      <c r="C810" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D816" s="4" t="inlineStr">
+      <c r="D810" s="4" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Masuk</t>
         </is>
       </c>
-      <c r="E816" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F816" s="3" t="inlineStr">
+      <c r="E810" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F810" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G816" s="4" t="inlineStr">
+      <c r="G810" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.</t>
         </is>
       </c>
-      <c r="H816" s="4" t="inlineStr">
+      <c r="H810" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Masuk.</t>
         </is>
       </c>
     </row>
-    <row r="817" ht="28" customHeight="1">
-      <c r="A817" s="43" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="B817" s="3" t="inlineStr">
+    <row r="811" ht="28" customHeight="1">
+      <c r="A811" s="43" t="inlineStr">
+        <is>
+          <t>64.5</t>
+        </is>
+      </c>
+      <c r="B811" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C817" s="3" t="inlineStr">
+      <c r="C811" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D817" s="4" t="inlineStr">
+      <c r="D811" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Masuk dengan keyword valid</t>
         </is>
       </c>
-      <c r="E817" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F817" s="3" t="inlineStr">
+      <c r="E811" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F811" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G817" s="4" t="inlineStr">
+      <c r="G811" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H817" s="4" t="inlineStr">
+      <c r="H811" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil mengisi field Cari Data.
@@ -36465,45 +36203,45 @@
         </is>
       </c>
     </row>
-    <row r="818" ht="28" customHeight="1">
-      <c r="A818" s="43" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="B818" s="3" t="inlineStr">
+    <row r="812" ht="42" customHeight="1">
+      <c r="A812" s="43" t="inlineStr">
+        <is>
+          <t>64.6</t>
+        </is>
+      </c>
+      <c r="B812" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C818" s="3" t="inlineStr">
+      <c r="C812" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D818" s="4" t="inlineStr">
+      <c r="D812" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E818" s="3" t="inlineStr">
+      <c r="E812" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F818" s="3" t="inlineStr">
+      <c r="F812" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G818" s="4" t="inlineStr">
+      <c r="G812" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H818" s="4" t="inlineStr">
+      <c r="H812" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil mengisi field Cari Data.
@@ -36511,89 +36249,89 @@
         </is>
       </c>
     </row>
-    <row r="819" ht="42" customHeight="1">
-      <c r="A819" s="43" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="B819" s="3" t="inlineStr">
+    <row r="813" ht="28" customHeight="1">
+      <c r="A813" s="43" t="inlineStr">
+        <is>
+          <t>64.7</t>
+        </is>
+      </c>
+      <c r="B813" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C819" s="3" t="inlineStr">
+      <c r="C813" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D819" s="4" t="inlineStr">
+      <c r="D813" s="4" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Masuk</t>
         </is>
       </c>
-      <c r="E819" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F819" s="3" t="inlineStr">
+      <c r="E813" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F813" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G819" s="4" t="inlineStr">
+      <c r="G813" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H819" s="4" t="inlineStr">
+      <c r="H813" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="820" ht="14" customHeight="1">
-      <c r="A820" s="43" t="inlineStr">
-        <is>
-          <t>65.8</t>
-        </is>
-      </c>
-      <c r="B820" s="3" t="inlineStr">
+    <row r="814" ht="28" customHeight="1">
+      <c r="A814" s="43" t="inlineStr">
+        <is>
+          <t>64.8</t>
+        </is>
+      </c>
+      <c r="B814" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C820" s="3" t="inlineStr">
+      <c r="C814" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D820" s="4" t="inlineStr">
+      <c r="D814" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Masuk</t>
         </is>
       </c>
-      <c r="E820" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F820" s="3" t="inlineStr">
+      <c r="E814" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F814" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G820" s="4" t="inlineStr">
+      <c r="G814" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H820" s="4" t="inlineStr">
+      <c r="H814" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil menampilkan panel Download Export.
@@ -36601,87 +36339,87 @@
         </is>
       </c>
     </row>
-    <row r="821" ht="56" customHeight="1">
-      <c r="A821" s="43" t="inlineStr">
-        <is>
-          <t>65.9</t>
-        </is>
-      </c>
-      <c r="B821" s="3" t="inlineStr">
+    <row r="815" ht="56" customHeight="1">
+      <c r="A815" s="43" t="inlineStr">
+        <is>
+          <t>64.9</t>
+        </is>
+      </c>
+      <c r="B815" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C821" s="3" t="inlineStr">
+      <c r="C815" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D821" s="4" t="inlineStr">
+      <c r="D815" s="4" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Closing</t>
         </is>
       </c>
-      <c r="E821" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F821" s="3" t="inlineStr">
+      <c r="E815" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F815" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G821" s="4" t="inlineStr">
+      <c r="G815" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.</t>
         </is>
       </c>
-      <c r="H821" s="4" t="inlineStr">
+      <c r="H815" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Closing.</t>
         </is>
       </c>
     </row>
-    <row r="822" ht="56" customHeight="1">
-      <c r="A822" s="43" t="inlineStr">
-        <is>
-          <t>65.10</t>
-        </is>
-      </c>
-      <c r="B822" s="3" t="inlineStr">
+    <row r="816" ht="56" customHeight="1">
+      <c r="A816" s="43" t="inlineStr">
+        <is>
+          <t>64.10</t>
+        </is>
+      </c>
+      <c r="B816" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C822" s="3" t="inlineStr">
+      <c r="C816" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D822" s="4" t="inlineStr">
+      <c r="D816" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Closing dengan keyword valid</t>
         </is>
       </c>
-      <c r="E822" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F822" s="3" t="inlineStr">
+      <c r="E816" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F816" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G822" s="4" t="inlineStr">
+      <c r="G816" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H822" s="4" t="inlineStr">
+      <c r="H816" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil mengisi field Cari Data.
@@ -36689,45 +36427,45 @@
         </is>
       </c>
     </row>
-    <row r="823" ht="56" customHeight="1">
-      <c r="A823" s="43" t="inlineStr">
-        <is>
-          <t>65.11</t>
-        </is>
-      </c>
-      <c r="B823" s="3" t="inlineStr">
+    <row r="817" ht="28" customHeight="1">
+      <c r="A817" s="43" t="inlineStr">
+        <is>
+          <t>64.11</t>
+        </is>
+      </c>
+      <c r="B817" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C823" s="3" t="inlineStr">
+      <c r="C817" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D823" s="4" t="inlineStr">
+      <c r="D817" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E823" s="3" t="inlineStr">
+      <c r="E817" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F823" s="3" t="inlineStr">
+      <c r="F817" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G823" s="4" t="inlineStr">
+      <c r="G817" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H823" s="4" t="inlineStr">
+      <c r="H817" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil mengisi field Cari Data.
@@ -36735,89 +36473,89 @@
         </is>
       </c>
     </row>
-    <row r="824" ht="14" customHeight="1">
-      <c r="A824" s="43" t="inlineStr">
-        <is>
-          <t>65.12</t>
-        </is>
-      </c>
-      <c r="B824" s="3" t="inlineStr">
+    <row r="818" ht="28" customHeight="1">
+      <c r="A818" s="43" t="inlineStr">
+        <is>
+          <t>64.12</t>
+        </is>
+      </c>
+      <c r="B818" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C824" s="3" t="inlineStr">
+      <c r="C818" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D824" s="4" t="inlineStr">
+      <c r="D818" s="4" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Closing</t>
         </is>
       </c>
-      <c r="E824" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F824" s="3" t="inlineStr">
+      <c r="E818" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F818" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G824" s="4" t="inlineStr">
+      <c r="G818" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H824" s="4" t="inlineStr">
+      <c r="H818" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="825" ht="14" customHeight="1">
-      <c r="A825" s="43" t="inlineStr">
-        <is>
-          <t>65.13</t>
-        </is>
-      </c>
-      <c r="B825" s="3" t="inlineStr">
+    <row r="819" ht="42" customHeight="1">
+      <c r="A819" s="43" t="inlineStr">
+        <is>
+          <t>64.13</t>
+        </is>
+      </c>
+      <c r="B819" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C825" s="3" t="inlineStr">
+      <c r="C819" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D825" s="4" t="inlineStr">
+      <c r="D819" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Closing</t>
         </is>
       </c>
-      <c r="E825" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F825" s="3" t="inlineStr">
+      <c r="E819" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F819" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G825" s="4" t="inlineStr">
+      <c r="G819" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H825" s="4" t="inlineStr">
+      <c r="H819" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil menampilkan panel Download Export.
@@ -36825,87 +36563,87 @@
         </is>
       </c>
     </row>
-    <row r="826" ht="14" customHeight="1">
-      <c r="A826" s="43" t="inlineStr">
-        <is>
-          <t>65.14</t>
-        </is>
-      </c>
-      <c r="B826" s="3" t="inlineStr">
+    <row r="820" ht="14" customHeight="1">
+      <c r="A820" s="43" t="inlineStr">
+        <is>
+          <t>64.14</t>
+        </is>
+      </c>
+      <c r="B820" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C826" s="3" t="inlineStr">
+      <c r="C820" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D826" s="4" t="inlineStr">
+      <c r="D820" s="4" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Referal</t>
         </is>
       </c>
-      <c r="E826" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F826" s="3" t="inlineStr">
+      <c r="E820" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F820" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G826" s="4" t="inlineStr">
+      <c r="G820" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.</t>
         </is>
       </c>
-      <c r="H826" s="4" t="inlineStr">
+      <c r="H820" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Referal.</t>
         </is>
       </c>
     </row>
-    <row r="827" ht="42" customHeight="1">
-      <c r="A827" s="43" t="inlineStr">
-        <is>
-          <t>65.15</t>
-        </is>
-      </c>
-      <c r="B827" s="3" t="inlineStr">
+    <row r="821" ht="56" customHeight="1">
+      <c r="A821" s="43" t="inlineStr">
+        <is>
+          <t>64.15</t>
+        </is>
+      </c>
+      <c r="B821" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C827" s="3" t="inlineStr">
+      <c r="C821" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D827" s="4" t="inlineStr">
+      <c r="D821" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal dengan keyword valid</t>
         </is>
       </c>
-      <c r="E827" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F827" s="3" t="inlineStr">
+      <c r="E821" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F821" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G827" s="4" t="inlineStr">
+      <c r="G821" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H827" s="4" t="inlineStr">
+      <c r="H821" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil mengisi field Cari Data.
@@ -36913,45 +36651,45 @@
         </is>
       </c>
     </row>
-    <row r="828" ht="14" customHeight="1">
-      <c r="A828" s="43" t="inlineStr">
-        <is>
-          <t>65.16</t>
-        </is>
-      </c>
-      <c r="B828" s="3" t="inlineStr">
+    <row r="822" ht="56" customHeight="1">
+      <c r="A822" s="43" t="inlineStr">
+        <is>
+          <t>64.16</t>
+        </is>
+      </c>
+      <c r="B822" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C828" s="3" t="inlineStr">
+      <c r="C822" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D828" s="4" t="inlineStr">
+      <c r="D822" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E828" s="3" t="inlineStr">
+      <c r="E822" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F828" s="3" t="inlineStr">
+      <c r="F822" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G828" s="4" t="inlineStr">
+      <c r="G822" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H828" s="4" t="inlineStr">
+      <c r="H822" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil mengisi field Cari Data.
@@ -36959,89 +36697,89 @@
         </is>
       </c>
     </row>
-    <row r="829" ht="56" customHeight="1">
-      <c r="A829" s="43" t="inlineStr">
-        <is>
-          <t>65.17</t>
-        </is>
-      </c>
-      <c r="B829" s="3" t="inlineStr">
+    <row r="823" ht="56" customHeight="1">
+      <c r="A823" s="43" t="inlineStr">
+        <is>
+          <t>64.17</t>
+        </is>
+      </c>
+      <c r="B823" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C829" s="3" t="inlineStr">
+      <c r="C823" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D829" s="4" t="inlineStr">
+      <c r="D823" s="4" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Referal</t>
         </is>
       </c>
-      <c r="E829" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F829" s="3" t="inlineStr">
+      <c r="E823" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F823" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G829" s="4" t="inlineStr">
+      <c r="G823" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H829" s="4" t="inlineStr">
+      <c r="H823" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="830" ht="28" customHeight="1">
-      <c r="A830" s="43" t="inlineStr">
-        <is>
-          <t>65.18</t>
-        </is>
-      </c>
-      <c r="B830" s="3" t="inlineStr">
+    <row r="824" ht="14" customHeight="1">
+      <c r="A824" s="43" t="inlineStr">
+        <is>
+          <t>64.18</t>
+        </is>
+      </c>
+      <c r="B824" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C830" s="3" t="inlineStr">
+      <c r="C824" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D830" s="4" t="inlineStr">
+      <c r="D824" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Referal</t>
         </is>
       </c>
-      <c r="E830" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F830" s="3" t="inlineStr">
+      <c r="E824" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F824" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G830" s="4" t="inlineStr">
+      <c r="G824" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H830" s="4" t="inlineStr">
+      <c r="H824" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil menampilkan panel Download Export.
@@ -37049,87 +36787,87 @@
         </is>
       </c>
     </row>
-    <row r="831" ht="42" customHeight="1">
-      <c r="A831" s="43" t="inlineStr">
-        <is>
-          <t>65.19</t>
-        </is>
-      </c>
-      <c r="B831" s="3" t="inlineStr">
+    <row r="825" ht="14" customHeight="1">
+      <c r="A825" s="43" t="inlineStr">
+        <is>
+          <t>64.19</t>
+        </is>
+      </c>
+      <c r="B825" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C831" s="3" t="inlineStr">
+      <c r="C825" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D831" s="4" t="inlineStr">
+      <c r="D825" s="4" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E831" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F831" s="3" t="inlineStr">
+      <c r="E825" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F825" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G831" s="4" t="inlineStr">
+      <c r="G825" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.</t>
         </is>
       </c>
-      <c r="H831" s="4" t="inlineStr">
+      <c r="H825" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
         </is>
       </c>
     </row>
-    <row r="832" ht="28" customHeight="1">
-      <c r="A832" s="43" t="inlineStr">
-        <is>
-          <t>65.20</t>
-        </is>
-      </c>
-      <c r="B832" s="3" t="inlineStr">
+    <row r="826" ht="14" customHeight="1">
+      <c r="A826" s="43" t="inlineStr">
+        <is>
+          <t>64.20</t>
+        </is>
+      </c>
+      <c r="B826" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C832" s="3" t="inlineStr">
+      <c r="C826" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D832" s="4" t="inlineStr">
+      <c r="D826" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
         </is>
       </c>
-      <c r="E832" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F832" s="3" t="inlineStr">
+      <c r="E826" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F826" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G832" s="4" t="inlineStr">
+      <c r="G826" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H832" s="4" t="inlineStr">
+      <c r="H826" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil mengisi field Cari Data.
@@ -37137,45 +36875,45 @@
         </is>
       </c>
     </row>
-    <row r="833" ht="14" customHeight="1">
-      <c r="A833" s="43" t="inlineStr">
-        <is>
-          <t>65.21</t>
-        </is>
-      </c>
-      <c r="B833" s="3" t="inlineStr">
+    <row r="827" ht="42" customHeight="1">
+      <c r="A827" s="43" t="inlineStr">
+        <is>
+          <t>64.21</t>
+        </is>
+      </c>
+      <c r="B827" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C833" s="3" t="inlineStr">
+      <c r="C827" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D833" s="4" t="inlineStr">
+      <c r="D827" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal Closing dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E833" s="3" t="inlineStr">
+      <c r="E827" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F833" s="3" t="inlineStr">
+      <c r="F827" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G833" s="4" t="inlineStr">
+      <c r="G827" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H833" s="4" t="inlineStr">
+      <c r="H827" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil mengisi field Cari Data.
@@ -37183,89 +36921,89 @@
         </is>
       </c>
     </row>
-    <row r="834" ht="14" customHeight="1">
-      <c r="A834" s="43" t="inlineStr">
-        <is>
-          <t>65.22</t>
-        </is>
-      </c>
-      <c r="B834" s="3" t="inlineStr">
+    <row r="828" ht="14" customHeight="1">
+      <c r="A828" s="43" t="inlineStr">
+        <is>
+          <t>64.22</t>
+        </is>
+      </c>
+      <c r="B828" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C834" s="3" t="inlineStr">
+      <c r="C828" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D834" s="4" t="inlineStr">
+      <c r="D828" s="4" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E834" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F834" s="3" t="inlineStr">
+      <c r="E828" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F828" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G834" s="4" t="inlineStr">
+      <c r="G828" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H834" s="4" t="inlineStr">
+      <c r="H828" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="835" ht="14" customHeight="1">
-      <c r="A835" s="43" t="inlineStr">
-        <is>
-          <t>65.23</t>
-        </is>
-      </c>
-      <c r="B835" s="3" t="inlineStr">
+    <row r="829" ht="56" customHeight="1">
+      <c r="A829" s="43" t="inlineStr">
+        <is>
+          <t>64.23</t>
+        </is>
+      </c>
+      <c r="B829" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C835" s="3" t="inlineStr">
+      <c r="C829" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D835" s="4" t="inlineStr">
+      <c r="D829" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E835" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F835" s="3" t="inlineStr">
+      <c r="E829" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F829" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G835" s="4" t="inlineStr">
+      <c r="G829" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H835" s="4" t="inlineStr">
+      <c r="H829" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil menampilkan panel Download Export.
@@ -37273,10 +37011,274 @@
         </is>
       </c>
     </row>
+    <row r="830" ht="28" customHeight="1">
+      <c r="A830" s="43" t="inlineStr">
+        <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="B830" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C830" s="3" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D830" s="4" t="inlineStr">
+        <is>
+          <t>Membuka halaman Personal Funnel</t>
+        </is>
+      </c>
+      <c r="E830" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F830" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G830" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Personal Funnel.</t>
+        </is>
+      </c>
+      <c r="H830" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Personal Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="831" ht="42" customHeight="1">
+      <c r="A831" s="43" t="inlineStr">
+        <is>
+          <t>65.2</t>
+        </is>
+      </c>
+      <c r="B831" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C831" s="3" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D831" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Personal Funnel</t>
+        </is>
+      </c>
+      <c r="E831" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F831" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G831" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengisi semua field filter mandatory.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H831" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi field filter mandatory.
+2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="832" ht="28" customHeight="1">
+      <c r="A832" s="43" t="inlineStr">
+        <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="B832" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C832" s="3" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D832" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E832" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F832" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G832" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengosongkan field filter mandatory.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H832" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan field filter mandatory.
+2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="833" ht="14" customHeight="1">
+      <c r="A833" s="43" t="inlineStr">
+        <is>
+          <t>65.4</t>
+        </is>
+      </c>
+      <c r="B833" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C833" s="3" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D833" s="4" t="inlineStr">
+        <is>
+          <t>Mengekspor data Personal Funnel</t>
+        </is>
+      </c>
+      <c r="E833" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F833" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G833" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Export.
+2. Klik icon download pada panel Download Export.</t>
+        </is>
+      </c>
+      <c r="H833" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan panel Download Export.
+2. Berhasil mendownload file export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="834" ht="14" customHeight="1">
+      <c r="A834" s="43" t="inlineStr">
+        <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="B834" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C834" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D834" s="4" t="inlineStr">
+        <is>
+          <t>Membuka halaman Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E834" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F834" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G834" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Rekap Funnel.</t>
+        </is>
+      </c>
+      <c r="H834" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Rekap Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="835" ht="14" customHeight="1">
+      <c r="A835" s="43" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="B835" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C835" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D835" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E835" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F835" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G835" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun).
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H835" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi field filter mandatory.
+2. Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
+        </is>
+      </c>
+    </row>
     <row r="836" ht="42" customHeight="1">
       <c r="A836" s="43" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="B836" s="3" t="inlineStr">
@@ -37286,12 +37288,12 @@
       </c>
       <c r="C836" s="3" t="inlineStr">
         <is>
-          <t>Personal Funnel</t>
+          <t>Rekap Funnel</t>
         </is>
       </c>
       <c r="D836" s="4" t="inlineStr">
         <is>
-          <t>Membuka halaman Personal Funnel</t>
+          <t>Melakukan filter data Rekap Funnel</t>
         </is>
       </c>
       <c r="E836" s="3" t="inlineStr">
@@ -37301,26 +37303,26 @@
       </c>
       <c r="F836" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G836" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Personal Funnel.</t>
+          <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
+2. Klik button Filter Data.</t>
         </is>
       </c>
       <c r="H836" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Personal Funnel.</t>
+          <t>1. Berhasil mengisi kriteria filter.
+2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="837" ht="28" customHeight="1">
       <c r="A837" s="43" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="B837" s="3" t="inlineStr">
@@ -37330,12 +37332,12 @@
       </c>
       <c r="C837" s="3" t="inlineStr">
         <is>
-          <t>Personal Funnel</t>
+          <t>Rekap Funnel</t>
         </is>
       </c>
       <c r="D837" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data Personal Funnel</t>
+          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E837" s="3" t="inlineStr">
@@ -37350,21 +37352,21 @@
       </c>
       <c r="G837" s="4" t="inlineStr">
         <is>
-          <t>1. Mengisi semua field filter mandatory.
-2. Klik button Submit.</t>
+          <t>1. Mengosongkan field filter mandatory.
+2. Klik button Filter Data.</t>
         </is>
       </c>
       <c r="H837" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+          <t>1. Berhasil mengosongkan field filter mandatory.
+2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="838" ht="28" customHeight="1">
       <c r="A838" s="43" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="B838" s="3" t="inlineStr">
@@ -37374,12 +37376,12 @@
       </c>
       <c r="C838" s="3" t="inlineStr">
         <is>
-          <t>Personal Funnel</t>
+          <t>Rekap Funnel</t>
         </is>
       </c>
       <c r="D838" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
+          <t>Mengunduh data Rekap Funnel</t>
         </is>
       </c>
       <c r="E838" s="3" t="inlineStr">
@@ -37389,26 +37391,24 @@
       </c>
       <c r="F838" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G838" s="4" t="inlineStr">
         <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Submit.</t>
+          <t>1. Klik button Download Excel.</t>
         </is>
       </c>
       <c r="H838" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>1. Berhasil mendownload file Excel data Rekap Funnel.</t>
         </is>
       </c>
     </row>
     <row r="839" ht="70" customHeight="1">
       <c r="A839" s="43" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="B839" s="3" t="inlineStr">
@@ -37418,12 +37418,12 @@
       </c>
       <c r="C839" s="3" t="inlineStr">
         <is>
-          <t>Personal Funnel</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D839" s="4" t="inlineStr">
         <is>
-          <t>Mengekspor data Personal Funnel</t>
+          <t>Membuka halaman Pengaturan Funnel Lending</t>
         </is>
       </c>
       <c r="E839" s="3" t="inlineStr">
@@ -37438,21 +37438,21 @@
       </c>
       <c r="G839" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Export.
-2. Klik icon download pada panel Download Export.</t>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Pengaturan Funnel.</t>
         </is>
       </c>
       <c r="H839" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan panel Download Export.
-2. Berhasil mendownload file export.</t>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
     <row r="840" ht="28" customHeight="1">
       <c r="A840" s="43" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="B840" s="3" t="inlineStr">
@@ -37462,12 +37462,12 @@
       </c>
       <c r="C840" s="3" t="inlineStr">
         <is>
-          <t>Rekap Funnel</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D840" s="4" t="inlineStr">
         <is>
-          <t>Membuka halaman Rekap Funnel</t>
+          <t>Mengubah data Pengaturan Funnel Lending</t>
         </is>
       </c>
       <c r="E840" s="3" t="inlineStr">
@@ -37482,21 +37482,21 @@
       </c>
       <c r="G840" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Rekap Funnel.</t>
+          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
+2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H840" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Rekap Funnel.</t>
+          <t>1. Berhasil mengisi field Performance Percentage.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
     <row r="841" ht="84" customHeight="1">
       <c r="A841" s="43" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="B841" s="3" t="inlineStr">
@@ -37506,12 +37506,12 @@
       </c>
       <c r="C841" s="3" t="inlineStr">
         <is>
-          <t>Rekap Funnel</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D841" s="4" t="inlineStr">
         <is>
-          <t>Menampilkan data Rekap Funnel</t>
+          <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E841" s="3" t="inlineStr">
@@ -37521,26 +37521,26 @@
       </c>
       <c r="F841" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G841" s="4" t="inlineStr">
         <is>
-          <t>1. Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun).
-2. Klik button Filter Data.</t>
+          <t>1. Mengosongkan field mandatory Performance Percentage.
+2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H841" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
+          <t>1. Berhasil mengosongkan field Performance Percentage.
+2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
     <row r="842" ht="28" customHeight="1">
       <c r="A842" s="43" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="B842" s="3" t="inlineStr">
@@ -37550,12 +37550,12 @@
       </c>
       <c r="C842" s="3" t="inlineStr">
         <is>
-          <t>Rekap Funnel</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D842" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data Rekap Funnel</t>
+          <t>Menambahkan Kondisi pada Indikator Performa</t>
         </is>
       </c>
       <c r="E842" s="3" t="inlineStr">
@@ -37565,411 +37565,17 @@
       </c>
       <c r="F842" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G842" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H842" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi kriteria filter.
-2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="843" ht="28" customHeight="1">
-      <c r="A843" s="43" t="inlineStr">
-        <is>
-          <t>67.4</t>
-        </is>
-      </c>
-      <c r="B843" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C843" s="3" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D843" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E843" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F843" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G843" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H843" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="844" ht="28" customHeight="1">
-      <c r="A844" s="43" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
-      <c r="B844" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C844" s="3" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D844" s="4" t="inlineStr">
-        <is>
-          <t>Mengunduh data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E844" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F844" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G844" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Download Excel.</t>
-        </is>
-      </c>
-      <c r="H844" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mendownload file Excel data Rekap Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="845" ht="42" customHeight="1">
-      <c r="A845" s="43" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="B845" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C845" s="3" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D845" s="4" t="inlineStr">
-        <is>
-          <t>Membuka halaman Regional Funnel</t>
-        </is>
-      </c>
-      <c r="E845" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F845" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G845" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Regional Funnel.</t>
-        </is>
-      </c>
-      <c r="H845" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Regional Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="846" ht="28" customHeight="1">
-      <c r="A846" s="43" t="inlineStr">
-        <is>
-          <t>68.2</t>
-        </is>
-      </c>
-      <c r="B846" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C846" s="3" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D846" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Regional Funnel</t>
-        </is>
-      </c>
-      <c r="E846" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F846" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G846" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi semua field filter mandatory.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H846" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="847" ht="14" customHeight="1">
-      <c r="A847" s="43" t="inlineStr">
-        <is>
-          <t>68.3</t>
-        </is>
-      </c>
-      <c r="B847" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C847" s="3" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D847" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E847" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F847" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G847" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H847" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="848" ht="14" customHeight="1">
-      <c r="A848" s="43" t="inlineStr">
-        <is>
-          <t>69.1</t>
-        </is>
-      </c>
-      <c r="B848" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C848" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D848" s="4" t="inlineStr">
-        <is>
-          <t>Membuka halaman Pengaturan Funnel Lending</t>
-        </is>
-      </c>
-      <c r="E848" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F848" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G848" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Pengaturan Funnel.</t>
-        </is>
-      </c>
-      <c r="H848" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Pengaturan Funnel Lending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="849" ht="42" customHeight="1">
-      <c r="A849" s="43" t="inlineStr">
-        <is>
-          <t>69.2</t>
-        </is>
-      </c>
-      <c r="B849" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C849" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D849" s="4" t="inlineStr">
-        <is>
-          <t>Mengubah data Pengaturan Funnel Lending</t>
-        </is>
-      </c>
-      <c r="E849" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F849" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G849" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
-2. Klik button Simpan Pengaturan.</t>
-        </is>
-      </c>
-      <c r="H849" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field Performance Percentage.
-2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="850" ht="28" customHeight="1">
-      <c r="A850" s="43" t="inlineStr">
-        <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="B850" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C850" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D850" s="4" t="inlineStr">
-        <is>
-          <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E850" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F850" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G850" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field mandatory Performance Percentage.
-2. Klik button Simpan Pengaturan.</t>
-        </is>
-      </c>
-      <c r="H850" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field Performance Percentage.
-2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="851" ht="28" customHeight="1">
-      <c r="A851" s="43" t="inlineStr">
-        <is>
-          <t>69.4</t>
-        </is>
-      </c>
-      <c r="B851" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C851" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D851" s="4" t="inlineStr">
-        <is>
-          <t>Menambahkan Kondisi pada Indikator Performa</t>
-        </is>
-      </c>
-      <c r="E851" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F851" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G851" s="4" t="inlineStr">
         <is>
           <t>1. Klik button + Tambah Kondisi pada bagian Indikator Performa.
 2. Mengisi semua field mandatory pada kondisi baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H851" s="4" t="inlineStr">
+      <c r="H842" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan form kondisi baru pada Indikator Performa.
 2. Berhasil mengisi field mandatory kondisi.
@@ -37977,89 +37583,89 @@
         </is>
       </c>
     </row>
-    <row r="852" ht="28" customHeight="1">
-      <c r="A852" s="43" t="inlineStr">
-        <is>
-          <t>69.5</t>
-        </is>
-      </c>
-      <c r="B852" s="3" t="inlineStr">
+    <row r="843" ht="28" customHeight="1">
+      <c r="A843" s="43" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="B843" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C852" s="3" t="inlineStr">
+      <c r="C843" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D852" s="4" t="inlineStr">
+      <c r="D843" s="4" t="inlineStr">
         <is>
           <t>Menghapus Kondisi pada Indikator Performa</t>
         </is>
       </c>
-      <c r="E852" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F852" s="3" t="inlineStr">
+      <c r="E843" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F843" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G852" s="4" t="inlineStr">
+      <c r="G843" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Hapus pada salah satu kondisi di Indikator Performa.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H852" s="4" t="inlineStr">
+      <c r="H843" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menghapus kondisi dari Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="853" ht="28" customHeight="1">
-      <c r="A853" s="43" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
-      <c r="B853" s="3" t="inlineStr">
+    <row r="844" ht="28" customHeight="1">
+      <c r="A844" s="43" t="inlineStr">
+        <is>
+          <t>67.6</t>
+        </is>
+      </c>
+      <c r="B844" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C853" s="3" t="inlineStr">
+      <c r="C844" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D853" s="4" t="inlineStr">
+      <c r="D844" s="4" t="inlineStr">
         <is>
           <t>Menambahkan Operator pada Kondisi</t>
         </is>
       </c>
-      <c r="E853" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F853" s="3" t="inlineStr">
+      <c r="E844" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F844" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G853" s="4" t="inlineStr">
+      <c r="G844" s="4" t="inlineStr">
         <is>
           <t>1. Klik link tambah operator pada salah satu kondisi di Indikator Performa.
 2. Mengisi field operator baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H853" s="4" t="inlineStr">
+      <c r="H844" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan baris operator baru pada kondisi.
 2. Berhasil mengisi data operator.
@@ -38067,170 +37673,170 @@
         </is>
       </c>
     </row>
-    <row r="854" ht="28" customHeight="1">
-      <c r="A854" s="43" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
-      <c r="B854" s="3" t="inlineStr">
+    <row r="845" ht="42" customHeight="1">
+      <c r="A845" s="43" t="inlineStr">
+        <is>
+          <t>67.7</t>
+        </is>
+      </c>
+      <c r="B845" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C854" s="3" t="inlineStr">
+      <c r="C845" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D854" s="4" t="inlineStr">
+      <c r="D845" s="4" t="inlineStr">
         <is>
           <t>Menghapus Operator pada Kondisi</t>
         </is>
       </c>
-      <c r="E854" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F854" s="3" t="inlineStr">
+      <c r="E845" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F845" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G854" s="4" t="inlineStr">
+      <c r="G845" s="4" t="inlineStr">
         <is>
           <t>1. Klik button x pada salah satu operator di Indikator Performa.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H854" s="4" t="inlineStr">
+      <c r="H845" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menghapus operator dari kondisi di Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="855" ht="28" customHeight="1">
-      <c r="A855" s="43" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
-      </c>
-      <c r="B855" s="3" t="inlineStr">
+    <row r="846" ht="28" customHeight="1">
+      <c r="A846" s="43" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="B846" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C855" s="3" t="inlineStr">
+      <c r="C846" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D855" s="4" t="inlineStr">
+      <c r="D846" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Approval non Banking</t>
         </is>
       </c>
-      <c r="E855" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F855" s="3" t="inlineStr">
+      <c r="E846" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F846" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G855" s="4" t="inlineStr">
+      <c r="G846" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Re-Assign &amp; Approval 
 2. Klik submenu Approval non banking</t>
         </is>
       </c>
-      <c r="H855" s="4" t="inlineStr">
+      <c r="H846" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan submenu Re-Assign &amp; Approval 
 2. Menampilkan halaman Approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="856" ht="28" customHeight="1">
-      <c r="A856" s="43" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="B856" s="3" t="inlineStr">
+    <row r="847" ht="14" customHeight="1">
+      <c r="A847" s="43" t="inlineStr">
+        <is>
+          <t>68.2</t>
+        </is>
+      </c>
+      <c r="B847" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C856" s="3" t="inlineStr">
+      <c r="C847" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D856" s="4" t="inlineStr">
+      <c r="D847" s="4" t="inlineStr">
         <is>
           <t>Melihat Detail data Approval non banking</t>
         </is>
       </c>
-      <c r="E856" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F856" s="3" t="inlineStr">
+      <c r="E847" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F847" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G856" s="4" t="inlineStr">
+      <c r="G847" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Detail</t>
         </is>
       </c>
-      <c r="H856" s="4" t="inlineStr">
+      <c r="H847" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan halaman detail data approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="857" ht="28" customHeight="1">
-      <c r="A857" s="43" t="inlineStr">
-        <is>
-          <t>70.3</t>
-        </is>
-      </c>
-      <c r="B857" s="3" t="inlineStr">
+    <row r="848" ht="14" customHeight="1">
+      <c r="A848" s="43" t="inlineStr">
+        <is>
+          <t>68.3</t>
+        </is>
+      </c>
+      <c r="B848" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C857" s="3" t="inlineStr">
+      <c r="C848" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D857" s="4" t="inlineStr">
+      <c r="D848" s="4" t="inlineStr">
         <is>
           <t>Menyetujui Prospek</t>
         </is>
       </c>
-      <c r="E857" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F857" s="3" t="inlineStr">
+      <c r="E848" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F848" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G857" s="4" t="inlineStr">
+      <c r="G848" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Setujui 
@@ -38239,7 +37845,7 @@
 5. Klik button Setujui</t>
         </is>
       </c>
-      <c r="H857" s="4" t="inlineStr">
+      <c r="H848" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan modal approve 
@@ -38249,87 +37855,87 @@
         </is>
       </c>
     </row>
-    <row r="858" ht="28" customHeight="1">
-      <c r="A858" s="43" t="inlineStr">
-        <is>
-          <t>70.4</t>
-        </is>
-      </c>
-      <c r="B858" s="3" t="inlineStr">
+    <row r="849" ht="42" customHeight="1">
+      <c r="A849" s="43" t="inlineStr">
+        <is>
+          <t>68.4</t>
+        </is>
+      </c>
+      <c r="B849" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C858" s="3" t="inlineStr">
+      <c r="C849" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D858" s="4" t="inlineStr">
+      <c r="D849" s="4" t="inlineStr">
         <is>
           <t>Batal menyetujui Prospek</t>
         </is>
       </c>
-      <c r="E858" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F858" s="3" t="inlineStr">
+      <c r="E849" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F849" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G858" s="4" t="inlineStr">
+      <c r="G849" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Batalkan pada modal approve</t>
         </is>
       </c>
-      <c r="H858" s="4" t="inlineStr">
+      <c r="H849" s="4" t="inlineStr">
         <is>
           <t>1. Modal approve tertutup dan tetap di halaman approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="859" ht="28" customHeight="1">
-      <c r="A859" s="43" t="inlineStr">
-        <is>
-          <t>70.5</t>
-        </is>
-      </c>
-      <c r="B859" s="3" t="inlineStr">
+    <row r="850" ht="28" customHeight="1">
+      <c r="A850" s="43" t="inlineStr">
+        <is>
+          <t>68.5</t>
+        </is>
+      </c>
+      <c r="B850" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C859" s="3" t="inlineStr">
+      <c r="C850" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D859" s="4" t="inlineStr">
+      <c r="D850" s="4" t="inlineStr">
         <is>
           <t>Tidak menginput nilai realisasi pada modal approve</t>
         </is>
       </c>
-      <c r="E859" s="3" t="inlineStr">
+      <c r="E850" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F859" s="3" t="inlineStr">
+      <c r="F850" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G859" s="4" t="inlineStr">
+      <c r="G850" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan nilai realisasi 
 2. Input remark 
 3. Klik button Setujui</t>
         </is>
       </c>
-      <c r="H859" s="4" t="inlineStr">
+      <c r="H850" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field realisasi 
 2. Berhasil menginput remark 
@@ -38337,122 +37943,122 @@
         </is>
       </c>
     </row>
-    <row r="860" ht="28" customHeight="1">
-      <c r="A860" s="43" t="inlineStr">
-        <is>
-          <t>70.6</t>
-        </is>
-      </c>
-      <c r="B860" s="3" t="inlineStr">
+    <row r="851" ht="28" customHeight="1">
+      <c r="A851" s="43" t="inlineStr">
+        <is>
+          <t>68.6</t>
+        </is>
+      </c>
+      <c r="B851" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C860" s="3" t="inlineStr">
+      <c r="C851" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D860" s="4" t="inlineStr">
+      <c r="D851" s="4" t="inlineStr">
         <is>
           <t>Tidak menginput remark pada modal approve</t>
         </is>
       </c>
-      <c r="E860" s="3" t="inlineStr">
+      <c r="E851" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F860" s="3" t="inlineStr">
+      <c r="F851" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G860" s="4" t="inlineStr">
+      <c r="G851" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan remark</t>
         </is>
       </c>
-      <c r="H860" s="4" t="inlineStr">
+      <c r="H851" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan alert 'Remark dibutuhkan!'</t>
         </is>
       </c>
     </row>
-    <row r="861" ht="28" customHeight="1">
-      <c r="A861" s="43" t="inlineStr">
-        <is>
-          <t>70.7</t>
-        </is>
-      </c>
-      <c r="B861" s="3" t="inlineStr">
+    <row r="852" ht="28" customHeight="1">
+      <c r="A852" s="43" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="B852" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C861" s="3" t="inlineStr">
+      <c r="C852" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D861" s="4" t="inlineStr">
+      <c r="D852" s="4" t="inlineStr">
         <is>
           <t>Menginput huruf pada field realisasi</t>
         </is>
       </c>
-      <c r="E861" s="3" t="inlineStr">
+      <c r="E852" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F861" s="3" t="inlineStr">
+      <c r="F852" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G861" s="4" t="inlineStr">
+      <c r="G852" s="4" t="inlineStr">
         <is>
           <t>1. Input huruf pada field realisasi kemudian pindah ke filed lain</t>
         </is>
       </c>
-      <c r="H861" s="4" t="inlineStr">
+      <c r="H852" s="4" t="inlineStr">
         <is>
           <t>1. Sistem menghapus input non-numerik secara otomatis saat field kehilangan fokus. Field Realiasi menjadi kosong</t>
         </is>
       </c>
     </row>
-    <row r="862" ht="28" customHeight="1">
-      <c r="A862" s="43" t="inlineStr">
-        <is>
-          <t>70.8</t>
-        </is>
-      </c>
-      <c r="B862" s="3" t="inlineStr">
+    <row r="853" ht="28" customHeight="1">
+      <c r="A853" s="43" t="inlineStr">
+        <is>
+          <t>68.8</t>
+        </is>
+      </c>
+      <c r="B853" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C862" s="3" t="inlineStr">
+      <c r="C853" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D862" s="4" t="inlineStr">
+      <c r="D853" s="4" t="inlineStr">
         <is>
           <t>Menolak Prospek</t>
         </is>
       </c>
-      <c r="E862" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F862" s="3" t="inlineStr">
+      <c r="E853" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F853" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G862" s="4" t="inlineStr">
+      <c r="G853" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Tolak 
@@ -38460,7 +38066,7 @@
 4. Klik button Tolak</t>
         </is>
       </c>
-      <c r="H862" s="4" t="inlineStr">
+      <c r="H853" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan modal tolak prospek
@@ -38469,210 +38075,210 @@
         </is>
       </c>
     </row>
-    <row r="863" ht="28" customHeight="1">
-      <c r="A863" s="43" t="inlineStr">
-        <is>
-          <t>70.9</t>
-        </is>
-      </c>
-      <c r="B863" s="3" t="inlineStr">
+    <row r="854" ht="28" customHeight="1">
+      <c r="A854" s="43" t="inlineStr">
+        <is>
+          <t>68.9</t>
+        </is>
+      </c>
+      <c r="B854" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C863" s="3" t="inlineStr">
+      <c r="C854" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D863" s="4" t="inlineStr">
+      <c r="D854" s="4" t="inlineStr">
         <is>
           <t>Batal menolak prospek</t>
         </is>
       </c>
-      <c r="E863" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F863" s="3" t="inlineStr">
+      <c r="E854" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F854" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G863" s="4" t="inlineStr">
+      <c r="G854" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Batalkan pada moal tolak prospek</t>
         </is>
       </c>
-      <c r="H863" s="4" t="inlineStr">
+      <c r="H854" s="4" t="inlineStr">
         <is>
           <t>1. Modal tolak prospek tertutup dan tetap berada di halaman approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="864" ht="28" customHeight="1">
-      <c r="A864" s="43" t="inlineStr">
-        <is>
-          <t>70.10</t>
-        </is>
-      </c>
-      <c r="B864" s="3" t="inlineStr">
+    <row r="855" ht="28" customHeight="1">
+      <c r="A855" s="43" t="inlineStr">
+        <is>
+          <t>68.10</t>
+        </is>
+      </c>
+      <c r="B855" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C864" s="3" t="inlineStr">
+      <c r="C855" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D864" s="4" t="inlineStr">
+      <c r="D855" s="4" t="inlineStr">
         <is>
           <t>Tidak menginput remark pada modal tolak prospek</t>
         </is>
       </c>
-      <c r="E864" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F864" s="3" t="inlineStr">
+      <c r="E855" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F855" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G864" s="4" t="inlineStr">
+      <c r="G855" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan remark 
 2. Klik button Tolak</t>
         </is>
       </c>
-      <c r="H864" s="4" t="inlineStr">
+      <c r="H855" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan remark 
 2. Menampilkan alert 'Remark dibutuhkan!'</t>
         </is>
       </c>
     </row>
-    <row r="865" ht="28" customHeight="1">
-      <c r="A865" s="43" t="inlineStr">
-        <is>
-          <t>70.11</t>
-        </is>
-      </c>
-      <c r="B865" s="3" t="inlineStr">
+    <row r="856" ht="28" customHeight="1">
+      <c r="A856" s="43" t="inlineStr">
+        <is>
+          <t>68.11</t>
+        </is>
+      </c>
+      <c r="B856" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C865" s="3" t="inlineStr">
+      <c r="C856" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D865" s="4" t="inlineStr">
+      <c r="D856" s="4" t="inlineStr">
         <is>
           <t>Filter kolom</t>
         </is>
       </c>
-      <c r="E865" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F865" s="3" t="inlineStr">
+      <c r="E856" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F856" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G865" s="4" t="inlineStr">
+      <c r="G856" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon filter kolom 
 2. Checklist/unchecklist kolom</t>
         </is>
       </c>
-      <c r="H865" s="4" t="inlineStr">
+      <c r="H856" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan list kolom tabel 
 2. Menampilkan data tabel sesuai dengan kolom yang di ceklis</t>
         </is>
       </c>
     </row>
-    <row r="866" ht="28" customHeight="1">
-      <c r="A866" s="43" t="inlineStr">
-        <is>
-          <t>70.12</t>
-        </is>
-      </c>
-      <c r="B866" s="3" t="inlineStr">
+    <row r="857" ht="28" customHeight="1">
+      <c r="A857" s="43" t="inlineStr">
+        <is>
+          <t>68.12</t>
+        </is>
+      </c>
+      <c r="B857" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C866" s="3" t="inlineStr">
+      <c r="C857" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D866" s="4" t="inlineStr">
+      <c r="D857" s="4" t="inlineStr">
         <is>
           <t>Reset ke Default pada filter kolom</t>
         </is>
       </c>
-      <c r="E866" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F866" s="3" t="inlineStr">
+      <c r="E857" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F857" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G866" s="4" t="inlineStr">
+      <c r="G857" s="4" t="inlineStr">
         <is>
           <t>1. Klik Reset ke Default</t>
         </is>
       </c>
-      <c r="H866" s="4" t="inlineStr">
+      <c r="H857" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data tabel dengan kolom default</t>
         </is>
       </c>
     </row>
-    <row r="867" ht="28" customHeight="1">
-      <c r="A867" s="43" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
-      <c r="B867" s="3" t="inlineStr">
+    <row r="858" ht="28" customHeight="1">
+      <c r="A858" s="43" t="inlineStr">
+        <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="B858" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C867" s="3" t="inlineStr">
+      <c r="C858" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D867" s="4" t="inlineStr">
+      <c r="D858" s="4" t="inlineStr">
         <is>
           <t>Filter data</t>
         </is>
       </c>
-      <c r="E867" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F867" s="3" t="inlineStr">
+      <c r="E858" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F858" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G867" s="4" t="inlineStr">
+      <c r="G858" s="4" t="inlineStr">
         <is>
           <t>1. Pilih kantor wilayah
 2. Pilih kantor cabang 
@@ -38682,7 +38288,7 @@
 6. Klik button Filter</t>
         </is>
       </c>
-      <c r="H867" s="4" t="inlineStr">
+      <c r="H858" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list data filter kantor wilayah dan dapat di pilih
 2. Menampilkan dropdown list data filter kantor cabang dan dapat di pilih
@@ -38693,126 +38299,126 @@
         </is>
       </c>
     </row>
-    <row r="868" ht="28" customHeight="1">
-      <c r="A868" s="43" t="inlineStr">
-        <is>
-          <t>71.2</t>
-        </is>
-      </c>
-      <c r="B868" s="3" t="inlineStr">
+    <row r="859" ht="28" customHeight="1">
+      <c r="A859" s="43" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="B859" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C868" s="3" t="inlineStr">
+      <c r="C859" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D868" s="4" t="inlineStr">
+      <c r="D859" s="4" t="inlineStr">
         <is>
           <t>Mencari data</t>
         </is>
       </c>
-      <c r="E868" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F868" s="3" t="inlineStr">
+      <c r="E859" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F859" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G868" s="4" t="inlineStr">
+      <c r="G859" s="4" t="inlineStr">
         <is>
           <t>1. Input keyword pada field search 
 2. Klik icon search yang ada di sebelah field</t>
         </is>
       </c>
-      <c r="H868" s="4" t="inlineStr">
+      <c r="H859" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput keyword 
 2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
         </is>
       </c>
     </row>
-    <row r="869" ht="28" customHeight="1">
-      <c r="A869" s="43" t="inlineStr">
-        <is>
-          <t>71.3</t>
-        </is>
-      </c>
-      <c r="B869" s="3" t="inlineStr">
+    <row r="860" ht="28" customHeight="1">
+      <c r="A860" s="43" t="inlineStr">
+        <is>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="B860" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C869" s="3" t="inlineStr">
+      <c r="C860" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D869" s="4" t="inlineStr">
+      <c r="D860" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E869" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F869" s="3" t="inlineStr">
+      <c r="E860" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F860" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G869" s="4" t="inlineStr">
+      <c r="G860" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Re-Assign &amp; Approval 
 2. Klik submenu Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="H869" s="4" t="inlineStr">
+      <c r="H860" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan submenu Re-Assign &amp; Approval 
 2. Menampilkan halaman Re-Assign Prospek</t>
         </is>
       </c>
     </row>
-    <row r="870" ht="28" customHeight="1">
-      <c r="A870" s="43" t="inlineStr">
-        <is>
-          <t>71.4</t>
-        </is>
-      </c>
-      <c r="B870" s="3" t="inlineStr">
+    <row r="861" ht="28" customHeight="1">
+      <c r="A861" s="43" t="inlineStr">
+        <is>
+          <t>69.4</t>
+        </is>
+      </c>
+      <c r="B861" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C870" s="3" t="inlineStr">
+      <c r="C861" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D870" s="4" t="inlineStr">
+      <c r="D861" s="4" t="inlineStr">
         <is>
           <t>Filter data</t>
         </is>
       </c>
-      <c r="E870" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F870" s="3" t="inlineStr">
+      <c r="E861" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F861" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G870" s="4" t="inlineStr">
+      <c r="G861" s="4" t="inlineStr">
         <is>
           <t>1. Pilih kantor wilayah
 2. Pilih kantor cabang 
@@ -38822,7 +38428,7 @@
 6. Klik button Filter</t>
         </is>
       </c>
-      <c r="H870" s="4" t="inlineStr">
+      <c r="H861" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list data filter kantor wilayah dan dapat di pilih
 2. Menampilkan dropdown list data filter kantor cabang dan dapat di pilih
@@ -38833,252 +38439,252 @@
         </is>
       </c>
     </row>
-    <row r="871" ht="28" customHeight="1">
-      <c r="A871" s="43" t="inlineStr">
-        <is>
-          <t>71.5</t>
-        </is>
-      </c>
-      <c r="B871" s="3" t="inlineStr">
+    <row r="862" ht="28" customHeight="1">
+      <c r="A862" s="43" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="B862" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C871" s="3" t="inlineStr">
+      <c r="C862" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D871" s="4" t="inlineStr">
+      <c r="D862" s="4" t="inlineStr">
         <is>
           <t>Mencari data</t>
         </is>
       </c>
-      <c r="E871" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F871" s="3" t="inlineStr">
+      <c r="E862" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F862" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G871" s="4" t="inlineStr">
+      <c r="G862" s="4" t="inlineStr">
         <is>
           <t>1. Input keyword pada field search 
 2. Klik icon search yang ada di sebelah field</t>
         </is>
       </c>
-      <c r="H871" s="4" t="inlineStr">
+      <c r="H862" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput keyword 
 2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
         </is>
       </c>
     </row>
-    <row r="872" ht="70" customHeight="1">
-      <c r="A872" s="43" t="inlineStr">
-        <is>
-          <t>71.6</t>
-        </is>
-      </c>
-      <c r="B872" s="3" t="inlineStr">
+    <row r="863" ht="28" customHeight="1">
+      <c r="A863" s="43" t="inlineStr">
+        <is>
+          <t>69.6</t>
+        </is>
+      </c>
+      <c r="B863" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C872" s="3" t="inlineStr">
+      <c r="C863" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D872" s="4" t="inlineStr">
+      <c r="D863" s="4" t="inlineStr">
         <is>
           <t>Validasi count checklist data</t>
         </is>
       </c>
-      <c r="E872" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F872" s="3" t="inlineStr">
+      <c r="E863" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F863" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G872" s="4" t="inlineStr">
+      <c r="G863" s="4" t="inlineStr">
         <is>
           <t>1. Cek informasi yang ada pada button Reassign () data</t>
         </is>
       </c>
-      <c r="H872" s="4" t="inlineStr">
+      <c r="H863" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan count angka yang sesuai dengan data yang di checklist</t>
         </is>
       </c>
     </row>
-    <row r="873" ht="42" customHeight="1">
-      <c r="A873" s="43" t="inlineStr">
-        <is>
-          <t>71.7</t>
-        </is>
-      </c>
-      <c r="B873" s="3" t="inlineStr">
+    <row r="864" ht="28" customHeight="1">
+      <c r="A864" s="43" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="B864" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C873" s="3" t="inlineStr">
+      <c r="C864" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D873" s="4" t="inlineStr">
+      <c r="D864" s="4" t="inlineStr">
         <is>
           <t>Validasi data yang sudah dii pilih</t>
         </is>
       </c>
-      <c r="E873" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F873" s="3" t="inlineStr">
+      <c r="E864" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F864" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G873" s="4" t="inlineStr">
+      <c r="G864" s="4" t="inlineStr">
         <is>
           <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi prospek yang di pilih</t>
         </is>
       </c>
-      <c r="H873" s="4" t="inlineStr">
+      <c r="H864" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan data tabel prospek yang di pilih saja</t>
         </is>
       </c>
     </row>
-    <row r="874" ht="42" customHeight="1">
-      <c r="A874" s="43" t="inlineStr">
-        <is>
-          <t>71.8</t>
-        </is>
-      </c>
-      <c r="B874" s="3" t="inlineStr">
+    <row r="865" ht="28" customHeight="1">
+      <c r="A865" s="43" t="inlineStr">
+        <is>
+          <t>69.8</t>
+        </is>
+      </c>
+      <c r="B865" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C874" s="3" t="inlineStr">
+      <c r="C865" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D874" s="4" t="inlineStr">
+      <c r="D865" s="4" t="inlineStr">
         <is>
           <t>Mengosongkan field inputan mandatory pada reassign prospek</t>
         </is>
       </c>
-      <c r="E874" s="3" t="inlineStr">
+      <c r="E865" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F874" s="3" t="inlineStr">
+      <c r="F865" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G874" s="4" t="inlineStr">
+      <c r="G865" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan salah satu atau semua field mandatory 
 2. Klik button Submit</t>
         </is>
       </c>
-      <c r="H874" s="4" t="inlineStr">
+      <c r="H865" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil tidak mengisi/mengosongkan field 
 2. Menampilkan alert pada setiap field mandatory bahwa field tersebut dibutuhkan / wajib diisi</t>
         </is>
       </c>
     </row>
-    <row r="875" ht="70" customHeight="1">
-      <c r="A875" s="43" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
-      </c>
-      <c r="B875" s="3" t="inlineStr">
+    <row r="866" ht="28" customHeight="1">
+      <c r="A866" s="43" t="inlineStr">
+        <is>
+          <t>69.9</t>
+        </is>
+      </c>
+      <c r="B866" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C875" s="3" t="inlineStr">
+      <c r="C866" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D875" s="4" t="inlineStr">
+      <c r="D866" s="4" t="inlineStr">
         <is>
           <t>Membatalkan Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E875" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F875" s="3" t="inlineStr">
+      <c r="E866" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F866" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G875" s="4" t="inlineStr">
+      <c r="G866" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
         </is>
       </c>
-      <c r="H875" s="4" t="inlineStr">
+      <c r="H866" s="4" t="inlineStr">
         <is>
           <t>1. Kembali ke halaman utama Re-assign Prospek</t>
         </is>
       </c>
     </row>
-    <row r="876" ht="28" customHeight="1">
-      <c r="A876" s="43" t="inlineStr">
-        <is>
-          <t>71.10</t>
-        </is>
-      </c>
-      <c r="B876" s="3" t="inlineStr">
+    <row r="867" ht="28" customHeight="1">
+      <c r="A867" s="43" t="inlineStr">
+        <is>
+          <t>69.10</t>
+        </is>
+      </c>
+      <c r="B867" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C876" s="3" t="inlineStr">
+      <c r="C867" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D876" s="4" t="inlineStr">
+      <c r="D867" s="4" t="inlineStr">
         <is>
           <t>Validasi data prospek yang di re-assign</t>
         </is>
       </c>
-      <c r="E876" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F876" s="3" t="inlineStr">
+      <c r="E867" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F867" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G876" s="4" t="inlineStr">
+      <c r="G867" s="4" t="inlineStr">
         <is>
           <t>1. Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek 
 2. Klik menu Lead Qualification 
@@ -39086,7 +38692,7 @@
 4. Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
-      <c r="H876" s="4" t="inlineStr">
+      <c r="H867" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login 
 2. Menampilkan dropdown submenu Lead Qualification 
@@ -39095,38 +38701,38 @@
         </is>
       </c>
     </row>
-    <row r="877" ht="42" customHeight="1">
-      <c r="A877" s="43" t="inlineStr">
-        <is>
-          <t>71.11</t>
-        </is>
-      </c>
-      <c r="B877" s="3" t="inlineStr">
+    <row r="868" ht="28" customHeight="1">
+      <c r="A868" s="43" t="inlineStr">
+        <is>
+          <t>69.11</t>
+        </is>
+      </c>
+      <c r="B868" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C877" s="3" t="inlineStr">
+      <c r="C868" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D877" s="4" t="inlineStr">
+      <c r="D868" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-assign prospek semua data</t>
         </is>
       </c>
-      <c r="E877" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F877" s="3" t="inlineStr">
+      <c r="E868" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F868" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G877" s="4" t="inlineStr">
+      <c r="G868" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Reassign semua data 
 2. Klik button Yes 
@@ -39137,7 +38743,7 @@
 7. Klik button Submit</t>
         </is>
       </c>
-      <c r="H877" s="4" t="inlineStr">
+      <c r="H868" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan popup konfirmasi 
 2. Menampilkan halaman pindah kelolaan 
@@ -39149,122 +38755,122 @@
         </is>
       </c>
     </row>
-    <row r="878" ht="28" customHeight="1">
-      <c r="A878" s="43" t="inlineStr">
-        <is>
-          <t>71.12</t>
-        </is>
-      </c>
-      <c r="B878" s="3" t="inlineStr">
+    <row r="869" ht="28" customHeight="1">
+      <c r="A869" s="43" t="inlineStr">
+        <is>
+          <t>69.12</t>
+        </is>
+      </c>
+      <c r="B869" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C878" s="3" t="inlineStr">
+      <c r="C869" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D878" s="4" t="inlineStr">
+      <c r="D869" s="4" t="inlineStr">
         <is>
           <t>Validasi semua data</t>
         </is>
       </c>
-      <c r="E878" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F878" s="3" t="inlineStr">
+      <c r="E869" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F869" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G878" s="4" t="inlineStr">
+      <c r="G869" s="4" t="inlineStr">
         <is>
           <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi semua prospek</t>
         </is>
       </c>
-      <c r="H878" s="4" t="inlineStr">
+      <c r="H869" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan data tabel yang berisi semua prospek</t>
         </is>
       </c>
     </row>
-    <row r="879" ht="28" customHeight="1">
-      <c r="A879" s="43" t="inlineStr">
-        <is>
-          <t>71.13</t>
-        </is>
-      </c>
-      <c r="B879" s="3" t="inlineStr">
+    <row r="870" ht="28" customHeight="1">
+      <c r="A870" s="43" t="inlineStr">
+        <is>
+          <t>69.13</t>
+        </is>
+      </c>
+      <c r="B870" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C879" s="3" t="inlineStr">
+      <c r="C870" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D879" s="4" t="inlineStr">
+      <c r="D870" s="4" t="inlineStr">
         <is>
           <t>Membatalkan Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E879" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F879" s="3" t="inlineStr">
+      <c r="E870" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F870" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G879" s="4" t="inlineStr">
+      <c r="G870" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
         </is>
       </c>
-      <c r="H879" s="4" t="inlineStr">
+      <c r="H870" s="4" t="inlineStr">
         <is>
           <t>1. Kembali ke halaman utama Re-assign Prospek</t>
         </is>
       </c>
     </row>
-    <row r="880" ht="28" customHeight="1">
-      <c r="A880" s="43" t="inlineStr">
-        <is>
-          <t>71.14</t>
-        </is>
-      </c>
-      <c r="B880" s="3" t="inlineStr">
+    <row r="871" ht="28" customHeight="1">
+      <c r="A871" s="43" t="inlineStr">
+        <is>
+          <t>69.14</t>
+        </is>
+      </c>
+      <c r="B871" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C880" s="3" t="inlineStr">
+      <c r="C871" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D880" s="4" t="inlineStr">
+      <c r="D871" s="4" t="inlineStr">
         <is>
           <t>Validasi semua data prospek yang di re-assign</t>
         </is>
       </c>
-      <c r="E880" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F880" s="3" t="inlineStr">
+      <c r="E871" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F871" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G880" s="4" t="inlineStr">
+      <c r="G871" s="4" t="inlineStr">
         <is>
           <t>1. Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek 
 2. Klik menu Lead Qualification 
@@ -39272,7 +38878,7 @@
 4. Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
-      <c r="H880" s="4" t="inlineStr">
+      <c r="H871" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login 
 2. Menampilkan dropdown submenu Lead Qualification 
@@ -39281,126 +38887,126 @@
         </is>
       </c>
     </row>
-    <row r="881" ht="14" customHeight="1">
-      <c r="A881" s="43" t="inlineStr">
-        <is>
-          <t>72.1</t>
-        </is>
-      </c>
-      <c r="B881" s="3" t="inlineStr">
+    <row r="872" ht="70" customHeight="1">
+      <c r="A872" s="43" t="inlineStr">
+        <is>
+          <t>70.1</t>
+        </is>
+      </c>
+      <c r="B872" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C881" s="3" t="inlineStr">
+      <c r="C872" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D881" s="4" t="inlineStr">
+      <c r="D872" s="4" t="inlineStr">
         <is>
           <t>Pagination</t>
         </is>
       </c>
-      <c r="E881" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F881" s="3" t="inlineStr">
+      <c r="E872" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F872" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G881" s="4" t="inlineStr">
+      <c r="G872" s="4" t="inlineStr">
         <is>
           <t>1. Klik pagination (10/halaman).
 2. Pilih berapa data yang ingin ditampilkan.</t>
         </is>
       </c>
-      <c r="H881" s="4" t="inlineStr">
+      <c r="H872" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengklik pagination.
 2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="882" ht="42" customHeight="1">
-      <c r="A882" s="43" t="inlineStr">
-        <is>
-          <t>72.2</t>
-        </is>
-      </c>
-      <c r="B882" s="3" t="inlineStr">
+    <row r="873" ht="42" customHeight="1">
+      <c r="A873" s="43" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="B873" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C882" s="3" t="inlineStr">
+      <c r="C873" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D882" s="4" t="inlineStr">
+      <c r="D873" s="4" t="inlineStr">
         <is>
           <t>Pindah Halaman</t>
         </is>
       </c>
-      <c r="E882" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F882" s="3" t="inlineStr">
+      <c r="E873" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F873" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G882" s="4" t="inlineStr">
+      <c r="G873" s="4" t="inlineStr">
         <is>
           <t>1. Input angka halaman di field pindah halaman.
 2. Klik Enter pada keyboard.</t>
         </is>
       </c>
-      <c r="H882" s="4" t="inlineStr">
+      <c r="H873" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput angka halaman.
 2. Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
-    <row r="883" ht="42" customHeight="1">
-      <c r="A883" s="43" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="B883" s="3" t="inlineStr">
+    <row r="874" ht="42" customHeight="1">
+      <c r="A874" s="43" t="inlineStr">
+        <is>
+          <t>70.3</t>
+        </is>
+      </c>
+      <c r="B874" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C883" s="3" t="inlineStr">
+      <c r="C874" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D883" s="4" t="inlineStr">
+      <c r="D874" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E883" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F883" s="3" t="inlineStr">
+      <c r="E874" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F874" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G883" s="4" t="inlineStr">
+      <c r="G874" s="4" t="inlineStr">
         <is>
           <t>1. Pilih prospek dengan klik checkbox yang ada di samping setiap data prospek 
 2. Klik button Reassign () data 
@@ -39409,7 +39015,7 @@
 5. Klik button Submit</t>
         </is>
       </c>
-      <c r="H883" s="4" t="inlineStr">
+      <c r="H874" s="4" t="inlineStr">
         <is>
           <t>1. Checkbox menjadi ceklis dan data berhasil di pilih 
 2. Menampilkan popup konfirmasi 
@@ -39419,258 +39025,258 @@
         </is>
       </c>
     </row>
-    <row r="884" ht="28" customHeight="1">
-      <c r="A884" s="43" t="inlineStr">
-        <is>
-          <t>72.4</t>
-        </is>
-      </c>
-      <c r="B884" s="3" t="inlineStr">
+    <row r="875" ht="70" customHeight="1">
+      <c r="A875" s="43" t="inlineStr">
+        <is>
+          <t>70.4</t>
+        </is>
+      </c>
+      <c r="B875" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C884" s="3" t="inlineStr">
+      <c r="C875" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D884" s="4" t="inlineStr">
+      <c r="D875" s="4" t="inlineStr">
         <is>
           <t>Pagination</t>
         </is>
       </c>
-      <c r="E884" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F884" s="3" t="inlineStr">
+      <c r="E875" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F875" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G884" s="4" t="inlineStr">
+      <c r="G875" s="4" t="inlineStr">
         <is>
           <t>1. Klik pagination (10/halaman).
 2. Pilih berapa data yang ingin ditampilkan.</t>
         </is>
       </c>
-      <c r="H884" s="4" t="inlineStr">
+      <c r="H875" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengklik pagination.
 2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="885" ht="42" customHeight="1">
-      <c r="A885" s="43" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
-      <c r="B885" s="3" t="inlineStr">
+    <row r="876" ht="28" customHeight="1">
+      <c r="A876" s="43" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
+      <c r="B876" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C885" s="3" t="inlineStr">
+      <c r="C876" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D885" s="4" t="inlineStr">
+      <c r="D876" s="4" t="inlineStr">
         <is>
           <t>Pindah Halaman</t>
         </is>
       </c>
-      <c r="E885" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F885" s="3" t="inlineStr">
+      <c r="E876" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F876" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G885" s="4" t="inlineStr">
+      <c r="G876" s="4" t="inlineStr">
         <is>
           <t>1. Input angka halaman di field pindah halaman.
 2. Klik Enter pada keyboard.</t>
         </is>
       </c>
-      <c r="H885" s="4" t="inlineStr">
+      <c r="H876" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput angka halaman.
 2. Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
-    <row r="886" ht="14" customHeight="1">
-      <c r="A886" s="43" t="inlineStr">
-        <is>
-          <t>72.6</t>
-        </is>
-      </c>
-      <c r="B886" s="3" t="inlineStr">
+    <row r="877" ht="42" customHeight="1">
+      <c r="A877" s="43" t="inlineStr">
+        <is>
+          <t>70.6</t>
+        </is>
+      </c>
+      <c r="B877" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C886" s="3" t="inlineStr">
+      <c r="C877" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D886" s="4" t="inlineStr">
+      <c r="D877" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Re-Assign Management</t>
         </is>
       </c>
-      <c r="E886" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F886" s="3" t="inlineStr">
+      <c r="E877" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F877" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G886" s="4" t="inlineStr">
+      <c r="G877" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Re-Assign &amp; Approval 
 2. Klik submenu Re-Assign Management</t>
         </is>
       </c>
-      <c r="H886" s="4" t="inlineStr">
+      <c r="H877" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list submenu Re-Assign &amp; Approval 
 2. Menampilkan halaman Re-Assign Management</t>
         </is>
       </c>
     </row>
-    <row r="887" ht="42" customHeight="1">
-      <c r="A887" s="43" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
-      <c r="B887" s="3" t="inlineStr">
+    <row r="878" ht="28" customHeight="1">
+      <c r="A878" s="43" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="B878" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C887" s="3" t="inlineStr">
+      <c r="C878" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D887" s="4" t="inlineStr">
+      <c r="D878" s="4" t="inlineStr">
         <is>
           <t>Mencari data prospek pada halaman Re-Assign Management</t>
         </is>
       </c>
-      <c r="E887" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F887" s="3" t="inlineStr">
+      <c r="E878" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F878" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G887" s="4" t="inlineStr">
+      <c r="G878" s="4" t="inlineStr">
         <is>
           <t>1. Input nama nasabah pada field search 
 2. Klik icon search atau klik Enter</t>
         </is>
       </c>
-      <c r="H887" s="4" t="inlineStr">
+      <c r="H878" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput nama nasabah
 2. Menampilkan data prospek Re-Assign Management sesuai dengan nama yang di cari</t>
         </is>
       </c>
     </row>
-    <row r="888" ht="42" customHeight="1">
-      <c r="A888" s="43" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
-      <c r="B888" s="3" t="inlineStr">
+    <row r="879" ht="28" customHeight="1">
+      <c r="A879" s="43" t="inlineStr">
+        <is>
+          <t>70.8</t>
+        </is>
+      </c>
+      <c r="B879" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C888" s="3" t="inlineStr">
+      <c r="C879" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D888" s="4" t="inlineStr">
+      <c r="D879" s="4" t="inlineStr">
         <is>
           <t>Mencari data prospek yang tidak ada pada halaman Re-Assign Management</t>
         </is>
       </c>
-      <c r="E888" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F888" s="3" t="inlineStr">
+      <c r="E879" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F879" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G888" s="4" t="inlineStr">
+      <c r="G879" s="4" t="inlineStr">
         <is>
           <t>1. Input nama nasabah yang datanya tidak ada 
 2. Klik icon search atau klik Enter</t>
         </is>
       </c>
-      <c r="H888" s="4" t="inlineStr">
+      <c r="H879" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput nama nasabah
 2. Menampilkan tabel kosong dengan keterangan no data</t>
         </is>
       </c>
     </row>
-    <row r="889" ht="28" customHeight="1">
-      <c r="A889" s="43" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
-      </c>
-      <c r="B889" s="3" t="inlineStr">
+    <row r="880" ht="28" customHeight="1">
+      <c r="A880" s="43" t="inlineStr">
+        <is>
+          <t>70.9</t>
+        </is>
+      </c>
+      <c r="B880" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C889" s="3" t="inlineStr">
+      <c r="C880" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D889" s="4" t="inlineStr">
+      <c r="D880" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E889" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F889" s="3" t="inlineStr">
+      <c r="E880" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F880" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G889" s="4" t="inlineStr">
+      <c r="G880" s="4" t="inlineStr">
         <is>
           <t>1. Pilih prospek dengan klik checkbox yang ada di samping setiap data prospek 
 2. Klik button Reassign () data 
@@ -39679,7 +39285,7 @@
 5. Klik button Submit</t>
         </is>
       </c>
-      <c r="H889" s="4" t="inlineStr">
+      <c r="H880" s="4" t="inlineStr">
         <is>
           <t>1. Checkbox menjadi ceklis dan data berhasil di pilih 
 2. Menampilkan popup konfirmasi 
@@ -39689,80 +39295,80 @@
         </is>
       </c>
     </row>
-    <row r="890" ht="42" customHeight="1">
-      <c r="A890" s="43" t="inlineStr">
-        <is>
-          <t>72.10</t>
-        </is>
-      </c>
-      <c r="B890" s="3" t="inlineStr">
+    <row r="881" ht="14" customHeight="1">
+      <c r="A881" s="43" t="inlineStr">
+        <is>
+          <t>70.10</t>
+        </is>
+      </c>
+      <c r="B881" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C890" s="3" t="inlineStr">
+      <c r="C881" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D890" s="4" t="inlineStr">
+      <c r="D881" s="4" t="inlineStr">
         <is>
           <t>Validasi jumlah data yang di pilih untuk reassign</t>
         </is>
       </c>
-      <c r="E890" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F890" s="3" t="inlineStr">
+      <c r="E881" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F881" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G890" s="4" t="inlineStr">
+      <c r="G881" s="4" t="inlineStr">
         <is>
           <t>1. cek jumlah data yang muncul pada button Reassign () data</t>
         </is>
       </c>
-      <c r="H890" s="4" t="inlineStr">
+      <c r="H881" s="4" t="inlineStr">
         <is>
           <t>1. Angka yang muncul pada button sesuai dengan jumlah data yang di pilih</t>
         </is>
       </c>
     </row>
-    <row r="891" ht="14" customHeight="1">
-      <c r="A891" s="43" t="inlineStr">
-        <is>
-          <t>72.11</t>
-        </is>
-      </c>
-      <c r="B891" s="3" t="inlineStr">
+    <row r="882" ht="42" customHeight="1">
+      <c r="A882" s="43" t="inlineStr">
+        <is>
+          <t>70.11</t>
+        </is>
+      </c>
+      <c r="B882" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C891" s="3" t="inlineStr">
+      <c r="C882" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D891" s="4" t="inlineStr">
+      <c r="D882" s="4" t="inlineStr">
         <is>
           <t>Validasi data prospek yang di re-assign ke sales</t>
         </is>
       </c>
-      <c r="E891" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F891" s="3" t="inlineStr">
+      <c r="E882" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F882" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G891" s="4" t="inlineStr">
+      <c r="G882" s="4" t="inlineStr">
         <is>
           <t>1. Login dengan akun sales yang sebelumnya sudah di pilih reassign management
 2. Klik menu Lead Qualification
@@ -39770,7 +39376,7 @@
 4. Cek data prospek yang sudah di reassign</t>
         </is>
       </c>
-      <c r="H891" s="4" t="inlineStr">
+      <c r="H882" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login akun sales
 2. Menampilkan dropdown submenu Lead Qualification
@@ -39779,25 +39385,407 @@
         </is>
       </c>
     </row>
+    <row r="883" ht="42" customHeight="1">
+      <c r="A883" s="43" t="inlineStr">
+        <is>
+          <t>70.12</t>
+        </is>
+      </c>
+      <c r="B883" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C883" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D883" s="4" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="E883" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F883" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G883" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik pagination (10/halaman).
+2. Pilih berapa data yang ingin ditampilkan.</t>
+        </is>
+      </c>
+      <c r="H883" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengklik pagination.
+2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="884" ht="28" customHeight="1">
+      <c r="A884" s="43" t="inlineStr">
+        <is>
+          <t>70.13</t>
+        </is>
+      </c>
+      <c r="B884" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C884" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D884" s="4" t="inlineStr">
+        <is>
+          <t>Pindah Halaman</t>
+        </is>
+      </c>
+      <c r="E884" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F884" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G884" s="4" t="inlineStr">
+        <is>
+          <t>1. Input angka halaman di field pindah halaman.
+2. Klik Enter pada keyboard.</t>
+        </is>
+      </c>
+      <c r="H884" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menginput angka halaman.
+2. Berhasil berpindah ke halaman yang dituju.</t>
+        </is>
+      </c>
+    </row>
+    <row r="885" ht="42" customHeight="1">
+      <c r="A885" s="43" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="B885" s="3" t="inlineStr">
+        <is>
+          <t>Export data management</t>
+        </is>
+      </c>
+      <c r="C885" s="3" t="inlineStr">
+        <is>
+          <t>Riwayat export saya</t>
+        </is>
+      </c>
+      <c r="D885" s="4" t="inlineStr">
+        <is>
+          <t>Membuka menu riwayat export saya</t>
+        </is>
+      </c>
+      <c r="E885" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F885" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G885" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu exported data management, klik submenu riwayat export saya</t>
+        </is>
+      </c>
+      <c r="H885" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan halaman riwayat export saya</t>
+        </is>
+      </c>
+    </row>
+    <row r="886" ht="14" customHeight="1">
+      <c r="A886" s="43" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="B886" s="3" t="inlineStr">
+        <is>
+          <t>Export data management</t>
+        </is>
+      </c>
+      <c r="C886" s="3" t="inlineStr">
+        <is>
+          <t>Riwayat export saya</t>
+        </is>
+      </c>
+      <c r="D886" s="4" t="inlineStr">
+        <is>
+          <t>Validasi card disetujui dengan data table</t>
+        </is>
+      </c>
+      <c r="E886" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F886" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G886" s="4" t="inlineStr">
+        <is>
+          <t>1. Melakukan filter data status approval dengan memilih status “Approved”</t>
+        </is>
+      </c>
+      <c r="H886" s="4" t="inlineStr">
+        <is>
+          <t>1. Jumlah data pada card dan table sesuai</t>
+        </is>
+      </c>
+    </row>
+    <row r="887" ht="42" customHeight="1">
+      <c r="A887" s="43" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="B887" s="3" t="inlineStr">
+        <is>
+          <t>Export data management</t>
+        </is>
+      </c>
+      <c r="C887" s="3" t="inlineStr">
+        <is>
+          <t>Riwayat export saya</t>
+        </is>
+      </c>
+      <c r="D887" s="4" t="inlineStr">
+        <is>
+          <t>Validasi card ditolak dengan data table</t>
+        </is>
+      </c>
+      <c r="E887" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F887" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G887" s="4" t="inlineStr">
+        <is>
+          <t>1. Melakukan filter data status approval dengan memilih status “Rejected”</t>
+        </is>
+      </c>
+      <c r="H887" s="4" t="inlineStr">
+        <is>
+          <t>1. Jumlah data pada card dan table sesuai</t>
+        </is>
+      </c>
+    </row>
+    <row r="888" ht="42" customHeight="1">
+      <c r="A888" s="43" t="inlineStr">
+        <is>
+          <t>71.4</t>
+        </is>
+      </c>
+      <c r="B888" s="3" t="inlineStr">
+        <is>
+          <t>Export data management</t>
+        </is>
+      </c>
+      <c r="C888" s="3" t="inlineStr">
+        <is>
+          <t>Riwayat export saya</t>
+        </is>
+      </c>
+      <c r="D888" s="4" t="inlineStr">
+        <is>
+          <t>Validasi card kadaluwarsa dengan data table</t>
+        </is>
+      </c>
+      <c r="E888" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F888" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G888" s="4" t="inlineStr">
+        <is>
+          <t>1. Melakukan filter data status approval dengan memilih status “Expired”</t>
+        </is>
+      </c>
+      <c r="H888" s="4" t="inlineStr">
+        <is>
+          <t>1. Jumlah data pada card dan table sesuai</t>
+        </is>
+      </c>
+    </row>
+    <row r="889" ht="28" customHeight="1">
+      <c r="A889" s="43" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="B889" s="3" t="inlineStr">
+        <is>
+          <t>Export data management</t>
+        </is>
+      </c>
+      <c r="C889" s="3" t="inlineStr">
+        <is>
+          <t>Riwayat export saya</t>
+        </is>
+      </c>
+      <c r="D889" s="4" t="inlineStr">
+        <is>
+          <t>Mengunduh data yang sudah di approve</t>
+        </is>
+      </c>
+      <c r="E889" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F889" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G889" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button download</t>
+        </is>
+      </c>
+      <c r="H889" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengunduh data</t>
+        </is>
+      </c>
+    </row>
+    <row r="890" ht="42" customHeight="1">
+      <c r="A890" s="43" t="inlineStr">
+        <is>
+          <t>71.6</t>
+        </is>
+      </c>
+      <c r="B890" s="3" t="inlineStr">
+        <is>
+          <t>Export data management</t>
+        </is>
+      </c>
+      <c r="C890" s="3" t="inlineStr">
+        <is>
+          <t>Riwayat export saya</t>
+        </is>
+      </c>
+      <c r="D890" s="4" t="inlineStr">
+        <is>
+          <t>Membuka dokumen hasil download</t>
+        </is>
+      </c>
+      <c r="E890" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F890" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G890" s="4" t="inlineStr">
+        <is>
+          <t>1. Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
+        </is>
+      </c>
+      <c r="H890" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka file hasil download</t>
+        </is>
+      </c>
+    </row>
+    <row r="891" ht="14" customHeight="1">
+      <c r="A891" s="43" t="inlineStr">
+        <is>
+          <t>72.1</t>
+        </is>
+      </c>
+      <c r="B891" s="3" t="inlineStr">
+        <is>
+          <t>Export data management</t>
+        </is>
+      </c>
+      <c r="C891" s="3" t="inlineStr">
+        <is>
+          <t>Management export</t>
+        </is>
+      </c>
+      <c r="D891" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data</t>
+        </is>
+      </c>
+      <c r="E891" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F891" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G891" s="4" t="inlineStr">
+        <is>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+        </is>
+      </c>
+      <c r="H891" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+        </is>
+      </c>
+    </row>
     <row r="892" ht="42" customHeight="1">
       <c r="A892" s="43" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="B892" s="3" t="inlineStr">
         <is>
-          <t>Re-Assign dan Approval</t>
+          <t>Export data management</t>
         </is>
       </c>
       <c r="C892" s="3" t="inlineStr">
         <is>
-          <t>Re-Assign Management</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D892" s="4" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E892" s="3" t="inlineStr">
@@ -39807,41 +39795,39 @@
       </c>
       <c r="F892" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G892" s="4" t="inlineStr">
         <is>
-          <t>1. Klik pagination (10/halaman).
-2. Pilih berapa data yang ingin ditampilkan.</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
         </is>
       </c>
       <c r="H892" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengklik pagination.
-2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="893" ht="42" customHeight="1">
       <c r="A893" s="43" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="B893" s="3" t="inlineStr">
         <is>
-          <t>Re-Assign dan Approval</t>
+          <t>Export data management</t>
         </is>
       </c>
       <c r="C893" s="3" t="inlineStr">
         <is>
-          <t>Re-Assign Management</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D893" s="4" t="inlineStr">
         <is>
-          <t>Pindah Halaman</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E893" s="3" t="inlineStr">
@@ -39851,26 +39837,24 @@
       </c>
       <c r="F893" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G893" s="4" t="inlineStr">
         <is>
-          <t>1. Input angka halaman di field pindah halaman.
-2. Klik Enter pada keyboard.</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H893" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menginput angka halaman.
-2. Berhasil berpindah ke halaman yang dituju.</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="894" ht="28" customHeight="1">
       <c r="A894" s="43" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="B894" s="3" t="inlineStr">
@@ -39880,17 +39864,17 @@
       </c>
       <c r="C894" s="3" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D894" s="4" t="inlineStr">
         <is>
-          <t>Membuka menu riwayat export saya</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E894" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F894" s="3" t="inlineStr">
@@ -39900,19 +39884,19 @@
       </c>
       <c r="G894" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu exported data management, klik submenu riwayat export saya</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H894" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan halaman riwayat export saya</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="895" ht="42" customHeight="1">
       <c r="A895" s="43" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="B895" s="3" t="inlineStr">
@@ -39922,12 +39906,12 @@
       </c>
       <c r="C895" s="3" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D895" s="4" t="inlineStr">
         <is>
-          <t>Validasi card disetujui dengan data table</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E895" s="3" t="inlineStr">
@@ -39937,24 +39921,24 @@
       </c>
       <c r="F895" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G895" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Approved”</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H895" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="896" ht="14" customHeight="1">
       <c r="A896" s="43" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="B896" s="3" t="inlineStr">
@@ -39964,12 +39948,12 @@
       </c>
       <c r="C896" s="3" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D896" s="4" t="inlineStr">
         <is>
-          <t>Validasi card ditolak dengan data table</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E896" s="3" t="inlineStr">
@@ -39984,19 +39968,19 @@
       </c>
       <c r="G896" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Rejected”</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H896" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="897" ht="42" customHeight="1">
       <c r="A897" s="43" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="B897" s="3" t="inlineStr">
@@ -40006,39 +39990,39 @@
       </c>
       <c r="C897" s="3" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D897" s="4" t="inlineStr">
         <is>
-          <t>Validasi card kadaluwarsa dengan data table</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E897" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F897" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G897" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Expired”</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H897" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="898" ht="42" customHeight="1">
       <c r="A898" s="43" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="B898" s="3" t="inlineStr">
@@ -40048,12 +40032,12 @@
       </c>
       <c r="C898" s="3" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D898" s="4" t="inlineStr">
         <is>
-          <t>Mengunduh data yang sudah di approve</t>
+          <t>Membuka menu Management Export</t>
         </is>
       </c>
       <c r="E898" s="3" t="inlineStr">
@@ -40068,19 +40052,19 @@
       </c>
       <c r="G898" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button download</t>
+          <t>1. Klik menu exported data management, klik submenu management export</t>
         </is>
       </c>
       <c r="H898" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengunduh data</t>
+          <t>1. Menampilkan halaman management export</t>
         </is>
       </c>
     </row>
     <row r="899" ht="28" customHeight="1">
       <c r="A899" s="43" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="B899" s="3" t="inlineStr">
@@ -40090,12 +40074,12 @@
       </c>
       <c r="C899" s="3" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D899" s="4" t="inlineStr">
         <is>
-          <t>Membuka dokumen hasil download</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E899" s="3" t="inlineStr">
@@ -40105,24 +40089,24 @@
       </c>
       <c r="F899" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G899" s="4" t="inlineStr">
         <is>
-          <t>1. Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H899" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka file hasil download</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="900" ht="42" customHeight="1">
       <c r="A900" s="43" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>72.10</t>
         </is>
       </c>
       <c r="B900" s="3" t="inlineStr">
@@ -40137,7 +40121,7 @@
       </c>
       <c r="D900" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E900" s="3" t="inlineStr">
@@ -40147,24 +40131,24 @@
       </c>
       <c r="F900" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G900" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H900" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="901" ht="28" customHeight="1">
       <c r="A901" s="43" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.11</t>
         </is>
       </c>
       <c r="B901" s="3" t="inlineStr">
@@ -40179,12 +40163,12 @@
       </c>
       <c r="D901" s="4" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E901" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F901" s="3" t="inlineStr">
@@ -40194,19 +40178,19 @@
       </c>
       <c r="G901" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H901" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="902" ht="28" customHeight="1">
       <c r="A902" s="43" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="B902" s="3" t="inlineStr">
@@ -40221,7 +40205,7 @@
       </c>
       <c r="D902" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E902" s="3" t="inlineStr">
@@ -40236,19 +40220,19 @@
       </c>
       <c r="G902" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
         </is>
       </c>
       <c r="H902" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="903" ht="28" customHeight="1">
       <c r="A903" s="43" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>72.13</t>
         </is>
       </c>
       <c r="B903" s="3" t="inlineStr">
@@ -40263,34 +40247,34 @@
       </c>
       <c r="D903" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Validasi card data file aktif dengan data table</t>
         </is>
       </c>
       <c r="E903" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F903" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G903" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
         </is>
       </c>
       <c r="H903" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="904" ht="28" customHeight="1">
       <c r="A904" s="43" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>72.14</t>
         </is>
       </c>
       <c r="B904" s="3" t="inlineStr">
@@ -40305,7 +40289,7 @@
       </c>
       <c r="D904" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Validasi card file kadaluwarsa dengan data table</t>
         </is>
       </c>
       <c r="E904" s="3" t="inlineStr">
@@ -40320,19 +40304,19 @@
       </c>
       <c r="G904" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
         </is>
       </c>
       <c r="H904" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="905" ht="28" customHeight="1">
       <c r="A905" s="43" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>72.15</t>
         </is>
       </c>
       <c r="B905" s="3" t="inlineStr">
@@ -40347,7 +40331,7 @@
       </c>
       <c r="D905" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Validasi card reject dengan data table</t>
         </is>
       </c>
       <c r="E905" s="3" t="inlineStr">
@@ -40362,19 +40346,19 @@
       </c>
       <c r="G905" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
         </is>
       </c>
       <c r="H905" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="906" ht="42" customHeight="1">
       <c r="A906" s="43" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="B906" s="3" t="inlineStr">
@@ -40384,39 +40368,39 @@
       </c>
       <c r="C906" s="3" t="inlineStr">
         <is>
-          <t>Management export</t>
+          <t>Persetujuan export</t>
         </is>
       </c>
       <c r="D906" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Lakukan login menggunakan user monitoring</t>
         </is>
       </c>
       <c r="E906" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F906" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G906" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Login menggunakan user monitoring</t>
         </is>
       </c>
       <c r="H906" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Berhasil melakukan login</t>
         </is>
       </c>
     </row>
     <row r="907" ht="42" customHeight="1">
       <c r="A907" s="43" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="B907" s="3" t="inlineStr">
@@ -40426,12 +40410,12 @@
       </c>
       <c r="C907" s="3" t="inlineStr">
         <is>
-          <t>Management export</t>
+          <t>Persetujuan export</t>
         </is>
       </c>
       <c r="D907" s="4" t="inlineStr">
         <is>
-          <t>Membuka menu Management Export</t>
+          <t>Membuka menu Persetujuan Export</t>
         </is>
       </c>
       <c r="E907" s="3" t="inlineStr">
@@ -40446,19 +40430,19 @@
       </c>
       <c r="G907" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu exported data management, klik submenu management export</t>
+          <t>1. Klik menu exported data management, klik submenu persetujuan export</t>
         </is>
       </c>
       <c r="H907" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan halaman management export</t>
+          <t>1. Menampilkan halaman persetujuan export</t>
         </is>
       </c>
     </row>
     <row r="908" ht="28" customHeight="1">
       <c r="A908" s="43" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="B908" s="3" t="inlineStr">
@@ -40468,12 +40452,12 @@
       </c>
       <c r="C908" s="3" t="inlineStr">
         <is>
-          <t>Management export</t>
+          <t>Persetujuan export</t>
         </is>
       </c>
       <c r="D908" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Melakukan approval data pengajuan export</t>
         </is>
       </c>
       <c r="E908" s="3" t="inlineStr">
@@ -40483,395 +40467,17 @@
       </c>
       <c r="F908" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G908" s="4" t="inlineStr">
-        <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
-        </is>
-      </c>
-      <c r="H908" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
-        </is>
-      </c>
-    </row>
-    <row r="909" ht="14" customHeight="1">
-      <c r="A909" s="43" t="inlineStr">
-        <is>
-          <t>74.10</t>
-        </is>
-      </c>
-      <c r="B909" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C909" s="3" t="inlineStr">
-        <is>
-          <t>Management export</t>
-        </is>
-      </c>
-      <c r="D909" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data pada kolom pencarian</t>
-        </is>
-      </c>
-      <c r="E909" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F909" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G909" s="4" t="inlineStr">
-        <is>
-          <t>1. Input data pada kolom pencarian</t>
-        </is>
-      </c>
-      <c r="H909" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
-        </is>
-      </c>
-    </row>
-    <row r="910" ht="28" customHeight="1">
-      <c r="A910" s="43" t="inlineStr">
-        <is>
-          <t>74.11</t>
-        </is>
-      </c>
-      <c r="B910" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C910" s="3" t="inlineStr">
-        <is>
-          <t>Management export</t>
-        </is>
-      </c>
-      <c r="D910" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data kata kunci salah</t>
-        </is>
-      </c>
-      <c r="E910" s="3" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F910" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G910" s="4" t="inlineStr">
-        <is>
-          <t>1. Input data yang belum terdaftar</t>
-        </is>
-      </c>
-      <c r="H910" s="4" t="inlineStr">
-        <is>
-          <t>1. Data tidak ditemukan</t>
-        </is>
-      </c>
-    </row>
-    <row r="911" ht="28" customHeight="1">
-      <c r="A911" s="43" t="inlineStr">
-        <is>
-          <t>74.12</t>
-        </is>
-      </c>
-      <c r="B911" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C911" s="3" t="inlineStr">
-        <is>
-          <t>Management export</t>
-        </is>
-      </c>
-      <c r="D911" s="4" t="inlineStr">
-        <is>
-          <t>Validasi card menunggu approval dengan data table</t>
-        </is>
-      </c>
-      <c r="E911" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F911" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G911" s="4" t="inlineStr">
-        <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
-        </is>
-      </c>
-      <c r="H911" s="4" t="inlineStr">
-        <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
-        </is>
-      </c>
-    </row>
-    <row r="912" ht="28" customHeight="1">
-      <c r="A912" s="43" t="inlineStr">
-        <is>
-          <t>74.13</t>
-        </is>
-      </c>
-      <c r="B912" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C912" s="3" t="inlineStr">
-        <is>
-          <t>Management export</t>
-        </is>
-      </c>
-      <c r="D912" s="4" t="inlineStr">
-        <is>
-          <t>Validasi card data file aktif dengan data table</t>
-        </is>
-      </c>
-      <c r="E912" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F912" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G912" s="4" t="inlineStr">
-        <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
-        </is>
-      </c>
-      <c r="H912" s="4" t="inlineStr">
-        <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
-        </is>
-      </c>
-    </row>
-    <row r="913" ht="28" customHeight="1">
-      <c r="A913" s="43" t="inlineStr">
-        <is>
-          <t>74.14</t>
-        </is>
-      </c>
-      <c r="B913" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C913" s="3" t="inlineStr">
-        <is>
-          <t>Management export</t>
-        </is>
-      </c>
-      <c r="D913" s="4" t="inlineStr">
-        <is>
-          <t>Validasi card file kadaluwarsa dengan data table</t>
-        </is>
-      </c>
-      <c r="E913" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F913" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G913" s="4" t="inlineStr">
-        <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
-        </is>
-      </c>
-      <c r="H913" s="4" t="inlineStr">
-        <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
-        </is>
-      </c>
-    </row>
-    <row r="914" ht="28" customHeight="1">
-      <c r="A914" s="43" t="inlineStr">
-        <is>
-          <t>74.15</t>
-        </is>
-      </c>
-      <c r="B914" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C914" s="3" t="inlineStr">
-        <is>
-          <t>Management export</t>
-        </is>
-      </c>
-      <c r="D914" s="4" t="inlineStr">
-        <is>
-          <t>Validasi card reject dengan data table</t>
-        </is>
-      </c>
-      <c r="E914" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F914" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G914" s="4" t="inlineStr">
-        <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
-        </is>
-      </c>
-      <c r="H914" s="4" t="inlineStr">
-        <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
-        </is>
-      </c>
-    </row>
-    <row r="915" ht="14" customHeight="1">
-      <c r="A915" s="43" t="inlineStr">
-        <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="B915" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C915" s="3" t="inlineStr">
-        <is>
-          <t>Persetujuan export</t>
-        </is>
-      </c>
-      <c r="D915" s="4" t="inlineStr">
-        <is>
-          <t>Lakukan login menggunakan user monitoring</t>
-        </is>
-      </c>
-      <c r="E915" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F915" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G915" s="4" t="inlineStr">
-        <is>
-          <t>1. Login menggunakan user monitoring</t>
-        </is>
-      </c>
-      <c r="H915" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil melakukan login</t>
-        </is>
-      </c>
-    </row>
-    <row r="916" ht="28" customHeight="1">
-      <c r="A916" s="43" t="inlineStr">
-        <is>
-          <t>75.2</t>
-        </is>
-      </c>
-      <c r="B916" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C916" s="3" t="inlineStr">
-        <is>
-          <t>Persetujuan export</t>
-        </is>
-      </c>
-      <c r="D916" s="4" t="inlineStr">
-        <is>
-          <t>Membuka menu Persetujuan Export</t>
-        </is>
-      </c>
-      <c r="E916" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F916" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G916" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu exported data management, klik submenu persetujuan export</t>
-        </is>
-      </c>
-      <c r="H916" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan halaman persetujuan export</t>
-        </is>
-      </c>
-    </row>
-    <row r="917" ht="14" customHeight="1">
-      <c r="A917" s="43" t="inlineStr">
-        <is>
-          <t>75.3</t>
-        </is>
-      </c>
-      <c r="B917" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C917" s="3" t="inlineStr">
-        <is>
-          <t>Persetujuan export</t>
-        </is>
-      </c>
-      <c r="D917" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan approval data pengajuan export</t>
-        </is>
-      </c>
-      <c r="E917" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F917" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G917" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon titik tiga pada data pengajuan.
 2. Klik menu Setuju.
 3. Klik button YA pada popup konfirmasi.</t>
         </is>
       </c>
-      <c r="H917" s="4" t="inlineStr">
+      <c r="H908" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan menu opsi.
 2. Berhasil menampilkan popup konfirmasi.
@@ -40879,48 +40485,57 @@
         </is>
       </c>
     </row>
-    <row r="918" ht="28" customHeight="1">
-      <c r="A918" s="43" t="inlineStr">
-        <is>
-          <t>75.4</t>
-        </is>
-      </c>
-      <c r="B918" s="3" t="inlineStr">
+    <row r="909" ht="14" customHeight="1">
+      <c r="A909" s="43" t="inlineStr">
+        <is>
+          <t>73.4</t>
+        </is>
+      </c>
+      <c r="B909" s="3" t="inlineStr">
         <is>
           <t>Export data management</t>
         </is>
       </c>
-      <c r="C918" s="3" t="inlineStr">
+      <c r="C909" s="3" t="inlineStr">
         <is>
           <t>Persetujuan export</t>
         </is>
       </c>
-      <c r="D918" s="4" t="inlineStr">
+      <c r="D909" s="4" t="inlineStr">
         <is>
           <t>Melakukan reject data pengajuan export</t>
         </is>
       </c>
-      <c r="E918" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F918" s="3" t="inlineStr">
+      <c r="E909" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F909" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G918" s="4" t="inlineStr">
+      <c r="G909" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon (titik tiga) klik tolak, input alasan, klik submit</t>
         </is>
       </c>
-      <c r="H918" s="4" t="inlineStr">
+      <c r="H909" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil melakukan reject data</t>
         </is>
       </c>
     </row>
+    <row r="910" ht="28" customHeight="1"/>
+    <row r="911" ht="28" customHeight="1"/>
+    <row r="912" ht="28" customHeight="1"/>
+    <row r="913" ht="28" customHeight="1"/>
+    <row r="914" ht="28" customHeight="1"/>
+    <row r="915" ht="14" customHeight="1"/>
+    <row r="916" ht="28" customHeight="1"/>
+    <row r="917" ht="14" customHeight="1"/>
+    <row r="918" ht="28" customHeight="1"/>
     <row r="919" ht="28" customHeight="1"/>
     <row r="920" ht="42" customHeight="1"/>
     <row r="921" ht="42" customHeight="1"/>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z909"/>
+  <dimension ref="A1:Z910"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="12.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -37073,509 +37073,553 @@
       </c>
       <c r="D831" s="4" t="inlineStr">
         <is>
+          <t>Menampilkan data tab Non PKS dan PKS</t>
+        </is>
+      </c>
+      <c r="E831" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F831" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G831" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Non PKS.
+2. Klik tab PKS.</t>
+        </is>
+      </c>
+      <c r="H831" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data pada tab Non PKS.
+2. Berhasil menampilkan data pada tab PKS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="832" ht="28" customHeight="1">
+      <c r="A832" s="43" t="inlineStr">
+        <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="B832" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C832" s="3" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D832" s="4" t="inlineStr">
+        <is>
           <t>Melakukan filter data Personal Funnel</t>
         </is>
       </c>
-      <c r="E831" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F831" s="3" t="inlineStr">
+      <c r="E832" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F832" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G831" s="4" t="inlineStr">
+      <c r="G832" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi semua field filter mandatory.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H831" s="4" t="inlineStr">
+      <c r="H832" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field filter mandatory.
 2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="832" ht="28" customHeight="1">
-      <c r="A832" s="43" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
-      <c r="B832" s="3" t="inlineStr">
+    <row r="833" ht="14" customHeight="1">
+      <c r="A833" s="43" t="inlineStr">
+        <is>
+          <t>65.4</t>
+        </is>
+      </c>
+      <c r="B833" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C832" s="3" t="inlineStr">
+      <c r="C833" s="3" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D832" s="4" t="inlineStr">
+      <c r="D833" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E832" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F832" s="3" t="inlineStr">
+      <c r="E833" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F833" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G832" s="4" t="inlineStr">
+      <c r="G833" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H832" s="4" t="inlineStr">
+      <c r="H833" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
-    <row r="833" ht="14" customHeight="1">
-      <c r="A833" s="43" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
-      </c>
-      <c r="B833" s="3" t="inlineStr">
+    <row r="834" ht="14" customHeight="1">
+      <c r="A834" s="43" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="B834" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C833" s="3" t="inlineStr">
+      <c r="C834" s="3" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D833" s="4" t="inlineStr">
+      <c r="D834" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data Personal Funnel</t>
         </is>
       </c>
-      <c r="E833" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F833" s="3" t="inlineStr">
+      <c r="E834" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F834" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G833" s="4" t="inlineStr">
+      <c r="G834" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Export.
 2. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H833" s="4" t="inlineStr">
+      <c r="H834" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan panel Download Export.
 2. Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
-    <row r="834" ht="14" customHeight="1">
-      <c r="A834" s="43" t="inlineStr">
+    <row r="835" ht="14" customHeight="1">
+      <c r="A835" s="43" t="inlineStr">
         <is>
           <t>66.1</t>
         </is>
       </c>
-      <c r="B834" s="3" t="inlineStr">
+      <c r="B835" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C834" s="3" t="inlineStr">
+      <c r="C835" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D834" s="4" t="inlineStr">
+      <c r="D835" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Rekap Funnel</t>
         </is>
       </c>
-      <c r="E834" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F834" s="3" t="inlineStr">
+      <c r="E835" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F835" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G834" s="4" t="inlineStr">
+      <c r="G835" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Lending.
 2. Klik sub menu Rekap Funnel.</t>
         </is>
       </c>
-      <c r="H834" s="4" t="inlineStr">
+      <c r="H835" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Lending.
 2. Berhasil menampilkan halaman Rekap Funnel.</t>
         </is>
       </c>
     </row>
-    <row r="835" ht="14" customHeight="1">
-      <c r="A835" s="43" t="inlineStr">
+    <row r="836" ht="42" customHeight="1">
+      <c r="A836" s="43" t="inlineStr">
         <is>
           <t>66.2</t>
         </is>
       </c>
-      <c r="B835" s="3" t="inlineStr">
+      <c r="B836" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C835" s="3" t="inlineStr">
+      <c r="C836" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D835" s="4" t="inlineStr">
+      <c r="D836" s="4" t="inlineStr">
         <is>
           <t>Menampilkan data Rekap Funnel</t>
         </is>
       </c>
-      <c r="E835" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F835" s="3" t="inlineStr">
+      <c r="E836" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F836" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G835" s="4" t="inlineStr">
+      <c r="G836" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun).
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H835" s="4" t="inlineStr">
+      <c r="H836" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field filter mandatory.
 2. Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
         </is>
       </c>
     </row>
-    <row r="836" ht="42" customHeight="1">
-      <c r="A836" s="43" t="inlineStr">
+    <row r="837" ht="28" customHeight="1">
+      <c r="A837" s="43" t="inlineStr">
         <is>
           <t>66.3</t>
         </is>
       </c>
-      <c r="B836" s="3" t="inlineStr">
+      <c r="B837" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C836" s="3" t="inlineStr">
+      <c r="C837" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D836" s="4" t="inlineStr">
+      <c r="D837" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Rekap Funnel</t>
         </is>
       </c>
-      <c r="E836" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F836" s="3" t="inlineStr">
+      <c r="E837" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F837" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G836" s="4" t="inlineStr">
+      <c r="G837" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H836" s="4" t="inlineStr">
+      <c r="H837" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi kriteria filter.
 2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="837" ht="28" customHeight="1">
-      <c r="A837" s="43" t="inlineStr">
+    <row r="838" ht="28" customHeight="1">
+      <c r="A838" s="43" t="inlineStr">
         <is>
           <t>66.4</t>
         </is>
       </c>
-      <c r="B837" s="3" t="inlineStr">
+      <c r="B838" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C837" s="3" t="inlineStr">
+      <c r="C838" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D837" s="4" t="inlineStr">
+      <c r="D838" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E837" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F837" s="3" t="inlineStr">
+      <c r="E838" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F838" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G837" s="4" t="inlineStr">
+      <c r="G838" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H837" s="4" t="inlineStr">
+      <c r="H838" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
-    <row r="838" ht="28" customHeight="1">
-      <c r="A838" s="43" t="inlineStr">
-        <is>
-          <t>66.5</t>
-        </is>
-      </c>
-      <c r="B838" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C838" s="3" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D838" s="4" t="inlineStr">
-        <is>
-          <t>Mengunduh data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E838" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F838" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G838" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Download Excel.</t>
-        </is>
-      </c>
-      <c r="H838" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mendownload file Excel data Rekap Funnel.</t>
-        </is>
-      </c>
-    </row>
     <row r="839" ht="70" customHeight="1">
       <c r="A839" s="43" t="inlineStr">
         <is>
+          <t>66.5</t>
+        </is>
+      </c>
+      <c r="B839" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C839" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D839" s="4" t="inlineStr">
+        <is>
+          <t>Mengunduh data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E839" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F839" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G839" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Download Excel.</t>
+        </is>
+      </c>
+      <c r="H839" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mendownload file Excel data Rekap Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="840" ht="28" customHeight="1">
+      <c r="A840" s="43" t="inlineStr">
+        <is>
           <t>67.1</t>
         </is>
       </c>
-      <c r="B839" s="3" t="inlineStr">
+      <c r="B840" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C839" s="3" t="inlineStr">
+      <c r="C840" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D839" s="4" t="inlineStr">
+      <c r="D840" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Pengaturan Funnel Lending</t>
         </is>
       </c>
-      <c r="E839" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F839" s="3" t="inlineStr">
+      <c r="E840" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F840" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G839" s="4" t="inlineStr">
+      <c r="G840" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Lending.
 2. Klik sub menu Pengaturan Funnel.</t>
         </is>
       </c>
-      <c r="H839" s="4" t="inlineStr">
+      <c r="H840" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Lending.
 2. Berhasil menampilkan halaman Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="840" ht="28" customHeight="1">
-      <c r="A840" s="43" t="inlineStr">
+    <row r="841" ht="84" customHeight="1">
+      <c r="A841" s="43" t="inlineStr">
         <is>
           <t>67.2</t>
         </is>
       </c>
-      <c r="B840" s="3" t="inlineStr">
+      <c r="B841" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C840" s="3" t="inlineStr">
+      <c r="C841" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D840" s="4" t="inlineStr">
+      <c r="D841" s="4" t="inlineStr">
         <is>
           <t>Mengubah data Pengaturan Funnel Lending</t>
         </is>
       </c>
-      <c r="E840" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F840" s="3" t="inlineStr">
+      <c r="E841" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F841" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G840" s="4" t="inlineStr">
+      <c r="G841" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H840" s="4" t="inlineStr">
+      <c r="H841" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field Performance Percentage.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="841" ht="84" customHeight="1">
-      <c r="A841" s="43" t="inlineStr">
+    <row r="842" ht="28" customHeight="1">
+      <c r="A842" s="43" t="inlineStr">
         <is>
           <t>67.3</t>
         </is>
       </c>
-      <c r="B841" s="3" t="inlineStr">
+      <c r="B842" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C841" s="3" t="inlineStr">
+      <c r="C842" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D841" s="4" t="inlineStr">
+      <c r="D842" s="4" t="inlineStr">
         <is>
           <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E841" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F841" s="3" t="inlineStr">
+      <c r="E842" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F842" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G841" s="4" t="inlineStr">
+      <c r="G842" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field mandatory Performance Percentage.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H841" s="4" t="inlineStr">
+      <c r="H842" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field Performance Percentage.
 2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
-    <row r="842" ht="28" customHeight="1">
-      <c r="A842" s="43" t="inlineStr">
+    <row r="843" ht="28" customHeight="1">
+      <c r="A843" s="43" t="inlineStr">
         <is>
           <t>67.4</t>
         </is>
       </c>
-      <c r="B842" s="3" t="inlineStr">
+      <c r="B843" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C842" s="3" t="inlineStr">
+      <c r="C843" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D842" s="4" t="inlineStr">
+      <c r="D843" s="4" t="inlineStr">
         <is>
           <t>Menambahkan Kondisi pada Indikator Performa</t>
         </is>
       </c>
-      <c r="E842" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F842" s="3" t="inlineStr">
+      <c r="E843" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F843" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G842" s="4" t="inlineStr">
+      <c r="G843" s="4" t="inlineStr">
         <is>
           <t>1. Klik button + Tambah Kondisi pada bagian Indikator Performa.
 2. Mengisi semua field mandatory pada kondisi baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H842" s="4" t="inlineStr">
+      <c r="H843" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan form kondisi baru pada Indikator Performa.
 2. Berhasil mengisi field mandatory kondisi.
@@ -37583,89 +37627,89 @@
         </is>
       </c>
     </row>
-    <row r="843" ht="28" customHeight="1">
-      <c r="A843" s="43" t="inlineStr">
+    <row r="844" ht="28" customHeight="1">
+      <c r="A844" s="43" t="inlineStr">
         <is>
           <t>67.5</t>
         </is>
       </c>
-      <c r="B843" s="3" t="inlineStr">
+      <c r="B844" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C843" s="3" t="inlineStr">
+      <c r="C844" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D843" s="4" t="inlineStr">
+      <c r="D844" s="4" t="inlineStr">
         <is>
           <t>Menghapus Kondisi pada Indikator Performa</t>
         </is>
       </c>
-      <c r="E843" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F843" s="3" t="inlineStr">
+      <c r="E844" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F844" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G843" s="4" t="inlineStr">
+      <c r="G844" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Hapus pada salah satu kondisi di Indikator Performa.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H843" s="4" t="inlineStr">
+      <c r="H844" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menghapus kondisi dari Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="844" ht="28" customHeight="1">
-      <c r="A844" s="43" t="inlineStr">
+    <row r="845" ht="42" customHeight="1">
+      <c r="A845" s="43" t="inlineStr">
         <is>
           <t>67.6</t>
         </is>
       </c>
-      <c r="B844" s="3" t="inlineStr">
+      <c r="B845" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C844" s="3" t="inlineStr">
+      <c r="C845" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D844" s="4" t="inlineStr">
+      <c r="D845" s="4" t="inlineStr">
         <is>
           <t>Menambahkan Operator pada Kondisi</t>
         </is>
       </c>
-      <c r="E844" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F844" s="3" t="inlineStr">
+      <c r="E845" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F845" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G844" s="4" t="inlineStr">
+      <c r="G845" s="4" t="inlineStr">
         <is>
           <t>1. Klik link tambah operator pada salah satu kondisi di Indikator Performa.
 2. Mengisi field operator baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H844" s="4" t="inlineStr">
+      <c r="H845" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan baris operator baru pada kondisi.
 2. Berhasil mengisi data operator.
@@ -37673,170 +37717,170 @@
         </is>
       </c>
     </row>
-    <row r="845" ht="42" customHeight="1">
-      <c r="A845" s="43" t="inlineStr">
+    <row r="846" ht="28" customHeight="1">
+      <c r="A846" s="43" t="inlineStr">
         <is>
           <t>67.7</t>
         </is>
       </c>
-      <c r="B845" s="3" t="inlineStr">
+      <c r="B846" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C845" s="3" t="inlineStr">
+      <c r="C846" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D845" s="4" t="inlineStr">
+      <c r="D846" s="4" t="inlineStr">
         <is>
           <t>Menghapus Operator pada Kondisi</t>
         </is>
       </c>
-      <c r="E845" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F845" s="3" t="inlineStr">
+      <c r="E846" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F846" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G845" s="4" t="inlineStr">
+      <c r="G846" s="4" t="inlineStr">
         <is>
           <t>1. Klik button x pada salah satu operator di Indikator Performa.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H845" s="4" t="inlineStr">
+      <c r="H846" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menghapus operator dari kondisi di Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="846" ht="28" customHeight="1">
-      <c r="A846" s="43" t="inlineStr">
+    <row r="847" ht="14" customHeight="1">
+      <c r="A847" s="43" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="B846" s="3" t="inlineStr">
+      <c r="B847" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C846" s="3" t="inlineStr">
+      <c r="C847" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D846" s="4" t="inlineStr">
+      <c r="D847" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Approval non Banking</t>
         </is>
       </c>
-      <c r="E846" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F846" s="3" t="inlineStr">
+      <c r="E847" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F847" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G846" s="4" t="inlineStr">
+      <c r="G847" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Re-Assign &amp; Approval 
 2. Klik submenu Approval non banking</t>
         </is>
       </c>
-      <c r="H846" s="4" t="inlineStr">
+      <c r="H847" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan submenu Re-Assign &amp; Approval 
 2. Menampilkan halaman Approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="847" ht="14" customHeight="1">
-      <c r="A847" s="43" t="inlineStr">
+    <row r="848" ht="14" customHeight="1">
+      <c r="A848" s="43" t="inlineStr">
         <is>
           <t>68.2</t>
         </is>
       </c>
-      <c r="B847" s="3" t="inlineStr">
+      <c r="B848" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C847" s="3" t="inlineStr">
+      <c r="C848" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D847" s="4" t="inlineStr">
+      <c r="D848" s="4" t="inlineStr">
         <is>
           <t>Melihat Detail data Approval non banking</t>
         </is>
       </c>
-      <c r="E847" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F847" s="3" t="inlineStr">
+      <c r="E848" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F848" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G847" s="4" t="inlineStr">
+      <c r="G848" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Detail</t>
         </is>
       </c>
-      <c r="H847" s="4" t="inlineStr">
+      <c r="H848" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan halaman detail data approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="848" ht="14" customHeight="1">
-      <c r="A848" s="43" t="inlineStr">
+    <row r="849" ht="42" customHeight="1">
+      <c r="A849" s="43" t="inlineStr">
         <is>
           <t>68.3</t>
         </is>
       </c>
-      <c r="B848" s="3" t="inlineStr">
+      <c r="B849" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C848" s="3" t="inlineStr">
+      <c r="C849" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D848" s="4" t="inlineStr">
+      <c r="D849" s="4" t="inlineStr">
         <is>
           <t>Menyetujui Prospek</t>
         </is>
       </c>
-      <c r="E848" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F848" s="3" t="inlineStr">
+      <c r="E849" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F849" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G848" s="4" t="inlineStr">
+      <c r="G849" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Setujui 
@@ -37845,7 +37889,7 @@
 5. Klik button Setujui</t>
         </is>
       </c>
-      <c r="H848" s="4" t="inlineStr">
+      <c r="H849" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan modal approve 
@@ -37855,87 +37899,87 @@
         </is>
       </c>
     </row>
-    <row r="849" ht="42" customHeight="1">
-      <c r="A849" s="43" t="inlineStr">
-        <is>
-          <t>68.4</t>
-        </is>
-      </c>
-      <c r="B849" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C849" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D849" s="4" t="inlineStr">
-        <is>
-          <t>Batal menyetujui Prospek</t>
-        </is>
-      </c>
-      <c r="E849" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F849" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G849" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Batalkan pada modal approve</t>
-        </is>
-      </c>
-      <c r="H849" s="4" t="inlineStr">
-        <is>
-          <t>1. Modal approve tertutup dan tetap di halaman approval non banking</t>
-        </is>
-      </c>
-    </row>
     <row r="850" ht="28" customHeight="1">
       <c r="A850" s="43" t="inlineStr">
         <is>
+          <t>68.4</t>
+        </is>
+      </c>
+      <c r="B850" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C850" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D850" s="4" t="inlineStr">
+        <is>
+          <t>Batal menyetujui Prospek</t>
+        </is>
+      </c>
+      <c r="E850" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F850" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G850" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Batalkan pada modal approve</t>
+        </is>
+      </c>
+      <c r="H850" s="4" t="inlineStr">
+        <is>
+          <t>1. Modal approve tertutup dan tetap di halaman approval non banking</t>
+        </is>
+      </c>
+    </row>
+    <row r="851" ht="28" customHeight="1">
+      <c r="A851" s="43" t="inlineStr">
+        <is>
           <t>68.5</t>
         </is>
       </c>
-      <c r="B850" s="3" t="inlineStr">
+      <c r="B851" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C850" s="3" t="inlineStr">
+      <c r="C851" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D850" s="4" t="inlineStr">
+      <c r="D851" s="4" t="inlineStr">
         <is>
           <t>Tidak menginput nilai realisasi pada modal approve</t>
         </is>
       </c>
-      <c r="E850" s="3" t="inlineStr">
+      <c r="E851" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F850" s="3" t="inlineStr">
+      <c r="F851" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G850" s="4" t="inlineStr">
+      <c r="G851" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan nilai realisasi 
 2. Input remark 
 3. Klik button Setujui</t>
         </is>
       </c>
-      <c r="H850" s="4" t="inlineStr">
+      <c r="H851" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field realisasi 
 2. Berhasil menginput remark 
@@ -37943,52 +37987,10 @@
         </is>
       </c>
     </row>
-    <row r="851" ht="28" customHeight="1">
-      <c r="A851" s="43" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
-      <c r="B851" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C851" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D851" s="4" t="inlineStr">
-        <is>
-          <t>Tidak menginput remark pada modal approve</t>
-        </is>
-      </c>
-      <c r="E851" s="3" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F851" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G851" s="4" t="inlineStr">
-        <is>
-          <t>1. Kosongkan remark</t>
-        </is>
-      </c>
-      <c r="H851" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan alert 'Remark dibutuhkan!'</t>
-        </is>
-      </c>
-    </row>
     <row r="852" ht="28" customHeight="1">
       <c r="A852" s="43" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="B852" s="3" t="inlineStr">
@@ -38003,7 +38005,7 @@
       </c>
       <c r="D852" s="4" t="inlineStr">
         <is>
-          <t>Menginput huruf pada field realisasi</t>
+          <t>Tidak menginput remark pada modal approve</t>
         </is>
       </c>
       <c r="E852" s="3" t="inlineStr">
@@ -38013,52 +38015,94 @@
       </c>
       <c r="F852" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G852" s="4" t="inlineStr">
         <is>
-          <t>1. Input huruf pada field realisasi kemudian pindah ke filed lain</t>
+          <t>1. Kosongkan remark</t>
         </is>
       </c>
       <c r="H852" s="4" t="inlineStr">
         <is>
-          <t>1. Sistem menghapus input non-numerik secara otomatis saat field kehilangan fokus. Field Realiasi menjadi kosong</t>
+          <t>1. Menampilkan alert 'Remark dibutuhkan!'</t>
         </is>
       </c>
     </row>
     <row r="853" ht="28" customHeight="1">
       <c r="A853" s="43" t="inlineStr">
         <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="B853" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C853" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D853" s="4" t="inlineStr">
+        <is>
+          <t>Menginput huruf pada field realisasi</t>
+        </is>
+      </c>
+      <c r="E853" s="3" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F853" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G853" s="4" t="inlineStr">
+        <is>
+          <t>1. Input huruf pada field realisasi kemudian pindah ke filed lain</t>
+        </is>
+      </c>
+      <c r="H853" s="4" t="inlineStr">
+        <is>
+          <t>1. Sistem menghapus input non-numerik secara otomatis saat field kehilangan fokus. Field Realiasi menjadi kosong</t>
+        </is>
+      </c>
+    </row>
+    <row r="854" ht="28" customHeight="1">
+      <c r="A854" s="43" t="inlineStr">
+        <is>
           <t>68.8</t>
         </is>
       </c>
-      <c r="B853" s="3" t="inlineStr">
+      <c r="B854" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C853" s="3" t="inlineStr">
+      <c r="C854" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D853" s="4" t="inlineStr">
+      <c r="D854" s="4" t="inlineStr">
         <is>
           <t>Menolak Prospek</t>
         </is>
       </c>
-      <c r="E853" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F853" s="3" t="inlineStr">
+      <c r="E854" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F854" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G853" s="4" t="inlineStr">
+      <c r="G854" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Tolak 
@@ -38066,7 +38110,7 @@
 4. Klik button Tolak</t>
         </is>
       </c>
-      <c r="H853" s="4" t="inlineStr">
+      <c r="H854" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan modal tolak prospek
@@ -38075,210 +38119,210 @@
         </is>
       </c>
     </row>
-    <row r="854" ht="28" customHeight="1">
-      <c r="A854" s="43" t="inlineStr">
-        <is>
-          <t>68.9</t>
-        </is>
-      </c>
-      <c r="B854" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C854" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D854" s="4" t="inlineStr">
-        <is>
-          <t>Batal menolak prospek</t>
-        </is>
-      </c>
-      <c r="E854" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F854" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G854" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Batalkan pada moal tolak prospek</t>
-        </is>
-      </c>
-      <c r="H854" s="4" t="inlineStr">
-        <is>
-          <t>1. Modal tolak prospek tertutup dan tetap berada di halaman approval non banking</t>
-        </is>
-      </c>
-    </row>
     <row r="855" ht="28" customHeight="1">
       <c r="A855" s="43" t="inlineStr">
         <is>
+          <t>68.9</t>
+        </is>
+      </c>
+      <c r="B855" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C855" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D855" s="4" t="inlineStr">
+        <is>
+          <t>Batal menolak prospek</t>
+        </is>
+      </c>
+      <c r="E855" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F855" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G855" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Batalkan pada moal tolak prospek</t>
+        </is>
+      </c>
+      <c r="H855" s="4" t="inlineStr">
+        <is>
+          <t>1. Modal tolak prospek tertutup dan tetap berada di halaman approval non banking</t>
+        </is>
+      </c>
+    </row>
+    <row r="856" ht="28" customHeight="1">
+      <c r="A856" s="43" t="inlineStr">
+        <is>
           <t>68.10</t>
         </is>
       </c>
-      <c r="B855" s="3" t="inlineStr">
+      <c r="B856" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C855" s="3" t="inlineStr">
+      <c r="C856" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D855" s="4" t="inlineStr">
+      <c r="D856" s="4" t="inlineStr">
         <is>
           <t>Tidak menginput remark pada modal tolak prospek</t>
         </is>
       </c>
-      <c r="E855" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F855" s="3" t="inlineStr">
+      <c r="E856" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F856" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G855" s="4" t="inlineStr">
+      <c r="G856" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan remark 
 2. Klik button Tolak</t>
         </is>
       </c>
-      <c r="H855" s="4" t="inlineStr">
+      <c r="H856" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan remark 
 2. Menampilkan alert 'Remark dibutuhkan!'</t>
         </is>
       </c>
     </row>
-    <row r="856" ht="28" customHeight="1">
-      <c r="A856" s="43" t="inlineStr">
+    <row r="857" ht="28" customHeight="1">
+      <c r="A857" s="43" t="inlineStr">
         <is>
           <t>68.11</t>
         </is>
       </c>
-      <c r="B856" s="3" t="inlineStr">
+      <c r="B857" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C856" s="3" t="inlineStr">
+      <c r="C857" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D856" s="4" t="inlineStr">
+      <c r="D857" s="4" t="inlineStr">
         <is>
           <t>Filter kolom</t>
         </is>
       </c>
-      <c r="E856" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F856" s="3" t="inlineStr">
+      <c r="E857" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F857" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G856" s="4" t="inlineStr">
+      <c r="G857" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon filter kolom 
 2. Checklist/unchecklist kolom</t>
         </is>
       </c>
-      <c r="H856" s="4" t="inlineStr">
+      <c r="H857" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan list kolom tabel 
 2. Menampilkan data tabel sesuai dengan kolom yang di ceklis</t>
         </is>
       </c>
     </row>
-    <row r="857" ht="28" customHeight="1">
-      <c r="A857" s="43" t="inlineStr">
-        <is>
-          <t>68.12</t>
-        </is>
-      </c>
-      <c r="B857" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C857" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D857" s="4" t="inlineStr">
-        <is>
-          <t>Reset ke Default pada filter kolom</t>
-        </is>
-      </c>
-      <c r="E857" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F857" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G857" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik Reset ke Default</t>
-        </is>
-      </c>
-      <c r="H857" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data tabel dengan kolom default</t>
-        </is>
-      </c>
-    </row>
     <row r="858" ht="28" customHeight="1">
       <c r="A858" s="43" t="inlineStr">
         <is>
+          <t>68.12</t>
+        </is>
+      </c>
+      <c r="B858" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C858" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D858" s="4" t="inlineStr">
+        <is>
+          <t>Reset ke Default pada filter kolom</t>
+        </is>
+      </c>
+      <c r="E858" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F858" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G858" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik Reset ke Default</t>
+        </is>
+      </c>
+      <c r="H858" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data tabel dengan kolom default</t>
+        </is>
+      </c>
+    </row>
+    <row r="859" ht="28" customHeight="1">
+      <c r="A859" s="43" t="inlineStr">
+        <is>
           <t>69.1</t>
         </is>
       </c>
-      <c r="B858" s="3" t="inlineStr">
+      <c r="B859" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C858" s="3" t="inlineStr">
+      <c r="C859" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D858" s="4" t="inlineStr">
+      <c r="D859" s="4" t="inlineStr">
         <is>
           <t>Filter data</t>
         </is>
       </c>
-      <c r="E858" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F858" s="3" t="inlineStr">
+      <c r="E859" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F859" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G858" s="4" t="inlineStr">
+      <c r="G859" s="4" t="inlineStr">
         <is>
           <t>1. Pilih kantor wilayah
 2. Pilih kantor cabang 
@@ -38288,7 +38332,7 @@
 6. Klik button Filter</t>
         </is>
       </c>
-      <c r="H858" s="4" t="inlineStr">
+      <c r="H859" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list data filter kantor wilayah dan dapat di pilih
 2. Menampilkan dropdown list data filter kantor cabang dan dapat di pilih
@@ -38299,126 +38343,126 @@
         </is>
       </c>
     </row>
-    <row r="859" ht="28" customHeight="1">
-      <c r="A859" s="43" t="inlineStr">
+    <row r="860" ht="28" customHeight="1">
+      <c r="A860" s="43" t="inlineStr">
         <is>
           <t>69.2</t>
         </is>
       </c>
-      <c r="B859" s="3" t="inlineStr">
+      <c r="B860" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C859" s="3" t="inlineStr">
+      <c r="C860" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D859" s="4" t="inlineStr">
+      <c r="D860" s="4" t="inlineStr">
         <is>
           <t>Mencari data</t>
         </is>
       </c>
-      <c r="E859" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F859" s="3" t="inlineStr">
+      <c r="E860" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F860" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G859" s="4" t="inlineStr">
+      <c r="G860" s="4" t="inlineStr">
         <is>
           <t>1. Input keyword pada field search 
 2. Klik icon search yang ada di sebelah field</t>
         </is>
       </c>
-      <c r="H859" s="4" t="inlineStr">
+      <c r="H860" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput keyword 
 2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
         </is>
       </c>
     </row>
-    <row r="860" ht="28" customHeight="1">
-      <c r="A860" s="43" t="inlineStr">
+    <row r="861" ht="28" customHeight="1">
+      <c r="A861" s="43" t="inlineStr">
         <is>
           <t>69.3</t>
         </is>
       </c>
-      <c r="B860" s="3" t="inlineStr">
+      <c r="B861" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C860" s="3" t="inlineStr">
+      <c r="C861" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D860" s="4" t="inlineStr">
+      <c r="D861" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E860" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F860" s="3" t="inlineStr">
+      <c r="E861" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F861" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G860" s="4" t="inlineStr">
+      <c r="G861" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Re-Assign &amp; Approval 
 2. Klik submenu Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="H860" s="4" t="inlineStr">
+      <c r="H861" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan submenu Re-Assign &amp; Approval 
 2. Menampilkan halaman Re-Assign Prospek</t>
         </is>
       </c>
     </row>
-    <row r="861" ht="28" customHeight="1">
-      <c r="A861" s="43" t="inlineStr">
+    <row r="862" ht="28" customHeight="1">
+      <c r="A862" s="43" t="inlineStr">
         <is>
           <t>69.4</t>
         </is>
       </c>
-      <c r="B861" s="3" t="inlineStr">
+      <c r="B862" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C861" s="3" t="inlineStr">
+      <c r="C862" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D861" s="4" t="inlineStr">
+      <c r="D862" s="4" t="inlineStr">
         <is>
           <t>Filter data</t>
         </is>
       </c>
-      <c r="E861" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F861" s="3" t="inlineStr">
+      <c r="E862" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F862" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G861" s="4" t="inlineStr">
+      <c r="G862" s="4" t="inlineStr">
         <is>
           <t>1. Pilih kantor wilayah
 2. Pilih kantor cabang 
@@ -38428,7 +38472,7 @@
 6. Klik button Filter</t>
         </is>
       </c>
-      <c r="H861" s="4" t="inlineStr">
+      <c r="H862" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list data filter kantor wilayah dan dapat di pilih
 2. Menampilkan dropdown list data filter kantor cabang dan dapat di pilih
@@ -38439,96 +38483,54 @@
         </is>
       </c>
     </row>
-    <row r="862" ht="28" customHeight="1">
-      <c r="A862" s="43" t="inlineStr">
+    <row r="863" ht="28" customHeight="1">
+      <c r="A863" s="43" t="inlineStr">
         <is>
           <t>69.5</t>
         </is>
       </c>
-      <c r="B862" s="3" t="inlineStr">
+      <c r="B863" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C862" s="3" t="inlineStr">
+      <c r="C863" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D862" s="4" t="inlineStr">
+      <c r="D863" s="4" t="inlineStr">
         <is>
           <t>Mencari data</t>
         </is>
       </c>
-      <c r="E862" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F862" s="3" t="inlineStr">
+      <c r="E863" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F863" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G862" s="4" t="inlineStr">
+      <c r="G863" s="4" t="inlineStr">
         <is>
           <t>1. Input keyword pada field search 
 2. Klik icon search yang ada di sebelah field</t>
         </is>
       </c>
-      <c r="H862" s="4" t="inlineStr">
+      <c r="H863" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput keyword 
 2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
         </is>
       </c>
     </row>
-    <row r="863" ht="28" customHeight="1">
-      <c r="A863" s="43" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
-      <c r="B863" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C863" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D863" s="4" t="inlineStr">
-        <is>
-          <t>Validasi count checklist data</t>
-        </is>
-      </c>
-      <c r="E863" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F863" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G863" s="4" t="inlineStr">
-        <is>
-          <t>1. Cek informasi yang ada pada button Reassign () data</t>
-        </is>
-      </c>
-      <c r="H863" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan count angka yang sesuai dengan data yang di checklist</t>
-        </is>
-      </c>
-    </row>
     <row r="864" ht="28" customHeight="1">
       <c r="A864" s="43" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="B864" s="3" t="inlineStr">
@@ -38543,7 +38545,7 @@
       </c>
       <c r="D864" s="4" t="inlineStr">
         <is>
-          <t>Validasi data yang sudah dii pilih</t>
+          <t>Validasi count checklist data</t>
         </is>
       </c>
       <c r="E864" s="3" t="inlineStr">
@@ -38558,133 +38560,175 @@
       </c>
       <c r="G864" s="4" t="inlineStr">
         <is>
-          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi prospek yang di pilih</t>
+          <t>1. Cek informasi yang ada pada button Reassign () data</t>
         </is>
       </c>
       <c r="H864" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data tabel prospek yang di pilih saja</t>
+          <t>1. Menampilkan count angka yang sesuai dengan data yang di checklist</t>
         </is>
       </c>
     </row>
     <row r="865" ht="28" customHeight="1">
       <c r="A865" s="43" t="inlineStr">
         <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="B865" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C865" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D865" s="4" t="inlineStr">
+        <is>
+          <t>Validasi data yang sudah dii pilih</t>
+        </is>
+      </c>
+      <c r="E865" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F865" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G865" s="4" t="inlineStr">
+        <is>
+          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi prospek yang di pilih</t>
+        </is>
+      </c>
+      <c r="H865" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan data tabel prospek yang di pilih saja</t>
+        </is>
+      </c>
+    </row>
+    <row r="866" ht="28" customHeight="1">
+      <c r="A866" s="43" t="inlineStr">
+        <is>
           <t>69.8</t>
         </is>
       </c>
-      <c r="B865" s="3" t="inlineStr">
+      <c r="B866" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C865" s="3" t="inlineStr">
+      <c r="C866" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D865" s="4" t="inlineStr">
+      <c r="D866" s="4" t="inlineStr">
         <is>
           <t>Mengosongkan field inputan mandatory pada reassign prospek</t>
         </is>
       </c>
-      <c r="E865" s="3" t="inlineStr">
+      <c r="E866" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F865" s="3" t="inlineStr">
+      <c r="F866" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G865" s="4" t="inlineStr">
+      <c r="G866" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan salah satu atau semua field mandatory 
 2. Klik button Submit</t>
         </is>
       </c>
-      <c r="H865" s="4" t="inlineStr">
+      <c r="H866" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil tidak mengisi/mengosongkan field 
 2. Menampilkan alert pada setiap field mandatory bahwa field tersebut dibutuhkan / wajib diisi</t>
         </is>
       </c>
     </row>
-    <row r="866" ht="28" customHeight="1">
-      <c r="A866" s="43" t="inlineStr">
-        <is>
-          <t>69.9</t>
-        </is>
-      </c>
-      <c r="B866" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C866" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D866" s="4" t="inlineStr">
-        <is>
-          <t>Membatalkan Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="E866" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F866" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G866" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
-        </is>
-      </c>
-      <c r="H866" s="4" t="inlineStr">
-        <is>
-          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
-        </is>
-      </c>
-    </row>
     <row r="867" ht="28" customHeight="1">
       <c r="A867" s="43" t="inlineStr">
         <is>
+          <t>69.9</t>
+        </is>
+      </c>
+      <c r="B867" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C867" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D867" s="4" t="inlineStr">
+        <is>
+          <t>Membatalkan Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="E867" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F867" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G867" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
+        </is>
+      </c>
+      <c r="H867" s="4" t="inlineStr">
+        <is>
+          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
+        </is>
+      </c>
+    </row>
+    <row r="868" ht="28" customHeight="1">
+      <c r="A868" s="43" t="inlineStr">
+        <is>
           <t>69.10</t>
         </is>
       </c>
-      <c r="B867" s="3" t="inlineStr">
+      <c r="B868" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C867" s="3" t="inlineStr">
+      <c r="C868" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D867" s="4" t="inlineStr">
+      <c r="D868" s="4" t="inlineStr">
         <is>
           <t>Validasi data prospek yang di re-assign</t>
         </is>
       </c>
-      <c r="E867" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F867" s="3" t="inlineStr">
+      <c r="E868" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F868" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G867" s="4" t="inlineStr">
+      <c r="G868" s="4" t="inlineStr">
         <is>
           <t>1. Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek 
 2. Klik menu Lead Qualification 
@@ -38692,7 +38736,7 @@
 4. Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
-      <c r="H867" s="4" t="inlineStr">
+      <c r="H868" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login 
 2. Menampilkan dropdown submenu Lead Qualification 
@@ -38701,38 +38745,38 @@
         </is>
       </c>
     </row>
-    <row r="868" ht="28" customHeight="1">
-      <c r="A868" s="43" t="inlineStr">
+    <row r="869" ht="28" customHeight="1">
+      <c r="A869" s="43" t="inlineStr">
         <is>
           <t>69.11</t>
         </is>
       </c>
-      <c r="B868" s="3" t="inlineStr">
+      <c r="B869" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C868" s="3" t="inlineStr">
+      <c r="C869" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D868" s="4" t="inlineStr">
+      <c r="D869" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-assign prospek semua data</t>
         </is>
       </c>
-      <c r="E868" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F868" s="3" t="inlineStr">
+      <c r="E869" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F869" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G868" s="4" t="inlineStr">
+      <c r="G869" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Reassign semua data 
 2. Klik button Yes 
@@ -38743,7 +38787,7 @@
 7. Klik button Submit</t>
         </is>
       </c>
-      <c r="H868" s="4" t="inlineStr">
+      <c r="H869" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan popup konfirmasi 
 2. Menampilkan halaman pindah kelolaan 
@@ -38755,52 +38799,10 @@
         </is>
       </c>
     </row>
-    <row r="869" ht="28" customHeight="1">
-      <c r="A869" s="43" t="inlineStr">
-        <is>
-          <t>69.12</t>
-        </is>
-      </c>
-      <c r="B869" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C869" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D869" s="4" t="inlineStr">
-        <is>
-          <t>Validasi semua data</t>
-        </is>
-      </c>
-      <c r="E869" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F869" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G869" s="4" t="inlineStr">
-        <is>
-          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi semua prospek</t>
-        </is>
-      </c>
-      <c r="H869" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan data tabel yang berisi semua prospek</t>
-        </is>
-      </c>
-    </row>
     <row r="870" ht="28" customHeight="1">
       <c r="A870" s="43" t="inlineStr">
         <is>
-          <t>69.13</t>
+          <t>69.12</t>
         </is>
       </c>
       <c r="B870" s="3" t="inlineStr">
@@ -38815,7 +38817,7 @@
       </c>
       <c r="D870" s="4" t="inlineStr">
         <is>
-          <t>Membatalkan Re-Assign Prospek</t>
+          <t>Validasi semua data</t>
         </is>
       </c>
       <c r="E870" s="3" t="inlineStr">
@@ -38825,52 +38827,94 @@
       </c>
       <c r="F870" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G870" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
+          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi semua prospek</t>
         </is>
       </c>
       <c r="H870" s="4" t="inlineStr">
         <is>
-          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
+          <t>1. Menampilkan data tabel yang berisi semua prospek</t>
         </is>
       </c>
     </row>
     <row r="871" ht="28" customHeight="1">
       <c r="A871" s="43" t="inlineStr">
         <is>
+          <t>69.13</t>
+        </is>
+      </c>
+      <c r="B871" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C871" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D871" s="4" t="inlineStr">
+        <is>
+          <t>Membatalkan Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="E871" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F871" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G871" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
+        </is>
+      </c>
+      <c r="H871" s="4" t="inlineStr">
+        <is>
+          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
+        </is>
+      </c>
+    </row>
+    <row r="872" ht="70" customHeight="1">
+      <c r="A872" s="43" t="inlineStr">
+        <is>
           <t>69.14</t>
         </is>
       </c>
-      <c r="B871" s="3" t="inlineStr">
+      <c r="B872" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C871" s="3" t="inlineStr">
+      <c r="C872" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D871" s="4" t="inlineStr">
+      <c r="D872" s="4" t="inlineStr">
         <is>
           <t>Validasi semua data prospek yang di re-assign</t>
         </is>
       </c>
-      <c r="E871" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F871" s="3" t="inlineStr">
+      <c r="E872" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F872" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G871" s="4" t="inlineStr">
+      <c r="G872" s="4" t="inlineStr">
         <is>
           <t>1. Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek 
 2. Klik menu Lead Qualification 
@@ -38878,7 +38922,7 @@
 4. Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
-      <c r="H871" s="4" t="inlineStr">
+      <c r="H872" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login 
 2. Menampilkan dropdown submenu Lead Qualification 
@@ -38887,126 +38931,126 @@
         </is>
       </c>
     </row>
-    <row r="872" ht="70" customHeight="1">
-      <c r="A872" s="43" t="inlineStr">
+    <row r="873" ht="42" customHeight="1">
+      <c r="A873" s="43" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="B872" s="3" t="inlineStr">
+      <c r="B873" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C872" s="3" t="inlineStr">
+      <c r="C873" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D872" s="4" t="inlineStr">
+      <c r="D873" s="4" t="inlineStr">
         <is>
           <t>Pagination</t>
         </is>
       </c>
-      <c r="E872" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F872" s="3" t="inlineStr">
+      <c r="E873" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F873" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G872" s="4" t="inlineStr">
+      <c r="G873" s="4" t="inlineStr">
         <is>
           <t>1. Klik pagination (10/halaman).
 2. Pilih berapa data yang ingin ditampilkan.</t>
         </is>
       </c>
-      <c r="H872" s="4" t="inlineStr">
+      <c r="H873" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengklik pagination.
 2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="873" ht="42" customHeight="1">
-      <c r="A873" s="43" t="inlineStr">
+    <row r="874" ht="42" customHeight="1">
+      <c r="A874" s="43" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="B873" s="3" t="inlineStr">
+      <c r="B874" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C873" s="3" t="inlineStr">
+      <c r="C874" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D873" s="4" t="inlineStr">
+      <c r="D874" s="4" t="inlineStr">
         <is>
           <t>Pindah Halaman</t>
         </is>
       </c>
-      <c r="E873" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F873" s="3" t="inlineStr">
+      <c r="E874" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F874" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G873" s="4" t="inlineStr">
+      <c r="G874" s="4" t="inlineStr">
         <is>
           <t>1. Input angka halaman di field pindah halaman.
 2. Klik Enter pada keyboard.</t>
         </is>
       </c>
-      <c r="H873" s="4" t="inlineStr">
+      <c r="H874" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput angka halaman.
 2. Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
-    <row r="874" ht="42" customHeight="1">
-      <c r="A874" s="43" t="inlineStr">
+    <row r="875" ht="70" customHeight="1">
+      <c r="A875" s="43" t="inlineStr">
         <is>
           <t>70.3</t>
         </is>
       </c>
-      <c r="B874" s="3" t="inlineStr">
+      <c r="B875" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C874" s="3" t="inlineStr">
+      <c r="C875" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D874" s="4" t="inlineStr">
+      <c r="D875" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E874" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F874" s="3" t="inlineStr">
+      <c r="E875" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F875" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G874" s="4" t="inlineStr">
+      <c r="G875" s="4" t="inlineStr">
         <is>
           <t>1. Pilih prospek dengan klik checkbox yang ada di samping setiap data prospek 
 2. Klik button Reassign () data 
@@ -39015,7 +39059,7 @@
 5. Klik button Submit</t>
         </is>
       </c>
-      <c r="H874" s="4" t="inlineStr">
+      <c r="H875" s="4" t="inlineStr">
         <is>
           <t>1. Checkbox menjadi ceklis dan data berhasil di pilih 
 2. Menampilkan popup konfirmasi 
@@ -39025,258 +39069,258 @@
         </is>
       </c>
     </row>
-    <row r="875" ht="70" customHeight="1">
-      <c r="A875" s="43" t="inlineStr">
+    <row r="876" ht="28" customHeight="1">
+      <c r="A876" s="43" t="inlineStr">
         <is>
           <t>70.4</t>
         </is>
       </c>
-      <c r="B875" s="3" t="inlineStr">
+      <c r="B876" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C875" s="3" t="inlineStr">
+      <c r="C876" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D875" s="4" t="inlineStr">
+      <c r="D876" s="4" t="inlineStr">
         <is>
           <t>Pagination</t>
         </is>
       </c>
-      <c r="E875" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F875" s="3" t="inlineStr">
+      <c r="E876" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F876" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G875" s="4" t="inlineStr">
+      <c r="G876" s="4" t="inlineStr">
         <is>
           <t>1. Klik pagination (10/halaman).
 2. Pilih berapa data yang ingin ditampilkan.</t>
         </is>
       </c>
-      <c r="H875" s="4" t="inlineStr">
+      <c r="H876" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengklik pagination.
 2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="876" ht="28" customHeight="1">
-      <c r="A876" s="43" t="inlineStr">
+    <row r="877" ht="42" customHeight="1">
+      <c r="A877" s="43" t="inlineStr">
         <is>
           <t>70.5</t>
         </is>
       </c>
-      <c r="B876" s="3" t="inlineStr">
+      <c r="B877" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C876" s="3" t="inlineStr">
+      <c r="C877" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D876" s="4" t="inlineStr">
+      <c r="D877" s="4" t="inlineStr">
         <is>
           <t>Pindah Halaman</t>
         </is>
       </c>
-      <c r="E876" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F876" s="3" t="inlineStr">
+      <c r="E877" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F877" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G876" s="4" t="inlineStr">
+      <c r="G877" s="4" t="inlineStr">
         <is>
           <t>1. Input angka halaman di field pindah halaman.
 2. Klik Enter pada keyboard.</t>
         </is>
       </c>
-      <c r="H876" s="4" t="inlineStr">
+      <c r="H877" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput angka halaman.
 2. Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
-    <row r="877" ht="42" customHeight="1">
-      <c r="A877" s="43" t="inlineStr">
+    <row r="878" ht="28" customHeight="1">
+      <c r="A878" s="43" t="inlineStr">
         <is>
           <t>70.6</t>
         </is>
       </c>
-      <c r="B877" s="3" t="inlineStr">
+      <c r="B878" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C877" s="3" t="inlineStr">
+      <c r="C878" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D877" s="4" t="inlineStr">
+      <c r="D878" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Re-Assign Management</t>
         </is>
       </c>
-      <c r="E877" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F877" s="3" t="inlineStr">
+      <c r="E878" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F878" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G877" s="4" t="inlineStr">
+      <c r="G878" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Re-Assign &amp; Approval 
 2. Klik submenu Re-Assign Management</t>
         </is>
       </c>
-      <c r="H877" s="4" t="inlineStr">
+      <c r="H878" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list submenu Re-Assign &amp; Approval 
 2. Menampilkan halaman Re-Assign Management</t>
         </is>
       </c>
     </row>
-    <row r="878" ht="28" customHeight="1">
-      <c r="A878" s="43" t="inlineStr">
+    <row r="879" ht="28" customHeight="1">
+      <c r="A879" s="43" t="inlineStr">
         <is>
           <t>70.7</t>
         </is>
       </c>
-      <c r="B878" s="3" t="inlineStr">
+      <c r="B879" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C878" s="3" t="inlineStr">
+      <c r="C879" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D878" s="4" t="inlineStr">
+      <c r="D879" s="4" t="inlineStr">
         <is>
           <t>Mencari data prospek pada halaman Re-Assign Management</t>
         </is>
       </c>
-      <c r="E878" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F878" s="3" t="inlineStr">
+      <c r="E879" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F879" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G878" s="4" t="inlineStr">
+      <c r="G879" s="4" t="inlineStr">
         <is>
           <t>1. Input nama nasabah pada field search 
 2. Klik icon search atau klik Enter</t>
         </is>
       </c>
-      <c r="H878" s="4" t="inlineStr">
+      <c r="H879" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput nama nasabah
 2. Menampilkan data prospek Re-Assign Management sesuai dengan nama yang di cari</t>
         </is>
       </c>
     </row>
-    <row r="879" ht="28" customHeight="1">
-      <c r="A879" s="43" t="inlineStr">
+    <row r="880" ht="28" customHeight="1">
+      <c r="A880" s="43" t="inlineStr">
         <is>
           <t>70.8</t>
         </is>
       </c>
-      <c r="B879" s="3" t="inlineStr">
+      <c r="B880" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C879" s="3" t="inlineStr">
+      <c r="C880" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D879" s="4" t="inlineStr">
+      <c r="D880" s="4" t="inlineStr">
         <is>
           <t>Mencari data prospek yang tidak ada pada halaman Re-Assign Management</t>
         </is>
       </c>
-      <c r="E879" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F879" s="3" t="inlineStr">
+      <c r="E880" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F880" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G879" s="4" t="inlineStr">
+      <c r="G880" s="4" t="inlineStr">
         <is>
           <t>1. Input nama nasabah yang datanya tidak ada 
 2. Klik icon search atau klik Enter</t>
         </is>
       </c>
-      <c r="H879" s="4" t="inlineStr">
+      <c r="H880" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput nama nasabah
 2. Menampilkan tabel kosong dengan keterangan no data</t>
         </is>
       </c>
     </row>
-    <row r="880" ht="28" customHeight="1">
-      <c r="A880" s="43" t="inlineStr">
+    <row r="881" ht="14" customHeight="1">
+      <c r="A881" s="43" t="inlineStr">
         <is>
           <t>70.9</t>
         </is>
       </c>
-      <c r="B880" s="3" t="inlineStr">
+      <c r="B881" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C880" s="3" t="inlineStr">
+      <c r="C881" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D880" s="4" t="inlineStr">
+      <c r="D881" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E880" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F880" s="3" t="inlineStr">
+      <c r="E881" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F881" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G880" s="4" t="inlineStr">
+      <c r="G881" s="4" t="inlineStr">
         <is>
           <t>1. Pilih prospek dengan klik checkbox yang ada di samping setiap data prospek 
 2. Klik button Reassign () data 
@@ -39285,7 +39329,7 @@
 5. Klik button Submit</t>
         </is>
       </c>
-      <c r="H880" s="4" t="inlineStr">
+      <c r="H881" s="4" t="inlineStr">
         <is>
           <t>1. Checkbox menjadi ceklis dan data berhasil di pilih 
 2. Menampilkan popup konfirmasi 
@@ -39295,80 +39339,80 @@
         </is>
       </c>
     </row>
-    <row r="881" ht="14" customHeight="1">
-      <c r="A881" s="43" t="inlineStr">
-        <is>
-          <t>70.10</t>
-        </is>
-      </c>
-      <c r="B881" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C881" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Management</t>
-        </is>
-      </c>
-      <c r="D881" s="4" t="inlineStr">
-        <is>
-          <t>Validasi jumlah data yang di pilih untuk reassign</t>
-        </is>
-      </c>
-      <c r="E881" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F881" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G881" s="4" t="inlineStr">
-        <is>
-          <t>1. cek jumlah data yang muncul pada button Reassign () data</t>
-        </is>
-      </c>
-      <c r="H881" s="4" t="inlineStr">
-        <is>
-          <t>1. Angka yang muncul pada button sesuai dengan jumlah data yang di pilih</t>
-        </is>
-      </c>
-    </row>
     <row r="882" ht="42" customHeight="1">
       <c r="A882" s="43" t="inlineStr">
         <is>
+          <t>70.10</t>
+        </is>
+      </c>
+      <c r="B882" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C882" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D882" s="4" t="inlineStr">
+        <is>
+          <t>Validasi jumlah data yang di pilih untuk reassign</t>
+        </is>
+      </c>
+      <c r="E882" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F882" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G882" s="4" t="inlineStr">
+        <is>
+          <t>1. cek jumlah data yang muncul pada button Reassign () data</t>
+        </is>
+      </c>
+      <c r="H882" s="4" t="inlineStr">
+        <is>
+          <t>1. Angka yang muncul pada button sesuai dengan jumlah data yang di pilih</t>
+        </is>
+      </c>
+    </row>
+    <row r="883" ht="42" customHeight="1">
+      <c r="A883" s="43" t="inlineStr">
+        <is>
           <t>70.11</t>
         </is>
       </c>
-      <c r="B882" s="3" t="inlineStr">
+      <c r="B883" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C882" s="3" t="inlineStr">
+      <c r="C883" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D882" s="4" t="inlineStr">
+      <c r="D883" s="4" t="inlineStr">
         <is>
           <t>Validasi data prospek yang di re-assign ke sales</t>
         </is>
       </c>
-      <c r="E882" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F882" s="3" t="inlineStr">
+      <c r="E883" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F883" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G882" s="4" t="inlineStr">
+      <c r="G883" s="4" t="inlineStr">
         <is>
           <t>1. Login dengan akun sales yang sebelumnya sudah di pilih reassign management
 2. Klik menu Lead Qualification
@@ -39376,7 +39420,7 @@
 4. Cek data prospek yang sudah di reassign</t>
         </is>
       </c>
-      <c r="H882" s="4" t="inlineStr">
+      <c r="H883" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login akun sales
 2. Menampilkan dropdown submenu Lead Qualification
@@ -39385,140 +39429,98 @@
         </is>
       </c>
     </row>
-    <row r="883" ht="42" customHeight="1">
-      <c r="A883" s="43" t="inlineStr">
+    <row r="884" ht="28" customHeight="1">
+      <c r="A884" s="43" t="inlineStr">
         <is>
           <t>70.12</t>
         </is>
       </c>
-      <c r="B883" s="3" t="inlineStr">
+      <c r="B884" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C883" s="3" t="inlineStr">
+      <c r="C884" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D883" s="4" t="inlineStr">
+      <c r="D884" s="4" t="inlineStr">
         <is>
           <t>Pagination</t>
         </is>
       </c>
-      <c r="E883" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F883" s="3" t="inlineStr">
+      <c r="E884" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F884" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G883" s="4" t="inlineStr">
+      <c r="G884" s="4" t="inlineStr">
         <is>
           <t>1. Klik pagination (10/halaman).
 2. Pilih berapa data yang ingin ditampilkan.</t>
         </is>
       </c>
-      <c r="H883" s="4" t="inlineStr">
+      <c r="H884" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengklik pagination.
 2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="884" ht="28" customHeight="1">
-      <c r="A884" s="43" t="inlineStr">
+    <row r="885" ht="42" customHeight="1">
+      <c r="A885" s="43" t="inlineStr">
         <is>
           <t>70.13</t>
         </is>
       </c>
-      <c r="B884" s="3" t="inlineStr">
+      <c r="B885" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C884" s="3" t="inlineStr">
+      <c r="C885" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D884" s="4" t="inlineStr">
+      <c r="D885" s="4" t="inlineStr">
         <is>
           <t>Pindah Halaman</t>
         </is>
       </c>
-      <c r="E884" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F884" s="3" t="inlineStr">
+      <c r="E885" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F885" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G884" s="4" t="inlineStr">
+      <c r="G885" s="4" t="inlineStr">
         <is>
           <t>1. Input angka halaman di field pindah halaman.
 2. Klik Enter pada keyboard.</t>
         </is>
       </c>
-      <c r="H884" s="4" t="inlineStr">
+      <c r="H885" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput angka halaman.
 2. Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
-    <row r="885" ht="42" customHeight="1">
-      <c r="A885" s="43" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
-      <c r="B885" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C885" s="3" t="inlineStr">
-        <is>
-          <t>Riwayat export saya</t>
-        </is>
-      </c>
-      <c r="D885" s="4" t="inlineStr">
-        <is>
-          <t>Membuka menu riwayat export saya</t>
-        </is>
-      </c>
-      <c r="E885" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F885" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G885" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu exported data management, klik submenu riwayat export saya</t>
-        </is>
-      </c>
-      <c r="H885" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan halaman riwayat export saya</t>
-        </is>
-      </c>
-    </row>
     <row r="886" ht="14" customHeight="1">
       <c r="A886" s="43" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="B886" s="3" t="inlineStr">
@@ -39533,7 +39535,7 @@
       </c>
       <c r="D886" s="4" t="inlineStr">
         <is>
-          <t>Validasi card disetujui dengan data table</t>
+          <t>Membuka menu riwayat export saya</t>
         </is>
       </c>
       <c r="E886" s="3" t="inlineStr">
@@ -39548,19 +39550,19 @@
       </c>
       <c r="G886" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Approved”</t>
+          <t>1. Klik menu exported data management, klik submenu riwayat export saya</t>
         </is>
       </c>
       <c r="H886" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Menampilkan halaman riwayat export saya</t>
         </is>
       </c>
     </row>
     <row r="887" ht="42" customHeight="1">
       <c r="A887" s="43" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="B887" s="3" t="inlineStr">
@@ -39575,7 +39577,7 @@
       </c>
       <c r="D887" s="4" t="inlineStr">
         <is>
-          <t>Validasi card ditolak dengan data table</t>
+          <t>Validasi card disetujui dengan data table</t>
         </is>
       </c>
       <c r="E887" s="3" t="inlineStr">
@@ -39590,7 +39592,7 @@
       </c>
       <c r="G887" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Rejected”</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Approved”</t>
         </is>
       </c>
       <c r="H887" s="4" t="inlineStr">
@@ -39602,7 +39604,7 @@
     <row r="888" ht="42" customHeight="1">
       <c r="A888" s="43" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="B888" s="3" t="inlineStr">
@@ -39617,7 +39619,7 @@
       </c>
       <c r="D888" s="4" t="inlineStr">
         <is>
-          <t>Validasi card kadaluwarsa dengan data table</t>
+          <t>Validasi card ditolak dengan data table</t>
         </is>
       </c>
       <c r="E888" s="3" t="inlineStr">
@@ -39627,12 +39629,12 @@
       </c>
       <c r="F888" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G888" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Expired”</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Rejected”</t>
         </is>
       </c>
       <c r="H888" s="4" t="inlineStr">
@@ -39644,7 +39646,7 @@
     <row r="889" ht="28" customHeight="1">
       <c r="A889" s="43" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="B889" s="3" t="inlineStr">
@@ -39659,7 +39661,7 @@
       </c>
       <c r="D889" s="4" t="inlineStr">
         <is>
-          <t>Mengunduh data yang sudah di approve</t>
+          <t>Validasi card kadaluwarsa dengan data table</t>
         </is>
       </c>
       <c r="E889" s="3" t="inlineStr">
@@ -39669,24 +39671,24 @@
       </c>
       <c r="F889" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G889" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button download</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Expired”</t>
         </is>
       </c>
       <c r="H889" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengunduh data</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="890" ht="42" customHeight="1">
       <c r="A890" s="43" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="B890" s="3" t="inlineStr">
@@ -39701,7 +39703,7 @@
       </c>
       <c r="D890" s="4" t="inlineStr">
         <is>
-          <t>Membuka dokumen hasil download</t>
+          <t>Mengunduh data yang sudah di approve</t>
         </is>
       </c>
       <c r="E890" s="3" t="inlineStr">
@@ -39716,19 +39718,19 @@
       </c>
       <c r="G890" s="4" t="inlineStr">
         <is>
-          <t>1. Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
+          <t>1. Klik button download</t>
         </is>
       </c>
       <c r="H890" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka file hasil download</t>
+          <t>1. Berhasil mengunduh data</t>
         </is>
       </c>
     </row>
     <row r="891" ht="14" customHeight="1">
       <c r="A891" s="43" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="B891" s="3" t="inlineStr">
@@ -39738,12 +39740,12 @@
       </c>
       <c r="C891" s="3" t="inlineStr">
         <is>
-          <t>Management export</t>
+          <t>Riwayat export saya</t>
         </is>
       </c>
       <c r="D891" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Membuka dokumen hasil download</t>
         </is>
       </c>
       <c r="E891" s="3" t="inlineStr">
@@ -39753,24 +39755,24 @@
       </c>
       <c r="F891" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G891" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
         </is>
       </c>
       <c r="H891" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Berhasil membuka file hasil download</t>
         </is>
       </c>
     </row>
     <row r="892" ht="42" customHeight="1">
       <c r="A892" s="43" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="B892" s="3" t="inlineStr">
@@ -39785,7 +39787,7 @@
       </c>
       <c r="D892" s="4" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E892" s="3" t="inlineStr">
@@ -39795,24 +39797,24 @@
       </c>
       <c r="F892" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G892" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H892" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="893" ht="42" customHeight="1">
       <c r="A893" s="43" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="B893" s="3" t="inlineStr">
@@ -39827,7 +39829,7 @@
       </c>
       <c r="D893" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E893" s="3" t="inlineStr">
@@ -39842,19 +39844,19 @@
       </c>
       <c r="G893" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
         </is>
       </c>
       <c r="H893" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="894" ht="28" customHeight="1">
       <c r="A894" s="43" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="B894" s="3" t="inlineStr">
@@ -39869,12 +39871,12 @@
       </c>
       <c r="D894" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E894" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F894" s="3" t="inlineStr">
@@ -39884,19 +39886,19 @@
       </c>
       <c r="G894" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H894" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="895" ht="42" customHeight="1">
       <c r="A895" s="43" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="B895" s="3" t="inlineStr">
@@ -39911,34 +39913,34 @@
       </c>
       <c r="D895" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E895" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F895" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G895" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H895" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="896" ht="14" customHeight="1">
       <c r="A896" s="43" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="B896" s="3" t="inlineStr">
@@ -39953,7 +39955,7 @@
       </c>
       <c r="D896" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E896" s="3" t="inlineStr">
@@ -39963,24 +39965,24 @@
       </c>
       <c r="F896" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G896" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H896" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="897" ht="42" customHeight="1">
       <c r="A897" s="43" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="B897" s="3" t="inlineStr">
@@ -39995,12 +39997,12 @@
       </c>
       <c r="D897" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E897" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F897" s="3" t="inlineStr">
@@ -40010,19 +40012,19 @@
       </c>
       <c r="G897" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H897" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="898" ht="42" customHeight="1">
       <c r="A898" s="43" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="B898" s="3" t="inlineStr">
@@ -40037,12 +40039,12 @@
       </c>
       <c r="D898" s="4" t="inlineStr">
         <is>
-          <t>Membuka menu Management Export</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E898" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F898" s="3" t="inlineStr">
@@ -40052,19 +40054,19 @@
       </c>
       <c r="G898" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu exported data management, klik submenu management export</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H898" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan halaman management export</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="899" ht="28" customHeight="1">
       <c r="A899" s="43" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="B899" s="3" t="inlineStr">
@@ -40079,7 +40081,7 @@
       </c>
       <c r="D899" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Membuka menu Management Export</t>
         </is>
       </c>
       <c r="E899" s="3" t="inlineStr">
@@ -40089,24 +40091,24 @@
       </c>
       <c r="F899" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G899" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Klik menu exported data management, klik submenu management export</t>
         </is>
       </c>
       <c r="H899" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Menampilkan halaman management export</t>
         </is>
       </c>
     </row>
     <row r="900" ht="42" customHeight="1">
       <c r="A900" s="43" t="inlineStr">
         <is>
-          <t>72.10</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="B900" s="3" t="inlineStr">
@@ -40121,7 +40123,7 @@
       </c>
       <c r="D900" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E900" s="3" t="inlineStr">
@@ -40131,24 +40133,24 @@
       </c>
       <c r="F900" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G900" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H900" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="901" ht="28" customHeight="1">
       <c r="A901" s="43" t="inlineStr">
         <is>
-          <t>72.11</t>
+          <t>72.10</t>
         </is>
       </c>
       <c r="B901" s="3" t="inlineStr">
@@ -40163,12 +40165,12 @@
       </c>
       <c r="D901" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E901" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F901" s="3" t="inlineStr">
@@ -40178,19 +40180,19 @@
       </c>
       <c r="G901" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H901" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="902" ht="28" customHeight="1">
       <c r="A902" s="43" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>72.11</t>
         </is>
       </c>
       <c r="B902" s="3" t="inlineStr">
@@ -40205,12 +40207,12 @@
       </c>
       <c r="D902" s="4" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E902" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F902" s="3" t="inlineStr">
@@ -40220,19 +40222,19 @@
       </c>
       <c r="G902" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H902" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="903" ht="28" customHeight="1">
       <c r="A903" s="43" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="B903" s="3" t="inlineStr">
@@ -40247,7 +40249,7 @@
       </c>
       <c r="D903" s="4" t="inlineStr">
         <is>
-          <t>Validasi card data file aktif dengan data table</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E903" s="3" t="inlineStr">
@@ -40257,12 +40259,12 @@
       </c>
       <c r="F903" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G903" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
         </is>
       </c>
       <c r="H903" s="4" t="inlineStr">
@@ -40274,7 +40276,7 @@
     <row r="904" ht="28" customHeight="1">
       <c r="A904" s="43" t="inlineStr">
         <is>
-          <t>72.14</t>
+          <t>72.13</t>
         </is>
       </c>
       <c r="B904" s="3" t="inlineStr">
@@ -40289,7 +40291,7 @@
       </c>
       <c r="D904" s="4" t="inlineStr">
         <is>
-          <t>Validasi card file kadaluwarsa dengan data table</t>
+          <t>Validasi card data file aktif dengan data table</t>
         </is>
       </c>
       <c r="E904" s="3" t="inlineStr">
@@ -40304,7 +40306,7 @@
       </c>
       <c r="G904" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
         </is>
       </c>
       <c r="H904" s="4" t="inlineStr">
@@ -40316,7 +40318,7 @@
     <row r="905" ht="28" customHeight="1">
       <c r="A905" s="43" t="inlineStr">
         <is>
-          <t>72.15</t>
+          <t>72.14</t>
         </is>
       </c>
       <c r="B905" s="3" t="inlineStr">
@@ -40331,7 +40333,7 @@
       </c>
       <c r="D905" s="4" t="inlineStr">
         <is>
-          <t>Validasi card reject dengan data table</t>
+          <t>Validasi card file kadaluwarsa dengan data table</t>
         </is>
       </c>
       <c r="E905" s="3" t="inlineStr">
@@ -40341,12 +40343,12 @@
       </c>
       <c r="F905" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G905" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
         </is>
       </c>
       <c r="H905" s="4" t="inlineStr">
@@ -40358,7 +40360,7 @@
     <row r="906" ht="42" customHeight="1">
       <c r="A906" s="43" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.15</t>
         </is>
       </c>
       <c r="B906" s="3" t="inlineStr">
@@ -40368,12 +40370,12 @@
       </c>
       <c r="C906" s="3" t="inlineStr">
         <is>
-          <t>Persetujuan export</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D906" s="4" t="inlineStr">
         <is>
-          <t>Lakukan login menggunakan user monitoring</t>
+          <t>Validasi card reject dengan data table</t>
         </is>
       </c>
       <c r="E906" s="3" t="inlineStr">
@@ -40383,24 +40385,24 @@
       </c>
       <c r="F906" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G906" s="4" t="inlineStr">
         <is>
-          <t>1. Login menggunakan user monitoring</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
         </is>
       </c>
       <c r="H906" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil melakukan login</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="907" ht="42" customHeight="1">
       <c r="A907" s="43" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="B907" s="3" t="inlineStr">
@@ -40415,7 +40417,7 @@
       </c>
       <c r="D907" s="4" t="inlineStr">
         <is>
-          <t>Membuka menu Persetujuan Export</t>
+          <t>Lakukan login menggunakan user monitoring</t>
         </is>
       </c>
       <c r="E907" s="3" t="inlineStr">
@@ -40425,59 +40427,101 @@
       </c>
       <c r="F907" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G907" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu exported data management, klik submenu persetujuan export</t>
+          <t>1. Login menggunakan user monitoring</t>
         </is>
       </c>
       <c r="H907" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan halaman persetujuan export</t>
+          <t>1. Berhasil melakukan login</t>
         </is>
       </c>
     </row>
     <row r="908" ht="28" customHeight="1">
       <c r="A908" s="43" t="inlineStr">
         <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="B908" s="3" t="inlineStr">
+        <is>
+          <t>Export data management</t>
+        </is>
+      </c>
+      <c r="C908" s="3" t="inlineStr">
+        <is>
+          <t>Persetujuan export</t>
+        </is>
+      </c>
+      <c r="D908" s="4" t="inlineStr">
+        <is>
+          <t>Membuka menu Persetujuan Export</t>
+        </is>
+      </c>
+      <c r="E908" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F908" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G908" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu exported data management, klik submenu persetujuan export</t>
+        </is>
+      </c>
+      <c r="H908" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan halaman persetujuan export</t>
+        </is>
+      </c>
+    </row>
+    <row r="909" ht="14" customHeight="1">
+      <c r="A909" s="43" t="inlineStr">
+        <is>
           <t>73.3</t>
         </is>
       </c>
-      <c r="B908" s="3" t="inlineStr">
+      <c r="B909" s="3" t="inlineStr">
         <is>
           <t>Export data management</t>
         </is>
       </c>
-      <c r="C908" s="3" t="inlineStr">
+      <c r="C909" s="3" t="inlineStr">
         <is>
           <t>Persetujuan export</t>
         </is>
       </c>
-      <c r="D908" s="4" t="inlineStr">
+      <c r="D909" s="4" t="inlineStr">
         <is>
           <t>Melakukan approval data pengajuan export</t>
         </is>
       </c>
-      <c r="E908" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F908" s="3" t="inlineStr">
+      <c r="E909" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F909" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G908" s="4" t="inlineStr">
+      <c r="G909" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon titik tiga pada data pengajuan.
 2. Klik menu Setuju.
 3. Klik button YA pada popup konfirmasi.</t>
         </is>
       </c>
-      <c r="H908" s="4" t="inlineStr">
+      <c r="H909" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan menu opsi.
 2. Berhasil menampilkan popup konfirmasi.
@@ -40485,49 +40529,48 @@
         </is>
       </c>
     </row>
-    <row r="909" ht="14" customHeight="1">
-      <c r="A909" s="43" t="inlineStr">
+    <row r="910" ht="28" customHeight="1">
+      <c r="A910" s="43" t="inlineStr">
         <is>
           <t>73.4</t>
         </is>
       </c>
-      <c r="B909" s="3" t="inlineStr">
+      <c r="B910" s="3" t="inlineStr">
         <is>
           <t>Export data management</t>
         </is>
       </c>
-      <c r="C909" s="3" t="inlineStr">
+      <c r="C910" s="3" t="inlineStr">
         <is>
           <t>Persetujuan export</t>
         </is>
       </c>
-      <c r="D909" s="4" t="inlineStr">
+      <c r="D910" s="4" t="inlineStr">
         <is>
           <t>Melakukan reject data pengajuan export</t>
         </is>
       </c>
-      <c r="E909" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F909" s="3" t="inlineStr">
+      <c r="E910" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F910" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G909" s="4" t="inlineStr">
+      <c r="G910" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon (titik tiga) klik tolak, input alasan, klik submit</t>
         </is>
       </c>
-      <c r="H909" s="4" t="inlineStr">
+      <c r="H910" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil melakukan reject data</t>
         </is>
       </c>
     </row>
-    <row r="910" ht="28" customHeight="1"/>
     <row r="911" ht="28" customHeight="1"/>
     <row r="912" ht="28" customHeight="1"/>
     <row r="913" ht="28" customHeight="1"/>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -37073,7 +37073,7 @@
       </c>
       <c r="D831" s="4" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Non PKS dan PKS</t>
+          <t>Menampilkan data Personal Funnel berdasarkan tab</t>
         </is>
       </c>
       <c r="E831" s="3" t="inlineStr">
@@ -37094,8 +37094,8 @@
       </c>
       <c r="H831" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data pada tab Non PKS.
-2. Berhasil menampilkan data pada tab PKS.</t>
+          <t>1. Berhasil menampilkan data Personal Funnel pada tab Non PKS.
+2. Berhasil menampilkan data Personal Funnel pada tab PKS.</t>
         </is>
       </c>
     </row>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -37088,14 +37088,16 @@
       </c>
       <c r="G831" s="4" t="inlineStr">
         <is>
-          <t>1. Klik tab Non PKS.
-2. Klik tab PKS.</t>
+          <t>1. Klik tab Semua.
+2. Klik tab Non PKS.
+3. Klik tab PKS.</t>
         </is>
       </c>
       <c r="H831" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data Personal Funnel pada tab Non PKS.
-2. Berhasil menampilkan data Personal Funnel pada tab PKS.</t>
+          <t>1. Berhasil menampilkan data Personal Funnel pada tab Semua.
+2. Berhasil menampilkan data Personal Funnel pada tab Non PKS.
+3. Berhasil menampilkan data Personal Funnel pada tab PKS.</t>
         </is>
       </c>
     </row>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z910"/>
+  <dimension ref="A1:Z908"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="12.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35498,10 +35498,8 @@
       </c>
     </row>
     <row r="796" ht="14" customHeight="1">
-      <c r="A796" s="43" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
+      <c r="A796" s="43" t="n">
+        <v>62.2</v>
       </c>
       <c r="B796" s="3" t="inlineStr">
         <is>
@@ -35515,7 +35513,7 @@
       </c>
       <c r="D796" s="4" t="inlineStr">
         <is>
-          <t>Menampilkan data Rekap Funnel</t>
+          <t>Melakukan filter data Rekap Funnel</t>
         </is>
       </c>
       <c r="E796" s="3" t="inlineStr">
@@ -35529,110 +35527,106 @@
         </is>
       </c>
       <c r="G796" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun).
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H796" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="797" ht="14" customHeight="1">
-      <c r="A797" s="43" t="inlineStr">
-        <is>
-          <t>62.3</t>
-        </is>
-      </c>
-      <c r="B797" s="3" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C797" s="3" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D797" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E797" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F797" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G797" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H797" s="4" t="inlineStr">
+      <c r="H796" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi kriteria filter.
 2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="798" ht="14" customHeight="1">
-      <c r="A798" s="43" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="B798" s="3" t="inlineStr">
+    <row r="797" ht="14" customHeight="1">
+      <c r="A797" s="43" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="B797" s="3" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C798" s="3" t="inlineStr">
+      <c r="C797" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D798" s="4" t="inlineStr">
+      <c r="D797" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E798" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F798" s="3" t="inlineStr">
+      <c r="E797" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F797" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G798" s="4" t="inlineStr">
+      <c r="G797" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H798" s="4" t="inlineStr">
+      <c r="H797" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
+    <row r="798" ht="14" customHeight="1">
+      <c r="A798" s="43" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="B798" s="3" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C798" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D798" s="4" t="inlineStr">
+        <is>
+          <t>Mengekspor data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E798" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F798" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G798" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Export.
+2. Klik icon download pada panel Download Export.</t>
+        </is>
+      </c>
+      <c r="H798" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan panel Download Export.
+2. Berhasil mendownload file export.</t>
+        </is>
+      </c>
+    </row>
     <row r="799" ht="14" customHeight="1">
       <c r="A799" s="43" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="B799" s="3" t="inlineStr">
@@ -35642,12 +35636,12 @@
       </c>
       <c r="C799" s="3" t="inlineStr">
         <is>
-          <t>Rekap Funnel</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D799" s="4" t="inlineStr">
         <is>
-          <t>Mengunduh data Rekap Funnel</t>
+          <t>Membuka halaman Pengaturan Funnel Funding</t>
         </is>
       </c>
       <c r="E799" s="3" t="inlineStr">
@@ -35662,19 +35656,21 @@
       </c>
       <c r="G799" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Download Excel.</t>
+          <t>1. Klik menu Report Funding.
+2. Klik sub menu Pengaturan Funnel.</t>
         </is>
       </c>
       <c r="H799" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mendownload file Excel data Rekap Funnel.</t>
+          <t>1. Berhasil membuka menu Report Funding.
+2. Berhasil menampilkan halaman Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
     <row r="800" ht="14" customHeight="1">
       <c r="A800" s="43" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="B800" s="3" t="inlineStr">
@@ -35689,7 +35685,7 @@
       </c>
       <c r="D800" s="4" t="inlineStr">
         <is>
-          <t>Membuka halaman Pengaturan Funnel Funding</t>
+          <t>Mengubah data Pengaturan Funnel Funding</t>
         </is>
       </c>
       <c r="E800" s="3" t="inlineStr">
@@ -35704,21 +35700,21 @@
       </c>
       <c r="G800" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu Report Funding.
-2. Klik sub menu Pengaturan Funnel.</t>
+          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H800" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Report Funding.
-2. Berhasil menampilkan halaman Pengaturan Funnel Funding.</t>
+          <t>1. Berhasil mengisi field Performance Percentage.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
     <row r="801" ht="14" customHeight="1">
       <c r="A801" s="43" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="B801" s="3" t="inlineStr">
@@ -35733,7 +35729,7 @@
       </c>
       <c r="D801" s="4" t="inlineStr">
         <is>
-          <t>Mengubah data Pengaturan Funnel Funding</t>
+          <t>Mengubah data Pengaturan Funnel Funding tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E801" s="3" t="inlineStr">
@@ -35748,21 +35744,21 @@
       </c>
       <c r="G801" s="4" t="inlineStr">
         <is>
-          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
+          <t>1. Mengosongkan field mandatory Performance Percentage.
 2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H801" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi field Performance Percentage.
-2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
+          <t>1. Berhasil mengosongkan field Performance Percentage.
+2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
     <row r="802" ht="14" customHeight="1">
       <c r="A802" s="43" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="B802" s="3" t="inlineStr">
@@ -35777,7 +35773,7 @@
       </c>
       <c r="D802" s="4" t="inlineStr">
         <is>
-          <t>Mengubah data Pengaturan Funnel Funding tanpa mengisi field mandatory</t>
+          <t>Menambahkan Kondisi pada Indikator Performa</t>
         </is>
       </c>
       <c r="E802" s="3" t="inlineStr">
@@ -35791,57 +35787,13 @@
         </is>
       </c>
       <c r="G802" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field mandatory Performance Percentage.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H802" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field Performance Percentage.
-2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="803" ht="14" customHeight="1">
-      <c r="A803" s="43" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="B803" s="3" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C803" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D803" s="4" t="inlineStr">
-        <is>
-          <t>Menambahkan Kondisi pada Indikator Performa</t>
-        </is>
-      </c>
-      <c r="E803" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F803" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G803" s="4" t="inlineStr">
         <is>
           <t>1. Klik button + Tambah Kondisi pada bagian Indikator Performa.
 2. Mengisi semua field mandatory pada kondisi baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H803" s="4" t="inlineStr">
+      <c r="H802" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan form kondisi baru pada Indikator Performa.
 2. Berhasil mengisi field mandatory kondisi.
@@ -35849,10 +35801,54 @@
         </is>
       </c>
     </row>
+    <row r="803" ht="14" customHeight="1">
+      <c r="A803" s="43" t="inlineStr">
+        <is>
+          <t>63.5</t>
+        </is>
+      </c>
+      <c r="B803" s="3" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C803" s="3" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D803" s="4" t="inlineStr">
+        <is>
+          <t>Menghapus Kondisi pada Indikator Performa</t>
+        </is>
+      </c>
+      <c r="E803" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F803" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G803" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Hapus pada salah satu kondisi di Indikator Performa.
+2. Klik button Simpan Pengaturan.</t>
+        </is>
+      </c>
+      <c r="H803" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menghapus kondisi dari Indikator Performa.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
+        </is>
+      </c>
+    </row>
     <row r="804" ht="14" customHeight="1">
       <c r="A804" s="43" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="B804" s="3" t="inlineStr">
@@ -35867,7 +35863,7 @@
       </c>
       <c r="D804" s="4" t="inlineStr">
         <is>
-          <t>Menghapus Kondisi pada Indikator Performa</t>
+          <t>Menambahkan Operator pada Kondisi</t>
         </is>
       </c>
       <c r="E804" s="3" t="inlineStr">
@@ -35881,57 +35877,13 @@
         </is>
       </c>
       <c r="G804" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Hapus pada salah satu kondisi di Indikator Performa.
-2. Klik button Simpan Pengaturan.</t>
-        </is>
-      </c>
-      <c r="H804" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menghapus kondisi dari Indikator Performa.
-2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="805" ht="14" customHeight="1">
-      <c r="A805" s="43" t="inlineStr">
-        <is>
-          <t>63.6</t>
-        </is>
-      </c>
-      <c r="B805" s="3" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C805" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D805" s="4" t="inlineStr">
-        <is>
-          <t>Menambahkan Operator pada Kondisi</t>
-        </is>
-      </c>
-      <c r="E805" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F805" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G805" s="4" t="inlineStr">
         <is>
           <t>1. Klik link tambah operator pada salah satu kondisi di Indikator Performa.
 2. Mengisi field operator baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H805" s="4" t="inlineStr">
+      <c r="H804" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan baris operator baru pada kondisi.
 2. Berhasil mengisi data operator.
@@ -35939,25 +35891,69 @@
         </is>
       </c>
     </row>
+    <row r="805" ht="14" customHeight="1">
+      <c r="A805" s="43" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="B805" s="3" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C805" s="3" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D805" s="4" t="inlineStr">
+        <is>
+          <t>Menghapus Operator pada Kondisi</t>
+        </is>
+      </c>
+      <c r="E805" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F805" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G805" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button x pada salah satu operator di Indikator Performa.
+2. Klik button Simpan Pengaturan.</t>
+        </is>
+      </c>
+      <c r="H805" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menghapus operator dari kondisi di Indikator Performa.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
+        </is>
+      </c>
+    </row>
     <row r="806" ht="14" customHeight="1">
       <c r="A806" s="43" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="B806" s="3" t="inlineStr">
         <is>
-          <t>Report Funding</t>
+          <t>Report Lending</t>
         </is>
       </c>
       <c r="C806" s="3" t="inlineStr">
         <is>
-          <t>Pengaturan Funnel</t>
+          <t>Daily Sales Agenda</t>
         </is>
       </c>
       <c r="D806" s="4" t="inlineStr">
         <is>
-          <t>Menghapus Operator pada Kondisi</t>
+          <t>Membuka halaman Daily Sales Agenda</t>
         </is>
       </c>
       <c r="E806" s="3" t="inlineStr">
@@ -35972,21 +35968,21 @@
       </c>
       <c r="G806" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button x pada salah satu operator di Indikator Performa.
-2. Klik button Simpan Pengaturan.</t>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Daily Sales Agenda.</t>
         </is>
       </c>
       <c r="H806" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menghapus operator dari kondisi di Indikator Performa.
-2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
         </is>
       </c>
     </row>
     <row r="807" ht="14" customHeight="1">
       <c r="A807" s="43" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="B807" s="3" t="inlineStr">
@@ -36001,7 +35997,7 @@
       </c>
       <c r="D807" s="4" t="inlineStr">
         <is>
-          <t>Membuka halaman Daily Sales Agenda</t>
+          <t>Melakukan filter data Daily Sales Agenda</t>
         </is>
       </c>
       <c r="E807" s="3" t="inlineStr">
@@ -36011,26 +36007,26 @@
       </c>
       <c r="F807" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G807" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Daily Sales Agenda.</t>
+          <t>1. Mengisi semua field filter mandatory.
+2. Klik button Filter Data.</t>
         </is>
       </c>
       <c r="H807" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
+          <t>1. Berhasil mengisi field filter mandatory.
+2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="808" ht="14" customHeight="1">
       <c r="A808" s="43" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="B808" s="3" t="inlineStr">
@@ -36045,7 +36041,7 @@
       </c>
       <c r="D808" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data Daily Sales Agenda</t>
+          <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E808" s="3" t="inlineStr">
@@ -36060,21 +36056,21 @@
       </c>
       <c r="G808" s="4" t="inlineStr">
         <is>
-          <t>1. Mengisi semua field filter mandatory.
+          <t>1. Mengosongkan field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
       <c r="H808" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+          <t>1. Berhasil mengosongkan field filter mandatory.
+2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="809" ht="14" customHeight="1">
       <c r="A809" s="43" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="B809" s="3" t="inlineStr">
@@ -36089,7 +36085,7 @@
       </c>
       <c r="D809" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
+          <t>Menampilkan data tab Prospek Masuk</t>
         </is>
       </c>
       <c r="E809" s="3" t="inlineStr">
@@ -36104,21 +36100,19 @@
       </c>
       <c r="G809" s="4" t="inlineStr">
         <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Filter Data.</t>
+          <t>1. Klik tab Prospek Masuk.</t>
         </is>
       </c>
       <c r="H809" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>1. Berhasil menampilkan data pada tab Prospek Masuk.</t>
         </is>
       </c>
     </row>
     <row r="810" ht="42" customHeight="1">
       <c r="A810" s="43" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="B810" s="3" t="inlineStr">
@@ -36133,7 +36127,7 @@
       </c>
       <c r="D810" s="4" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Masuk</t>
+          <t>Mencari data Prospek Masuk dengan keyword valid</t>
         </is>
       </c>
       <c r="E810" s="3" t="inlineStr">
@@ -36143,59 +36137,17 @@
       </c>
       <c r="F810" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G810" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Masuk.</t>
-        </is>
-      </c>
-      <c r="H810" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data pada tab Prospek Masuk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="811" ht="28" customHeight="1">
-      <c r="A811" s="43" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
-      <c r="B811" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C811" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D811" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data Prospek Masuk dengan keyword valid</t>
-        </is>
-      </c>
-      <c r="E811" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F811" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G811" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H811" s="4" t="inlineStr">
+      <c r="H810" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil mengisi field Cari Data.
@@ -36203,45 +36155,45 @@
         </is>
       </c>
     </row>
-    <row r="812" ht="42" customHeight="1">
-      <c r="A812" s="43" t="inlineStr">
+    <row r="811" ht="28" customHeight="1">
+      <c r="A811" s="43" t="inlineStr">
         <is>
           <t>64.6</t>
         </is>
       </c>
-      <c r="B812" s="3" t="inlineStr">
+      <c r="B811" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C812" s="3" t="inlineStr">
+      <c r="C811" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D812" s="4" t="inlineStr">
+      <c r="D811" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E812" s="3" t="inlineStr">
+      <c r="E811" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F812" s="3" t="inlineStr">
+      <c r="F811" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G812" s="4" t="inlineStr">
+      <c r="G811" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H812" s="4" t="inlineStr">
+      <c r="H811" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil mengisi field Cari Data.
@@ -36249,10 +36201,54 @@
         </is>
       </c>
     </row>
+    <row r="812" ht="42" customHeight="1">
+      <c r="A812" s="43" t="inlineStr">
+        <is>
+          <t>64.7</t>
+        </is>
+      </c>
+      <c r="B812" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C812" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D812" s="4" t="inlineStr">
+        <is>
+          <t>Melihat detail Prospek Masuk</t>
+        </is>
+      </c>
+      <c r="E812" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F812" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G812" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Masuk.
+2. Klik salah satu nama prospek pada tabel.</t>
+        </is>
+      </c>
+      <c r="H812" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Masuk.
+2. Berhasil menampilkan halaman detail prospek.</t>
+        </is>
+      </c>
+    </row>
     <row r="813" ht="28" customHeight="1">
       <c r="A813" s="43" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="B813" s="3" t="inlineStr">
@@ -36267,7 +36263,7 @@
       </c>
       <c r="D813" s="4" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Masuk</t>
+          <t>Mengekspor data tab Prospek Masuk</t>
         </is>
       </c>
       <c r="E813" s="3" t="inlineStr">
@@ -36277,61 +36273,17 @@
       </c>
       <c r="F813" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G813" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Masuk.
-2. Klik salah satu nama prospek pada tabel.</t>
-        </is>
-      </c>
-      <c r="H813" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Masuk.
-2. Berhasil menampilkan halaman detail prospek.</t>
-        </is>
-      </c>
-    </row>
-    <row r="814" ht="28" customHeight="1">
-      <c r="A814" s="43" t="inlineStr">
-        <is>
-          <t>64.8</t>
-        </is>
-      </c>
-      <c r="B814" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C814" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D814" s="4" t="inlineStr">
-        <is>
-          <t>Mengekspor data tab Prospek Masuk</t>
-        </is>
-      </c>
-      <c r="E814" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F814" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G814" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H814" s="4" t="inlineStr">
+      <c r="H813" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil menampilkan panel Download Export.
@@ -36339,10 +36291,52 @@
         </is>
       </c>
     </row>
+    <row r="814" ht="28" customHeight="1">
+      <c r="A814" s="43" t="inlineStr">
+        <is>
+          <t>64.9</t>
+        </is>
+      </c>
+      <c r="B814" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C814" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D814" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data tab Prospek Closing</t>
+        </is>
+      </c>
+      <c r="E814" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F814" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G814" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Closing.</t>
+        </is>
+      </c>
+      <c r="H814" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data pada tab Prospek Closing.</t>
+        </is>
+      </c>
+    </row>
     <row r="815" ht="56" customHeight="1">
       <c r="A815" s="43" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>64.10</t>
         </is>
       </c>
       <c r="B815" s="3" t="inlineStr">
@@ -36357,7 +36351,7 @@
       </c>
       <c r="D815" s="4" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Closing</t>
+          <t>Mencari data Prospek Closing dengan keyword valid</t>
         </is>
       </c>
       <c r="E815" s="3" t="inlineStr">
@@ -36367,59 +36361,17 @@
       </c>
       <c r="F815" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G815" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Closing.</t>
-        </is>
-      </c>
-      <c r="H815" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data pada tab Prospek Closing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="816" ht="56" customHeight="1">
-      <c r="A816" s="43" t="inlineStr">
-        <is>
-          <t>64.10</t>
-        </is>
-      </c>
-      <c r="B816" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C816" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D816" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data Prospek Closing dengan keyword valid</t>
-        </is>
-      </c>
-      <c r="E816" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F816" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G816" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H816" s="4" t="inlineStr">
+      <c r="H815" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil mengisi field Cari Data.
@@ -36427,45 +36379,45 @@
         </is>
       </c>
     </row>
-    <row r="817" ht="28" customHeight="1">
-      <c r="A817" s="43" t="inlineStr">
+    <row r="816" ht="56" customHeight="1">
+      <c r="A816" s="43" t="inlineStr">
         <is>
           <t>64.11</t>
         </is>
       </c>
-      <c r="B817" s="3" t="inlineStr">
+      <c r="B816" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C817" s="3" t="inlineStr">
+      <c r="C816" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D817" s="4" t="inlineStr">
+      <c r="D816" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E817" s="3" t="inlineStr">
+      <c r="E816" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F817" s="3" t="inlineStr">
+      <c r="F816" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G817" s="4" t="inlineStr">
+      <c r="G816" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H817" s="4" t="inlineStr">
+      <c r="H816" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil mengisi field Cari Data.
@@ -36473,10 +36425,54 @@
         </is>
       </c>
     </row>
+    <row r="817" ht="28" customHeight="1">
+      <c r="A817" s="43" t="inlineStr">
+        <is>
+          <t>64.12</t>
+        </is>
+      </c>
+      <c r="B817" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C817" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D817" s="4" t="inlineStr">
+        <is>
+          <t>Melihat detail Prospek Closing</t>
+        </is>
+      </c>
+      <c r="E817" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F817" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G817" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Closing.
+2. Klik salah satu nama prospek pada tabel.</t>
+        </is>
+      </c>
+      <c r="H817" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Closing.
+2. Berhasil menampilkan halaman detail prospek.</t>
+        </is>
+      </c>
+    </row>
     <row r="818" ht="28" customHeight="1">
       <c r="A818" s="43" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.13</t>
         </is>
       </c>
       <c r="B818" s="3" t="inlineStr">
@@ -36491,7 +36487,7 @@
       </c>
       <c r="D818" s="4" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Closing</t>
+          <t>Mengekspor data tab Prospek Closing</t>
         </is>
       </c>
       <c r="E818" s="3" t="inlineStr">
@@ -36501,61 +36497,17 @@
       </c>
       <c r="F818" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G818" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Closing.
-2. Klik salah satu nama prospek pada tabel.</t>
-        </is>
-      </c>
-      <c r="H818" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Closing.
-2. Berhasil menampilkan halaman detail prospek.</t>
-        </is>
-      </c>
-    </row>
-    <row r="819" ht="42" customHeight="1">
-      <c r="A819" s="43" t="inlineStr">
-        <is>
-          <t>64.13</t>
-        </is>
-      </c>
-      <c r="B819" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C819" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D819" s="4" t="inlineStr">
-        <is>
-          <t>Mengekspor data tab Prospek Closing</t>
-        </is>
-      </c>
-      <c r="E819" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F819" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G819" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H819" s="4" t="inlineStr">
+      <c r="H818" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil menampilkan panel Download Export.
@@ -36563,10 +36515,52 @@
         </is>
       </c>
     </row>
+    <row r="819" ht="42" customHeight="1">
+      <c r="A819" s="43" t="inlineStr">
+        <is>
+          <t>64.14</t>
+        </is>
+      </c>
+      <c r="B819" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C819" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D819" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data tab Prospek Referal</t>
+        </is>
+      </c>
+      <c r="E819" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F819" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G819" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal.</t>
+        </is>
+      </c>
+      <c r="H819" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data pada tab Prospek Referal.</t>
+        </is>
+      </c>
+    </row>
     <row r="820" ht="14" customHeight="1">
       <c r="A820" s="43" t="inlineStr">
         <is>
-          <t>64.14</t>
+          <t>64.15</t>
         </is>
       </c>
       <c r="B820" s="3" t="inlineStr">
@@ -36581,7 +36575,7 @@
       </c>
       <c r="D820" s="4" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Referal</t>
+          <t>Mencari data Prospek Referal dengan keyword valid</t>
         </is>
       </c>
       <c r="E820" s="3" t="inlineStr">
@@ -36591,59 +36585,17 @@
       </c>
       <c r="F820" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G820" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal.</t>
-        </is>
-      </c>
-      <c r="H820" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data pada tab Prospek Referal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="821" ht="56" customHeight="1">
-      <c r="A821" s="43" t="inlineStr">
-        <is>
-          <t>64.15</t>
-        </is>
-      </c>
-      <c r="B821" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C821" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D821" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data Prospek Referal dengan keyword valid</t>
-        </is>
-      </c>
-      <c r="E821" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F821" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G821" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H821" s="4" t="inlineStr">
+      <c r="H820" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil mengisi field Cari Data.
@@ -36651,45 +36603,45 @@
         </is>
       </c>
     </row>
-    <row r="822" ht="56" customHeight="1">
-      <c r="A822" s="43" t="inlineStr">
+    <row r="821" ht="56" customHeight="1">
+      <c r="A821" s="43" t="inlineStr">
         <is>
           <t>64.16</t>
         </is>
       </c>
-      <c r="B822" s="3" t="inlineStr">
+      <c r="B821" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C822" s="3" t="inlineStr">
+      <c r="C821" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D822" s="4" t="inlineStr">
+      <c r="D821" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E822" s="3" t="inlineStr">
+      <c r="E821" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F822" s="3" t="inlineStr">
+      <c r="F821" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G822" s="4" t="inlineStr">
+      <c r="G821" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H822" s="4" t="inlineStr">
+      <c r="H821" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil mengisi field Cari Data.
@@ -36697,10 +36649,54 @@
         </is>
       </c>
     </row>
+    <row r="822" ht="56" customHeight="1">
+      <c r="A822" s="43" t="inlineStr">
+        <is>
+          <t>64.17</t>
+        </is>
+      </c>
+      <c r="B822" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C822" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D822" s="4" t="inlineStr">
+        <is>
+          <t>Melihat detail Prospek Referal</t>
+        </is>
+      </c>
+      <c r="E822" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F822" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G822" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal.
+2. Klik salah satu nama prospek pada tabel.</t>
+        </is>
+      </c>
+      <c r="H822" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Referal.
+2. Berhasil menampilkan halaman detail prospek.</t>
+        </is>
+      </c>
+    </row>
     <row r="823" ht="56" customHeight="1">
       <c r="A823" s="43" t="inlineStr">
         <is>
-          <t>64.17</t>
+          <t>64.18</t>
         </is>
       </c>
       <c r="B823" s="3" t="inlineStr">
@@ -36715,7 +36711,7 @@
       </c>
       <c r="D823" s="4" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Referal</t>
+          <t>Mengekspor data tab Prospek Referal</t>
         </is>
       </c>
       <c r="E823" s="3" t="inlineStr">
@@ -36725,61 +36721,17 @@
       </c>
       <c r="F823" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G823" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal.
-2. Klik salah satu nama prospek pada tabel.</t>
-        </is>
-      </c>
-      <c r="H823" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Referal.
-2. Berhasil menampilkan halaman detail prospek.</t>
-        </is>
-      </c>
-    </row>
-    <row r="824" ht="14" customHeight="1">
-      <c r="A824" s="43" t="inlineStr">
-        <is>
-          <t>64.18</t>
-        </is>
-      </c>
-      <c r="B824" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C824" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D824" s="4" t="inlineStr">
-        <is>
-          <t>Mengekspor data tab Prospek Referal</t>
-        </is>
-      </c>
-      <c r="E824" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F824" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G824" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H824" s="4" t="inlineStr">
+      <c r="H823" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil menampilkan panel Download Export.
@@ -36787,10 +36739,52 @@
         </is>
       </c>
     </row>
+    <row r="824" ht="14" customHeight="1">
+      <c r="A824" s="43" t="inlineStr">
+        <is>
+          <t>64.19</t>
+        </is>
+      </c>
+      <c r="B824" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C824" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D824" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data tab Prospek Referal Closing</t>
+        </is>
+      </c>
+      <c r="E824" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F824" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G824" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal Closing.</t>
+        </is>
+      </c>
+      <c r="H824" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
+        </is>
+      </c>
+    </row>
     <row r="825" ht="14" customHeight="1">
       <c r="A825" s="43" t="inlineStr">
         <is>
-          <t>64.19</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="B825" s="3" t="inlineStr">
@@ -36805,7 +36799,7 @@
       </c>
       <c r="D825" s="4" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Referal Closing</t>
+          <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
         </is>
       </c>
       <c r="E825" s="3" t="inlineStr">
@@ -36815,59 +36809,17 @@
       </c>
       <c r="F825" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G825" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal Closing.</t>
-        </is>
-      </c>
-      <c r="H825" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="826" ht="14" customHeight="1">
-      <c r="A826" s="43" t="inlineStr">
-        <is>
-          <t>64.20</t>
-        </is>
-      </c>
-      <c r="B826" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C826" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D826" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
-        </is>
-      </c>
-      <c r="E826" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F826" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G826" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H826" s="4" t="inlineStr">
+      <c r="H825" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil mengisi field Cari Data.
@@ -36875,45 +36827,45 @@
         </is>
       </c>
     </row>
-    <row r="827" ht="42" customHeight="1">
-      <c r="A827" s="43" t="inlineStr">
+    <row r="826" ht="14" customHeight="1">
+      <c r="A826" s="43" t="inlineStr">
         <is>
           <t>64.21</t>
         </is>
       </c>
-      <c r="B827" s="3" t="inlineStr">
+      <c r="B826" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C827" s="3" t="inlineStr">
+      <c r="C826" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D827" s="4" t="inlineStr">
+      <c r="D826" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal Closing dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E827" s="3" t="inlineStr">
+      <c r="E826" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F827" s="3" t="inlineStr">
+      <c r="F826" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G827" s="4" t="inlineStr">
+      <c r="G826" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H827" s="4" t="inlineStr">
+      <c r="H826" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil mengisi field Cari Data.
@@ -36921,10 +36873,54 @@
         </is>
       </c>
     </row>
+    <row r="827" ht="42" customHeight="1">
+      <c r="A827" s="43" t="inlineStr">
+        <is>
+          <t>64.22</t>
+        </is>
+      </c>
+      <c r="B827" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C827" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D827" s="4" t="inlineStr">
+        <is>
+          <t>Melihat detail Prospek Referal Closing</t>
+        </is>
+      </c>
+      <c r="E827" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F827" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G827" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal Closing.
+2. Klik salah satu nama prospek pada tabel.</t>
+        </is>
+      </c>
+      <c r="H827" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan tab Prospek Referal Closing.
+2. Berhasil menampilkan halaman detail prospek.</t>
+        </is>
+      </c>
+    </row>
     <row r="828" ht="14" customHeight="1">
       <c r="A828" s="43" t="inlineStr">
         <is>
-          <t>64.22</t>
+          <t>64.23</t>
         </is>
       </c>
       <c r="B828" s="3" t="inlineStr">
@@ -36939,7 +36935,7 @@
       </c>
       <c r="D828" s="4" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Referal Closing</t>
+          <t>Mengekspor data tab Prospek Referal Closing</t>
         </is>
       </c>
       <c r="E828" s="3" t="inlineStr">
@@ -36949,61 +36945,17 @@
       </c>
       <c r="F828" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G828" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal Closing.
-2. Klik salah satu nama prospek pada tabel.</t>
-        </is>
-      </c>
-      <c r="H828" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan tab Prospek Referal Closing.
-2. Berhasil menampilkan halaman detail prospek.</t>
-        </is>
-      </c>
-    </row>
-    <row r="829" ht="56" customHeight="1">
-      <c r="A829" s="43" t="inlineStr">
-        <is>
-          <t>64.23</t>
-        </is>
-      </c>
-      <c r="B829" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C829" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D829" s="4" t="inlineStr">
-        <is>
-          <t>Mengekspor data tab Prospek Referal Closing</t>
-        </is>
-      </c>
-      <c r="E829" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F829" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G829" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H829" s="4" t="inlineStr">
+      <c r="H828" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil menampilkan panel Download Export.
@@ -37011,10 +36963,54 @@
         </is>
       </c>
     </row>
+    <row r="829" ht="56" customHeight="1">
+      <c r="A829" s="43" t="inlineStr">
+        <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="B829" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C829" s="3" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D829" s="4" t="inlineStr">
+        <is>
+          <t>Membuka halaman Personal Funnel</t>
+        </is>
+      </c>
+      <c r="E829" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F829" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G829" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Personal Funnel.</t>
+        </is>
+      </c>
+      <c r="H829" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Personal Funnel.</t>
+        </is>
+      </c>
+    </row>
     <row r="830" ht="28" customHeight="1">
       <c r="A830" s="43" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="B830" s="3" t="inlineStr">
@@ -37029,7 +37025,7 @@
       </c>
       <c r="D830" s="4" t="inlineStr">
         <is>
-          <t>Membuka halaman Personal Funnel</t>
+          <t>Menampilkan data Personal Funnel berdasarkan tab</t>
         </is>
       </c>
       <c r="E830" s="3" t="inlineStr">
@@ -37039,61 +37035,17 @@
       </c>
       <c r="F830" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G830" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Personal Funnel.</t>
-        </is>
-      </c>
-      <c r="H830" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Personal Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="831" ht="42" customHeight="1">
-      <c r="A831" s="43" t="inlineStr">
-        <is>
-          <t>65.2</t>
-        </is>
-      </c>
-      <c r="B831" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C831" s="3" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
-      <c r="D831" s="4" t="inlineStr">
-        <is>
-          <t>Menampilkan data Personal Funnel berdasarkan tab</t>
-        </is>
-      </c>
-      <c r="E831" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F831" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G831" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Semua.
 2. Klik tab Non PKS.
 3. Klik tab PKS.</t>
         </is>
       </c>
-      <c r="H831" s="4" t="inlineStr">
+      <c r="H830" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data Personal Funnel pada tab Semua.
 2. Berhasil menampilkan data Personal Funnel pada tab Non PKS.
@@ -37101,10 +37053,54 @@
         </is>
       </c>
     </row>
+    <row r="831" ht="42" customHeight="1">
+      <c r="A831" s="43" t="inlineStr">
+        <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="B831" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C831" s="3" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D831" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Personal Funnel</t>
+        </is>
+      </c>
+      <c r="E831" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F831" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G831" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengisi semua field filter mandatory.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H831" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi field filter mandatory.
+2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+        </is>
+      </c>
+    </row>
     <row r="832" ht="28" customHeight="1">
       <c r="A832" s="43" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="B832" s="3" t="inlineStr">
@@ -37119,7 +37115,7 @@
       </c>
       <c r="D832" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data Personal Funnel</t>
+          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E832" s="3" t="inlineStr">
@@ -37134,21 +37130,21 @@
       </c>
       <c r="G832" s="4" t="inlineStr">
         <is>
-          <t>1. Mengisi semua field filter mandatory.
+          <t>1. Mengosongkan field filter mandatory.
 2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H832" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+          <t>1. Berhasil mengosongkan field filter mandatory.
+2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="833" ht="14" customHeight="1">
       <c r="A833" s="43" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="B833" s="3" t="inlineStr">
@@ -37163,7 +37159,7 @@
       </c>
       <c r="D833" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
+          <t>Mengekspor data Personal Funnel</t>
         </is>
       </c>
       <c r="E833" s="3" t="inlineStr">
@@ -37173,202 +37169,196 @@
       </c>
       <c r="F833" s="3" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G833" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Export.
+2. Klik icon download pada panel Download Export.</t>
+        </is>
+      </c>
+      <c r="H833" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan panel Download Export.
+2. Berhasil mendownload file export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="834" ht="14" customHeight="1">
+      <c r="A834" s="43" t="inlineStr">
+        <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="B834" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C834" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D834" s="4" t="inlineStr">
+        <is>
+          <t>Membuka halaman Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E834" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F834" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G834" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Rekap Funnel.</t>
+        </is>
+      </c>
+      <c r="H834" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Rekap Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="835" ht="14" customHeight="1">
+      <c r="A835" s="43" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="B835" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C835" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D835" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E835" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F835" s="3" t="inlineStr">
+        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G833" s="4" t="inlineStr">
+      <c r="G835" s="4" t="inlineStr">
+        <is>
+          <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H835" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi kriteria filter.
+2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="836" ht="42" customHeight="1">
+      <c r="A836" s="43" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="B836" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C836" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D836" s="4" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E836" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F836" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G836" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H833" s="4" t="inlineStr">
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H836" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
-    <row r="834" ht="14" customHeight="1">
-      <c r="A834" s="43" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="B834" s="3" t="inlineStr">
+    <row r="837" ht="28" customHeight="1">
+      <c r="A837" s="43" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="B837" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C834" s="3" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
-      <c r="D834" s="4" t="inlineStr">
-        <is>
-          <t>Mengekspor data Personal Funnel</t>
-        </is>
-      </c>
-      <c r="E834" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F834" s="3" t="inlineStr">
+      <c r="C837" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D837" s="4" t="inlineStr">
+        <is>
+          <t>Mengekspor data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E837" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F837" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G834" s="4" t="inlineStr">
+      <c r="G837" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Export.
 2. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H834" s="4" t="inlineStr">
+      <c r="H837" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan panel Download Export.
 2. Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
-    <row r="835" ht="14" customHeight="1">
-      <c r="A835" s="43" t="inlineStr">
-        <is>
-          <t>66.1</t>
-        </is>
-      </c>
-      <c r="B835" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C835" s="3" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D835" s="4" t="inlineStr">
-        <is>
-          <t>Membuka halaman Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E835" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F835" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G835" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Rekap Funnel.</t>
-        </is>
-      </c>
-      <c r="H835" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Rekap Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="836" ht="42" customHeight="1">
-      <c r="A836" s="43" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="B836" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C836" s="3" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D836" s="4" t="inlineStr">
-        <is>
-          <t>Menampilkan data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E836" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F836" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G836" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun).
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H836" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="837" ht="28" customHeight="1">
-      <c r="A837" s="43" t="inlineStr">
-        <is>
-          <t>66.3</t>
-        </is>
-      </c>
-      <c r="B837" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C837" s="3" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D837" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E837" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F837" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G837" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H837" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi kriteria filter.
-2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
-        </is>
-      </c>
-    </row>
     <row r="838" ht="28" customHeight="1">
       <c r="A838" s="43" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="B838" s="3" t="inlineStr">
@@ -37378,12 +37368,12 @@
       </c>
       <c r="C838" s="3" t="inlineStr">
         <is>
-          <t>Rekap Funnel</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D838" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
+          <t>Membuka halaman Pengaturan Funnel Lending</t>
         </is>
       </c>
       <c r="E838" s="3" t="inlineStr">
@@ -37393,26 +37383,26 @@
       </c>
       <c r="F838" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G838" s="4" t="inlineStr">
         <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Filter Data.</t>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Pengaturan Funnel.</t>
         </is>
       </c>
       <c r="H838" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
     <row r="839" ht="70" customHeight="1">
       <c r="A839" s="43" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="B839" s="3" t="inlineStr">
@@ -37422,12 +37412,12 @@
       </c>
       <c r="C839" s="3" t="inlineStr">
         <is>
-          <t>Rekap Funnel</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D839" s="4" t="inlineStr">
         <is>
-          <t>Mengunduh data Rekap Funnel</t>
+          <t>Mengubah data Pengaturan Funnel Lending</t>
         </is>
       </c>
       <c r="E839" s="3" t="inlineStr">
@@ -37442,19 +37432,21 @@
       </c>
       <c r="G839" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Download Excel.</t>
+          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
+2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H839" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mendownload file Excel data Rekap Funnel.</t>
+          <t>1. Berhasil mengisi field Performance Percentage.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
     <row r="840" ht="28" customHeight="1">
       <c r="A840" s="43" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="B840" s="3" t="inlineStr">
@@ -37469,7 +37461,7 @@
       </c>
       <c r="D840" s="4" t="inlineStr">
         <is>
-          <t>Membuka halaman Pengaturan Funnel Lending</t>
+          <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E840" s="3" t="inlineStr">
@@ -37484,21 +37476,21 @@
       </c>
       <c r="G840" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Pengaturan Funnel.</t>
+          <t>1. Mengosongkan field mandatory Performance Percentage.
+2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
       <c r="H840" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Pengaturan Funnel Lending.</t>
+          <t>1. Berhasil mengosongkan field Performance Percentage.
+2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
     <row r="841" ht="84" customHeight="1">
       <c r="A841" s="43" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="B841" s="3" t="inlineStr">
@@ -37513,7 +37505,7 @@
       </c>
       <c r="D841" s="4" t="inlineStr">
         <is>
-          <t>Mengubah data Pengaturan Funnel Lending</t>
+          <t>Menambahkan Kondisi pada Indikator Performa</t>
         </is>
       </c>
       <c r="E841" s="3" t="inlineStr">
@@ -37527,101 +37519,13 @@
         </is>
       </c>
       <c r="G841" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
-2. Klik button Simpan Pengaturan.</t>
-        </is>
-      </c>
-      <c r="H841" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field Performance Percentage.
-2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="842" ht="28" customHeight="1">
-      <c r="A842" s="43" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="B842" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C842" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D842" s="4" t="inlineStr">
-        <is>
-          <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E842" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F842" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G842" s="4" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field mandatory Performance Percentage.
-2. Klik button Simpan Pengaturan.</t>
-        </is>
-      </c>
-      <c r="H842" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field Performance Percentage.
-2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="843" ht="28" customHeight="1">
-      <c r="A843" s="43" t="inlineStr">
-        <is>
-          <t>67.4</t>
-        </is>
-      </c>
-      <c r="B843" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C843" s="3" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D843" s="4" t="inlineStr">
-        <is>
-          <t>Menambahkan Kondisi pada Indikator Performa</t>
-        </is>
-      </c>
-      <c r="E843" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F843" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G843" s="4" t="inlineStr">
         <is>
           <t>1. Klik button + Tambah Kondisi pada bagian Indikator Performa.
 2. Mengisi semua field mandatory pada kondisi baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H843" s="4" t="inlineStr">
+      <c r="H841" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan form kondisi baru pada Indikator Performa.
 2. Berhasil mengisi field mandatory kondisi.
@@ -37629,89 +37533,89 @@
         </is>
       </c>
     </row>
-    <row r="844" ht="28" customHeight="1">
-      <c r="A844" s="43" t="inlineStr">
+    <row r="842" ht="28" customHeight="1">
+      <c r="A842" s="43" t="inlineStr">
         <is>
           <t>67.5</t>
         </is>
       </c>
-      <c r="B844" s="3" t="inlineStr">
+      <c r="B842" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C844" s="3" t="inlineStr">
+      <c r="C842" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D844" s="4" t="inlineStr">
+      <c r="D842" s="4" t="inlineStr">
         <is>
           <t>Menghapus Kondisi pada Indikator Performa</t>
         </is>
       </c>
-      <c r="E844" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F844" s="3" t="inlineStr">
+      <c r="E842" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F842" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G844" s="4" t="inlineStr">
+      <c r="G842" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Hapus pada salah satu kondisi di Indikator Performa.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H844" s="4" t="inlineStr">
+      <c r="H842" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menghapus kondisi dari Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="845" ht="42" customHeight="1">
-      <c r="A845" s="43" t="inlineStr">
+    <row r="843" ht="28" customHeight="1">
+      <c r="A843" s="43" t="inlineStr">
         <is>
           <t>67.6</t>
         </is>
       </c>
-      <c r="B845" s="3" t="inlineStr">
+      <c r="B843" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C845" s="3" t="inlineStr">
+      <c r="C843" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D845" s="4" t="inlineStr">
+      <c r="D843" s="4" t="inlineStr">
         <is>
           <t>Menambahkan Operator pada Kondisi</t>
         </is>
       </c>
-      <c r="E845" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F845" s="3" t="inlineStr">
+      <c r="E843" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F843" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G845" s="4" t="inlineStr">
+      <c r="G843" s="4" t="inlineStr">
         <is>
           <t>1. Klik link tambah operator pada salah satu kondisi di Indikator Performa.
 2. Mengisi field operator baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H845" s="4" t="inlineStr">
+      <c r="H843" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan baris operator baru pada kondisi.
 2. Berhasil mengisi data operator.
@@ -37719,25 +37623,113 @@
         </is>
       </c>
     </row>
+    <row r="844" ht="28" customHeight="1">
+      <c r="A844" s="43" t="inlineStr">
+        <is>
+          <t>67.7</t>
+        </is>
+      </c>
+      <c r="B844" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C844" s="3" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D844" s="4" t="inlineStr">
+        <is>
+          <t>Menghapus Operator pada Kondisi</t>
+        </is>
+      </c>
+      <c r="E844" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F844" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G844" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button x pada salah satu operator di Indikator Performa.
+2. Klik button Simpan Pengaturan.</t>
+        </is>
+      </c>
+      <c r="H844" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menghapus operator dari kondisi di Indikator Performa.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="845" ht="42" customHeight="1">
+      <c r="A845" s="43" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="B845" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C845" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D845" s="4" t="inlineStr">
+        <is>
+          <t>Membuka halaman Approval non Banking</t>
+        </is>
+      </c>
+      <c r="E845" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F845" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G845" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu Re-Assign &amp; Approval 
+2. Klik submenu Approval non banking</t>
+        </is>
+      </c>
+      <c r="H845" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan submenu Re-Assign &amp; Approval 
+2. Menampilkan halaman Approval non banking</t>
+        </is>
+      </c>
+    </row>
     <row r="846" ht="28" customHeight="1">
       <c r="A846" s="43" t="inlineStr">
         <is>
-          <t>67.7</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="B846" s="3" t="inlineStr">
         <is>
-          <t>Report Lending</t>
+          <t>Re-Assign dan Approval</t>
         </is>
       </c>
       <c r="C846" s="3" t="inlineStr">
         <is>
-          <t>Pengaturan Funnel</t>
+          <t>Approval Non Banking</t>
         </is>
       </c>
       <c r="D846" s="4" t="inlineStr">
         <is>
-          <t>Menghapus Operator pada Kondisi</t>
+          <t>Melihat Detail data Approval non banking</t>
         </is>
       </c>
       <c r="E846" s="3" t="inlineStr">
@@ -37752,21 +37744,21 @@
       </c>
       <c r="G846" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button x pada salah satu operator di Indikator Performa.
-2. Klik button Simpan Pengaturan.</t>
+          <t>1. Klik titik tiga 
+2. Klik Detail</t>
         </is>
       </c>
       <c r="H846" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menghapus operator dari kondisi di Indikator Performa.
-2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
+          <t>1. Menampilkan beberapa action (detail, setujui, tolak)
+2. Menampilkan halaman detail data approval non banking</t>
         </is>
       </c>
     </row>
     <row r="847" ht="14" customHeight="1">
       <c r="A847" s="43" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="B847" s="3" t="inlineStr">
@@ -37781,7 +37773,7 @@
       </c>
       <c r="D847" s="4" t="inlineStr">
         <is>
-          <t>Membuka halaman Approval non Banking</t>
+          <t>Menyetujui Prospek</t>
         </is>
       </c>
       <c r="E847" s="3" t="inlineStr">
@@ -37791,98 +37783,10 @@
       </c>
       <c r="F847" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G847" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Re-Assign &amp; Approval 
-2. Klik submenu Approval non banking</t>
-        </is>
-      </c>
-      <c r="H847" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan submenu Re-Assign &amp; Approval 
-2. Menampilkan halaman Approval non banking</t>
-        </is>
-      </c>
-    </row>
-    <row r="848" ht="14" customHeight="1">
-      <c r="A848" s="43" t="inlineStr">
-        <is>
-          <t>68.2</t>
-        </is>
-      </c>
-      <c r="B848" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C848" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D848" s="4" t="inlineStr">
-        <is>
-          <t>Melihat Detail data Approval non banking</t>
-        </is>
-      </c>
-      <c r="E848" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F848" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G848" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik titik tiga 
-2. Klik Detail</t>
-        </is>
-      </c>
-      <c r="H848" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan beberapa action (detail, setujui, tolak)
-2. Menampilkan halaman detail data approval non banking</t>
-        </is>
-      </c>
-    </row>
-    <row r="849" ht="42" customHeight="1">
-      <c r="A849" s="43" t="inlineStr">
-        <is>
-          <t>68.3</t>
-        </is>
-      </c>
-      <c r="B849" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C849" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D849" s="4" t="inlineStr">
-        <is>
-          <t>Menyetujui Prospek</t>
-        </is>
-      </c>
-      <c r="E849" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F849" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G849" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Setujui 
@@ -37891,7 +37795,7 @@
 5. Klik button Setujui</t>
         </is>
       </c>
-      <c r="H849" s="4" t="inlineStr">
+      <c r="H847" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan modal approve 
@@ -37901,87 +37805,87 @@
         </is>
       </c>
     </row>
-    <row r="850" ht="28" customHeight="1">
-      <c r="A850" s="43" t="inlineStr">
+    <row r="848" ht="14" customHeight="1">
+      <c r="A848" s="43" t="inlineStr">
         <is>
           <t>68.4</t>
         </is>
       </c>
-      <c r="B850" s="3" t="inlineStr">
+      <c r="B848" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C850" s="3" t="inlineStr">
+      <c r="C848" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D850" s="4" t="inlineStr">
+      <c r="D848" s="4" t="inlineStr">
         <is>
           <t>Batal menyetujui Prospek</t>
         </is>
       </c>
-      <c r="E850" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F850" s="3" t="inlineStr">
+      <c r="E848" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F848" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G850" s="4" t="inlineStr">
+      <c r="G848" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Batalkan pada modal approve</t>
         </is>
       </c>
-      <c r="H850" s="4" t="inlineStr">
+      <c r="H848" s="4" t="inlineStr">
         <is>
           <t>1. Modal approve tertutup dan tetap di halaman approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="851" ht="28" customHeight="1">
-      <c r="A851" s="43" t="inlineStr">
+    <row r="849" ht="42" customHeight="1">
+      <c r="A849" s="43" t="inlineStr">
         <is>
           <t>68.5</t>
         </is>
       </c>
-      <c r="B851" s="3" t="inlineStr">
+      <c r="B849" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C851" s="3" t="inlineStr">
+      <c r="C849" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D851" s="4" t="inlineStr">
+      <c r="D849" s="4" t="inlineStr">
         <is>
           <t>Tidak menginput nilai realisasi pada modal approve</t>
         </is>
       </c>
-      <c r="E851" s="3" t="inlineStr">
+      <c r="E849" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F851" s="3" t="inlineStr">
+      <c r="F849" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G851" s="4" t="inlineStr">
+      <c r="G849" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan nilai realisasi 
 2. Input remark 
 3. Klik button Setujui</t>
         </is>
       </c>
-      <c r="H851" s="4" t="inlineStr">
+      <c r="H849" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field realisasi 
 2. Berhasil menginput remark 
@@ -37989,10 +37893,94 @@
         </is>
       </c>
     </row>
+    <row r="850" ht="28" customHeight="1">
+      <c r="A850" s="43" t="inlineStr">
+        <is>
+          <t>68.6</t>
+        </is>
+      </c>
+      <c r="B850" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C850" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D850" s="4" t="inlineStr">
+        <is>
+          <t>Tidak menginput remark pada modal approve</t>
+        </is>
+      </c>
+      <c r="E850" s="3" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F850" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G850" s="4" t="inlineStr">
+        <is>
+          <t>1. Kosongkan remark</t>
+        </is>
+      </c>
+      <c r="H850" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan alert 'Remark dibutuhkan!'</t>
+        </is>
+      </c>
+    </row>
+    <row r="851" ht="28" customHeight="1">
+      <c r="A851" s="43" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="B851" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C851" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D851" s="4" t="inlineStr">
+        <is>
+          <t>Menginput huruf pada field realisasi</t>
+        </is>
+      </c>
+      <c r="E851" s="3" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F851" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G851" s="4" t="inlineStr">
+        <is>
+          <t>1. Input huruf pada field realisasi kemudian pindah ke filed lain</t>
+        </is>
+      </c>
+      <c r="H851" s="4" t="inlineStr">
+        <is>
+          <t>1. Sistem menghapus input non-numerik secara otomatis saat field kehilangan fokus. Field Realiasi menjadi kosong</t>
+        </is>
+      </c>
+    </row>
     <row r="852" ht="28" customHeight="1">
       <c r="A852" s="43" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="B852" s="3" t="inlineStr">
@@ -38007,104 +37995,20 @@
       </c>
       <c r="D852" s="4" t="inlineStr">
         <is>
-          <t>Tidak menginput remark pada modal approve</t>
+          <t>Menolak Prospek</t>
         </is>
       </c>
       <c r="E852" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F852" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G852" s="4" t="inlineStr">
-        <is>
-          <t>1. Kosongkan remark</t>
-        </is>
-      </c>
-      <c r="H852" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan alert 'Remark dibutuhkan!'</t>
-        </is>
-      </c>
-    </row>
-    <row r="853" ht="28" customHeight="1">
-      <c r="A853" s="43" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="B853" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C853" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D853" s="4" t="inlineStr">
-        <is>
-          <t>Menginput huruf pada field realisasi</t>
-        </is>
-      </c>
-      <c r="E853" s="3" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F853" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G853" s="4" t="inlineStr">
-        <is>
-          <t>1. Input huruf pada field realisasi kemudian pindah ke filed lain</t>
-        </is>
-      </c>
-      <c r="H853" s="4" t="inlineStr">
-        <is>
-          <t>1. Sistem menghapus input non-numerik secara otomatis saat field kehilangan fokus. Field Realiasi menjadi kosong</t>
-        </is>
-      </c>
-    </row>
-    <row r="854" ht="28" customHeight="1">
-      <c r="A854" s="43" t="inlineStr">
-        <is>
-          <t>68.8</t>
-        </is>
-      </c>
-      <c r="B854" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C854" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D854" s="4" t="inlineStr">
-        <is>
-          <t>Menolak Prospek</t>
-        </is>
-      </c>
-      <c r="E854" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F854" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G854" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Tolak 
@@ -38112,7 +38016,7 @@
 4. Klik button Tolak</t>
         </is>
       </c>
-      <c r="H854" s="4" t="inlineStr">
+      <c r="H852" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan modal tolak prospek
@@ -38121,10 +38025,96 @@
         </is>
       </c>
     </row>
+    <row r="853" ht="28" customHeight="1">
+      <c r="A853" s="43" t="inlineStr">
+        <is>
+          <t>68.9</t>
+        </is>
+      </c>
+      <c r="B853" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C853" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D853" s="4" t="inlineStr">
+        <is>
+          <t>Batal menolak prospek</t>
+        </is>
+      </c>
+      <c r="E853" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F853" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G853" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Batalkan pada moal tolak prospek</t>
+        </is>
+      </c>
+      <c r="H853" s="4" t="inlineStr">
+        <is>
+          <t>1. Modal tolak prospek tertutup dan tetap berada di halaman approval non banking</t>
+        </is>
+      </c>
+    </row>
+    <row r="854" ht="28" customHeight="1">
+      <c r="A854" s="43" t="inlineStr">
+        <is>
+          <t>68.10</t>
+        </is>
+      </c>
+      <c r="B854" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C854" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D854" s="4" t="inlineStr">
+        <is>
+          <t>Tidak menginput remark pada modal tolak prospek</t>
+        </is>
+      </c>
+      <c r="E854" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F854" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G854" s="4" t="inlineStr">
+        <is>
+          <t>1. Kosongkan remark 
+2. Klik button Tolak</t>
+        </is>
+      </c>
+      <c r="H854" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan remark 
+2. Menampilkan alert 'Remark dibutuhkan!'</t>
+        </is>
+      </c>
+    </row>
     <row r="855" ht="28" customHeight="1">
       <c r="A855" s="43" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>68.11</t>
         </is>
       </c>
       <c r="B855" s="3" t="inlineStr">
@@ -38139,7 +38129,7 @@
       </c>
       <c r="D855" s="4" t="inlineStr">
         <is>
-          <t>Batal menolak prospek</t>
+          <t>Filter kolom</t>
         </is>
       </c>
       <c r="E855" s="3" t="inlineStr">
@@ -38154,19 +38144,21 @@
       </c>
       <c r="G855" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button Batalkan pada moal tolak prospek</t>
+          <t>1. Klik icon filter kolom 
+2. Checklist/unchecklist kolom</t>
         </is>
       </c>
       <c r="H855" s="4" t="inlineStr">
         <is>
-          <t>1. Modal tolak prospek tertutup dan tetap berada di halaman approval non banking</t>
+          <t>1. Menampilkan list kolom tabel 
+2. Menampilkan data tabel sesuai dengan kolom yang di ceklis</t>
         </is>
       </c>
     </row>
     <row r="856" ht="28" customHeight="1">
       <c r="A856" s="43" t="inlineStr">
         <is>
-          <t>68.10</t>
+          <t>68.12</t>
         </is>
       </c>
       <c r="B856" s="3" t="inlineStr">
@@ -38181,7 +38173,7 @@
       </c>
       <c r="D856" s="4" t="inlineStr">
         <is>
-          <t>Tidak menginput remark pada modal tolak prospek</t>
+          <t>Reset ke Default pada filter kolom</t>
         </is>
       </c>
       <c r="E856" s="3" t="inlineStr">
@@ -38191,26 +38183,24 @@
       </c>
       <c r="F856" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G856" s="4" t="inlineStr">
         <is>
-          <t>1. Kosongkan remark 
-2. Klik button Tolak</t>
+          <t>1. Klik Reset ke Default</t>
         </is>
       </c>
       <c r="H856" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan remark 
-2. Menampilkan alert 'Remark dibutuhkan!'</t>
+          <t>1. Berhasil menampilkan data tabel dengan kolom default</t>
         </is>
       </c>
     </row>
     <row r="857" ht="28" customHeight="1">
       <c r="A857" s="43" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="B857" s="3" t="inlineStr">
@@ -38220,12 +38210,12 @@
       </c>
       <c r="C857" s="3" t="inlineStr">
         <is>
-          <t>Approval Non Banking</t>
+          <t>Re-Assign Prospek</t>
         </is>
       </c>
       <c r="D857" s="4" t="inlineStr">
         <is>
-          <t>Filter kolom</t>
+          <t>Filter data</t>
         </is>
       </c>
       <c r="E857" s="3" t="inlineStr">
@@ -38239,92 +38229,6 @@
         </is>
       </c>
       <c r="G857" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik icon filter kolom 
-2. Checklist/unchecklist kolom</t>
-        </is>
-      </c>
-      <c r="H857" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan list kolom tabel 
-2. Menampilkan data tabel sesuai dengan kolom yang di ceklis</t>
-        </is>
-      </c>
-    </row>
-    <row r="858" ht="28" customHeight="1">
-      <c r="A858" s="43" t="inlineStr">
-        <is>
-          <t>68.12</t>
-        </is>
-      </c>
-      <c r="B858" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C858" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D858" s="4" t="inlineStr">
-        <is>
-          <t>Reset ke Default pada filter kolom</t>
-        </is>
-      </c>
-      <c r="E858" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F858" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G858" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik Reset ke Default</t>
-        </is>
-      </c>
-      <c r="H858" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data tabel dengan kolom default</t>
-        </is>
-      </c>
-    </row>
-    <row r="859" ht="28" customHeight="1">
-      <c r="A859" s="43" t="inlineStr">
-        <is>
-          <t>69.1</t>
-        </is>
-      </c>
-      <c r="B859" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C859" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D859" s="4" t="inlineStr">
-        <is>
-          <t>Filter data</t>
-        </is>
-      </c>
-      <c r="E859" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F859" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G859" s="4" t="inlineStr">
         <is>
           <t>1. Pilih kantor wilayah
 2. Pilih kantor cabang 
@@ -38334,7 +38238,7 @@
 6. Klik button Filter</t>
         </is>
       </c>
-      <c r="H859" s="4" t="inlineStr">
+      <c r="H857" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list data filter kantor wilayah dan dapat di pilih
 2. Menampilkan dropdown list data filter kantor cabang dan dapat di pilih
@@ -38345,10 +38249,98 @@
         </is>
       </c>
     </row>
+    <row r="858" ht="28" customHeight="1">
+      <c r="A858" s="43" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="B858" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C858" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D858" s="4" t="inlineStr">
+        <is>
+          <t>Mencari data</t>
+        </is>
+      </c>
+      <c r="E858" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F858" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G858" s="4" t="inlineStr">
+        <is>
+          <t>1. Input keyword pada field search 
+2. Klik icon search yang ada di sebelah field</t>
+        </is>
+      </c>
+      <c r="H858" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menginput keyword 
+2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
+        </is>
+      </c>
+    </row>
+    <row r="859" ht="28" customHeight="1">
+      <c r="A859" s="43" t="inlineStr">
+        <is>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="B859" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C859" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D859" s="4" t="inlineStr">
+        <is>
+          <t>Membuka halaman Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="E859" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F859" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G859" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu Re-Assign &amp; Approval 
+2. Klik submenu Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="H859" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan submenu Re-Assign &amp; Approval 
+2. Menampilkan halaman Re-Assign Prospek</t>
+        </is>
+      </c>
+    </row>
     <row r="860" ht="28" customHeight="1">
       <c r="A860" s="43" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="B860" s="3" t="inlineStr">
@@ -38363,7 +38355,7 @@
       </c>
       <c r="D860" s="4" t="inlineStr">
         <is>
-          <t>Mencari data</t>
+          <t>Filter data</t>
         </is>
       </c>
       <c r="E860" s="3" t="inlineStr">
@@ -38373,98 +38365,10 @@
       </c>
       <c r="F860" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G860" s="4" t="inlineStr">
-        <is>
-          <t>1. Input keyword pada field search 
-2. Klik icon search yang ada di sebelah field</t>
-        </is>
-      </c>
-      <c r="H860" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menginput keyword 
-2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
-        </is>
-      </c>
-    </row>
-    <row r="861" ht="28" customHeight="1">
-      <c r="A861" s="43" t="inlineStr">
-        <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="B861" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C861" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D861" s="4" t="inlineStr">
-        <is>
-          <t>Membuka halaman Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="E861" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F861" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G861" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu Re-Assign &amp; Approval 
-2. Klik submenu Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="H861" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan submenu Re-Assign &amp; Approval 
-2. Menampilkan halaman Re-Assign Prospek</t>
-        </is>
-      </c>
-    </row>
-    <row r="862" ht="28" customHeight="1">
-      <c r="A862" s="43" t="inlineStr">
-        <is>
-          <t>69.4</t>
-        </is>
-      </c>
-      <c r="B862" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C862" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D862" s="4" t="inlineStr">
-        <is>
-          <t>Filter data</t>
-        </is>
-      </c>
-      <c r="E862" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F862" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G862" s="4" t="inlineStr">
         <is>
           <t>1. Pilih kantor wilayah
 2. Pilih kantor cabang 
@@ -38474,7 +38378,7 @@
 6. Klik button Filter</t>
         </is>
       </c>
-      <c r="H862" s="4" t="inlineStr">
+      <c r="H860" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list data filter kantor wilayah dan dapat di pilih
 2. Menampilkan dropdown list data filter kantor cabang dan dapat di pilih
@@ -38485,10 +38389,96 @@
         </is>
       </c>
     </row>
+    <row r="861" ht="28" customHeight="1">
+      <c r="A861" s="43" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="B861" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C861" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D861" s="4" t="inlineStr">
+        <is>
+          <t>Mencari data</t>
+        </is>
+      </c>
+      <c r="E861" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F861" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G861" s="4" t="inlineStr">
+        <is>
+          <t>1. Input keyword pada field search 
+2. Klik icon search yang ada di sebelah field</t>
+        </is>
+      </c>
+      <c r="H861" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menginput keyword 
+2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
+        </is>
+      </c>
+    </row>
+    <row r="862" ht="28" customHeight="1">
+      <c r="A862" s="43" t="inlineStr">
+        <is>
+          <t>69.6</t>
+        </is>
+      </c>
+      <c r="B862" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C862" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D862" s="4" t="inlineStr">
+        <is>
+          <t>Validasi count checklist data</t>
+        </is>
+      </c>
+      <c r="E862" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F862" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G862" s="4" t="inlineStr">
+        <is>
+          <t>1. Cek informasi yang ada pada button Reassign () data</t>
+        </is>
+      </c>
+      <c r="H862" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan count angka yang sesuai dengan data yang di checklist</t>
+        </is>
+      </c>
+    </row>
     <row r="863" ht="28" customHeight="1">
       <c r="A863" s="43" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="B863" s="3" t="inlineStr">
@@ -38503,7 +38493,7 @@
       </c>
       <c r="D863" s="4" t="inlineStr">
         <is>
-          <t>Mencari data</t>
+          <t>Validasi data yang sudah dii pilih</t>
         </is>
       </c>
       <c r="E863" s="3" t="inlineStr">
@@ -38513,26 +38503,24 @@
       </c>
       <c r="F863" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G863" s="4" t="inlineStr">
         <is>
-          <t>1. Input keyword pada field search 
-2. Klik icon search yang ada di sebelah field</t>
+          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi prospek yang di pilih</t>
         </is>
       </c>
       <c r="H863" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menginput keyword 
-2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
+          <t>1. Menampilkan data tabel prospek yang di pilih saja</t>
         </is>
       </c>
     </row>
     <row r="864" ht="28" customHeight="1">
       <c r="A864" s="43" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="B864" s="3" t="inlineStr">
@@ -38547,34 +38535,36 @@
       </c>
       <c r="D864" s="4" t="inlineStr">
         <is>
-          <t>Validasi count checklist data</t>
+          <t>Mengosongkan field inputan mandatory pada reassign prospek</t>
         </is>
       </c>
       <c r="E864" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F864" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G864" s="4" t="inlineStr">
         <is>
-          <t>1. Cek informasi yang ada pada button Reassign () data</t>
+          <t>1. Kosongkan salah satu atau semua field mandatory 
+2. Klik button Submit</t>
         </is>
       </c>
       <c r="H864" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan count angka yang sesuai dengan data yang di checklist</t>
+          <t>1. Berhasil tidak mengisi/mengosongkan field 
+2. Menampilkan alert pada setiap field mandatory bahwa field tersebut dibutuhkan / wajib diisi</t>
         </is>
       </c>
     </row>
     <row r="865" ht="28" customHeight="1">
       <c r="A865" s="43" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="B865" s="3" t="inlineStr">
@@ -38589,7 +38579,7 @@
       </c>
       <c r="D865" s="4" t="inlineStr">
         <is>
-          <t>Validasi data yang sudah dii pilih</t>
+          <t>Membatalkan Re-Assign Prospek</t>
         </is>
       </c>
       <c r="E865" s="3" t="inlineStr">
@@ -38599,24 +38589,24 @@
       </c>
       <c r="F865" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G865" s="4" t="inlineStr">
         <is>
-          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi prospek yang di pilih</t>
+          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
         </is>
       </c>
       <c r="H865" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data tabel prospek yang di pilih saja</t>
+          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
         </is>
       </c>
     </row>
     <row r="866" ht="28" customHeight="1">
       <c r="A866" s="43" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.10</t>
         </is>
       </c>
       <c r="B866" s="3" t="inlineStr">
@@ -38631,12 +38621,12 @@
       </c>
       <c r="D866" s="4" t="inlineStr">
         <is>
-          <t>Mengosongkan field inputan mandatory pada reassign prospek</t>
+          <t>Validasi data prospek yang di re-assign</t>
         </is>
       </c>
       <c r="E866" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F866" s="3" t="inlineStr">
@@ -38645,92 +38635,6 @@
         </is>
       </c>
       <c r="G866" s="4" t="inlineStr">
-        <is>
-          <t>1. Kosongkan salah satu atau semua field mandatory 
-2. Klik button Submit</t>
-        </is>
-      </c>
-      <c r="H866" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil tidak mengisi/mengosongkan field 
-2. Menampilkan alert pada setiap field mandatory bahwa field tersebut dibutuhkan / wajib diisi</t>
-        </is>
-      </c>
-    </row>
-    <row r="867" ht="28" customHeight="1">
-      <c r="A867" s="43" t="inlineStr">
-        <is>
-          <t>69.9</t>
-        </is>
-      </c>
-      <c r="B867" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C867" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D867" s="4" t="inlineStr">
-        <is>
-          <t>Membatalkan Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="E867" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F867" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G867" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
-        </is>
-      </c>
-      <c r="H867" s="4" t="inlineStr">
-        <is>
-          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
-        </is>
-      </c>
-    </row>
-    <row r="868" ht="28" customHeight="1">
-      <c r="A868" s="43" t="inlineStr">
-        <is>
-          <t>69.10</t>
-        </is>
-      </c>
-      <c r="B868" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C868" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D868" s="4" t="inlineStr">
-        <is>
-          <t>Validasi data prospek yang di re-assign</t>
-        </is>
-      </c>
-      <c r="E868" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F868" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G868" s="4" t="inlineStr">
         <is>
           <t>1. Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek 
 2. Klik menu Lead Qualification 
@@ -38738,7 +38642,7 @@
 4. Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
-      <c r="H868" s="4" t="inlineStr">
+      <c r="H866" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login 
 2. Menampilkan dropdown submenu Lead Qualification 
@@ -38747,38 +38651,38 @@
         </is>
       </c>
     </row>
-    <row r="869" ht="28" customHeight="1">
-      <c r="A869" s="43" t="inlineStr">
+    <row r="867" ht="28" customHeight="1">
+      <c r="A867" s="43" t="inlineStr">
         <is>
           <t>69.11</t>
         </is>
       </c>
-      <c r="B869" s="3" t="inlineStr">
+      <c r="B867" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C869" s="3" t="inlineStr">
+      <c r="C867" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D869" s="4" t="inlineStr">
+      <c r="D867" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-assign prospek semua data</t>
         </is>
       </c>
-      <c r="E869" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F869" s="3" t="inlineStr">
+      <c r="E867" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F867" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G869" s="4" t="inlineStr">
+      <c r="G867" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Reassign semua data 
 2. Klik button Yes 
@@ -38789,7 +38693,7 @@
 7. Klik button Submit</t>
         </is>
       </c>
-      <c r="H869" s="4" t="inlineStr">
+      <c r="H867" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan popup konfirmasi 
 2. Menampilkan halaman pindah kelolaan 
@@ -38801,10 +38705,94 @@
         </is>
       </c>
     </row>
+    <row r="868" ht="28" customHeight="1">
+      <c r="A868" s="43" t="inlineStr">
+        <is>
+          <t>69.12</t>
+        </is>
+      </c>
+      <c r="B868" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C868" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D868" s="4" t="inlineStr">
+        <is>
+          <t>Validasi semua data</t>
+        </is>
+      </c>
+      <c r="E868" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F868" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G868" s="4" t="inlineStr">
+        <is>
+          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi semua prospek</t>
+        </is>
+      </c>
+      <c r="H868" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan data tabel yang berisi semua prospek</t>
+        </is>
+      </c>
+    </row>
+    <row r="869" ht="28" customHeight="1">
+      <c r="A869" s="43" t="inlineStr">
+        <is>
+          <t>69.13</t>
+        </is>
+      </c>
+      <c r="B869" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C869" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D869" s="4" t="inlineStr">
+        <is>
+          <t>Membatalkan Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="E869" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F869" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G869" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
+        </is>
+      </c>
+      <c r="H869" s="4" t="inlineStr">
+        <is>
+          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
+        </is>
+      </c>
+    </row>
     <row r="870" ht="28" customHeight="1">
       <c r="A870" s="43" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="B870" s="3" t="inlineStr">
@@ -38819,7 +38807,7 @@
       </c>
       <c r="D870" s="4" t="inlineStr">
         <is>
-          <t>Validasi semua data</t>
+          <t>Validasi semua data prospek yang di re-assign</t>
         </is>
       </c>
       <c r="E870" s="3" t="inlineStr">
@@ -38833,90 +38821,6 @@
         </is>
       </c>
       <c r="G870" s="4" t="inlineStr">
-        <is>
-          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi semua prospek</t>
-        </is>
-      </c>
-      <c r="H870" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan data tabel yang berisi semua prospek</t>
-        </is>
-      </c>
-    </row>
-    <row r="871" ht="28" customHeight="1">
-      <c r="A871" s="43" t="inlineStr">
-        <is>
-          <t>69.13</t>
-        </is>
-      </c>
-      <c r="B871" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C871" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D871" s="4" t="inlineStr">
-        <is>
-          <t>Membatalkan Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="E871" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F871" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G871" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
-        </is>
-      </c>
-      <c r="H871" s="4" t="inlineStr">
-        <is>
-          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
-        </is>
-      </c>
-    </row>
-    <row r="872" ht="70" customHeight="1">
-      <c r="A872" s="43" t="inlineStr">
-        <is>
-          <t>69.14</t>
-        </is>
-      </c>
-      <c r="B872" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C872" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D872" s="4" t="inlineStr">
-        <is>
-          <t>Validasi semua data prospek yang di re-assign</t>
-        </is>
-      </c>
-      <c r="E872" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F872" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G872" s="4" t="inlineStr">
         <is>
           <t>1. Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek 
 2. Klik menu Lead Qualification 
@@ -38924,7 +38828,7 @@
 4. Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
-      <c r="H872" s="4" t="inlineStr">
+      <c r="H870" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login 
 2. Menampilkan dropdown submenu Lead Qualification 
@@ -38933,10 +38837,98 @@
         </is>
       </c>
     </row>
+    <row r="871" ht="28" customHeight="1">
+      <c r="A871" s="43" t="inlineStr">
+        <is>
+          <t>70.1</t>
+        </is>
+      </c>
+      <c r="B871" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C871" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D871" s="4" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="E871" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F871" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G871" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik pagination (10/halaman).
+2. Pilih berapa data yang ingin ditampilkan.</t>
+        </is>
+      </c>
+      <c r="H871" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengklik pagination.
+2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="872" ht="70" customHeight="1">
+      <c r="A872" s="43" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="B872" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C872" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D872" s="4" t="inlineStr">
+        <is>
+          <t>Pindah Halaman</t>
+        </is>
+      </c>
+      <c r="E872" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F872" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G872" s="4" t="inlineStr">
+        <is>
+          <t>1. Input angka halaman di field pindah halaman.
+2. Klik Enter pada keyboard.</t>
+        </is>
+      </c>
+      <c r="H872" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menginput angka halaman.
+2. Berhasil berpindah ke halaman yang dituju.</t>
+        </is>
+      </c>
+    </row>
     <row r="873" ht="42" customHeight="1">
       <c r="A873" s="43" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="B873" s="3" t="inlineStr">
@@ -38951,7 +38943,7 @@
       </c>
       <c r="D873" s="4" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
       <c r="E873" s="3" t="inlineStr">
@@ -38961,98 +38953,10 @@
       </c>
       <c r="F873" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G873" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik pagination (10/halaman).
-2. Pilih berapa data yang ingin ditampilkan.</t>
-        </is>
-      </c>
-      <c r="H873" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengklik pagination.
-2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="874" ht="42" customHeight="1">
-      <c r="A874" s="43" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="B874" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C874" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Management</t>
-        </is>
-      </c>
-      <c r="D874" s="4" t="inlineStr">
-        <is>
-          <t>Pindah Halaman</t>
-        </is>
-      </c>
-      <c r="E874" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F874" s="3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G874" s="4" t="inlineStr">
-        <is>
-          <t>1. Input angka halaman di field pindah halaman.
-2. Klik Enter pada keyboard.</t>
-        </is>
-      </c>
-      <c r="H874" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menginput angka halaman.
-2. Berhasil berpindah ke halaman yang dituju.</t>
-        </is>
-      </c>
-    </row>
-    <row r="875" ht="70" customHeight="1">
-      <c r="A875" s="43" t="inlineStr">
-        <is>
-          <t>70.3</t>
-        </is>
-      </c>
-      <c r="B875" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C875" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Management</t>
-        </is>
-      </c>
-      <c r="D875" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="E875" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F875" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G875" s="4" t="inlineStr">
         <is>
           <t>1. Pilih prospek dengan klik checkbox yang ada di samping setiap data prospek 
 2. Klik button Reassign () data 
@@ -39061,7 +38965,7 @@
 5. Klik button Submit</t>
         </is>
       </c>
-      <c r="H875" s="4" t="inlineStr">
+      <c r="H873" s="4" t="inlineStr">
         <is>
           <t>1. Checkbox menjadi ceklis dan data berhasil di pilih 
 2. Menampilkan popup konfirmasi 
@@ -39071,10 +38975,98 @@
         </is>
       </c>
     </row>
+    <row r="874" ht="42" customHeight="1">
+      <c r="A874" s="43" t="inlineStr">
+        <is>
+          <t>70.4</t>
+        </is>
+      </c>
+      <c r="B874" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C874" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D874" s="4" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="E874" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F874" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G874" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik pagination (10/halaman).
+2. Pilih berapa data yang ingin ditampilkan.</t>
+        </is>
+      </c>
+      <c r="H874" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengklik pagination.
+2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="875" ht="70" customHeight="1">
+      <c r="A875" s="43" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
+      <c r="B875" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C875" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D875" s="4" t="inlineStr">
+        <is>
+          <t>Pindah Halaman</t>
+        </is>
+      </c>
+      <c r="E875" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F875" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G875" s="4" t="inlineStr">
+        <is>
+          <t>1. Input angka halaman di field pindah halaman.
+2. Klik Enter pada keyboard.</t>
+        </is>
+      </c>
+      <c r="H875" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menginput angka halaman.
+2. Berhasil berpindah ke halaman yang dituju.</t>
+        </is>
+      </c>
+    </row>
     <row r="876" ht="28" customHeight="1">
       <c r="A876" s="43" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="B876" s="3" t="inlineStr">
@@ -39089,7 +39081,7 @@
       </c>
       <c r="D876" s="4" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Membuka halaman Re-Assign Management</t>
         </is>
       </c>
       <c r="E876" s="3" t="inlineStr">
@@ -39099,26 +39091,26 @@
       </c>
       <c r="F876" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G876" s="4" t="inlineStr">
         <is>
-          <t>1. Klik pagination (10/halaman).
-2. Pilih berapa data yang ingin ditampilkan.</t>
+          <t>1. Klik menu Re-Assign &amp; Approval 
+2. Klik submenu Re-Assign Management</t>
         </is>
       </c>
       <c r="H876" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengklik pagination.
-2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+          <t>1. Menampilkan dropdown list submenu Re-Assign &amp; Approval 
+2. Menampilkan halaman Re-Assign Management</t>
         </is>
       </c>
     </row>
     <row r="877" ht="42" customHeight="1">
       <c r="A877" s="43" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="B877" s="3" t="inlineStr">
@@ -39133,7 +39125,7 @@
       </c>
       <c r="D877" s="4" t="inlineStr">
         <is>
-          <t>Pindah Halaman</t>
+          <t>Mencari data prospek pada halaman Re-Assign Management</t>
         </is>
       </c>
       <c r="E877" s="3" t="inlineStr">
@@ -39143,26 +39135,26 @@
       </c>
       <c r="F877" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G877" s="4" t="inlineStr">
         <is>
-          <t>1. Input angka halaman di field pindah halaman.
-2. Klik Enter pada keyboard.</t>
+          <t>1. Input nama nasabah pada field search 
+2. Klik icon search atau klik Enter</t>
         </is>
       </c>
       <c r="H877" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menginput angka halaman.
-2. Berhasil berpindah ke halaman yang dituju.</t>
+          <t>1. Berhasil menginput nama nasabah
+2. Menampilkan data prospek Re-Assign Management sesuai dengan nama yang di cari</t>
         </is>
       </c>
     </row>
     <row r="878" ht="28" customHeight="1">
       <c r="A878" s="43" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="B878" s="3" t="inlineStr">
@@ -39177,7 +39169,7 @@
       </c>
       <c r="D878" s="4" t="inlineStr">
         <is>
-          <t>Membuka halaman Re-Assign Management</t>
+          <t>Mencari data prospek yang tidak ada pada halaman Re-Assign Management</t>
         </is>
       </c>
       <c r="E878" s="3" t="inlineStr">
@@ -39192,21 +39184,21 @@
       </c>
       <c r="G878" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu Re-Assign &amp; Approval 
-2. Klik submenu Re-Assign Management</t>
+          <t>1. Input nama nasabah yang datanya tidak ada 
+2. Klik icon search atau klik Enter</t>
         </is>
       </c>
       <c r="H878" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan dropdown list submenu Re-Assign &amp; Approval 
-2. Menampilkan halaman Re-Assign Management</t>
+          <t>1. Berhasil menginput nama nasabah
+2. Menampilkan tabel kosong dengan keterangan no data</t>
         </is>
       </c>
     </row>
     <row r="879" ht="28" customHeight="1">
       <c r="A879" s="43" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="B879" s="3" t="inlineStr">
@@ -39221,7 +39213,7 @@
       </c>
       <c r="D879" s="4" t="inlineStr">
         <is>
-          <t>Mencari data prospek pada halaman Re-Assign Management</t>
+          <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
       <c r="E879" s="3" t="inlineStr">
@@ -39235,94 +39227,6 @@
         </is>
       </c>
       <c r="G879" s="4" t="inlineStr">
-        <is>
-          <t>1. Input nama nasabah pada field search 
-2. Klik icon search atau klik Enter</t>
-        </is>
-      </c>
-      <c r="H879" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menginput nama nasabah
-2. Menampilkan data prospek Re-Assign Management sesuai dengan nama yang di cari</t>
-        </is>
-      </c>
-    </row>
-    <row r="880" ht="28" customHeight="1">
-      <c r="A880" s="43" t="inlineStr">
-        <is>
-          <t>70.8</t>
-        </is>
-      </c>
-      <c r="B880" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C880" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Management</t>
-        </is>
-      </c>
-      <c r="D880" s="4" t="inlineStr">
-        <is>
-          <t>Mencari data prospek yang tidak ada pada halaman Re-Assign Management</t>
-        </is>
-      </c>
-      <c r="E880" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F880" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G880" s="4" t="inlineStr">
-        <is>
-          <t>1. Input nama nasabah yang datanya tidak ada 
-2. Klik icon search atau klik Enter</t>
-        </is>
-      </c>
-      <c r="H880" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menginput nama nasabah
-2. Menampilkan tabel kosong dengan keterangan no data</t>
-        </is>
-      </c>
-    </row>
-    <row r="881" ht="14" customHeight="1">
-      <c r="A881" s="43" t="inlineStr">
-        <is>
-          <t>70.9</t>
-        </is>
-      </c>
-      <c r="B881" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C881" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Management</t>
-        </is>
-      </c>
-      <c r="D881" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="E881" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F881" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G881" s="4" t="inlineStr">
         <is>
           <t>1. Pilih prospek dengan klik checkbox yang ada di samping setiap data prospek 
 2. Klik button Reassign () data 
@@ -39331,7 +39235,7 @@
 5. Klik button Submit</t>
         </is>
       </c>
-      <c r="H881" s="4" t="inlineStr">
+      <c r="H879" s="4" t="inlineStr">
         <is>
           <t>1. Checkbox menjadi ceklis dan data berhasil di pilih 
 2. Menampilkan popup konfirmasi 
@@ -39341,80 +39245,80 @@
         </is>
       </c>
     </row>
-    <row r="882" ht="42" customHeight="1">
-      <c r="A882" s="43" t="inlineStr">
+    <row r="880" ht="28" customHeight="1">
+      <c r="A880" s="43" t="inlineStr">
         <is>
           <t>70.10</t>
         </is>
       </c>
-      <c r="B882" s="3" t="inlineStr">
+      <c r="B880" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C882" s="3" t="inlineStr">
+      <c r="C880" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D882" s="4" t="inlineStr">
+      <c r="D880" s="4" t="inlineStr">
         <is>
           <t>Validasi jumlah data yang di pilih untuk reassign</t>
         </is>
       </c>
-      <c r="E882" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F882" s="3" t="inlineStr">
+      <c r="E880" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F880" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G882" s="4" t="inlineStr">
+      <c r="G880" s="4" t="inlineStr">
         <is>
           <t>1. cek jumlah data yang muncul pada button Reassign () data</t>
         </is>
       </c>
-      <c r="H882" s="4" t="inlineStr">
+      <c r="H880" s="4" t="inlineStr">
         <is>
           <t>1. Angka yang muncul pada button sesuai dengan jumlah data yang di pilih</t>
         </is>
       </c>
     </row>
-    <row r="883" ht="42" customHeight="1">
-      <c r="A883" s="43" t="inlineStr">
+    <row r="881" ht="14" customHeight="1">
+      <c r="A881" s="43" t="inlineStr">
         <is>
           <t>70.11</t>
         </is>
       </c>
-      <c r="B883" s="3" t="inlineStr">
+      <c r="B881" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C883" s="3" t="inlineStr">
+      <c r="C881" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D883" s="4" t="inlineStr">
+      <c r="D881" s="4" t="inlineStr">
         <is>
           <t>Validasi data prospek yang di re-assign ke sales</t>
         </is>
       </c>
-      <c r="E883" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F883" s="3" t="inlineStr">
+      <c r="E881" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F881" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G883" s="4" t="inlineStr">
+      <c r="G881" s="4" t="inlineStr">
         <is>
           <t>1. Login dengan akun sales yang sebelumnya sudah di pilih reassign management
 2. Klik menu Lead Qualification
@@ -39422,7 +39326,7 @@
 4. Cek data prospek yang sudah di reassign</t>
         </is>
       </c>
-      <c r="H883" s="4" t="inlineStr">
+      <c r="H881" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login akun sales
 2. Menampilkan dropdown submenu Lead Qualification
@@ -39431,25 +39335,113 @@
         </is>
       </c>
     </row>
+    <row r="882" ht="42" customHeight="1">
+      <c r="A882" s="43" t="inlineStr">
+        <is>
+          <t>70.12</t>
+        </is>
+      </c>
+      <c r="B882" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C882" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D882" s="4" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="E882" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F882" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G882" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik pagination (10/halaman).
+2. Pilih berapa data yang ingin ditampilkan.</t>
+        </is>
+      </c>
+      <c r="H882" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengklik pagination.
+2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="883" ht="42" customHeight="1">
+      <c r="A883" s="43" t="inlineStr">
+        <is>
+          <t>70.13</t>
+        </is>
+      </c>
+      <c r="B883" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C883" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Management</t>
+        </is>
+      </c>
+      <c r="D883" s="4" t="inlineStr">
+        <is>
+          <t>Pindah Halaman</t>
+        </is>
+      </c>
+      <c r="E883" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F883" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G883" s="4" t="inlineStr">
+        <is>
+          <t>1. Input angka halaman di field pindah halaman.
+2. Klik Enter pada keyboard.</t>
+        </is>
+      </c>
+      <c r="H883" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menginput angka halaman.
+2. Berhasil berpindah ke halaman yang dituju.</t>
+        </is>
+      </c>
+    </row>
     <row r="884" ht="28" customHeight="1">
       <c r="A884" s="43" t="inlineStr">
         <is>
-          <t>70.12</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="B884" s="3" t="inlineStr">
         <is>
-          <t>Re-Assign dan Approval</t>
+          <t>Export data management</t>
         </is>
       </c>
       <c r="C884" s="3" t="inlineStr">
         <is>
-          <t>Re-Assign Management</t>
+          <t>Riwayat export saya</t>
         </is>
       </c>
       <c r="D884" s="4" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Membuka menu riwayat export saya</t>
         </is>
       </c>
       <c r="E884" s="3" t="inlineStr">
@@ -39459,41 +39451,39 @@
       </c>
       <c r="F884" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G884" s="4" t="inlineStr">
         <is>
-          <t>1. Klik pagination (10/halaman).
-2. Pilih berapa data yang ingin ditampilkan.</t>
+          <t>1. Klik menu exported data management, klik submenu riwayat export saya</t>
         </is>
       </c>
       <c r="H884" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengklik pagination.
-2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+          <t>1. Menampilkan halaman riwayat export saya</t>
         </is>
       </c>
     </row>
     <row r="885" ht="42" customHeight="1">
       <c r="A885" s="43" t="inlineStr">
         <is>
-          <t>70.13</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="B885" s="3" t="inlineStr">
         <is>
-          <t>Re-Assign dan Approval</t>
+          <t>Export data management</t>
         </is>
       </c>
       <c r="C885" s="3" t="inlineStr">
         <is>
-          <t>Re-Assign Management</t>
+          <t>Riwayat export saya</t>
         </is>
       </c>
       <c r="D885" s="4" t="inlineStr">
         <is>
-          <t>Pindah Halaman</t>
+          <t>Validasi card disetujui dengan data table</t>
         </is>
       </c>
       <c r="E885" s="3" t="inlineStr">
@@ -39503,26 +39493,24 @@
       </c>
       <c r="F885" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G885" s="4" t="inlineStr">
         <is>
-          <t>1. Input angka halaman di field pindah halaman.
-2. Klik Enter pada keyboard.</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Approved”</t>
         </is>
       </c>
       <c r="H885" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil menginput angka halaman.
-2. Berhasil berpindah ke halaman yang dituju.</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="886" ht="14" customHeight="1">
       <c r="A886" s="43" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="B886" s="3" t="inlineStr">
@@ -39537,7 +39525,7 @@
       </c>
       <c r="D886" s="4" t="inlineStr">
         <is>
-          <t>Membuka menu riwayat export saya</t>
+          <t>Validasi card ditolak dengan data table</t>
         </is>
       </c>
       <c r="E886" s="3" t="inlineStr">
@@ -39552,19 +39540,19 @@
       </c>
       <c r="G886" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu exported data management, klik submenu riwayat export saya</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Rejected”</t>
         </is>
       </c>
       <c r="H886" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan halaman riwayat export saya</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="887" ht="42" customHeight="1">
       <c r="A887" s="43" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="B887" s="3" t="inlineStr">
@@ -39579,7 +39567,7 @@
       </c>
       <c r="D887" s="4" t="inlineStr">
         <is>
-          <t>Validasi card disetujui dengan data table</t>
+          <t>Validasi card kadaluwarsa dengan data table</t>
         </is>
       </c>
       <c r="E887" s="3" t="inlineStr">
@@ -39589,12 +39577,12 @@
       </c>
       <c r="F887" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G887" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Approved”</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Expired”</t>
         </is>
       </c>
       <c r="H887" s="4" t="inlineStr">
@@ -39606,7 +39594,7 @@
     <row r="888" ht="42" customHeight="1">
       <c r="A888" s="43" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="B888" s="3" t="inlineStr">
@@ -39621,7 +39609,7 @@
       </c>
       <c r="D888" s="4" t="inlineStr">
         <is>
-          <t>Validasi card ditolak dengan data table</t>
+          <t>Mengunduh data yang sudah di approve</t>
         </is>
       </c>
       <c r="E888" s="3" t="inlineStr">
@@ -39636,19 +39624,19 @@
       </c>
       <c r="G888" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Rejected”</t>
+          <t>1. Klik button download</t>
         </is>
       </c>
       <c r="H888" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Berhasil mengunduh data</t>
         </is>
       </c>
     </row>
     <row r="889" ht="28" customHeight="1">
       <c r="A889" s="43" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="B889" s="3" t="inlineStr">
@@ -39663,7 +39651,7 @@
       </c>
       <c r="D889" s="4" t="inlineStr">
         <is>
-          <t>Validasi card kadaluwarsa dengan data table</t>
+          <t>Membuka dokumen hasil download</t>
         </is>
       </c>
       <c r="E889" s="3" t="inlineStr">
@@ -39673,24 +39661,24 @@
       </c>
       <c r="F889" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G889" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Expired”</t>
+          <t>1. Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
         </is>
       </c>
       <c r="H889" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Berhasil membuka file hasil download</t>
         </is>
       </c>
     </row>
     <row r="890" ht="42" customHeight="1">
       <c r="A890" s="43" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="B890" s="3" t="inlineStr">
@@ -39700,12 +39688,12 @@
       </c>
       <c r="C890" s="3" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D890" s="4" t="inlineStr">
         <is>
-          <t>Mengunduh data yang sudah di approve</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E890" s="3" t="inlineStr">
@@ -39715,24 +39703,24 @@
       </c>
       <c r="F890" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G890" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button download</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H890" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengunduh data</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="891" ht="14" customHeight="1">
       <c r="A891" s="43" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="B891" s="3" t="inlineStr">
@@ -39742,12 +39730,12 @@
       </c>
       <c r="C891" s="3" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D891" s="4" t="inlineStr">
         <is>
-          <t>Membuka dokumen hasil download</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E891" s="3" t="inlineStr">
@@ -39762,19 +39750,19 @@
       </c>
       <c r="G891" s="4" t="inlineStr">
         <is>
-          <t>1. Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
         </is>
       </c>
       <c r="H891" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka file hasil download</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="892" ht="42" customHeight="1">
       <c r="A892" s="43" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="B892" s="3" t="inlineStr">
@@ -39789,7 +39777,7 @@
       </c>
       <c r="D892" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E892" s="3" t="inlineStr">
@@ -39799,24 +39787,24 @@
       </c>
       <c r="F892" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G892" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H892" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="893" ht="42" customHeight="1">
       <c r="A893" s="43" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="B893" s="3" t="inlineStr">
@@ -39831,12 +39819,12 @@
       </c>
       <c r="D893" s="4" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E893" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F893" s="3" t="inlineStr">
@@ -39846,19 +39834,19 @@
       </c>
       <c r="G893" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H893" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="894" ht="28" customHeight="1">
       <c r="A894" s="43" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="B894" s="3" t="inlineStr">
@@ -39873,7 +39861,7 @@
       </c>
       <c r="D894" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E894" s="3" t="inlineStr">
@@ -39883,24 +39871,24 @@
       </c>
       <c r="F894" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G894" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H894" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="895" ht="42" customHeight="1">
       <c r="A895" s="43" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="B895" s="3" t="inlineStr">
@@ -39915,12 +39903,12 @@
       </c>
       <c r="D895" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E895" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F895" s="3" t="inlineStr">
@@ -39930,19 +39918,19 @@
       </c>
       <c r="G895" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H895" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="896" ht="14" customHeight="1">
       <c r="A896" s="43" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="B896" s="3" t="inlineStr">
@@ -39957,34 +39945,34 @@
       </c>
       <c r="D896" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E896" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F896" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G896" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H896" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="897" ht="42" customHeight="1">
       <c r="A897" s="43" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="B897" s="3" t="inlineStr">
@@ -39999,7 +39987,7 @@
       </c>
       <c r="D897" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Membuka menu Management Export</t>
         </is>
       </c>
       <c r="E897" s="3" t="inlineStr">
@@ -40014,19 +40002,19 @@
       </c>
       <c r="G897" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Klik menu exported data management, klik submenu management export</t>
         </is>
       </c>
       <c r="H897" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Menampilkan halaman management export</t>
         </is>
       </c>
     </row>
     <row r="898" ht="42" customHeight="1">
       <c r="A898" s="43" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="B898" s="3" t="inlineStr">
@@ -40041,34 +40029,34 @@
       </c>
       <c r="D898" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E898" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F898" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G898" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H898" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="899" ht="28" customHeight="1">
       <c r="A899" s="43" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.10</t>
         </is>
       </c>
       <c r="B899" s="3" t="inlineStr">
@@ -40083,7 +40071,7 @@
       </c>
       <c r="D899" s="4" t="inlineStr">
         <is>
-          <t>Membuka menu Management Export</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E899" s="3" t="inlineStr">
@@ -40098,19 +40086,19 @@
       </c>
       <c r="G899" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu exported data management, klik submenu management export</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H899" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan halaman management export</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="900" ht="42" customHeight="1">
       <c r="A900" s="43" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>72.11</t>
         </is>
       </c>
       <c r="B900" s="3" t="inlineStr">
@@ -40125,34 +40113,34 @@
       </c>
       <c r="D900" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E900" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F900" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G900" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H900" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="901" ht="28" customHeight="1">
       <c r="A901" s="43" t="inlineStr">
         <is>
-          <t>72.10</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="B901" s="3" t="inlineStr">
@@ -40167,7 +40155,7 @@
       </c>
       <c r="D901" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E901" s="3" t="inlineStr">
@@ -40182,19 +40170,19 @@
       </c>
       <c r="G901" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
         </is>
       </c>
       <c r="H901" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="902" ht="28" customHeight="1">
       <c r="A902" s="43" t="inlineStr">
         <is>
-          <t>72.11</t>
+          <t>72.13</t>
         </is>
       </c>
       <c r="B902" s="3" t="inlineStr">
@@ -40209,34 +40197,34 @@
       </c>
       <c r="D902" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Validasi card data file aktif dengan data table</t>
         </is>
       </c>
       <c r="E902" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F902" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G902" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
         </is>
       </c>
       <c r="H902" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="903" ht="28" customHeight="1">
       <c r="A903" s="43" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>72.14</t>
         </is>
       </c>
       <c r="B903" s="3" t="inlineStr">
@@ -40251,7 +40239,7 @@
       </c>
       <c r="D903" s="4" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Validasi card file kadaluwarsa dengan data table</t>
         </is>
       </c>
       <c r="E903" s="3" t="inlineStr">
@@ -40261,12 +40249,12 @@
       </c>
       <c r="F903" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G903" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
         </is>
       </c>
       <c r="H903" s="4" t="inlineStr">
@@ -40278,7 +40266,7 @@
     <row r="904" ht="28" customHeight="1">
       <c r="A904" s="43" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>72.15</t>
         </is>
       </c>
       <c r="B904" s="3" t="inlineStr">
@@ -40293,7 +40281,7 @@
       </c>
       <c r="D904" s="4" t="inlineStr">
         <is>
-          <t>Validasi card data file aktif dengan data table</t>
+          <t>Validasi card reject dengan data table</t>
         </is>
       </c>
       <c r="E904" s="3" t="inlineStr">
@@ -40303,12 +40291,12 @@
       </c>
       <c r="F904" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G904" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
         </is>
       </c>
       <c r="H904" s="4" t="inlineStr">
@@ -40320,7 +40308,7 @@
     <row r="905" ht="28" customHeight="1">
       <c r="A905" s="43" t="inlineStr">
         <is>
-          <t>72.14</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="B905" s="3" t="inlineStr">
@@ -40330,12 +40318,12 @@
       </c>
       <c r="C905" s="3" t="inlineStr">
         <is>
-          <t>Management export</t>
+          <t>Persetujuan export</t>
         </is>
       </c>
       <c r="D905" s="4" t="inlineStr">
         <is>
-          <t>Validasi card file kadaluwarsa dengan data table</t>
+          <t>Lakukan login menggunakan user monitoring</t>
         </is>
       </c>
       <c r="E905" s="3" t="inlineStr">
@@ -40350,19 +40338,19 @@
       </c>
       <c r="G905" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
+          <t>1. Login menggunakan user monitoring</t>
         </is>
       </c>
       <c r="H905" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Berhasil melakukan login</t>
         </is>
       </c>
     </row>
     <row r="906" ht="42" customHeight="1">
       <c r="A906" s="43" t="inlineStr">
         <is>
-          <t>72.15</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="B906" s="3" t="inlineStr">
@@ -40372,12 +40360,12 @@
       </c>
       <c r="C906" s="3" t="inlineStr">
         <is>
-          <t>Management export</t>
+          <t>Persetujuan export</t>
         </is>
       </c>
       <c r="D906" s="4" t="inlineStr">
         <is>
-          <t>Validasi card reject dengan data table</t>
+          <t>Membuka menu Persetujuan Export</t>
         </is>
       </c>
       <c r="E906" s="3" t="inlineStr">
@@ -40392,19 +40380,19 @@
       </c>
       <c r="G906" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
+          <t>1. Klik menu exported data management, klik submenu persetujuan export</t>
         </is>
       </c>
       <c r="H906" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Menampilkan halaman persetujuan export</t>
         </is>
       </c>
     </row>
     <row r="907" ht="42" customHeight="1">
       <c r="A907" s="43" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="B907" s="3" t="inlineStr">
@@ -40419,7 +40407,7 @@
       </c>
       <c r="D907" s="4" t="inlineStr">
         <is>
-          <t>Lakukan login menggunakan user monitoring</t>
+          <t>Melakukan approval data pengajuan export</t>
         </is>
       </c>
       <c r="E907" s="3" t="inlineStr">
@@ -40429,101 +40417,17 @@
       </c>
       <c r="F907" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G907" s="4" t="inlineStr">
-        <is>
-          <t>1. Login menggunakan user monitoring</t>
-        </is>
-      </c>
-      <c r="H907" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil melakukan login</t>
-        </is>
-      </c>
-    </row>
-    <row r="908" ht="28" customHeight="1">
-      <c r="A908" s="43" t="inlineStr">
-        <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="B908" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C908" s="3" t="inlineStr">
-        <is>
-          <t>Persetujuan export</t>
-        </is>
-      </c>
-      <c r="D908" s="4" t="inlineStr">
-        <is>
-          <t>Membuka menu Persetujuan Export</t>
-        </is>
-      </c>
-      <c r="E908" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F908" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G908" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu exported data management, klik submenu persetujuan export</t>
-        </is>
-      </c>
-      <c r="H908" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan halaman persetujuan export</t>
-        </is>
-      </c>
-    </row>
-    <row r="909" ht="14" customHeight="1">
-      <c r="A909" s="43" t="inlineStr">
-        <is>
-          <t>73.3</t>
-        </is>
-      </c>
-      <c r="B909" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C909" s="3" t="inlineStr">
-        <is>
-          <t>Persetujuan export</t>
-        </is>
-      </c>
-      <c r="D909" s="4" t="inlineStr">
-        <is>
-          <t>Melakukan approval data pengajuan export</t>
-        </is>
-      </c>
-      <c r="E909" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F909" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G909" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon titik tiga pada data pengajuan.
 2. Klik menu Setuju.
 3. Klik button YA pada popup konfirmasi.</t>
         </is>
       </c>
-      <c r="H909" s="4" t="inlineStr">
+      <c r="H907" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan menu opsi.
 2. Berhasil menampilkan popup konfirmasi.
@@ -40531,48 +40435,50 @@
         </is>
       </c>
     </row>
-    <row r="910" ht="28" customHeight="1">
-      <c r="A910" s="43" t="inlineStr">
+    <row r="908" ht="28" customHeight="1">
+      <c r="A908" s="43" t="inlineStr">
         <is>
           <t>73.4</t>
         </is>
       </c>
-      <c r="B910" s="3" t="inlineStr">
+      <c r="B908" s="3" t="inlineStr">
         <is>
           <t>Export data management</t>
         </is>
       </c>
-      <c r="C910" s="3" t="inlineStr">
+      <c r="C908" s="3" t="inlineStr">
         <is>
           <t>Persetujuan export</t>
         </is>
       </c>
-      <c r="D910" s="4" t="inlineStr">
+      <c r="D908" s="4" t="inlineStr">
         <is>
           <t>Melakukan reject data pengajuan export</t>
         </is>
       </c>
-      <c r="E910" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F910" s="3" t="inlineStr">
+      <c r="E908" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F908" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G910" s="4" t="inlineStr">
+      <c r="G908" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon (titik tiga) klik tolak, input alasan, klik submit</t>
         </is>
       </c>
-      <c r="H910" s="4" t="inlineStr">
+      <c r="H908" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil melakukan reject data</t>
         </is>
       </c>
     </row>
+    <row r="909" ht="14" customHeight="1"/>
+    <row r="910" ht="28" customHeight="1"/>
     <row r="911" ht="28" customHeight="1"/>
     <row r="912" ht="28" customHeight="1"/>
     <row r="913" ht="28" customHeight="1"/>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z908"/>
+  <dimension ref="A1:Z910"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="12.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35582,218 +35582,258 @@
       </c>
     </row>
     <row r="798" ht="14" customHeight="1">
-      <c r="A798" s="43" t="n">
+      <c r="A798" t="n">
         <v>62.4</v>
       </c>
-      <c r="B798" s="3" t="inlineStr">
+      <c r="B798" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C798" s="3" t="inlineStr">
+      <c r="C798" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D798" s="4" t="inlineStr">
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Mereset filter data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>1. Klik button Reset pada panel Filter.</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan kriteria filter dan mengembalikan kondisi filter ke default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="799" ht="14" customHeight="1">
+      <c r="A799" s="43" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="B799" s="3" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C799" s="3" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D799" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data Rekap Funnel</t>
         </is>
       </c>
-      <c r="E798" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F798" s="3" t="inlineStr">
+      <c r="E799" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F799" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G798" s="4" t="inlineStr">
+      <c r="G799" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Export.
 2. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H798" s="4" t="inlineStr">
+      <c r="H799" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan panel Download Export.
 2. Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
-    <row r="799" ht="14" customHeight="1">
-      <c r="A799" s="43" t="inlineStr">
+    <row r="800" ht="14" customHeight="1">
+      <c r="A800" s="43" t="inlineStr">
         <is>
           <t>63.1</t>
         </is>
       </c>
-      <c r="B799" s="3" t="inlineStr">
+      <c r="B800" s="3" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C799" s="3" t="inlineStr">
+      <c r="C800" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D799" s="4" t="inlineStr">
+      <c r="D800" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Pengaturan Funnel Funding</t>
         </is>
       </c>
-      <c r="E799" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F799" s="3" t="inlineStr">
+      <c r="E800" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F800" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G799" s="4" t="inlineStr">
+      <c r="G800" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Funding.
 2. Klik sub menu Pengaturan Funnel.</t>
         </is>
       </c>
-      <c r="H799" s="4" t="inlineStr">
+      <c r="H800" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Funding.
 2. Berhasil menampilkan halaman Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
-    <row r="800" ht="14" customHeight="1">
-      <c r="A800" s="43" t="inlineStr">
+    <row r="801" ht="14" customHeight="1">
+      <c r="A801" s="43" t="inlineStr">
         <is>
           <t>63.2</t>
         </is>
       </c>
-      <c r="B800" s="3" t="inlineStr">
+      <c r="B801" s="3" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C800" s="3" t="inlineStr">
+      <c r="C801" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D800" s="4" t="inlineStr">
+      <c r="D801" s="4" t="inlineStr">
         <is>
           <t>Mengubah data Pengaturan Funnel Funding</t>
         </is>
       </c>
-      <c r="E800" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F800" s="3" t="inlineStr">
+      <c r="E801" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F801" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G800" s="4" t="inlineStr">
+      <c r="G801" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H800" s="4" t="inlineStr">
+      <c r="H801" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field Performance Percentage.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
-    <row r="801" ht="14" customHeight="1">
-      <c r="A801" s="43" t="inlineStr">
+    <row r="802" ht="14" customHeight="1">
+      <c r="A802" s="43" t="inlineStr">
         <is>
           <t>63.3</t>
         </is>
       </c>
-      <c r="B801" s="3" t="inlineStr">
+      <c r="B802" s="3" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C801" s="3" t="inlineStr">
+      <c r="C802" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D801" s="4" t="inlineStr">
+      <c r="D802" s="4" t="inlineStr">
         <is>
           <t>Mengubah data Pengaturan Funnel Funding tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E801" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F801" s="3" t="inlineStr">
+      <c r="E802" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F802" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G801" s="4" t="inlineStr">
+      <c r="G802" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field mandatory Performance Percentage.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H801" s="4" t="inlineStr">
+      <c r="H802" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field Performance Percentage.
 2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
-    <row r="802" ht="14" customHeight="1">
-      <c r="A802" s="43" t="inlineStr">
+    <row r="803" ht="14" customHeight="1">
+      <c r="A803" s="43" t="inlineStr">
         <is>
           <t>63.4</t>
         </is>
       </c>
-      <c r="B802" s="3" t="inlineStr">
+      <c r="B803" s="3" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C802" s="3" t="inlineStr">
+      <c r="C803" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D802" s="4" t="inlineStr">
+      <c r="D803" s="4" t="inlineStr">
         <is>
           <t>Menambahkan Kondisi pada Indikator Performa</t>
         </is>
       </c>
-      <c r="E802" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F802" s="3" t="inlineStr">
+      <c r="E803" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F803" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G802" s="4" t="inlineStr">
+      <c r="G803" s="4" t="inlineStr">
         <is>
           <t>1. Klik button + Tambah Kondisi pada bagian Indikator Performa.
 2. Mengisi semua field mandatory pada kondisi baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H802" s="4" t="inlineStr">
+      <c r="H803" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan form kondisi baru pada Indikator Performa.
 2. Berhasil mengisi field mandatory kondisi.
@@ -35801,89 +35841,89 @@
         </is>
       </c>
     </row>
-    <row r="803" ht="14" customHeight="1">
-      <c r="A803" s="43" t="inlineStr">
+    <row r="804" ht="14" customHeight="1">
+      <c r="A804" s="43" t="inlineStr">
         <is>
           <t>63.5</t>
         </is>
       </c>
-      <c r="B803" s="3" t="inlineStr">
+      <c r="B804" s="3" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C803" s="3" t="inlineStr">
+      <c r="C804" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D803" s="4" t="inlineStr">
+      <c r="D804" s="4" t="inlineStr">
         <is>
           <t>Menghapus Kondisi pada Indikator Performa</t>
         </is>
       </c>
-      <c r="E803" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F803" s="3" t="inlineStr">
+      <c r="E804" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F804" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G803" s="4" t="inlineStr">
+      <c r="G804" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Hapus pada salah satu kondisi di Indikator Performa.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H803" s="4" t="inlineStr">
+      <c r="H804" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menghapus kondisi dari Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
-    <row r="804" ht="14" customHeight="1">
-      <c r="A804" s="43" t="inlineStr">
+    <row r="805" ht="14" customHeight="1">
+      <c r="A805" s="43" t="inlineStr">
         <is>
           <t>63.6</t>
         </is>
       </c>
-      <c r="B804" s="3" t="inlineStr">
+      <c r="B805" s="3" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C804" s="3" t="inlineStr">
+      <c r="C805" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D804" s="4" t="inlineStr">
+      <c r="D805" s="4" t="inlineStr">
         <is>
           <t>Menambahkan Operator pada Kondisi</t>
         </is>
       </c>
-      <c r="E804" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F804" s="3" t="inlineStr">
+      <c r="E805" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F805" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G804" s="4" t="inlineStr">
+      <c r="G805" s="4" t="inlineStr">
         <is>
           <t>1. Klik link tambah operator pada salah satu kondisi di Indikator Performa.
 2. Mengisi field operator baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H804" s="4" t="inlineStr">
+      <c r="H805" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan baris operator baru pada kondisi.
 2. Berhasil mengisi data operator.
@@ -35891,263 +35931,263 @@
         </is>
       </c>
     </row>
-    <row r="805" ht="14" customHeight="1">
-      <c r="A805" s="43" t="inlineStr">
+    <row r="806" ht="14" customHeight="1">
+      <c r="A806" s="43" t="inlineStr">
         <is>
           <t>63.7</t>
         </is>
       </c>
-      <c r="B805" s="3" t="inlineStr">
+      <c r="B806" s="3" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C805" s="3" t="inlineStr">
+      <c r="C806" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D805" s="4" t="inlineStr">
+      <c r="D806" s="4" t="inlineStr">
         <is>
           <t>Menghapus Operator pada Kondisi</t>
         </is>
       </c>
-      <c r="E805" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F805" s="3" t="inlineStr">
+      <c r="E806" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F806" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G805" s="4" t="inlineStr">
+      <c r="G806" s="4" t="inlineStr">
         <is>
           <t>1. Klik button x pada salah satu operator di Indikator Performa.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H805" s="4" t="inlineStr">
+      <c r="H806" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menghapus operator dari kondisi di Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
-    <row r="806" ht="14" customHeight="1">
-      <c r="A806" s="43" t="inlineStr">
+    <row r="807" ht="14" customHeight="1">
+      <c r="A807" s="43" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="B806" s="3" t="inlineStr">
+      <c r="B807" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C806" s="3" t="inlineStr">
+      <c r="C807" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D806" s="4" t="inlineStr">
+      <c r="D807" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="E806" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F806" s="3" t="inlineStr">
+      <c r="E807" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F807" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G806" s="4" t="inlineStr">
+      <c r="G807" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Lending.
 2. Klik sub menu Daily Sales Agenda.</t>
         </is>
       </c>
-      <c r="H806" s="4" t="inlineStr">
+      <c r="H807" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Lending.
 2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
         </is>
       </c>
     </row>
-    <row r="807" ht="14" customHeight="1">
-      <c r="A807" s="43" t="inlineStr">
+    <row r="808" ht="14" customHeight="1">
+      <c r="A808" s="43" t="inlineStr">
         <is>
           <t>64.2</t>
         </is>
       </c>
-      <c r="B807" s="3" t="inlineStr">
+      <c r="B808" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C807" s="3" t="inlineStr">
+      <c r="C808" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D807" s="4" t="inlineStr">
+      <c r="D808" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="E807" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F807" s="3" t="inlineStr">
+      <c r="E808" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F808" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G807" s="4" t="inlineStr">
+      <c r="G808" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi semua field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H807" s="4" t="inlineStr">
+      <c r="H808" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field filter mandatory.
 2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="808" ht="14" customHeight="1">
-      <c r="A808" s="43" t="inlineStr">
+    <row r="809" ht="14" customHeight="1">
+      <c r="A809" s="43" t="inlineStr">
         <is>
           <t>64.3</t>
         </is>
       </c>
-      <c r="B808" s="3" t="inlineStr">
+      <c r="B809" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C808" s="3" t="inlineStr">
+      <c r="C809" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D808" s="4" t="inlineStr">
+      <c r="D809" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E808" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F808" s="3" t="inlineStr">
+      <c r="E809" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F809" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G808" s="4" t="inlineStr">
+      <c r="G809" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H808" s="4" t="inlineStr">
+      <c r="H809" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
-    <row r="809" ht="14" customHeight="1">
-      <c r="A809" s="43" t="inlineStr">
-        <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="B809" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C809" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D809" s="4" t="inlineStr">
-        <is>
-          <t>Menampilkan data tab Prospek Masuk</t>
-        </is>
-      </c>
-      <c r="E809" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F809" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G809" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Masuk.</t>
-        </is>
-      </c>
-      <c r="H809" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data pada tab Prospek Masuk.</t>
-        </is>
-      </c>
-    </row>
     <row r="810" ht="42" customHeight="1">
       <c r="A810" s="43" t="inlineStr">
         <is>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="B810" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C810" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D810" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data tab Prospek Masuk</t>
+        </is>
+      </c>
+      <c r="E810" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F810" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G810" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Masuk.</t>
+        </is>
+      </c>
+      <c r="H810" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data pada tab Prospek Masuk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="811" ht="28" customHeight="1">
+      <c r="A811" s="43" t="inlineStr">
+        <is>
           <t>64.5</t>
         </is>
       </c>
-      <c r="B810" s="3" t="inlineStr">
+      <c r="B811" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C810" s="3" t="inlineStr">
+      <c r="C811" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D810" s="4" t="inlineStr">
+      <c r="D811" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Masuk dengan keyword valid</t>
         </is>
       </c>
-      <c r="E810" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F810" s="3" t="inlineStr">
+      <c r="E811" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F811" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G810" s="4" t="inlineStr">
+      <c r="G811" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H810" s="4" t="inlineStr">
+      <c r="H811" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil mengisi field Cari Data.
@@ -36155,45 +36195,45 @@
         </is>
       </c>
     </row>
-    <row r="811" ht="28" customHeight="1">
-      <c r="A811" s="43" t="inlineStr">
+    <row r="812" ht="42" customHeight="1">
+      <c r="A812" s="43" t="inlineStr">
         <is>
           <t>64.6</t>
         </is>
       </c>
-      <c r="B811" s="3" t="inlineStr">
+      <c r="B812" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C811" s="3" t="inlineStr">
+      <c r="C812" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D811" s="4" t="inlineStr">
+      <c r="D812" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E811" s="3" t="inlineStr">
+      <c r="E812" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F811" s="3" t="inlineStr">
+      <c r="F812" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G811" s="4" t="inlineStr">
+      <c r="G812" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H811" s="4" t="inlineStr">
+      <c r="H812" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil mengisi field Cari Data.
@@ -36201,89 +36241,89 @@
         </is>
       </c>
     </row>
-    <row r="812" ht="42" customHeight="1">
-      <c r="A812" s="43" t="inlineStr">
+    <row r="813" ht="28" customHeight="1">
+      <c r="A813" s="43" t="inlineStr">
         <is>
           <t>64.7</t>
         </is>
       </c>
-      <c r="B812" s="3" t="inlineStr">
+      <c r="B813" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C812" s="3" t="inlineStr">
+      <c r="C813" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D812" s="4" t="inlineStr">
+      <c r="D813" s="4" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Masuk</t>
         </is>
       </c>
-      <c r="E812" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F812" s="3" t="inlineStr">
+      <c r="E813" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F813" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G812" s="4" t="inlineStr">
+      <c r="G813" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H812" s="4" t="inlineStr">
+      <c r="H813" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="813" ht="28" customHeight="1">
-      <c r="A813" s="43" t="inlineStr">
+    <row r="814" ht="28" customHeight="1">
+      <c r="A814" s="43" t="inlineStr">
         <is>
           <t>64.8</t>
         </is>
       </c>
-      <c r="B813" s="3" t="inlineStr">
+      <c r="B814" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C813" s="3" t="inlineStr">
+      <c r="C814" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D813" s="4" t="inlineStr">
+      <c r="D814" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Masuk</t>
         </is>
       </c>
-      <c r="E813" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F813" s="3" t="inlineStr">
+      <c r="E814" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F814" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G813" s="4" t="inlineStr">
+      <c r="G814" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H813" s="4" t="inlineStr">
+      <c r="H814" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil menampilkan panel Download Export.
@@ -36291,87 +36331,87 @@
         </is>
       </c>
     </row>
-    <row r="814" ht="28" customHeight="1">
-      <c r="A814" s="43" t="inlineStr">
-        <is>
-          <t>64.9</t>
-        </is>
-      </c>
-      <c r="B814" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C814" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D814" s="4" t="inlineStr">
-        <is>
-          <t>Menampilkan data tab Prospek Closing</t>
-        </is>
-      </c>
-      <c r="E814" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F814" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G814" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Closing.</t>
-        </is>
-      </c>
-      <c r="H814" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data pada tab Prospek Closing.</t>
-        </is>
-      </c>
-    </row>
     <row r="815" ht="56" customHeight="1">
       <c r="A815" s="43" t="inlineStr">
         <is>
+          <t>64.9</t>
+        </is>
+      </c>
+      <c r="B815" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C815" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D815" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data tab Prospek Closing</t>
+        </is>
+      </c>
+      <c r="E815" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F815" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G815" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Closing.</t>
+        </is>
+      </c>
+      <c r="H815" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data pada tab Prospek Closing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="816" ht="56" customHeight="1">
+      <c r="A816" s="43" t="inlineStr">
+        <is>
           <t>64.10</t>
         </is>
       </c>
-      <c r="B815" s="3" t="inlineStr">
+      <c r="B816" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C815" s="3" t="inlineStr">
+      <c r="C816" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D815" s="4" t="inlineStr">
+      <c r="D816" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Closing dengan keyword valid</t>
         </is>
       </c>
-      <c r="E815" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F815" s="3" t="inlineStr">
+      <c r="E816" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F816" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G815" s="4" t="inlineStr">
+      <c r="G816" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H815" s="4" t="inlineStr">
+      <c r="H816" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil mengisi field Cari Data.
@@ -36379,45 +36419,45 @@
         </is>
       </c>
     </row>
-    <row r="816" ht="56" customHeight="1">
-      <c r="A816" s="43" t="inlineStr">
+    <row r="817" ht="28" customHeight="1">
+      <c r="A817" s="43" t="inlineStr">
         <is>
           <t>64.11</t>
         </is>
       </c>
-      <c r="B816" s="3" t="inlineStr">
+      <c r="B817" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C816" s="3" t="inlineStr">
+      <c r="C817" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D816" s="4" t="inlineStr">
+      <c r="D817" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E816" s="3" t="inlineStr">
+      <c r="E817" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F816" s="3" t="inlineStr">
+      <c r="F817" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G816" s="4" t="inlineStr">
+      <c r="G817" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H816" s="4" t="inlineStr">
+      <c r="H817" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil mengisi field Cari Data.
@@ -36425,89 +36465,89 @@
         </is>
       </c>
     </row>
-    <row r="817" ht="28" customHeight="1">
-      <c r="A817" s="43" t="inlineStr">
+    <row r="818" ht="28" customHeight="1">
+      <c r="A818" s="43" t="inlineStr">
         <is>
           <t>64.12</t>
         </is>
       </c>
-      <c r="B817" s="3" t="inlineStr">
+      <c r="B818" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C817" s="3" t="inlineStr">
+      <c r="C818" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D817" s="4" t="inlineStr">
+      <c r="D818" s="4" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Closing</t>
         </is>
       </c>
-      <c r="E817" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F817" s="3" t="inlineStr">
+      <c r="E818" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F818" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G817" s="4" t="inlineStr">
+      <c r="G818" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H817" s="4" t="inlineStr">
+      <c r="H818" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="818" ht="28" customHeight="1">
-      <c r="A818" s="43" t="inlineStr">
+    <row r="819" ht="42" customHeight="1">
+      <c r="A819" s="43" t="inlineStr">
         <is>
           <t>64.13</t>
         </is>
       </c>
-      <c r="B818" s="3" t="inlineStr">
+      <c r="B819" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C818" s="3" t="inlineStr">
+      <c r="C819" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D818" s="4" t="inlineStr">
+      <c r="D819" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Closing</t>
         </is>
       </c>
-      <c r="E818" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F818" s="3" t="inlineStr">
+      <c r="E819" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F819" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G818" s="4" t="inlineStr">
+      <c r="G819" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H818" s="4" t="inlineStr">
+      <c r="H819" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil menampilkan panel Download Export.
@@ -36515,87 +36555,87 @@
         </is>
       </c>
     </row>
-    <row r="819" ht="42" customHeight="1">
-      <c r="A819" s="43" t="inlineStr">
-        <is>
-          <t>64.14</t>
-        </is>
-      </c>
-      <c r="B819" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C819" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D819" s="4" t="inlineStr">
-        <is>
-          <t>Menampilkan data tab Prospek Referal</t>
-        </is>
-      </c>
-      <c r="E819" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F819" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G819" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal.</t>
-        </is>
-      </c>
-      <c r="H819" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data pada tab Prospek Referal.</t>
-        </is>
-      </c>
-    </row>
     <row r="820" ht="14" customHeight="1">
       <c r="A820" s="43" t="inlineStr">
         <is>
+          <t>64.14</t>
+        </is>
+      </c>
+      <c r="B820" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C820" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D820" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data tab Prospek Referal</t>
+        </is>
+      </c>
+      <c r="E820" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F820" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G820" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal.</t>
+        </is>
+      </c>
+      <c r="H820" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data pada tab Prospek Referal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="821" ht="56" customHeight="1">
+      <c r="A821" s="43" t="inlineStr">
+        <is>
           <t>64.15</t>
         </is>
       </c>
-      <c r="B820" s="3" t="inlineStr">
+      <c r="B821" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C820" s="3" t="inlineStr">
+      <c r="C821" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D820" s="4" t="inlineStr">
+      <c r="D821" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal dengan keyword valid</t>
         </is>
       </c>
-      <c r="E820" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F820" s="3" t="inlineStr">
+      <c r="E821" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F821" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G820" s="4" t="inlineStr">
+      <c r="G821" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H820" s="4" t="inlineStr">
+      <c r="H821" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil mengisi field Cari Data.
@@ -36603,45 +36643,45 @@
         </is>
       </c>
     </row>
-    <row r="821" ht="56" customHeight="1">
-      <c r="A821" s="43" t="inlineStr">
+    <row r="822" ht="56" customHeight="1">
+      <c r="A822" s="43" t="inlineStr">
         <is>
           <t>64.16</t>
         </is>
       </c>
-      <c r="B821" s="3" t="inlineStr">
+      <c r="B822" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C821" s="3" t="inlineStr">
+      <c r="C822" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D821" s="4" t="inlineStr">
+      <c r="D822" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E821" s="3" t="inlineStr">
+      <c r="E822" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F821" s="3" t="inlineStr">
+      <c r="F822" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G821" s="4" t="inlineStr">
+      <c r="G822" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H821" s="4" t="inlineStr">
+      <c r="H822" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil mengisi field Cari Data.
@@ -36649,89 +36689,89 @@
         </is>
       </c>
     </row>
-    <row r="822" ht="56" customHeight="1">
-      <c r="A822" s="43" t="inlineStr">
+    <row r="823" ht="56" customHeight="1">
+      <c r="A823" s="43" t="inlineStr">
         <is>
           <t>64.17</t>
         </is>
       </c>
-      <c r="B822" s="3" t="inlineStr">
+      <c r="B823" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C822" s="3" t="inlineStr">
+      <c r="C823" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D822" s="4" t="inlineStr">
+      <c r="D823" s="4" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Referal</t>
         </is>
       </c>
-      <c r="E822" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F822" s="3" t="inlineStr">
+      <c r="E823" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F823" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G822" s="4" t="inlineStr">
+      <c r="G823" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H822" s="4" t="inlineStr">
+      <c r="H823" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="823" ht="56" customHeight="1">
-      <c r="A823" s="43" t="inlineStr">
+    <row r="824" ht="14" customHeight="1">
+      <c r="A824" s="43" t="inlineStr">
         <is>
           <t>64.18</t>
         </is>
       </c>
-      <c r="B823" s="3" t="inlineStr">
+      <c r="B824" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C823" s="3" t="inlineStr">
+      <c r="C824" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D823" s="4" t="inlineStr">
+      <c r="D824" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Referal</t>
         </is>
       </c>
-      <c r="E823" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F823" s="3" t="inlineStr">
+      <c r="E824" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F824" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G823" s="4" t="inlineStr">
+      <c r="G824" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H823" s="4" t="inlineStr">
+      <c r="H824" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil menampilkan panel Download Export.
@@ -36739,87 +36779,87 @@
         </is>
       </c>
     </row>
-    <row r="824" ht="14" customHeight="1">
-      <c r="A824" s="43" t="inlineStr">
-        <is>
-          <t>64.19</t>
-        </is>
-      </c>
-      <c r="B824" s="3" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C824" s="3" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D824" s="4" t="inlineStr">
-        <is>
-          <t>Menampilkan data tab Prospek Referal Closing</t>
-        </is>
-      </c>
-      <c r="E824" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F824" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G824" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek Referal Closing.</t>
-        </is>
-      </c>
-      <c r="H824" s="4" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
-        </is>
-      </c>
-    </row>
     <row r="825" ht="14" customHeight="1">
       <c r="A825" s="43" t="inlineStr">
         <is>
+          <t>64.19</t>
+        </is>
+      </c>
+      <c r="B825" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C825" s="3" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D825" s="4" t="inlineStr">
+        <is>
+          <t>Menampilkan data tab Prospek Referal Closing</t>
+        </is>
+      </c>
+      <c r="E825" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F825" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G825" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik tab Prospek Referal Closing.</t>
+        </is>
+      </c>
+      <c r="H825" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="826" ht="14" customHeight="1">
+      <c r="A826" s="43" t="inlineStr">
+        <is>
           <t>64.20</t>
         </is>
       </c>
-      <c r="B825" s="3" t="inlineStr">
+      <c r="B826" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C825" s="3" t="inlineStr">
+      <c r="C826" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D825" s="4" t="inlineStr">
+      <c r="D826" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
         </is>
       </c>
-      <c r="E825" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F825" s="3" t="inlineStr">
+      <c r="E826" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F826" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G825" s="4" t="inlineStr">
+      <c r="G826" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H825" s="4" t="inlineStr">
+      <c r="H826" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil mengisi field Cari Data.
@@ -36827,45 +36867,45 @@
         </is>
       </c>
     </row>
-    <row r="826" ht="14" customHeight="1">
-      <c r="A826" s="43" t="inlineStr">
+    <row r="827" ht="42" customHeight="1">
+      <c r="A827" s="43" t="inlineStr">
         <is>
           <t>64.21</t>
         </is>
       </c>
-      <c r="B826" s="3" t="inlineStr">
+      <c r="B827" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C826" s="3" t="inlineStr">
+      <c r="C827" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D826" s="4" t="inlineStr">
+      <c r="D827" s="4" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal Closing dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E826" s="3" t="inlineStr">
+      <c r="E827" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F826" s="3" t="inlineStr">
+      <c r="F827" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G826" s="4" t="inlineStr">
+      <c r="G827" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H826" s="4" t="inlineStr">
+      <c r="H827" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil mengisi field Cari Data.
@@ -36873,89 +36913,89 @@
         </is>
       </c>
     </row>
-    <row r="827" ht="42" customHeight="1">
-      <c r="A827" s="43" t="inlineStr">
+    <row r="828" ht="14" customHeight="1">
+      <c r="A828" s="43" t="inlineStr">
         <is>
           <t>64.22</t>
         </is>
       </c>
-      <c r="B827" s="3" t="inlineStr">
+      <c r="B828" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C827" s="3" t="inlineStr">
+      <c r="C828" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D827" s="4" t="inlineStr">
+      <c r="D828" s="4" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E827" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F827" s="3" t="inlineStr">
+      <c r="E828" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F828" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G827" s="4" t="inlineStr">
+      <c r="G828" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H827" s="4" t="inlineStr">
+      <c r="H828" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="828" ht="14" customHeight="1">
-      <c r="A828" s="43" t="inlineStr">
+    <row r="829" ht="56" customHeight="1">
+      <c r="A829" s="43" t="inlineStr">
         <is>
           <t>64.23</t>
         </is>
       </c>
-      <c r="B828" s="3" t="inlineStr">
+      <c r="B829" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C828" s="3" t="inlineStr">
+      <c r="C829" s="3" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D828" s="4" t="inlineStr">
+      <c r="D829" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E828" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F828" s="3" t="inlineStr">
+      <c r="E829" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F829" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G828" s="4" t="inlineStr">
+      <c r="G829" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H828" s="4" t="inlineStr">
+      <c r="H829" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil menampilkan panel Download Export.
@@ -36963,89 +37003,89 @@
         </is>
       </c>
     </row>
-    <row r="829" ht="56" customHeight="1">
-      <c r="A829" s="43" t="inlineStr">
+    <row r="830" ht="28" customHeight="1">
+      <c r="A830" s="43" t="inlineStr">
         <is>
           <t>65.1</t>
         </is>
       </c>
-      <c r="B829" s="3" t="inlineStr">
+      <c r="B830" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C829" s="3" t="inlineStr">
+      <c r="C830" s="3" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D829" s="4" t="inlineStr">
+      <c r="D830" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Personal Funnel</t>
         </is>
       </c>
-      <c r="E829" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F829" s="3" t="inlineStr">
+      <c r="E830" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F830" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G829" s="4" t="inlineStr">
+      <c r="G830" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Lending.
 2. Klik sub menu Personal Funnel.</t>
         </is>
       </c>
-      <c r="H829" s="4" t="inlineStr">
+      <c r="H830" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Lending.
 2. Berhasil menampilkan halaman Personal Funnel.</t>
         </is>
       </c>
     </row>
-    <row r="830" ht="28" customHeight="1">
-      <c r="A830" s="43" t="inlineStr">
+    <row r="831" ht="42" customHeight="1">
+      <c r="A831" s="43" t="inlineStr">
         <is>
           <t>65.2</t>
         </is>
       </c>
-      <c r="B830" s="3" t="inlineStr">
+      <c r="B831" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C830" s="3" t="inlineStr">
+      <c r="C831" s="3" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D830" s="4" t="inlineStr">
+      <c r="D831" s="4" t="inlineStr">
         <is>
           <t>Menampilkan data Personal Funnel berdasarkan tab</t>
         </is>
       </c>
-      <c r="E830" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F830" s="3" t="inlineStr">
+      <c r="E831" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F831" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G830" s="4" t="inlineStr">
+      <c r="G831" s="4" t="inlineStr">
         <is>
           <t>1. Klik tab Semua.
 2. Klik tab Non PKS.
 3. Klik tab PKS.</t>
         </is>
       </c>
-      <c r="H830" s="4" t="inlineStr">
+      <c r="H831" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data Personal Funnel pada tab Semua.
 2. Berhasil menampilkan data Personal Funnel pada tab Non PKS.
@@ -37053,479 +37093,517 @@
         </is>
       </c>
     </row>
-    <row r="831" ht="42" customHeight="1">
-      <c r="A831" s="43" t="inlineStr">
+    <row r="832" ht="28" customHeight="1">
+      <c r="A832" s="43" t="inlineStr">
         <is>
           <t>65.3</t>
         </is>
       </c>
-      <c r="B831" s="3" t="inlineStr">
+      <c r="B832" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C831" s="3" t="inlineStr">
+      <c r="C832" s="3" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D831" s="4" t="inlineStr">
+      <c r="D832" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Personal Funnel</t>
         </is>
       </c>
-      <c r="E831" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F831" s="3" t="inlineStr">
+      <c r="E832" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F832" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G831" s="4" t="inlineStr">
+      <c r="G832" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi semua field filter mandatory.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H831" s="4" t="inlineStr">
+      <c r="H832" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field filter mandatory.
 2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="832" ht="28" customHeight="1">
-      <c r="A832" s="43" t="inlineStr">
+    <row r="833" ht="14" customHeight="1">
+      <c r="A833" s="43" t="inlineStr">
         <is>
           <t>65.4</t>
         </is>
       </c>
-      <c r="B832" s="3" t="inlineStr">
+      <c r="B833" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C832" s="3" t="inlineStr">
+      <c r="C833" s="3" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D832" s="4" t="inlineStr">
+      <c r="D833" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E832" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F832" s="3" t="inlineStr">
+      <c r="E833" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F833" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G832" s="4" t="inlineStr">
+      <c r="G833" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H832" s="4" t="inlineStr">
+      <c r="H833" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
-    <row r="833" ht="14" customHeight="1">
-      <c r="A833" s="43" t="inlineStr">
+    <row r="834" ht="14" customHeight="1">
+      <c r="A834" s="43" t="inlineStr">
         <is>
           <t>65.5</t>
         </is>
       </c>
-      <c r="B833" s="3" t="inlineStr">
+      <c r="B834" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C833" s="3" t="inlineStr">
+      <c r="C834" s="3" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D833" s="4" t="inlineStr">
+      <c r="D834" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data Personal Funnel</t>
         </is>
       </c>
-      <c r="E833" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F833" s="3" t="inlineStr">
+      <c r="E834" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F834" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G833" s="4" t="inlineStr">
+      <c r="G834" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Export.
 2. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H833" s="4" t="inlineStr">
+      <c r="H834" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan panel Download Export.
 2. Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
-    <row r="834" ht="14" customHeight="1">
-      <c r="A834" s="43" t="inlineStr">
+    <row r="835" ht="14" customHeight="1">
+      <c r="A835" s="43" t="inlineStr">
         <is>
           <t>66.1</t>
         </is>
       </c>
-      <c r="B834" s="3" t="inlineStr">
+      <c r="B835" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C834" s="3" t="inlineStr">
+      <c r="C835" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D834" s="4" t="inlineStr">
+      <c r="D835" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Rekap Funnel</t>
         </is>
       </c>
-      <c r="E834" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F834" s="3" t="inlineStr">
+      <c r="E835" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F835" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G834" s="4" t="inlineStr">
+      <c r="G835" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Lending.
 2. Klik sub menu Rekap Funnel.</t>
         </is>
       </c>
-      <c r="H834" s="4" t="inlineStr">
+      <c r="H835" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Lending.
 2. Berhasil menampilkan halaman Rekap Funnel.</t>
         </is>
       </c>
     </row>
-    <row r="835" ht="14" customHeight="1">
-      <c r="A835" s="43" t="n">
+    <row r="836" ht="42" customHeight="1">
+      <c r="A836" s="43" t="n">
         <v>66.2</v>
       </c>
-      <c r="B835" s="3" t="inlineStr">
+      <c r="B836" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C835" s="3" t="inlineStr">
+      <c r="C836" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D835" s="4" t="inlineStr">
+      <c r="D836" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Rekap Funnel</t>
         </is>
       </c>
-      <c r="E835" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F835" s="3" t="inlineStr">
+      <c r="E836" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F836" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G835" s="4" t="inlineStr">
+      <c r="G836" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H835" s="4" t="inlineStr">
+      <c r="H836" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi kriteria filter.
 2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="836" ht="42" customHeight="1">
-      <c r="A836" s="43" t="n">
+    <row r="837" ht="28" customHeight="1">
+      <c r="A837" s="43" t="n">
         <v>66.3</v>
       </c>
-      <c r="B836" s="3" t="inlineStr">
+      <c r="B837" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C836" s="3" t="inlineStr">
+      <c r="C837" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D836" s="4" t="inlineStr">
+      <c r="D837" s="4" t="inlineStr">
         <is>
           <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E836" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F836" s="3" t="inlineStr">
+      <c r="E837" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F837" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G836" s="4" t="inlineStr">
+      <c r="G837" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H836" s="4" t="inlineStr">
+      <c r="H837" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
-    <row r="837" ht="28" customHeight="1">
-      <c r="A837" s="43" t="n">
+    <row r="838" ht="28" customHeight="1">
+      <c r="A838" s="43" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="B837" s="3" t="inlineStr">
+      <c r="B838" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C837" s="3" t="inlineStr">
+      <c r="C838" s="3" t="inlineStr">
         <is>
           <t>Rekap Funnel</t>
         </is>
       </c>
-      <c r="D837" s="4" t="inlineStr">
+      <c r="D838" s="4" t="inlineStr">
         <is>
           <t>Mengekspor data Rekap Funnel</t>
         </is>
       </c>
-      <c r="E837" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F837" s="3" t="inlineStr">
+      <c r="E838" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F838" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G837" s="4" t="inlineStr">
+      <c r="G838" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Export.
 2. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H837" s="4" t="inlineStr">
+      <c r="H838" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan panel Download Export.
 2. Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
-    <row r="838" ht="28" customHeight="1">
-      <c r="A838" s="43" t="inlineStr">
-        <is>
-          <t>67.1</t>
-        </is>
-      </c>
-      <c r="B838" s="3" t="inlineStr">
+    <row r="839" ht="70" customHeight="1">
+      <c r="A839" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="B839" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C838" s="3" t="inlineStr">
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Mereset filter data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>1. Klik button Reset pada panel Filter.</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan kriteria filter dan mengembalikan kondisi filter ke default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="840" ht="28" customHeight="1">
+      <c r="A840" s="43" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="B840" s="3" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C840" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D838" s="4" t="inlineStr">
+      <c r="D840" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Pengaturan Funnel Lending</t>
         </is>
       </c>
-      <c r="E838" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F838" s="3" t="inlineStr">
+      <c r="E840" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F840" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G838" s="4" t="inlineStr">
+      <c r="G840" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Report Lending.
 2. Klik sub menu Pengaturan Funnel.</t>
         </is>
       </c>
-      <c r="H838" s="4" t="inlineStr">
+      <c r="H840" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Lending.
 2. Berhasil menampilkan halaman Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="839" ht="70" customHeight="1">
-      <c r="A839" s="43" t="inlineStr">
+    <row r="841" ht="84" customHeight="1">
+      <c r="A841" s="43" t="inlineStr">
         <is>
           <t>67.2</t>
         </is>
       </c>
-      <c r="B839" s="3" t="inlineStr">
+      <c r="B841" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C839" s="3" t="inlineStr">
+      <c r="C841" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D839" s="4" t="inlineStr">
+      <c r="D841" s="4" t="inlineStr">
         <is>
           <t>Mengubah data Pengaturan Funnel Lending</t>
         </is>
       </c>
-      <c r="E839" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F839" s="3" t="inlineStr">
+      <c r="E841" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F841" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G839" s="4" t="inlineStr">
+      <c r="G841" s="4" t="inlineStr">
         <is>
           <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H839" s="4" t="inlineStr">
+      <c r="H841" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field Performance Percentage.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="840" ht="28" customHeight="1">
-      <c r="A840" s="43" t="inlineStr">
+    <row r="842" ht="28" customHeight="1">
+      <c r="A842" s="43" t="inlineStr">
         <is>
           <t>67.3</t>
         </is>
       </c>
-      <c r="B840" s="3" t="inlineStr">
+      <c r="B842" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C840" s="3" t="inlineStr">
+      <c r="C842" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D840" s="4" t="inlineStr">
+      <c r="D842" s="4" t="inlineStr">
         <is>
           <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E840" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F840" s="3" t="inlineStr">
+      <c r="E842" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F842" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G840" s="4" t="inlineStr">
+      <c r="G842" s="4" t="inlineStr">
         <is>
           <t>1. Mengosongkan field mandatory Performance Percentage.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H840" s="4" t="inlineStr">
+      <c r="H842" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field Performance Percentage.
 2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
-    <row r="841" ht="84" customHeight="1">
-      <c r="A841" s="43" t="inlineStr">
+    <row r="843" ht="28" customHeight="1">
+      <c r="A843" s="43" t="inlineStr">
         <is>
           <t>67.4</t>
         </is>
       </c>
-      <c r="B841" s="3" t="inlineStr">
+      <c r="B843" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C841" s="3" t="inlineStr">
+      <c r="C843" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D841" s="4" t="inlineStr">
+      <c r="D843" s="4" t="inlineStr">
         <is>
           <t>Menambahkan Kondisi pada Indikator Performa</t>
         </is>
       </c>
-      <c r="E841" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F841" s="3" t="inlineStr">
+      <c r="E843" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F843" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G841" s="4" t="inlineStr">
+      <c r="G843" s="4" t="inlineStr">
         <is>
           <t>1. Klik button + Tambah Kondisi pada bagian Indikator Performa.
 2. Mengisi semua field mandatory pada kondisi baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H841" s="4" t="inlineStr">
+      <c r="H843" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan form kondisi baru pada Indikator Performa.
 2. Berhasil mengisi field mandatory kondisi.
@@ -37533,89 +37611,89 @@
         </is>
       </c>
     </row>
-    <row r="842" ht="28" customHeight="1">
-      <c r="A842" s="43" t="inlineStr">
+    <row r="844" ht="28" customHeight="1">
+      <c r="A844" s="43" t="inlineStr">
         <is>
           <t>67.5</t>
         </is>
       </c>
-      <c r="B842" s="3" t="inlineStr">
+      <c r="B844" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C842" s="3" t="inlineStr">
+      <c r="C844" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D842" s="4" t="inlineStr">
+      <c r="D844" s="4" t="inlineStr">
         <is>
           <t>Menghapus Kondisi pada Indikator Performa</t>
         </is>
       </c>
-      <c r="E842" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F842" s="3" t="inlineStr">
+      <c r="E844" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F844" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G842" s="4" t="inlineStr">
+      <c r="G844" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Hapus pada salah satu kondisi di Indikator Performa.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H842" s="4" t="inlineStr">
+      <c r="H844" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menghapus kondisi dari Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="843" ht="28" customHeight="1">
-      <c r="A843" s="43" t="inlineStr">
+    <row r="845" ht="42" customHeight="1">
+      <c r="A845" s="43" t="inlineStr">
         <is>
           <t>67.6</t>
         </is>
       </c>
-      <c r="B843" s="3" t="inlineStr">
+      <c r="B845" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C843" s="3" t="inlineStr">
+      <c r="C845" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D843" s="4" t="inlineStr">
+      <c r="D845" s="4" t="inlineStr">
         <is>
           <t>Menambahkan Operator pada Kondisi</t>
         </is>
       </c>
-      <c r="E843" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F843" s="3" t="inlineStr">
+      <c r="E845" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F845" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G843" s="4" t="inlineStr">
+      <c r="G845" s="4" t="inlineStr">
         <is>
           <t>1. Klik link tambah operator pada salah satu kondisi di Indikator Performa.
 2. Mengisi field operator baru.
 3. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H843" s="4" t="inlineStr">
+      <c r="H845" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan baris operator baru pada kondisi.
 2. Berhasil mengisi data operator.
@@ -37623,170 +37701,170 @@
         </is>
       </c>
     </row>
-    <row r="844" ht="28" customHeight="1">
-      <c r="A844" s="43" t="inlineStr">
+    <row r="846" ht="28" customHeight="1">
+      <c r="A846" s="43" t="inlineStr">
         <is>
           <t>67.7</t>
         </is>
       </c>
-      <c r="B844" s="3" t="inlineStr">
+      <c r="B846" s="3" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C844" s="3" t="inlineStr">
+      <c r="C846" s="3" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D844" s="4" t="inlineStr">
+      <c r="D846" s="4" t="inlineStr">
         <is>
           <t>Menghapus Operator pada Kondisi</t>
         </is>
       </c>
-      <c r="E844" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F844" s="3" t="inlineStr">
+      <c r="E846" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F846" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G844" s="4" t="inlineStr">
+      <c r="G846" s="4" t="inlineStr">
         <is>
           <t>1. Klik button x pada salah satu operator di Indikator Performa.
 2. Klik button Simpan Pengaturan.</t>
         </is>
       </c>
-      <c r="H844" s="4" t="inlineStr">
+      <c r="H846" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menghapus operator dari kondisi di Indikator Performa.
 2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
-    <row r="845" ht="42" customHeight="1">
-      <c r="A845" s="43" t="inlineStr">
+    <row r="847" ht="14" customHeight="1">
+      <c r="A847" s="43" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="B845" s="3" t="inlineStr">
+      <c r="B847" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C845" s="3" t="inlineStr">
+      <c r="C847" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D845" s="4" t="inlineStr">
+      <c r="D847" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Approval non Banking</t>
         </is>
       </c>
-      <c r="E845" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F845" s="3" t="inlineStr">
+      <c r="E847" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F847" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G845" s="4" t="inlineStr">
+      <c r="G847" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Re-Assign &amp; Approval 
 2. Klik submenu Approval non banking</t>
         </is>
       </c>
-      <c r="H845" s="4" t="inlineStr">
+      <c r="H847" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan submenu Re-Assign &amp; Approval 
 2. Menampilkan halaman Approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="846" ht="28" customHeight="1">
-      <c r="A846" s="43" t="inlineStr">
+    <row r="848" ht="14" customHeight="1">
+      <c r="A848" s="43" t="inlineStr">
         <is>
           <t>68.2</t>
         </is>
       </c>
-      <c r="B846" s="3" t="inlineStr">
+      <c r="B848" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C846" s="3" t="inlineStr">
+      <c r="C848" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D846" s="4" t="inlineStr">
+      <c r="D848" s="4" t="inlineStr">
         <is>
           <t>Melihat Detail data Approval non banking</t>
         </is>
       </c>
-      <c r="E846" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F846" s="3" t="inlineStr">
+      <c r="E848" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F848" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G846" s="4" t="inlineStr">
+      <c r="G848" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Detail</t>
         </is>
       </c>
-      <c r="H846" s="4" t="inlineStr">
+      <c r="H848" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan halaman detail data approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="847" ht="14" customHeight="1">
-      <c r="A847" s="43" t="inlineStr">
+    <row r="849" ht="42" customHeight="1">
+      <c r="A849" s="43" t="inlineStr">
         <is>
           <t>68.3</t>
         </is>
       </c>
-      <c r="B847" s="3" t="inlineStr">
+      <c r="B849" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C847" s="3" t="inlineStr">
+      <c r="C849" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D847" s="4" t="inlineStr">
+      <c r="D849" s="4" t="inlineStr">
         <is>
           <t>Menyetujui Prospek</t>
         </is>
       </c>
-      <c r="E847" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F847" s="3" t="inlineStr">
+      <c r="E849" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F849" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G847" s="4" t="inlineStr">
+      <c r="G849" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Setujui 
@@ -37795,7 +37873,7 @@
 5. Klik button Setujui</t>
         </is>
       </c>
-      <c r="H847" s="4" t="inlineStr">
+      <c r="H849" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan modal approve 
@@ -37805,87 +37883,87 @@
         </is>
       </c>
     </row>
-    <row r="848" ht="14" customHeight="1">
-      <c r="A848" s="43" t="inlineStr">
+    <row r="850" ht="28" customHeight="1">
+      <c r="A850" s="43" t="inlineStr">
         <is>
           <t>68.4</t>
         </is>
       </c>
-      <c r="B848" s="3" t="inlineStr">
+      <c r="B850" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C848" s="3" t="inlineStr">
+      <c r="C850" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D848" s="4" t="inlineStr">
+      <c r="D850" s="4" t="inlineStr">
         <is>
           <t>Batal menyetujui Prospek</t>
         </is>
       </c>
-      <c r="E848" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F848" s="3" t="inlineStr">
+      <c r="E850" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F850" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G848" s="4" t="inlineStr">
+      <c r="G850" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Batalkan pada modal approve</t>
         </is>
       </c>
-      <c r="H848" s="4" t="inlineStr">
+      <c r="H850" s="4" t="inlineStr">
         <is>
           <t>1. Modal approve tertutup dan tetap di halaman approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="849" ht="42" customHeight="1">
-      <c r="A849" s="43" t="inlineStr">
+    <row r="851" ht="28" customHeight="1">
+      <c r="A851" s="43" t="inlineStr">
         <is>
           <t>68.5</t>
         </is>
       </c>
-      <c r="B849" s="3" t="inlineStr">
+      <c r="B851" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C849" s="3" t="inlineStr">
+      <c r="C851" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D849" s="4" t="inlineStr">
+      <c r="D851" s="4" t="inlineStr">
         <is>
           <t>Tidak menginput nilai realisasi pada modal approve</t>
         </is>
       </c>
-      <c r="E849" s="3" t="inlineStr">
+      <c r="E851" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F849" s="3" t="inlineStr">
+      <c r="F851" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G849" s="4" t="inlineStr">
+      <c r="G851" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan nilai realisasi 
 2. Input remark 
 3. Klik button Setujui</t>
         </is>
       </c>
-      <c r="H849" s="4" t="inlineStr">
+      <c r="H851" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field realisasi 
 2. Berhasil menginput remark 
@@ -37893,122 +37971,122 @@
         </is>
       </c>
     </row>
-    <row r="850" ht="28" customHeight="1">
-      <c r="A850" s="43" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
-      <c r="B850" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C850" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D850" s="4" t="inlineStr">
-        <is>
-          <t>Tidak menginput remark pada modal approve</t>
-        </is>
-      </c>
-      <c r="E850" s="3" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F850" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G850" s="4" t="inlineStr">
-        <is>
-          <t>1. Kosongkan remark</t>
-        </is>
-      </c>
-      <c r="H850" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan alert 'Remark dibutuhkan!'</t>
-        </is>
-      </c>
-    </row>
-    <row r="851" ht="28" customHeight="1">
-      <c r="A851" s="43" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="B851" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C851" s="3" t="inlineStr">
-        <is>
-          <t>Approval Non Banking</t>
-        </is>
-      </c>
-      <c r="D851" s="4" t="inlineStr">
-        <is>
-          <t>Menginput huruf pada field realisasi</t>
-        </is>
-      </c>
-      <c r="E851" s="3" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F851" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G851" s="4" t="inlineStr">
-        <is>
-          <t>1. Input huruf pada field realisasi kemudian pindah ke filed lain</t>
-        </is>
-      </c>
-      <c r="H851" s="4" t="inlineStr">
-        <is>
-          <t>1. Sistem menghapus input non-numerik secara otomatis saat field kehilangan fokus. Field Realiasi menjadi kosong</t>
-        </is>
-      </c>
-    </row>
     <row r="852" ht="28" customHeight="1">
       <c r="A852" s="43" t="inlineStr">
         <is>
+          <t>68.6</t>
+        </is>
+      </c>
+      <c r="B852" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C852" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D852" s="4" t="inlineStr">
+        <is>
+          <t>Tidak menginput remark pada modal approve</t>
+        </is>
+      </c>
+      <c r="E852" s="3" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F852" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G852" s="4" t="inlineStr">
+        <is>
+          <t>1. Kosongkan remark</t>
+        </is>
+      </c>
+      <c r="H852" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan alert 'Remark dibutuhkan!'</t>
+        </is>
+      </c>
+    </row>
+    <row r="853" ht="28" customHeight="1">
+      <c r="A853" s="43" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="B853" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C853" s="3" t="inlineStr">
+        <is>
+          <t>Approval Non Banking</t>
+        </is>
+      </c>
+      <c r="D853" s="4" t="inlineStr">
+        <is>
+          <t>Menginput huruf pada field realisasi</t>
+        </is>
+      </c>
+      <c r="E853" s="3" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F853" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G853" s="4" t="inlineStr">
+        <is>
+          <t>1. Input huruf pada field realisasi kemudian pindah ke filed lain</t>
+        </is>
+      </c>
+      <c r="H853" s="4" t="inlineStr">
+        <is>
+          <t>1. Sistem menghapus input non-numerik secara otomatis saat field kehilangan fokus. Field Realiasi menjadi kosong</t>
+        </is>
+      </c>
+    </row>
+    <row r="854" ht="28" customHeight="1">
+      <c r="A854" s="43" t="inlineStr">
+        <is>
           <t>68.8</t>
         </is>
       </c>
-      <c r="B852" s="3" t="inlineStr">
+      <c r="B854" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C852" s="3" t="inlineStr">
+      <c r="C854" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D852" s="4" t="inlineStr">
+      <c r="D854" s="4" t="inlineStr">
         <is>
           <t>Menolak Prospek</t>
         </is>
       </c>
-      <c r="E852" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F852" s="3" t="inlineStr">
+      <c r="E854" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F854" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G852" s="4" t="inlineStr">
+      <c r="G854" s="4" t="inlineStr">
         <is>
           <t>1. Klik titik tiga 
 2. Klik Tolak 
@@ -38016,7 +38094,7 @@
 4. Klik button Tolak</t>
         </is>
       </c>
-      <c r="H852" s="4" t="inlineStr">
+      <c r="H854" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan beberapa action (detail, setujui, tolak)
 2. Menampilkan modal tolak prospek
@@ -38025,210 +38103,210 @@
         </is>
       </c>
     </row>
-    <row r="853" ht="28" customHeight="1">
-      <c r="A853" s="43" t="inlineStr">
+    <row r="855" ht="28" customHeight="1">
+      <c r="A855" s="43" t="inlineStr">
         <is>
           <t>68.9</t>
         </is>
       </c>
-      <c r="B853" s="3" t="inlineStr">
+      <c r="B855" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C853" s="3" t="inlineStr">
+      <c r="C855" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D853" s="4" t="inlineStr">
+      <c r="D855" s="4" t="inlineStr">
         <is>
           <t>Batal menolak prospek</t>
         </is>
       </c>
-      <c r="E853" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F853" s="3" t="inlineStr">
+      <c r="E855" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F855" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G853" s="4" t="inlineStr">
+      <c r="G855" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Batalkan pada moal tolak prospek</t>
         </is>
       </c>
-      <c r="H853" s="4" t="inlineStr">
+      <c r="H855" s="4" t="inlineStr">
         <is>
           <t>1. Modal tolak prospek tertutup dan tetap berada di halaman approval non banking</t>
         </is>
       </c>
     </row>
-    <row r="854" ht="28" customHeight="1">
-      <c r="A854" s="43" t="inlineStr">
+    <row r="856" ht="28" customHeight="1">
+      <c r="A856" s="43" t="inlineStr">
         <is>
           <t>68.10</t>
         </is>
       </c>
-      <c r="B854" s="3" t="inlineStr">
+      <c r="B856" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C854" s="3" t="inlineStr">
+      <c r="C856" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D854" s="4" t="inlineStr">
+      <c r="D856" s="4" t="inlineStr">
         <is>
           <t>Tidak menginput remark pada modal tolak prospek</t>
         </is>
       </c>
-      <c r="E854" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F854" s="3" t="inlineStr">
+      <c r="E856" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F856" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G854" s="4" t="inlineStr">
+      <c r="G856" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan remark 
 2. Klik button Tolak</t>
         </is>
       </c>
-      <c r="H854" s="4" t="inlineStr">
+      <c r="H856" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan remark 
 2. Menampilkan alert 'Remark dibutuhkan!'</t>
         </is>
       </c>
     </row>
-    <row r="855" ht="28" customHeight="1">
-      <c r="A855" s="43" t="inlineStr">
+    <row r="857" ht="28" customHeight="1">
+      <c r="A857" s="43" t="inlineStr">
         <is>
           <t>68.11</t>
         </is>
       </c>
-      <c r="B855" s="3" t="inlineStr">
+      <c r="B857" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C855" s="3" t="inlineStr">
+      <c r="C857" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D855" s="4" t="inlineStr">
+      <c r="D857" s="4" t="inlineStr">
         <is>
           <t>Filter kolom</t>
         </is>
       </c>
-      <c r="E855" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F855" s="3" t="inlineStr">
+      <c r="E857" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F857" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G855" s="4" t="inlineStr">
+      <c r="G857" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon filter kolom 
 2. Checklist/unchecklist kolom</t>
         </is>
       </c>
-      <c r="H855" s="4" t="inlineStr">
+      <c r="H857" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan list kolom tabel 
 2. Menampilkan data tabel sesuai dengan kolom yang di ceklis</t>
         </is>
       </c>
     </row>
-    <row r="856" ht="28" customHeight="1">
-      <c r="A856" s="43" t="inlineStr">
+    <row r="858" ht="28" customHeight="1">
+      <c r="A858" s="43" t="inlineStr">
         <is>
           <t>68.12</t>
         </is>
       </c>
-      <c r="B856" s="3" t="inlineStr">
+      <c r="B858" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C856" s="3" t="inlineStr">
+      <c r="C858" s="3" t="inlineStr">
         <is>
           <t>Approval Non Banking</t>
         </is>
       </c>
-      <c r="D856" s="4" t="inlineStr">
+      <c r="D858" s="4" t="inlineStr">
         <is>
           <t>Reset ke Default pada filter kolom</t>
         </is>
       </c>
-      <c r="E856" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F856" s="3" t="inlineStr">
+      <c r="E858" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F858" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G856" s="4" t="inlineStr">
+      <c r="G858" s="4" t="inlineStr">
         <is>
           <t>1. Klik Reset ke Default</t>
         </is>
       </c>
-      <c r="H856" s="4" t="inlineStr">
+      <c r="H858" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data tabel dengan kolom default</t>
         </is>
       </c>
     </row>
-    <row r="857" ht="28" customHeight="1">
-      <c r="A857" s="43" t="inlineStr">
+    <row r="859" ht="28" customHeight="1">
+      <c r="A859" s="43" t="inlineStr">
         <is>
           <t>69.1</t>
         </is>
       </c>
-      <c r="B857" s="3" t="inlineStr">
+      <c r="B859" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C857" s="3" t="inlineStr">
+      <c r="C859" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D857" s="4" t="inlineStr">
+      <c r="D859" s="4" t="inlineStr">
         <is>
           <t>Filter data</t>
         </is>
       </c>
-      <c r="E857" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F857" s="3" t="inlineStr">
+      <c r="E859" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F859" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G857" s="4" t="inlineStr">
+      <c r="G859" s="4" t="inlineStr">
         <is>
           <t>1. Pilih kantor wilayah
 2. Pilih kantor cabang 
@@ -38238,7 +38316,7 @@
 6. Klik button Filter</t>
         </is>
       </c>
-      <c r="H857" s="4" t="inlineStr">
+      <c r="H859" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list data filter kantor wilayah dan dapat di pilih
 2. Menampilkan dropdown list data filter kantor cabang dan dapat di pilih
@@ -38249,126 +38327,126 @@
         </is>
       </c>
     </row>
-    <row r="858" ht="28" customHeight="1">
-      <c r="A858" s="43" t="inlineStr">
+    <row r="860" ht="28" customHeight="1">
+      <c r="A860" s="43" t="inlineStr">
         <is>
           <t>69.2</t>
         </is>
       </c>
-      <c r="B858" s="3" t="inlineStr">
+      <c r="B860" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C858" s="3" t="inlineStr">
+      <c r="C860" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D858" s="4" t="inlineStr">
+      <c r="D860" s="4" t="inlineStr">
         <is>
           <t>Mencari data</t>
         </is>
       </c>
-      <c r="E858" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F858" s="3" t="inlineStr">
+      <c r="E860" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F860" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G858" s="4" t="inlineStr">
+      <c r="G860" s="4" t="inlineStr">
         <is>
           <t>1. Input keyword pada field search 
 2. Klik icon search yang ada di sebelah field</t>
         </is>
       </c>
-      <c r="H858" s="4" t="inlineStr">
+      <c r="H860" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput keyword 
 2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
         </is>
       </c>
     </row>
-    <row r="859" ht="28" customHeight="1">
-      <c r="A859" s="43" t="inlineStr">
+    <row r="861" ht="28" customHeight="1">
+      <c r="A861" s="43" t="inlineStr">
         <is>
           <t>69.3</t>
         </is>
       </c>
-      <c r="B859" s="3" t="inlineStr">
+      <c r="B861" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C859" s="3" t="inlineStr">
+      <c r="C861" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D859" s="4" t="inlineStr">
+      <c r="D861" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E859" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F859" s="3" t="inlineStr">
+      <c r="E861" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F861" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G859" s="4" t="inlineStr">
+      <c r="G861" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Re-Assign &amp; Approval 
 2. Klik submenu Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="H859" s="4" t="inlineStr">
+      <c r="H861" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan submenu Re-Assign &amp; Approval 
 2. Menampilkan halaman Re-Assign Prospek</t>
         </is>
       </c>
     </row>
-    <row r="860" ht="28" customHeight="1">
-      <c r="A860" s="43" t="inlineStr">
+    <row r="862" ht="28" customHeight="1">
+      <c r="A862" s="43" t="inlineStr">
         <is>
           <t>69.4</t>
         </is>
       </c>
-      <c r="B860" s="3" t="inlineStr">
+      <c r="B862" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C860" s="3" t="inlineStr">
+      <c r="C862" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D860" s="4" t="inlineStr">
+      <c r="D862" s="4" t="inlineStr">
         <is>
           <t>Filter data</t>
         </is>
       </c>
-      <c r="E860" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F860" s="3" t="inlineStr">
+      <c r="E862" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F862" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G860" s="4" t="inlineStr">
+      <c r="G862" s="4" t="inlineStr">
         <is>
           <t>1. Pilih kantor wilayah
 2. Pilih kantor cabang 
@@ -38378,7 +38456,7 @@
 6. Klik button Filter</t>
         </is>
       </c>
-      <c r="H860" s="4" t="inlineStr">
+      <c r="H862" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list data filter kantor wilayah dan dapat di pilih
 2. Menampilkan dropdown list data filter kantor cabang dan dapat di pilih
@@ -38389,252 +38467,252 @@
         </is>
       </c>
     </row>
-    <row r="861" ht="28" customHeight="1">
-      <c r="A861" s="43" t="inlineStr">
+    <row r="863" ht="28" customHeight="1">
+      <c r="A863" s="43" t="inlineStr">
         <is>
           <t>69.5</t>
         </is>
       </c>
-      <c r="B861" s="3" t="inlineStr">
+      <c r="B863" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C861" s="3" t="inlineStr">
+      <c r="C863" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D861" s="4" t="inlineStr">
+      <c r="D863" s="4" t="inlineStr">
         <is>
           <t>Mencari data</t>
         </is>
       </c>
-      <c r="E861" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F861" s="3" t="inlineStr">
+      <c r="E863" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F863" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G861" s="4" t="inlineStr">
+      <c r="G863" s="4" t="inlineStr">
         <is>
           <t>1. Input keyword pada field search 
 2. Klik icon search yang ada di sebelah field</t>
         </is>
       </c>
-      <c r="H861" s="4" t="inlineStr">
+      <c r="H863" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput keyword 
 2. Menampilkan data Re-Assign Prospek sesuai dengan keyword yang di cari</t>
         </is>
       </c>
     </row>
-    <row r="862" ht="28" customHeight="1">
-      <c r="A862" s="43" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
-      <c r="B862" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C862" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D862" s="4" t="inlineStr">
-        <is>
-          <t>Validasi count checklist data</t>
-        </is>
-      </c>
-      <c r="E862" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F862" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G862" s="4" t="inlineStr">
-        <is>
-          <t>1. Cek informasi yang ada pada button Reassign () data</t>
-        </is>
-      </c>
-      <c r="H862" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan count angka yang sesuai dengan data yang di checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="863" ht="28" customHeight="1">
-      <c r="A863" s="43" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
-      <c r="B863" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C863" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D863" s="4" t="inlineStr">
-        <is>
-          <t>Validasi data yang sudah dii pilih</t>
-        </is>
-      </c>
-      <c r="E863" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F863" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G863" s="4" t="inlineStr">
-        <is>
-          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi prospek yang di pilih</t>
-        </is>
-      </c>
-      <c r="H863" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan data tabel prospek yang di pilih saja</t>
-        </is>
-      </c>
-    </row>
     <row r="864" ht="28" customHeight="1">
       <c r="A864" s="43" t="inlineStr">
         <is>
+          <t>69.6</t>
+        </is>
+      </c>
+      <c r="B864" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C864" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D864" s="4" t="inlineStr">
+        <is>
+          <t>Validasi count checklist data</t>
+        </is>
+      </c>
+      <c r="E864" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F864" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G864" s="4" t="inlineStr">
+        <is>
+          <t>1. Cek informasi yang ada pada button Reassign () data</t>
+        </is>
+      </c>
+      <c r="H864" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan count angka yang sesuai dengan data yang di checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="865" ht="28" customHeight="1">
+      <c r="A865" s="43" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="B865" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C865" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D865" s="4" t="inlineStr">
+        <is>
+          <t>Validasi data yang sudah dii pilih</t>
+        </is>
+      </c>
+      <c r="E865" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F865" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G865" s="4" t="inlineStr">
+        <is>
+          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi prospek yang di pilih</t>
+        </is>
+      </c>
+      <c r="H865" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan data tabel prospek yang di pilih saja</t>
+        </is>
+      </c>
+    </row>
+    <row r="866" ht="28" customHeight="1">
+      <c r="A866" s="43" t="inlineStr">
+        <is>
           <t>69.8</t>
         </is>
       </c>
-      <c r="B864" s="3" t="inlineStr">
+      <c r="B866" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C864" s="3" t="inlineStr">
+      <c r="C866" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D864" s="4" t="inlineStr">
+      <c r="D866" s="4" t="inlineStr">
         <is>
           <t>Mengosongkan field inputan mandatory pada reassign prospek</t>
         </is>
       </c>
-      <c r="E864" s="3" t="inlineStr">
+      <c r="E866" s="3" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F864" s="3" t="inlineStr">
+      <c r="F866" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G864" s="4" t="inlineStr">
+      <c r="G866" s="4" t="inlineStr">
         <is>
           <t>1. Kosongkan salah satu atau semua field mandatory 
 2. Klik button Submit</t>
         </is>
       </c>
-      <c r="H864" s="4" t="inlineStr">
+      <c r="H866" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil tidak mengisi/mengosongkan field 
 2. Menampilkan alert pada setiap field mandatory bahwa field tersebut dibutuhkan / wajib diisi</t>
         </is>
       </c>
     </row>
-    <row r="865" ht="28" customHeight="1">
-      <c r="A865" s="43" t="inlineStr">
+    <row r="867" ht="28" customHeight="1">
+      <c r="A867" s="43" t="inlineStr">
         <is>
           <t>69.9</t>
         </is>
       </c>
-      <c r="B865" s="3" t="inlineStr">
+      <c r="B867" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C865" s="3" t="inlineStr">
+      <c r="C867" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D865" s="4" t="inlineStr">
+      <c r="D867" s="4" t="inlineStr">
         <is>
           <t>Membatalkan Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E865" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F865" s="3" t="inlineStr">
+      <c r="E867" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F867" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G865" s="4" t="inlineStr">
+      <c r="G867" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
         </is>
       </c>
-      <c r="H865" s="4" t="inlineStr">
+      <c r="H867" s="4" t="inlineStr">
         <is>
           <t>1. Kembali ke halaman utama Re-assign Prospek</t>
         </is>
       </c>
     </row>
-    <row r="866" ht="28" customHeight="1">
-      <c r="A866" s="43" t="inlineStr">
+    <row r="868" ht="28" customHeight="1">
+      <c r="A868" s="43" t="inlineStr">
         <is>
           <t>69.10</t>
         </is>
       </c>
-      <c r="B866" s="3" t="inlineStr">
+      <c r="B868" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C866" s="3" t="inlineStr">
+      <c r="C868" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D866" s="4" t="inlineStr">
+      <c r="D868" s="4" t="inlineStr">
         <is>
           <t>Validasi data prospek yang di re-assign</t>
         </is>
       </c>
-      <c r="E866" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F866" s="3" t="inlineStr">
+      <c r="E868" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F868" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G866" s="4" t="inlineStr">
+      <c r="G868" s="4" t="inlineStr">
         <is>
           <t>1. Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek 
 2. Klik menu Lead Qualification 
@@ -38642,7 +38720,7 @@
 4. Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
-      <c r="H866" s="4" t="inlineStr">
+      <c r="H868" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login 
 2. Menampilkan dropdown submenu Lead Qualification 
@@ -38651,38 +38729,38 @@
         </is>
       </c>
     </row>
-    <row r="867" ht="28" customHeight="1">
-      <c r="A867" s="43" t="inlineStr">
+    <row r="869" ht="28" customHeight="1">
+      <c r="A869" s="43" t="inlineStr">
         <is>
           <t>69.11</t>
         </is>
       </c>
-      <c r="B867" s="3" t="inlineStr">
+      <c r="B869" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C867" s="3" t="inlineStr">
+      <c r="C869" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D867" s="4" t="inlineStr">
+      <c r="D869" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-assign prospek semua data</t>
         </is>
       </c>
-      <c r="E867" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F867" s="3" t="inlineStr">
+      <c r="E869" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F869" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G867" s="4" t="inlineStr">
+      <c r="G869" s="4" t="inlineStr">
         <is>
           <t>1. Klik button Reassign semua data 
 2. Klik button Yes 
@@ -38693,7 +38771,7 @@
 7. Klik button Submit</t>
         </is>
       </c>
-      <c r="H867" s="4" t="inlineStr">
+      <c r="H869" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan popup konfirmasi 
 2. Menampilkan halaman pindah kelolaan 
@@ -38705,122 +38783,122 @@
         </is>
       </c>
     </row>
-    <row r="868" ht="28" customHeight="1">
-      <c r="A868" s="43" t="inlineStr">
-        <is>
-          <t>69.12</t>
-        </is>
-      </c>
-      <c r="B868" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C868" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D868" s="4" t="inlineStr">
-        <is>
-          <t>Validasi semua data</t>
-        </is>
-      </c>
-      <c r="E868" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F868" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G868" s="4" t="inlineStr">
-        <is>
-          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi semua prospek</t>
-        </is>
-      </c>
-      <c r="H868" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan data tabel yang berisi semua prospek</t>
-        </is>
-      </c>
-    </row>
-    <row r="869" ht="28" customHeight="1">
-      <c r="A869" s="43" t="inlineStr">
-        <is>
-          <t>69.13</t>
-        </is>
-      </c>
-      <c r="B869" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign dan Approval</t>
-        </is>
-      </c>
-      <c r="C869" s="3" t="inlineStr">
-        <is>
-          <t>Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="D869" s="4" t="inlineStr">
-        <is>
-          <t>Membatalkan Re-Assign Prospek</t>
-        </is>
-      </c>
-      <c r="E869" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F869" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G869" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
-        </is>
-      </c>
-      <c r="H869" s="4" t="inlineStr">
-        <is>
-          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
-        </is>
-      </c>
-    </row>
     <row r="870" ht="28" customHeight="1">
       <c r="A870" s="43" t="inlineStr">
         <is>
+          <t>69.12</t>
+        </is>
+      </c>
+      <c r="B870" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C870" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D870" s="4" t="inlineStr">
+        <is>
+          <t>Validasi semua data</t>
+        </is>
+      </c>
+      <c r="E870" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F870" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G870" s="4" t="inlineStr">
+        <is>
+          <t>1. Cek pada halaman pindah kelolaan, data tabel nya berisi semua prospek</t>
+        </is>
+      </c>
+      <c r="H870" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan data tabel yang berisi semua prospek</t>
+        </is>
+      </c>
+    </row>
+    <row r="871" ht="28" customHeight="1">
+      <c r="A871" s="43" t="inlineStr">
+        <is>
+          <t>69.13</t>
+        </is>
+      </c>
+      <c r="B871" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign dan Approval</t>
+        </is>
+      </c>
+      <c r="C871" s="3" t="inlineStr">
+        <is>
+          <t>Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="D871" s="4" t="inlineStr">
+        <is>
+          <t>Membatalkan Re-Assign Prospek</t>
+        </is>
+      </c>
+      <c r="E871" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F871" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G871" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik button Batalkan pada halaman pindah kelolaan</t>
+        </is>
+      </c>
+      <c r="H871" s="4" t="inlineStr">
+        <is>
+          <t>1. Kembali ke halaman utama Re-assign Prospek</t>
+        </is>
+      </c>
+    </row>
+    <row r="872" ht="70" customHeight="1">
+      <c r="A872" s="43" t="inlineStr">
+        <is>
           <t>69.14</t>
         </is>
       </c>
-      <c r="B870" s="3" t="inlineStr">
+      <c r="B872" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C870" s="3" t="inlineStr">
+      <c r="C872" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="D870" s="4" t="inlineStr">
+      <c r="D872" s="4" t="inlineStr">
         <is>
           <t>Validasi semua data prospek yang di re-assign</t>
         </is>
       </c>
-      <c r="E870" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F870" s="3" t="inlineStr">
+      <c r="E872" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F872" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G870" s="4" t="inlineStr">
+      <c r="G872" s="4" t="inlineStr">
         <is>
           <t>1. Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek 
 2. Klik menu Lead Qualification 
@@ -38828,7 +38906,7 @@
 4. Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
-      <c r="H870" s="4" t="inlineStr">
+      <c r="H872" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login 
 2. Menampilkan dropdown submenu Lead Qualification 
@@ -38837,126 +38915,126 @@
         </is>
       </c>
     </row>
-    <row r="871" ht="28" customHeight="1">
-      <c r="A871" s="43" t="inlineStr">
+    <row r="873" ht="42" customHeight="1">
+      <c r="A873" s="43" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="B871" s="3" t="inlineStr">
+      <c r="B873" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C871" s="3" t="inlineStr">
+      <c r="C873" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D871" s="4" t="inlineStr">
+      <c r="D873" s="4" t="inlineStr">
         <is>
           <t>Pagination</t>
         </is>
       </c>
-      <c r="E871" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F871" s="3" t="inlineStr">
+      <c r="E873" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F873" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G871" s="4" t="inlineStr">
+      <c r="G873" s="4" t="inlineStr">
         <is>
           <t>1. Klik pagination (10/halaman).
 2. Pilih berapa data yang ingin ditampilkan.</t>
         </is>
       </c>
-      <c r="H871" s="4" t="inlineStr">
+      <c r="H873" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengklik pagination.
 2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="872" ht="70" customHeight="1">
-      <c r="A872" s="43" t="inlineStr">
+    <row r="874" ht="42" customHeight="1">
+      <c r="A874" s="43" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="B872" s="3" t="inlineStr">
+      <c r="B874" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C872" s="3" t="inlineStr">
+      <c r="C874" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D872" s="4" t="inlineStr">
+      <c r="D874" s="4" t="inlineStr">
         <is>
           <t>Pindah Halaman</t>
         </is>
       </c>
-      <c r="E872" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F872" s="3" t="inlineStr">
+      <c r="E874" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F874" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G872" s="4" t="inlineStr">
+      <c r="G874" s="4" t="inlineStr">
         <is>
           <t>1. Input angka halaman di field pindah halaman.
 2. Klik Enter pada keyboard.</t>
         </is>
       </c>
-      <c r="H872" s="4" t="inlineStr">
+      <c r="H874" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput angka halaman.
 2. Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
-    <row r="873" ht="42" customHeight="1">
-      <c r="A873" s="43" t="inlineStr">
+    <row r="875" ht="70" customHeight="1">
+      <c r="A875" s="43" t="inlineStr">
         <is>
           <t>70.3</t>
         </is>
       </c>
-      <c r="B873" s="3" t="inlineStr">
+      <c r="B875" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C873" s="3" t="inlineStr">
+      <c r="C875" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D873" s="4" t="inlineStr">
+      <c r="D875" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E873" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F873" s="3" t="inlineStr">
+      <c r="E875" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F875" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G873" s="4" t="inlineStr">
+      <c r="G875" s="4" t="inlineStr">
         <is>
           <t>1. Pilih prospek dengan klik checkbox yang ada di samping setiap data prospek 
 2. Klik button Reassign () data 
@@ -38965,7 +39043,7 @@
 5. Klik button Submit</t>
         </is>
       </c>
-      <c r="H873" s="4" t="inlineStr">
+      <c r="H875" s="4" t="inlineStr">
         <is>
           <t>1. Checkbox menjadi ceklis dan data berhasil di pilih 
 2. Menampilkan popup konfirmasi 
@@ -38975,258 +39053,258 @@
         </is>
       </c>
     </row>
-    <row r="874" ht="42" customHeight="1">
-      <c r="A874" s="43" t="inlineStr">
+    <row r="876" ht="28" customHeight="1">
+      <c r="A876" s="43" t="inlineStr">
         <is>
           <t>70.4</t>
         </is>
       </c>
-      <c r="B874" s="3" t="inlineStr">
+      <c r="B876" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C874" s="3" t="inlineStr">
+      <c r="C876" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D874" s="4" t="inlineStr">
+      <c r="D876" s="4" t="inlineStr">
         <is>
           <t>Pagination</t>
         </is>
       </c>
-      <c r="E874" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F874" s="3" t="inlineStr">
+      <c r="E876" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F876" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G874" s="4" t="inlineStr">
+      <c r="G876" s="4" t="inlineStr">
         <is>
           <t>1. Klik pagination (10/halaman).
 2. Pilih berapa data yang ingin ditampilkan.</t>
         </is>
       </c>
-      <c r="H874" s="4" t="inlineStr">
+      <c r="H876" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengklik pagination.
 2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="875" ht="70" customHeight="1">
-      <c r="A875" s="43" t="inlineStr">
+    <row r="877" ht="42" customHeight="1">
+      <c r="A877" s="43" t="inlineStr">
         <is>
           <t>70.5</t>
         </is>
       </c>
-      <c r="B875" s="3" t="inlineStr">
+      <c r="B877" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C875" s="3" t="inlineStr">
+      <c r="C877" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D875" s="4" t="inlineStr">
+      <c r="D877" s="4" t="inlineStr">
         <is>
           <t>Pindah Halaman</t>
         </is>
       </c>
-      <c r="E875" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F875" s="3" t="inlineStr">
+      <c r="E877" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F877" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G875" s="4" t="inlineStr">
+      <c r="G877" s="4" t="inlineStr">
         <is>
           <t>1. Input angka halaman di field pindah halaman.
 2. Klik Enter pada keyboard.</t>
         </is>
       </c>
-      <c r="H875" s="4" t="inlineStr">
+      <c r="H877" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput angka halaman.
 2. Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
-    <row r="876" ht="28" customHeight="1">
-      <c r="A876" s="43" t="inlineStr">
+    <row r="878" ht="28" customHeight="1">
+      <c r="A878" s="43" t="inlineStr">
         <is>
           <t>70.6</t>
         </is>
       </c>
-      <c r="B876" s="3" t="inlineStr">
+      <c r="B878" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C876" s="3" t="inlineStr">
+      <c r="C878" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D876" s="4" t="inlineStr">
+      <c r="D878" s="4" t="inlineStr">
         <is>
           <t>Membuka halaman Re-Assign Management</t>
         </is>
       </c>
-      <c r="E876" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F876" s="3" t="inlineStr">
+      <c r="E878" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F878" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G876" s="4" t="inlineStr">
+      <c r="G878" s="4" t="inlineStr">
         <is>
           <t>1. Klik menu Re-Assign &amp; Approval 
 2. Klik submenu Re-Assign Management</t>
         </is>
       </c>
-      <c r="H876" s="4" t="inlineStr">
+      <c r="H878" s="4" t="inlineStr">
         <is>
           <t>1. Menampilkan dropdown list submenu Re-Assign &amp; Approval 
 2. Menampilkan halaman Re-Assign Management</t>
         </is>
       </c>
     </row>
-    <row r="877" ht="42" customHeight="1">
-      <c r="A877" s="43" t="inlineStr">
+    <row r="879" ht="28" customHeight="1">
+      <c r="A879" s="43" t="inlineStr">
         <is>
           <t>70.7</t>
         </is>
       </c>
-      <c r="B877" s="3" t="inlineStr">
+      <c r="B879" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C877" s="3" t="inlineStr">
+      <c r="C879" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D877" s="4" t="inlineStr">
+      <c r="D879" s="4" t="inlineStr">
         <is>
           <t>Mencari data prospek pada halaman Re-Assign Management</t>
         </is>
       </c>
-      <c r="E877" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F877" s="3" t="inlineStr">
+      <c r="E879" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F879" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G877" s="4" t="inlineStr">
+      <c r="G879" s="4" t="inlineStr">
         <is>
           <t>1. Input nama nasabah pada field search 
 2. Klik icon search atau klik Enter</t>
         </is>
       </c>
-      <c r="H877" s="4" t="inlineStr">
+      <c r="H879" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput nama nasabah
 2. Menampilkan data prospek Re-Assign Management sesuai dengan nama yang di cari</t>
         </is>
       </c>
     </row>
-    <row r="878" ht="28" customHeight="1">
-      <c r="A878" s="43" t="inlineStr">
+    <row r="880" ht="28" customHeight="1">
+      <c r="A880" s="43" t="inlineStr">
         <is>
           <t>70.8</t>
         </is>
       </c>
-      <c r="B878" s="3" t="inlineStr">
+      <c r="B880" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C878" s="3" t="inlineStr">
+      <c r="C880" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D878" s="4" t="inlineStr">
+      <c r="D880" s="4" t="inlineStr">
         <is>
           <t>Mencari data prospek yang tidak ada pada halaman Re-Assign Management</t>
         </is>
       </c>
-      <c r="E878" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F878" s="3" t="inlineStr">
+      <c r="E880" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F880" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G878" s="4" t="inlineStr">
+      <c r="G880" s="4" t="inlineStr">
         <is>
           <t>1. Input nama nasabah yang datanya tidak ada 
 2. Klik icon search atau klik Enter</t>
         </is>
       </c>
-      <c r="H878" s="4" t="inlineStr">
+      <c r="H880" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput nama nasabah
 2. Menampilkan tabel kosong dengan keterangan no data</t>
         </is>
       </c>
     </row>
-    <row r="879" ht="28" customHeight="1">
-      <c r="A879" s="43" t="inlineStr">
+    <row r="881" ht="14" customHeight="1">
+      <c r="A881" s="43" t="inlineStr">
         <is>
           <t>70.9</t>
         </is>
       </c>
-      <c r="B879" s="3" t="inlineStr">
+      <c r="B881" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C879" s="3" t="inlineStr">
+      <c r="C881" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D879" s="4" t="inlineStr">
+      <c r="D881" s="4" t="inlineStr">
         <is>
           <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
-      <c r="E879" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F879" s="3" t="inlineStr">
+      <c r="E881" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F881" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G879" s="4" t="inlineStr">
+      <c r="G881" s="4" t="inlineStr">
         <is>
           <t>1. Pilih prospek dengan klik checkbox yang ada di samping setiap data prospek 
 2. Klik button Reassign () data 
@@ -39235,7 +39313,7 @@
 5. Klik button Submit</t>
         </is>
       </c>
-      <c r="H879" s="4" t="inlineStr">
+      <c r="H881" s="4" t="inlineStr">
         <is>
           <t>1. Checkbox menjadi ceklis dan data berhasil di pilih 
 2. Menampilkan popup konfirmasi 
@@ -39245,80 +39323,80 @@
         </is>
       </c>
     </row>
-    <row r="880" ht="28" customHeight="1">
-      <c r="A880" s="43" t="inlineStr">
+    <row r="882" ht="42" customHeight="1">
+      <c r="A882" s="43" t="inlineStr">
         <is>
           <t>70.10</t>
         </is>
       </c>
-      <c r="B880" s="3" t="inlineStr">
+      <c r="B882" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C880" s="3" t="inlineStr">
+      <c r="C882" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D880" s="4" t="inlineStr">
+      <c r="D882" s="4" t="inlineStr">
         <is>
           <t>Validasi jumlah data yang di pilih untuk reassign</t>
         </is>
       </c>
-      <c r="E880" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F880" s="3" t="inlineStr">
+      <c r="E882" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F882" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G880" s="4" t="inlineStr">
+      <c r="G882" s="4" t="inlineStr">
         <is>
           <t>1. cek jumlah data yang muncul pada button Reassign () data</t>
         </is>
       </c>
-      <c r="H880" s="4" t="inlineStr">
+      <c r="H882" s="4" t="inlineStr">
         <is>
           <t>1. Angka yang muncul pada button sesuai dengan jumlah data yang di pilih</t>
         </is>
       </c>
     </row>
-    <row r="881" ht="14" customHeight="1">
-      <c r="A881" s="43" t="inlineStr">
+    <row r="883" ht="42" customHeight="1">
+      <c r="A883" s="43" t="inlineStr">
         <is>
           <t>70.11</t>
         </is>
       </c>
-      <c r="B881" s="3" t="inlineStr">
+      <c r="B883" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C881" s="3" t="inlineStr">
+      <c r="C883" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D881" s="4" t="inlineStr">
+      <c r="D883" s="4" t="inlineStr">
         <is>
           <t>Validasi data prospek yang di re-assign ke sales</t>
         </is>
       </c>
-      <c r="E881" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F881" s="3" t="inlineStr">
+      <c r="E883" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F883" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G881" s="4" t="inlineStr">
+      <c r="G883" s="4" t="inlineStr">
         <is>
           <t>1. Login dengan akun sales yang sebelumnya sudah di pilih reassign management
 2. Klik menu Lead Qualification
@@ -39326,7 +39404,7 @@
 4. Cek data prospek yang sudah di reassign</t>
         </is>
       </c>
-      <c r="H881" s="4" t="inlineStr">
+      <c r="H883" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil login akun sales
 2. Menampilkan dropdown submenu Lead Qualification
@@ -39335,182 +39413,98 @@
         </is>
       </c>
     </row>
-    <row r="882" ht="42" customHeight="1">
-      <c r="A882" s="43" t="inlineStr">
+    <row r="884" ht="28" customHeight="1">
+      <c r="A884" s="43" t="inlineStr">
         <is>
           <t>70.12</t>
         </is>
       </c>
-      <c r="B882" s="3" t="inlineStr">
+      <c r="B884" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C882" s="3" t="inlineStr">
+      <c r="C884" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D882" s="4" t="inlineStr">
+      <c r="D884" s="4" t="inlineStr">
         <is>
           <t>Pagination</t>
         </is>
       </c>
-      <c r="E882" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F882" s="3" t="inlineStr">
+      <c r="E884" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F884" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G882" s="4" t="inlineStr">
+      <c r="G884" s="4" t="inlineStr">
         <is>
           <t>1. Klik pagination (10/halaman).
 2. Pilih berapa data yang ingin ditampilkan.</t>
         </is>
       </c>
-      <c r="H882" s="4" t="inlineStr">
+      <c r="H884" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil mengklik pagination.
 2. Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="883" ht="42" customHeight="1">
-      <c r="A883" s="43" t="inlineStr">
+    <row r="885" ht="42" customHeight="1">
+      <c r="A885" s="43" t="inlineStr">
         <is>
           <t>70.13</t>
         </is>
       </c>
-      <c r="B883" s="3" t="inlineStr">
+      <c r="B885" s="3" t="inlineStr">
         <is>
           <t>Re-Assign dan Approval</t>
         </is>
       </c>
-      <c r="C883" s="3" t="inlineStr">
+      <c r="C885" s="3" t="inlineStr">
         <is>
           <t>Re-Assign Management</t>
         </is>
       </c>
-      <c r="D883" s="4" t="inlineStr">
+      <c r="D885" s="4" t="inlineStr">
         <is>
           <t>Pindah Halaman</t>
         </is>
       </c>
-      <c r="E883" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F883" s="3" t="inlineStr">
+      <c r="E885" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F885" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G883" s="4" t="inlineStr">
+      <c r="G885" s="4" t="inlineStr">
         <is>
           <t>1. Input angka halaman di field pindah halaman.
 2. Klik Enter pada keyboard.</t>
         </is>
       </c>
-      <c r="H883" s="4" t="inlineStr">
+      <c r="H885" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menginput angka halaman.
 2. Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
-    <row r="884" ht="28" customHeight="1">
-      <c r="A884" s="43" t="inlineStr">
-        <is>
-          <t>71.1</t>
-        </is>
-      </c>
-      <c r="B884" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C884" s="3" t="inlineStr">
-        <is>
-          <t>Riwayat export saya</t>
-        </is>
-      </c>
-      <c r="D884" s="4" t="inlineStr">
-        <is>
-          <t>Membuka menu riwayat export saya</t>
-        </is>
-      </c>
-      <c r="E884" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F884" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G884" s="4" t="inlineStr">
-        <is>
-          <t>1. Klik menu exported data management, klik submenu riwayat export saya</t>
-        </is>
-      </c>
-      <c r="H884" s="4" t="inlineStr">
-        <is>
-          <t>1. Menampilkan halaman riwayat export saya</t>
-        </is>
-      </c>
-    </row>
-    <row r="885" ht="42" customHeight="1">
-      <c r="A885" s="43" t="inlineStr">
-        <is>
-          <t>71.2</t>
-        </is>
-      </c>
-      <c r="B885" s="3" t="inlineStr">
-        <is>
-          <t>Export data management</t>
-        </is>
-      </c>
-      <c r="C885" s="3" t="inlineStr">
-        <is>
-          <t>Riwayat export saya</t>
-        </is>
-      </c>
-      <c r="D885" s="4" t="inlineStr">
-        <is>
-          <t>Validasi card disetujui dengan data table</t>
-        </is>
-      </c>
-      <c r="E885" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F885" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G885" s="4" t="inlineStr">
-        <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Approved”</t>
-        </is>
-      </c>
-      <c r="H885" s="4" t="inlineStr">
-        <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
-        </is>
-      </c>
-    </row>
     <row r="886" ht="14" customHeight="1">
       <c r="A886" s="43" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="B886" s="3" t="inlineStr">
@@ -39525,7 +39519,7 @@
       </c>
       <c r="D886" s="4" t="inlineStr">
         <is>
-          <t>Validasi card ditolak dengan data table</t>
+          <t>Membuka menu riwayat export saya</t>
         </is>
       </c>
       <c r="E886" s="3" t="inlineStr">
@@ -39540,19 +39534,19 @@
       </c>
       <c r="G886" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Rejected”</t>
+          <t>1. Klik menu exported data management, klik submenu riwayat export saya</t>
         </is>
       </c>
       <c r="H886" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Menampilkan halaman riwayat export saya</t>
         </is>
       </c>
     </row>
     <row r="887" ht="42" customHeight="1">
       <c r="A887" s="43" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="B887" s="3" t="inlineStr">
@@ -39567,7 +39561,7 @@
       </c>
       <c r="D887" s="4" t="inlineStr">
         <is>
-          <t>Validasi card kadaluwarsa dengan data table</t>
+          <t>Validasi card disetujui dengan data table</t>
         </is>
       </c>
       <c r="E887" s="3" t="inlineStr">
@@ -39577,12 +39571,12 @@
       </c>
       <c r="F887" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G887" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data status approval dengan memilih status “Expired”</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Approved”</t>
         </is>
       </c>
       <c r="H887" s="4" t="inlineStr">
@@ -39594,7 +39588,7 @@
     <row r="888" ht="42" customHeight="1">
       <c r="A888" s="43" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="B888" s="3" t="inlineStr">
@@ -39609,7 +39603,7 @@
       </c>
       <c r="D888" s="4" t="inlineStr">
         <is>
-          <t>Mengunduh data yang sudah di approve</t>
+          <t>Validasi card ditolak dengan data table</t>
         </is>
       </c>
       <c r="E888" s="3" t="inlineStr">
@@ -39624,19 +39618,19 @@
       </c>
       <c r="G888" s="4" t="inlineStr">
         <is>
-          <t>1. Klik button download</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Rejected”</t>
         </is>
       </c>
       <c r="H888" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil mengunduh data</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="889" ht="28" customHeight="1">
       <c r="A889" s="43" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="B889" s="3" t="inlineStr">
@@ -39651,7 +39645,7 @@
       </c>
       <c r="D889" s="4" t="inlineStr">
         <is>
-          <t>Membuka dokumen hasil download</t>
+          <t>Validasi card kadaluwarsa dengan data table</t>
         </is>
       </c>
       <c r="E889" s="3" t="inlineStr">
@@ -39661,24 +39655,24 @@
       </c>
       <c r="F889" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G889" s="4" t="inlineStr">
         <is>
-          <t>1. Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
+          <t>1. Melakukan filter data status approval dengan memilih status “Expired”</t>
         </is>
       </c>
       <c r="H889" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka file hasil download</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="890" ht="42" customHeight="1">
       <c r="A890" s="43" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="B890" s="3" t="inlineStr">
@@ -39688,12 +39682,12 @@
       </c>
       <c r="C890" s="3" t="inlineStr">
         <is>
-          <t>Management export</t>
+          <t>Riwayat export saya</t>
         </is>
       </c>
       <c r="D890" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mengunduh data yang sudah di approve</t>
         </is>
       </c>
       <c r="E890" s="3" t="inlineStr">
@@ -39703,24 +39697,24 @@
       </c>
       <c r="F890" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G890" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Klik button download</t>
         </is>
       </c>
       <c r="H890" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Berhasil mengunduh data</t>
         </is>
       </c>
     </row>
     <row r="891" ht="14" customHeight="1">
       <c r="A891" s="43" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="B891" s="3" t="inlineStr">
@@ -39730,12 +39724,12 @@
       </c>
       <c r="C891" s="3" t="inlineStr">
         <is>
-          <t>Management export</t>
+          <t>Riwayat export saya</t>
         </is>
       </c>
       <c r="D891" s="4" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Membuka dokumen hasil download</t>
         </is>
       </c>
       <c r="E891" s="3" t="inlineStr">
@@ -39750,19 +39744,19 @@
       </c>
       <c r="G891" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
+          <t>1. Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
         </is>
       </c>
       <c r="H891" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Berhasil membuka file hasil download</t>
         </is>
       </c>
     </row>
     <row r="892" ht="42" customHeight="1">
       <c r="A892" s="43" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="B892" s="3" t="inlineStr">
@@ -39777,7 +39771,7 @@
       </c>
       <c r="D892" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E892" s="3" t="inlineStr">
@@ -39787,24 +39781,24 @@
       </c>
       <c r="F892" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G892" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H892" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="893" ht="42" customHeight="1">
       <c r="A893" s="43" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="B893" s="3" t="inlineStr">
@@ -39819,12 +39813,12 @@
       </c>
       <c r="D893" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E893" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F893" s="3" t="inlineStr">
@@ -39834,19 +39828,19 @@
       </c>
       <c r="G893" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
         </is>
       </c>
       <c r="H893" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="894" ht="28" customHeight="1">
       <c r="A894" s="43" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="B894" s="3" t="inlineStr">
@@ -39861,7 +39855,7 @@
       </c>
       <c r="D894" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E894" s="3" t="inlineStr">
@@ -39871,24 +39865,24 @@
       </c>
       <c r="F894" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G894" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H894" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="895" ht="42" customHeight="1">
       <c r="A895" s="43" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="B895" s="3" t="inlineStr">
@@ -39903,12 +39897,12 @@
       </c>
       <c r="D895" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E895" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F895" s="3" t="inlineStr">
@@ -39918,19 +39912,19 @@
       </c>
       <c r="G895" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H895" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="896" ht="14" customHeight="1">
       <c r="A896" s="43" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="B896" s="3" t="inlineStr">
@@ -39945,34 +39939,34 @@
       </c>
       <c r="D896" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E896" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F896" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G896" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H896" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="897" ht="42" customHeight="1">
       <c r="A897" s="43" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="B897" s="3" t="inlineStr">
@@ -39987,7 +39981,7 @@
       </c>
       <c r="D897" s="4" t="inlineStr">
         <is>
-          <t>Membuka menu Management Export</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E897" s="3" t="inlineStr">
@@ -40002,19 +39996,19 @@
       </c>
       <c r="G897" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu exported data management, klik submenu management export</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H897" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan halaman management export</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="898" ht="42" customHeight="1">
       <c r="A898" s="43" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="B898" s="3" t="inlineStr">
@@ -40029,34 +40023,34 @@
       </c>
       <c r="D898" s="4" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E898" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F898" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G898" s="4" t="inlineStr">
         <is>
-          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H898" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai filter yang dipilih</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="899" ht="28" customHeight="1">
       <c r="A899" s="43" t="inlineStr">
         <is>
-          <t>72.10</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="B899" s="3" t="inlineStr">
@@ -40071,7 +40065,7 @@
       </c>
       <c r="D899" s="4" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Membuka menu Management Export</t>
         </is>
       </c>
       <c r="E899" s="3" t="inlineStr">
@@ -40086,19 +40080,19 @@
       </c>
       <c r="G899" s="4" t="inlineStr">
         <is>
-          <t>1. Input data pada kolom pencarian</t>
+          <t>1. Klik menu exported data management, klik submenu management export</t>
         </is>
       </c>
       <c r="H899" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan data sesuai kata kunci</t>
+          <t>1. Menampilkan halaman management export</t>
         </is>
       </c>
     </row>
     <row r="900" ht="42" customHeight="1">
       <c r="A900" s="43" t="inlineStr">
         <is>
-          <t>72.11</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="B900" s="3" t="inlineStr">
@@ -40113,34 +40107,34 @@
       </c>
       <c r="D900" s="4" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E900" s="3" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F900" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G900" s="4" t="inlineStr">
         <is>
-          <t>1. Input data yang belum terdaftar</t>
+          <t>1. Pilih kantor wilayah, kantor cabang, cabang pembantu, job role, info user, status approval, status export, modul dan tanggal, klik button filter data</t>
         </is>
       </c>
       <c r="H900" s="4" t="inlineStr">
         <is>
-          <t>1. Data tidak ditemukan</t>
+          <t>1. Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="901" ht="28" customHeight="1">
       <c r="A901" s="43" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>72.10</t>
         </is>
       </c>
       <c r="B901" s="3" t="inlineStr">
@@ -40155,7 +40149,7 @@
       </c>
       <c r="D901" s="4" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E901" s="3" t="inlineStr">
@@ -40170,19 +40164,19 @@
       </c>
       <c r="G901" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
+          <t>1. Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H901" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="902" ht="28" customHeight="1">
       <c r="A902" s="43" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>72.11</t>
         </is>
       </c>
       <c r="B902" s="3" t="inlineStr">
@@ -40197,34 +40191,34 @@
       </c>
       <c r="D902" s="4" t="inlineStr">
         <is>
-          <t>Validasi card data file aktif dengan data table</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E902" s="3" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F902" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G902" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
+          <t>1. Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H902" s="4" t="inlineStr">
         <is>
-          <t>1. Jumlah data pada card dan table sesuai</t>
+          <t>1. Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="903" ht="28" customHeight="1">
       <c r="A903" s="43" t="inlineStr">
         <is>
-          <t>72.14</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="B903" s="3" t="inlineStr">
@@ -40239,7 +40233,7 @@
       </c>
       <c r="D903" s="4" t="inlineStr">
         <is>
-          <t>Validasi card file kadaluwarsa dengan data table</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E903" s="3" t="inlineStr">
@@ -40249,12 +40243,12 @@
       </c>
       <c r="F903" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G903" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “pending” dan status exportnya “Generate”</t>
         </is>
       </c>
       <c r="H903" s="4" t="inlineStr">
@@ -40266,7 +40260,7 @@
     <row r="904" ht="28" customHeight="1">
       <c r="A904" s="43" t="inlineStr">
         <is>
-          <t>72.15</t>
+          <t>72.13</t>
         </is>
       </c>
       <c r="B904" s="3" t="inlineStr">
@@ -40281,7 +40275,7 @@
       </c>
       <c r="D904" s="4" t="inlineStr">
         <is>
-          <t>Validasi card reject dengan data table</t>
+          <t>Validasi card data file aktif dengan data table</t>
         </is>
       </c>
       <c r="E904" s="3" t="inlineStr">
@@ -40291,12 +40285,12 @@
       </c>
       <c r="F904" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G904" s="4" t="inlineStr">
         <is>
-          <t>1. Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
         </is>
       </c>
       <c r="H904" s="4" t="inlineStr">
@@ -40308,7 +40302,7 @@
     <row r="905" ht="28" customHeight="1">
       <c r="A905" s="43" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.14</t>
         </is>
       </c>
       <c r="B905" s="3" t="inlineStr">
@@ -40318,12 +40312,12 @@
       </c>
       <c r="C905" s="3" t="inlineStr">
         <is>
-          <t>Persetujuan export</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D905" s="4" t="inlineStr">
         <is>
-          <t>Lakukan login menggunakan user monitoring</t>
+          <t>Validasi card file kadaluwarsa dengan data table</t>
         </is>
       </c>
       <c r="E905" s="3" t="inlineStr">
@@ -40338,19 +40332,19 @@
       </c>
       <c r="G905" s="4" t="inlineStr">
         <is>
-          <t>1. Login menggunakan user monitoring</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
         </is>
       </c>
       <c r="H905" s="4" t="inlineStr">
         <is>
-          <t>1. Berhasil melakukan login</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="906" ht="42" customHeight="1">
       <c r="A906" s="43" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.15</t>
         </is>
       </c>
       <c r="B906" s="3" t="inlineStr">
@@ -40360,12 +40354,12 @@
       </c>
       <c r="C906" s="3" t="inlineStr">
         <is>
-          <t>Persetujuan export</t>
+          <t>Management export</t>
         </is>
       </c>
       <c r="D906" s="4" t="inlineStr">
         <is>
-          <t>Membuka menu Persetujuan Export</t>
+          <t>Validasi card reject dengan data table</t>
         </is>
       </c>
       <c r="E906" s="3" t="inlineStr">
@@ -40380,54 +40374,138 @@
       </c>
       <c r="G906" s="4" t="inlineStr">
         <is>
-          <t>1. Klik menu exported data management, klik submenu persetujuan export</t>
+          <t>1. Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
         </is>
       </c>
       <c r="H906" s="4" t="inlineStr">
         <is>
-          <t>1. Menampilkan halaman persetujuan export</t>
+          <t>1. Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="907" ht="42" customHeight="1">
       <c r="A907" s="43" t="inlineStr">
         <is>
+          <t>73.1</t>
+        </is>
+      </c>
+      <c r="B907" s="3" t="inlineStr">
+        <is>
+          <t>Export data management</t>
+        </is>
+      </c>
+      <c r="C907" s="3" t="inlineStr">
+        <is>
+          <t>Persetujuan export</t>
+        </is>
+      </c>
+      <c r="D907" s="4" t="inlineStr">
+        <is>
+          <t>Lakukan login menggunakan user monitoring</t>
+        </is>
+      </c>
+      <c r="E907" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F907" s="3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G907" s="4" t="inlineStr">
+        <is>
+          <t>1. Login menggunakan user monitoring</t>
+        </is>
+      </c>
+      <c r="H907" s="4" t="inlineStr">
+        <is>
+          <t>1. Berhasil melakukan login</t>
+        </is>
+      </c>
+    </row>
+    <row r="908" ht="28" customHeight="1">
+      <c r="A908" s="43" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="B908" s="3" t="inlineStr">
+        <is>
+          <t>Export data management</t>
+        </is>
+      </c>
+      <c r="C908" s="3" t="inlineStr">
+        <is>
+          <t>Persetujuan export</t>
+        </is>
+      </c>
+      <c r="D908" s="4" t="inlineStr">
+        <is>
+          <t>Membuka menu Persetujuan Export</t>
+        </is>
+      </c>
+      <c r="E908" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F908" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G908" s="4" t="inlineStr">
+        <is>
+          <t>1. Klik menu exported data management, klik submenu persetujuan export</t>
+        </is>
+      </c>
+      <c r="H908" s="4" t="inlineStr">
+        <is>
+          <t>1. Menampilkan halaman persetujuan export</t>
+        </is>
+      </c>
+    </row>
+    <row r="909" ht="14" customHeight="1">
+      <c r="A909" s="43" t="inlineStr">
+        <is>
           <t>73.3</t>
         </is>
       </c>
-      <c r="B907" s="3" t="inlineStr">
+      <c r="B909" s="3" t="inlineStr">
         <is>
           <t>Export data management</t>
         </is>
       </c>
-      <c r="C907" s="3" t="inlineStr">
+      <c r="C909" s="3" t="inlineStr">
         <is>
           <t>Persetujuan export</t>
         </is>
       </c>
-      <c r="D907" s="4" t="inlineStr">
+      <c r="D909" s="4" t="inlineStr">
         <is>
           <t>Melakukan approval data pengajuan export</t>
         </is>
       </c>
-      <c r="E907" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F907" s="3" t="inlineStr">
+      <c r="E909" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F909" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G907" s="4" t="inlineStr">
+      <c r="G909" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon titik tiga pada data pengajuan.
 2. Klik menu Setuju.
 3. Klik button YA pada popup konfirmasi.</t>
         </is>
       </c>
-      <c r="H907" s="4" t="inlineStr">
+      <c r="H909" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan menu opsi.
 2. Berhasil menampilkan popup konfirmasi.
@@ -40435,50 +40513,48 @@
         </is>
       </c>
     </row>
-    <row r="908" ht="28" customHeight="1">
-      <c r="A908" s="43" t="inlineStr">
+    <row r="910" ht="28" customHeight="1">
+      <c r="A910" s="43" t="inlineStr">
         <is>
           <t>73.4</t>
         </is>
       </c>
-      <c r="B908" s="3" t="inlineStr">
+      <c r="B910" s="3" t="inlineStr">
         <is>
           <t>Export data management</t>
         </is>
       </c>
-      <c r="C908" s="3" t="inlineStr">
+      <c r="C910" s="3" t="inlineStr">
         <is>
           <t>Persetujuan export</t>
         </is>
       </c>
-      <c r="D908" s="4" t="inlineStr">
+      <c r="D910" s="4" t="inlineStr">
         <is>
           <t>Melakukan reject data pengajuan export</t>
         </is>
       </c>
-      <c r="E908" s="3" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F908" s="3" t="inlineStr">
+      <c r="E910" s="3" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F910" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G908" s="4" t="inlineStr">
+      <c r="G910" s="4" t="inlineStr">
         <is>
           <t>1. Klik icon (titik tiga) klik tolak, input alasan, klik submit</t>
         </is>
       </c>
-      <c r="H908" s="4" t="inlineStr">
+      <c r="H910" s="4" t="inlineStr">
         <is>
           <t>1. Berhasil melakukan reject data</t>
         </is>
       </c>
     </row>
-    <row r="909" ht="14" customHeight="1"/>
-    <row r="910" ht="28" customHeight="1"/>
     <row r="911" ht="28" customHeight="1"/>
     <row r="912" ht="28" customHeight="1"/>
     <row r="913" ht="28" customHeight="1"/>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -105,6 +105,10 @@
       <name val="Arial"/>
       <color theme="1"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="15">
@@ -273,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -388,6 +392,18 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -48641,7 +48657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA171"/>
+  <dimension ref="A1:AA214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53898,2745 +53914,1825 @@
       <c r="AA86" s="49" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="51" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="B87" s="46" t="inlineStr">
+      <c r="B87" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C87" s="53" t="n"/>
+      <c r="D87" s="54" t="inlineStr">
+        <is>
+          <t>Membuka halaman Kalender</t>
+        </is>
+      </c>
+      <c r="E87" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F87" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G87" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada menu Beranda, klik icon Lainnya pada Aksi Cepat.
+2. Klik menu Kalender pada kategori Absensi.</t>
+        </is>
+      </c>
+      <c r="H87" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan halaman Semua Menu.
+2. Berhasil menampilkan halaman Kalender beserta kalender bulanan, legend kategori, dan agenda harian.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="51" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="B88" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C88" s="53" t="n"/>
+      <c r="D88" s="54" t="inlineStr">
+        <is>
+          <t>Melakukan navigasi bulan pada Kalender</t>
+        </is>
+      </c>
+      <c r="E88" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F88" s="52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G88" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Kalender, klik icon panah kanan (&gt;) untuk ke bulan berikutnya.
+2. Klik icon panah kiri (&lt;) untuk kembali ke bulan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="H88" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil berpindah ke tampilan bulan berikutnya.
+2. Berhasil berpindah ke tampilan bulan sebelumnya dan menampilkan penanggalan yang sesuai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="51" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="B89" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C89" s="53" t="n"/>
+      <c r="D89" s="54" t="inlineStr">
+        <is>
+          <t>Memilih tanggal tertentu pada Kalender</t>
+        </is>
+      </c>
+      <c r="E89" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F89" s="52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G89" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik salah satu tanggal pada tampilan kalender bulanan.</t>
+        </is>
+      </c>
+      <c r="H89" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil memilih tanggal tersebut dan menampilkan daftar agenda harian pada tanggal yang dipilih di bagian bawah kalender.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="51" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="B90" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C90" s="53" t="n"/>
+      <c r="D90" s="54" t="inlineStr">
+        <is>
+          <t>Melihat detail agenda kerja pada Kalender</t>
+        </is>
+      </c>
+      <c r="E90" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F90" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G90" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik salah satu card agenda harian pada kalender (contoh: Jam Kerja).</t>
+        </is>
+      </c>
+      <c r="H90" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan bottom sheet Detail Agenda yang memuat nama agenda, kategori, tanggal, dan rentang jam kerja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="51" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="B91" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C91" s="53" t="n"/>
+      <c r="D91" s="54" t="inlineStr">
+        <is>
+          <t>Melakukan filter agenda Kalender</t>
+        </is>
+      </c>
+      <c r="E91" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F91" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G91" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon Filter pada pojok kanan atas halaman Kalender.
+2. Pilih salah satu kategori filter (contoh: Task / Event / Holiday / Time off / Work pattern).
+3. Klik button Terapkan.</t>
+        </is>
+      </c>
+      <c r="H91" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan bottom sheet Filter Kalender.
+2. Kategori filter berhasil dipilih.
+3. Berhasil memfilter dan menampilkan agenda pada kalender sesuai kategori yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="51" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="B92" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C92" s="53" t="n"/>
+      <c r="D92" s="54" t="inlineStr">
+        <is>
+          <t>Mereset filter agenda Kalender</t>
+        </is>
+      </c>
+      <c r="E92" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F92" s="52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G92" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon Filter pada pojok kanan atas halaman Kalender.
+2. Klik icon Reset (refresh) pada pojok kanan atas bottom sheet.
+3. Klik button Terapkan.</t>
+        </is>
+      </c>
+      <c r="H92" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan bottom sheet Filter Kalender.
+2. Pilihan filter kembali terpilih ke 'All'.
+3. Berhasil menampilkan seluruh agenda kalender ke kondisi default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="51" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="B93" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C93" s="53" t="n"/>
+      <c r="D93" s="54" t="inlineStr">
+        <is>
+          <t>Menambahkan task baru dengan data valid</t>
+        </is>
+      </c>
+      <c r="E93" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F93" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G93" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon titik tiga pada pojok kanan atas halaman Kalender.
+2. Pilih menu Tambah Task.
+3. Masukkan judul task pada field Judul dan lengkapi data task (Deskripsi, Prioritas, Visibilitas, Jatuh Tempo).
+4. Klik button Simpan.</t>
+        </is>
+      </c>
+      <c r="H93" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu.
+2. Berhasil menampilkan form Tambah Task.
+3. Berhasil mengisi data task.
+4. Berhasil menyimpan task baru dan kembali ke halaman Kalender dengan task baru tertampil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="51" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="B94" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C94" s="53" t="n"/>
+      <c r="D94" s="54" t="inlineStr">
+        <is>
+          <t>Menambahkan task baru tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E94" s="52" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F94" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G94" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon titik tiga pada pojok kanan atas halaman Kalender.
+2. Pilih menu Tambah Task.
+3. Kosongkan field Judul.
+4. Klik button Simpan.</t>
+        </is>
+      </c>
+      <c r="H94" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu.
+2. Berhasil menampilkan form Tambah Task.
+3. Field Judul dalam kondisi kosong.
+4. Sistem menampilkan pesan validasi bahwa field Judul wajib diisi dan task tidak tersimpan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="51" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="B95" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C95" s="53" t="n"/>
+      <c r="D95" s="54" t="inlineStr">
+        <is>
+          <t>Menambahkan acara baru dengan data valid</t>
+        </is>
+      </c>
+      <c r="E95" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F95" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G95" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon titik tiga pada pojok kanan atas halaman Kalender.
+2. Pilih menu Tambah Acara.
+3. Masukkan judul acara pada field Judul dan tentukan waktu Mulai &amp; Selesai.
+4. Klik button Simpan.</t>
+        </is>
+      </c>
+      <c r="H95" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu.
+2. Berhasil menampilkan form Tambah Acara.
+3. Berhasil mengisi data acara.
+4. Berhasil menyimpan acara baru dan kembali ke halaman Kalender dengan acara baru tertampil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="51" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B96" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C96" s="53" t="n"/>
+      <c r="D96" s="54" t="inlineStr">
+        <is>
+          <t>Menambahkan acara baru tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E96" s="52" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F96" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G96" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon titik tiga pada pojok kanan atas halaman Kalender.
+2. Pilih menu Tambah Acara.
+3. Kosongkan field Judul.
+4. Klik button Simpan.</t>
+        </is>
+      </c>
+      <c r="H96" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu.
+2. Berhasil menampilkan form Tambah Acara.
+3. Field Judul dalam kondisi kosong.
+4. Sistem menampilkan pesan validasi bahwa field Judul wajib diisi dan acara tidak tersimpan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="51" t="inlineStr">
+        <is>
+          <t>10.11</t>
+        </is>
+      </c>
+      <c r="B97" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C97" s="53" t="n"/>
+      <c r="D97" s="54" t="inlineStr">
+        <is>
+          <t>Membuka halaman Daftar Task</t>
+        </is>
+      </c>
+      <c r="E97" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F97" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G97" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Kalender, klik icon titik tiga pada pojok kanan atas.
+2. Pilih menu Daftar Task.</t>
+        </is>
+      </c>
+      <c r="H97" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu.
+2. Berhasil menampilkan halaman Daftar Task beserta tab status counter dan daftar task.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="51" t="inlineStr">
+        <is>
+          <t>10.12</t>
+        </is>
+      </c>
+      <c r="B98" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C98" s="53" t="n"/>
+      <c r="D98" s="54" t="inlineStr">
+        <is>
+          <t>Mencari task dengan kata kunci valid</t>
+        </is>
+      </c>
+      <c r="E98" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F98" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G98" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon Search pada header halaman Daftar Task.
+2. Masukkan kata kunci pencarian task yang valid.</t>
+        </is>
+      </c>
+      <c r="H98" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan kolom pencarian.
+2. Berhasil menampilkan data task yang sesuai dengan kata kunci pencarian.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="51" t="inlineStr">
+        <is>
+          <t>10.13</t>
+        </is>
+      </c>
+      <c r="B99" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C99" s="53" t="n"/>
+      <c r="D99" s="54" t="inlineStr">
+        <is>
+          <t>Mencari task dengan kata kunci tidak valid</t>
+        </is>
+      </c>
+      <c r="E99" s="52" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F99" s="52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G99" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon Search pada header halaman Daftar Task.
+2. Masukkan kata kunci pencarian yang tidak terdaftar.</t>
+        </is>
+      </c>
+      <c r="H99" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan kolom pencarian.
+2. Sistem menampilkan pesan bahwa data task tidak ditemukan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="51" t="inlineStr">
+        <is>
+          <t>10.14</t>
+        </is>
+      </c>
+      <c r="B100" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C100" s="53" t="n"/>
+      <c r="D100" s="54" t="inlineStr">
+        <is>
+          <t>Melakukan filter Daftar Task</t>
+        </is>
+      </c>
+      <c r="E100" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F100" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G100" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon Filter pada pojok kanan atas halaman Daftar Task.
+2. Pilih kriteria filter (Status, Prioritas, atau Rentang tanggal).
+3. Klik button Terapkan.</t>
+        </is>
+      </c>
+      <c r="H100" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan bottom sheet Filter Task.
+2. Berhasil menentukan kriteria filter.
+3. Berhasil memfilter dan menampilkan daftar task sesuai kriteria yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="51" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="B101" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C101" s="53" t="n"/>
+      <c r="D101" s="54" t="inlineStr">
+        <is>
+          <t>Mereset filter Daftar Task</t>
+        </is>
+      </c>
+      <c r="E101" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F101" s="52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G101" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon Filter pada pojok kanan atas halaman Daftar Task.
+2. Klik icon Reset pada pojok kanan atas bottom sheet Filter Task.
+3. Klik button Terapkan.</t>
+        </is>
+      </c>
+      <c r="H101" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan bottom sheet Filter Task.
+2. Seluruh kriteria filter kembali ke kondisi default (Semua).
+3. Berhasil menampilkan seluruh daftar task.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="51" t="inlineStr">
+        <is>
+          <t>10.16</t>
+        </is>
+      </c>
+      <c r="B102" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C102" s="53" t="n"/>
+      <c r="D102" s="54" t="inlineStr">
+        <is>
+          <t>Melihat detail task</t>
+        </is>
+      </c>
+      <c r="E102" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F102" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G102" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik salah satu card task pada Daftar Task.</t>
+        </is>
+      </c>
+      <c r="H102" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka halaman Detail Task yang memuat tab Detail (Status, Visibilitas, Prioritas, Tenggat, Pemilik, Deskripsi, Lampiran).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="51" t="inlineStr">
+        <is>
+          <t>10.17</t>
+        </is>
+      </c>
+      <c r="B103" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C103" s="53" t="n"/>
+      <c r="D103" s="54" t="inlineStr">
+        <is>
+          <t>Mengubah data task dengan data valid</t>
+        </is>
+      </c>
+      <c r="E103" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F103" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G103" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Task, klik icon Edit (pensil) di pojok kanan atas.
+2. Ubah data task pada field yang diinginkan.
+3. Klik button Simpan.</t>
+        </is>
+      </c>
+      <c r="H103" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan form Edit Task.
+2. Berhasil mengubah data task.
+3. Berhasil menyimpan perubahan dan data task terupdate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="51" t="inlineStr">
+        <is>
+          <t>10.18</t>
+        </is>
+      </c>
+      <c r="B104" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C104" s="53" t="n"/>
+      <c r="D104" s="54" t="inlineStr">
+        <is>
+          <t>Mengubah data task tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E104" s="52" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F104" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G104" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Task, klik icon Edit (pensil) di pojok kanan atas.
+2. Kosongkan field Judul.
+3. Klik button Simpan.</t>
+        </is>
+      </c>
+      <c r="H104" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan form Edit Task.
+2. Field Judul dalam kondisi kosong.
+3. Sistem menampilkan pesan validasi bahwa field Judul wajib diisi dan perubahan tidak tersimpan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="51" t="inlineStr">
+        <is>
+          <t>10.19</t>
+        </is>
+      </c>
+      <c r="B105" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C105" s="53" t="n"/>
+      <c r="D105" s="54" t="inlineStr">
+        <is>
+          <t>Membagikan task kepada user</t>
+        </is>
+      </c>
+      <c r="E105" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F105" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G105" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Task, klik icon Bagikan (share) di pojok kanan atas.
+2. Pilih opsi Pengguna pada field Bagikan ke.
+3. Pilih peran dan user yang ditugaskan (Assignee).
+4. Klik button Bagikan.</t>
+        </is>
+      </c>
+      <c r="H105" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan form Bagikan Task.
+2. Berhasil memilih opsi penerima Pengguna.
+3. Berhasil memilih user yang ditugaskan.
+4. Berhasil membagikan task dan user penerima muncul pada daftar penugasan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="51" t="inlineStr">
+        <is>
+          <t>10.20</t>
+        </is>
+      </c>
+      <c r="B106" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C106" s="53" t="n"/>
+      <c r="D106" s="54" t="inlineStr">
+        <is>
+          <t>Menghapus penugasan task kepada user</t>
+        </is>
+      </c>
+      <c r="E106" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F106" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G106" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada form Bagikan Task, periksa daftar Ditugaskan ke (User).
+2. Klik icon hapus (tempat sampah) pada user yang ditugaskan.
+3. Konfirmasi penghapusan penugasan task.</t>
+        </is>
+      </c>
+      <c r="H106" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan daftar user yang ditugaskan.
+2. Berhasil memilih user yang akan dihapus dari penugasan.
+3. Berhasil menghapus penugasan task kepada user tersebut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="51" t="inlineStr">
+        <is>
+          <t>10.21</t>
+        </is>
+      </c>
+      <c r="B107" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C107" s="53" t="n"/>
+      <c r="D107" s="54" t="inlineStr">
+        <is>
+          <t>Menambahkan komentar pada task</t>
+        </is>
+      </c>
+      <c r="E107" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F107" s="52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G107" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Task, klik tab Aktivitas &amp; Percakapan.
+2. Tulis komentar pada kolom Tulis komentar.
+3. Klik button Kirim.</t>
+        </is>
+      </c>
+      <c r="H107" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil berpindah ke tab Aktivitas &amp; Percakapan.
+2. Berhasil mengisi kolom komentar.
+3. Berhasil mengirim komentar dan komentar baru tertampil pada riwayat percakapan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="51" t="inlineStr">
+        <is>
+          <t>10.22</t>
+        </is>
+      </c>
+      <c r="B108" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C108" s="53" t="n"/>
+      <c r="D108" s="54" t="inlineStr">
+        <is>
+          <t>Menghapus komentar pada task</t>
+        </is>
+      </c>
+      <c r="E108" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F108" s="52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G108" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Task, klik tab Aktivitas &amp; Percakapan.
+2. Klik icon hapus (tempat sampah) pada salah satu komentar yang ingin dihapus.
+3. Konfirmasi penghapusan komentar.</t>
+        </is>
+      </c>
+      <c r="H108" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil berpindah ke tab Aktivitas &amp; Percakapan.
+2. Berhasil memilih komentar.
+3. Berhasil menghapus komentar dan komentar tersebut hilang dari riwayat percakapan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="51" t="inlineStr">
+        <is>
+          <t>10.23</t>
+        </is>
+      </c>
+      <c r="B109" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C109" s="53" t="n"/>
+      <c r="D109" s="54" t="inlineStr">
+        <is>
+          <t>Memulai pengerjaan task</t>
+        </is>
+      </c>
+      <c r="E109" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F109" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G109" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada card task di Daftar Task, klik icon titik tiga.
+2. Pilih menu Mulai.
+3. Klik button Ya pada pop-up konfirmasi aksi.</t>
+        </is>
+      </c>
+      <c r="H109" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu card task.
+2. Berhasil menampilkan pop-up konfirmasi start.
+3. Berhasil mengubah status task menjadi 'Sedang Dikerjakan'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="51" t="inlineStr">
+        <is>
+          <t>10.24</t>
+        </is>
+      </c>
+      <c r="B110" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C110" s="53" t="n"/>
+      <c r="D110" s="54" t="inlineStr">
+        <is>
+          <t>Menyelesaikan task</t>
+        </is>
+      </c>
+      <c r="E110" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F110" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G110" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada card task di Daftar Task, klik icon titik tiga.
+2. Pilih menu Selesaikan.
+3. Klik button Ya pada pop-up konfirmasi aksi.</t>
+        </is>
+      </c>
+      <c r="H110" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu card task.
+2. Berhasil menampilkan pop-up konfirmasi complete.
+3. Berhasil mengubah status task menjadi 'Selesai'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="51" t="inlineStr">
+        <is>
+          <t>10.25</t>
+        </is>
+      </c>
+      <c r="B111" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C111" s="53" t="n"/>
+      <c r="D111" s="54" t="inlineStr">
+        <is>
+          <t>Membatalkan task</t>
+        </is>
+      </c>
+      <c r="E111" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F111" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G111" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada card task di Daftar Task, klik icon titik tiga.
+2. Pilih menu Batalkan.
+3. Klik button Ya pada pop-up konfirmasi aksi.</t>
+        </is>
+      </c>
+      <c r="H111" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu card task.
+2. Berhasil menampilkan pop-up konfirmasi cancel.
+3. Berhasil membatalkan task dan status task terupdate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="51" t="inlineStr">
+        <is>
+          <t>10.26</t>
+        </is>
+      </c>
+      <c r="B112" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C112" s="53" t="n"/>
+      <c r="D112" s="54" t="inlineStr">
+        <is>
+          <t>Membuka kembali task yang telah selesai</t>
+        </is>
+      </c>
+      <c r="E112" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F112" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G112" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada card task yang berstatus Selesai, klik icon titik tiga.
+2. Pilih menu Buka Kembali.
+3. Klik button Ya pada pop-up konfirmasi aksi.</t>
+        </is>
+      </c>
+      <c r="H112" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu card task.
+2. Berhasil menampilkan pop-up konfirmasi aksi.
+3. Berhasil membuka kembali task dan status task berubah menjadi 'Terbuka'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="51" t="inlineStr">
+        <is>
+          <t>10.27</t>
+        </is>
+      </c>
+      <c r="B113" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C113" s="53" t="n"/>
+      <c r="D113" s="54" t="inlineStr">
+        <is>
+          <t>Menghapus task secara permanen</t>
+        </is>
+      </c>
+      <c r="E113" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F113" s="52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G113" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada card task di Daftar Task, klik icon titik tiga.
+2. Pilih menu Hapus Permanen.
+3. Konfirmasi penghapusan task.</t>
+        </is>
+      </c>
+      <c r="H113" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu card task.
+2. Berhasil mengonfirmasi penghapusan.
+3. Berhasil menghapus task secara permanen dari daftar task.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="51" t="inlineStr">
+        <is>
+          <t>10.28</t>
+        </is>
+      </c>
+      <c r="B114" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C114" s="53" t="n"/>
+      <c r="D114" s="54" t="inlineStr">
+        <is>
+          <t>Membuka halaman Daftar Acara</t>
+        </is>
+      </c>
+      <c r="E114" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F114" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G114" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Kalender, klik icon titik tiga pada pojok kanan atas.
+2. Pilih menu Daftar Acara.</t>
+        </is>
+      </c>
+      <c r="H114" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu.
+2. Berhasil menampilkan halaman Daftar Acara beserta daftar acara yang terdaftar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="51" t="inlineStr">
+        <is>
+          <t>10.29</t>
+        </is>
+      </c>
+      <c r="B115" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C115" s="53" t="n"/>
+      <c r="D115" s="54" t="inlineStr">
+        <is>
+          <t>Mencari acara dengan kata kunci valid</t>
+        </is>
+      </c>
+      <c r="E115" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F115" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G115" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon Search pada header halaman Daftar Acara.
+2. Masukkan kata kunci pencarian acara yang valid.</t>
+        </is>
+      </c>
+      <c r="H115" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan kolom pencarian.
+2. Berhasil menampilkan data acara yang sesuai dengan kata kunci pencarian.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="51" t="inlineStr">
+        <is>
+          <t>10.30</t>
+        </is>
+      </c>
+      <c r="B116" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C116" s="53" t="n"/>
+      <c r="D116" s="54" t="inlineStr">
+        <is>
+          <t>Mencari acara dengan kata kunci tidak valid</t>
+        </is>
+      </c>
+      <c r="E116" s="52" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F116" s="52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G116" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon Search pada header halaman Daftar Acara.
+2. Masukkan kata kunci pencarian yang tidak terdaftar.</t>
+        </is>
+      </c>
+      <c r="H116" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan kolom pencarian.
+2. Sistem menampilkan pesan bahwa data acara tidak ditemukan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="51" t="inlineStr">
+        <is>
+          <t>10.31</t>
+        </is>
+      </c>
+      <c r="B117" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C117" s="53" t="n"/>
+      <c r="D117" s="54" t="inlineStr">
+        <is>
+          <t>Melakukan filter Daftar Acara</t>
+        </is>
+      </c>
+      <c r="E117" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F117" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G117" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon Filter pada pojok kanan atas halaman Daftar Acara.
+2. Pilih kriteria Status filter yang diinginkan.
+3. Klik button Terapkan.</t>
+        </is>
+      </c>
+      <c r="H117" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan bottom sheet Filter Acara.
+2. Berhasil memilih kriteria status.
+3. Berhasil memfilter dan menampilkan daftar acara sesuai status yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="51" t="inlineStr">
+        <is>
+          <t>10.32</t>
+        </is>
+      </c>
+      <c r="B118" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C118" s="53" t="n"/>
+      <c r="D118" s="54" t="inlineStr">
+        <is>
+          <t>Mereset filter Daftar Acara</t>
+        </is>
+      </c>
+      <c r="E118" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F118" s="52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G118" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon Filter pada pojok kanan atas halaman Daftar Acara.
+2. Klik icon Reset pada pojok kanan atas bottom sheet Filter Acara.
+3. Klik button Terapkan.</t>
+        </is>
+      </c>
+      <c r="H118" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan bottom sheet Filter Acara.
+2. Kriteria filter kembali ke kondisi default (Semua).
+3. Berhasil menampilkan seluruh daftar acara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="51" t="inlineStr">
+        <is>
+          <t>10.33</t>
+        </is>
+      </c>
+      <c r="B119" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C119" s="53" t="n"/>
+      <c r="D119" s="54" t="inlineStr">
+        <is>
+          <t>Melihat detail acara</t>
+        </is>
+      </c>
+      <c r="E119" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F119" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G119" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik salah satu card acara pada Daftar Acara.</t>
+        </is>
+      </c>
+      <c r="H119" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka halaman Detail Acara yang memuat tab Detail (Status, Visibilitas, Mulai, Selesai, Zona Waktu, Pemilik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="51" t="inlineStr">
+        <is>
+          <t>10.34</t>
+        </is>
+      </c>
+      <c r="B120" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C120" s="53" t="n"/>
+      <c r="D120" s="54" t="inlineStr">
+        <is>
+          <t>Mengubah data acara dengan data valid</t>
+        </is>
+      </c>
+      <c r="E120" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F120" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G120" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Acara, klik icon Edit (pensil) di pojok kanan atas.
+2. Ubah data acara pada field yang diinginkan.
+3. Klik button Simpan.</t>
+        </is>
+      </c>
+      <c r="H120" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan form Edit Acara.
+2. Berhasil mengubah data acara.
+3. Berhasil menyimpan perubahan dan data acara terupdate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="51" t="inlineStr">
+        <is>
+          <t>10.35</t>
+        </is>
+      </c>
+      <c r="B121" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C121" s="53" t="n"/>
+      <c r="D121" s="54" t="inlineStr">
+        <is>
+          <t>Mengubah data acara tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E121" s="52" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F121" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G121" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Acara, klik icon Edit (pensil) di pojok kanan atas.
+2. Kosongkan field Judul.
+3. Klik button Simpan.</t>
+        </is>
+      </c>
+      <c r="H121" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan form Edit Acara.
+2. Field Judul dalam kondisi kosong.
+3. Sistem menampilkan pesan validasi bahwa field Judul wajib diisi dan perubahan tidak tersimpan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="51" t="inlineStr">
+        <is>
+          <t>10.36</t>
+        </is>
+      </c>
+      <c r="B122" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C122" s="53" t="n"/>
+      <c r="D122" s="54" t="inlineStr">
+        <is>
+          <t>Membagikan acara kepada user</t>
+        </is>
+      </c>
+      <c r="E122" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F122" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G122" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Acara, klik icon Bagikan (share) di pojok kanan atas.
+2. Pilih opsi penerima pada field Bagikan ke.
+3. Tentukan user yang ditugaskan.
+4. Klik button Bagikan.</t>
+        </is>
+      </c>
+      <c r="H122" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan form Bagikan Acara.
+2. Berhasil memilih penerima dan user yang ditugaskan.
+3. Berhasil membagikan acara dan user penerima muncul pada daftar penugasan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="51" t="inlineStr">
+        <is>
+          <t>10.37</t>
+        </is>
+      </c>
+      <c r="B123" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C123" s="53" t="n"/>
+      <c r="D123" s="54" t="inlineStr">
+        <is>
+          <t>Menghapus penugasan acara kepada user</t>
+        </is>
+      </c>
+      <c r="E123" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F123" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G123" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada form Bagikan Acara, periksa daftar Ditugaskan ke (User).
+2. Klik icon hapus (tempat sampah) pada user yang ditugaskan.
+3. Konfirmasi penghapusan penugasan acara.</t>
+        </is>
+      </c>
+      <c r="H123" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan daftar user yang ditugaskan.
+2. Berhasil memilih user yang akan dihapus dari penugasan.
+3. Berhasil menghapus penugasan acara kepada user tersebut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="51" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="B124" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C124" s="53" t="n"/>
+      <c r="D124" s="54" t="inlineStr">
+        <is>
+          <t>Membatalkan acara</t>
+        </is>
+      </c>
+      <c r="E124" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F124" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G124" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada card acara di Daftar Acara, klik icon titik tiga.
+2. Pilih menu Batalkan.
+3. Klik button Ya pada pop-up konfirmasi aksi.</t>
+        </is>
+      </c>
+      <c r="H124" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu card acara.
+2. Berhasil menampilkan pop-up konfirmasi batalkan.
+3. Berhasil membatalkan acara dan status acara terupdate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="51" t="inlineStr">
+        <is>
+          <t>10.39</t>
+        </is>
+      </c>
+      <c r="B125" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C125" s="53" t="n"/>
+      <c r="D125" s="54" t="inlineStr">
+        <is>
+          <t>Menghapus acara secara permanen</t>
+        </is>
+      </c>
+      <c r="E125" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F125" s="52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G125" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada card acara di Daftar Acara, klik icon titik tiga.
+2. Pilih menu Hapus Permanen.
+3. Klik button Ya pada pop-up konfirmasi aksi.</t>
+        </is>
+      </c>
+      <c r="H125" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu card acara.
+2. Berhasil menampilkan pop-up konfirmasi hapus permanen.
+3. Berhasil menghapus acara secara permanen dari daftar acara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="51" t="inlineStr">
+        <is>
+          <t>10.40</t>
+        </is>
+      </c>
+      <c r="B126" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C126" s="53" t="n"/>
+      <c r="D126" s="54" t="inlineStr">
+        <is>
+          <t>Membuka halaman Kelola Label</t>
+        </is>
+      </c>
+      <c r="E126" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F126" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G126" s="54" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Kalender, klik icon titik tiga pada pojok kanan atas.
+2. Pilih menu Kelola Label.</t>
+        </is>
+      </c>
+      <c r="H126" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up action menu.
+2. Berhasil menampilkan halaman Kelola Label beserta form tambah label dan daftar label yang tersedia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="51" t="inlineStr">
+        <is>
+          <t>10.41</t>
+        </is>
+      </c>
+      <c r="B127" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C127" s="53" t="n"/>
+      <c r="D127" s="54" t="inlineStr">
+        <is>
+          <t>Menambahkan label baru dengan data valid</t>
+        </is>
+      </c>
+      <c r="E127" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F127" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G127" s="54" t="inlineStr">
+        <is>
+          <t>1. Masukkan nama label pada field Nama label.
+2. Pilih warna label pada dropdown Warna.
+3. Klik button Tambah.</t>
+        </is>
+      </c>
+      <c r="H127" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi field Nama label.
+2. Berhasil memilih warna label.
+3. Berhasil menambahkan label baru dan label tertampil pada daftar label di bawah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="51" t="inlineStr">
+        <is>
+          <t>10.42</t>
+        </is>
+      </c>
+      <c r="B128" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C128" s="53" t="n"/>
+      <c r="D128" s="54" t="inlineStr">
+        <is>
+          <t>Menambahkan label baru tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E128" s="52" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F128" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G128" s="54" t="inlineStr">
+        <is>
+          <t>1. Kosongkan field Nama label.
+2. Klik button Tambah.</t>
+        </is>
+      </c>
+      <c r="H128" s="54" t="inlineStr">
+        <is>
+          <t>1. Field Nama label dalam kondisi kosong.
+2. Sistem menampilkan pesan validasi bahwa Nama label wajib diisi dan label tidak ditambahkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="51" t="inlineStr">
+        <is>
+          <t>10.43</t>
+        </is>
+      </c>
+      <c r="B129" s="52" t="inlineStr">
+        <is>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C129" s="53" t="n"/>
+      <c r="D129" s="54" t="inlineStr">
+        <is>
+          <t>Menghapus label</t>
+        </is>
+      </c>
+      <c r="E129" s="52" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F129" s="52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G129" s="54" t="inlineStr">
+        <is>
+          <t>1. Klik icon hapus (tempat sampah) pada salah satu item label di daftar label.
+2. Konfirmasi penghapusan label.</t>
+        </is>
+      </c>
+      <c r="H129" s="54" t="inlineStr">
+        <is>
+          <t>1. Berhasil memilih label yang akan dihapus.
+2. Berhasil menghapus label dan label tersebut terhapus dari daftar label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="B130" s="46" t="inlineStr">
         <is>
           <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
-      <c r="C87" s="46" t="inlineStr">
+      <c r="C130" s="46" t="inlineStr">
         <is>
           <t>Aktifitas Prospek</t>
         </is>
       </c>
-      <c r="D87" s="48" t="inlineStr">
+      <c r="D130" s="48" t="inlineStr">
         <is>
           <t>Membuka halaman Aktifitas Prospek</t>
         </is>
       </c>
-      <c r="E87" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F87" s="46" t="inlineStr">
+      <c r="E130" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F130" s="46" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G87" s="48" t="inlineStr">
+      <c r="G130" s="48" t="inlineStr">
         <is>
           <t>1. Buka menu Lainnya.
 2. Klik menu Aktifitas Prospek.</t>
         </is>
       </c>
-      <c r="H87" s="48" t="inlineStr">
+      <c r="H130" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Lainnya.
 2. Berhasil menampilkan halaman Aktifitas Prospek.</t>
-        </is>
-      </c>
-      <c r="I87" s="49" t="n"/>
-      <c r="J87" s="49" t="n"/>
-      <c r="K87" s="49" t="n"/>
-      <c r="L87" s="49" t="n"/>
-      <c r="M87" s="49" t="n"/>
-      <c r="N87" s="49" t="n"/>
-      <c r="O87" s="49" t="n"/>
-      <c r="P87" s="49" t="n"/>
-      <c r="Q87" s="49" t="n"/>
-      <c r="R87" s="49" t="n"/>
-      <c r="S87" s="49" t="n"/>
-      <c r="T87" s="49" t="n"/>
-      <c r="U87" s="49" t="n"/>
-      <c r="V87" s="49" t="n"/>
-      <c r="W87" s="49" t="n"/>
-      <c r="X87" s="49" t="n"/>
-      <c r="Y87" s="49" t="n"/>
-      <c r="Z87" s="49" t="n"/>
-      <c r="AA87" s="49" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="B88" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C88" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D88" s="48" t="inlineStr">
-        <is>
-          <t>Mencari prospek menggunakan Search Bar</t>
-        </is>
-      </c>
-      <c r="E88" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F88" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G88" s="48" t="inlineStr">
-        <is>
-          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
-        </is>
-      </c>
-      <c r="H88" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data prospek yang sesuai dengan kata kunci pencarian.</t>
-        </is>
-      </c>
-      <c r="I88" s="49" t="n"/>
-      <c r="J88" s="49" t="n"/>
-      <c r="K88" s="49" t="n"/>
-      <c r="L88" s="49" t="n"/>
-      <c r="M88" s="49" t="n"/>
-      <c r="N88" s="49" t="n"/>
-      <c r="O88" s="49" t="n"/>
-      <c r="P88" s="49" t="n"/>
-      <c r="Q88" s="49" t="n"/>
-      <c r="R88" s="49" t="n"/>
-      <c r="S88" s="49" t="n"/>
-      <c r="T88" s="49" t="n"/>
-      <c r="U88" s="49" t="n"/>
-      <c r="V88" s="49" t="n"/>
-      <c r="W88" s="49" t="n"/>
-      <c r="X88" s="49" t="n"/>
-      <c r="Y88" s="49" t="n"/>
-      <c r="Z88" s="49" t="n"/>
-      <c r="AA88" s="49" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="B89" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C89" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D89" s="48" t="inlineStr">
-        <is>
-          <t>Mencari prospek dengan keyword tidak valid</t>
-        </is>
-      </c>
-      <c r="E89" s="46" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F89" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G89" s="48" t="inlineStr">
-        <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
-        </is>
-      </c>
-      <c r="H89" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
-        </is>
-      </c>
-      <c r="I89" s="49" t="n"/>
-      <c r="J89" s="49" t="n"/>
-      <c r="K89" s="49" t="n"/>
-      <c r="L89" s="49" t="n"/>
-      <c r="M89" s="49" t="n"/>
-      <c r="N89" s="49" t="n"/>
-      <c r="O89" s="49" t="n"/>
-      <c r="P89" s="49" t="n"/>
-      <c r="Q89" s="49" t="n"/>
-      <c r="R89" s="49" t="n"/>
-      <c r="S89" s="49" t="n"/>
-      <c r="T89" s="49" t="n"/>
-      <c r="U89" s="49" t="n"/>
-      <c r="V89" s="49" t="n"/>
-      <c r="W89" s="49" t="n"/>
-      <c r="X89" s="49" t="n"/>
-      <c r="Y89" s="49" t="n"/>
-      <c r="Z89" s="49" t="n"/>
-      <c r="AA89" s="49" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
-      <c r="B90" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C90" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D90" s="48" t="inlineStr">
-        <is>
-          <t>Melakukan filter data prospek</t>
-        </is>
-      </c>
-      <c r="E90" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F90" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G90" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik button Filter di halaman Aktifitas Prospek.
-2. Pilih kriteria filter pada form Filter.
-3. Klik button Simpan.</t>
-        </is>
-      </c>
-      <c r="H90" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka form Filter.
-2. Berhasil memilih kriteria filter.
-3. Berhasil menampilkan daftar prospek yang sesuai dengan kriteria filter.</t>
-        </is>
-      </c>
-      <c r="I90" s="49" t="n"/>
-      <c r="J90" s="49" t="n"/>
-      <c r="K90" s="49" t="n"/>
-      <c r="L90" s="49" t="n"/>
-      <c r="M90" s="49" t="n"/>
-      <c r="N90" s="49" t="n"/>
-      <c r="O90" s="49" t="n"/>
-      <c r="P90" s="49" t="n"/>
-      <c r="Q90" s="49" t="n"/>
-      <c r="R90" s="49" t="n"/>
-      <c r="S90" s="49" t="n"/>
-      <c r="T90" s="49" t="n"/>
-      <c r="U90" s="49" t="n"/>
-      <c r="V90" s="49" t="n"/>
-      <c r="W90" s="49" t="n"/>
-      <c r="X90" s="49" t="n"/>
-      <c r="Y90" s="49" t="n"/>
-      <c r="Z90" s="49" t="n"/>
-      <c r="AA90" s="49" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="B91" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C91" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D91" s="48" t="inlineStr">
-        <is>
-          <t>Melihat Detail Prospek</t>
-        </is>
-      </c>
-      <c r="E91" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F91" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G91" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik menu titik tiga pada salah satu card prospek.
-2. Pilih Detail Prospek.</t>
-        </is>
-      </c>
-      <c r="H91" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan menu pilihan.
-2. Berhasil menampilkan detail data prospek.</t>
-        </is>
-      </c>
-      <c r="I91" s="49" t="n"/>
-      <c r="J91" s="49" t="n"/>
-      <c r="K91" s="49" t="n"/>
-      <c r="L91" s="49" t="n"/>
-      <c r="M91" s="49" t="n"/>
-      <c r="N91" s="49" t="n"/>
-      <c r="O91" s="49" t="n"/>
-      <c r="P91" s="49" t="n"/>
-      <c r="Q91" s="49" t="n"/>
-      <c r="R91" s="49" t="n"/>
-      <c r="S91" s="49" t="n"/>
-      <c r="T91" s="49" t="n"/>
-      <c r="U91" s="49" t="n"/>
-      <c r="V91" s="49" t="n"/>
-      <c r="W91" s="49" t="n"/>
-      <c r="X91" s="49" t="n"/>
-      <c r="Y91" s="49" t="n"/>
-      <c r="Z91" s="49" t="n"/>
-      <c r="AA91" s="49" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>10.6</t>
-        </is>
-      </c>
-      <c r="B92" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C92" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D92" s="48" t="inlineStr">
-        <is>
-          <t>Melihat Riwayat Prospek</t>
-        </is>
-      </c>
-      <c r="E92" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F92" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G92" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik menu titik tiga pada salah satu card prospek.
-2. Pilih Riwayat.</t>
-        </is>
-      </c>
-      <c r="H92" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan menu pilihan.
-2. Berhasil membuka halaman Riwayat dan menampilkan daftar log riwayat.</t>
-        </is>
-      </c>
-      <c r="I92" s="49" t="n"/>
-      <c r="J92" s="49" t="n"/>
-      <c r="K92" s="49" t="n"/>
-      <c r="L92" s="49" t="n"/>
-      <c r="M92" s="49" t="n"/>
-      <c r="N92" s="49" t="n"/>
-      <c r="O92" s="49" t="n"/>
-      <c r="P92" s="49" t="n"/>
-      <c r="Q92" s="49" t="n"/>
-      <c r="R92" s="49" t="n"/>
-      <c r="S92" s="49" t="n"/>
-      <c r="T92" s="49" t="n"/>
-      <c r="U92" s="49" t="n"/>
-      <c r="V92" s="49" t="n"/>
-      <c r="W92" s="49" t="n"/>
-      <c r="X92" s="49" t="n"/>
-      <c r="Y92" s="49" t="n"/>
-      <c r="Z92" s="49" t="n"/>
-      <c r="AA92" s="49" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
-      </c>
-      <c r="B93" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C93" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D93" s="48" t="inlineStr">
-        <is>
-          <t>Mencari data pada halaman Riwayat</t>
-        </is>
-      </c>
-      <c r="E93" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F93" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G93" s="48" t="inlineStr">
-        <is>
-          <t>1. Masukkan kata kunci pada Search Bar global.</t>
-        </is>
-      </c>
-      <c r="H93" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil memfilter data riwayat sesuai kata kunci pencarian.</t>
-        </is>
-      </c>
-      <c r="I93" s="49" t="n"/>
-      <c r="J93" s="49" t="n"/>
-      <c r="K93" s="49" t="n"/>
-      <c r="L93" s="49" t="n"/>
-      <c r="M93" s="49" t="n"/>
-      <c r="N93" s="49" t="n"/>
-      <c r="O93" s="49" t="n"/>
-      <c r="P93" s="49" t="n"/>
-      <c r="Q93" s="49" t="n"/>
-      <c r="R93" s="49" t="n"/>
-      <c r="S93" s="49" t="n"/>
-      <c r="T93" s="49" t="n"/>
-      <c r="U93" s="49" t="n"/>
-      <c r="V93" s="49" t="n"/>
-      <c r="W93" s="49" t="n"/>
-      <c r="X93" s="49" t="n"/>
-      <c r="Y93" s="49" t="n"/>
-      <c r="Z93" s="49" t="n"/>
-      <c r="AA93" s="49" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="B94" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C94" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D94" s="48" t="inlineStr">
-        <is>
-          <t>Mencari data dengan keyword tidak valid pada halaman Riwayat</t>
-        </is>
-      </c>
-      <c r="E94" s="46" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F94" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G94" s="48" t="inlineStr">
-        <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
-        </is>
-      </c>
-      <c r="H94" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
-        </is>
-      </c>
-      <c r="I94" s="49" t="n"/>
-      <c r="J94" s="49" t="n"/>
-      <c r="K94" s="49" t="n"/>
-      <c r="L94" s="49" t="n"/>
-      <c r="M94" s="49" t="n"/>
-      <c r="N94" s="49" t="n"/>
-      <c r="O94" s="49" t="n"/>
-      <c r="P94" s="49" t="n"/>
-      <c r="Q94" s="49" t="n"/>
-      <c r="R94" s="49" t="n"/>
-      <c r="S94" s="49" t="n"/>
-      <c r="T94" s="49" t="n"/>
-      <c r="U94" s="49" t="n"/>
-      <c r="V94" s="49" t="n"/>
-      <c r="W94" s="49" t="n"/>
-      <c r="X94" s="49" t="n"/>
-      <c r="Y94" s="49" t="n"/>
-      <c r="Z94" s="49" t="n"/>
-      <c r="AA94" s="49" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="B95" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C95" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D95" s="48" t="inlineStr">
-        <is>
-          <t>Membuka form Input Aktifitas</t>
-        </is>
-      </c>
-      <c r="E95" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F95" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G95" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik button Aktifitas pada prospek yang berstatus aktif (belum closing).</t>
-        </is>
-      </c>
-      <c r="H95" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka halaman Aktifitas Marketing dan menampilkan tab Prospek, Call, Visit, dan NOA Open Account.</t>
-        </is>
-      </c>
-      <c r="I95" s="49" t="n"/>
-      <c r="J95" s="49" t="n"/>
-      <c r="K95" s="49" t="n"/>
-      <c r="L95" s="49" t="n"/>
-      <c r="M95" s="49" t="n"/>
-      <c r="N95" s="49" t="n"/>
-      <c r="O95" s="49" t="n"/>
-      <c r="P95" s="49" t="n"/>
-      <c r="Q95" s="49" t="n"/>
-      <c r="R95" s="49" t="n"/>
-      <c r="S95" s="49" t="n"/>
-      <c r="T95" s="49" t="n"/>
-      <c r="U95" s="49" t="n"/>
-      <c r="V95" s="49" t="n"/>
-      <c r="W95" s="49" t="n"/>
-      <c r="X95" s="49" t="n"/>
-      <c r="Y95" s="49" t="n"/>
-      <c r="Z95" s="49" t="n"/>
-      <c r="AA95" s="49" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>10.10</t>
-        </is>
-      </c>
-      <c r="B96" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C96" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D96" s="48" t="inlineStr">
-        <is>
-          <t>Membuka tab Prospek pada halaman Aktifitas Marketing</t>
-        </is>
-      </c>
-      <c r="E96" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F96" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G96" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik tab Prospek.</t>
-        </is>
-      </c>
-      <c r="H96" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil berpindah ke tab Prospek dan menampilkan form informasi prospek.</t>
-        </is>
-      </c>
-      <c r="I96" s="49" t="n"/>
-      <c r="J96" s="49" t="n"/>
-      <c r="K96" s="49" t="n"/>
-      <c r="L96" s="49" t="n"/>
-      <c r="M96" s="49" t="n"/>
-      <c r="N96" s="49" t="n"/>
-      <c r="O96" s="49" t="n"/>
-      <c r="P96" s="49" t="n"/>
-      <c r="Q96" s="49" t="n"/>
-      <c r="R96" s="49" t="n"/>
-      <c r="S96" s="49" t="n"/>
-      <c r="T96" s="49" t="n"/>
-      <c r="U96" s="49" t="n"/>
-      <c r="V96" s="49" t="n"/>
-      <c r="W96" s="49" t="n"/>
-      <c r="X96" s="49" t="n"/>
-      <c r="Y96" s="49" t="n"/>
-      <c r="Z96" s="49" t="n"/>
-      <c r="AA96" s="49" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>10.11</t>
-        </is>
-      </c>
-      <c r="B97" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C97" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D97" s="48" t="inlineStr">
-        <is>
-          <t>Mengedit data pada tab Prospek</t>
-        </is>
-      </c>
-      <c r="E97" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F97" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G97" s="48" t="inlineStr">
-        <is>
-          <t>1. Ubah data pada form informasi prospek.
-2. Klik button Edit.
-3. Klik button Next.</t>
-        </is>
-      </c>
-      <c r="H97" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengubah data pada form.
-2. Berhasil mengaktifkan mode edit form.
-3. Berhasil menyimpan perubahan dan melanjutkan ke tahap berikutnya.</t>
-        </is>
-      </c>
-      <c r="I97" s="49" t="n"/>
-      <c r="J97" s="49" t="n"/>
-      <c r="K97" s="49" t="n"/>
-      <c r="L97" s="49" t="n"/>
-      <c r="M97" s="49" t="n"/>
-      <c r="N97" s="49" t="n"/>
-      <c r="O97" s="49" t="n"/>
-      <c r="P97" s="49" t="n"/>
-      <c r="Q97" s="49" t="n"/>
-      <c r="R97" s="49" t="n"/>
-      <c r="S97" s="49" t="n"/>
-      <c r="T97" s="49" t="n"/>
-      <c r="U97" s="49" t="n"/>
-      <c r="V97" s="49" t="n"/>
-      <c r="W97" s="49" t="n"/>
-      <c r="X97" s="49" t="n"/>
-      <c r="Y97" s="49" t="n"/>
-      <c r="Z97" s="49" t="n"/>
-      <c r="AA97" s="49" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>10.12</t>
-        </is>
-      </c>
-      <c r="B98" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C98" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D98" s="48" t="inlineStr">
-        <is>
-          <t>Membuka tab Call pada halaman Aktifitas Marketing</t>
-        </is>
-      </c>
-      <c r="E98" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F98" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G98" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik tab Call.</t>
-        </is>
-      </c>
-      <c r="H98" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil berpindah ke tab Call dan menampilkan form input Call serta Log Staging Call.</t>
-        </is>
-      </c>
-      <c r="I98" s="49" t="n"/>
-      <c r="J98" s="49" t="n"/>
-      <c r="K98" s="49" t="n"/>
-      <c r="L98" s="49" t="n"/>
-      <c r="M98" s="49" t="n"/>
-      <c r="N98" s="49" t="n"/>
-      <c r="O98" s="49" t="n"/>
-      <c r="P98" s="49" t="n"/>
-      <c r="Q98" s="49" t="n"/>
-      <c r="R98" s="49" t="n"/>
-      <c r="S98" s="49" t="n"/>
-      <c r="T98" s="49" t="n"/>
-      <c r="U98" s="49" t="n"/>
-      <c r="V98" s="49" t="n"/>
-      <c r="W98" s="49" t="n"/>
-      <c r="X98" s="49" t="n"/>
-      <c r="Y98" s="49" t="n"/>
-      <c r="Z98" s="49" t="n"/>
-      <c r="AA98" s="49" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>10.13</t>
-        </is>
-      </c>
-      <c r="B99" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C99" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D99" s="48" t="inlineStr">
-        <is>
-          <t>Melakukan panggilan langsung melalui tombol Call</t>
-        </is>
-      </c>
-      <c r="E99" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F99" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G99" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik button Call di samping nomor handphone.</t>
-        </is>
-      </c>
-      <c r="H99" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengarahkan ke aplikasi telepon bawaan perangkat (dialer).</t>
-        </is>
-      </c>
-      <c r="I99" s="49" t="n"/>
-      <c r="J99" s="49" t="n"/>
-      <c r="K99" s="49" t="n"/>
-      <c r="L99" s="49" t="n"/>
-      <c r="M99" s="49" t="n"/>
-      <c r="N99" s="49" t="n"/>
-      <c r="O99" s="49" t="n"/>
-      <c r="P99" s="49" t="n"/>
-      <c r="Q99" s="49" t="n"/>
-      <c r="R99" s="49" t="n"/>
-      <c r="S99" s="49" t="n"/>
-      <c r="T99" s="49" t="n"/>
-      <c r="U99" s="49" t="n"/>
-      <c r="V99" s="49" t="n"/>
-      <c r="W99" s="49" t="n"/>
-      <c r="X99" s="49" t="n"/>
-      <c r="Y99" s="49" t="n"/>
-      <c r="Z99" s="49" t="n"/>
-      <c r="AA99" s="49" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>10.14</t>
-        </is>
-      </c>
-      <c r="B100" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C100" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D100" s="48" t="inlineStr">
-        <is>
-          <t>Menyimpan log Call dengan data valid</t>
-        </is>
-      </c>
-      <c r="E100" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F100" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G100" s="48" t="inlineStr">
-        <is>
-          <t>1. Isi field Status Call dan Keterangan dengan data valid.
-2. Klik button Simpan.</t>
-        </is>
-      </c>
-      <c r="H100" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field Status Call dan Keterangan.
-2. Berhasil menyimpan aktifitas Call dan menambahkannya ke Log Staging Call.</t>
-        </is>
-      </c>
-      <c r="I100" s="49" t="n"/>
-      <c r="J100" s="49" t="n"/>
-      <c r="K100" s="49" t="n"/>
-      <c r="L100" s="49" t="n"/>
-      <c r="M100" s="49" t="n"/>
-      <c r="N100" s="49" t="n"/>
-      <c r="O100" s="49" t="n"/>
-      <c r="P100" s="49" t="n"/>
-      <c r="Q100" s="49" t="n"/>
-      <c r="R100" s="49" t="n"/>
-      <c r="S100" s="49" t="n"/>
-      <c r="T100" s="49" t="n"/>
-      <c r="U100" s="49" t="n"/>
-      <c r="V100" s="49" t="n"/>
-      <c r="W100" s="49" t="n"/>
-      <c r="X100" s="49" t="n"/>
-      <c r="Y100" s="49" t="n"/>
-      <c r="Z100" s="49" t="n"/>
-      <c r="AA100" s="49" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="B101" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C101" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D101" s="48" t="inlineStr">
-        <is>
-          <t>Menyimpan log Call tanpa field mandatory</t>
-        </is>
-      </c>
-      <c r="E101" s="46" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F101" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G101" s="48" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field Status Call dan Keterangan.
-2. Klik button Simpan.</t>
-        </is>
-      </c>
-      <c r="H101" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field mandatory.
-2. Menampilkan pesan validasi bahwa field Status Call dan Keterangan wajib diisi.</t>
-        </is>
-      </c>
-      <c r="I101" s="49" t="n"/>
-      <c r="J101" s="49" t="n"/>
-      <c r="K101" s="49" t="n"/>
-      <c r="L101" s="49" t="n"/>
-      <c r="M101" s="49" t="n"/>
-      <c r="N101" s="49" t="n"/>
-      <c r="O101" s="49" t="n"/>
-      <c r="P101" s="49" t="n"/>
-      <c r="Q101" s="49" t="n"/>
-      <c r="R101" s="49" t="n"/>
-      <c r="S101" s="49" t="n"/>
-      <c r="T101" s="49" t="n"/>
-      <c r="U101" s="49" t="n"/>
-      <c r="V101" s="49" t="n"/>
-      <c r="W101" s="49" t="n"/>
-      <c r="X101" s="49" t="n"/>
-      <c r="Y101" s="49" t="n"/>
-      <c r="Z101" s="49" t="n"/>
-      <c r="AA101" s="49" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>10.16</t>
-        </is>
-      </c>
-      <c r="B102" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C102" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D102" s="48" t="inlineStr">
-        <is>
-          <t>Membuka tab Visit pada halaman Aktifitas Marketing</t>
-        </is>
-      </c>
-      <c r="E102" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F102" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G102" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik tab Visit.</t>
-        </is>
-      </c>
-      <c r="H102" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil berpindah ke tab Visit dan menampilkan button Visit In serta Log Staging Visit.</t>
-        </is>
-      </c>
-      <c r="I102" s="49" t="n"/>
-      <c r="J102" s="49" t="n"/>
-      <c r="K102" s="49" t="n"/>
-      <c r="L102" s="49" t="n"/>
-      <c r="M102" s="49" t="n"/>
-      <c r="N102" s="49" t="n"/>
-      <c r="O102" s="49" t="n"/>
-      <c r="P102" s="49" t="n"/>
-      <c r="Q102" s="49" t="n"/>
-      <c r="R102" s="49" t="n"/>
-      <c r="S102" s="49" t="n"/>
-      <c r="T102" s="49" t="n"/>
-      <c r="U102" s="49" t="n"/>
-      <c r="V102" s="49" t="n"/>
-      <c r="W102" s="49" t="n"/>
-      <c r="X102" s="49" t="n"/>
-      <c r="Y102" s="49" t="n"/>
-      <c r="Z102" s="49" t="n"/>
-      <c r="AA102" s="49" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>10.17</t>
-        </is>
-      </c>
-      <c r="B103" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C103" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D103" s="48" t="inlineStr">
-        <is>
-          <t>Melakukan Visit In</t>
-        </is>
-      </c>
-      <c r="E103" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F103" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G103" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik button Visit In.</t>
-        </is>
-      </c>
-      <c r="H103" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengarahkan ke halaman Kunjungan dan menampilkan pop up pilihan tipe Visit.</t>
-        </is>
-      </c>
-      <c r="I103" s="49" t="n"/>
-      <c r="J103" s="49" t="n"/>
-      <c r="K103" s="49" t="n"/>
-      <c r="L103" s="49" t="n"/>
-      <c r="M103" s="49" t="n"/>
-      <c r="N103" s="49" t="n"/>
-      <c r="O103" s="49" t="n"/>
-      <c r="P103" s="49" t="n"/>
-      <c r="Q103" s="49" t="n"/>
-      <c r="R103" s="49" t="n"/>
-      <c r="S103" s="49" t="n"/>
-      <c r="T103" s="49" t="n"/>
-      <c r="U103" s="49" t="n"/>
-      <c r="V103" s="49" t="n"/>
-      <c r="W103" s="49" t="n"/>
-      <c r="X103" s="49" t="n"/>
-      <c r="Y103" s="49" t="n"/>
-      <c r="Z103" s="49" t="n"/>
-      <c r="AA103" s="49" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>10.18</t>
-        </is>
-      </c>
-      <c r="B104" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C104" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D104" s="48" t="inlineStr">
-        <is>
-          <t>Membuka tab NOA Open Account pada halaman Aktifitas Marketing</t>
-        </is>
-      </c>
-      <c r="E104" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F104" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G104" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik tab NOA Open Account.</t>
-        </is>
-      </c>
-      <c r="H104" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil berpindah ke tab NOA Open Account dan menampilkan form NOA Open Account.</t>
-        </is>
-      </c>
-      <c r="I104" s="49" t="n"/>
-      <c r="J104" s="49" t="n"/>
-      <c r="K104" s="49" t="n"/>
-      <c r="L104" s="49" t="n"/>
-      <c r="M104" s="49" t="n"/>
-      <c r="N104" s="49" t="n"/>
-      <c r="O104" s="49" t="n"/>
-      <c r="P104" s="49" t="n"/>
-      <c r="Q104" s="49" t="n"/>
-      <c r="R104" s="49" t="n"/>
-      <c r="S104" s="49" t="n"/>
-      <c r="T104" s="49" t="n"/>
-      <c r="U104" s="49" t="n"/>
-      <c r="V104" s="49" t="n"/>
-      <c r="W104" s="49" t="n"/>
-      <c r="X104" s="49" t="n"/>
-      <c r="Y104" s="49" t="n"/>
-      <c r="Z104" s="49" t="n"/>
-      <c r="AA104" s="49" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>10.19</t>
-        </is>
-      </c>
-      <c r="B105" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C105" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D105" s="48" t="inlineStr">
-        <is>
-          <t>Melakukan Submit NOA Open Account dengan data valid</t>
-        </is>
-      </c>
-      <c r="E105" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F105" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G105" s="48" t="inlineStr">
-        <is>
-          <t>1. Mengisi seluruh field pada form NOA Open Account dengan data valid.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H105" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi data pada form NOA Open Account.
-2. Berhasil men-submit form dan menyimpan data Open Account.</t>
-        </is>
-      </c>
-      <c r="I105" s="49" t="n"/>
-      <c r="J105" s="49" t="n"/>
-      <c r="K105" s="49" t="n"/>
-      <c r="L105" s="49" t="n"/>
-      <c r="M105" s="49" t="n"/>
-      <c r="N105" s="49" t="n"/>
-      <c r="O105" s="49" t="n"/>
-      <c r="P105" s="49" t="n"/>
-      <c r="Q105" s="49" t="n"/>
-      <c r="R105" s="49" t="n"/>
-      <c r="S105" s="49" t="n"/>
-      <c r="T105" s="49" t="n"/>
-      <c r="U105" s="49" t="n"/>
-      <c r="V105" s="49" t="n"/>
-      <c r="W105" s="49" t="n"/>
-      <c r="X105" s="49" t="n"/>
-      <c r="Y105" s="49" t="n"/>
-      <c r="Z105" s="49" t="n"/>
-      <c r="AA105" s="49" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>10.20</t>
-        </is>
-      </c>
-      <c r="B106" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C106" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D106" s="48" t="inlineStr">
-        <is>
-          <t>Melakukan Submit NOA Open Account tanpa field mandatory</t>
-        </is>
-      </c>
-      <c r="E106" s="46" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F106" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G106" s="48" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan seluruh field mandatory pada form NOA Open Account.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H106" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field mandatory.
-2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
-        </is>
-      </c>
-      <c r="I106" s="49" t="n"/>
-      <c r="J106" s="49" t="n"/>
-      <c r="K106" s="49" t="n"/>
-      <c r="L106" s="49" t="n"/>
-      <c r="M106" s="49" t="n"/>
-      <c r="N106" s="49" t="n"/>
-      <c r="O106" s="49" t="n"/>
-      <c r="P106" s="49" t="n"/>
-      <c r="Q106" s="49" t="n"/>
-      <c r="R106" s="49" t="n"/>
-      <c r="S106" s="49" t="n"/>
-      <c r="T106" s="49" t="n"/>
-      <c r="U106" s="49" t="n"/>
-      <c r="V106" s="49" t="n"/>
-      <c r="W106" s="49" t="n"/>
-      <c r="X106" s="49" t="n"/>
-      <c r="Y106" s="49" t="n"/>
-      <c r="Z106" s="49" t="n"/>
-      <c r="AA106" s="49" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>10.21</t>
-        </is>
-      </c>
-      <c r="B107" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C107" s="46" t="inlineStr">
-        <is>
-          <t>Aktifitas Prospek</t>
-        </is>
-      </c>
-      <c r="D107" s="48" t="inlineStr">
-        <is>
-          <t>Membatalkan prospek melalui menu titik tiga</t>
-        </is>
-      </c>
-      <c r="E107" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F107" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G107" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik menu titik tiga pada pojok kanan atas.
-2. Pilih Batalkan Prospek.
-3. Klik button Batalkan pada pop-up konfirmasi.</t>
-        </is>
-      </c>
-      <c r="H107" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu dropdown.
-2. Berhasil menampilkan pop-up konfirmasi pembatalan.
-3. Berhasil membatalkan prospek dan prospek tidak dapat dilanjutkan kembali.</t>
-        </is>
-      </c>
-      <c r="I107" s="49" t="n"/>
-      <c r="J107" s="49" t="n"/>
-      <c r="K107" s="49" t="n"/>
-      <c r="L107" s="49" t="n"/>
-      <c r="M107" s="49" t="n"/>
-      <c r="N107" s="49" t="n"/>
-      <c r="O107" s="49" t="n"/>
-      <c r="P107" s="49" t="n"/>
-      <c r="Q107" s="49" t="n"/>
-      <c r="R107" s="49" t="n"/>
-      <c r="S107" s="49" t="n"/>
-      <c r="T107" s="49" t="n"/>
-      <c r="U107" s="49" t="n"/>
-      <c r="V107" s="49" t="n"/>
-      <c r="W107" s="49" t="n"/>
-      <c r="X107" s="49" t="n"/>
-      <c r="Y107" s="49" t="n"/>
-      <c r="Z107" s="49" t="n"/>
-      <c r="AA107" s="49" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B108" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C108" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D108" s="48" t="inlineStr">
-        <is>
-          <t>Membuka halaman Input Prospek melalui navigation bar bawah</t>
-        </is>
-      </c>
-      <c r="E108" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F108" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G108" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik menu Input pada navigation bar bawah.</t>
-        </is>
-      </c>
-      <c r="H108" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka halaman Input Prospek dan menampilkan pop up tipe prospek.</t>
-        </is>
-      </c>
-      <c r="I108" s="49" t="n"/>
-      <c r="J108" s="49" t="n"/>
-      <c r="K108" s="49" t="n"/>
-      <c r="L108" s="49" t="n"/>
-      <c r="M108" s="49" t="n"/>
-      <c r="N108" s="49" t="n"/>
-      <c r="O108" s="49" t="n"/>
-      <c r="P108" s="49" t="n"/>
-      <c r="Q108" s="49" t="n"/>
-      <c r="R108" s="49" t="n"/>
-      <c r="S108" s="49" t="n"/>
-      <c r="T108" s="49" t="n"/>
-      <c r="U108" s="49" t="n"/>
-      <c r="V108" s="49" t="n"/>
-      <c r="W108" s="49" t="n"/>
-      <c r="X108" s="49" t="n"/>
-      <c r="Y108" s="49" t="n"/>
-      <c r="Z108" s="49" t="n"/>
-      <c r="AA108" s="49" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="B109" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C109" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D109" s="48" t="inlineStr">
-        <is>
-          <t>Membuka halaman Input Prospek melalui menu Lainnya</t>
-        </is>
-      </c>
-      <c r="E109" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F109" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G109" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik menu Lainnya pada navigation bar bawah.
-2. Klik menu Input Prospek.</t>
-        </is>
-      </c>
-      <c r="H109" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil membuka halaman Input Prospek dan menampilkan pop up tipe prospek.</t>
-        </is>
-      </c>
-      <c r="I109" s="49" t="n"/>
-      <c r="J109" s="49" t="n"/>
-      <c r="K109" s="49" t="n"/>
-      <c r="L109" s="49" t="n"/>
-      <c r="M109" s="49" t="n"/>
-      <c r="N109" s="49" t="n"/>
-      <c r="O109" s="49" t="n"/>
-      <c r="P109" s="49" t="n"/>
-      <c r="Q109" s="49" t="n"/>
-      <c r="R109" s="49" t="n"/>
-      <c r="S109" s="49" t="n"/>
-      <c r="T109" s="49" t="n"/>
-      <c r="U109" s="49" t="n"/>
-      <c r="V109" s="49" t="n"/>
-      <c r="W109" s="49" t="n"/>
-      <c r="X109" s="49" t="n"/>
-      <c r="Y109" s="49" t="n"/>
-      <c r="Z109" s="49" t="n"/>
-      <c r="AA109" s="49" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="B110" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C110" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D110" s="48" t="inlineStr">
-        <is>
-          <t>Memilih tipe Prospek Individu</t>
-        </is>
-      </c>
-      <c r="E110" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F110" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G110" s="48" t="inlineStr">
-        <is>
-          <t>1. Buka halaman Input Prospek.
-2. Klik pilihan Individu.</t>
-        </is>
-      </c>
-      <c r="H110" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka halaman Input Prospek.
-2. Berhasil menampilkan form Step 1 Informasi.</t>
-        </is>
-      </c>
-      <c r="I110" s="49" t="n"/>
-      <c r="J110" s="49" t="n"/>
-      <c r="K110" s="49" t="n"/>
-      <c r="L110" s="49" t="n"/>
-      <c r="M110" s="49" t="n"/>
-      <c r="N110" s="49" t="n"/>
-      <c r="O110" s="49" t="n"/>
-      <c r="P110" s="49" t="n"/>
-      <c r="Q110" s="49" t="n"/>
-      <c r="R110" s="49" t="n"/>
-      <c r="S110" s="49" t="n"/>
-      <c r="T110" s="49" t="n"/>
-      <c r="U110" s="49" t="n"/>
-      <c r="V110" s="49" t="n"/>
-      <c r="W110" s="49" t="n"/>
-      <c r="X110" s="49" t="n"/>
-      <c r="Y110" s="49" t="n"/>
-      <c r="Z110" s="49" t="n"/>
-      <c r="AA110" s="49" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="B111" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C111" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D111" s="48" t="inlineStr">
-        <is>
-          <t>Mengisi form Step 1 (Informasi) dengan data valid</t>
-        </is>
-      </c>
-      <c r="E111" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F111" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G111" s="48" t="inlineStr">
-        <is>
-          <t>1. Buka form Input Prospek Individu (Step 1 Informasi).
-2. Mengisi seluruh field pada Step 1 Informasi dengan data valid.
-3. Klik button Next.</t>
-        </is>
-      </c>
-      <c r="H111" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan form Step 1 Informasi.
-2. Berhasil mengisi data pada Step 1 Informasi.
-3. Berhasil menyimpan data Step 1 dan berpindah ke Step 2 Data Pribadi.</t>
-        </is>
-      </c>
-      <c r="I111" s="49" t="n"/>
-      <c r="J111" s="49" t="n"/>
-      <c r="K111" s="49" t="n"/>
-      <c r="L111" s="49" t="n"/>
-      <c r="M111" s="49" t="n"/>
-      <c r="N111" s="49" t="n"/>
-      <c r="O111" s="49" t="n"/>
-      <c r="P111" s="49" t="n"/>
-      <c r="Q111" s="49" t="n"/>
-      <c r="R111" s="49" t="n"/>
-      <c r="S111" s="49" t="n"/>
-      <c r="T111" s="49" t="n"/>
-      <c r="U111" s="49" t="n"/>
-      <c r="V111" s="49" t="n"/>
-      <c r="W111" s="49" t="n"/>
-      <c r="X111" s="49" t="n"/>
-      <c r="Y111" s="49" t="n"/>
-      <c r="Z111" s="49" t="n"/>
-      <c r="AA111" s="49" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="B112" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C112" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D112" s="48" t="inlineStr">
-        <is>
-          <t>Mengisi form Step 1 (Informasi) tanpa field mandatory</t>
-        </is>
-      </c>
-      <c r="E112" s="46" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F112" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G112" s="48" t="inlineStr">
-        <is>
-          <t>1. Buka form Input Prospek Individu (Step 1 Informasi).
-2. Mengosongkan field Nama Lengkap dan No. Telepon.
-3. Klik button Next.</t>
-        </is>
-      </c>
-      <c r="H112" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan form Step 1 Informasi.
-2. Berhasil mengosongkan field mandatory.
-3. Menampilkan pesan validasi bahwa field Nama Lengkap dan No. Telepon wajib diisi.</t>
-        </is>
-      </c>
-      <c r="I112" s="49" t="n"/>
-      <c r="J112" s="49" t="n"/>
-      <c r="K112" s="49" t="n"/>
-      <c r="L112" s="49" t="n"/>
-      <c r="M112" s="49" t="n"/>
-      <c r="N112" s="49" t="n"/>
-      <c r="O112" s="49" t="n"/>
-      <c r="P112" s="49" t="n"/>
-      <c r="Q112" s="49" t="n"/>
-      <c r="R112" s="49" t="n"/>
-      <c r="S112" s="49" t="n"/>
-      <c r="T112" s="49" t="n"/>
-      <c r="U112" s="49" t="n"/>
-      <c r="V112" s="49" t="n"/>
-      <c r="W112" s="49" t="n"/>
-      <c r="X112" s="49" t="n"/>
-      <c r="Y112" s="49" t="n"/>
-      <c r="Z112" s="49" t="n"/>
-      <c r="AA112" s="49" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
-      <c r="B113" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C113" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D113" s="48" t="inlineStr">
-        <is>
-          <t>Melakukan Check CIF pada form Step 1</t>
-        </is>
-      </c>
-      <c r="E113" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F113" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G113" s="48" t="inlineStr">
-        <is>
-          <t>1. Buka form Input Prospek Individu (Step 1 Informasi).
-2. Isi field No KTP dengan nomor KTP valid.
-3. Klik button Check CIF.</t>
-        </is>
-      </c>
-      <c r="H113" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan form Step 1 Informasi.
-2. Berhasil mengisi field No KTP.
-3. Berhasil menampilkan hasil Check CIF berdasarkan No KTP.</t>
-        </is>
-      </c>
-      <c r="I113" s="49" t="n"/>
-      <c r="J113" s="49" t="n"/>
-      <c r="K113" s="49" t="n"/>
-      <c r="L113" s="49" t="n"/>
-      <c r="M113" s="49" t="n"/>
-      <c r="N113" s="49" t="n"/>
-      <c r="O113" s="49" t="n"/>
-      <c r="P113" s="49" t="n"/>
-      <c r="Q113" s="49" t="n"/>
-      <c r="R113" s="49" t="n"/>
-      <c r="S113" s="49" t="n"/>
-      <c r="T113" s="49" t="n"/>
-      <c r="U113" s="49" t="n"/>
-      <c r="V113" s="49" t="n"/>
-      <c r="W113" s="49" t="n"/>
-      <c r="X113" s="49" t="n"/>
-      <c r="Y113" s="49" t="n"/>
-      <c r="Z113" s="49" t="n"/>
-      <c r="AA113" s="49" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="B114" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C114" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D114" s="48" t="inlineStr">
-        <is>
-          <t>Mengisi form Step 2 (Data Pribadi) dengan data valid</t>
-        </is>
-      </c>
-      <c r="E114" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F114" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G114" s="48" t="inlineStr">
-        <is>
-          <t>1. Mengisi seluruh field pada Step 2 Data Pribadi dengan data valid.
-2. Klik button Next.</t>
-        </is>
-      </c>
-      <c r="H114" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi data pada Step 2 Data Pribadi.
-2. Berhasil menyimpan data Step 2 dan berpindah ke Step 3 Pekerjaan.</t>
-        </is>
-      </c>
-      <c r="I114" s="49" t="n"/>
-      <c r="J114" s="49" t="n"/>
-      <c r="K114" s="49" t="n"/>
-      <c r="L114" s="49" t="n"/>
-      <c r="M114" s="49" t="n"/>
-      <c r="N114" s="49" t="n"/>
-      <c r="O114" s="49" t="n"/>
-      <c r="P114" s="49" t="n"/>
-      <c r="Q114" s="49" t="n"/>
-      <c r="R114" s="49" t="n"/>
-      <c r="S114" s="49" t="n"/>
-      <c r="T114" s="49" t="n"/>
-      <c r="U114" s="49" t="n"/>
-      <c r="V114" s="49" t="n"/>
-      <c r="W114" s="49" t="n"/>
-      <c r="X114" s="49" t="n"/>
-      <c r="Y114" s="49" t="n"/>
-      <c r="Z114" s="49" t="n"/>
-      <c r="AA114" s="49" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="B115" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C115" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D115" s="48" t="inlineStr">
-        <is>
-          <t>Mengisi form Step 3 (Pekerjaan) dengan data valid</t>
-        </is>
-      </c>
-      <c r="E115" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F115" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G115" s="48" t="inlineStr">
-        <is>
-          <t>1. Mengisi seluruh field pada Step 3 Pekerjaan dengan data valid.
-2. Klik button Next.</t>
-        </is>
-      </c>
-      <c r="H115" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi data pada Step 3 Pekerjaan.
-2. Berhasil menyimpan data Step 3 dan berpindah ke Step 4 Prospek.</t>
-        </is>
-      </c>
-      <c r="I115" s="49" t="n"/>
-      <c r="J115" s="49" t="n"/>
-      <c r="K115" s="49" t="n"/>
-      <c r="L115" s="49" t="n"/>
-      <c r="M115" s="49" t="n"/>
-      <c r="N115" s="49" t="n"/>
-      <c r="O115" s="49" t="n"/>
-      <c r="P115" s="49" t="n"/>
-      <c r="Q115" s="49" t="n"/>
-      <c r="R115" s="49" t="n"/>
-      <c r="S115" s="49" t="n"/>
-      <c r="T115" s="49" t="n"/>
-      <c r="U115" s="49" t="n"/>
-      <c r="V115" s="49" t="n"/>
-      <c r="W115" s="49" t="n"/>
-      <c r="X115" s="49" t="n"/>
-      <c r="Y115" s="49" t="n"/>
-      <c r="Z115" s="49" t="n"/>
-      <c r="AA115" s="49" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="B116" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C116" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D116" s="48" t="inlineStr">
-        <is>
-          <t>Mengisi form Step 4 (Prospek) NTB dengan data valid</t>
-        </is>
-      </c>
-      <c r="E116" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F116" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G116" s="48" t="inlineStr">
-        <is>
-          <t>1. Mengisi seluruh field pada Step 4 Prospek dengan data valid.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H116" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi data pada Step 4 Prospek.
-2. Berhasil menyimpan data prospek Individu NTB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
-        </is>
-      </c>
-      <c r="I116" s="49" t="n"/>
-      <c r="J116" s="49" t="n"/>
-      <c r="K116" s="49" t="n"/>
-      <c r="L116" s="49" t="n"/>
-      <c r="M116" s="49" t="n"/>
-      <c r="N116" s="49" t="n"/>
-      <c r="O116" s="49" t="n"/>
-      <c r="P116" s="49" t="n"/>
-      <c r="Q116" s="49" t="n"/>
-      <c r="R116" s="49" t="n"/>
-      <c r="S116" s="49" t="n"/>
-      <c r="T116" s="49" t="n"/>
-      <c r="U116" s="49" t="n"/>
-      <c r="V116" s="49" t="n"/>
-      <c r="W116" s="49" t="n"/>
-      <c r="X116" s="49" t="n"/>
-      <c r="Y116" s="49" t="n"/>
-      <c r="Z116" s="49" t="n"/>
-      <c r="AA116" s="49" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B117" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C117" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D117" s="48" t="inlineStr">
-        <is>
-          <t>Mengisi form Step 4 (Prospek) ETB dengan mengubah status NTB</t>
-        </is>
-      </c>
-      <c r="E117" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F117" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G117" s="48" t="inlineStr">
-        <is>
-          <t>1. Aktifkan toggle Ubah NTB ke ETB.
-2. Isi field No CIF.
-3. Mengisi seluruh field pada Step 4 Prospek dengan data valid.
-4. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H117" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengaktifkan toggle NTB ke ETB.
-2. Berhasil mengisi No CIF.
-3. Berhasil mengisi data pada Step 4 Prospek.
-4. Berhasil menyimpan data prospek Individu ETB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
-        </is>
-      </c>
-      <c r="I117" s="49" t="n"/>
-      <c r="J117" s="49" t="n"/>
-      <c r="K117" s="49" t="n"/>
-      <c r="L117" s="49" t="n"/>
-      <c r="M117" s="49" t="n"/>
-      <c r="N117" s="49" t="n"/>
-      <c r="O117" s="49" t="n"/>
-      <c r="P117" s="49" t="n"/>
-      <c r="Q117" s="49" t="n"/>
-      <c r="R117" s="49" t="n"/>
-      <c r="S117" s="49" t="n"/>
-      <c r="T117" s="49" t="n"/>
-      <c r="U117" s="49" t="n"/>
-      <c r="V117" s="49" t="n"/>
-      <c r="W117" s="49" t="n"/>
-      <c r="X117" s="49" t="n"/>
-      <c r="Y117" s="49" t="n"/>
-      <c r="Z117" s="49" t="n"/>
-      <c r="AA117" s="49" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="B118" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C118" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D118" s="48" t="inlineStr">
-        <is>
-          <t>Mengisi form Step 4 (Prospek) tanpa field mandatory</t>
-        </is>
-      </c>
-      <c r="E118" s="46" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F118" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G118" s="48" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan seluruh field mandatory pada Step 4 Prospek.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H118" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field mandatory.
-2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
-        </is>
-      </c>
-      <c r="I118" s="49" t="n"/>
-      <c r="J118" s="49" t="n"/>
-      <c r="K118" s="49" t="n"/>
-      <c r="L118" s="49" t="n"/>
-      <c r="M118" s="49" t="n"/>
-      <c r="N118" s="49" t="n"/>
-      <c r="O118" s="49" t="n"/>
-      <c r="P118" s="49" t="n"/>
-      <c r="Q118" s="49" t="n"/>
-      <c r="R118" s="49" t="n"/>
-      <c r="S118" s="49" t="n"/>
-      <c r="T118" s="49" t="n"/>
-      <c r="U118" s="49" t="n"/>
-      <c r="V118" s="49" t="n"/>
-      <c r="W118" s="49" t="n"/>
-      <c r="X118" s="49" t="n"/>
-      <c r="Y118" s="49" t="n"/>
-      <c r="Z118" s="49" t="n"/>
-      <c r="AA118" s="49" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>11.12</t>
-        </is>
-      </c>
-      <c r="B119" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C119" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D119" s="48" t="inlineStr">
-        <is>
-          <t>Navigasi ke halaman Aktifitas dari layar konfirmasi Prospek Berhasil Dibuat</t>
-        </is>
-      </c>
-      <c r="E119" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F119" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G119" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik button Lihat Aktifitas.</t>
-        </is>
-      </c>
-      <c r="H119" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengarahkan pengguna ke halaman Lead Qualification Aktifitas.</t>
-        </is>
-      </c>
-      <c r="I119" s="49" t="n"/>
-      <c r="J119" s="49" t="n"/>
-      <c r="K119" s="49" t="n"/>
-      <c r="L119" s="49" t="n"/>
-      <c r="M119" s="49" t="n"/>
-      <c r="N119" s="49" t="n"/>
-      <c r="O119" s="49" t="n"/>
-      <c r="P119" s="49" t="n"/>
-      <c r="Q119" s="49" t="n"/>
-      <c r="R119" s="49" t="n"/>
-      <c r="S119" s="49" t="n"/>
-      <c r="T119" s="49" t="n"/>
-      <c r="U119" s="49" t="n"/>
-      <c r="V119" s="49" t="n"/>
-      <c r="W119" s="49" t="n"/>
-      <c r="X119" s="49" t="n"/>
-      <c r="Y119" s="49" t="n"/>
-      <c r="Z119" s="49" t="n"/>
-      <c r="AA119" s="49" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>11.13</t>
-        </is>
-      </c>
-      <c r="B120" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C120" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D120" s="48" t="inlineStr">
-        <is>
-          <t>Kembali ke halaman utama dari layar konfirmasi Prospek Berhasil Dibuat</t>
-        </is>
-      </c>
-      <c r="E120" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F120" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G120" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik button Kembali.</t>
-        </is>
-      </c>
-      <c r="H120" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengarahkan pengguna kembali ke halaman utama / form input.</t>
-        </is>
-      </c>
-      <c r="I120" s="49" t="n"/>
-      <c r="J120" s="49" t="n"/>
-      <c r="K120" s="49" t="n"/>
-      <c r="L120" s="49" t="n"/>
-      <c r="M120" s="49" t="n"/>
-      <c r="N120" s="49" t="n"/>
-      <c r="O120" s="49" t="n"/>
-      <c r="P120" s="49" t="n"/>
-      <c r="Q120" s="49" t="n"/>
-      <c r="R120" s="49" t="n"/>
-      <c r="S120" s="49" t="n"/>
-      <c r="T120" s="49" t="n"/>
-      <c r="U120" s="49" t="n"/>
-      <c r="V120" s="49" t="n"/>
-      <c r="W120" s="49" t="n"/>
-      <c r="X120" s="49" t="n"/>
-      <c r="Y120" s="49" t="n"/>
-      <c r="Z120" s="49" t="n"/>
-      <c r="AA120" s="49" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>11.14</t>
-        </is>
-      </c>
-      <c r="B121" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C121" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D121" s="48" t="inlineStr">
-        <is>
-          <t>Memilih tipe Prospek Lembaga</t>
-        </is>
-      </c>
-      <c r="E121" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F121" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G121" s="48" t="inlineStr">
-        <is>
-          <t>1. Buka halaman Input Prospek.
-2. Klik pilihan Lembaga.</t>
-        </is>
-      </c>
-      <c r="H121" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka halaman Input Prospek.
-2. Berhasil menampilkan form Step 1 Informasi Lembaga.</t>
-        </is>
-      </c>
-      <c r="I121" s="49" t="n"/>
-      <c r="J121" s="49" t="n"/>
-      <c r="K121" s="49" t="n"/>
-      <c r="L121" s="49" t="n"/>
-      <c r="M121" s="49" t="n"/>
-      <c r="N121" s="49" t="n"/>
-      <c r="O121" s="49" t="n"/>
-      <c r="P121" s="49" t="n"/>
-      <c r="Q121" s="49" t="n"/>
-      <c r="R121" s="49" t="n"/>
-      <c r="S121" s="49" t="n"/>
-      <c r="T121" s="49" t="n"/>
-      <c r="U121" s="49" t="n"/>
-      <c r="V121" s="49" t="n"/>
-      <c r="W121" s="49" t="n"/>
-      <c r="X121" s="49" t="n"/>
-      <c r="Y121" s="49" t="n"/>
-      <c r="Z121" s="49" t="n"/>
-      <c r="AA121" s="49" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>11.15</t>
-        </is>
-      </c>
-      <c r="B122" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C122" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D122" s="48" t="inlineStr">
-        <is>
-          <t>Mengisi form Step 1 (Informasi Lembaga) dengan data valid</t>
-        </is>
-      </c>
-      <c r="E122" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F122" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G122" s="48" t="inlineStr">
-        <is>
-          <t>1. Buka form Input Prospek Lembaga (Step 1 Informasi Lembaga).
-2. Mengisi field NPWP dengan NPWP valid.
-3. Klik button Next.</t>
-        </is>
-      </c>
-      <c r="H122" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan form Step 1 Informasi Lembaga.
-2. Berhasil mengisi field NPWP.
-3. Berhasil menyimpan data Step 1 dan berpindah ke Step 2 Data Lembaga.</t>
-        </is>
-      </c>
-      <c r="I122" s="49" t="n"/>
-      <c r="J122" s="49" t="n"/>
-      <c r="K122" s="49" t="n"/>
-      <c r="L122" s="49" t="n"/>
-      <c r="M122" s="49" t="n"/>
-      <c r="N122" s="49" t="n"/>
-      <c r="O122" s="49" t="n"/>
-      <c r="P122" s="49" t="n"/>
-      <c r="Q122" s="49" t="n"/>
-      <c r="R122" s="49" t="n"/>
-      <c r="S122" s="49" t="n"/>
-      <c r="T122" s="49" t="n"/>
-      <c r="U122" s="49" t="n"/>
-      <c r="V122" s="49" t="n"/>
-      <c r="W122" s="49" t="n"/>
-      <c r="X122" s="49" t="n"/>
-      <c r="Y122" s="49" t="n"/>
-      <c r="Z122" s="49" t="n"/>
-      <c r="AA122" s="49" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>11.16</t>
-        </is>
-      </c>
-      <c r="B123" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C123" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D123" s="48" t="inlineStr">
-        <is>
-          <t>Mengisi form Step 2 (Data Lembaga) dengan data valid</t>
-        </is>
-      </c>
-      <c r="E123" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F123" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G123" s="48" t="inlineStr">
-        <is>
-          <t>1. Mengisi seluruh field pada Step 2 Data Lembaga dengan data valid.
-2. Klik button Next.</t>
-        </is>
-      </c>
-      <c r="H123" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi data pada Step 2 Data Lembaga.
-2. Berhasil menyimpan data Step 2 dan berpindah ke Step 3 Prospek.</t>
-        </is>
-      </c>
-      <c r="I123" s="49" t="n"/>
-      <c r="J123" s="49" t="n"/>
-      <c r="K123" s="49" t="n"/>
-      <c r="L123" s="49" t="n"/>
-      <c r="M123" s="49" t="n"/>
-      <c r="N123" s="49" t="n"/>
-      <c r="O123" s="49" t="n"/>
-      <c r="P123" s="49" t="n"/>
-      <c r="Q123" s="49" t="n"/>
-      <c r="R123" s="49" t="n"/>
-      <c r="S123" s="49" t="n"/>
-      <c r="T123" s="49" t="n"/>
-      <c r="U123" s="49" t="n"/>
-      <c r="V123" s="49" t="n"/>
-      <c r="W123" s="49" t="n"/>
-      <c r="X123" s="49" t="n"/>
-      <c r="Y123" s="49" t="n"/>
-      <c r="Z123" s="49" t="n"/>
-      <c r="AA123" s="49" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>11.17</t>
-        </is>
-      </c>
-      <c r="B124" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C124" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D124" s="48" t="inlineStr">
-        <is>
-          <t>Mengisi form Step 2 (Data Lembaga) tanpa field mandatory</t>
-        </is>
-      </c>
-      <c r="E124" s="46" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F124" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G124" s="48" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field Nama Perusahaan dan Telepon Perusahaan.
-2. Klik button Next.</t>
-        </is>
-      </c>
-      <c r="H124" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field mandatory.
-2. Menampilkan pesan validasi bahwa field Nama Perusahaan dan Telepon Perusahaan wajib diisi.</t>
-        </is>
-      </c>
-      <c r="I124" s="49" t="n"/>
-      <c r="J124" s="49" t="n"/>
-      <c r="K124" s="49" t="n"/>
-      <c r="L124" s="49" t="n"/>
-      <c r="M124" s="49" t="n"/>
-      <c r="N124" s="49" t="n"/>
-      <c r="O124" s="49" t="n"/>
-      <c r="P124" s="49" t="n"/>
-      <c r="Q124" s="49" t="n"/>
-      <c r="R124" s="49" t="n"/>
-      <c r="S124" s="49" t="n"/>
-      <c r="T124" s="49" t="n"/>
-      <c r="U124" s="49" t="n"/>
-      <c r="V124" s="49" t="n"/>
-      <c r="W124" s="49" t="n"/>
-      <c r="X124" s="49" t="n"/>
-      <c r="Y124" s="49" t="n"/>
-      <c r="Z124" s="49" t="n"/>
-      <c r="AA124" s="49" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>11.18</t>
-        </is>
-      </c>
-      <c r="B125" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C125" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D125" s="48" t="inlineStr">
-        <is>
-          <t>Mengisi form Step 3 (Prospek Lembaga) NTB dengan data valid</t>
-        </is>
-      </c>
-      <c r="E125" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F125" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G125" s="48" t="inlineStr">
-        <is>
-          <t>1. Mengisi seluruh field pada Step 3 Prospek Lembaga dengan data valid.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H125" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi data pada Step 3 Prospek Lembaga.
-2. Berhasil menyimpan data prospek Lembaga NTB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
-        </is>
-      </c>
-      <c r="I125" s="49" t="n"/>
-      <c r="J125" s="49" t="n"/>
-      <c r="K125" s="49" t="n"/>
-      <c r="L125" s="49" t="n"/>
-      <c r="M125" s="49" t="n"/>
-      <c r="N125" s="49" t="n"/>
-      <c r="O125" s="49" t="n"/>
-      <c r="P125" s="49" t="n"/>
-      <c r="Q125" s="49" t="n"/>
-      <c r="R125" s="49" t="n"/>
-      <c r="S125" s="49" t="n"/>
-      <c r="T125" s="49" t="n"/>
-      <c r="U125" s="49" t="n"/>
-      <c r="V125" s="49" t="n"/>
-      <c r="W125" s="49" t="n"/>
-      <c r="X125" s="49" t="n"/>
-      <c r="Y125" s="49" t="n"/>
-      <c r="Z125" s="49" t="n"/>
-      <c r="AA125" s="49" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>11.19</t>
-        </is>
-      </c>
-      <c r="B126" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C126" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D126" s="48" t="inlineStr">
-        <is>
-          <t>Mengisi form Step 3 (Prospek Lembaga) ETB dengan mengubah status NTB</t>
-        </is>
-      </c>
-      <c r="E126" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F126" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G126" s="48" t="inlineStr">
-        <is>
-          <t>1. Aktifkan toggle Ubah NTB ke ETB.
-2. Isi field No CIF.
-3. Mengisi seluruh field pada Step 3 Prospek Lembaga dengan data valid.
-4. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H126" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengaktifkan toggle NTB ke ETB.
-2. Berhasil mengisi No CIF.
-3. Berhasil mengisi data pada Step 3 Prospek Lembaga.
-4. Berhasil menyimpan data prospek Lembaga ETB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
-        </is>
-      </c>
-      <c r="I126" s="49" t="n"/>
-      <c r="J126" s="49" t="n"/>
-      <c r="K126" s="49" t="n"/>
-      <c r="L126" s="49" t="n"/>
-      <c r="M126" s="49" t="n"/>
-      <c r="N126" s="49" t="n"/>
-      <c r="O126" s="49" t="n"/>
-      <c r="P126" s="49" t="n"/>
-      <c r="Q126" s="49" t="n"/>
-      <c r="R126" s="49" t="n"/>
-      <c r="S126" s="49" t="n"/>
-      <c r="T126" s="49" t="n"/>
-      <c r="U126" s="49" t="n"/>
-      <c r="V126" s="49" t="n"/>
-      <c r="W126" s="49" t="n"/>
-      <c r="X126" s="49" t="n"/>
-      <c r="Y126" s="49" t="n"/>
-      <c r="Z126" s="49" t="n"/>
-      <c r="AA126" s="49" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>11.20</t>
-        </is>
-      </c>
-      <c r="B127" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C127" s="46" t="inlineStr">
-        <is>
-          <t>Input Prospek</t>
-        </is>
-      </c>
-      <c r="D127" s="48" t="inlineStr">
-        <is>
-          <t>Mengisi form Step 3 (Prospek Lembaga) tanpa field mandatory</t>
-        </is>
-      </c>
-      <c r="E127" s="46" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F127" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G127" s="48" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan seluruh field mandatory pada Step 3 Prospek Lembaga.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H127" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field mandatory.
-2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
-        </is>
-      </c>
-      <c r="I127" s="49" t="n"/>
-      <c r="J127" s="49" t="n"/>
-      <c r="K127" s="49" t="n"/>
-      <c r="L127" s="49" t="n"/>
-      <c r="M127" s="49" t="n"/>
-      <c r="N127" s="49" t="n"/>
-      <c r="O127" s="49" t="n"/>
-      <c r="P127" s="49" t="n"/>
-      <c r="Q127" s="49" t="n"/>
-      <c r="R127" s="49" t="n"/>
-      <c r="S127" s="49" t="n"/>
-      <c r="T127" s="49" t="n"/>
-      <c r="U127" s="49" t="n"/>
-      <c r="V127" s="49" t="n"/>
-      <c r="W127" s="49" t="n"/>
-      <c r="X127" s="49" t="n"/>
-      <c r="Y127" s="49" t="n"/>
-      <c r="Z127" s="49" t="n"/>
-      <c r="AA127" s="49" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="B128" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C128" s="46" t="inlineStr">
-        <is>
-          <t>List Nasabah ETB</t>
-        </is>
-      </c>
-      <c r="D128" s="48" t="inlineStr">
-        <is>
-          <t>Membuka halaman List Nasabah ETB</t>
-        </is>
-      </c>
-      <c r="E128" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F128" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G128" s="48" t="inlineStr">
-        <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu List Nasabah ETB.</t>
-        </is>
-      </c>
-      <c r="H128" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman List Nasabah ETB.</t>
-        </is>
-      </c>
-      <c r="I128" s="49" t="n"/>
-      <c r="J128" s="49" t="n"/>
-      <c r="K128" s="49" t="n"/>
-      <c r="L128" s="49" t="n"/>
-      <c r="M128" s="49" t="n"/>
-      <c r="N128" s="49" t="n"/>
-      <c r="O128" s="49" t="n"/>
-      <c r="P128" s="49" t="n"/>
-      <c r="Q128" s="49" t="n"/>
-      <c r="R128" s="49" t="n"/>
-      <c r="S128" s="49" t="n"/>
-      <c r="T128" s="49" t="n"/>
-      <c r="U128" s="49" t="n"/>
-      <c r="V128" s="49" t="n"/>
-      <c r="W128" s="49" t="n"/>
-      <c r="X128" s="49" t="n"/>
-      <c r="Y128" s="49" t="n"/>
-      <c r="Z128" s="49" t="n"/>
-      <c r="AA128" s="49" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="B129" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C129" s="46" t="inlineStr">
-        <is>
-          <t>List Nasabah ETB</t>
-        </is>
-      </c>
-      <c r="D129" s="48" t="inlineStr">
-        <is>
-          <t>Mencari nasabah menggunakan Search Bar</t>
-        </is>
-      </c>
-      <c r="E129" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F129" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G129" s="48" t="inlineStr">
-        <is>
-          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
-        </is>
-      </c>
-      <c r="H129" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data nasabah yang sesuai dengan kata kunci pencarian.</t>
-        </is>
-      </c>
-      <c r="I129" s="49" t="n"/>
-      <c r="J129" s="49" t="n"/>
-      <c r="K129" s="49" t="n"/>
-      <c r="L129" s="49" t="n"/>
-      <c r="M129" s="49" t="n"/>
-      <c r="N129" s="49" t="n"/>
-      <c r="O129" s="49" t="n"/>
-      <c r="P129" s="49" t="n"/>
-      <c r="Q129" s="49" t="n"/>
-      <c r="R129" s="49" t="n"/>
-      <c r="S129" s="49" t="n"/>
-      <c r="T129" s="49" t="n"/>
-      <c r="U129" s="49" t="n"/>
-      <c r="V129" s="49" t="n"/>
-      <c r="W129" s="49" t="n"/>
-      <c r="X129" s="49" t="n"/>
-      <c r="Y129" s="49" t="n"/>
-      <c r="Z129" s="49" t="n"/>
-      <c r="AA129" s="49" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="B130" s="46" t="inlineStr">
-        <is>
-          <t>Prospek &amp; Nasabah</t>
-        </is>
-      </c>
-      <c r="C130" s="46" t="inlineStr">
-        <is>
-          <t>List Nasabah ETB</t>
-        </is>
-      </c>
-      <c r="D130" s="48" t="inlineStr">
-        <is>
-          <t>Mencari nasabah dengan keyword tidak valid</t>
-        </is>
-      </c>
-      <c r="E130" s="46" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F130" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G130" s="48" t="inlineStr">
-        <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
-        </is>
-      </c>
-      <c r="H130" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
       <c r="I130" s="49" t="n"/>
@@ -56662,7 +55758,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="B131" s="46" t="inlineStr">
@@ -56672,12 +55768,12 @@
       </c>
       <c r="C131" s="46" t="inlineStr">
         <is>
-          <t>List Nasabah ETB</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D131" s="48" t="inlineStr">
         <is>
-          <t>Melakukan filter data nasabah</t>
+          <t>Mencari prospek menggunakan Search Bar</t>
         </is>
       </c>
       <c r="E131" s="46" t="inlineStr">
@@ -56692,16 +55788,12 @@
       </c>
       <c r="G131" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Filter di halaman List Nasabah ETB.
-2. Pilih kriteria filter pada form Filter.
-3. Klik button Simpan.</t>
+          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
         </is>
       </c>
       <c r="H131" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka form Filter.
-2. Berhasil memilih kriteria filter.
-3. Berhasil menampilkan daftar nasabah yang sesuai dengan kriteria filter.</t>
+          <t>1. Berhasil menampilkan data prospek yang sesuai dengan kata kunci pencarian.</t>
         </is>
       </c>
       <c r="I131" s="49" t="n"/>
@@ -56727,7 +55819,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="B132" s="46" t="inlineStr">
@@ -56737,34 +55829,32 @@
       </c>
       <c r="C132" s="46" t="inlineStr">
         <is>
-          <t>List Nasabah ETB</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D132" s="48" t="inlineStr">
         <is>
-          <t>Melihat Detail Prospek Nasabah ETB</t>
+          <t>Mencari prospek dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E132" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F132" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G132" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu titik tiga pada salah satu card nasabah.
-2. Pilih Detail Prospek.</t>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
         </is>
       </c>
       <c r="H132" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan menu Lainnya.
-2. Berhasil membuka halaman Detail Prospek dan menampilkan informasi nasabah secara lengkap.</t>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
       <c r="I132" s="49" t="n"/>
@@ -56790,7 +55880,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="B133" s="46" t="inlineStr">
@@ -56800,12 +55890,12 @@
       </c>
       <c r="C133" s="46" t="inlineStr">
         <is>
-          <t>List Nasabah ETB</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D133" s="48" t="inlineStr">
         <is>
-          <t>Membuka form Prospek Ulang</t>
+          <t>Melakukan filter data prospek</t>
         </is>
       </c>
       <c r="E133" s="46" t="inlineStr">
@@ -56815,19 +55905,21 @@
       </c>
       <c r="F133" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G133" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu titik tiga pada salah satu card nasabah.
-2. Pilih Prospek Ulang.</t>
+          <t>1. Klik button Filter di halaman Aktifitas Prospek.
+2. Pilih kriteria filter pada form Filter.
+3. Klik button Simpan.</t>
         </is>
       </c>
       <c r="H133" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan menu Lainnya.
-2. Berhasil membuka form Prospek Ulang.</t>
+          <t>1. Berhasil membuka form Filter.
+2. Berhasil memilih kriteria filter.
+3. Berhasil menampilkan daftar prospek yang sesuai dengan kriteria filter.</t>
         </is>
       </c>
       <c r="I133" s="49" t="n"/>
@@ -56853,7 +55945,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="B134" s="46" t="inlineStr">
@@ -56863,12 +55955,12 @@
       </c>
       <c r="C134" s="46" t="inlineStr">
         <is>
-          <t>List Nasabah ETB</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D134" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Prospek Ulang dengan data valid</t>
+          <t>Melihat Detail Prospek</t>
         </is>
       </c>
       <c r="E134" s="46" t="inlineStr">
@@ -56883,14 +55975,14 @@
       </c>
       <c r="G134" s="48" t="inlineStr">
         <is>
-          <t>1. Mengisi seluruh field pada form Prospek Ulang dengan data valid.
-2. Klik button Submit.</t>
+          <t>1. Klik menu titik tiga pada salah satu card prospek.
+2. Pilih Detail Prospek.</t>
         </is>
       </c>
       <c r="H134" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengisi data pada form Prospek Ulang.
-2. Berhasil men-submit form dan memperbarui data prospek.</t>
+          <t>1. Berhasil menampilkan menu pilihan.
+2. Berhasil menampilkan detail data prospek.</t>
         </is>
       </c>
       <c r="I134" s="49" t="n"/>
@@ -56916,7 +56008,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="B135" s="46" t="inlineStr">
@@ -56926,34 +56018,34 @@
       </c>
       <c r="C135" s="46" t="inlineStr">
         <is>
-          <t>List Nasabah ETB</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D135" s="48" t="inlineStr">
         <is>
-          <t>Melakukan Prospek Ulang tanpa field mandatory</t>
+          <t>Melihat Riwayat Prospek</t>
         </is>
       </c>
       <c r="E135" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F135" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G135" s="48" t="inlineStr">
         <is>
-          <t>1. Mengosongkan seluruh field mandatory pada form Prospek Ulang.
-2. Klik button Submit.</t>
+          <t>1. Klik menu titik tiga pada salah satu card prospek.
+2. Pilih Riwayat.</t>
         </is>
       </c>
       <c r="H135" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengosongkan field mandatory.
-2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
+          <t>1. Berhasil menampilkan menu pilihan.
+2. Berhasil membuka halaman Riwayat dan menampilkan daftar log riwayat.</t>
         </is>
       </c>
       <c r="I135" s="49" t="n"/>
@@ -56979,7 +56071,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="B136" s="46" t="inlineStr">
@@ -56989,12 +56081,12 @@
       </c>
       <c r="C136" s="46" t="inlineStr">
         <is>
-          <t>List Nasabah ETB</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D136" s="48" t="inlineStr">
         <is>
-          <t>Melihat Informasi Rekening</t>
+          <t>Mencari data pada halaman Riwayat</t>
         </is>
       </c>
       <c r="E136" s="46" t="inlineStr">
@@ -57004,19 +56096,17 @@
       </c>
       <c r="F136" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G136" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu titik tiga pada salah satu card nasabah.
-2. Pilih Informasi Rekening.</t>
+          <t>1. Masukkan kata kunci pada Search Bar global.</t>
         </is>
       </c>
       <c r="H136" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan menu Lainnya.
-2. Berhasil menampilkan detail rekening nasabah (nomor rekening dan saldo).</t>
+          <t>1. Berhasil memfilter data riwayat sesuai kata kunci pencarian.</t>
         </is>
       </c>
       <c r="I136" s="49" t="n"/>
@@ -57042,7 +56132,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="B137" s="46" t="inlineStr">
@@ -57052,36 +56142,32 @@
       </c>
       <c r="C137" s="46" t="inlineStr">
         <is>
-          <t>List Nasabah ETB</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D137" s="48" t="inlineStr">
         <is>
-          <t>Menghapus data nasabah</t>
+          <t>Mencari data dengan keyword tidak valid pada halaman Riwayat</t>
         </is>
       </c>
       <c r="E137" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F137" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G137" s="48" t="inlineStr">
         <is>
-          <t>1. Klik menu titik tiga pada salah satu card nasabah.
-2. Pilih Hapus.
-3. Klik button Ya pada pop-up konfirmasi.</t>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
         </is>
       </c>
       <c r="H137" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan menu Lainnya.
-2. Berhasil menampilkan pop-up konfirmasi hapus data.
-3. Berhasil menghapus data nasabah dari daftar List Nasabah ETB.</t>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
       <c r="I137" s="49" t="n"/>
@@ -57107,7 +56193,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="B138" s="46" t="inlineStr">
@@ -57117,12 +56203,12 @@
       </c>
       <c r="C138" s="46" t="inlineStr">
         <is>
-          <t>Nasabah Referal</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D138" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Nasabah Referal</t>
+          <t>Membuka form Input Aktifitas</t>
         </is>
       </c>
       <c r="E138" s="46" t="inlineStr">
@@ -57137,14 +56223,12 @@
       </c>
       <c r="G138" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Nasabah Referal.</t>
+          <t>1. Klik button Aktifitas pada prospek yang berstatus aktif (belum closing).</t>
         </is>
       </c>
       <c r="H138" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Nasabah Referal.</t>
+          <t>1. Berhasil membuka halaman Aktifitas Marketing dan menampilkan tab Prospek, Call, Visit, dan NOA Open Account.</t>
         </is>
       </c>
       <c r="I138" s="49" t="n"/>
@@ -57170,7 +56254,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>11.10</t>
         </is>
       </c>
       <c r="B139" s="46" t="inlineStr">
@@ -57180,12 +56264,12 @@
       </c>
       <c r="C139" s="46" t="inlineStr">
         <is>
-          <t>Nasabah Referal</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D139" s="48" t="inlineStr">
         <is>
-          <t>Mencari nasabah referal menggunakan Search Bar</t>
+          <t>Membuka tab Prospek pada halaman Aktifitas Marketing</t>
         </is>
       </c>
       <c r="E139" s="46" t="inlineStr">
@@ -57195,17 +56279,17 @@
       </c>
       <c r="F139" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G139" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
+          <t>1. Klik tab Prospek.</t>
         </is>
       </c>
       <c r="H139" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data nasabah referal yang sesuai dengan kata kunci pencarian.</t>
+          <t>1. Berhasil berpindah ke tab Prospek dan menampilkan form informasi prospek.</t>
         </is>
       </c>
       <c r="I139" s="49" t="n"/>
@@ -57231,7 +56315,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="B140" s="46" t="inlineStr">
@@ -57241,17 +56325,17 @@
       </c>
       <c r="C140" s="46" t="inlineStr">
         <is>
-          <t>Nasabah Referal</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D140" s="48" t="inlineStr">
         <is>
-          <t>Mencari nasabah referal dengan keyword tidak valid</t>
+          <t>Mengedit data pada tab Prospek</t>
         </is>
       </c>
       <c r="E140" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F140" s="46" t="inlineStr">
@@ -57261,12 +56345,16 @@
       </c>
       <c r="G140" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+          <t>1. Ubah data pada form informasi prospek.
+2. Klik button Edit.
+3. Klik button Next.</t>
         </is>
       </c>
       <c r="H140" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+          <t>1. Berhasil mengubah data pada form.
+2. Berhasil mengaktifkan mode edit form.
+3. Berhasil menyimpan perubahan dan melanjutkan ke tahap berikutnya.</t>
         </is>
       </c>
       <c r="I140" s="49" t="n"/>
@@ -57292,7 +56380,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="B141" s="46" t="inlineStr">
@@ -57302,12 +56390,12 @@
       </c>
       <c r="C141" s="46" t="inlineStr">
         <is>
-          <t>Nasabah Referal</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D141" s="48" t="inlineStr">
         <is>
-          <t>Melihat Detail Prospek nasabah referal</t>
+          <t>Membuka tab Call pada halaman Aktifitas Marketing</t>
         </is>
       </c>
       <c r="E141" s="46" t="inlineStr">
@@ -57317,17 +56405,17 @@
       </c>
       <c r="F141" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G141" s="48" t="inlineStr">
         <is>
-          <t>1. Klik salah satu card nasabah referal.</t>
+          <t>1. Klik tab Call.</t>
         </is>
       </c>
       <c r="H141" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail nasabah referal.</t>
+          <t>1. Berhasil berpindah ke tab Call dan menampilkan form input Call serta Log Staging Call.</t>
         </is>
       </c>
       <c r="I141" s="49" t="n"/>
@@ -57353,22 +56441,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>11.13</t>
         </is>
       </c>
       <c r="B142" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C142" s="46" t="inlineStr">
         <is>
-          <t>Pengingat</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D142" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Pengingat</t>
+          <t>Melakukan panggilan langsung melalui tombol Call</t>
         </is>
       </c>
       <c r="E142" s="46" t="inlineStr">
@@ -57378,19 +56466,17 @@
       </c>
       <c r="F142" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G142" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Pengingat.</t>
+          <t>1. Klik button Call di samping nomor handphone.</t>
         </is>
       </c>
       <c r="H142" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Pengingat.</t>
+          <t>1. Berhasil mengarahkan ke aplikasi telepon bawaan perangkat (dialer).</t>
         </is>
       </c>
       <c r="I142" s="49" t="n"/>
@@ -57416,22 +56502,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>11.14</t>
         </is>
       </c>
       <c r="B143" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C143" s="46" t="inlineStr">
         <is>
-          <t>Pengingat</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D143" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar pengingat pada tab Aktif</t>
+          <t>Menyimpan log Call dengan data valid</t>
         </is>
       </c>
       <c r="E143" s="46" t="inlineStr">
@@ -57441,17 +56527,19 @@
       </c>
       <c r="F143" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G143" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Aktif.</t>
+          <t>1. Isi field Status Call dan Keterangan dengan data valid.
+2. Klik button Simpan.</t>
         </is>
       </c>
       <c r="H143" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar pengingat yang sedang aktif.</t>
+          <t>1. Berhasil mengisi field Status Call dan Keterangan.
+2. Berhasil menyimpan aktifitas Call dan menambahkannya ke Log Staging Call.</t>
         </is>
       </c>
       <c r="I143" s="49" t="n"/>
@@ -57477,27 +56565,27 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="B144" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C144" s="46" t="inlineStr">
         <is>
-          <t>Pengingat</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D144" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar pengingat pada tab Selesai</t>
+          <t>Menyimpan log Call tanpa field mandatory</t>
         </is>
       </c>
       <c r="E144" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F144" s="46" t="inlineStr">
@@ -57507,12 +56595,14 @@
       </c>
       <c r="G144" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Selesai.</t>
+          <t>1. Mengosongkan field Status Call dan Keterangan.
+2. Klik button Simpan.</t>
         </is>
       </c>
       <c r="H144" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar pengingat yang sudah selesai.</t>
+          <t>1. Berhasil mengosongkan field mandatory.
+2. Menampilkan pesan validasi bahwa field Status Call dan Keterangan wajib diisi.</t>
         </is>
       </c>
       <c r="I144" s="49" t="n"/>
@@ -57538,22 +56628,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>11.16</t>
         </is>
       </c>
       <c r="B145" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C145" s="46" t="inlineStr">
         <is>
-          <t>Pengingat</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D145" s="48" t="inlineStr">
         <is>
-          <t>Menambahkan pengingat baru dengan data valid</t>
+          <t>Membuka tab Visit pada halaman Aktifitas Marketing</t>
         </is>
       </c>
       <c r="E145" s="46" t="inlineStr">
@@ -57563,21 +56653,17 @@
       </c>
       <c r="F145" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G145" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button + Baru.
-2. Mengisi seluruh field mandatory pada form Tambah Pengingat dengan data valid.
-3. Klik button Simpan.</t>
+          <t>1. Klik tab Visit.</t>
         </is>
       </c>
       <c r="H145" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka form Tambah Pengingat.
-2. Berhasil mengisi seluruh field mandatory pada form Tambah Pengingat.
-3. Berhasil menyimpan pengingat dan menampilkan pengingat baru pada daftar.</t>
+          <t>1. Berhasil berpindah ke tab Visit dan menampilkan button Visit In serta Log Staging Visit.</t>
         </is>
       </c>
       <c r="I145" s="49" t="n"/>
@@ -57603,46 +56689,42 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="B146" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C146" s="46" t="inlineStr">
         <is>
-          <t>Pengingat</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D146" s="48" t="inlineStr">
         <is>
-          <t>Menambahkan pengingat baru tanpa mengisi field mandatory</t>
+          <t>Melakukan Visit In</t>
         </is>
       </c>
       <c r="E146" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F146" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G146" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button + Baru.
-2. Mengosongkan seluruh field mandatory pada form Tambah Pengingat.
-3. Klik button Simpan.</t>
+          <t>1. Klik button Visit In.</t>
         </is>
       </c>
       <c r="H146" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka form Tambah Pengingat.
-2. Field mandatory berhasil dikosongkan.
-3. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+          <t>1. Berhasil mengarahkan ke halaman Kunjungan dan menampilkan pop up pilihan tipe Visit.</t>
         </is>
       </c>
       <c r="I146" s="49" t="n"/>
@@ -57668,22 +56750,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="B147" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C147" s="46" t="inlineStr">
         <is>
-          <t>Pengingat</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D147" s="48" t="inlineStr">
         <is>
-          <t>Menandai pengingat sebagai selesai</t>
+          <t>Membuka tab NOA Open Account pada halaman Aktifitas Marketing</t>
         </is>
       </c>
       <c r="E147" s="46" t="inlineStr">
@@ -57693,19 +56775,17 @@
       </c>
       <c r="F147" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G147" s="48" t="inlineStr">
         <is>
-          <t>1. Centang checkbox pada salah satu card pengingat aktif.
-2. Klik button Ya pada pop-up konfirmasi.</t>
+          <t>1. Klik tab NOA Open Account.</t>
         </is>
       </c>
       <c r="H147" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan pop-up konfirmasi selesai.
-2. Berhasil menandai pengingat sebagai selesai dan memindahkan pengingat ke tab Selesai.</t>
+          <t>1. Berhasil berpindah ke tab NOA Open Account dan menampilkan form NOA Open Account.</t>
         </is>
       </c>
       <c r="I147" s="49" t="n"/>
@@ -57731,22 +56811,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="B148" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C148" s="46" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D148" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Daily Sales Agenda</t>
+          <t>Melakukan Submit NOA Open Account dengan data valid</t>
         </is>
       </c>
       <c r="E148" s="46" t="inlineStr">
@@ -57761,14 +56841,14 @@
       </c>
       <c r="G148" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Daily Sales Agenda.</t>
+          <t>1. Mengisi seluruh field pada form NOA Open Account dengan data valid.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H148" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
+          <t>1. Berhasil mengisi data pada form NOA Open Account.
+2. Berhasil men-submit form dan menyimpan data Open Account.</t>
         </is>
       </c>
       <c r="I148" s="49" t="n"/>
@@ -57794,27 +56874,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="B149" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C149" s="46" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D149" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar agenda pada tab Masuk</t>
+          <t>Melakukan Submit NOA Open Account tanpa field mandatory</t>
         </is>
       </c>
       <c r="E149" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F149" s="46" t="inlineStr">
@@ -57824,12 +56904,14 @@
       </c>
       <c r="G149" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Masuk.</t>
+          <t>1. Mengosongkan seluruh field mandatory pada form NOA Open Account.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H149" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar nasabah yang masuk pada Daily Sales Agenda.</t>
+          <t>1. Berhasil mengosongkan field mandatory.
+2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
         </is>
       </c>
       <c r="I149" s="49" t="n"/>
@@ -57855,22 +56937,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="B150" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C150" s="46" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Aktifitas Prospek</t>
         </is>
       </c>
       <c r="D150" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar agenda pada tab Closing</t>
+          <t>Membatalkan prospek melalui menu titik tiga</t>
         </is>
       </c>
       <c r="E150" s="46" t="inlineStr">
@@ -57880,17 +56962,21 @@
       </c>
       <c r="F150" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G150" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Closing.</t>
+          <t>1. Klik menu titik tiga pada pojok kanan atas.
+2. Pilih Batalkan Prospek.
+3. Klik button Batalkan pada pop-up konfirmasi.</t>
         </is>
       </c>
       <c r="H150" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar nasabah yang closing pada Daily Sales Agenda.</t>
+          <t>1. Berhasil membuka menu dropdown.
+2. Berhasil menampilkan pop-up konfirmasi pembatalan.
+3. Berhasil membatalkan prospek dan prospek tidak dapat dilanjutkan kembali.</t>
         </is>
       </c>
       <c r="I150" s="49" t="n"/>
@@ -57916,22 +57002,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B151" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C151" s="46" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D151" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar agenda pada tab Referral</t>
+          <t>Membuka halaman Input Prospek melalui navigation bar bawah</t>
         </is>
       </c>
       <c r="E151" s="46" t="inlineStr">
@@ -57941,17 +57027,17 @@
       </c>
       <c r="F151" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G151" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Referral.</t>
+          <t>1. Klik menu Input pada navigation bar bawah.</t>
         </is>
       </c>
       <c r="H151" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar nasabah referral pada Daily Sales Agenda.</t>
+          <t>1. Berhasil membuka halaman Input Prospek dan menampilkan pop up tipe prospek.</t>
         </is>
       </c>
       <c r="I151" s="49" t="n"/>
@@ -57977,22 +57063,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="B152" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C152" s="46" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D152" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar agenda pada tab Ref. Closing</t>
+          <t>Membuka halaman Input Prospek melalui menu Lainnya</t>
         </is>
       </c>
       <c r="E152" s="46" t="inlineStr">
@@ -58002,17 +57088,19 @@
       </c>
       <c r="F152" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G152" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Ref. Closing.</t>
+          <t>1. Klik menu Lainnya pada navigation bar bawah.
+2. Klik menu Input Prospek.</t>
         </is>
       </c>
       <c r="H152" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar nasabah referral yang closing pada Daily Sales Agenda.</t>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil membuka halaman Input Prospek dan menampilkan pop up tipe prospek.</t>
         </is>
       </c>
       <c r="I152" s="49" t="n"/>
@@ -58038,22 +57126,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="B153" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C153" s="46" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D153" s="48" t="inlineStr">
         <is>
-          <t>Mencari agenda menggunakan Search Bar</t>
+          <t>Memilih tipe Prospek Individu</t>
         </is>
       </c>
       <c r="E153" s="46" t="inlineStr">
@@ -58068,12 +57156,14 @@
       </c>
       <c r="G153" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
+          <t>1. Buka halaman Input Prospek.
+2. Klik pilihan Individu.</t>
         </is>
       </c>
       <c r="H153" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data agenda yang sesuai dengan kata kunci pencarian.</t>
+          <t>1. Berhasil membuka halaman Input Prospek.
+2. Berhasil menampilkan form Step 1 Informasi.</t>
         </is>
       </c>
       <c r="I153" s="49" t="n"/>
@@ -58099,42 +57189,46 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="B154" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C154" s="46" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D154" s="48" t="inlineStr">
         <is>
-          <t>Mencari agenda dengan keyword tidak valid</t>
+          <t>Mengisi form Step 1 (Informasi) dengan data valid</t>
         </is>
       </c>
       <c r="E154" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F154" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G154" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+          <t>1. Buka form Input Prospek Individu (Step 1 Informasi).
+2. Mengisi seluruh field pada Step 1 Informasi dengan data valid.
+3. Klik button Next.</t>
         </is>
       </c>
       <c r="H154" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+          <t>1. Berhasil menampilkan form Step 1 Informasi.
+2. Berhasil mengisi data pada Step 1 Informasi.
+3. Berhasil menyimpan data Step 1 dan berpindah ke Step 2 Data Pribadi.</t>
         </is>
       </c>
       <c r="I154" s="49" t="n"/>
@@ -58160,46 +57254,46 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="B155" s="46" t="inlineStr">
         <is>
-          <t>Agenda</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C155" s="46" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D155" s="48" t="inlineStr">
         <is>
-          <t>Melakukan filter data Daily Sales Agenda</t>
+          <t>Mengisi form Step 1 (Informasi) tanpa field mandatory</t>
         </is>
       </c>
       <c r="E155" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F155" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G155" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button Filter.
-2. Pilih kriteria filter pada form Filter (Product, Bulan, Tahun).
-3. Klik button Submit.</t>
+          <t>1. Buka form Input Prospek Individu (Step 1 Informasi).
+2. Mengosongkan field Nama Lengkap dan No. Telepon.
+3. Klik button Next.</t>
         </is>
       </c>
       <c r="H155" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka form Filter.
-2. Berhasil memilih kriteria filter.
-3. Berhasil menampilkan data Daily Sales Agenda sesuai filter yang dipilih.</t>
+          <t>1. Berhasil menampilkan form Step 1 Informasi.
+2. Berhasil mengosongkan field mandatory.
+3. Menampilkan pesan validasi bahwa field Nama Lengkap dan No. Telepon wajib diisi.</t>
         </is>
       </c>
       <c r="I155" s="49" t="n"/>
@@ -58225,22 +57319,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="B156" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C156" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D156" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Marketing Toolkit</t>
+          <t>Melakukan Check CIF pada form Step 1</t>
         </is>
       </c>
       <c r="E156" s="46" t="inlineStr">
@@ -58250,19 +57344,21 @@
       </c>
       <c r="F156" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G156" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Marketing Toolkit.</t>
+          <t>1. Buka form Input Prospek Individu (Step 1 Informasi).
+2. Isi field No KTP dengan nomor KTP valid.
+3. Klik button Check CIF.</t>
         </is>
       </c>
       <c r="H156" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Marketing Toolkit.</t>
+          <t>1. Berhasil menampilkan form Step 1 Informasi.
+2. Berhasil mengisi field No KTP.
+3. Berhasil menampilkan hasil Check CIF berdasarkan No KTP.</t>
         </is>
       </c>
       <c r="I156" s="49" t="n"/>
@@ -58288,22 +57384,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="B157" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C157" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D157" s="48" t="inlineStr">
         <is>
-          <t>Mengubah tampilan folder menjadi List View</t>
+          <t>Mengisi form Step 2 (Data Pribadi) dengan data valid</t>
         </is>
       </c>
       <c r="E157" s="46" t="inlineStr">
@@ -58313,17 +57409,19 @@
       </c>
       <c r="F157" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G157" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon tampilan List pada halaman Marketing Toolkit.</t>
+          <t>1. Mengisi seluruh field pada Step 2 Data Pribadi dengan data valid.
+2. Klik button Next.</t>
         </is>
       </c>
       <c r="H157" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengubah tampilan folder menjadi List View.</t>
+          <t>1. Berhasil mengisi data pada Step 2 Data Pribadi.
+2. Berhasil menyimpan data Step 2 dan berpindah ke Step 3 Pekerjaan.</t>
         </is>
       </c>
       <c r="I157" s="49" t="n"/>
@@ -58349,22 +57447,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="B158" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C158" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D158" s="48" t="inlineStr">
         <is>
-          <t>Mengubah tampilan folder menjadi Grid View</t>
+          <t>Mengisi form Step 3 (Pekerjaan) dengan data valid</t>
         </is>
       </c>
       <c r="E158" s="46" t="inlineStr">
@@ -58374,17 +57472,19 @@
       </c>
       <c r="F158" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G158" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon tampilan Grid pada halaman Marketing Toolkit.</t>
+          <t>1. Mengisi seluruh field pada Step 3 Pekerjaan dengan data valid.
+2. Klik button Next.</t>
         </is>
       </c>
       <c r="H158" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengubah tampilan folder menjadi Grid View.</t>
+          <t>1. Berhasil mengisi data pada Step 3 Pekerjaan.
+2. Berhasil menyimpan data Step 3 dan berpindah ke Step 4 Prospek.</t>
         </is>
       </c>
       <c r="I158" s="49" t="n"/>
@@ -58410,22 +57510,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="B159" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C159" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D159" s="48" t="inlineStr">
         <is>
-          <t>Membuka folder pada Marketing Toolkit</t>
+          <t>Mengisi form Step 4 (Prospek) NTB dengan data valid</t>
         </is>
       </c>
       <c r="E159" s="46" t="inlineStr">
@@ -58440,12 +57540,14 @@
       </c>
       <c r="G159" s="48" t="inlineStr">
         <is>
-          <t>1. Klik salah satu folder pada daftar Folder.</t>
+          <t>1. Mengisi seluruh field pada Step 4 Prospek dengan data valid.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H159" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka folder Marketing Toolkit.</t>
+          <t>1. Berhasil mengisi data pada Step 4 Prospek.
+2. Berhasil menyimpan data prospek Individu NTB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
         </is>
       </c>
       <c r="I159" s="49" t="n"/>
@@ -58471,22 +57573,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="B160" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C160" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D160" s="48" t="inlineStr">
         <is>
-          <t>Mencari konten di dalam folder menggunakan Search Bar</t>
+          <t>Mengisi form Step 4 (Prospek) ETB dengan mengubah status NTB</t>
         </is>
       </c>
       <c r="E160" s="46" t="inlineStr">
@@ -58501,12 +57603,18 @@
       </c>
       <c r="G160" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
+          <t>1. Aktifkan toggle Ubah NTB ke ETB.
+2. Isi field No CIF.
+3. Mengisi seluruh field pada Step 4 Prospek dengan data valid.
+4. Klik button Submit.</t>
         </is>
       </c>
       <c r="H160" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data yang sesuai dengan kata kunci pencarian.</t>
+          <t>1. Berhasil mengaktifkan toggle NTB ke ETB.
+2. Berhasil mengisi No CIF.
+3. Berhasil mengisi data pada Step 4 Prospek.
+4. Berhasil menyimpan data prospek Individu ETB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
         </is>
       </c>
       <c r="I160" s="49" t="n"/>
@@ -58532,22 +57640,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="B161" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C161" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D161" s="48" t="inlineStr">
         <is>
-          <t>Mencari konten di dalam folder dengan keyword tidak valid</t>
+          <t>Mengisi form Step 4 (Prospek) tanpa field mandatory</t>
         </is>
       </c>
       <c r="E161" s="46" t="inlineStr">
@@ -58562,12 +57670,14 @@
       </c>
       <c r="G161" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+          <t>1. Mengosongkan seluruh field mandatory pada Step 4 Prospek.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H161" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+          <t>1. Berhasil mengosongkan field mandatory.
+2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
         </is>
       </c>
       <c r="I161" s="49" t="n"/>
@@ -58593,22 +57703,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="B162" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C162" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D162" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail konten Marketing Toolkit</t>
+          <t>Navigasi ke halaman Aktifitas dari layar konfirmasi Prospek Berhasil Dibuat</t>
         </is>
       </c>
       <c r="E162" s="46" t="inlineStr">
@@ -58623,12 +57733,12 @@
       </c>
       <c r="G162" s="48" t="inlineStr">
         <is>
-          <t>1. Klik salah satu sub-folder pada daftar folder.</t>
+          <t>1. Klik button Lihat Aktifitas.</t>
         </is>
       </c>
       <c r="H162" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail konten Marketing Toolkit.</t>
+          <t>1. Berhasil mengarahkan pengguna ke halaman Lead Qualification Aktifitas.</t>
         </is>
       </c>
       <c r="I162" s="49" t="n"/>
@@ -58654,22 +57764,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="B163" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C163" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D163" s="48" t="inlineStr">
         <is>
-          <t>Mengunduh lampiran pada konten Marketing Toolkit</t>
+          <t>Kembali ke halaman utama dari layar konfirmasi Prospek Berhasil Dibuat</t>
         </is>
       </c>
       <c r="E163" s="46" t="inlineStr">
@@ -58679,19 +57789,17 @@
       </c>
       <c r="F163" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G163" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon titik tiga pada salah satu lampiran.
-2. Pilih Download.</t>
+          <t>1. Klik button Kembali.</t>
         </is>
       </c>
       <c r="H163" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan opsi aksi pada lampiran.
-2. Berhasil mengunduh lampiran ke perangkat.</t>
+          <t>1. Berhasil mengarahkan pengguna kembali ke halaman utama / form input.</t>
         </is>
       </c>
       <c r="I163" s="49" t="n"/>
@@ -58717,22 +57825,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="B164" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C164" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D164" s="48" t="inlineStr">
         <is>
-          <t>Berbagi lampiran pada konten Marketing Toolkit</t>
+          <t>Memilih tipe Prospek Lembaga</t>
         </is>
       </c>
       <c r="E164" s="46" t="inlineStr">
@@ -58742,19 +57850,19 @@
       </c>
       <c r="F164" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G164" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon titik tiga pada salah satu lampiran.
-2. Pilih Share.</t>
+          <t>1. Buka halaman Input Prospek.
+2. Klik pilihan Lembaga.</t>
         </is>
       </c>
       <c r="H164" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan opsi aksi pada lampiran.
-2. Berhasil menampilkan pilihan aplikasi berbagi.</t>
+          <t>1. Berhasil membuka halaman Input Prospek.
+2. Berhasil menampilkan form Step 1 Informasi Lembaga.</t>
         </is>
       </c>
       <c r="I164" s="49" t="n"/>
@@ -58780,22 +57888,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="B165" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C165" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D165" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Dashboard Sales Code</t>
+          <t>Mengisi form Step 1 (Informasi Lembaga) dengan data valid</t>
         </is>
       </c>
       <c r="E165" s="46" t="inlineStr">
@@ -58810,14 +57918,16 @@
       </c>
       <c r="G165" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Dashboard Sales Code.</t>
+          <t>1. Buka form Input Prospek Lembaga (Step 1 Informasi Lembaga).
+2. Mengisi field NPWP dengan NPWP valid.
+3. Klik button Next.</t>
         </is>
       </c>
       <c r="H165" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Dashboard Sales Code.</t>
+          <t>1. Berhasil menampilkan form Step 1 Informasi Lembaga.
+2. Berhasil mengisi field NPWP.
+3. Berhasil menyimpan data Step 1 dan berpindah ke Step 2 Data Lembaga.</t>
         </is>
       </c>
       <c r="I165" s="49" t="n"/>
@@ -58843,22 +57953,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>12.16</t>
         </is>
       </c>
       <c r="B166" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C166" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D166" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail Voa Realization</t>
+          <t>Mengisi form Step 2 (Data Lembaga) dengan data valid</t>
         </is>
       </c>
       <c r="E166" s="46" t="inlineStr">
@@ -58873,12 +57983,14 @@
       </c>
       <c r="G166" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Voa Realization.</t>
+          <t>1. Mengisi seluruh field pada Step 2 Data Lembaga dengan data valid.
+2. Klik button Next.</t>
         </is>
       </c>
       <c r="H166" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Voa Realization.</t>
+          <t>1. Berhasil mengisi data pada Step 2 Data Lembaga.
+2. Berhasil menyimpan data Step 2 dan berpindah ke Step 3 Prospek.</t>
         </is>
       </c>
       <c r="I166" s="49" t="n"/>
@@ -58904,44 +58016,44 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>12.17</t>
         </is>
       </c>
       <c r="B167" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C167" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D167" s="48" t="inlineStr">
         <is>
-          <t>Melihat Daftar Pipeline pada Voa Realization</t>
+          <t>Mengisi form Step 2 (Data Lembaga) tanpa field mandatory</t>
         </is>
       </c>
       <c r="E167" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F167" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G167" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Voa Realization.
-2. Klik Lihat Daftar Pipeline.</t>
+          <t>1. Mengosongkan field Nama Perusahaan dan Telepon Perusahaan.
+2. Klik button Next.</t>
         </is>
       </c>
       <c r="H167" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Voa Realization.
-2. Berhasil menampilkan Daftar Pipeline.</t>
+          <t>1. Berhasil mengosongkan field mandatory.
+2. Menampilkan pesan validasi bahwa field Nama Perusahaan dan Telepon Perusahaan wajib diisi.</t>
         </is>
       </c>
       <c r="I167" s="49" t="n"/>
@@ -58967,22 +58079,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="B168" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C168" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D168" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail CIF Kelolaan</t>
+          <t>Mengisi form Step 3 (Prospek Lembaga) NTB dengan data valid</t>
         </is>
       </c>
       <c r="E168" s="46" t="inlineStr">
@@ -58992,17 +58104,19 @@
       </c>
       <c r="F168" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G168" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card CIF Kelolaan.</t>
+          <t>1. Mengisi seluruh field pada Step 3 Prospek Lembaga dengan data valid.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H168" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail CIF Kelolaan.</t>
+          <t>1. Berhasil mengisi data pada Step 3 Prospek Lembaga.
+2. Berhasil menyimpan data prospek Lembaga NTB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
         </is>
       </c>
       <c r="I168" s="49" t="n"/>
@@ -59028,22 +58142,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="B169" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C169" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D169" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail Realisasi Konek E-Channel</t>
+          <t>Mengisi form Step 3 (Prospek Lembaga) ETB dengan mengubah status NTB</t>
         </is>
       </c>
       <c r="E169" s="46" t="inlineStr">
@@ -59058,12 +58172,18 @@
       </c>
       <c r="G169" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Realisasi Konek E-Channel.</t>
+          <t>1. Aktifkan toggle Ubah NTB ke ETB.
+2. Isi field No CIF.
+3. Mengisi seluruh field pada Step 3 Prospek Lembaga dengan data valid.
+4. Klik button Submit.</t>
         </is>
       </c>
       <c r="H169" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Realisasi Konek E-Channel.</t>
+          <t>1. Berhasil mengaktifkan toggle NTB ke ETB.
+2. Berhasil mengisi No CIF.
+3. Berhasil mengisi data pada Step 3 Prospek Lembaga.
+4. Berhasil menyimpan data prospek Lembaga ETB dan menampilkan layar konfirmasi Prospek Berhasil Dibuat.</t>
         </is>
       </c>
       <c r="I169" s="49" t="n"/>
@@ -59089,42 +58209,44 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="B170" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C170" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>Input Prospek</t>
         </is>
       </c>
       <c r="D170" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail Realisasi Akuisisi Merchant</t>
+          <t>Mengisi form Step 3 (Prospek Lembaga) tanpa field mandatory</t>
         </is>
       </c>
       <c r="E170" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F170" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G170" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Realisasi Akuisisi Merchant.</t>
+          <t>1. Mengosongkan seluruh field mandatory pada Step 3 Prospek Lembaga.
+2. Klik button Submit.</t>
         </is>
       </c>
       <c r="H170" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Realisasi Akuisisi Merchant.</t>
+          <t>1. Berhasil mengosongkan field mandatory.
+2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
         </is>
       </c>
       <c r="I170" s="49" t="n"/>
@@ -59150,22 +58272,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="B171" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Prospek &amp; Nasabah</t>
         </is>
       </c>
       <c r="C171" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>List Nasabah ETB</t>
         </is>
       </c>
       <c r="D171" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail Eligible Upgrade to Prospera/Prioritas</t>
+          <t>Membuka halaman List Nasabah ETB</t>
         </is>
       </c>
       <c r="E171" s="46" t="inlineStr">
@@ -59180,12 +58302,14 @@
       </c>
       <c r="G171" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Eligible Upgrade to Prospera/Prioritas.</t>
+          <t>1. Buka menu Lainnya.
+2. Klik menu List Nasabah ETB.</t>
         </is>
       </c>
       <c r="H171" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Eligible Upgrade to Prospera &amp; Prioritas.</t>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman List Nasabah ETB.</t>
         </is>
       </c>
       <c r="I171" s="49" t="n"/>
@@ -59208,6 +58332,2677 @@
       <c r="Z171" s="49" t="n"/>
       <c r="AA171" s="49" t="n"/>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="B172" s="46" t="inlineStr">
+        <is>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C172" s="46" t="inlineStr">
+        <is>
+          <t>List Nasabah ETB</t>
+        </is>
+      </c>
+      <c r="D172" s="48" t="inlineStr">
+        <is>
+          <t>Mencari nasabah menggunakan Search Bar</t>
+        </is>
+      </c>
+      <c r="E172" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F172" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G172" s="48" t="inlineStr">
+        <is>
+          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
+        </is>
+      </c>
+      <c r="H172" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data nasabah yang sesuai dengan kata kunci pencarian.</t>
+        </is>
+      </c>
+      <c r="I172" s="49" t="n"/>
+      <c r="J172" s="49" t="n"/>
+      <c r="K172" s="49" t="n"/>
+      <c r="L172" s="49" t="n"/>
+      <c r="M172" s="49" t="n"/>
+      <c r="N172" s="49" t="n"/>
+      <c r="O172" s="49" t="n"/>
+      <c r="P172" s="49" t="n"/>
+      <c r="Q172" s="49" t="n"/>
+      <c r="R172" s="49" t="n"/>
+      <c r="S172" s="49" t="n"/>
+      <c r="T172" s="49" t="n"/>
+      <c r="U172" s="49" t="n"/>
+      <c r="V172" s="49" t="n"/>
+      <c r="W172" s="49" t="n"/>
+      <c r="X172" s="49" t="n"/>
+      <c r="Y172" s="49" t="n"/>
+      <c r="Z172" s="49" t="n"/>
+      <c r="AA172" s="49" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="B173" s="46" t="inlineStr">
+        <is>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C173" s="46" t="inlineStr">
+        <is>
+          <t>List Nasabah ETB</t>
+        </is>
+      </c>
+      <c r="D173" s="48" t="inlineStr">
+        <is>
+          <t>Mencari nasabah dengan keyword tidak valid</t>
+        </is>
+      </c>
+      <c r="E173" s="46" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F173" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G173" s="48" t="inlineStr">
+        <is>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+        </is>
+      </c>
+      <c r="H173" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+        </is>
+      </c>
+      <c r="I173" s="49" t="n"/>
+      <c r="J173" s="49" t="n"/>
+      <c r="K173" s="49" t="n"/>
+      <c r="L173" s="49" t="n"/>
+      <c r="M173" s="49" t="n"/>
+      <c r="N173" s="49" t="n"/>
+      <c r="O173" s="49" t="n"/>
+      <c r="P173" s="49" t="n"/>
+      <c r="Q173" s="49" t="n"/>
+      <c r="R173" s="49" t="n"/>
+      <c r="S173" s="49" t="n"/>
+      <c r="T173" s="49" t="n"/>
+      <c r="U173" s="49" t="n"/>
+      <c r="V173" s="49" t="n"/>
+      <c r="W173" s="49" t="n"/>
+      <c r="X173" s="49" t="n"/>
+      <c r="Y173" s="49" t="n"/>
+      <c r="Z173" s="49" t="n"/>
+      <c r="AA173" s="49" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="B174" s="46" t="inlineStr">
+        <is>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C174" s="46" t="inlineStr">
+        <is>
+          <t>List Nasabah ETB</t>
+        </is>
+      </c>
+      <c r="D174" s="48" t="inlineStr">
+        <is>
+          <t>Melakukan filter data nasabah</t>
+        </is>
+      </c>
+      <c r="E174" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F174" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G174" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik button Filter di halaman List Nasabah ETB.
+2. Pilih kriteria filter pada form Filter.
+3. Klik button Simpan.</t>
+        </is>
+      </c>
+      <c r="H174" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka form Filter.
+2. Berhasil memilih kriteria filter.
+3. Berhasil menampilkan daftar nasabah yang sesuai dengan kriteria filter.</t>
+        </is>
+      </c>
+      <c r="I174" s="49" t="n"/>
+      <c r="J174" s="49" t="n"/>
+      <c r="K174" s="49" t="n"/>
+      <c r="L174" s="49" t="n"/>
+      <c r="M174" s="49" t="n"/>
+      <c r="N174" s="49" t="n"/>
+      <c r="O174" s="49" t="n"/>
+      <c r="P174" s="49" t="n"/>
+      <c r="Q174" s="49" t="n"/>
+      <c r="R174" s="49" t="n"/>
+      <c r="S174" s="49" t="n"/>
+      <c r="T174" s="49" t="n"/>
+      <c r="U174" s="49" t="n"/>
+      <c r="V174" s="49" t="n"/>
+      <c r="W174" s="49" t="n"/>
+      <c r="X174" s="49" t="n"/>
+      <c r="Y174" s="49" t="n"/>
+      <c r="Z174" s="49" t="n"/>
+      <c r="AA174" s="49" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="B175" s="46" t="inlineStr">
+        <is>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C175" s="46" t="inlineStr">
+        <is>
+          <t>List Nasabah ETB</t>
+        </is>
+      </c>
+      <c r="D175" s="48" t="inlineStr">
+        <is>
+          <t>Melihat Detail Prospek Nasabah ETB</t>
+        </is>
+      </c>
+      <c r="E175" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F175" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G175" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik menu titik tiga pada salah satu card nasabah.
+2. Pilih Detail Prospek.</t>
+        </is>
+      </c>
+      <c r="H175" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan menu Lainnya.
+2. Berhasil membuka halaman Detail Prospek dan menampilkan informasi nasabah secara lengkap.</t>
+        </is>
+      </c>
+      <c r="I175" s="49" t="n"/>
+      <c r="J175" s="49" t="n"/>
+      <c r="K175" s="49" t="n"/>
+      <c r="L175" s="49" t="n"/>
+      <c r="M175" s="49" t="n"/>
+      <c r="N175" s="49" t="n"/>
+      <c r="O175" s="49" t="n"/>
+      <c r="P175" s="49" t="n"/>
+      <c r="Q175" s="49" t="n"/>
+      <c r="R175" s="49" t="n"/>
+      <c r="S175" s="49" t="n"/>
+      <c r="T175" s="49" t="n"/>
+      <c r="U175" s="49" t="n"/>
+      <c r="V175" s="49" t="n"/>
+      <c r="W175" s="49" t="n"/>
+      <c r="X175" s="49" t="n"/>
+      <c r="Y175" s="49" t="n"/>
+      <c r="Z175" s="49" t="n"/>
+      <c r="AA175" s="49" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="B176" s="46" t="inlineStr">
+        <is>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C176" s="46" t="inlineStr">
+        <is>
+          <t>List Nasabah ETB</t>
+        </is>
+      </c>
+      <c r="D176" s="48" t="inlineStr">
+        <is>
+          <t>Membuka form Prospek Ulang</t>
+        </is>
+      </c>
+      <c r="E176" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F176" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G176" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik menu titik tiga pada salah satu card nasabah.
+2. Pilih Prospek Ulang.</t>
+        </is>
+      </c>
+      <c r="H176" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan menu Lainnya.
+2. Berhasil membuka form Prospek Ulang.</t>
+        </is>
+      </c>
+      <c r="I176" s="49" t="n"/>
+      <c r="J176" s="49" t="n"/>
+      <c r="K176" s="49" t="n"/>
+      <c r="L176" s="49" t="n"/>
+      <c r="M176" s="49" t="n"/>
+      <c r="N176" s="49" t="n"/>
+      <c r="O176" s="49" t="n"/>
+      <c r="P176" s="49" t="n"/>
+      <c r="Q176" s="49" t="n"/>
+      <c r="R176" s="49" t="n"/>
+      <c r="S176" s="49" t="n"/>
+      <c r="T176" s="49" t="n"/>
+      <c r="U176" s="49" t="n"/>
+      <c r="V176" s="49" t="n"/>
+      <c r="W176" s="49" t="n"/>
+      <c r="X176" s="49" t="n"/>
+      <c r="Y176" s="49" t="n"/>
+      <c r="Z176" s="49" t="n"/>
+      <c r="AA176" s="49" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="B177" s="46" t="inlineStr">
+        <is>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C177" s="46" t="inlineStr">
+        <is>
+          <t>List Nasabah ETB</t>
+        </is>
+      </c>
+      <c r="D177" s="48" t="inlineStr">
+        <is>
+          <t>Melakukan Prospek Ulang dengan data valid</t>
+        </is>
+      </c>
+      <c r="E177" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F177" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G177" s="48" t="inlineStr">
+        <is>
+          <t>1. Mengisi seluruh field pada form Prospek Ulang dengan data valid.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H177" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi data pada form Prospek Ulang.
+2. Berhasil men-submit form dan memperbarui data prospek.</t>
+        </is>
+      </c>
+      <c r="I177" s="49" t="n"/>
+      <c r="J177" s="49" t="n"/>
+      <c r="K177" s="49" t="n"/>
+      <c r="L177" s="49" t="n"/>
+      <c r="M177" s="49" t="n"/>
+      <c r="N177" s="49" t="n"/>
+      <c r="O177" s="49" t="n"/>
+      <c r="P177" s="49" t="n"/>
+      <c r="Q177" s="49" t="n"/>
+      <c r="R177" s="49" t="n"/>
+      <c r="S177" s="49" t="n"/>
+      <c r="T177" s="49" t="n"/>
+      <c r="U177" s="49" t="n"/>
+      <c r="V177" s="49" t="n"/>
+      <c r="W177" s="49" t="n"/>
+      <c r="X177" s="49" t="n"/>
+      <c r="Y177" s="49" t="n"/>
+      <c r="Z177" s="49" t="n"/>
+      <c r="AA177" s="49" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>13.8</t>
+        </is>
+      </c>
+      <c r="B178" s="46" t="inlineStr">
+        <is>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C178" s="46" t="inlineStr">
+        <is>
+          <t>List Nasabah ETB</t>
+        </is>
+      </c>
+      <c r="D178" s="48" t="inlineStr">
+        <is>
+          <t>Melakukan Prospek Ulang tanpa field mandatory</t>
+        </is>
+      </c>
+      <c r="E178" s="46" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F178" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G178" s="48" t="inlineStr">
+        <is>
+          <t>1. Mengosongkan seluruh field mandatory pada form Prospek Ulang.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H178" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan field mandatory.
+2. Menampilkan pesan validasi bahwa field mandatory wajib diisi.</t>
+        </is>
+      </c>
+      <c r="I178" s="49" t="n"/>
+      <c r="J178" s="49" t="n"/>
+      <c r="K178" s="49" t="n"/>
+      <c r="L178" s="49" t="n"/>
+      <c r="M178" s="49" t="n"/>
+      <c r="N178" s="49" t="n"/>
+      <c r="O178" s="49" t="n"/>
+      <c r="P178" s="49" t="n"/>
+      <c r="Q178" s="49" t="n"/>
+      <c r="R178" s="49" t="n"/>
+      <c r="S178" s="49" t="n"/>
+      <c r="T178" s="49" t="n"/>
+      <c r="U178" s="49" t="n"/>
+      <c r="V178" s="49" t="n"/>
+      <c r="W178" s="49" t="n"/>
+      <c r="X178" s="49" t="n"/>
+      <c r="Y178" s="49" t="n"/>
+      <c r="Z178" s="49" t="n"/>
+      <c r="AA178" s="49" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>13.9</t>
+        </is>
+      </c>
+      <c r="B179" s="46" t="inlineStr">
+        <is>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C179" s="46" t="inlineStr">
+        <is>
+          <t>List Nasabah ETB</t>
+        </is>
+      </c>
+      <c r="D179" s="48" t="inlineStr">
+        <is>
+          <t>Melihat Informasi Rekening</t>
+        </is>
+      </c>
+      <c r="E179" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F179" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G179" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik menu titik tiga pada salah satu card nasabah.
+2. Pilih Informasi Rekening.</t>
+        </is>
+      </c>
+      <c r="H179" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan menu Lainnya.
+2. Berhasil menampilkan detail rekening nasabah (nomor rekening dan saldo).</t>
+        </is>
+      </c>
+      <c r="I179" s="49" t="n"/>
+      <c r="J179" s="49" t="n"/>
+      <c r="K179" s="49" t="n"/>
+      <c r="L179" s="49" t="n"/>
+      <c r="M179" s="49" t="n"/>
+      <c r="N179" s="49" t="n"/>
+      <c r="O179" s="49" t="n"/>
+      <c r="P179" s="49" t="n"/>
+      <c r="Q179" s="49" t="n"/>
+      <c r="R179" s="49" t="n"/>
+      <c r="S179" s="49" t="n"/>
+      <c r="T179" s="49" t="n"/>
+      <c r="U179" s="49" t="n"/>
+      <c r="V179" s="49" t="n"/>
+      <c r="W179" s="49" t="n"/>
+      <c r="X179" s="49" t="n"/>
+      <c r="Y179" s="49" t="n"/>
+      <c r="Z179" s="49" t="n"/>
+      <c r="AA179" s="49" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>13.10</t>
+        </is>
+      </c>
+      <c r="B180" s="46" t="inlineStr">
+        <is>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C180" s="46" t="inlineStr">
+        <is>
+          <t>List Nasabah ETB</t>
+        </is>
+      </c>
+      <c r="D180" s="48" t="inlineStr">
+        <is>
+          <t>Menghapus data nasabah</t>
+        </is>
+      </c>
+      <c r="E180" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F180" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G180" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik menu titik tiga pada salah satu card nasabah.
+2. Pilih Hapus.
+3. Klik button Ya pada pop-up konfirmasi.</t>
+        </is>
+      </c>
+      <c r="H180" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan menu Lainnya.
+2. Berhasil menampilkan pop-up konfirmasi hapus data.
+3. Berhasil menghapus data nasabah dari daftar List Nasabah ETB.</t>
+        </is>
+      </c>
+      <c r="I180" s="49" t="n"/>
+      <c r="J180" s="49" t="n"/>
+      <c r="K180" s="49" t="n"/>
+      <c r="L180" s="49" t="n"/>
+      <c r="M180" s="49" t="n"/>
+      <c r="N180" s="49" t="n"/>
+      <c r="O180" s="49" t="n"/>
+      <c r="P180" s="49" t="n"/>
+      <c r="Q180" s="49" t="n"/>
+      <c r="R180" s="49" t="n"/>
+      <c r="S180" s="49" t="n"/>
+      <c r="T180" s="49" t="n"/>
+      <c r="U180" s="49" t="n"/>
+      <c r="V180" s="49" t="n"/>
+      <c r="W180" s="49" t="n"/>
+      <c r="X180" s="49" t="n"/>
+      <c r="Y180" s="49" t="n"/>
+      <c r="Z180" s="49" t="n"/>
+      <c r="AA180" s="49" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="B181" s="46" t="inlineStr">
+        <is>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C181" s="46" t="inlineStr">
+        <is>
+          <t>Nasabah Referal</t>
+        </is>
+      </c>
+      <c r="D181" s="48" t="inlineStr">
+        <is>
+          <t>Membuka halaman Nasabah Referal</t>
+        </is>
+      </c>
+      <c r="E181" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F181" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G181" s="48" t="inlineStr">
+        <is>
+          <t>1. Buka menu Lainnya.
+2. Klik menu Nasabah Referal.</t>
+        </is>
+      </c>
+      <c r="H181" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman Nasabah Referal.</t>
+        </is>
+      </c>
+      <c r="I181" s="49" t="n"/>
+      <c r="J181" s="49" t="n"/>
+      <c r="K181" s="49" t="n"/>
+      <c r="L181" s="49" t="n"/>
+      <c r="M181" s="49" t="n"/>
+      <c r="N181" s="49" t="n"/>
+      <c r="O181" s="49" t="n"/>
+      <c r="P181" s="49" t="n"/>
+      <c r="Q181" s="49" t="n"/>
+      <c r="R181" s="49" t="n"/>
+      <c r="S181" s="49" t="n"/>
+      <c r="T181" s="49" t="n"/>
+      <c r="U181" s="49" t="n"/>
+      <c r="V181" s="49" t="n"/>
+      <c r="W181" s="49" t="n"/>
+      <c r="X181" s="49" t="n"/>
+      <c r="Y181" s="49" t="n"/>
+      <c r="Z181" s="49" t="n"/>
+      <c r="AA181" s="49" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="B182" s="46" t="inlineStr">
+        <is>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C182" s="46" t="inlineStr">
+        <is>
+          <t>Nasabah Referal</t>
+        </is>
+      </c>
+      <c r="D182" s="48" t="inlineStr">
+        <is>
+          <t>Mencari nasabah referal menggunakan Search Bar</t>
+        </is>
+      </c>
+      <c r="E182" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F182" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G182" s="48" t="inlineStr">
+        <is>
+          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
+        </is>
+      </c>
+      <c r="H182" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data nasabah referal yang sesuai dengan kata kunci pencarian.</t>
+        </is>
+      </c>
+      <c r="I182" s="49" t="n"/>
+      <c r="J182" s="49" t="n"/>
+      <c r="K182" s="49" t="n"/>
+      <c r="L182" s="49" t="n"/>
+      <c r="M182" s="49" t="n"/>
+      <c r="N182" s="49" t="n"/>
+      <c r="O182" s="49" t="n"/>
+      <c r="P182" s="49" t="n"/>
+      <c r="Q182" s="49" t="n"/>
+      <c r="R182" s="49" t="n"/>
+      <c r="S182" s="49" t="n"/>
+      <c r="T182" s="49" t="n"/>
+      <c r="U182" s="49" t="n"/>
+      <c r="V182" s="49" t="n"/>
+      <c r="W182" s="49" t="n"/>
+      <c r="X182" s="49" t="n"/>
+      <c r="Y182" s="49" t="n"/>
+      <c r="Z182" s="49" t="n"/>
+      <c r="AA182" s="49" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="B183" s="46" t="inlineStr">
+        <is>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C183" s="46" t="inlineStr">
+        <is>
+          <t>Nasabah Referal</t>
+        </is>
+      </c>
+      <c r="D183" s="48" t="inlineStr">
+        <is>
+          <t>Mencari nasabah referal dengan keyword tidak valid</t>
+        </is>
+      </c>
+      <c r="E183" s="46" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F183" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G183" s="48" t="inlineStr">
+        <is>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+        </is>
+      </c>
+      <c r="H183" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+        </is>
+      </c>
+      <c r="I183" s="49" t="n"/>
+      <c r="J183" s="49" t="n"/>
+      <c r="K183" s="49" t="n"/>
+      <c r="L183" s="49" t="n"/>
+      <c r="M183" s="49" t="n"/>
+      <c r="N183" s="49" t="n"/>
+      <c r="O183" s="49" t="n"/>
+      <c r="P183" s="49" t="n"/>
+      <c r="Q183" s="49" t="n"/>
+      <c r="R183" s="49" t="n"/>
+      <c r="S183" s="49" t="n"/>
+      <c r="T183" s="49" t="n"/>
+      <c r="U183" s="49" t="n"/>
+      <c r="V183" s="49" t="n"/>
+      <c r="W183" s="49" t="n"/>
+      <c r="X183" s="49" t="n"/>
+      <c r="Y183" s="49" t="n"/>
+      <c r="Z183" s="49" t="n"/>
+      <c r="AA183" s="49" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="B184" s="46" t="inlineStr">
+        <is>
+          <t>Prospek &amp; Nasabah</t>
+        </is>
+      </c>
+      <c r="C184" s="46" t="inlineStr">
+        <is>
+          <t>Nasabah Referal</t>
+        </is>
+      </c>
+      <c r="D184" s="48" t="inlineStr">
+        <is>
+          <t>Melihat Detail Prospek nasabah referal</t>
+        </is>
+      </c>
+      <c r="E184" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F184" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G184" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik salah satu card nasabah referal.</t>
+        </is>
+      </c>
+      <c r="H184" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail nasabah referal.</t>
+        </is>
+      </c>
+      <c r="I184" s="49" t="n"/>
+      <c r="J184" s="49" t="n"/>
+      <c r="K184" s="49" t="n"/>
+      <c r="L184" s="49" t="n"/>
+      <c r="M184" s="49" t="n"/>
+      <c r="N184" s="49" t="n"/>
+      <c r="O184" s="49" t="n"/>
+      <c r="P184" s="49" t="n"/>
+      <c r="Q184" s="49" t="n"/>
+      <c r="R184" s="49" t="n"/>
+      <c r="S184" s="49" t="n"/>
+      <c r="T184" s="49" t="n"/>
+      <c r="U184" s="49" t="n"/>
+      <c r="V184" s="49" t="n"/>
+      <c r="W184" s="49" t="n"/>
+      <c r="X184" s="49" t="n"/>
+      <c r="Y184" s="49" t="n"/>
+      <c r="Z184" s="49" t="n"/>
+      <c r="AA184" s="49" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="B185" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C185" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D185" s="48" t="inlineStr">
+        <is>
+          <t>Membuka halaman Pengingat</t>
+        </is>
+      </c>
+      <c r="E185" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F185" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G185" s="48" t="inlineStr">
+        <is>
+          <t>1. Buka menu Lainnya.
+2. Klik menu Pengingat.</t>
+        </is>
+      </c>
+      <c r="H185" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman Pengingat.</t>
+        </is>
+      </c>
+      <c r="I185" s="49" t="n"/>
+      <c r="J185" s="49" t="n"/>
+      <c r="K185" s="49" t="n"/>
+      <c r="L185" s="49" t="n"/>
+      <c r="M185" s="49" t="n"/>
+      <c r="N185" s="49" t="n"/>
+      <c r="O185" s="49" t="n"/>
+      <c r="P185" s="49" t="n"/>
+      <c r="Q185" s="49" t="n"/>
+      <c r="R185" s="49" t="n"/>
+      <c r="S185" s="49" t="n"/>
+      <c r="T185" s="49" t="n"/>
+      <c r="U185" s="49" t="n"/>
+      <c r="V185" s="49" t="n"/>
+      <c r="W185" s="49" t="n"/>
+      <c r="X185" s="49" t="n"/>
+      <c r="Y185" s="49" t="n"/>
+      <c r="Z185" s="49" t="n"/>
+      <c r="AA185" s="49" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="B186" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C186" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D186" s="48" t="inlineStr">
+        <is>
+          <t>Melihat daftar pengingat pada tab Aktif</t>
+        </is>
+      </c>
+      <c r="E186" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F186" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G186" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik tab Aktif.</t>
+        </is>
+      </c>
+      <c r="H186" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan daftar pengingat yang sedang aktif.</t>
+        </is>
+      </c>
+      <c r="I186" s="49" t="n"/>
+      <c r="J186" s="49" t="n"/>
+      <c r="K186" s="49" t="n"/>
+      <c r="L186" s="49" t="n"/>
+      <c r="M186" s="49" t="n"/>
+      <c r="N186" s="49" t="n"/>
+      <c r="O186" s="49" t="n"/>
+      <c r="P186" s="49" t="n"/>
+      <c r="Q186" s="49" t="n"/>
+      <c r="R186" s="49" t="n"/>
+      <c r="S186" s="49" t="n"/>
+      <c r="T186" s="49" t="n"/>
+      <c r="U186" s="49" t="n"/>
+      <c r="V186" s="49" t="n"/>
+      <c r="W186" s="49" t="n"/>
+      <c r="X186" s="49" t="n"/>
+      <c r="Y186" s="49" t="n"/>
+      <c r="Z186" s="49" t="n"/>
+      <c r="AA186" s="49" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="B187" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C187" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D187" s="48" t="inlineStr">
+        <is>
+          <t>Melihat daftar pengingat pada tab Selesai</t>
+        </is>
+      </c>
+      <c r="E187" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F187" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G187" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik tab Selesai.</t>
+        </is>
+      </c>
+      <c r="H187" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan daftar pengingat yang sudah selesai.</t>
+        </is>
+      </c>
+      <c r="I187" s="49" t="n"/>
+      <c r="J187" s="49" t="n"/>
+      <c r="K187" s="49" t="n"/>
+      <c r="L187" s="49" t="n"/>
+      <c r="M187" s="49" t="n"/>
+      <c r="N187" s="49" t="n"/>
+      <c r="O187" s="49" t="n"/>
+      <c r="P187" s="49" t="n"/>
+      <c r="Q187" s="49" t="n"/>
+      <c r="R187" s="49" t="n"/>
+      <c r="S187" s="49" t="n"/>
+      <c r="T187" s="49" t="n"/>
+      <c r="U187" s="49" t="n"/>
+      <c r="V187" s="49" t="n"/>
+      <c r="W187" s="49" t="n"/>
+      <c r="X187" s="49" t="n"/>
+      <c r="Y187" s="49" t="n"/>
+      <c r="Z187" s="49" t="n"/>
+      <c r="AA187" s="49" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="B188" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C188" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D188" s="48" t="inlineStr">
+        <is>
+          <t>Menambahkan pengingat baru dengan data valid</t>
+        </is>
+      </c>
+      <c r="E188" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F188" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G188" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik button + Baru.
+2. Mengisi seluruh field mandatory pada form Tambah Pengingat dengan data valid.
+3. Klik button Simpan.</t>
+        </is>
+      </c>
+      <c r="H188" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka form Tambah Pengingat.
+2. Berhasil mengisi seluruh field mandatory pada form Tambah Pengingat.
+3. Berhasil menyimpan pengingat dan menampilkan pengingat baru pada daftar.</t>
+        </is>
+      </c>
+      <c r="I188" s="49" t="n"/>
+      <c r="J188" s="49" t="n"/>
+      <c r="K188" s="49" t="n"/>
+      <c r="L188" s="49" t="n"/>
+      <c r="M188" s="49" t="n"/>
+      <c r="N188" s="49" t="n"/>
+      <c r="O188" s="49" t="n"/>
+      <c r="P188" s="49" t="n"/>
+      <c r="Q188" s="49" t="n"/>
+      <c r="R188" s="49" t="n"/>
+      <c r="S188" s="49" t="n"/>
+      <c r="T188" s="49" t="n"/>
+      <c r="U188" s="49" t="n"/>
+      <c r="V188" s="49" t="n"/>
+      <c r="W188" s="49" t="n"/>
+      <c r="X188" s="49" t="n"/>
+      <c r="Y188" s="49" t="n"/>
+      <c r="Z188" s="49" t="n"/>
+      <c r="AA188" s="49" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="B189" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C189" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D189" s="48" t="inlineStr">
+        <is>
+          <t>Menambahkan pengingat baru tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E189" s="46" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F189" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G189" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik button + Baru.
+2. Mengosongkan seluruh field mandatory pada form Tambah Pengingat.
+3. Klik button Simpan.</t>
+        </is>
+      </c>
+      <c r="H189" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka form Tambah Pengingat.
+2. Field mandatory berhasil dikosongkan.
+3. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+        </is>
+      </c>
+      <c r="I189" s="49" t="n"/>
+      <c r="J189" s="49" t="n"/>
+      <c r="K189" s="49" t="n"/>
+      <c r="L189" s="49" t="n"/>
+      <c r="M189" s="49" t="n"/>
+      <c r="N189" s="49" t="n"/>
+      <c r="O189" s="49" t="n"/>
+      <c r="P189" s="49" t="n"/>
+      <c r="Q189" s="49" t="n"/>
+      <c r="R189" s="49" t="n"/>
+      <c r="S189" s="49" t="n"/>
+      <c r="T189" s="49" t="n"/>
+      <c r="U189" s="49" t="n"/>
+      <c r="V189" s="49" t="n"/>
+      <c r="W189" s="49" t="n"/>
+      <c r="X189" s="49" t="n"/>
+      <c r="Y189" s="49" t="n"/>
+      <c r="Z189" s="49" t="n"/>
+      <c r="AA189" s="49" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="B190" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C190" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D190" s="48" t="inlineStr">
+        <is>
+          <t>Menandai pengingat sebagai selesai</t>
+        </is>
+      </c>
+      <c r="E190" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F190" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G190" s="48" t="inlineStr">
+        <is>
+          <t>1. Centang checkbox pada salah satu card pengingat aktif.
+2. Klik button Ya pada pop-up konfirmasi.</t>
+        </is>
+      </c>
+      <c r="H190" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan pop-up konfirmasi selesai.
+2. Berhasil menandai pengingat sebagai selesai dan memindahkan pengingat ke tab Selesai.</t>
+        </is>
+      </c>
+      <c r="I190" s="49" t="n"/>
+      <c r="J190" s="49" t="n"/>
+      <c r="K190" s="49" t="n"/>
+      <c r="L190" s="49" t="n"/>
+      <c r="M190" s="49" t="n"/>
+      <c r="N190" s="49" t="n"/>
+      <c r="O190" s="49" t="n"/>
+      <c r="P190" s="49" t="n"/>
+      <c r="Q190" s="49" t="n"/>
+      <c r="R190" s="49" t="n"/>
+      <c r="S190" s="49" t="n"/>
+      <c r="T190" s="49" t="n"/>
+      <c r="U190" s="49" t="n"/>
+      <c r="V190" s="49" t="n"/>
+      <c r="W190" s="49" t="n"/>
+      <c r="X190" s="49" t="n"/>
+      <c r="Y190" s="49" t="n"/>
+      <c r="Z190" s="49" t="n"/>
+      <c r="AA190" s="49" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="B191" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C191" s="46" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D191" s="48" t="inlineStr">
+        <is>
+          <t>Membuka halaman Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="E191" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F191" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G191" s="48" t="inlineStr">
+        <is>
+          <t>1. Buka menu Lainnya.
+2. Klik menu Daily Sales Agenda.</t>
+        </is>
+      </c>
+      <c r="H191" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
+        </is>
+      </c>
+      <c r="I191" s="49" t="n"/>
+      <c r="J191" s="49" t="n"/>
+      <c r="K191" s="49" t="n"/>
+      <c r="L191" s="49" t="n"/>
+      <c r="M191" s="49" t="n"/>
+      <c r="N191" s="49" t="n"/>
+      <c r="O191" s="49" t="n"/>
+      <c r="P191" s="49" t="n"/>
+      <c r="Q191" s="49" t="n"/>
+      <c r="R191" s="49" t="n"/>
+      <c r="S191" s="49" t="n"/>
+      <c r="T191" s="49" t="n"/>
+      <c r="U191" s="49" t="n"/>
+      <c r="V191" s="49" t="n"/>
+      <c r="W191" s="49" t="n"/>
+      <c r="X191" s="49" t="n"/>
+      <c r="Y191" s="49" t="n"/>
+      <c r="Z191" s="49" t="n"/>
+      <c r="AA191" s="49" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="B192" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C192" s="46" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D192" s="48" t="inlineStr">
+        <is>
+          <t>Melihat daftar agenda pada tab Masuk</t>
+        </is>
+      </c>
+      <c r="E192" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F192" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G192" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik tab Masuk.</t>
+        </is>
+      </c>
+      <c r="H192" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan daftar nasabah yang masuk pada Daily Sales Agenda.</t>
+        </is>
+      </c>
+      <c r="I192" s="49" t="n"/>
+      <c r="J192" s="49" t="n"/>
+      <c r="K192" s="49" t="n"/>
+      <c r="L192" s="49" t="n"/>
+      <c r="M192" s="49" t="n"/>
+      <c r="N192" s="49" t="n"/>
+      <c r="O192" s="49" t="n"/>
+      <c r="P192" s="49" t="n"/>
+      <c r="Q192" s="49" t="n"/>
+      <c r="R192" s="49" t="n"/>
+      <c r="S192" s="49" t="n"/>
+      <c r="T192" s="49" t="n"/>
+      <c r="U192" s="49" t="n"/>
+      <c r="V192" s="49" t="n"/>
+      <c r="W192" s="49" t="n"/>
+      <c r="X192" s="49" t="n"/>
+      <c r="Y192" s="49" t="n"/>
+      <c r="Z192" s="49" t="n"/>
+      <c r="AA192" s="49" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="B193" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C193" s="46" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D193" s="48" t="inlineStr">
+        <is>
+          <t>Melihat daftar agenda pada tab Closing</t>
+        </is>
+      </c>
+      <c r="E193" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F193" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G193" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik tab Closing.</t>
+        </is>
+      </c>
+      <c r="H193" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan daftar nasabah yang closing pada Daily Sales Agenda.</t>
+        </is>
+      </c>
+      <c r="I193" s="49" t="n"/>
+      <c r="J193" s="49" t="n"/>
+      <c r="K193" s="49" t="n"/>
+      <c r="L193" s="49" t="n"/>
+      <c r="M193" s="49" t="n"/>
+      <c r="N193" s="49" t="n"/>
+      <c r="O193" s="49" t="n"/>
+      <c r="P193" s="49" t="n"/>
+      <c r="Q193" s="49" t="n"/>
+      <c r="R193" s="49" t="n"/>
+      <c r="S193" s="49" t="n"/>
+      <c r="T193" s="49" t="n"/>
+      <c r="U193" s="49" t="n"/>
+      <c r="V193" s="49" t="n"/>
+      <c r="W193" s="49" t="n"/>
+      <c r="X193" s="49" t="n"/>
+      <c r="Y193" s="49" t="n"/>
+      <c r="Z193" s="49" t="n"/>
+      <c r="AA193" s="49" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="B194" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C194" s="46" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D194" s="48" t="inlineStr">
+        <is>
+          <t>Melihat daftar agenda pada tab Referral</t>
+        </is>
+      </c>
+      <c r="E194" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F194" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G194" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik tab Referral.</t>
+        </is>
+      </c>
+      <c r="H194" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan daftar nasabah referral pada Daily Sales Agenda.</t>
+        </is>
+      </c>
+      <c r="I194" s="49" t="n"/>
+      <c r="J194" s="49" t="n"/>
+      <c r="K194" s="49" t="n"/>
+      <c r="L194" s="49" t="n"/>
+      <c r="M194" s="49" t="n"/>
+      <c r="N194" s="49" t="n"/>
+      <c r="O194" s="49" t="n"/>
+      <c r="P194" s="49" t="n"/>
+      <c r="Q194" s="49" t="n"/>
+      <c r="R194" s="49" t="n"/>
+      <c r="S194" s="49" t="n"/>
+      <c r="T194" s="49" t="n"/>
+      <c r="U194" s="49" t="n"/>
+      <c r="V194" s="49" t="n"/>
+      <c r="W194" s="49" t="n"/>
+      <c r="X194" s="49" t="n"/>
+      <c r="Y194" s="49" t="n"/>
+      <c r="Z194" s="49" t="n"/>
+      <c r="AA194" s="49" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="B195" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C195" s="46" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D195" s="48" t="inlineStr">
+        <is>
+          <t>Melihat daftar agenda pada tab Ref. Closing</t>
+        </is>
+      </c>
+      <c r="E195" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F195" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G195" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik tab Ref. Closing.</t>
+        </is>
+      </c>
+      <c r="H195" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan daftar nasabah referral yang closing pada Daily Sales Agenda.</t>
+        </is>
+      </c>
+      <c r="I195" s="49" t="n"/>
+      <c r="J195" s="49" t="n"/>
+      <c r="K195" s="49" t="n"/>
+      <c r="L195" s="49" t="n"/>
+      <c r="M195" s="49" t="n"/>
+      <c r="N195" s="49" t="n"/>
+      <c r="O195" s="49" t="n"/>
+      <c r="P195" s="49" t="n"/>
+      <c r="Q195" s="49" t="n"/>
+      <c r="R195" s="49" t="n"/>
+      <c r="S195" s="49" t="n"/>
+      <c r="T195" s="49" t="n"/>
+      <c r="U195" s="49" t="n"/>
+      <c r="V195" s="49" t="n"/>
+      <c r="W195" s="49" t="n"/>
+      <c r="X195" s="49" t="n"/>
+      <c r="Y195" s="49" t="n"/>
+      <c r="Z195" s="49" t="n"/>
+      <c r="AA195" s="49" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>16.6</t>
+        </is>
+      </c>
+      <c r="B196" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C196" s="46" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D196" s="48" t="inlineStr">
+        <is>
+          <t>Mencari agenda menggunakan Search Bar</t>
+        </is>
+      </c>
+      <c r="E196" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F196" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G196" s="48" t="inlineStr">
+        <is>
+          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
+        </is>
+      </c>
+      <c r="H196" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data agenda yang sesuai dengan kata kunci pencarian.</t>
+        </is>
+      </c>
+      <c r="I196" s="49" t="n"/>
+      <c r="J196" s="49" t="n"/>
+      <c r="K196" s="49" t="n"/>
+      <c r="L196" s="49" t="n"/>
+      <c r="M196" s="49" t="n"/>
+      <c r="N196" s="49" t="n"/>
+      <c r="O196" s="49" t="n"/>
+      <c r="P196" s="49" t="n"/>
+      <c r="Q196" s="49" t="n"/>
+      <c r="R196" s="49" t="n"/>
+      <c r="S196" s="49" t="n"/>
+      <c r="T196" s="49" t="n"/>
+      <c r="U196" s="49" t="n"/>
+      <c r="V196" s="49" t="n"/>
+      <c r="W196" s="49" t="n"/>
+      <c r="X196" s="49" t="n"/>
+      <c r="Y196" s="49" t="n"/>
+      <c r="Z196" s="49" t="n"/>
+      <c r="AA196" s="49" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="B197" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C197" s="46" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D197" s="48" t="inlineStr">
+        <is>
+          <t>Mencari agenda dengan keyword tidak valid</t>
+        </is>
+      </c>
+      <c r="E197" s="46" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F197" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G197" s="48" t="inlineStr">
+        <is>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+        </is>
+      </c>
+      <c r="H197" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+        </is>
+      </c>
+      <c r="I197" s="49" t="n"/>
+      <c r="J197" s="49" t="n"/>
+      <c r="K197" s="49" t="n"/>
+      <c r="L197" s="49" t="n"/>
+      <c r="M197" s="49" t="n"/>
+      <c r="N197" s="49" t="n"/>
+      <c r="O197" s="49" t="n"/>
+      <c r="P197" s="49" t="n"/>
+      <c r="Q197" s="49" t="n"/>
+      <c r="R197" s="49" t="n"/>
+      <c r="S197" s="49" t="n"/>
+      <c r="T197" s="49" t="n"/>
+      <c r="U197" s="49" t="n"/>
+      <c r="V197" s="49" t="n"/>
+      <c r="W197" s="49" t="n"/>
+      <c r="X197" s="49" t="n"/>
+      <c r="Y197" s="49" t="n"/>
+      <c r="Z197" s="49" t="n"/>
+      <c r="AA197" s="49" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
+      </c>
+      <c r="B198" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C198" s="46" t="inlineStr">
+        <is>
+          <t>Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="D198" s="48" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Daily Sales Agenda</t>
+        </is>
+      </c>
+      <c r="E198" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F198" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G198" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik button Filter.
+2. Pilih kriteria filter pada form Filter (Product, Bulan, Tahun).
+3. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H198" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka form Filter.
+2. Berhasil memilih kriteria filter.
+3. Berhasil menampilkan data Daily Sales Agenda sesuai filter yang dipilih.</t>
+        </is>
+      </c>
+      <c r="I198" s="49" t="n"/>
+      <c r="J198" s="49" t="n"/>
+      <c r="K198" s="49" t="n"/>
+      <c r="L198" s="49" t="n"/>
+      <c r="M198" s="49" t="n"/>
+      <c r="N198" s="49" t="n"/>
+      <c r="O198" s="49" t="n"/>
+      <c r="P198" s="49" t="n"/>
+      <c r="Q198" s="49" t="n"/>
+      <c r="R198" s="49" t="n"/>
+      <c r="S198" s="49" t="n"/>
+      <c r="T198" s="49" t="n"/>
+      <c r="U198" s="49" t="n"/>
+      <c r="V198" s="49" t="n"/>
+      <c r="W198" s="49" t="n"/>
+      <c r="X198" s="49" t="n"/>
+      <c r="Y198" s="49" t="n"/>
+      <c r="Z198" s="49" t="n"/>
+      <c r="AA198" s="49" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="B199" s="46" t="inlineStr">
+        <is>
+          <t>Fitur</t>
+        </is>
+      </c>
+      <c r="C199" s="46" t="inlineStr">
+        <is>
+          <t>Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="D199" s="48" t="inlineStr">
+        <is>
+          <t>Membuka halaman Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="E199" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F199" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G199" s="48" t="inlineStr">
+        <is>
+          <t>1. Buka menu Lainnya.
+2. Klik menu Marketing Toolkit.</t>
+        </is>
+      </c>
+      <c r="H199" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman Marketing Toolkit.</t>
+        </is>
+      </c>
+      <c r="I199" s="49" t="n"/>
+      <c r="J199" s="49" t="n"/>
+      <c r="K199" s="49" t="n"/>
+      <c r="L199" s="49" t="n"/>
+      <c r="M199" s="49" t="n"/>
+      <c r="N199" s="49" t="n"/>
+      <c r="O199" s="49" t="n"/>
+      <c r="P199" s="49" t="n"/>
+      <c r="Q199" s="49" t="n"/>
+      <c r="R199" s="49" t="n"/>
+      <c r="S199" s="49" t="n"/>
+      <c r="T199" s="49" t="n"/>
+      <c r="U199" s="49" t="n"/>
+      <c r="V199" s="49" t="n"/>
+      <c r="W199" s="49" t="n"/>
+      <c r="X199" s="49" t="n"/>
+      <c r="Y199" s="49" t="n"/>
+      <c r="Z199" s="49" t="n"/>
+      <c r="AA199" s="49" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="B200" s="46" t="inlineStr">
+        <is>
+          <t>Fitur</t>
+        </is>
+      </c>
+      <c r="C200" s="46" t="inlineStr">
+        <is>
+          <t>Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="D200" s="48" t="inlineStr">
+        <is>
+          <t>Mengubah tampilan folder menjadi List View</t>
+        </is>
+      </c>
+      <c r="E200" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F200" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G200" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon tampilan List pada halaman Marketing Toolkit.</t>
+        </is>
+      </c>
+      <c r="H200" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengubah tampilan folder menjadi List View.</t>
+        </is>
+      </c>
+      <c r="I200" s="49" t="n"/>
+      <c r="J200" s="49" t="n"/>
+      <c r="K200" s="49" t="n"/>
+      <c r="L200" s="49" t="n"/>
+      <c r="M200" s="49" t="n"/>
+      <c r="N200" s="49" t="n"/>
+      <c r="O200" s="49" t="n"/>
+      <c r="P200" s="49" t="n"/>
+      <c r="Q200" s="49" t="n"/>
+      <c r="R200" s="49" t="n"/>
+      <c r="S200" s="49" t="n"/>
+      <c r="T200" s="49" t="n"/>
+      <c r="U200" s="49" t="n"/>
+      <c r="V200" s="49" t="n"/>
+      <c r="W200" s="49" t="n"/>
+      <c r="X200" s="49" t="n"/>
+      <c r="Y200" s="49" t="n"/>
+      <c r="Z200" s="49" t="n"/>
+      <c r="AA200" s="49" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="B201" s="46" t="inlineStr">
+        <is>
+          <t>Fitur</t>
+        </is>
+      </c>
+      <c r="C201" s="46" t="inlineStr">
+        <is>
+          <t>Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="D201" s="48" t="inlineStr">
+        <is>
+          <t>Mengubah tampilan folder menjadi Grid View</t>
+        </is>
+      </c>
+      <c r="E201" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F201" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G201" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon tampilan Grid pada halaman Marketing Toolkit.</t>
+        </is>
+      </c>
+      <c r="H201" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengubah tampilan folder menjadi Grid View.</t>
+        </is>
+      </c>
+      <c r="I201" s="49" t="n"/>
+      <c r="J201" s="49" t="n"/>
+      <c r="K201" s="49" t="n"/>
+      <c r="L201" s="49" t="n"/>
+      <c r="M201" s="49" t="n"/>
+      <c r="N201" s="49" t="n"/>
+      <c r="O201" s="49" t="n"/>
+      <c r="P201" s="49" t="n"/>
+      <c r="Q201" s="49" t="n"/>
+      <c r="R201" s="49" t="n"/>
+      <c r="S201" s="49" t="n"/>
+      <c r="T201" s="49" t="n"/>
+      <c r="U201" s="49" t="n"/>
+      <c r="V201" s="49" t="n"/>
+      <c r="W201" s="49" t="n"/>
+      <c r="X201" s="49" t="n"/>
+      <c r="Y201" s="49" t="n"/>
+      <c r="Z201" s="49" t="n"/>
+      <c r="AA201" s="49" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="B202" s="46" t="inlineStr">
+        <is>
+          <t>Fitur</t>
+        </is>
+      </c>
+      <c r="C202" s="46" t="inlineStr">
+        <is>
+          <t>Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="D202" s="48" t="inlineStr">
+        <is>
+          <t>Membuka folder pada Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="E202" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F202" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G202" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik salah satu folder pada daftar Folder.</t>
+        </is>
+      </c>
+      <c r="H202" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka folder Marketing Toolkit.</t>
+        </is>
+      </c>
+      <c r="I202" s="49" t="n"/>
+      <c r="J202" s="49" t="n"/>
+      <c r="K202" s="49" t="n"/>
+      <c r="L202" s="49" t="n"/>
+      <c r="M202" s="49" t="n"/>
+      <c r="N202" s="49" t="n"/>
+      <c r="O202" s="49" t="n"/>
+      <c r="P202" s="49" t="n"/>
+      <c r="Q202" s="49" t="n"/>
+      <c r="R202" s="49" t="n"/>
+      <c r="S202" s="49" t="n"/>
+      <c r="T202" s="49" t="n"/>
+      <c r="U202" s="49" t="n"/>
+      <c r="V202" s="49" t="n"/>
+      <c r="W202" s="49" t="n"/>
+      <c r="X202" s="49" t="n"/>
+      <c r="Y202" s="49" t="n"/>
+      <c r="Z202" s="49" t="n"/>
+      <c r="AA202" s="49" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="B203" s="46" t="inlineStr">
+        <is>
+          <t>Fitur</t>
+        </is>
+      </c>
+      <c r="C203" s="46" t="inlineStr">
+        <is>
+          <t>Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="D203" s="48" t="inlineStr">
+        <is>
+          <t>Mencari konten di dalam folder menggunakan Search Bar</t>
+        </is>
+      </c>
+      <c r="E203" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F203" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G203" s="48" t="inlineStr">
+        <is>
+          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
+        </is>
+      </c>
+      <c r="H203" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan data yang sesuai dengan kata kunci pencarian.</t>
+        </is>
+      </c>
+      <c r="I203" s="49" t="n"/>
+      <c r="J203" s="49" t="n"/>
+      <c r="K203" s="49" t="n"/>
+      <c r="L203" s="49" t="n"/>
+      <c r="M203" s="49" t="n"/>
+      <c r="N203" s="49" t="n"/>
+      <c r="O203" s="49" t="n"/>
+      <c r="P203" s="49" t="n"/>
+      <c r="Q203" s="49" t="n"/>
+      <c r="R203" s="49" t="n"/>
+      <c r="S203" s="49" t="n"/>
+      <c r="T203" s="49" t="n"/>
+      <c r="U203" s="49" t="n"/>
+      <c r="V203" s="49" t="n"/>
+      <c r="W203" s="49" t="n"/>
+      <c r="X203" s="49" t="n"/>
+      <c r="Y203" s="49" t="n"/>
+      <c r="Z203" s="49" t="n"/>
+      <c r="AA203" s="49" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="B204" s="46" t="inlineStr">
+        <is>
+          <t>Fitur</t>
+        </is>
+      </c>
+      <c r="C204" s="46" t="inlineStr">
+        <is>
+          <t>Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="D204" s="48" t="inlineStr">
+        <is>
+          <t>Mencari konten di dalam folder dengan keyword tidak valid</t>
+        </is>
+      </c>
+      <c r="E204" s="46" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F204" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G204" s="48" t="inlineStr">
+        <is>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+        </is>
+      </c>
+      <c r="H204" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+        </is>
+      </c>
+      <c r="I204" s="49" t="n"/>
+      <c r="J204" s="49" t="n"/>
+      <c r="K204" s="49" t="n"/>
+      <c r="L204" s="49" t="n"/>
+      <c r="M204" s="49" t="n"/>
+      <c r="N204" s="49" t="n"/>
+      <c r="O204" s="49" t="n"/>
+      <c r="P204" s="49" t="n"/>
+      <c r="Q204" s="49" t="n"/>
+      <c r="R204" s="49" t="n"/>
+      <c r="S204" s="49" t="n"/>
+      <c r="T204" s="49" t="n"/>
+      <c r="U204" s="49" t="n"/>
+      <c r="V204" s="49" t="n"/>
+      <c r="W204" s="49" t="n"/>
+      <c r="X204" s="49" t="n"/>
+      <c r="Y204" s="49" t="n"/>
+      <c r="Z204" s="49" t="n"/>
+      <c r="AA204" s="49" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="B205" s="46" t="inlineStr">
+        <is>
+          <t>Fitur</t>
+        </is>
+      </c>
+      <c r="C205" s="46" t="inlineStr">
+        <is>
+          <t>Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="D205" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail konten Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="E205" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F205" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G205" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik salah satu sub-folder pada daftar folder.</t>
+        </is>
+      </c>
+      <c r="H205" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail konten Marketing Toolkit.</t>
+        </is>
+      </c>
+      <c r="I205" s="49" t="n"/>
+      <c r="J205" s="49" t="n"/>
+      <c r="K205" s="49" t="n"/>
+      <c r="L205" s="49" t="n"/>
+      <c r="M205" s="49" t="n"/>
+      <c r="N205" s="49" t="n"/>
+      <c r="O205" s="49" t="n"/>
+      <c r="P205" s="49" t="n"/>
+      <c r="Q205" s="49" t="n"/>
+      <c r="R205" s="49" t="n"/>
+      <c r="S205" s="49" t="n"/>
+      <c r="T205" s="49" t="n"/>
+      <c r="U205" s="49" t="n"/>
+      <c r="V205" s="49" t="n"/>
+      <c r="W205" s="49" t="n"/>
+      <c r="X205" s="49" t="n"/>
+      <c r="Y205" s="49" t="n"/>
+      <c r="Z205" s="49" t="n"/>
+      <c r="AA205" s="49" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="B206" s="46" t="inlineStr">
+        <is>
+          <t>Fitur</t>
+        </is>
+      </c>
+      <c r="C206" s="46" t="inlineStr">
+        <is>
+          <t>Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="D206" s="48" t="inlineStr">
+        <is>
+          <t>Mengunduh lampiran pada konten Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="E206" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F206" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G206" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon titik tiga pada salah satu lampiran.
+2. Pilih Download.</t>
+        </is>
+      </c>
+      <c r="H206" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan opsi aksi pada lampiran.
+2. Berhasil mengunduh lampiran ke perangkat.</t>
+        </is>
+      </c>
+      <c r="I206" s="49" t="n"/>
+      <c r="J206" s="49" t="n"/>
+      <c r="K206" s="49" t="n"/>
+      <c r="L206" s="49" t="n"/>
+      <c r="M206" s="49" t="n"/>
+      <c r="N206" s="49" t="n"/>
+      <c r="O206" s="49" t="n"/>
+      <c r="P206" s="49" t="n"/>
+      <c r="Q206" s="49" t="n"/>
+      <c r="R206" s="49" t="n"/>
+      <c r="S206" s="49" t="n"/>
+      <c r="T206" s="49" t="n"/>
+      <c r="U206" s="49" t="n"/>
+      <c r="V206" s="49" t="n"/>
+      <c r="W206" s="49" t="n"/>
+      <c r="X206" s="49" t="n"/>
+      <c r="Y206" s="49" t="n"/>
+      <c r="Z206" s="49" t="n"/>
+      <c r="AA206" s="49" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="B207" s="46" t="inlineStr">
+        <is>
+          <t>Fitur</t>
+        </is>
+      </c>
+      <c r="C207" s="46" t="inlineStr">
+        <is>
+          <t>Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="D207" s="48" t="inlineStr">
+        <is>
+          <t>Berbagi lampiran pada konten Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="E207" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F207" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G207" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon titik tiga pada salah satu lampiran.
+2. Pilih Share.</t>
+        </is>
+      </c>
+      <c r="H207" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan opsi aksi pada lampiran.
+2. Berhasil menampilkan pilihan aplikasi berbagi.</t>
+        </is>
+      </c>
+      <c r="I207" s="49" t="n"/>
+      <c r="J207" s="49" t="n"/>
+      <c r="K207" s="49" t="n"/>
+      <c r="L207" s="49" t="n"/>
+      <c r="M207" s="49" t="n"/>
+      <c r="N207" s="49" t="n"/>
+      <c r="O207" s="49" t="n"/>
+      <c r="P207" s="49" t="n"/>
+      <c r="Q207" s="49" t="n"/>
+      <c r="R207" s="49" t="n"/>
+      <c r="S207" s="49" t="n"/>
+      <c r="T207" s="49" t="n"/>
+      <c r="U207" s="49" t="n"/>
+      <c r="V207" s="49" t="n"/>
+      <c r="W207" s="49" t="n"/>
+      <c r="X207" s="49" t="n"/>
+      <c r="Y207" s="49" t="n"/>
+      <c r="Z207" s="49" t="n"/>
+      <c r="AA207" s="49" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="B208" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C208" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D208" s="48" t="inlineStr">
+        <is>
+          <t>Membuka halaman Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="E208" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F208" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G208" s="48" t="inlineStr">
+        <is>
+          <t>1. Buka menu Lainnya.
+2. Klik menu Dashboard Sales Code.</t>
+        </is>
+      </c>
+      <c r="H208" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman Dashboard Sales Code.</t>
+        </is>
+      </c>
+      <c r="I208" s="49" t="n"/>
+      <c r="J208" s="49" t="n"/>
+      <c r="K208" s="49" t="n"/>
+      <c r="L208" s="49" t="n"/>
+      <c r="M208" s="49" t="n"/>
+      <c r="N208" s="49" t="n"/>
+      <c r="O208" s="49" t="n"/>
+      <c r="P208" s="49" t="n"/>
+      <c r="Q208" s="49" t="n"/>
+      <c r="R208" s="49" t="n"/>
+      <c r="S208" s="49" t="n"/>
+      <c r="T208" s="49" t="n"/>
+      <c r="U208" s="49" t="n"/>
+      <c r="V208" s="49" t="n"/>
+      <c r="W208" s="49" t="n"/>
+      <c r="X208" s="49" t="n"/>
+      <c r="Y208" s="49" t="n"/>
+      <c r="Z208" s="49" t="n"/>
+      <c r="AA208" s="49" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="B209" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C209" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D209" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail Voa Realization</t>
+        </is>
+      </c>
+      <c r="E209" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F209" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G209" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon expand pada card Voa Realization.</t>
+        </is>
+      </c>
+      <c r="H209" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail Voa Realization.</t>
+        </is>
+      </c>
+      <c r="I209" s="49" t="n"/>
+      <c r="J209" s="49" t="n"/>
+      <c r="K209" s="49" t="n"/>
+      <c r="L209" s="49" t="n"/>
+      <c r="M209" s="49" t="n"/>
+      <c r="N209" s="49" t="n"/>
+      <c r="O209" s="49" t="n"/>
+      <c r="P209" s="49" t="n"/>
+      <c r="Q209" s="49" t="n"/>
+      <c r="R209" s="49" t="n"/>
+      <c r="S209" s="49" t="n"/>
+      <c r="T209" s="49" t="n"/>
+      <c r="U209" s="49" t="n"/>
+      <c r="V209" s="49" t="n"/>
+      <c r="W209" s="49" t="n"/>
+      <c r="X209" s="49" t="n"/>
+      <c r="Y209" s="49" t="n"/>
+      <c r="Z209" s="49" t="n"/>
+      <c r="AA209" s="49" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="B210" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C210" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D210" s="48" t="inlineStr">
+        <is>
+          <t>Melihat Daftar Pipeline pada Voa Realization</t>
+        </is>
+      </c>
+      <c r="E210" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F210" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G210" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon expand pada card Voa Realization.
+2. Klik Lihat Daftar Pipeline.</t>
+        </is>
+      </c>
+      <c r="H210" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail Voa Realization.
+2. Berhasil menampilkan Daftar Pipeline.</t>
+        </is>
+      </c>
+      <c r="I210" s="49" t="n"/>
+      <c r="J210" s="49" t="n"/>
+      <c r="K210" s="49" t="n"/>
+      <c r="L210" s="49" t="n"/>
+      <c r="M210" s="49" t="n"/>
+      <c r="N210" s="49" t="n"/>
+      <c r="O210" s="49" t="n"/>
+      <c r="P210" s="49" t="n"/>
+      <c r="Q210" s="49" t="n"/>
+      <c r="R210" s="49" t="n"/>
+      <c r="S210" s="49" t="n"/>
+      <c r="T210" s="49" t="n"/>
+      <c r="U210" s="49" t="n"/>
+      <c r="V210" s="49" t="n"/>
+      <c r="W210" s="49" t="n"/>
+      <c r="X210" s="49" t="n"/>
+      <c r="Y210" s="49" t="n"/>
+      <c r="Z210" s="49" t="n"/>
+      <c r="AA210" s="49" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="B211" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C211" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D211" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail CIF Kelolaan</t>
+        </is>
+      </c>
+      <c r="E211" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F211" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G211" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon expand pada card CIF Kelolaan.</t>
+        </is>
+      </c>
+      <c r="H211" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail CIF Kelolaan.</t>
+        </is>
+      </c>
+      <c r="I211" s="49" t="n"/>
+      <c r="J211" s="49" t="n"/>
+      <c r="K211" s="49" t="n"/>
+      <c r="L211" s="49" t="n"/>
+      <c r="M211" s="49" t="n"/>
+      <c r="N211" s="49" t="n"/>
+      <c r="O211" s="49" t="n"/>
+      <c r="P211" s="49" t="n"/>
+      <c r="Q211" s="49" t="n"/>
+      <c r="R211" s="49" t="n"/>
+      <c r="S211" s="49" t="n"/>
+      <c r="T211" s="49" t="n"/>
+      <c r="U211" s="49" t="n"/>
+      <c r="V211" s="49" t="n"/>
+      <c r="W211" s="49" t="n"/>
+      <c r="X211" s="49" t="n"/>
+      <c r="Y211" s="49" t="n"/>
+      <c r="Z211" s="49" t="n"/>
+      <c r="AA211" s="49" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="B212" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C212" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D212" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail Realisasi Konek E-Channel</t>
+        </is>
+      </c>
+      <c r="E212" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F212" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G212" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon expand pada card Realisasi Konek E-Channel.</t>
+        </is>
+      </c>
+      <c r="H212" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail Realisasi Konek E-Channel.</t>
+        </is>
+      </c>
+      <c r="I212" s="49" t="n"/>
+      <c r="J212" s="49" t="n"/>
+      <c r="K212" s="49" t="n"/>
+      <c r="L212" s="49" t="n"/>
+      <c r="M212" s="49" t="n"/>
+      <c r="N212" s="49" t="n"/>
+      <c r="O212" s="49" t="n"/>
+      <c r="P212" s="49" t="n"/>
+      <c r="Q212" s="49" t="n"/>
+      <c r="R212" s="49" t="n"/>
+      <c r="S212" s="49" t="n"/>
+      <c r="T212" s="49" t="n"/>
+      <c r="U212" s="49" t="n"/>
+      <c r="V212" s="49" t="n"/>
+      <c r="W212" s="49" t="n"/>
+      <c r="X212" s="49" t="n"/>
+      <c r="Y212" s="49" t="n"/>
+      <c r="Z212" s="49" t="n"/>
+      <c r="AA212" s="49" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="B213" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C213" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D213" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail Realisasi Akuisisi Merchant</t>
+        </is>
+      </c>
+      <c r="E213" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F213" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G213" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon expand pada card Realisasi Akuisisi Merchant.</t>
+        </is>
+      </c>
+      <c r="H213" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail Realisasi Akuisisi Merchant.</t>
+        </is>
+      </c>
+      <c r="I213" s="49" t="n"/>
+      <c r="J213" s="49" t="n"/>
+      <c r="K213" s="49" t="n"/>
+      <c r="L213" s="49" t="n"/>
+      <c r="M213" s="49" t="n"/>
+      <c r="N213" s="49" t="n"/>
+      <c r="O213" s="49" t="n"/>
+      <c r="P213" s="49" t="n"/>
+      <c r="Q213" s="49" t="n"/>
+      <c r="R213" s="49" t="n"/>
+      <c r="S213" s="49" t="n"/>
+      <c r="T213" s="49" t="n"/>
+      <c r="U213" s="49" t="n"/>
+      <c r="V213" s="49" t="n"/>
+      <c r="W213" s="49" t="n"/>
+      <c r="X213" s="49" t="n"/>
+      <c r="Y213" s="49" t="n"/>
+      <c r="Z213" s="49" t="n"/>
+      <c r="AA213" s="49" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="B214" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C214" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D214" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail Eligible Upgrade to Prospera/Prioritas</t>
+        </is>
+      </c>
+      <c r="E214" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F214" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G214" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon expand pada card Eligible Upgrade to Prospera/Prioritas.</t>
+        </is>
+      </c>
+      <c r="H214" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail Eligible Upgrade to Prospera &amp; Prioritas.</t>
+        </is>
+      </c>
+      <c r="I214" s="49" t="n"/>
+      <c r="J214" s="49" t="n"/>
+      <c r="K214" s="49" t="n"/>
+      <c r="L214" s="49" t="n"/>
+      <c r="M214" s="49" t="n"/>
+      <c r="N214" s="49" t="n"/>
+      <c r="O214" s="49" t="n"/>
+      <c r="P214" s="49" t="n"/>
+      <c r="Q214" s="49" t="n"/>
+      <c r="R214" s="49" t="n"/>
+      <c r="S214" s="49" t="n"/>
+      <c r="T214" s="49" t="n"/>
+      <c r="U214" s="49" t="n"/>
+      <c r="V214" s="49" t="n"/>
+      <c r="W214" s="49" t="n"/>
+      <c r="X214" s="49" t="n"/>
+      <c r="Y214" s="49" t="n"/>
+      <c r="Z214" s="49" t="n"/>
+      <c r="AA214" s="49" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -683,7 +683,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z982"/>
+  <dimension ref="A1:Z994"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="12.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -43630,18 +43630,510 @@
         </is>
       </c>
     </row>
-    <row r="983" ht="28" customHeight="1"/>
-    <row r="984" ht="140" customHeight="1"/>
-    <row r="985" ht="14" customHeight="1"/>
-    <row r="986" ht="14" customHeight="1"/>
-    <row r="987" ht="42" customHeight="1"/>
-    <row r="988" ht="14" customHeight="1"/>
-    <row r="989" ht="70" customHeight="1"/>
-    <row r="990" ht="168" customHeight="1"/>
-    <row r="991" ht="14" customHeight="1"/>
-    <row r="992" ht="14" customHeight="1"/>
-    <row r="993" ht="70" customHeight="1"/>
-    <row r="994" ht="28" customHeight="1"/>
+    <row r="983" ht="28" customHeight="1">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>15.11</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Bisnis dan Produk</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Group Produk</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Melakukan validasi data hasil export</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>Hasil yang diharapkan [STATUS]: Data pada excel sesuai dengan data pada tabel – [Success]</t>
+        </is>
+      </c>
+    </row>
+    <row r="984" ht="140" customHeight="1">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Upload Bulk</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Upload Target Bulk</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Menampilkan detail batch</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>Hasil yang diharapkan [STATUS]: Berhasil menampilkan data detail – [Success]</t>
+        </is>
+      </c>
+    </row>
+    <row r="985" ht="14" customHeight="1">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Upload Bulk</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Upload Target Bulk</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Download source File</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>Hasil yang diharapkan [STATUS]: Data source berhasil didownload – [Success]</t>
+        </is>
+      </c>
+    </row>
+    <row r="986" ht="14" customHeight="1">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Upload Bulk</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Upload Target Bulk</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Menampilkan preview data</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>Hasil yang diharapkan [STATUS]: Berhasil menampilkan detail data hasil upload dan penjelasan jika terdapat validasi error pada file yang diupload – [Success]</t>
+        </is>
+      </c>
+    </row>
+    <row r="987" ht="42" customHeight="1">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>23.9</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Upload Bulk</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Upload Target Bulk</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Menghapus batch data</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>Hasil yang diharapkan [STATUS]: Data berhasil dihapus – [Success]</t>
+        </is>
+      </c>
+    </row>
+    <row r="988" ht="14" customHeight="1">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>23.10</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Upload Bulk</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Upload Target Bulk</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Download error file</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>Hasil yang diharapkan [STATUS]: Berhasil mendownload error file – [Success]</t>
+        </is>
+      </c>
+    </row>
+    <row r="989" ht="70" customHeight="1">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>23.11</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Upload Bulk</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Upload Target Bulk</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Batalkan batch</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>Hasil yang diharapkan [STATUS]: Berhasil membatalkan batch – [Success]</t>
+        </is>
+      </c>
+    </row>
+    <row r="990" ht="168" customHeight="1">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>23.12</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Upload Bulk</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Upload Target Bulk</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>Upload ulang file gagal</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>Hasil yang diharapkan [STATUS]: Berhasil mengupload ulang file– [Success]</t>
+        </is>
+      </c>
+    </row>
+    <row r="991" ht="14" customHeight="1">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>46.16</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Approval Target Growth</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>Mencari data kata kunci yang tidak sesuai</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>Hasil yang diharapkan [STATUS]: Data tidak ditemukan – [Success]</t>
+        </is>
+      </c>
+    </row>
+    <row r="992" ht="14" customHeight="1">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Approval Sales Code</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Melihat detail data</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>Hasil yang diharapkan [STATUS]: Berhasil menampilkan detail data – [Success]</t>
+        </is>
+      </c>
+    </row>
+    <row r="993" ht="70" customHeight="1">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>47.8</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Approval Sales Code</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>Mencari data kata kunci invalid</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>Hasil yang diharapkan [STATUS]: Data tidak ditemukan – [Success]</t>
+        </is>
+      </c>
+    </row>
+    <row r="994" ht="28" customHeight="1">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>58.7</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Pipeline - Setting Validate Pipeline</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Mencari data kata kunci tidak valid (Negative test)</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>Hasil yang diharapkan [STATUS]: Data Tidak ditemukan – [Success]</t>
+        </is>
+      </c>
+    </row>
     <row r="995" ht="28" customHeight="1"/>
     <row r="996" ht="42" customHeight="1"/>
     <row r="997" ht="42" customHeight="1"/>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -49149,7 +49149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA214"/>
+  <dimension ref="A1:AA222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59670,14 +59670,14 @@
       </c>
       <c r="G185" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Pengingat.</t>
+          <t>1. Buka menu Lainnya pada Aksi Cepat di Beranda.
+2. Klik menu Pengingat pada kelompok Agenda.</t>
         </is>
       </c>
       <c r="H185" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Pengingat.</t>
+2. Berhasil menampilkan halaman Pengingat beserta daftar tugas pada tab default (Task).</t>
         </is>
       </c>
       <c r="I185" s="49" t="n"/>
@@ -59718,7 +59718,7 @@
       </c>
       <c r="D186" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar pengingat pada tab Aktif</t>
+          <t>Melihat daftar agenda pada tab Acara</t>
         </is>
       </c>
       <c r="E186" s="46" t="inlineStr">
@@ -59733,12 +59733,13 @@
       </c>
       <c r="G186" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Aktif.</t>
+          <t>1. Pada halaman Pengingat, klik tab Acara.</t>
         </is>
       </c>
       <c r="H186" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar pengingat yang sedang aktif.</t>
+          <t>1. Berhasil berpindah ke tab Acara.
+2. Berhasil menampilkan daftar acara yang terdaftar pada tab Acara.</t>
         </is>
       </c>
       <c r="I186" s="49" t="n"/>
@@ -59779,7 +59780,7 @@
       </c>
       <c r="D187" s="48" t="inlineStr">
         <is>
-          <t>Melihat daftar pengingat pada tab Selesai</t>
+          <t>Melihat detail task</t>
         </is>
       </c>
       <c r="E187" s="46" t="inlineStr">
@@ -59789,17 +59790,18 @@
       </c>
       <c r="F187" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G187" s="48" t="inlineStr">
         <is>
-          <t>1. Klik tab Selesai.</t>
+          <t>1. Pada tab Task, klik salah satu card task yang terdaftar.</t>
         </is>
       </c>
       <c r="H187" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan daftar pengingat yang sudah selesai.</t>
+          <t>1. Berhasil membuka halaman Detail Task.
+2. Berhasil menampilkan informasi status, visibilitas, prioritas, tenggat, zona waktu, pemilik, deskripsi, dan lampiran.</t>
         </is>
       </c>
       <c r="I187" s="49" t="n"/>
@@ -59840,7 +59842,7 @@
       </c>
       <c r="D188" s="48" t="inlineStr">
         <is>
-          <t>Menambahkan pengingat baru dengan data valid</t>
+          <t>Mengubah data task dengan data valid</t>
         </is>
       </c>
       <c r="E188" s="46" t="inlineStr">
@@ -59855,16 +59857,15 @@
       </c>
       <c r="G188" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button + Baru.
-2. Mengisi seluruh field mandatory pada form Tambah Pengingat dengan data valid.
+          <t>1. Pada halaman Detail Task, klik icon Edit (pensil).
+2. Ubah data task pada form Edit Task.
 3. Klik button Simpan.</t>
         </is>
       </c>
       <c r="H188" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka form Tambah Pengingat.
-2. Berhasil mengisi seluruh field mandatory pada form Tambah Pengingat.
-3. Berhasil menyimpan pengingat dan menampilkan pengingat baru pada daftar.</t>
+          <t>1. Berhasil membuka form Edit Task.
+2. Berhasil menyimpan perubahan data task dengan data yang valid.</t>
         </is>
       </c>
       <c r="I188" s="49" t="n"/>
@@ -59905,31 +59906,30 @@
       </c>
       <c r="D189" s="48" t="inlineStr">
         <is>
-          <t>Menambahkan pengingat baru tanpa mengisi field mandatory</t>
+          <t>Membagikan task kepada user</t>
         </is>
       </c>
       <c r="E189" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F189" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G189" s="48" t="inlineStr">
         <is>
-          <t>1. Klik button + Baru.
-2. Mengosongkan seluruh field mandatory pada form Tambah Pengingat.
-3. Klik button Simpan.</t>
+          <t>1. Pada halaman Detail Task, klik icon Bagikan (share).
+2. Pilih role atau user yang ditugaskan.
+3. Klik button Bagikan.</t>
         </is>
       </c>
       <c r="H189" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka form Tambah Pengingat.
-2. Field mandatory berhasil dikosongkan.
-3. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+          <t>1. Berhasil membuka form Bagikan Task.
+2. Berhasil membagikan task kepada user dan menampilkan pesan konfirmasi Task berhasil dibagikan.</t>
         </is>
       </c>
       <c r="I189" s="49" t="n"/>
@@ -59970,7 +59970,7 @@
       </c>
       <c r="D190" s="48" t="inlineStr">
         <is>
-          <t>Menandai pengingat sebagai selesai</t>
+          <t>Menghapus penugasan task kepada user</t>
         </is>
       </c>
       <c r="E190" s="46" t="inlineStr">
@@ -59985,14 +59985,15 @@
       </c>
       <c r="G190" s="48" t="inlineStr">
         <is>
-          <t>1. Centang checkbox pada salah satu card pengingat aktif.
-2. Klik button Ya pada pop-up konfirmasi.</t>
+          <t>1. Pada form Bagikan Task, periksa daftar Ditugaskan ke (User).
+2. Klik icon hapus (tempat sampah) pada user yang ditugaskan.
+3. Konfirmasi penghapusan penugasan task.</t>
         </is>
       </c>
       <c r="H190" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan pop-up konfirmasi selesai.
-2. Berhasil menandai pengingat sebagai selesai dan memindahkan pengingat ke tab Selesai.</t>
+          <t>1. Berhasil menampilkan dialog konfirmasi penghapusan penugasan.
+2. Berhasil menghapus penugasan task kepada user dari daftar pembagian task.</t>
         </is>
       </c>
       <c r="I190" s="49" t="n"/>
@@ -60018,538 +60019,402 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
+          <t>15.7</t>
+        </is>
+      </c>
+      <c r="B191" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C191" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D191" s="48" t="inlineStr">
+        <is>
+          <t>Menambahkan komentar pada task</t>
+        </is>
+      </c>
+      <c r="E191" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F191" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G191" s="48" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Task, klik tab Aktivitas &amp; Percakapan.
+2. Tulis komentar pada kolom Tulis komentar.
+3. Klik button Kirim.</t>
+        </is>
+      </c>
+      <c r="H191" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menginput teks komentar.
+2. Berhasil mengirimkan komentar dan menampilkan komentar baru pada daftar riwayat aktivitas task.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="B192" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C192" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D192" s="48" t="inlineStr">
+        <is>
+          <t>Menghapus komentar pada task</t>
+        </is>
+      </c>
+      <c r="E192" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F192" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G192" s="48" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Task, klik tab Aktivitas &amp; Percakapan.
+2. Klik icon hapus (tempat sampah) pada komentar yang ingin dihapus.
+3. Konfirmasi penghapusan komentar.</t>
+        </is>
+      </c>
+      <c r="H192" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan dialog konfirmasi penghapusan komentar.
+2. Berhasil menghapus komentar dari daftar aktivitas dan percakapan task.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>15.9</t>
+        </is>
+      </c>
+      <c r="B193" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C193" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D193" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail acara</t>
+        </is>
+      </c>
+      <c r="E193" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F193" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G193" s="48" t="inlineStr">
+        <is>
+          <t>1. Pada tab Acara, klik salah satu card acara yang terdaftar.</t>
+        </is>
+      </c>
+      <c r="H193" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka halaman Detail Acara.
+2. Berhasil menampilkan informasi status, visibilitas, tanggal/waktu mulai &amp; selesai, zona waktu, dan pemilik acara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>15.10</t>
+        </is>
+      </c>
+      <c r="B194" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C194" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D194" s="48" t="inlineStr">
+        <is>
+          <t>Mengubah data acara dengan data valid</t>
+        </is>
+      </c>
+      <c r="E194" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F194" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G194" s="48" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Acara, klik icon Edit (pensil).
+2. Ubah data acara pada form Edit Acara.
+3. Klik button Simpan.</t>
+        </is>
+      </c>
+      <c r="H194" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka form Edit Acara.
+2. Berhasil menyimpan perubahan data acara dengan data yang valid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>15.11</t>
+        </is>
+      </c>
+      <c r="B195" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C195" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D195" s="48" t="inlineStr">
+        <is>
+          <t>Membagikan acara kepada user</t>
+        </is>
+      </c>
+      <c r="E195" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F195" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G195" s="48" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Acara, klik icon Bagikan (share).
+2. Tentukan user watcher/assignee pada form Bagikan Acara.
+3. Klik button Bagikan.</t>
+        </is>
+      </c>
+      <c r="H195" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka form Bagikan Acara.
+2. Berhasil membagikan acara kepada user dan memicu notifikasi kepada penerima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>15.12</t>
+        </is>
+      </c>
+      <c r="B196" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C196" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D196" s="48" t="inlineStr">
+        <is>
+          <t>Menghapus penugasan acara kepada user</t>
+        </is>
+      </c>
+      <c r="E196" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F196" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G196" s="48" t="inlineStr">
+        <is>
+          <t>1. Pada form Bagikan Acara, periksa daftar Ditugaskan ke (User).
+2. Klik icon hapus (tempat sampah) pada user yang ditugaskan.
+3. Konfirmasi penghapusan penugasan acara.</t>
+        </is>
+      </c>
+      <c r="H196" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan dialog konfirmasi penghapusan penugasan.
+2. Berhasil menghapus penugasan acara kepada user dari daftar pembagian acara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>15.13</t>
+        </is>
+      </c>
+      <c r="B197" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C197" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D197" s="48" t="inlineStr">
+        <is>
+          <t>Menambahkan komentar pada acara</t>
+        </is>
+      </c>
+      <c r="E197" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F197" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G197" s="48" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Acara, klik tab Aktivitas &amp; Percakapan.
+2. Tulis komentar pada kolom Tulis komentar.
+3. Klik button Kirim.</t>
+        </is>
+      </c>
+      <c r="H197" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menginput teks komentar.
+2. Berhasil mengirimkan komentar dan menampilkan komentar baru pada daftar riwayat aktivitas acara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>15.14</t>
+        </is>
+      </c>
+      <c r="B198" s="46" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="C198" s="46" t="inlineStr">
+        <is>
+          <t>Pengingat</t>
+        </is>
+      </c>
+      <c r="D198" s="48" t="inlineStr">
+        <is>
+          <t>Menghapus komentar pada acara</t>
+        </is>
+      </c>
+      <c r="E198" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F198" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G198" s="48" t="inlineStr">
+        <is>
+          <t>1. Pada halaman Detail Acara, klik tab Aktivitas &amp; Percakapan.
+2. Klik icon hapus (tempat sampah) pada komentar yang ingin dihapus.
+3. Konfirmasi penghapusan komentar.</t>
+        </is>
+      </c>
+      <c r="H198" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan dialog konfirmasi penghapusan komentar.
+2. Berhasil menghapus komentar dari daftar aktivitas dan percakapan acara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
           <t>16.1</t>
         </is>
       </c>
-      <c r="B191" s="46" t="inlineStr">
+      <c r="B199" s="46" t="inlineStr">
         <is>
           <t>Agenda</t>
         </is>
       </c>
-      <c r="C191" s="46" t="inlineStr">
+      <c r="C199" s="46" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D191" s="48" t="inlineStr">
+      <c r="D199" s="48" t="inlineStr">
         <is>
           <t>Membuka halaman Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="E191" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F191" s="46" t="inlineStr">
+      <c r="E199" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F199" s="46" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G191" s="48" t="inlineStr">
+      <c r="G199" s="48" t="inlineStr">
         <is>
           <t>1. Buka menu Lainnya.
 2. Klik menu Daily Sales Agenda.</t>
         </is>
       </c>
-      <c r="H191" s="48" t="inlineStr">
+      <c r="H199" s="48" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Lainnya.
 2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
-        </is>
-      </c>
-      <c r="I191" s="49" t="n"/>
-      <c r="J191" s="49" t="n"/>
-      <c r="K191" s="49" t="n"/>
-      <c r="L191" s="49" t="n"/>
-      <c r="M191" s="49" t="n"/>
-      <c r="N191" s="49" t="n"/>
-      <c r="O191" s="49" t="n"/>
-      <c r="P191" s="49" t="n"/>
-      <c r="Q191" s="49" t="n"/>
-      <c r="R191" s="49" t="n"/>
-      <c r="S191" s="49" t="n"/>
-      <c r="T191" s="49" t="n"/>
-      <c r="U191" s="49" t="n"/>
-      <c r="V191" s="49" t="n"/>
-      <c r="W191" s="49" t="n"/>
-      <c r="X191" s="49" t="n"/>
-      <c r="Y191" s="49" t="n"/>
-      <c r="Z191" s="49" t="n"/>
-      <c r="AA191" s="49" t="n"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
-      </c>
-      <c r="B192" s="46" t="inlineStr">
-        <is>
-          <t>Agenda</t>
-        </is>
-      </c>
-      <c r="C192" s="46" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D192" s="48" t="inlineStr">
-        <is>
-          <t>Melihat daftar agenda pada tab Masuk</t>
-        </is>
-      </c>
-      <c r="E192" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F192" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G192" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik tab Masuk.</t>
-        </is>
-      </c>
-      <c r="H192" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan daftar nasabah yang masuk pada Daily Sales Agenda.</t>
-        </is>
-      </c>
-      <c r="I192" s="49" t="n"/>
-      <c r="J192" s="49" t="n"/>
-      <c r="K192" s="49" t="n"/>
-      <c r="L192" s="49" t="n"/>
-      <c r="M192" s="49" t="n"/>
-      <c r="N192" s="49" t="n"/>
-      <c r="O192" s="49" t="n"/>
-      <c r="P192" s="49" t="n"/>
-      <c r="Q192" s="49" t="n"/>
-      <c r="R192" s="49" t="n"/>
-      <c r="S192" s="49" t="n"/>
-      <c r="T192" s="49" t="n"/>
-      <c r="U192" s="49" t="n"/>
-      <c r="V192" s="49" t="n"/>
-      <c r="W192" s="49" t="n"/>
-      <c r="X192" s="49" t="n"/>
-      <c r="Y192" s="49" t="n"/>
-      <c r="Z192" s="49" t="n"/>
-      <c r="AA192" s="49" t="n"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="B193" s="46" t="inlineStr">
-        <is>
-          <t>Agenda</t>
-        </is>
-      </c>
-      <c r="C193" s="46" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D193" s="48" t="inlineStr">
-        <is>
-          <t>Melihat daftar agenda pada tab Closing</t>
-        </is>
-      </c>
-      <c r="E193" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F193" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G193" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik tab Closing.</t>
-        </is>
-      </c>
-      <c r="H193" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan daftar nasabah yang closing pada Daily Sales Agenda.</t>
-        </is>
-      </c>
-      <c r="I193" s="49" t="n"/>
-      <c r="J193" s="49" t="n"/>
-      <c r="K193" s="49" t="n"/>
-      <c r="L193" s="49" t="n"/>
-      <c r="M193" s="49" t="n"/>
-      <c r="N193" s="49" t="n"/>
-      <c r="O193" s="49" t="n"/>
-      <c r="P193" s="49" t="n"/>
-      <c r="Q193" s="49" t="n"/>
-      <c r="R193" s="49" t="n"/>
-      <c r="S193" s="49" t="n"/>
-      <c r="T193" s="49" t="n"/>
-      <c r="U193" s="49" t="n"/>
-      <c r="V193" s="49" t="n"/>
-      <c r="W193" s="49" t="n"/>
-      <c r="X193" s="49" t="n"/>
-      <c r="Y193" s="49" t="n"/>
-      <c r="Z193" s="49" t="n"/>
-      <c r="AA193" s="49" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
-      <c r="B194" s="46" t="inlineStr">
-        <is>
-          <t>Agenda</t>
-        </is>
-      </c>
-      <c r="C194" s="46" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D194" s="48" t="inlineStr">
-        <is>
-          <t>Melihat daftar agenda pada tab Referral</t>
-        </is>
-      </c>
-      <c r="E194" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F194" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G194" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik tab Referral.</t>
-        </is>
-      </c>
-      <c r="H194" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan daftar nasabah referral pada Daily Sales Agenda.</t>
-        </is>
-      </c>
-      <c r="I194" s="49" t="n"/>
-      <c r="J194" s="49" t="n"/>
-      <c r="K194" s="49" t="n"/>
-      <c r="L194" s="49" t="n"/>
-      <c r="M194" s="49" t="n"/>
-      <c r="N194" s="49" t="n"/>
-      <c r="O194" s="49" t="n"/>
-      <c r="P194" s="49" t="n"/>
-      <c r="Q194" s="49" t="n"/>
-      <c r="R194" s="49" t="n"/>
-      <c r="S194" s="49" t="n"/>
-      <c r="T194" s="49" t="n"/>
-      <c r="U194" s="49" t="n"/>
-      <c r="V194" s="49" t="n"/>
-      <c r="W194" s="49" t="n"/>
-      <c r="X194" s="49" t="n"/>
-      <c r="Y194" s="49" t="n"/>
-      <c r="Z194" s="49" t="n"/>
-      <c r="AA194" s="49" t="n"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>16.5</t>
-        </is>
-      </c>
-      <c r="B195" s="46" t="inlineStr">
-        <is>
-          <t>Agenda</t>
-        </is>
-      </c>
-      <c r="C195" s="46" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D195" s="48" t="inlineStr">
-        <is>
-          <t>Melihat daftar agenda pada tab Ref. Closing</t>
-        </is>
-      </c>
-      <c r="E195" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F195" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G195" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik tab Ref. Closing.</t>
-        </is>
-      </c>
-      <c r="H195" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan daftar nasabah referral yang closing pada Daily Sales Agenda.</t>
-        </is>
-      </c>
-      <c r="I195" s="49" t="n"/>
-      <c r="J195" s="49" t="n"/>
-      <c r="K195" s="49" t="n"/>
-      <c r="L195" s="49" t="n"/>
-      <c r="M195" s="49" t="n"/>
-      <c r="N195" s="49" t="n"/>
-      <c r="O195" s="49" t="n"/>
-      <c r="P195" s="49" t="n"/>
-      <c r="Q195" s="49" t="n"/>
-      <c r="R195" s="49" t="n"/>
-      <c r="S195" s="49" t="n"/>
-      <c r="T195" s="49" t="n"/>
-      <c r="U195" s="49" t="n"/>
-      <c r="V195" s="49" t="n"/>
-      <c r="W195" s="49" t="n"/>
-      <c r="X195" s="49" t="n"/>
-      <c r="Y195" s="49" t="n"/>
-      <c r="Z195" s="49" t="n"/>
-      <c r="AA195" s="49" t="n"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>16.6</t>
-        </is>
-      </c>
-      <c r="B196" s="46" t="inlineStr">
-        <is>
-          <t>Agenda</t>
-        </is>
-      </c>
-      <c r="C196" s="46" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D196" s="48" t="inlineStr">
-        <is>
-          <t>Mencari agenda menggunakan Search Bar</t>
-        </is>
-      </c>
-      <c r="E196" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F196" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G196" s="48" t="inlineStr">
-        <is>
-          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
-        </is>
-      </c>
-      <c r="H196" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan data agenda yang sesuai dengan kata kunci pencarian.</t>
-        </is>
-      </c>
-      <c r="I196" s="49" t="n"/>
-      <c r="J196" s="49" t="n"/>
-      <c r="K196" s="49" t="n"/>
-      <c r="L196" s="49" t="n"/>
-      <c r="M196" s="49" t="n"/>
-      <c r="N196" s="49" t="n"/>
-      <c r="O196" s="49" t="n"/>
-      <c r="P196" s="49" t="n"/>
-      <c r="Q196" s="49" t="n"/>
-      <c r="R196" s="49" t="n"/>
-      <c r="S196" s="49" t="n"/>
-      <c r="T196" s="49" t="n"/>
-      <c r="U196" s="49" t="n"/>
-      <c r="V196" s="49" t="n"/>
-      <c r="W196" s="49" t="n"/>
-      <c r="X196" s="49" t="n"/>
-      <c r="Y196" s="49" t="n"/>
-      <c r="Z196" s="49" t="n"/>
-      <c r="AA196" s="49" t="n"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="B197" s="46" t="inlineStr">
-        <is>
-          <t>Agenda</t>
-        </is>
-      </c>
-      <c r="C197" s="46" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D197" s="48" t="inlineStr">
-        <is>
-          <t>Mencari agenda dengan keyword tidak valid</t>
-        </is>
-      </c>
-      <c r="E197" s="46" t="inlineStr">
-        <is>
-          <t>Negative Case</t>
-        </is>
-      </c>
-      <c r="F197" s="46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G197" s="48" t="inlineStr">
-        <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
-        </is>
-      </c>
-      <c r="H197" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
-        </is>
-      </c>
-      <c r="I197" s="49" t="n"/>
-      <c r="J197" s="49" t="n"/>
-      <c r="K197" s="49" t="n"/>
-      <c r="L197" s="49" t="n"/>
-      <c r="M197" s="49" t="n"/>
-      <c r="N197" s="49" t="n"/>
-      <c r="O197" s="49" t="n"/>
-      <c r="P197" s="49" t="n"/>
-      <c r="Q197" s="49" t="n"/>
-      <c r="R197" s="49" t="n"/>
-      <c r="S197" s="49" t="n"/>
-      <c r="T197" s="49" t="n"/>
-      <c r="U197" s="49" t="n"/>
-      <c r="V197" s="49" t="n"/>
-      <c r="W197" s="49" t="n"/>
-      <c r="X197" s="49" t="n"/>
-      <c r="Y197" s="49" t="n"/>
-      <c r="Z197" s="49" t="n"/>
-      <c r="AA197" s="49" t="n"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
-      <c r="B198" s="46" t="inlineStr">
-        <is>
-          <t>Agenda</t>
-        </is>
-      </c>
-      <c r="C198" s="46" t="inlineStr">
-        <is>
-          <t>Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="D198" s="48" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Daily Sales Agenda</t>
-        </is>
-      </c>
-      <c r="E198" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F198" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G198" s="48" t="inlineStr">
-        <is>
-          <t>1. Klik button Filter.
-2. Pilih kriteria filter pada form Filter (Product, Bulan, Tahun).
-3. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H198" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka form Filter.
-2. Berhasil memilih kriteria filter.
-3. Berhasil menampilkan data Daily Sales Agenda sesuai filter yang dipilih.</t>
-        </is>
-      </c>
-      <c r="I198" s="49" t="n"/>
-      <c r="J198" s="49" t="n"/>
-      <c r="K198" s="49" t="n"/>
-      <c r="L198" s="49" t="n"/>
-      <c r="M198" s="49" t="n"/>
-      <c r="N198" s="49" t="n"/>
-      <c r="O198" s="49" t="n"/>
-      <c r="P198" s="49" t="n"/>
-      <c r="Q198" s="49" t="n"/>
-      <c r="R198" s="49" t="n"/>
-      <c r="S198" s="49" t="n"/>
-      <c r="T198" s="49" t="n"/>
-      <c r="U198" s="49" t="n"/>
-      <c r="V198" s="49" t="n"/>
-      <c r="W198" s="49" t="n"/>
-      <c r="X198" s="49" t="n"/>
-      <c r="Y198" s="49" t="n"/>
-      <c r="Z198" s="49" t="n"/>
-      <c r="AA198" s="49" t="n"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="B199" s="46" t="inlineStr">
-        <is>
-          <t>Fitur</t>
-        </is>
-      </c>
-      <c r="C199" s="46" t="inlineStr">
-        <is>
-          <t>Marketing Toolkit</t>
-        </is>
-      </c>
-      <c r="D199" s="48" t="inlineStr">
-        <is>
-          <t>Membuka halaman Marketing Toolkit</t>
-        </is>
-      </c>
-      <c r="E199" s="46" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F199" s="46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G199" s="48" t="inlineStr">
-        <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Marketing Toolkit.</t>
-        </is>
-      </c>
-      <c r="H199" s="48" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Marketing Toolkit.</t>
         </is>
       </c>
       <c r="I199" s="49" t="n"/>
@@ -60575,22 +60440,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="B200" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Agenda</t>
         </is>
       </c>
       <c r="C200" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Daily Sales Agenda</t>
         </is>
       </c>
       <c r="D200" s="48" t="inlineStr">
         <is>
-          <t>Mengubah tampilan folder menjadi List View</t>
+          <t>Melihat daftar agenda pada tab Masuk</t>
         </is>
       </c>
       <c r="E200" s="46" t="inlineStr">
@@ -60605,12 +60470,12 @@
       </c>
       <c r="G200" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon tampilan List pada halaman Marketing Toolkit.</t>
+          <t>1. Klik tab Masuk.</t>
         </is>
       </c>
       <c r="H200" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengubah tampilan folder menjadi List View.</t>
+          <t>1. Berhasil menampilkan daftar nasabah yang masuk pada Daily Sales Agenda.</t>
         </is>
       </c>
       <c r="I200" s="49" t="n"/>
@@ -60636,22 +60501,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="B201" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Agenda</t>
         </is>
       </c>
       <c r="C201" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Daily Sales Agenda</t>
         </is>
       </c>
       <c r="D201" s="48" t="inlineStr">
         <is>
-          <t>Mengubah tampilan folder menjadi Grid View</t>
+          <t>Melihat daftar agenda pada tab Closing</t>
         </is>
       </c>
       <c r="E201" s="46" t="inlineStr">
@@ -60666,12 +60531,12 @@
       </c>
       <c r="G201" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon tampilan Grid pada halaman Marketing Toolkit.</t>
+          <t>1. Klik tab Closing.</t>
         </is>
       </c>
       <c r="H201" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil mengubah tampilan folder menjadi Grid View.</t>
+          <t>1. Berhasil menampilkan daftar nasabah yang closing pada Daily Sales Agenda.</t>
         </is>
       </c>
       <c r="I201" s="49" t="n"/>
@@ -60697,22 +60562,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="B202" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Agenda</t>
         </is>
       </c>
       <c r="C202" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Daily Sales Agenda</t>
         </is>
       </c>
       <c r="D202" s="48" t="inlineStr">
         <is>
-          <t>Membuka folder pada Marketing Toolkit</t>
+          <t>Melihat daftar agenda pada tab Referral</t>
         </is>
       </c>
       <c r="E202" s="46" t="inlineStr">
@@ -60722,17 +60587,17 @@
       </c>
       <c r="F202" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G202" s="48" t="inlineStr">
         <is>
-          <t>1. Klik salah satu folder pada daftar Folder.</t>
+          <t>1. Klik tab Referral.</t>
         </is>
       </c>
       <c r="H202" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka folder Marketing Toolkit.</t>
+          <t>1. Berhasil menampilkan daftar nasabah referral pada Daily Sales Agenda.</t>
         </is>
       </c>
       <c r="I202" s="49" t="n"/>
@@ -60758,22 +60623,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="B203" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Agenda</t>
         </is>
       </c>
       <c r="C203" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Daily Sales Agenda</t>
         </is>
       </c>
       <c r="D203" s="48" t="inlineStr">
         <is>
-          <t>Mencari konten di dalam folder menggunakan Search Bar</t>
+          <t>Melihat daftar agenda pada tab Ref. Closing</t>
         </is>
       </c>
       <c r="E203" s="46" t="inlineStr">
@@ -60783,17 +60648,17 @@
       </c>
       <c r="F203" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G203" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
+          <t>1. Klik tab Ref. Closing.</t>
         </is>
       </c>
       <c r="H203" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan data yang sesuai dengan kata kunci pencarian.</t>
+          <t>1. Berhasil menampilkan daftar nasabah referral yang closing pada Daily Sales Agenda.</t>
         </is>
       </c>
       <c r="I203" s="49" t="n"/>
@@ -60819,42 +60684,42 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="B204" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Agenda</t>
         </is>
       </c>
       <c r="C204" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Daily Sales Agenda</t>
         </is>
       </c>
       <c r="D204" s="48" t="inlineStr">
         <is>
-          <t>Mencari konten di dalam folder dengan keyword tidak valid</t>
+          <t>Mencari agenda menggunakan Search Bar</t>
         </is>
       </c>
       <c r="E204" s="46" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F204" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G204" s="48" t="inlineStr">
         <is>
-          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
+          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
         </is>
       </c>
       <c r="H204" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
+          <t>1. Berhasil menampilkan data agenda yang sesuai dengan kata kunci pencarian.</t>
         </is>
       </c>
       <c r="I204" s="49" t="n"/>
@@ -60880,42 +60745,42 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="B205" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Agenda</t>
         </is>
       </c>
       <c r="C205" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Daily Sales Agenda</t>
         </is>
       </c>
       <c r="D205" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail konten Marketing Toolkit</t>
+          <t>Mencari agenda dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E205" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F205" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G205" s="48" t="inlineStr">
         <is>
-          <t>1. Klik salah satu sub-folder pada daftar folder.</t>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
         </is>
       </c>
       <c r="H205" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail konten Marketing Toolkit.</t>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
       <c r="I205" s="49" t="n"/>
@@ -60941,22 +60806,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="B206" s="46" t="inlineStr">
         <is>
-          <t>Fitur</t>
+          <t>Agenda</t>
         </is>
       </c>
       <c r="C206" s="46" t="inlineStr">
         <is>
-          <t>Marketing Toolkit</t>
+          <t>Daily Sales Agenda</t>
         </is>
       </c>
       <c r="D206" s="48" t="inlineStr">
         <is>
-          <t>Mengunduh lampiran pada konten Marketing Toolkit</t>
+          <t>Melakukan filter data Daily Sales Agenda</t>
         </is>
       </c>
       <c r="E206" s="46" t="inlineStr">
@@ -60971,14 +60836,16 @@
       </c>
       <c r="G206" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon titik tiga pada salah satu lampiran.
-2. Pilih Download.</t>
+          <t>1. Klik button Filter.
+2. Pilih kriteria filter pada form Filter (Product, Bulan, Tahun).
+3. Klik button Submit.</t>
         </is>
       </c>
       <c r="H206" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan opsi aksi pada lampiran.
-2. Berhasil mengunduh lampiran ke perangkat.</t>
+          <t>1. Berhasil membuka form Filter.
+2. Berhasil memilih kriteria filter.
+3. Berhasil menampilkan data Daily Sales Agenda sesuai filter yang dipilih.</t>
         </is>
       </c>
       <c r="I206" s="49" t="n"/>
@@ -61004,7 +60871,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="B207" s="46" t="inlineStr">
@@ -61019,7 +60886,7 @@
       </c>
       <c r="D207" s="48" t="inlineStr">
         <is>
-          <t>Berbagi lampiran pada konten Marketing Toolkit</t>
+          <t>Membuka halaman Marketing Toolkit</t>
         </is>
       </c>
       <c r="E207" s="46" t="inlineStr">
@@ -61029,19 +60896,19 @@
       </c>
       <c r="F207" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G207" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon titik tiga pada salah satu lampiran.
-2. Pilih Share.</t>
+          <t>1. Buka menu Lainnya.
+2. Klik menu Marketing Toolkit.</t>
         </is>
       </c>
       <c r="H207" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan opsi aksi pada lampiran.
-2. Berhasil menampilkan pilihan aplikasi berbagi.</t>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman Marketing Toolkit.</t>
         </is>
       </c>
       <c r="I207" s="49" t="n"/>
@@ -61067,22 +60934,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="B208" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Fitur</t>
         </is>
       </c>
       <c r="C208" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>Marketing Toolkit</t>
         </is>
       </c>
       <c r="D208" s="48" t="inlineStr">
         <is>
-          <t>Membuka halaman Dashboard Sales Code</t>
+          <t>Mengubah tampilan folder menjadi List View</t>
         </is>
       </c>
       <c r="E208" s="46" t="inlineStr">
@@ -61092,19 +60959,17 @@
       </c>
       <c r="F208" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G208" s="48" t="inlineStr">
         <is>
-          <t>1. Buka menu Lainnya.
-2. Klik menu Dashboard Sales Code.</t>
+          <t>1. Klik icon tampilan List pada halaman Marketing Toolkit.</t>
         </is>
       </c>
       <c r="H208" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil membuka menu Lainnya.
-2. Berhasil menampilkan halaman Dashboard Sales Code.</t>
+          <t>1. Berhasil mengubah tampilan folder menjadi List View.</t>
         </is>
       </c>
       <c r="I208" s="49" t="n"/>
@@ -61130,22 +60995,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="B209" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Fitur</t>
         </is>
       </c>
       <c r="C209" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>Marketing Toolkit</t>
         </is>
       </c>
       <c r="D209" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail Voa Realization</t>
+          <t>Mengubah tampilan folder menjadi Grid View</t>
         </is>
       </c>
       <c r="E209" s="46" t="inlineStr">
@@ -61155,17 +61020,17 @@
       </c>
       <c r="F209" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G209" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Voa Realization.</t>
+          <t>1. Klik icon tampilan Grid pada halaman Marketing Toolkit.</t>
         </is>
       </c>
       <c r="H209" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Voa Realization.</t>
+          <t>1. Berhasil mengubah tampilan folder menjadi Grid View.</t>
         </is>
       </c>
       <c r="I209" s="49" t="n"/>
@@ -61191,22 +61056,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="B210" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Fitur</t>
         </is>
       </c>
       <c r="C210" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>Marketing Toolkit</t>
         </is>
       </c>
       <c r="D210" s="48" t="inlineStr">
         <is>
-          <t>Melihat Daftar Pipeline pada Voa Realization</t>
+          <t>Membuka folder pada Marketing Toolkit</t>
         </is>
       </c>
       <c r="E210" s="46" t="inlineStr">
@@ -61221,14 +61086,12 @@
       </c>
       <c r="G210" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Voa Realization.
-2. Klik Lihat Daftar Pipeline.</t>
+          <t>1. Klik salah satu folder pada daftar Folder.</t>
         </is>
       </c>
       <c r="H210" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Voa Realization.
-2. Berhasil menampilkan Daftar Pipeline.</t>
+          <t>1. Berhasil membuka folder Marketing Toolkit.</t>
         </is>
       </c>
       <c r="I210" s="49" t="n"/>
@@ -61254,22 +61117,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="B211" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Fitur</t>
         </is>
       </c>
       <c r="C211" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>Marketing Toolkit</t>
         </is>
       </c>
       <c r="D211" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail CIF Kelolaan</t>
+          <t>Mencari konten di dalam folder menggunakan Search Bar</t>
         </is>
       </c>
       <c r="E211" s="46" t="inlineStr">
@@ -61279,17 +61142,17 @@
       </c>
       <c r="F211" s="46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G211" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card CIF Kelolaan.</t>
+          <t>1. Masukkan kata kunci pencarian pada Search Bar.</t>
         </is>
       </c>
       <c r="H211" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail CIF Kelolaan.</t>
+          <t>1. Berhasil menampilkan data yang sesuai dengan kata kunci pencarian.</t>
         </is>
       </c>
       <c r="I211" s="49" t="n"/>
@@ -61315,42 +61178,42 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="B212" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Fitur</t>
         </is>
       </c>
       <c r="C212" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>Marketing Toolkit</t>
         </is>
       </c>
       <c r="D212" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail Realisasi Konek E-Channel</t>
+          <t>Mencari konten di dalam folder dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E212" s="46" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F212" s="46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G212" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Realisasi Konek E-Channel.</t>
+          <t>1. Masukkan keyword tidak valid pada Search Bar.</t>
         </is>
       </c>
       <c r="H212" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Realisasi Konek E-Channel.</t>
+          <t>1. Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
       <c r="I212" s="49" t="n"/>
@@ -61376,22 +61239,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="B213" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Fitur</t>
         </is>
       </c>
       <c r="C213" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>Marketing Toolkit</t>
         </is>
       </c>
       <c r="D213" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail Realisasi Akuisisi Merchant</t>
+          <t>Melihat detail konten Marketing Toolkit</t>
         </is>
       </c>
       <c r="E213" s="46" t="inlineStr">
@@ -61406,12 +61269,12 @@
       </c>
       <c r="G213" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Realisasi Akuisisi Merchant.</t>
+          <t>1. Klik salah satu sub-folder pada daftar folder.</t>
         </is>
       </c>
       <c r="H213" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Realisasi Akuisisi Merchant.</t>
+          <t>1. Berhasil menampilkan detail konten Marketing Toolkit.</t>
         </is>
       </c>
       <c r="I213" s="49" t="n"/>
@@ -61437,22 +61300,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="B214" s="46" t="inlineStr">
         <is>
-          <t>Sales Force</t>
+          <t>Fitur</t>
         </is>
       </c>
       <c r="C214" s="46" t="inlineStr">
         <is>
-          <t>Dashboard Sales Code</t>
+          <t>Marketing Toolkit</t>
         </is>
       </c>
       <c r="D214" s="48" t="inlineStr">
         <is>
-          <t>Melihat detail Eligible Upgrade to Prospera/Prioritas</t>
+          <t>Mengunduh lampiran pada konten Marketing Toolkit</t>
         </is>
       </c>
       <c r="E214" s="46" t="inlineStr">
@@ -61467,12 +61330,14 @@
       </c>
       <c r="G214" s="48" t="inlineStr">
         <is>
-          <t>1. Klik icon expand pada card Eligible Upgrade to Prospera/Prioritas.</t>
+          <t>1. Klik icon titik tiga pada salah satu lampiran.
+2. Pilih Download.</t>
         </is>
       </c>
       <c r="H214" s="48" t="inlineStr">
         <is>
-          <t>1. Berhasil menampilkan detail Eligible Upgrade to Prospera &amp; Prioritas.</t>
+          <t>1. Berhasil menampilkan opsi aksi pada lampiran.
+2. Berhasil mengunduh lampiran ke perangkat.</t>
         </is>
       </c>
       <c r="I214" s="49" t="n"/>
@@ -61495,6 +61360,500 @@
       <c r="Z214" s="49" t="n"/>
       <c r="AA214" s="49" t="n"/>
     </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="B215" s="46" t="inlineStr">
+        <is>
+          <t>Fitur</t>
+        </is>
+      </c>
+      <c r="C215" s="46" t="inlineStr">
+        <is>
+          <t>Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="D215" s="48" t="inlineStr">
+        <is>
+          <t>Berbagi lampiran pada konten Marketing Toolkit</t>
+        </is>
+      </c>
+      <c r="E215" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F215" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G215" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon titik tiga pada salah satu lampiran.
+2. Pilih Share.</t>
+        </is>
+      </c>
+      <c r="H215" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan opsi aksi pada lampiran.
+2. Berhasil menampilkan pilihan aplikasi berbagi.</t>
+        </is>
+      </c>
+      <c r="I215" s="49" t="n"/>
+      <c r="J215" s="49" t="n"/>
+      <c r="K215" s="49" t="n"/>
+      <c r="L215" s="49" t="n"/>
+      <c r="M215" s="49" t="n"/>
+      <c r="N215" s="49" t="n"/>
+      <c r="O215" s="49" t="n"/>
+      <c r="P215" s="49" t="n"/>
+      <c r="Q215" s="49" t="n"/>
+      <c r="R215" s="49" t="n"/>
+      <c r="S215" s="49" t="n"/>
+      <c r="T215" s="49" t="n"/>
+      <c r="U215" s="49" t="n"/>
+      <c r="V215" s="49" t="n"/>
+      <c r="W215" s="49" t="n"/>
+      <c r="X215" s="49" t="n"/>
+      <c r="Y215" s="49" t="n"/>
+      <c r="Z215" s="49" t="n"/>
+      <c r="AA215" s="49" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="B216" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C216" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D216" s="48" t="inlineStr">
+        <is>
+          <t>Membuka halaman Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="E216" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F216" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G216" s="48" t="inlineStr">
+        <is>
+          <t>1. Buka menu Lainnya.
+2. Klik menu Dashboard Sales Code.</t>
+        </is>
+      </c>
+      <c r="H216" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Lainnya.
+2. Berhasil menampilkan halaman Dashboard Sales Code.</t>
+        </is>
+      </c>
+      <c r="I216" s="49" t="n"/>
+      <c r="J216" s="49" t="n"/>
+      <c r="K216" s="49" t="n"/>
+      <c r="L216" s="49" t="n"/>
+      <c r="M216" s="49" t="n"/>
+      <c r="N216" s="49" t="n"/>
+      <c r="O216" s="49" t="n"/>
+      <c r="P216" s="49" t="n"/>
+      <c r="Q216" s="49" t="n"/>
+      <c r="R216" s="49" t="n"/>
+      <c r="S216" s="49" t="n"/>
+      <c r="T216" s="49" t="n"/>
+      <c r="U216" s="49" t="n"/>
+      <c r="V216" s="49" t="n"/>
+      <c r="W216" s="49" t="n"/>
+      <c r="X216" s="49" t="n"/>
+      <c r="Y216" s="49" t="n"/>
+      <c r="Z216" s="49" t="n"/>
+      <c r="AA216" s="49" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="B217" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C217" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D217" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail Voa Realization</t>
+        </is>
+      </c>
+      <c r="E217" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F217" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G217" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon expand pada card Voa Realization.</t>
+        </is>
+      </c>
+      <c r="H217" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail Voa Realization.</t>
+        </is>
+      </c>
+      <c r="I217" s="49" t="n"/>
+      <c r="J217" s="49" t="n"/>
+      <c r="K217" s="49" t="n"/>
+      <c r="L217" s="49" t="n"/>
+      <c r="M217" s="49" t="n"/>
+      <c r="N217" s="49" t="n"/>
+      <c r="O217" s="49" t="n"/>
+      <c r="P217" s="49" t="n"/>
+      <c r="Q217" s="49" t="n"/>
+      <c r="R217" s="49" t="n"/>
+      <c r="S217" s="49" t="n"/>
+      <c r="T217" s="49" t="n"/>
+      <c r="U217" s="49" t="n"/>
+      <c r="V217" s="49" t="n"/>
+      <c r="W217" s="49" t="n"/>
+      <c r="X217" s="49" t="n"/>
+      <c r="Y217" s="49" t="n"/>
+      <c r="Z217" s="49" t="n"/>
+      <c r="AA217" s="49" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="B218" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C218" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D218" s="48" t="inlineStr">
+        <is>
+          <t>Melihat Daftar Pipeline pada Voa Realization</t>
+        </is>
+      </c>
+      <c r="E218" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F218" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G218" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon expand pada card Voa Realization.
+2. Klik Lihat Daftar Pipeline.</t>
+        </is>
+      </c>
+      <c r="H218" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail Voa Realization.
+2. Berhasil menampilkan Daftar Pipeline.</t>
+        </is>
+      </c>
+      <c r="I218" s="49" t="n"/>
+      <c r="J218" s="49" t="n"/>
+      <c r="K218" s="49" t="n"/>
+      <c r="L218" s="49" t="n"/>
+      <c r="M218" s="49" t="n"/>
+      <c r="N218" s="49" t="n"/>
+      <c r="O218" s="49" t="n"/>
+      <c r="P218" s="49" t="n"/>
+      <c r="Q218" s="49" t="n"/>
+      <c r="R218" s="49" t="n"/>
+      <c r="S218" s="49" t="n"/>
+      <c r="T218" s="49" t="n"/>
+      <c r="U218" s="49" t="n"/>
+      <c r="V218" s="49" t="n"/>
+      <c r="W218" s="49" t="n"/>
+      <c r="X218" s="49" t="n"/>
+      <c r="Y218" s="49" t="n"/>
+      <c r="Z218" s="49" t="n"/>
+      <c r="AA218" s="49" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="B219" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C219" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D219" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail CIF Kelolaan</t>
+        </is>
+      </c>
+      <c r="E219" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F219" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G219" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon expand pada card CIF Kelolaan.</t>
+        </is>
+      </c>
+      <c r="H219" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail CIF Kelolaan.</t>
+        </is>
+      </c>
+      <c r="I219" s="49" t="n"/>
+      <c r="J219" s="49" t="n"/>
+      <c r="K219" s="49" t="n"/>
+      <c r="L219" s="49" t="n"/>
+      <c r="M219" s="49" t="n"/>
+      <c r="N219" s="49" t="n"/>
+      <c r="O219" s="49" t="n"/>
+      <c r="P219" s="49" t="n"/>
+      <c r="Q219" s="49" t="n"/>
+      <c r="R219" s="49" t="n"/>
+      <c r="S219" s="49" t="n"/>
+      <c r="T219" s="49" t="n"/>
+      <c r="U219" s="49" t="n"/>
+      <c r="V219" s="49" t="n"/>
+      <c r="W219" s="49" t="n"/>
+      <c r="X219" s="49" t="n"/>
+      <c r="Y219" s="49" t="n"/>
+      <c r="Z219" s="49" t="n"/>
+      <c r="AA219" s="49" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="B220" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C220" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D220" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail Realisasi Konek E-Channel</t>
+        </is>
+      </c>
+      <c r="E220" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F220" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G220" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon expand pada card Realisasi Konek E-Channel.</t>
+        </is>
+      </c>
+      <c r="H220" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail Realisasi Konek E-Channel.</t>
+        </is>
+      </c>
+      <c r="I220" s="49" t="n"/>
+      <c r="J220" s="49" t="n"/>
+      <c r="K220" s="49" t="n"/>
+      <c r="L220" s="49" t="n"/>
+      <c r="M220" s="49" t="n"/>
+      <c r="N220" s="49" t="n"/>
+      <c r="O220" s="49" t="n"/>
+      <c r="P220" s="49" t="n"/>
+      <c r="Q220" s="49" t="n"/>
+      <c r="R220" s="49" t="n"/>
+      <c r="S220" s="49" t="n"/>
+      <c r="T220" s="49" t="n"/>
+      <c r="U220" s="49" t="n"/>
+      <c r="V220" s="49" t="n"/>
+      <c r="W220" s="49" t="n"/>
+      <c r="X220" s="49" t="n"/>
+      <c r="Y220" s="49" t="n"/>
+      <c r="Z220" s="49" t="n"/>
+      <c r="AA220" s="49" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="B221" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C221" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D221" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail Realisasi Akuisisi Merchant</t>
+        </is>
+      </c>
+      <c r="E221" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F221" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G221" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon expand pada card Realisasi Akuisisi Merchant.</t>
+        </is>
+      </c>
+      <c r="H221" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail Realisasi Akuisisi Merchant.</t>
+        </is>
+      </c>
+      <c r="I221" s="49" t="n"/>
+      <c r="J221" s="49" t="n"/>
+      <c r="K221" s="49" t="n"/>
+      <c r="L221" s="49" t="n"/>
+      <c r="M221" s="49" t="n"/>
+      <c r="N221" s="49" t="n"/>
+      <c r="O221" s="49" t="n"/>
+      <c r="P221" s="49" t="n"/>
+      <c r="Q221" s="49" t="n"/>
+      <c r="R221" s="49" t="n"/>
+      <c r="S221" s="49" t="n"/>
+      <c r="T221" s="49" t="n"/>
+      <c r="U221" s="49" t="n"/>
+      <c r="V221" s="49" t="n"/>
+      <c r="W221" s="49" t="n"/>
+      <c r="X221" s="49" t="n"/>
+      <c r="Y221" s="49" t="n"/>
+      <c r="Z221" s="49" t="n"/>
+      <c r="AA221" s="49" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="B222" s="46" t="inlineStr">
+        <is>
+          <t>Sales Force</t>
+        </is>
+      </c>
+      <c r="C222" s="46" t="inlineStr">
+        <is>
+          <t>Dashboard Sales Code</t>
+        </is>
+      </c>
+      <c r="D222" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail Eligible Upgrade to Prospera/Prioritas</t>
+        </is>
+      </c>
+      <c r="E222" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F222" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G222" s="48" t="inlineStr">
+        <is>
+          <t>1. Klik icon expand pada card Eligible Upgrade to Prospera/Prioritas.</t>
+        </is>
+      </c>
+      <c r="H222" s="48" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan detail Eligible Upgrade to Prospera &amp; Prioritas.</t>
+        </is>
+      </c>
+      <c r="I222" s="49" t="n"/>
+      <c r="J222" s="49" t="n"/>
+      <c r="K222" s="49" t="n"/>
+      <c r="L222" s="49" t="n"/>
+      <c r="M222" s="49" t="n"/>
+      <c r="N222" s="49" t="n"/>
+      <c r="O222" s="49" t="n"/>
+      <c r="P222" s="49" t="n"/>
+      <c r="Q222" s="49" t="n"/>
+      <c r="R222" s="49" t="n"/>
+      <c r="S222" s="49" t="n"/>
+      <c r="T222" s="49" t="n"/>
+      <c r="U222" s="49" t="n"/>
+      <c r="V222" s="49" t="n"/>
+      <c r="W222" s="49" t="n"/>
+      <c r="X222" s="49" t="n"/>
+      <c r="Y222" s="49" t="n"/>
+      <c r="Z222" s="49" t="n"/>
+      <c r="AA222" s="49" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -32456,206 +32456,1164 @@
       </c>
       <c r="C740" s="56" t="inlineStr">
         <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D740" s="56" t="inlineStr">
+        <is>
+          <t>Membuka halaman Personal Funnel</t>
+        </is>
+      </c>
+      <c r="E740" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F740" s="55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G740" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Funding.
+2. Klik sub menu Personal Funnel.</t>
+        </is>
+      </c>
+      <c r="H740" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Funding.
+2. Berhasil menampilkan halaman Personal Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="741" ht="56" customHeight="1">
+      <c r="A741" s="55" t="inlineStr">
+        <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="B741" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C741" s="56" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D741" s="56" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Personal Funnel</t>
+        </is>
+      </c>
+      <c r="E741" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F741" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G741" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengisi semua field filter mandatory.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H741" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi field filter mandatory.
+2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="742" ht="14" customHeight="1">
+      <c r="A742" s="55" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="B742" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C742" s="56" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D742" s="56" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E742" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F742" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G742" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengosongkan field filter mandatory.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H742" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan field filter mandatory.
+2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="743" ht="14" customHeight="1">
+      <c r="A743" s="55" t="inlineStr">
+        <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="B743" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C743" s="56" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D743" s="56" t="inlineStr">
+        <is>
+          <t>Mengekspor data Personal Funnel</t>
+        </is>
+      </c>
+      <c r="E743" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F743" s="55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G743" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik button Export.
+2. Klik icon download pada panel Download Export.</t>
+        </is>
+      </c>
+      <c r="H743" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan panel Download Export.
+2. Berhasil mendownload file export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="744" ht="14" customHeight="1">
+      <c r="A744" s="55" t="inlineStr">
+        <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="B744" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C744" s="56" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D744" s="56" t="inlineStr">
+        <is>
+          <t>Membuka halaman Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E744" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F744" s="55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G744" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Funding.
+2. Klik sub menu Rekap Funnel.</t>
+        </is>
+      </c>
+      <c r="H744" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Funding.
+2. Berhasil menampilkan halaman Rekap Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="745" ht="14" customHeight="1">
+      <c r="A745" s="55" t="inlineStr">
+        <is>
+          <t>61.2</t>
+        </is>
+      </c>
+      <c r="B745" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C745" s="56" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D745" s="56" t="inlineStr">
+        <is>
+          <t>Menampilkan data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E745" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F745" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G745" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun).
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H745" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Menampilkan data Rekap Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="746" ht="28" customHeight="1">
+      <c r="A746" s="55" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="B746" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C746" s="56" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D746" s="56" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E746" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F746" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G746" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H746" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi kriteria filter.
+2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="747" ht="42" customHeight="1">
+      <c r="A747" s="55" t="inlineStr">
+        <is>
+          <t>61.4</t>
+        </is>
+      </c>
+      <c r="B747" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C747" s="56" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D747" s="56" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E747" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F747" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G747" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengosongkan field filter mandatory.
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H747" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan field filter mandatory.
+2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="748" ht="28" customHeight="1">
+      <c r="A748" s="55" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="B748" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C748" s="56" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D748" s="56" t="inlineStr">
+        <is>
+          <t>Mengunduh data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E748" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F748" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G748" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik button Download Excel.</t>
+        </is>
+      </c>
+      <c r="H748" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Mengunduh data Rekap Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="749" ht="14" customHeight="1">
+      <c r="A749" s="55" t="inlineStr">
+        <is>
+          <t>62.1</t>
+        </is>
+      </c>
+      <c r="B749" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C749" s="56" t="inlineStr">
+        <is>
+          <t>Regional Funnel</t>
+        </is>
+      </c>
+      <c r="D749" s="56" t="inlineStr">
+        <is>
+          <t>Membuka halaman Regional Funnel</t>
+        </is>
+      </c>
+      <c r="E749" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F749" s="55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G749" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Personal Funnel.</t>
+        </is>
+      </c>
+      <c r="H749" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Personal Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="750" ht="14" customHeight="1">
+      <c r="A750" s="55" t="inlineStr">
+        <is>
+          <t>62.2</t>
+        </is>
+      </c>
+      <c r="B750" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C750" s="56" t="inlineStr">
+        <is>
+          <t>Regional Funnel</t>
+        </is>
+      </c>
+      <c r="D750" s="56" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Regional Funnel</t>
+        </is>
+      </c>
+      <c r="E750" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F750" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G750" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengisi semua field filter mandatory.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H750" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi field filter mandatory.
+2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="751" ht="14" customHeight="1">
+      <c r="A751" s="55" t="inlineStr">
+        <is>
+          <t>62.3</t>
+        </is>
+      </c>
+      <c r="B751" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C751" s="56" t="inlineStr">
+        <is>
+          <t>Regional Funnel</t>
+        </is>
+      </c>
+      <c r="D751" s="56" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E751" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F751" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G751" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengosongkan field filter mandatory.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H751" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan field filter mandatory.
+2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="752" ht="14" customHeight="1">
+      <c r="A752" s="55" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="B752" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C752" s="56" t="inlineStr">
+        <is>
+          <t>Regional Funnel</t>
+        </is>
+      </c>
+      <c r="D752" s="56" t="inlineStr">
+        <is>
+          <t>Mencari data Regional Funnel dengan keyword valid</t>
+        </is>
+      </c>
+      <c r="E752" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F752" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G752" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengisi field Cari Data dengan keyword valid.
+2. Klik button Search.</t>
+        </is>
+      </c>
+      <c r="H752" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Mencari data Regional Funnel dengan keyword valid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="753" ht="14" customHeight="1">
+      <c r="A753" s="55" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="B753" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C753" s="56" t="inlineStr">
+        <is>
+          <t>Regional Funnel</t>
+        </is>
+      </c>
+      <c r="D753" s="56" t="inlineStr">
+        <is>
+          <t>Mencari data Regional Funnel dengan keyword tidak valid</t>
+        </is>
+      </c>
+      <c r="E753" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F753" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G753" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengisi field Cari Data dengan keyword tidak valid.
+2. Klik button Search.</t>
+        </is>
+      </c>
+      <c r="H753" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Mencari data Regional Funnel dengan keyword tidak valid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="754" ht="14" customHeight="1">
+      <c r="A754" s="55" t="inlineStr">
+        <is>
+          <t>62.6</t>
+        </is>
+      </c>
+      <c r="B754" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C754" s="56" t="inlineStr">
+        <is>
+          <t>Regional Funnel</t>
+        </is>
+      </c>
+      <c r="D754" s="56" t="inlineStr">
+        <is>
+          <t>Menampilkan data prospek berdasarkan kantor cabang</t>
+        </is>
+      </c>
+      <c r="E754" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F754" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G754" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik salah satu daftar kantor cabang pada tabel.</t>
+        </is>
+      </c>
+      <c r="H754" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Menampilkan data prospek berdasarkan kantor cabang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="755" ht="14" customHeight="1">
+      <c r="A755" s="55" t="inlineStr">
+        <is>
+          <t>63.1</t>
+        </is>
+      </c>
+      <c r="B755" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C755" s="56" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D755" s="56" t="inlineStr">
+        <is>
+          <t>Membuka halaman Pengaturan Funnel Funding</t>
+        </is>
+      </c>
+      <c r="E755" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F755" s="55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G755" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Funding.
+2. Klik sub menu Pengaturan Funnel.</t>
+        </is>
+      </c>
+      <c r="H755" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Funding.
+2. Berhasil menampilkan halaman Pengaturan Funnel Funding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="756" ht="14" customHeight="1">
+      <c r="A756" s="55" t="inlineStr">
+        <is>
+          <t>63.2</t>
+        </is>
+      </c>
+      <c r="B756" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C756" s="56" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D756" s="56" t="inlineStr">
+        <is>
+          <t>Menampilkan data Pengaturan Funnel Funding berdasarkan section</t>
+        </is>
+      </c>
+      <c r="E756" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F756" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G756" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik salah satu daftar section pada tabel.</t>
+        </is>
+      </c>
+      <c r="H756" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Menampilkan data Pengaturan Funnel Funding berdasarkan section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="757" ht="14" customHeight="1">
+      <c r="A757" s="55" t="inlineStr">
+        <is>
+          <t>63.3</t>
+        </is>
+      </c>
+      <c r="B757" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C757" s="56" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D757" s="56" t="inlineStr">
+        <is>
+          <t>Mengubah data Pengaturan Funnel Funding</t>
+        </is>
+      </c>
+      <c r="E757" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F757" s="55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G757" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H757" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi field Performance Percentage.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="758" ht="14" customHeight="1">
+      <c r="A758" s="55" t="inlineStr">
+        <is>
+          <t>63.4</t>
+        </is>
+      </c>
+      <c r="B758" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C758" s="56" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D758" s="56" t="inlineStr">
+        <is>
+          <t>Mengubah data Pengaturan Funnel Funding tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E758" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F758" s="55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G758" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengosongkan field mandatory Performance Percentage.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H758" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan field Performance Percentage.
+2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="759" ht="14" customHeight="1">
+      <c r="A759" s="55" t="inlineStr">
+        <is>
+          <t>63.5</t>
+        </is>
+      </c>
+      <c r="B759" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C759" s="56" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D759" s="56" t="inlineStr">
+        <is>
+          <t>Menambahkan Condition pada Performance Indicator</t>
+        </is>
+      </c>
+      <c r="E759" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F759" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G759" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik button Add Condition pada bagian Performance Indicator.
+2. Mengisi semua field mandatory pada condition baru.
+3. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H759" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Menambahkan Condition pada Performance Indicator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="760" ht="14" customHeight="1">
+      <c r="A760" s="55" t="inlineStr">
+        <is>
+          <t>63.6</t>
+        </is>
+      </c>
+      <c r="B760" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C760" s="56" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D760" s="56" t="inlineStr">
+        <is>
+          <t>Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E760" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F760" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G760" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik button Add Condition pada bagian Performance Indicator.
+2. Mengosongkan field mandatory pada condition baru.
+3. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H760" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="761" ht="14" customHeight="1">
+      <c r="A761" s="55" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="B761" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C761" s="56" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D761" s="56" t="inlineStr">
+        <is>
+          <t>Menghapus Condition pada Performance Indicator</t>
+        </is>
+      </c>
+      <c r="E761" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F761" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G761" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik button Remove pada salah satu condition di Performance Indicator.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H761" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Menghapus Condition pada Performance Indicator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="762" ht="14" customHeight="1">
+      <c r="A762" s="55" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="B762" s="56" t="inlineStr">
+        <is>
+          <t>Report Funding</t>
+        </is>
+      </c>
+      <c r="C762" s="56" t="inlineStr">
+        <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D740" s="56" t="inlineStr">
+      <c r="D762" s="56" t="inlineStr">
         <is>
           <t>Membuka halaman Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="E740" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F740" s="55" t="inlineStr">
+      <c r="E762" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F762" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G740" s="56" t="inlineStr">
+      <c r="G762" s="56" t="inlineStr">
         <is>
           <t>1. Klik menu Report Funding.
 2. Klik sub menu Daily Sales Agenda.</t>
         </is>
       </c>
-      <c r="H740" s="56" t="inlineStr">
+      <c r="H762" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Funding.
 2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
         </is>
       </c>
     </row>
-    <row r="741" ht="56" customHeight="1">
-      <c r="A741" s="55" t="inlineStr">
-        <is>
-          <t>60.2</t>
-        </is>
-      </c>
-      <c r="B741" s="56" t="inlineStr">
+    <row r="763" ht="14" customHeight="1">
+      <c r="A763" s="55" t="inlineStr">
+        <is>
+          <t>64.2</t>
+        </is>
+      </c>
+      <c r="B763" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C741" s="56" t="inlineStr">
+      <c r="C763" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D741" s="56" t="inlineStr">
+      <c r="D763" s="56" t="inlineStr">
         <is>
           <t>Melakukan filter data Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="E741" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F741" s="55" t="inlineStr">
+      <c r="E763" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F763" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G741" s="56" t="inlineStr">
+      <c r="G763" s="56" t="inlineStr">
         <is>
           <t>1. Mengisi semua field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H741" s="56" t="inlineStr">
+      <c r="H763" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field filter mandatory.
 2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="742" ht="14" customHeight="1">
-      <c r="A742" s="55" t="inlineStr">
-        <is>
-          <t>60.3</t>
-        </is>
-      </c>
-      <c r="B742" s="56" t="inlineStr">
+    <row r="764" ht="14" customHeight="1">
+      <c r="A764" s="55" t="inlineStr">
+        <is>
+          <t>64.3</t>
+        </is>
+      </c>
+      <c r="B764" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C742" s="56" t="inlineStr">
+      <c r="C764" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D742" s="56" t="inlineStr">
+      <c r="D764" s="56" t="inlineStr">
         <is>
           <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E742" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F742" s="55" t="inlineStr">
+      <c r="E764" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F764" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G742" s="56" t="inlineStr">
+      <c r="G764" s="56" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H742" s="56" t="inlineStr">
+      <c r="H764" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
-    <row r="743" ht="14" customHeight="1">
-      <c r="A743" s="55" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="B743" s="56" t="inlineStr">
+    <row r="765" ht="14" customHeight="1">
+      <c r="A765" s="55" t="inlineStr">
+        <is>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="B765" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C743" s="56" t="inlineStr">
+      <c r="C765" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D743" s="56" t="inlineStr">
+      <c r="D765" s="56" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Masuk</t>
         </is>
       </c>
-      <c r="E743" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F743" s="55" t="inlineStr">
+      <c r="E765" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F765" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G743" s="56" t="inlineStr">
+      <c r="G765" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.</t>
         </is>
       </c>
-      <c r="H743" s="56" t="inlineStr">
+      <c r="H765" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Masuk.</t>
         </is>
       </c>
     </row>
-    <row r="744" ht="14" customHeight="1">
-      <c r="A744" s="55" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="B744" s="56" t="inlineStr">
+    <row r="766" ht="14" customHeight="1">
+      <c r="A766" s="55" t="inlineStr">
+        <is>
+          <t>64.5</t>
+        </is>
+      </c>
+      <c r="B766" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C744" s="56" t="inlineStr">
+      <c r="C766" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D744" s="56" t="inlineStr">
+      <c r="D766" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Masuk dengan keyword valid</t>
         </is>
       </c>
-      <c r="E744" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F744" s="55" t="inlineStr">
+      <c r="E766" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F766" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G744" s="56" t="inlineStr">
+      <c r="G766" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H744" s="56" t="inlineStr">
+      <c r="H766" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil mengisi field Cari Data.
@@ -32663,45 +33621,45 @@
         </is>
       </c>
     </row>
-    <row r="745" ht="14" customHeight="1">
-      <c r="A745" s="55" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="B745" s="56" t="inlineStr">
+    <row r="767" ht="28" customHeight="1">
+      <c r="A767" s="55" t="inlineStr">
+        <is>
+          <t>64.6</t>
+        </is>
+      </c>
+      <c r="B767" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C745" s="56" t="inlineStr">
+      <c r="C767" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D745" s="56" t="inlineStr">
+      <c r="D767" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E745" s="56" t="inlineStr">
+      <c r="E767" s="56" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F745" s="55" t="inlineStr">
+      <c r="F767" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G745" s="56" t="inlineStr">
+      <c r="G767" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H745" s="56" t="inlineStr">
+      <c r="H767" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil mengisi field Cari Data.
@@ -32709,89 +33667,89 @@
         </is>
       </c>
     </row>
-    <row r="746" ht="28" customHeight="1">
-      <c r="A746" s="55" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="B746" s="56" t="inlineStr">
+    <row r="768" ht="14" customHeight="1">
+      <c r="A768" s="55" t="inlineStr">
+        <is>
+          <t>64.7</t>
+        </is>
+      </c>
+      <c r="B768" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C746" s="56" t="inlineStr">
+      <c r="C768" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D746" s="56" t="inlineStr">
+      <c r="D768" s="56" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Masuk</t>
         </is>
       </c>
-      <c r="E746" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F746" s="55" t="inlineStr">
+      <c r="E768" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F768" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G746" s="56" t="inlineStr">
+      <c r="G768" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H746" s="56" t="inlineStr">
+      <c r="H768" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="747" ht="42" customHeight="1">
-      <c r="A747" s="55" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="B747" s="56" t="inlineStr">
+    <row r="769" ht="14" customHeight="1">
+      <c r="A769" s="55" t="inlineStr">
+        <is>
+          <t>64.8</t>
+        </is>
+      </c>
+      <c r="B769" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C747" s="56" t="inlineStr">
+      <c r="C769" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D747" s="56" t="inlineStr">
+      <c r="D769" s="56" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Masuk</t>
         </is>
       </c>
-      <c r="E747" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F747" s="55" t="inlineStr">
+      <c r="E769" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F769" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G747" s="56" t="inlineStr">
+      <c r="G769" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H747" s="56" t="inlineStr">
+      <c r="H769" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil menampilkan panel Download Export.
@@ -32799,87 +33757,87 @@
         </is>
       </c>
     </row>
-    <row r="748" ht="28" customHeight="1">
-      <c r="A748" s="55" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="B748" s="56" t="inlineStr">
+    <row r="770" ht="14" customHeight="1">
+      <c r="A770" s="55" t="inlineStr">
+        <is>
+          <t>64.9</t>
+        </is>
+      </c>
+      <c r="B770" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C748" s="56" t="inlineStr">
+      <c r="C770" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D748" s="56" t="inlineStr">
+      <c r="D770" s="56" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Closing</t>
         </is>
       </c>
-      <c r="E748" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F748" s="55" t="inlineStr">
+      <c r="E770" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F770" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G748" s="56" t="inlineStr">
+      <c r="G770" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.</t>
         </is>
       </c>
-      <c r="H748" s="56" t="inlineStr">
+      <c r="H770" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Closing.</t>
         </is>
       </c>
     </row>
-    <row r="749" ht="14" customHeight="1">
-      <c r="A749" s="55" t="inlineStr">
-        <is>
-          <t>60.10</t>
-        </is>
-      </c>
-      <c r="B749" s="56" t="inlineStr">
+    <row r="771" ht="14" customHeight="1">
+      <c r="A771" s="55" t="inlineStr">
+        <is>
+          <t>64.10</t>
+        </is>
+      </c>
+      <c r="B771" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C749" s="56" t="inlineStr">
+      <c r="C771" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D749" s="56" t="inlineStr">
+      <c r="D771" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Closing dengan keyword valid</t>
         </is>
       </c>
-      <c r="E749" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F749" s="55" t="inlineStr">
+      <c r="E771" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F771" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G749" s="56" t="inlineStr">
+      <c r="G771" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H749" s="56" t="inlineStr">
+      <c r="H771" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil mengisi field Cari Data.
@@ -32887,45 +33845,45 @@
         </is>
       </c>
     </row>
-    <row r="750" ht="14" customHeight="1">
-      <c r="A750" s="55" t="inlineStr">
-        <is>
-          <t>60.11</t>
-        </is>
-      </c>
-      <c r="B750" s="56" t="inlineStr">
+    <row r="772" ht="14" customHeight="1">
+      <c r="A772" s="55" t="inlineStr">
+        <is>
+          <t>64.11</t>
+        </is>
+      </c>
+      <c r="B772" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C750" s="56" t="inlineStr">
+      <c r="C772" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D750" s="56" t="inlineStr">
+      <c r="D772" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E750" s="56" t="inlineStr">
+      <c r="E772" s="56" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F750" s="55" t="inlineStr">
+      <c r="F772" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G750" s="56" t="inlineStr">
+      <c r="G772" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H750" s="56" t="inlineStr">
+      <c r="H772" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil mengisi field Cari Data.
@@ -32933,89 +33891,89 @@
         </is>
       </c>
     </row>
-    <row r="751" ht="14" customHeight="1">
-      <c r="A751" s="55" t="inlineStr">
-        <is>
-          <t>60.12</t>
-        </is>
-      </c>
-      <c r="B751" s="56" t="inlineStr">
+    <row r="773" ht="14" customHeight="1">
+      <c r="A773" s="55" t="inlineStr">
+        <is>
+          <t>64.12</t>
+        </is>
+      </c>
+      <c r="B773" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C751" s="56" t="inlineStr">
+      <c r="C773" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D751" s="56" t="inlineStr">
+      <c r="D773" s="56" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Closing</t>
         </is>
       </c>
-      <c r="E751" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F751" s="55" t="inlineStr">
+      <c r="E773" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F773" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G751" s="56" t="inlineStr">
+      <c r="G773" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H751" s="56" t="inlineStr">
+      <c r="H773" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="752" ht="14" customHeight="1">
-      <c r="A752" s="55" t="inlineStr">
-        <is>
-          <t>60.13</t>
-        </is>
-      </c>
-      <c r="B752" s="56" t="inlineStr">
+    <row r="774" ht="14" customHeight="1">
+      <c r="A774" s="55" t="inlineStr">
+        <is>
+          <t>64.13</t>
+        </is>
+      </c>
+      <c r="B774" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C752" s="56" t="inlineStr">
+      <c r="C774" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D752" s="56" t="inlineStr">
+      <c r="D774" s="56" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Closing</t>
         </is>
       </c>
-      <c r="E752" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F752" s="55" t="inlineStr">
+      <c r="E774" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F774" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G752" s="56" t="inlineStr">
+      <c r="G774" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H752" s="56" t="inlineStr">
+      <c r="H774" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil menampilkan panel Download Export.
@@ -33023,87 +33981,87 @@
         </is>
       </c>
     </row>
-    <row r="753" ht="14" customHeight="1">
-      <c r="A753" s="55" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
-      </c>
-      <c r="B753" s="56" t="inlineStr">
+    <row r="775" ht="14" customHeight="1">
+      <c r="A775" s="55" t="inlineStr">
+        <is>
+          <t>64.14</t>
+        </is>
+      </c>
+      <c r="B775" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C753" s="56" t="inlineStr">
+      <c r="C775" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D753" s="56" t="inlineStr">
+      <c r="D775" s="56" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Referal</t>
         </is>
       </c>
-      <c r="E753" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F753" s="55" t="inlineStr">
+      <c r="E775" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F775" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G753" s="56" t="inlineStr">
+      <c r="G775" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.</t>
         </is>
       </c>
-      <c r="H753" s="56" t="inlineStr">
+      <c r="H775" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Referal.</t>
         </is>
       </c>
     </row>
-    <row r="754" ht="14" customHeight="1">
-      <c r="A754" s="55" t="inlineStr">
-        <is>
-          <t>60.15</t>
-        </is>
-      </c>
-      <c r="B754" s="56" t="inlineStr">
+    <row r="776" ht="14" customHeight="1">
+      <c r="A776" s="55" t="inlineStr">
+        <is>
+          <t>64.15</t>
+        </is>
+      </c>
+      <c r="B776" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C754" s="56" t="inlineStr">
+      <c r="C776" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D754" s="56" t="inlineStr">
+      <c r="D776" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal dengan keyword valid</t>
         </is>
       </c>
-      <c r="E754" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F754" s="55" t="inlineStr">
+      <c r="E776" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F776" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G754" s="56" t="inlineStr">
+      <c r="G776" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H754" s="56" t="inlineStr">
+      <c r="H776" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil mengisi field Cari Data.
@@ -33111,45 +34069,45 @@
         </is>
       </c>
     </row>
-    <row r="755" ht="14" customHeight="1">
-      <c r="A755" s="55" t="inlineStr">
-        <is>
-          <t>60.16</t>
-        </is>
-      </c>
-      <c r="B755" s="56" t="inlineStr">
+    <row r="777" ht="14" customHeight="1">
+      <c r="A777" s="55" t="inlineStr">
+        <is>
+          <t>64.16</t>
+        </is>
+      </c>
+      <c r="B777" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C755" s="56" t="inlineStr">
+      <c r="C777" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D755" s="56" t="inlineStr">
+      <c r="D777" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E755" s="56" t="inlineStr">
+      <c r="E777" s="56" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F755" s="55" t="inlineStr">
+      <c r="F777" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G755" s="56" t="inlineStr">
+      <c r="G777" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H755" s="56" t="inlineStr">
+      <c r="H777" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil mengisi field Cari Data.
@@ -33157,89 +34115,89 @@
         </is>
       </c>
     </row>
-    <row r="756" ht="14" customHeight="1">
-      <c r="A756" s="55" t="inlineStr">
-        <is>
-          <t>60.17</t>
-        </is>
-      </c>
-      <c r="B756" s="56" t="inlineStr">
+    <row r="778" ht="14" customHeight="1">
+      <c r="A778" s="55" t="inlineStr">
+        <is>
+          <t>64.17</t>
+        </is>
+      </c>
+      <c r="B778" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C756" s="56" t="inlineStr">
+      <c r="C778" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D756" s="56" t="inlineStr">
+      <c r="D778" s="56" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Referal</t>
         </is>
       </c>
-      <c r="E756" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F756" s="55" t="inlineStr">
+      <c r="E778" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F778" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G756" s="56" t="inlineStr">
+      <c r="G778" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H756" s="56" t="inlineStr">
+      <c r="H778" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="757" ht="14" customHeight="1">
-      <c r="A757" s="55" t="inlineStr">
-        <is>
-          <t>60.18</t>
-        </is>
-      </c>
-      <c r="B757" s="56" t="inlineStr">
+    <row r="779" ht="28" customHeight="1">
+      <c r="A779" s="55" t="inlineStr">
+        <is>
+          <t>64.18</t>
+        </is>
+      </c>
+      <c r="B779" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C757" s="56" t="inlineStr">
+      <c r="C779" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D757" s="56" t="inlineStr">
+      <c r="D779" s="56" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Referal</t>
         </is>
       </c>
-      <c r="E757" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F757" s="55" t="inlineStr">
+      <c r="E779" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F779" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G757" s="56" t="inlineStr">
+      <c r="G779" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H757" s="56" t="inlineStr">
+      <c r="H779" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil menampilkan panel Download Export.
@@ -33247,87 +34205,87 @@
         </is>
       </c>
     </row>
-    <row r="758" ht="14" customHeight="1">
-      <c r="A758" s="55" t="inlineStr">
-        <is>
-          <t>60.19</t>
-        </is>
-      </c>
-      <c r="B758" s="56" t="inlineStr">
+    <row r="780" ht="14" customHeight="1">
+      <c r="A780" s="55" t="inlineStr">
+        <is>
+          <t>64.19</t>
+        </is>
+      </c>
+      <c r="B780" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C758" s="56" t="inlineStr">
+      <c r="C780" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D758" s="56" t="inlineStr">
+      <c r="D780" s="56" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E758" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F758" s="55" t="inlineStr">
+      <c r="E780" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F780" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G758" s="56" t="inlineStr">
+      <c r="G780" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.</t>
         </is>
       </c>
-      <c r="H758" s="56" t="inlineStr">
+      <c r="H780" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
         </is>
       </c>
     </row>
-    <row r="759" ht="14" customHeight="1">
-      <c r="A759" s="55" t="inlineStr">
-        <is>
-          <t>60.20</t>
-        </is>
-      </c>
-      <c r="B759" s="56" t="inlineStr">
+    <row r="781" ht="28" customHeight="1">
+      <c r="A781" s="55" t="inlineStr">
+        <is>
+          <t>64.20</t>
+        </is>
+      </c>
+      <c r="B781" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C759" s="56" t="inlineStr">
+      <c r="C781" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D759" s="56" t="inlineStr">
+      <c r="D781" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
         </is>
       </c>
-      <c r="E759" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F759" s="55" t="inlineStr">
+      <c r="E781" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F781" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G759" s="56" t="inlineStr">
+      <c r="G781" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H759" s="56" t="inlineStr">
+      <c r="H781" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil mengisi field Cari Data.
@@ -33335,45 +34293,45 @@
         </is>
       </c>
     </row>
-    <row r="760" ht="14" customHeight="1">
-      <c r="A760" s="55" t="inlineStr">
-        <is>
-          <t>60.21</t>
-        </is>
-      </c>
-      <c r="B760" s="56" t="inlineStr">
+    <row r="782" ht="14" customHeight="1">
+      <c r="A782" s="55" t="inlineStr">
+        <is>
+          <t>64.21</t>
+        </is>
+      </c>
+      <c r="B782" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C760" s="56" t="inlineStr">
+      <c r="C782" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D760" s="56" t="inlineStr">
+      <c r="D782" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal Closing dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E760" s="56" t="inlineStr">
+      <c r="E782" s="56" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F760" s="55" t="inlineStr">
+      <c r="F782" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G760" s="56" t="inlineStr">
+      <c r="G782" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H760" s="56" t="inlineStr">
+      <c r="H782" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil mengisi field Cari Data.
@@ -33381,89 +34339,89 @@
         </is>
       </c>
     </row>
-    <row r="761" ht="14" customHeight="1">
-      <c r="A761" s="55" t="inlineStr">
-        <is>
-          <t>60.22</t>
-        </is>
-      </c>
-      <c r="B761" s="56" t="inlineStr">
+    <row r="783" ht="14" customHeight="1">
+      <c r="A783" s="55" t="inlineStr">
+        <is>
+          <t>64.22</t>
+        </is>
+      </c>
+      <c r="B783" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C761" s="56" t="inlineStr">
+      <c r="C783" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D761" s="56" t="inlineStr">
+      <c r="D783" s="56" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E761" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F761" s="55" t="inlineStr">
+      <c r="E783" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F783" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G761" s="56" t="inlineStr">
+      <c r="G783" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H761" s="56" t="inlineStr">
+      <c r="H783" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="762" ht="14" customHeight="1">
-      <c r="A762" s="55" t="inlineStr">
-        <is>
-          <t>60.23</t>
-        </is>
-      </c>
-      <c r="B762" s="56" t="inlineStr">
+    <row r="784" ht="14" customHeight="1">
+      <c r="A784" s="55" t="inlineStr">
+        <is>
+          <t>64.23</t>
+        </is>
+      </c>
+      <c r="B784" s="56" t="inlineStr">
         <is>
           <t>Report Funding</t>
         </is>
       </c>
-      <c r="C762" s="56" t="inlineStr">
+      <c r="C784" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D762" s="56" t="inlineStr">
+      <c r="D784" s="56" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E762" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F762" s="55" t="inlineStr">
+      <c r="E784" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F784" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G762" s="56" t="inlineStr">
+      <c r="G784" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H762" s="56" t="inlineStr">
+      <c r="H784" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil menampilkan panel Download Export.
@@ -33471,1177 +34429,1043 @@
         </is>
       </c>
     </row>
-    <row r="763" ht="14" customHeight="1">
-      <c r="A763" s="55" t="inlineStr">
-        <is>
-          <t>61.1</t>
-        </is>
-      </c>
-      <c r="B763" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C763" s="56" t="inlineStr">
+    <row r="785" ht="14" customHeight="1">
+      <c r="A785" s="55" t="inlineStr">
+        <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="B785" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C785" s="56" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D763" s="56" t="inlineStr">
+      <c r="D785" s="56" t="inlineStr">
         <is>
           <t>Membuka halaman Personal Funnel</t>
         </is>
       </c>
-      <c r="E763" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F763" s="55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G763" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Funding.
+      <c r="E785" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F785" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G785" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
 2. Klik sub menu Personal Funnel.</t>
         </is>
       </c>
-      <c r="H763" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Funding.
-2. Berhasil menampilkan halaman Personal Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="764" ht="14" customHeight="1">
-      <c r="A764" s="55" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="B764" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C764" s="56" t="inlineStr">
+      <c r="H785" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Membuka halaman Personal Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="786" ht="14" customHeight="1">
+      <c r="A786" s="55" t="inlineStr">
+        <is>
+          <t>65.2</t>
+        </is>
+      </c>
+      <c r="B786" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C786" s="56" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D764" s="56" t="inlineStr">
+      <c r="D786" s="56" t="inlineStr">
         <is>
           <t>Melakukan filter data Personal Funnel</t>
         </is>
       </c>
-      <c r="E764" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F764" s="55" t="inlineStr">
+      <c r="E786" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F786" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G764" s="56" t="inlineStr">
+      <c r="G786" s="56" t="inlineStr">
         <is>
           <t>1. Mengisi semua field filter mandatory.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H764" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="765" ht="14" customHeight="1">
-      <c r="A765" s="55" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="B765" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C765" s="56" t="inlineStr">
+      <c r="H786" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Melakukan filter data Personal Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="787" ht="14" customHeight="1">
+      <c r="A787" s="55" t="inlineStr">
+        <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="B787" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C787" s="56" t="inlineStr">
         <is>
           <t>Personal Funnel</t>
         </is>
       </c>
-      <c r="D765" s="56" t="inlineStr">
+      <c r="D787" s="56" t="inlineStr">
         <is>
           <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E765" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F765" s="55" t="inlineStr">
+      <c r="E787" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F787" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G765" s="56" t="inlineStr">
+      <c r="G787" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengosongkan field filter mandatory.
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H787" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengosongkan field filter mandatory.
+2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="788" ht="14" customHeight="1">
+      <c r="A788" s="55" t="inlineStr">
+        <is>
+          <t>65.4</t>
+        </is>
+      </c>
+      <c r="B788" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C788" s="56" t="inlineStr">
+        <is>
+          <t>Personal Funnel</t>
+        </is>
+      </c>
+      <c r="D788" s="56" t="inlineStr">
+        <is>
+          <t>Mengekspor data Personal Funnel</t>
+        </is>
+      </c>
+      <c r="E788" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F788" s="55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G788" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik button Export.
+2. Klik icon download pada panel Download Export.</t>
+        </is>
+      </c>
+      <c r="H788" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil menampilkan panel Download Export.
+2. Berhasil mendownload file export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="789" ht="14" customHeight="1">
+      <c r="A789" s="55" t="inlineStr">
+        <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="B789" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C789" s="56" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D789" s="56" t="inlineStr">
+        <is>
+          <t>Membuka halaman Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E789" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F789" s="55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G789" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Rekap Funnel.</t>
+        </is>
+      </c>
+      <c r="H789" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Rekap Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="790" ht="14" customHeight="1">
+      <c r="A790" s="55" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="B790" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C790" s="56" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D790" s="56" t="inlineStr">
+        <is>
+          <t>Menampilkan data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E790" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F790" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G790" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun).
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H790" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Menampilkan data Rekap Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="791" ht="14" customHeight="1">
+      <c r="A791" s="55" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="B791" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C791" s="56" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D791" s="56" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E791" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F791" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G791" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H791" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi kriteria filter.
+2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="792" ht="14" customHeight="1">
+      <c r="A792" s="55" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="B792" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C792" s="56" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D792" s="56" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E792" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F792" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G792" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengosongkan field filter mandatory.
+2. Klik button Filter Data.</t>
+        </is>
+      </c>
+      <c r="H792" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Melakukan filter data Rekap Funnel tanpa mengisi field mandatory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="793" ht="14" customHeight="1">
+      <c r="A793" s="55" t="inlineStr">
+        <is>
+          <t>66.5</t>
+        </is>
+      </c>
+      <c r="B793" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C793" s="56" t="inlineStr">
+        <is>
+          <t>Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="D793" s="56" t="inlineStr">
+        <is>
+          <t>Mengunduh data Rekap Funnel</t>
+        </is>
+      </c>
+      <c r="E793" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F793" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G793" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik button Download Excel.</t>
+        </is>
+      </c>
+      <c r="H793" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Mengunduh data Rekap Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="794" ht="14" customHeight="1">
+      <c r="A794" s="55" t="inlineStr">
+        <is>
+          <t>67.1</t>
+        </is>
+      </c>
+      <c r="B794" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C794" s="56" t="inlineStr">
+        <is>
+          <t>Regional Funnel</t>
+        </is>
+      </c>
+      <c r="D794" s="56" t="inlineStr">
+        <is>
+          <t>Membuka halaman Regional Funnel</t>
+        </is>
+      </c>
+      <c r="E794" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F794" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G794" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Regional Funnel.</t>
+        </is>
+      </c>
+      <c r="H794" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Membuka halaman Regional Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="795" ht="14" customHeight="1">
+      <c r="A795" s="55" t="inlineStr">
+        <is>
+          <t>67.2</t>
+        </is>
+      </c>
+      <c r="B795" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C795" s="56" t="inlineStr">
+        <is>
+          <t>Regional Funnel</t>
+        </is>
+      </c>
+      <c r="D795" s="56" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Regional Funnel</t>
+        </is>
+      </c>
+      <c r="E795" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F795" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G795" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengisi semua field filter mandatory.
+2. Klik button Submit.</t>
+        </is>
+      </c>
+      <c r="H795" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Melakukan filter data Regional Funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="796" ht="14" customHeight="1">
+      <c r="A796" s="55" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="B796" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C796" s="56" t="inlineStr">
+        <is>
+          <t>Regional Funnel</t>
+        </is>
+      </c>
+      <c r="D796" s="56" t="inlineStr">
+        <is>
+          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E796" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F796" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G796" s="56" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H765" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="766" ht="14" customHeight="1">
-      <c r="A766" s="55" t="inlineStr">
-        <is>
-          <t>61.4</t>
-        </is>
-      </c>
-      <c r="B766" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C766" s="56" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
-      <c r="D766" s="56" t="inlineStr">
-        <is>
-          <t>Mengekspor data Personal Funnel</t>
-        </is>
-      </c>
-      <c r="E766" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F766" s="55" t="inlineStr">
+      <c r="H796" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Melakukan filter data Regional Funnel tanpa mengisi field mandatory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="797" ht="14" customHeight="1">
+      <c r="A797" s="55" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="B797" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C797" s="56" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D797" s="56" t="inlineStr">
+        <is>
+          <t>Membuka halaman Pengaturan Funnel Lending</t>
+        </is>
+      </c>
+      <c r="E797" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F797" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G766" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik button Export.
-2. Klik icon download pada panel Download Export.</t>
-        </is>
-      </c>
-      <c r="H766" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan panel Download Export.
-2. Berhasil mendownload file export.</t>
-        </is>
-      </c>
-    </row>
-    <row r="767" ht="28" customHeight="1">
-      <c r="A767" s="55" t="inlineStr">
-        <is>
-          <t>62.1</t>
-        </is>
-      </c>
-      <c r="B767" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C767" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D767" s="56" t="inlineStr">
-        <is>
-          <t>Membuka halaman Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E767" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F767" s="55" t="inlineStr">
+      <c r="G797" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik menu Report Lending.
+2. Klik sub menu Pengaturan Funnel.</t>
+        </is>
+      </c>
+      <c r="H797" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil membuka menu Report Lending.
+2. Berhasil menampilkan halaman Pengaturan Funnel Lending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="798" ht="14" customHeight="1">
+      <c r="A798" s="55" t="inlineStr">
+        <is>
+          <t>68.2</t>
+        </is>
+      </c>
+      <c r="B798" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C798" s="56" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D798" s="56" t="inlineStr">
+        <is>
+          <t>Menampilkan data Pengaturan Funnel Lending berdasarkan section</t>
+        </is>
+      </c>
+      <c r="E798" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F798" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G798" s="56" t="inlineStr">
+        <is>
+          <t>1. Klik salah satu daftar section pada tabel.</t>
+        </is>
+      </c>
+      <c r="H798" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil Menampilkan data Pengaturan Funnel Lending berdasarkan section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="799" ht="14" customHeight="1">
+      <c r="A799" s="55" t="inlineStr">
+        <is>
+          <t>68.3</t>
+        </is>
+      </c>
+      <c r="B799" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C799" s="56" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D799" s="56" t="inlineStr">
+        <is>
+          <t>Mengubah data Pengaturan Funnel Lending</t>
+        </is>
+      </c>
+      <c r="E799" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F799" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G767" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Funding.
-2. Klik sub menu Rekap Funnel.</t>
-        </is>
-      </c>
-      <c r="H767" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Funding.
-2. Berhasil menampilkan halaman Rekap Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="768" ht="14" customHeight="1">
-      <c r="A768" s="55" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
-      </c>
-      <c r="B768" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C768" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D768" s="56" t="inlineStr">
-        <is>
-          <t>Menampilkan data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E768" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F768" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G768" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun).
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H768" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Menampilkan data Rekap Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="769" ht="14" customHeight="1">
-      <c r="A769" s="55" t="inlineStr">
-        <is>
-          <t>62.3</t>
-        </is>
-      </c>
-      <c r="B769" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C769" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D769" s="56" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E769" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F769" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G769" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H769" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi kriteria filter.
-2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="770" ht="14" customHeight="1">
-      <c r="A770" s="55" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="B770" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C770" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D770" s="56" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E770" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F770" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G770" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H770" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="771" ht="14" customHeight="1">
-      <c r="A771" s="55" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="B771" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C771" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D771" s="56" t="inlineStr">
-        <is>
-          <t>Mengunduh data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E771" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F771" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G771" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik button Download Excel.</t>
-        </is>
-      </c>
-      <c r="H771" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Mengunduh data Rekap Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="772" ht="14" customHeight="1">
-      <c r="A772" s="55" t="inlineStr">
-        <is>
-          <t>63.1</t>
-        </is>
-      </c>
-      <c r="B772" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C772" s="56" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D772" s="56" t="inlineStr">
-        <is>
-          <t>Membuka halaman Regional Funnel</t>
-        </is>
-      </c>
-      <c r="E772" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F772" s="55" t="inlineStr">
+      <c r="G799" s="56" t="inlineStr">
+        <is>
+          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
+2. Klik button Simpan Pengaturan.</t>
+        </is>
+      </c>
+      <c r="H799" s="56" t="inlineStr">
+        <is>
+          <t>1. Berhasil mengisi field Performance Percentage.
+2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="800" ht="14" customHeight="1">
+      <c r="A800" s="55" t="inlineStr">
+        <is>
+          <t>68.4</t>
+        </is>
+      </c>
+      <c r="B800" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C800" s="56" t="inlineStr">
+        <is>
+          <t>Pengaturan Funnel</t>
+        </is>
+      </c>
+      <c r="D800" s="56" t="inlineStr">
+        <is>
+          <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
+        </is>
+      </c>
+      <c r="E800" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F800" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G772" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Personal Funnel.</t>
-        </is>
-      </c>
-      <c r="H772" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Personal Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="773" ht="14" customHeight="1">
-      <c r="A773" s="55" t="inlineStr">
-        <is>
-          <t>63.2</t>
-        </is>
-      </c>
-      <c r="B773" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C773" s="56" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D773" s="56" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Regional Funnel</t>
-        </is>
-      </c>
-      <c r="E773" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F773" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G773" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengisi semua field filter mandatory.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H773" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field filter mandatory.
-2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="774" ht="14" customHeight="1">
-      <c r="A774" s="55" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
-      </c>
-      <c r="B774" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C774" s="56" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D774" s="56" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E774" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F774" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G774" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H774" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="775" ht="14" customHeight="1">
-      <c r="A775" s="55" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="B775" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C775" s="56" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D775" s="56" t="inlineStr">
-        <is>
-          <t>Mencari data Regional Funnel dengan keyword valid</t>
-        </is>
-      </c>
-      <c r="E775" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F775" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G775" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengisi field Cari Data dengan keyword valid.
-2. Klik button Search.</t>
-        </is>
-      </c>
-      <c r="H775" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Mencari data Regional Funnel dengan keyword valid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="776" ht="14" customHeight="1">
-      <c r="A776" s="55" t="inlineStr">
-        <is>
-          <t>63.5</t>
-        </is>
-      </c>
-      <c r="B776" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C776" s="56" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D776" s="56" t="inlineStr">
-        <is>
-          <t>Mencari data Regional Funnel dengan keyword tidak valid</t>
-        </is>
-      </c>
-      <c r="E776" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F776" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G776" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengisi field Cari Data dengan keyword tidak valid.
-2. Klik button Search.</t>
-        </is>
-      </c>
-      <c r="H776" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Mencari data Regional Funnel dengan keyword tidak valid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="777" ht="14" customHeight="1">
-      <c r="A777" s="55" t="inlineStr">
-        <is>
-          <t>63.6</t>
-        </is>
-      </c>
-      <c r="B777" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C777" s="56" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D777" s="56" t="inlineStr">
-        <is>
-          <t>Menampilkan data prospek berdasarkan kantor cabang</t>
-        </is>
-      </c>
-      <c r="E777" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F777" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G777" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik salah satu daftar kantor cabang pada tabel.</t>
-        </is>
-      </c>
-      <c r="H777" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Menampilkan data prospek berdasarkan kantor cabang.</t>
-        </is>
-      </c>
-    </row>
-    <row r="778" ht="14" customHeight="1">
-      <c r="A778" s="55" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="B778" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C778" s="56" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D778" s="56" t="inlineStr">
-        <is>
-          <t>Membuka halaman Pengaturan Funnel Funding</t>
-        </is>
-      </c>
-      <c r="E778" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F778" s="55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G778" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Funding.
-2. Klik sub menu Pengaturan Funnel.</t>
-        </is>
-      </c>
-      <c r="H778" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Funding.
-2. Berhasil menampilkan halaman Pengaturan Funnel Funding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="779" ht="28" customHeight="1">
-      <c r="A779" s="55" t="inlineStr">
-        <is>
-          <t>64.2</t>
-        </is>
-      </c>
-      <c r="B779" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C779" s="56" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D779" s="56" t="inlineStr">
-        <is>
-          <t>Menampilkan data Pengaturan Funnel Funding berdasarkan section</t>
-        </is>
-      </c>
-      <c r="E779" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F779" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G779" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik salah satu daftar section pada tabel.</t>
-        </is>
-      </c>
-      <c r="H779" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Menampilkan data Pengaturan Funnel Funding berdasarkan section.</t>
-        </is>
-      </c>
-    </row>
-    <row r="780" ht="14" customHeight="1">
-      <c r="A780" s="55" t="inlineStr">
-        <is>
-          <t>64.3</t>
-        </is>
-      </c>
-      <c r="B780" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C780" s="56" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D780" s="56" t="inlineStr">
-        <is>
-          <t>Mengubah data Pengaturan Funnel Funding</t>
-        </is>
-      </c>
-      <c r="E780" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F780" s="55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G780" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H780" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field Performance Percentage.
-2. Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="781" ht="28" customHeight="1">
-      <c r="A781" s="55" t="inlineStr">
-        <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="B781" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C781" s="56" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D781" s="56" t="inlineStr">
-        <is>
-          <t>Mengubah data Pengaturan Funnel Funding tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E781" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F781" s="55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G781" s="56" t="inlineStr">
+      <c r="G800" s="56" t="inlineStr">
         <is>
           <t>1. Mengosongkan field mandatory Performance Percentage.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H781" s="56" t="inlineStr">
+2. Klik button Simpan Pengaturan.</t>
+        </is>
+      </c>
+      <c r="H800" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field Performance Percentage.
 2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
-    <row r="782" ht="14" customHeight="1">
-      <c r="A782" s="55" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
-      <c r="B782" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C782" s="56" t="inlineStr">
+    <row r="801" ht="14" customHeight="1">
+      <c r="A801" s="55" t="inlineStr">
+        <is>
+          <t>68.5</t>
+        </is>
+      </c>
+      <c r="B801" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C801" s="56" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D782" s="56" t="inlineStr">
+      <c r="D801" s="56" t="inlineStr">
         <is>
           <t>Menambahkan Condition pada Performance Indicator</t>
         </is>
       </c>
-      <c r="E782" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F782" s="55" t="inlineStr">
+      <c r="E801" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F801" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G782" s="56" t="inlineStr">
+      <c r="G801" s="56" t="inlineStr">
         <is>
           <t>1. Klik button Add Condition pada bagian Performance Indicator.
 2. Mengisi semua field mandatory pada condition baru.
 3. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H782" s="56" t="inlineStr">
+      <c r="H801" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil Menambahkan Condition pada Performance Indicator.</t>
         </is>
       </c>
     </row>
-    <row r="783" ht="14" customHeight="1">
-      <c r="A783" s="55" t="inlineStr">
-        <is>
-          <t>64.6</t>
-        </is>
-      </c>
-      <c r="B783" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C783" s="56" t="inlineStr">
+    <row r="802" ht="14" customHeight="1">
+      <c r="A802" s="55" t="inlineStr">
+        <is>
+          <t>68.6</t>
+        </is>
+      </c>
+      <c r="B802" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C802" s="56" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D783" s="56" t="inlineStr">
+      <c r="D802" s="56" t="inlineStr">
         <is>
           <t>Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E783" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F783" s="55" t="inlineStr">
+      <c r="E802" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F802" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G783" s="56" t="inlineStr">
+      <c r="G802" s="56" t="inlineStr">
         <is>
           <t>1. Klik button Add Condition pada bagian Performance Indicator.
 2. Mengosongkan field mandatory pada condition baru.
 3. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H783" s="56" t="inlineStr">
+      <c r="H802" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory.</t>
         </is>
       </c>
     </row>
-    <row r="784" ht="14" customHeight="1">
-      <c r="A784" s="55" t="inlineStr">
-        <is>
-          <t>64.7</t>
-        </is>
-      </c>
-      <c r="B784" s="56" t="inlineStr">
-        <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C784" s="56" t="inlineStr">
+    <row r="803" ht="14" customHeight="1">
+      <c r="A803" s="55" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="B803" s="56" t="inlineStr">
+        <is>
+          <t>Report Lending</t>
+        </is>
+      </c>
+      <c r="C803" s="56" t="inlineStr">
         <is>
           <t>Pengaturan Funnel</t>
         </is>
       </c>
-      <c r="D784" s="56" t="inlineStr">
+      <c r="D803" s="56" t="inlineStr">
         <is>
           <t>Menghapus Condition pada Performance Indicator</t>
         </is>
       </c>
-      <c r="E784" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F784" s="55" t="inlineStr">
+      <c r="E803" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F803" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G784" s="56" t="inlineStr">
+      <c r="G803" s="56" t="inlineStr">
         <is>
           <t>1. Klik button Remove pada salah satu condition di Performance Indicator.
 2. Klik button Submit.</t>
         </is>
       </c>
-      <c r="H784" s="56" t="inlineStr">
+      <c r="H803" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil Menghapus Condition pada Performance Indicator.</t>
         </is>
       </c>
     </row>
-    <row r="785" ht="14" customHeight="1">
-      <c r="A785" s="55" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
-      <c r="B785" s="56" t="inlineStr">
+    <row r="804" ht="14" customHeight="1">
+      <c r="A804" s="55" t="inlineStr">
+        <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="B804" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C785" s="56" t="inlineStr">
+      <c r="C804" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D785" s="56" t="inlineStr">
+      <c r="D804" s="56" t="inlineStr">
         <is>
           <t>Membuka halaman Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="E785" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F785" s="55" t="inlineStr">
+      <c r="E804" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F804" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G785" s="56" t="inlineStr">
+      <c r="G804" s="56" t="inlineStr">
         <is>
           <t>1. Klik menu Report Lending.
 2. Klik sub menu Daily Sales Agenda.</t>
         </is>
       </c>
-      <c r="H785" s="56" t="inlineStr">
+      <c r="H804" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil membuka menu Report Lending.
 2. Berhasil menampilkan halaman Daily Sales Agenda.</t>
         </is>
       </c>
     </row>
-    <row r="786" ht="14" customHeight="1">
-      <c r="A786" s="55" t="inlineStr">
-        <is>
-          <t>65.2</t>
-        </is>
-      </c>
-      <c r="B786" s="56" t="inlineStr">
+    <row r="805" ht="14" customHeight="1">
+      <c r="A805" s="55" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="B805" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C786" s="56" t="inlineStr">
+      <c r="C805" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D786" s="56" t="inlineStr">
+      <c r="D805" s="56" t="inlineStr">
         <is>
           <t>Melakukan filter data Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="E786" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F786" s="55" t="inlineStr">
+      <c r="E805" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F805" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G786" s="56" t="inlineStr">
+      <c r="G805" s="56" t="inlineStr">
         <is>
           <t>1. Mengisi semua field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H786" s="56" t="inlineStr">
+      <c r="H805" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil mengisi field filter mandatory.
 2. Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
-    <row r="787" ht="14" customHeight="1">
-      <c r="A787" s="55" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
-      <c r="B787" s="56" t="inlineStr">
+    <row r="806" ht="14" customHeight="1">
+      <c r="A806" s="55" t="inlineStr">
+        <is>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="B806" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C787" s="56" t="inlineStr">
+      <c r="C806" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D787" s="56" t="inlineStr">
+      <c r="D806" s="56" t="inlineStr">
         <is>
           <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
         </is>
       </c>
-      <c r="E787" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F787" s="55" t="inlineStr">
+      <c r="E806" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F806" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G787" s="56" t="inlineStr">
+      <c r="G806" s="56" t="inlineStr">
         <is>
           <t>1. Mengosongkan field filter mandatory.
 2. Klik button Filter Data.</t>
         </is>
       </c>
-      <c r="H787" s="56" t="inlineStr">
+      <c r="H806" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil mengosongkan field filter mandatory.
 2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
-    <row r="788" ht="14" customHeight="1">
-      <c r="A788" s="55" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
-      </c>
-      <c r="B788" s="56" t="inlineStr">
+    <row r="807" ht="14" customHeight="1">
+      <c r="A807" s="55" t="inlineStr">
+        <is>
+          <t>69.4</t>
+        </is>
+      </c>
+      <c r="B807" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C788" s="56" t="inlineStr">
+      <c r="C807" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D788" s="56" t="inlineStr">
+      <c r="D807" s="56" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Masuk</t>
         </is>
       </c>
-      <c r="E788" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F788" s="55" t="inlineStr">
+      <c r="E807" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F807" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G788" s="56" t="inlineStr">
+      <c r="G807" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.</t>
         </is>
       </c>
-      <c r="H788" s="56" t="inlineStr">
+      <c r="H807" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Masuk.</t>
         </is>
       </c>
     </row>
-    <row r="789" ht="14" customHeight="1">
-      <c r="A789" s="55" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="B789" s="56" t="inlineStr">
+    <row r="808" ht="14" customHeight="1">
+      <c r="A808" s="55" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="B808" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C789" s="56" t="inlineStr">
+      <c r="C808" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D789" s="56" t="inlineStr">
+      <c r="D808" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Masuk dengan keyword valid</t>
         </is>
       </c>
-      <c r="E789" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F789" s="55" t="inlineStr">
+      <c r="E808" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F808" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G789" s="56" t="inlineStr">
+      <c r="G808" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H789" s="56" t="inlineStr">
+      <c r="H808" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil mengisi field Cari Data.
@@ -34649,45 +35473,45 @@
         </is>
       </c>
     </row>
-    <row r="790" ht="14" customHeight="1">
-      <c r="A790" s="55" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="B790" s="56" t="inlineStr">
+    <row r="809" ht="14" customHeight="1">
+      <c r="A809" s="55" t="inlineStr">
+        <is>
+          <t>69.6</t>
+        </is>
+      </c>
+      <c r="B809" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C790" s="56" t="inlineStr">
+      <c r="C809" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D790" s="56" t="inlineStr">
+      <c r="D809" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E790" s="56" t="inlineStr">
+      <c r="E809" s="56" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F790" s="55" t="inlineStr">
+      <c r="F809" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G790" s="56" t="inlineStr">
+      <c r="G809" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H790" s="56" t="inlineStr">
+      <c r="H809" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil mengisi field Cari Data.
@@ -34695,89 +35519,89 @@
         </is>
       </c>
     </row>
-    <row r="791" ht="14" customHeight="1">
-      <c r="A791" s="55" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="B791" s="56" t="inlineStr">
+    <row r="810" ht="42" customHeight="1">
+      <c r="A810" s="55" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="B810" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C791" s="56" t="inlineStr">
+      <c r="C810" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D791" s="56" t="inlineStr">
+      <c r="D810" s="56" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Masuk</t>
         </is>
       </c>
-      <c r="E791" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F791" s="55" t="inlineStr">
+      <c r="E810" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F810" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G791" s="56" t="inlineStr">
+      <c r="G810" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H791" s="56" t="inlineStr">
+      <c r="H810" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="792" ht="14" customHeight="1">
-      <c r="A792" s="55" t="inlineStr">
-        <is>
-          <t>65.8</t>
-        </is>
-      </c>
-      <c r="B792" s="56" t="inlineStr">
+    <row r="811" ht="28" customHeight="1">
+      <c r="A811" s="55" t="inlineStr">
+        <is>
+          <t>69.8</t>
+        </is>
+      </c>
+      <c r="B811" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C792" s="56" t="inlineStr">
+      <c r="C811" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D792" s="56" t="inlineStr">
+      <c r="D811" s="56" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Masuk</t>
         </is>
       </c>
-      <c r="E792" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F792" s="55" t="inlineStr">
+      <c r="E811" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F811" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G792" s="56" t="inlineStr">
+      <c r="G811" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Masuk.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H792" s="56" t="inlineStr">
+      <c r="H811" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Masuk.
 2. Berhasil menampilkan panel Download Export.
@@ -34785,87 +35609,87 @@
         </is>
       </c>
     </row>
-    <row r="793" ht="14" customHeight="1">
-      <c r="A793" s="55" t="inlineStr">
-        <is>
-          <t>65.9</t>
-        </is>
-      </c>
-      <c r="B793" s="56" t="inlineStr">
+    <row r="812" ht="42" customHeight="1">
+      <c r="A812" s="55" t="inlineStr">
+        <is>
+          <t>69.9</t>
+        </is>
+      </c>
+      <c r="B812" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C793" s="56" t="inlineStr">
+      <c r="C812" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D793" s="56" t="inlineStr">
+      <c r="D812" s="56" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Closing</t>
         </is>
       </c>
-      <c r="E793" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F793" s="55" t="inlineStr">
+      <c r="E812" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F812" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G793" s="56" t="inlineStr">
+      <c r="G812" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.</t>
         </is>
       </c>
-      <c r="H793" s="56" t="inlineStr">
+      <c r="H812" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Closing.</t>
         </is>
       </c>
     </row>
-    <row r="794" ht="14" customHeight="1">
-      <c r="A794" s="55" t="inlineStr">
-        <is>
-          <t>65.10</t>
-        </is>
-      </c>
-      <c r="B794" s="56" t="inlineStr">
+    <row r="813" ht="28" customHeight="1">
+      <c r="A813" s="55" t="inlineStr">
+        <is>
+          <t>69.10</t>
+        </is>
+      </c>
+      <c r="B813" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C794" s="56" t="inlineStr">
+      <c r="C813" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D794" s="56" t="inlineStr">
+      <c r="D813" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Closing dengan keyword valid</t>
         </is>
       </c>
-      <c r="E794" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F794" s="55" t="inlineStr">
+      <c r="E813" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F813" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G794" s="56" t="inlineStr">
+      <c r="G813" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H794" s="56" t="inlineStr">
+      <c r="H813" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil mengisi field Cari Data.
@@ -34873,45 +35697,45 @@
         </is>
       </c>
     </row>
-    <row r="795" ht="14" customHeight="1">
-      <c r="A795" s="55" t="inlineStr">
-        <is>
-          <t>65.11</t>
-        </is>
-      </c>
-      <c r="B795" s="56" t="inlineStr">
+    <row r="814" ht="28" customHeight="1">
+      <c r="A814" s="55" t="inlineStr">
+        <is>
+          <t>69.11</t>
+        </is>
+      </c>
+      <c r="B814" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C795" s="56" t="inlineStr">
+      <c r="C814" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D795" s="56" t="inlineStr">
+      <c r="D814" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E795" s="56" t="inlineStr">
+      <c r="E814" s="56" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F795" s="55" t="inlineStr">
+      <c r="F814" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G795" s="56" t="inlineStr">
+      <c r="G814" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H795" s="56" t="inlineStr">
+      <c r="H814" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil mengisi field Cari Data.
@@ -34919,89 +35743,89 @@
         </is>
       </c>
     </row>
-    <row r="796" ht="14" customHeight="1">
-      <c r="A796" s="55" t="inlineStr">
-        <is>
-          <t>65.12</t>
-        </is>
-      </c>
-      <c r="B796" s="56" t="inlineStr">
+    <row r="815" ht="56" customHeight="1">
+      <c r="A815" s="55" t="inlineStr">
+        <is>
+          <t>69.12</t>
+        </is>
+      </c>
+      <c r="B815" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C796" s="56" t="inlineStr">
+      <c r="C815" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D796" s="56" t="inlineStr">
+      <c r="D815" s="56" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Closing</t>
         </is>
       </c>
-      <c r="E796" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F796" s="55" t="inlineStr">
+      <c r="E815" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F815" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G796" s="56" t="inlineStr">
+      <c r="G815" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H796" s="56" t="inlineStr">
+      <c r="H815" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="797" ht="14" customHeight="1">
-      <c r="A797" s="55" t="inlineStr">
-        <is>
-          <t>65.13</t>
-        </is>
-      </c>
-      <c r="B797" s="56" t="inlineStr">
+    <row r="816" ht="56" customHeight="1">
+      <c r="A816" s="55" t="inlineStr">
+        <is>
+          <t>69.13</t>
+        </is>
+      </c>
+      <c r="B816" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C797" s="56" t="inlineStr">
+      <c r="C816" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D797" s="56" t="inlineStr">
+      <c r="D816" s="56" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Closing</t>
         </is>
       </c>
-      <c r="E797" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F797" s="55" t="inlineStr">
+      <c r="E816" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F816" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G797" s="56" t="inlineStr">
+      <c r="G816" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Closing.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H797" s="56" t="inlineStr">
+      <c r="H816" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Closing.
 2. Berhasil menampilkan panel Download Export.
@@ -35009,87 +35833,87 @@
         </is>
       </c>
     </row>
-    <row r="798" ht="14" customHeight="1">
-      <c r="A798" s="55" t="inlineStr">
-        <is>
-          <t>65.14</t>
-        </is>
-      </c>
-      <c r="B798" s="56" t="inlineStr">
+    <row r="817" ht="28" customHeight="1">
+      <c r="A817" s="55" t="inlineStr">
+        <is>
+          <t>69.14</t>
+        </is>
+      </c>
+      <c r="B817" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C798" s="56" t="inlineStr">
+      <c r="C817" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D798" s="56" t="inlineStr">
+      <c r="D817" s="56" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Referal</t>
         </is>
       </c>
-      <c r="E798" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F798" s="55" t="inlineStr">
+      <c r="E817" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F817" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G798" s="56" t="inlineStr">
+      <c r="G817" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.</t>
         </is>
       </c>
-      <c r="H798" s="56" t="inlineStr">
+      <c r="H817" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Referal.</t>
         </is>
       </c>
     </row>
-    <row r="799" ht="14" customHeight="1">
-      <c r="A799" s="55" t="inlineStr">
-        <is>
-          <t>65.15</t>
-        </is>
-      </c>
-      <c r="B799" s="56" t="inlineStr">
+    <row r="818" ht="28" customHeight="1">
+      <c r="A818" s="55" t="inlineStr">
+        <is>
+          <t>69.15</t>
+        </is>
+      </c>
+      <c r="B818" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C799" s="56" t="inlineStr">
+      <c r="C818" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D799" s="56" t="inlineStr">
+      <c r="D818" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal dengan keyword valid</t>
         </is>
       </c>
-      <c r="E799" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F799" s="55" t="inlineStr">
+      <c r="E818" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F818" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G799" s="56" t="inlineStr">
+      <c r="G818" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H799" s="56" t="inlineStr">
+      <c r="H818" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil mengisi field Cari Data.
@@ -35097,45 +35921,45 @@
         </is>
       </c>
     </row>
-    <row r="800" ht="14" customHeight="1">
-      <c r="A800" s="55" t="inlineStr">
-        <is>
-          <t>65.16</t>
-        </is>
-      </c>
-      <c r="B800" s="56" t="inlineStr">
+    <row r="819" ht="42" customHeight="1">
+      <c r="A819" s="55" t="inlineStr">
+        <is>
+          <t>69.16</t>
+        </is>
+      </c>
+      <c r="B819" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C800" s="56" t="inlineStr">
+      <c r="C819" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D800" s="56" t="inlineStr">
+      <c r="D819" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E800" s="56" t="inlineStr">
+      <c r="E819" s="56" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F800" s="55" t="inlineStr">
+      <c r="F819" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G800" s="56" t="inlineStr">
+      <c r="G819" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H800" s="56" t="inlineStr">
+      <c r="H819" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil mengisi field Cari Data.
@@ -35143,89 +35967,89 @@
         </is>
       </c>
     </row>
-    <row r="801" ht="14" customHeight="1">
-      <c r="A801" s="55" t="inlineStr">
-        <is>
-          <t>65.17</t>
-        </is>
-      </c>
-      <c r="B801" s="56" t="inlineStr">
+    <row r="820" ht="14" customHeight="1">
+      <c r="A820" s="55" t="inlineStr">
+        <is>
+          <t>69.17</t>
+        </is>
+      </c>
+      <c r="B820" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C801" s="56" t="inlineStr">
+      <c r="C820" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D801" s="56" t="inlineStr">
+      <c r="D820" s="56" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Referal</t>
         </is>
       </c>
-      <c r="E801" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F801" s="55" t="inlineStr">
+      <c r="E820" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F820" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G801" s="56" t="inlineStr">
+      <c r="G820" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H801" s="56" t="inlineStr">
+      <c r="H820" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="802" ht="14" customHeight="1">
-      <c r="A802" s="55" t="inlineStr">
-        <is>
-          <t>65.18</t>
-        </is>
-      </c>
-      <c r="B802" s="56" t="inlineStr">
+    <row r="821" ht="56" customHeight="1">
+      <c r="A821" s="55" t="inlineStr">
+        <is>
+          <t>69.18</t>
+        </is>
+      </c>
+      <c r="B821" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C802" s="56" t="inlineStr">
+      <c r="C821" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D802" s="56" t="inlineStr">
+      <c r="D821" s="56" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Referal</t>
         </is>
       </c>
-      <c r="E802" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F802" s="55" t="inlineStr">
+      <c r="E821" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F821" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G802" s="56" t="inlineStr">
+      <c r="G821" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H802" s="56" t="inlineStr">
+      <c r="H821" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal.
 2. Berhasil menampilkan panel Download Export.
@@ -35233,87 +36057,87 @@
         </is>
       </c>
     </row>
-    <row r="803" ht="14" customHeight="1">
-      <c r="A803" s="55" t="inlineStr">
-        <is>
-          <t>65.19</t>
-        </is>
-      </c>
-      <c r="B803" s="56" t="inlineStr">
+    <row r="822" ht="56" customHeight="1">
+      <c r="A822" s="55" t="inlineStr">
+        <is>
+          <t>69.19</t>
+        </is>
+      </c>
+      <c r="B822" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C803" s="56" t="inlineStr">
+      <c r="C822" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D803" s="56" t="inlineStr">
+      <c r="D822" s="56" t="inlineStr">
         <is>
           <t>Menampilkan data tab Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E803" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F803" s="55" t="inlineStr">
+      <c r="E822" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F822" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G803" s="56" t="inlineStr">
+      <c r="G822" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.</t>
         </is>
       </c>
-      <c r="H803" s="56" t="inlineStr">
+      <c r="H822" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
         </is>
       </c>
     </row>
-    <row r="804" ht="14" customHeight="1">
-      <c r="A804" s="55" t="inlineStr">
-        <is>
-          <t>65.20</t>
-        </is>
-      </c>
-      <c r="B804" s="56" t="inlineStr">
+    <row r="823" ht="56" customHeight="1">
+      <c r="A823" s="55" t="inlineStr">
+        <is>
+          <t>69.20</t>
+        </is>
+      </c>
+      <c r="B823" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C804" s="56" t="inlineStr">
+      <c r="C823" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D804" s="56" t="inlineStr">
+      <c r="D823" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
         </is>
       </c>
-      <c r="E804" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F804" s="55" t="inlineStr">
+      <c r="E823" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F823" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G804" s="56" t="inlineStr">
+      <c r="G823" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Mengisi field Cari Data dengan keyword valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H804" s="56" t="inlineStr">
+      <c r="H823" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil mengisi field Cari Data.
@@ -35321,45 +36145,45 @@
         </is>
       </c>
     </row>
-    <row r="805" ht="14" customHeight="1">
-      <c r="A805" s="55" t="inlineStr">
-        <is>
-          <t>65.21</t>
-        </is>
-      </c>
-      <c r="B805" s="56" t="inlineStr">
+    <row r="824" ht="14" customHeight="1">
+      <c r="A824" s="55" t="inlineStr">
+        <is>
+          <t>69.21</t>
+        </is>
+      </c>
+      <c r="B824" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C805" s="56" t="inlineStr">
+      <c r="C824" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D805" s="56" t="inlineStr">
+      <c r="D824" s="56" t="inlineStr">
         <is>
           <t>Mencari data Prospek Referal Closing dengan keyword tidak valid</t>
         </is>
       </c>
-      <c r="E805" s="56" t="inlineStr">
+      <c r="E824" s="56" t="inlineStr">
         <is>
           <t>Negative Case</t>
         </is>
       </c>
-      <c r="F805" s="55" t="inlineStr">
+      <c r="F824" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G805" s="56" t="inlineStr">
+      <c r="G824" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Mengisi field Cari Data dengan keyword tidak valid.
 3. Klik button Search.</t>
         </is>
       </c>
-      <c r="H805" s="56" t="inlineStr">
+      <c r="H824" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil mengisi field Cari Data.
@@ -35367,917 +36191,93 @@
         </is>
       </c>
     </row>
-    <row r="806" ht="14" customHeight="1">
-      <c r="A806" s="55" t="inlineStr">
-        <is>
-          <t>65.22</t>
-        </is>
-      </c>
-      <c r="B806" s="56" t="inlineStr">
+    <row r="825" ht="14" customHeight="1">
+      <c r="A825" s="55" t="inlineStr">
+        <is>
+          <t>69.22</t>
+        </is>
+      </c>
+      <c r="B825" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C806" s="56" t="inlineStr">
+      <c r="C825" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D806" s="56" t="inlineStr">
+      <c r="D825" s="56" t="inlineStr">
         <is>
           <t>Melihat detail Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E806" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F806" s="55" t="inlineStr">
+      <c r="E825" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F825" s="55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="G806" s="56" t="inlineStr">
+      <c r="G825" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Klik salah satu nama prospek pada tabel.</t>
         </is>
       </c>
-      <c r="H806" s="56" t="inlineStr">
+      <c r="H825" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
-    <row r="807" ht="14" customHeight="1">
-      <c r="A807" s="55" t="inlineStr">
-        <is>
-          <t>65.23</t>
-        </is>
-      </c>
-      <c r="B807" s="56" t="inlineStr">
+    <row r="826" ht="14" customHeight="1">
+      <c r="A826" s="55" t="inlineStr">
+        <is>
+          <t>69.23</t>
+        </is>
+      </c>
+      <c r="B826" s="56" t="inlineStr">
         <is>
           <t>Report Lending</t>
         </is>
       </c>
-      <c r="C807" s="56" t="inlineStr">
+      <c r="C826" s="56" t="inlineStr">
         <is>
           <t>Daily Sales Agenda</t>
         </is>
       </c>
-      <c r="D807" s="56" t="inlineStr">
+      <c r="D826" s="56" t="inlineStr">
         <is>
           <t>Mengekspor data tab Prospek Referal Closing</t>
         </is>
       </c>
-      <c r="E807" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F807" s="55" t="inlineStr">
+      <c r="E826" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F826" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G807" s="56" t="inlineStr">
+      <c r="G826" s="56" t="inlineStr">
         <is>
           <t>1. Klik tab Prospek Referal Closing.
 2. Klik button Export.
 3. Klik icon download pada panel Download Export.</t>
         </is>
       </c>
-      <c r="H807" s="56" t="inlineStr">
+      <c r="H826" s="56" t="inlineStr">
         <is>
           <t>1. Berhasil menampilkan tab Prospek Referal Closing.
 2. Berhasil menampilkan panel Download Export.
 3. Berhasil mendownload file export.</t>
-        </is>
-      </c>
-    </row>
-    <row r="808" ht="14" customHeight="1">
-      <c r="A808" s="55" t="inlineStr">
-        <is>
-          <t>66.1</t>
-        </is>
-      </c>
-      <c r="B808" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C808" s="56" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
-      <c r="D808" s="56" t="inlineStr">
-        <is>
-          <t>Membuka halaman Personal Funnel</t>
-        </is>
-      </c>
-      <c r="E808" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F808" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G808" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Personal Funnel.</t>
-        </is>
-      </c>
-      <c r="H808" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Membuka halaman Personal Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="809" ht="14" customHeight="1">
-      <c r="A809" s="55" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="B809" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C809" s="56" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
-      <c r="D809" s="56" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Personal Funnel</t>
-        </is>
-      </c>
-      <c r="E809" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F809" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G809" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengisi semua field filter mandatory.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H809" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Melakukan filter data Personal Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="810" ht="42" customHeight="1">
-      <c r="A810" s="55" t="inlineStr">
-        <is>
-          <t>66.3</t>
-        </is>
-      </c>
-      <c r="B810" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C810" s="56" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
-      <c r="D810" s="56" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E810" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F810" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G810" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H810" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field filter mandatory.
-2. Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="811" ht="28" customHeight="1">
-      <c r="A811" s="55" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="B811" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C811" s="56" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
-      <c r="D811" s="56" t="inlineStr">
-        <is>
-          <t>Mengekspor data Personal Funnel</t>
-        </is>
-      </c>
-      <c r="E811" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F811" s="55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G811" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik button Export.
-2. Klik icon download pada panel Download Export.</t>
-        </is>
-      </c>
-      <c r="H811" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil menampilkan panel Download Export.
-2. Berhasil mendownload file export.</t>
-        </is>
-      </c>
-    </row>
-    <row r="812" ht="42" customHeight="1">
-      <c r="A812" s="55" t="inlineStr">
-        <is>
-          <t>67.1</t>
-        </is>
-      </c>
-      <c r="B812" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C812" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D812" s="56" t="inlineStr">
-        <is>
-          <t>Membuka halaman Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E812" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F812" s="55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G812" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Rekap Funnel.</t>
-        </is>
-      </c>
-      <c r="H812" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Rekap Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="813" ht="28" customHeight="1">
-      <c r="A813" s="55" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
-      </c>
-      <c r="B813" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C813" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D813" s="56" t="inlineStr">
-        <is>
-          <t>Menampilkan data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E813" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F813" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G813" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun).
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H813" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Menampilkan data Rekap Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="814" ht="28" customHeight="1">
-      <c r="A814" s="55" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="B814" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C814" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D814" s="56" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E814" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F814" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G814" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role).
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H814" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi kriteria filter.
-2. Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
-        </is>
-      </c>
-    </row>
-    <row r="815" ht="56" customHeight="1">
-      <c r="A815" s="55" t="inlineStr">
-        <is>
-          <t>67.4</t>
-        </is>
-      </c>
-      <c r="B815" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C815" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D815" s="56" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E815" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F815" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G815" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Filter Data.</t>
-        </is>
-      </c>
-      <c r="H815" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Melakukan filter data Rekap Funnel tanpa mengisi field mandatory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="816" ht="56" customHeight="1">
-      <c r="A816" s="55" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
-      <c r="B816" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C816" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="D816" s="56" t="inlineStr">
-        <is>
-          <t>Mengunduh data Rekap Funnel</t>
-        </is>
-      </c>
-      <c r="E816" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F816" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G816" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik button Download Excel.</t>
-        </is>
-      </c>
-      <c r="H816" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Mengunduh data Rekap Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="817" ht="28" customHeight="1">
-      <c r="A817" s="55" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="B817" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C817" s="56" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D817" s="56" t="inlineStr">
-        <is>
-          <t>Membuka halaman Regional Funnel</t>
-        </is>
-      </c>
-      <c r="E817" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F817" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G817" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Regional Funnel.</t>
-        </is>
-      </c>
-      <c r="H817" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Membuka halaman Regional Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="818" ht="28" customHeight="1">
-      <c r="A818" s="55" t="inlineStr">
-        <is>
-          <t>68.2</t>
-        </is>
-      </c>
-      <c r="B818" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C818" s="56" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D818" s="56" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Regional Funnel</t>
-        </is>
-      </c>
-      <c r="E818" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F818" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G818" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengisi semua field filter mandatory.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H818" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Melakukan filter data Regional Funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="819" ht="42" customHeight="1">
-      <c r="A819" s="55" t="inlineStr">
-        <is>
-          <t>68.3</t>
-        </is>
-      </c>
-      <c r="B819" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C819" s="56" t="inlineStr">
-        <is>
-          <t>Regional Funnel</t>
-        </is>
-      </c>
-      <c r="D819" s="56" t="inlineStr">
-        <is>
-          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E819" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F819" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G819" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field filter mandatory.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H819" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Melakukan filter data Regional Funnel tanpa mengisi field mandatory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="820" ht="14" customHeight="1">
-      <c r="A820" s="55" t="inlineStr">
-        <is>
-          <t>69.1</t>
-        </is>
-      </c>
-      <c r="B820" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C820" s="56" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D820" s="56" t="inlineStr">
-        <is>
-          <t>Membuka halaman Pengaturan Funnel Lending</t>
-        </is>
-      </c>
-      <c r="E820" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F820" s="55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G820" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik menu Report Lending.
-2. Klik sub menu Pengaturan Funnel.</t>
-        </is>
-      </c>
-      <c r="H820" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil membuka menu Report Lending.
-2. Berhasil menampilkan halaman Pengaturan Funnel Lending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="821" ht="56" customHeight="1">
-      <c r="A821" s="55" t="inlineStr">
-        <is>
-          <t>69.2</t>
-        </is>
-      </c>
-      <c r="B821" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C821" s="56" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D821" s="56" t="inlineStr">
-        <is>
-          <t>Menampilkan data Pengaturan Funnel Lending berdasarkan section</t>
-        </is>
-      </c>
-      <c r="E821" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F821" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G821" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik salah satu daftar section pada tabel.</t>
-        </is>
-      </c>
-      <c r="H821" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Menampilkan data Pengaturan Funnel Lending berdasarkan section.</t>
-        </is>
-      </c>
-    </row>
-    <row r="822" ht="56" customHeight="1">
-      <c r="A822" s="55" t="inlineStr">
-        <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="B822" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C822" s="56" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D822" s="56" t="inlineStr">
-        <is>
-          <t>Mengubah data Pengaturan Funnel Lending</t>
-        </is>
-      </c>
-      <c r="E822" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F822" s="55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G822" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel.
-2. Klik button Simpan Pengaturan.</t>
-        </is>
-      </c>
-      <c r="H822" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengisi field Performance Percentage.
-2. Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="823" ht="56" customHeight="1">
-      <c r="A823" s="55" t="inlineStr">
-        <is>
-          <t>69.4</t>
-        </is>
-      </c>
-      <c r="B823" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C823" s="56" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D823" s="56" t="inlineStr">
-        <is>
-          <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E823" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F823" s="55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G823" s="56" t="inlineStr">
-        <is>
-          <t>1. Mengosongkan field mandatory Performance Percentage.
-2. Klik button Simpan Pengaturan.</t>
-        </is>
-      </c>
-      <c r="H823" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil mengosongkan field Performance Percentage.
-2. Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="824" ht="14" customHeight="1">
-      <c r="A824" s="55" t="inlineStr">
-        <is>
-          <t>69.5</t>
-        </is>
-      </c>
-      <c r="B824" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C824" s="56" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D824" s="56" t="inlineStr">
-        <is>
-          <t>Menambahkan Condition pada Performance Indicator</t>
-        </is>
-      </c>
-      <c r="E824" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F824" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G824" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik button Add Condition pada bagian Performance Indicator.
-2. Mengisi semua field mandatory pada condition baru.
-3. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H824" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Menambahkan Condition pada Performance Indicator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="825" ht="14" customHeight="1">
-      <c r="A825" s="55" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
-      <c r="B825" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C825" s="56" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D825" s="56" t="inlineStr">
-        <is>
-          <t>Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory</t>
-        </is>
-      </c>
-      <c r="E825" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F825" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G825" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik button Add Condition pada bagian Performance Indicator.
-2. Mengosongkan field mandatory pada condition baru.
-3. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H825" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="826" ht="14" customHeight="1">
-      <c r="A826" s="55" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
-      <c r="B826" s="56" t="inlineStr">
-        <is>
-          <t>Report Lending</t>
-        </is>
-      </c>
-      <c r="C826" s="56" t="inlineStr">
-        <is>
-          <t>Pengaturan Funnel</t>
-        </is>
-      </c>
-      <c r="D826" s="56" t="inlineStr">
-        <is>
-          <t>Menghapus Condition pada Performance Indicator</t>
-        </is>
-      </c>
-      <c r="E826" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F826" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G826" s="56" t="inlineStr">
-        <is>
-          <t>1. Klik button Remove pada salah satu condition di Performance Indicator.
-2. Klik button Submit.</t>
-        </is>
-      </c>
-      <c r="H826" s="56" t="inlineStr">
-        <is>
-          <t>1. Berhasil Menghapus Condition pada Performance Indicator.</t>
         </is>
       </c>
     </row>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z890"/>
+  <dimension ref="A1:Z891"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="12.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -26692,7 +26692,7 @@
       </c>
       <c r="D627" s="56" t="inlineStr">
         <is>
-          <t>mengunduh data tab sforce</t>
+          <t>mengunduh data sforce</t>
         </is>
       </c>
       <c r="E627" s="56" t="inlineStr">
@@ -29674,7 +29674,7 @@
       </c>
       <c r="D698" s="56" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci tidak valid (Negative test)</t>
+          <t>Mencari data kata kunci tidak valid</t>
         </is>
       </c>
       <c r="E698" s="56" t="inlineStr">
@@ -30435,12 +30435,12 @@
       </c>
       <c r="E716" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan membukan menu dashboard validate pipeline</t>
         </is>
       </c>
       <c r="F716" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G716" s="56" t="inlineStr">
@@ -30477,12 +30477,12 @@
       </c>
       <c r="E717" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan melakukan filter data bulan</t>
         </is>
       </c>
       <c r="F717" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G717" s="56" t="inlineStr">
@@ -30497,44 +30497,44 @@
       </c>
     </row>
     <row r="718" ht="28" customHeight="1">
-      <c r="A718" s="55" t="inlineStr">
+      <c r="A718" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="B718" s="56" t="inlineStr">
+      <c r="B718" t="inlineStr">
         <is>
           <t>Sales Force</t>
         </is>
       </c>
-      <c r="C718" s="56" t="inlineStr">
+      <c r="C718" t="inlineStr">
         <is>
           <t>Dashboard Validate Pipeline</t>
         </is>
       </c>
-      <c r="D718" s="56" t="inlineStr">
-        <is>
-          <t>Membuka detail Chart total pipeline DPK</t>
-        </is>
-      </c>
-      <c r="E718" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F718" s="55" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G718" s="56" t="inlineStr">
-        <is>
-          <t>Klik icon (Tanda Panah) pada Chart pipeline data kantor cabang</t>
-        </is>
-      </c>
-      <c r="H718" s="56" t="inlineStr">
-        <is>
-          <t>Menampilkan halaman detail pipeline data kantor cabang</t>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Melakukan filter data</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Memastikan melakukan filter data</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>Klik button filter – pilih kantor wilayah, kantor cabang, cabang pembantu – kemudian klik apply</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
@@ -30556,27 +30556,27 @@
       </c>
       <c r="D719" s="56" t="inlineStr">
         <is>
-          <t>Melihat data validate</t>
+          <t>Membuka detail Chart total pipeline DPK</t>
         </is>
       </c>
       <c r="E719" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan membuka detail chart total pipeline dpk</t>
         </is>
       </c>
       <c r="F719" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G719" s="56" t="inlineStr">
         <is>
-          <t>1. Klik button view validate</t>
+          <t>Klik icon (Tanda Panah) pada Chart pipeline data kantor cabang</t>
         </is>
       </c>
       <c r="H719" s="56" t="inlineStr">
         <is>
-          <t>Berhasil Menampilka list history validation</t>
+          <t>Menampilkan halaman detail pipeline data kantor cabang</t>
         </is>
       </c>
     </row>
@@ -30598,27 +30598,27 @@
       </c>
       <c r="D720" s="56" t="inlineStr">
         <is>
-          <t>Membuka detail</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E720" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="F720" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G720" s="56" t="inlineStr">
         <is>
-          <t>Klik button detail</t>
+          <t>Input kata kunci pada kolom pencarian</t>
         </is>
       </c>
       <c r="H720" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman detail Validate pipeline</t>
+          <t>Menampilkan data sesuai kata kunci yang diinput</t>
         </is>
       </c>
     </row>
@@ -30640,27 +30640,27 @@
       </c>
       <c r="D721" s="56" t="inlineStr">
         <is>
-          <t>Membuka detail Chart pipeline data kantor cabang</t>
+          <t>Membuka detail</t>
         </is>
       </c>
       <c r="E721" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan membuka detail</t>
         </is>
       </c>
       <c r="F721" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G721" s="56" t="inlineStr">
         <is>
-          <t>Klik icon (Tanda Panah) pada Chart pipeline data kantor cabang</t>
+          <t>Klik button detail</t>
         </is>
       </c>
       <c r="H721" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman detail pipeline data kantor cabang</t>
+          <t>Menampilkan halaman detail Validate pipeline</t>
         </is>
       </c>
     </row>
@@ -30682,27 +30682,27 @@
       </c>
       <c r="D722" s="56" t="inlineStr">
         <is>
-          <t>Melihat data validate</t>
+          <t>Membuka detail Chart pipeline data kantor cabang</t>
         </is>
       </c>
       <c r="E722" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan membuka detail chart pipeline data kantor cabang</t>
         </is>
       </c>
       <c r="F722" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G722" s="56" t="inlineStr">
         <is>
-          <t>1. Klik button view validate</t>
+          <t>Klik icon (Tanda Panah) pada Chart pipeline data kantor cabang</t>
         </is>
       </c>
       <c r="H722" s="56" t="inlineStr">
         <is>
-          <t>Berhasil Menampilka list history validation</t>
+          <t>Menampilkan halaman detail pipeline data kantor cabang</t>
         </is>
       </c>
     </row>
@@ -30724,27 +30724,27 @@
       </c>
       <c r="D723" s="56" t="inlineStr">
         <is>
-          <t>Membuka detail</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E723" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="F723" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G723" s="56" t="inlineStr">
         <is>
-          <t>Klik button detail</t>
+          <t>Input kata kunci pada kolom pencarian</t>
         </is>
       </c>
       <c r="H723" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman detail Validate pipeline</t>
+          <t>Menampilkan data sesuai kata kunci yang diinput</t>
         </is>
       </c>
     </row>
@@ -30766,27 +30766,27 @@
       </c>
       <c r="D724" s="56" t="inlineStr">
         <is>
-          <t>Membuka detail Chart Sales Input Pipeline</t>
+          <t>Membuka detail</t>
         </is>
       </c>
       <c r="E724" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan membuka detail</t>
         </is>
       </c>
       <c r="F724" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G724" s="56" t="inlineStr">
         <is>
-          <t>Klik icon (Tanda Panah) pada chart Sales Input Pipeline</t>
+          <t>Klik button detail</t>
         </is>
       </c>
       <c r="H724" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman detail Sales Input Pipeline</t>
+          <t>Menampilkan halaman detail Validate pipeline</t>
         </is>
       </c>
     </row>
@@ -30808,27 +30808,27 @@
       </c>
       <c r="D725" s="56" t="inlineStr">
         <is>
-          <t>Melihat data validate</t>
+          <t>Membuka detail Chart Sales Input Pipeline</t>
         </is>
       </c>
       <c r="E725" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan membuka detail chart sales input pipeline</t>
         </is>
       </c>
       <c r="F725" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G725" s="56" t="inlineStr">
         <is>
-          <t>1. Klik button view validate</t>
+          <t>Klik icon (Tanda Panah) pada chart Sales Input Pipeline</t>
         </is>
       </c>
       <c r="H725" s="56" t="inlineStr">
         <is>
-          <t>Berhasil Menampilka list history validation</t>
+          <t>Menampilkan halaman detail Sales Input Pipeline</t>
         </is>
       </c>
     </row>
@@ -30850,27 +30850,27 @@
       </c>
       <c r="D726" s="56" t="inlineStr">
         <is>
-          <t>Membuka detail</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E726" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="F726" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G726" s="56" t="inlineStr">
         <is>
-          <t>Klik button detail</t>
+          <t>Input kata kunci pada kolom pencarian</t>
         </is>
       </c>
       <c r="H726" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman detail Validate pipeline</t>
+          <t>Menampilkan data sesuai kata kunci yang diinput</t>
         </is>
       </c>
     </row>
@@ -30892,27 +30892,27 @@
       </c>
       <c r="D727" s="56" t="inlineStr">
         <is>
-          <t>Membuka detail Chart Pipeline Category</t>
+          <t>Membuka detail</t>
         </is>
       </c>
       <c r="E727" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan membuka detail</t>
         </is>
       </c>
       <c r="F727" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G727" s="56" t="inlineStr">
         <is>
-          <t>Klik icon (Tanda Panah) pada chart Pipeline Category</t>
+          <t>Klik button detail</t>
         </is>
       </c>
       <c r="H727" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman detail Pipeline Category</t>
+          <t>Menampilkan halaman detail Validate pipeline</t>
         </is>
       </c>
     </row>
@@ -30934,27 +30934,27 @@
       </c>
       <c r="D728" s="56" t="inlineStr">
         <is>
-          <t>Melihat data validate</t>
+          <t>Membuka detail Chart Pipeline Category</t>
         </is>
       </c>
       <c r="E728" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan membuka detail chart pipeline category</t>
         </is>
       </c>
       <c r="F728" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G728" s="56" t="inlineStr">
         <is>
-          <t>1. Klik button view validate</t>
+          <t>Klik icon (Tanda Panah) pada chart Pipeline Category</t>
         </is>
       </c>
       <c r="H728" s="56" t="inlineStr">
         <is>
-          <t>Berhasil Menampilka list history validation</t>
+          <t>Menampilkan halaman detail Pipeline Category</t>
         </is>
       </c>
     </row>
@@ -30976,27 +30976,27 @@
       </c>
       <c r="D729" s="56" t="inlineStr">
         <is>
-          <t>Membuka detail</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E729" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="F729" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G729" s="56" t="inlineStr">
         <is>
-          <t>Klik button detail</t>
+          <t>Input kata kunci pada kolom pencarian</t>
         </is>
       </c>
       <c r="H729" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman detail Validate pipeline</t>
+          <t>Menampilkan data sesuai kata kunci yang diinput</t>
         </is>
       </c>
     </row>
@@ -31018,27 +31018,27 @@
       </c>
       <c r="D730" s="56" t="inlineStr">
         <is>
-          <t>List validate Pipeline - mencari data pada kolom pencarian</t>
+          <t>Membuka detail</t>
         </is>
       </c>
       <c r="E730" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan membuka detail</t>
         </is>
       </c>
       <c r="F730" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G730" s="56" t="inlineStr">
         <is>
-          <t>Input data pada kolom pencarian</t>
+          <t>Klik button detail</t>
         </is>
       </c>
       <c r="H730" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai kata kunci yang diinput</t>
+          <t>Menampilkan halaman detail Validate pipeline</t>
         </is>
       </c>
     </row>
@@ -31060,27 +31060,27 @@
       </c>
       <c r="D731" s="56" t="inlineStr">
         <is>
-          <t>Membuka detail list validate pipeline</t>
+          <t>List validate Pipeline - mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E731" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan list validate pipeline - mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="F731" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G731" s="56" t="inlineStr">
         <is>
-          <t>Klik icon (Tanda Panah) pada list validate pipeline</t>
+          <t>Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H731" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman detail validate pipeline</t>
+          <t>Menampilkan data sesuai kata kunci yang diinput</t>
         </is>
       </c>
     </row>
@@ -31102,27 +31102,27 @@
       </c>
       <c r="D732" s="56" t="inlineStr">
         <is>
-          <t>Detail Validate Pipeline - Melakukan Filter data</t>
+          <t>Membuka detail list validate pipeline</t>
         </is>
       </c>
       <c r="E732" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan membuka detail list validate pipeline</t>
         </is>
       </c>
       <c r="F732" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G732" s="56" t="inlineStr">
         <is>
-          <t>Pilih kontor wilayah, kantor cabang, cabang pembantu, sales, job role, jenis Lembaga kemudian klik button filter</t>
+          <t>Klik icon (Tanda Panah) pada list validate pipeline</t>
         </is>
       </c>
       <c r="H732" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai filter yang dipilih</t>
+          <t>Menampilkan halaman detail validate pipeline</t>
         </is>
       </c>
     </row>
@@ -31144,27 +31144,27 @@
       </c>
       <c r="D733" s="56" t="inlineStr">
         <is>
-          <t>Detail Validate pipeline - mengunduh data validate pipeline</t>
+          <t>Detail Validate Pipeline - Melakukan Filter data</t>
         </is>
       </c>
       <c r="E733" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan detail validate pipeline - melakukan filter data</t>
         </is>
       </c>
       <c r="F733" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G733" s="56" t="inlineStr">
         <is>
-          <t>Klik button export data</t>
+          <t>Pilih kontor wilayah, kantor cabang, cabang pembantu, sales, job role, jenis Lembaga kemudian klik button filter</t>
         </is>
       </c>
       <c r="H733" s="56" t="inlineStr">
         <is>
-          <t>Berhasil megunduh data</t>
+          <t>Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
@@ -31186,27 +31186,27 @@
       </c>
       <c r="D734" s="56" t="inlineStr">
         <is>
-          <t>Melakukan Validate data menggunaka user BM</t>
+          <t>Detail Validate pipeline - mengunduh data validate pipeline</t>
         </is>
       </c>
       <c r="E734" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan detail validate pipeline - mengunduh data validate pipeline</t>
         </is>
       </c>
       <c r="F734" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G734" s="56" t="inlineStr">
         <is>
-          <t>Login menggunakan user BM - Masuk ke menu dashboard valiadate pipeline halaman detail validate - Pilih data dengan klik checkbox pada table - klik button validate - klik ok</t>
+          <t>Klik button export data</t>
         </is>
       </c>
       <c r="H734" s="56" t="inlineStr">
         <is>
-          <t>Berhasil melakukan validate pipeline dan data akan tampil pada user RO Head</t>
+          <t>Berhasil megunduh data</t>
         </is>
       </c>
     </row>
@@ -31228,27 +31228,27 @@
       </c>
       <c r="D735" s="56" t="inlineStr">
         <is>
-          <t>Melakukan validate all data menggunakan user BM</t>
+          <t>Melakukan Validate data menggunaka user BM</t>
         </is>
       </c>
       <c r="E735" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan melakukan validate data menggunaka user bm</t>
         </is>
       </c>
       <c r="F735" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G735" s="56" t="inlineStr">
         <is>
-          <t>Klik button validate all data - Klik ok</t>
+          <t>Login menggunakan user BM - Masuk ke menu dashboard valiadate pipeline halaman detail validate - Pilih data dengan klik checkbox pada table - klik button validate - klik ok</t>
         </is>
       </c>
       <c r="H735" s="56" t="inlineStr">
         <is>
-          <t>Berhasil melakukan validate data secara bersamaan dan data akan tampil pada user RO Head</t>
+          <t>Berhasil melakukan validate pipeline dan data akan tampil pada user RO Head</t>
         </is>
       </c>
     </row>
@@ -31270,27 +31270,27 @@
       </c>
       <c r="D736" s="56" t="inlineStr">
         <is>
-          <t>Melakukan unvalidate data menggunakan user BM</t>
+          <t>Melakukan validate all data menggunakan user BM</t>
         </is>
       </c>
       <c r="E736" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan melakukan validate all data menggunakan user bm</t>
         </is>
       </c>
       <c r="F736" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G736" s="56" t="inlineStr">
         <is>
-          <t>Klik Manage pada data yang sudah di validate - Klik button unalidate - input reason kemudian klik button submit</t>
+          <t>Klik button validate all data - Klik ok</t>
         </is>
       </c>
       <c r="H736" s="56" t="inlineStr">
         <is>
-          <t>Berhasil unvalidate pipeline</t>
+          <t>Berhasil melakukan validate data secara bersamaan dan data akan tampil pada user RO Head</t>
         </is>
       </c>
     </row>
@@ -31312,27 +31312,27 @@
       </c>
       <c r="D737" s="56" t="inlineStr">
         <is>
-          <t>Melakukan Validate data menggunaka user RO Head</t>
+          <t>Melakukan unvalidate data menggunakan user BM</t>
         </is>
       </c>
       <c r="E737" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan melakukan unvalidate data menggunakan user bm</t>
         </is>
       </c>
       <c r="F737" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G737" s="56" t="inlineStr">
         <is>
-          <t>Login menggunakan user RO Head - Masuk ke menu dashboard valiadate pipeline halaman detail validate - Pilih data dengan klik checkbox pada table - klik button validate - klik ok</t>
+          <t>Klik Manage pada data yang sudah di validate - Klik button unalidate - input reason kemudian klik button submit</t>
         </is>
       </c>
       <c r="H737" s="56" t="inlineStr">
         <is>
-          <t>Berhasil melakukan validate pipeline</t>
+          <t>Berhasil unvalidate pipeline</t>
         </is>
       </c>
     </row>
@@ -31354,27 +31354,27 @@
       </c>
       <c r="D738" s="56" t="inlineStr">
         <is>
-          <t>Melakukan validate all data menggunakan user RO Head</t>
+          <t>Melakukan Validate data menggunaka user RO Head</t>
         </is>
       </c>
       <c r="E738" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan melakukan validate data menggunaka user ro head</t>
         </is>
       </c>
       <c r="F738" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G738" s="56" t="inlineStr">
         <is>
-          <t>Klik button validate all data - Klik ok</t>
+          <t>Login menggunakan user RO Head - Masuk ke menu dashboard valiadate pipeline halaman detail validate - Pilih data dengan klik checkbox pada table - klik button validate - klik ok</t>
         </is>
       </c>
       <c r="H738" s="56" t="inlineStr">
         <is>
-          <t>Berhasil melakukan validate data secara bersamaan</t>
+          <t>Berhasil melakukan validate pipeline</t>
         </is>
       </c>
     </row>
@@ -31396,76 +31396,76 @@
       </c>
       <c r="D739" s="56" t="inlineStr">
         <is>
-          <t>Melakukan unvalidate data menggunakan user RO Head</t>
+          <t>Melakukan validate all data menggunakan user RO Head</t>
         </is>
       </c>
       <c r="E739" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan melakukan validate all data menggunakan user ro head</t>
         </is>
       </c>
       <c r="F739" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G739" s="56" t="inlineStr">
         <is>
-          <t>Klik Manage pada data yang sudah di validate - Klik button unalidate - input reason kemudian klik button submit</t>
+          <t>Klik button validate all data - Klik ok</t>
         </is>
       </c>
       <c r="H739" s="56" t="inlineStr">
         <is>
-          <t>Berhasil unvalidate pipeline</t>
+          <t>Berhasil melakukan validate data secara bersamaan</t>
         </is>
       </c>
     </row>
     <row r="740" ht="56" customHeight="1">
       <c r="A740" s="55" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.25</t>
         </is>
       </c>
       <c r="B740" s="56" t="inlineStr">
         <is>
-          <t>Report Funding</t>
+          <t>Sales Force</t>
         </is>
       </c>
       <c r="C740" s="56" t="inlineStr">
         <is>
-          <t>Personal Funnel</t>
+          <t>Dashboard Validate Pipeline</t>
         </is>
       </c>
       <c r="D740" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Personal Funnel</t>
+          <t>Melakukan unvalidate data menggunakan user RO Head</t>
         </is>
       </c>
       <c r="E740" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Memastikan melakukan unvalidate data menggunakan user ro head</t>
         </is>
       </c>
       <c r="F740" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G740" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Funding - Klik sub menu Personal Funnel</t>
+          <t>Klik Manage pada data yang sudah di validate - Klik button unalidate - input reason kemudian klik button submit</t>
         </is>
       </c>
       <c r="H740" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Personal Funnel.</t>
+          <t>Berhasil unvalidate pipeline</t>
         </is>
       </c>
     </row>
     <row r="741" ht="56" customHeight="1">
       <c r="A741" s="55" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="B741" s="56" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="D741" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Personal Funnel</t>
+          <t>Membuka halaman Personal Funnel</t>
         </is>
       </c>
       <c r="E741" s="56" t="inlineStr">
@@ -31490,24 +31490,24 @@
       </c>
       <c r="F741" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G741" s="56" t="inlineStr">
         <is>
-          <t>Mengisi semua field filter mandatory - Klik button Submit</t>
+          <t>Klik menu Report Funding - Klik sub menu Personal Funnel</t>
         </is>
       </c>
       <c r="H741" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+          <t>Berhasil menampilkan halaman Personal Funnel.</t>
         </is>
       </c>
     </row>
     <row r="742" ht="14" customHeight="1">
       <c r="A742" s="55" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="B742" s="56" t="inlineStr">
@@ -31522,7 +31522,7 @@
       </c>
       <c r="D742" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
+          <t>Melakukan filter data Personal Funnel</t>
         </is>
       </c>
       <c r="E742" s="56" t="inlineStr">
@@ -31537,19 +31537,19 @@
       </c>
       <c r="G742" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field filter mandatory - Klik button Submit</t>
+          <t>Mengisi semua field filter mandatory - Klik button Submit</t>
         </is>
       </c>
       <c r="H742" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="743" ht="14" customHeight="1">
       <c r="A743" s="55" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="B743" s="56" t="inlineStr">
@@ -31564,7 +31564,7 @@
       </c>
       <c r="D743" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data Personal Funnel</t>
+          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E743" s="56" t="inlineStr">
@@ -31574,24 +31574,24 @@
       </c>
       <c r="F743" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G743" s="56" t="inlineStr">
         <is>
-          <t>Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Mengosongkan field filter mandatory - Klik button Submit</t>
         </is>
       </c>
       <c r="H743" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="744" ht="14" customHeight="1">
       <c r="A744" s="55" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="B744" s="56" t="inlineStr">
@@ -31601,12 +31601,12 @@
       </c>
       <c r="C744" s="56" t="inlineStr">
         <is>
-          <t>Rekap Funnel</t>
+          <t>Personal Funnel</t>
         </is>
       </c>
       <c r="D744" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Rekap Funnel</t>
+          <t>Mengekspor data Personal Funnel</t>
         </is>
       </c>
       <c r="E744" s="56" t="inlineStr">
@@ -31621,19 +31621,19 @@
       </c>
       <c r="G744" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Funding - Klik sub menu Rekap Funnel</t>
+          <t>Klik button Export - Klik icon download pada panel Download Export</t>
         </is>
       </c>
       <c r="H744" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Rekap Funnel.</t>
+          <t>Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
     <row r="745" ht="14" customHeight="1">
       <c r="A745" s="55" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="B745" s="56" t="inlineStr">
@@ -31648,7 +31648,7 @@
       </c>
       <c r="D745" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data Rekap Funnel</t>
+          <t>Membuka halaman Rekap Funnel</t>
         </is>
       </c>
       <c r="E745" s="56" t="inlineStr">
@@ -31658,24 +31658,24 @@
       </c>
       <c r="F745" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G745" s="56" t="inlineStr">
         <is>
-          <t>Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun) - Klik button Filter Data</t>
+          <t>Klik menu Report Funding - Klik sub menu Rekap Funnel</t>
         </is>
       </c>
       <c r="H745" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
+          <t>Berhasil menampilkan halaman Rekap Funnel.</t>
         </is>
       </c>
     </row>
     <row r="746" ht="28" customHeight="1">
       <c r="A746" s="55" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="B746" s="56" t="inlineStr">
@@ -31690,7 +31690,7 @@
       </c>
       <c r="D746" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Rekap Funnel</t>
+          <t>Menampilkan data Rekap Funnel</t>
         </is>
       </c>
       <c r="E746" s="56" t="inlineStr">
@@ -31705,19 +31705,19 @@
       </c>
       <c r="G746" s="56" t="inlineStr">
         <is>
-          <t>Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role) - Klik button Filter Data</t>
+          <t>Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun) - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H746" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
+          <t>Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
         </is>
       </c>
     </row>
     <row r="747" ht="42" customHeight="1">
       <c r="A747" s="55" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="B747" s="56" t="inlineStr">
@@ -31732,7 +31732,7 @@
       </c>
       <c r="D747" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
+          <t>Melakukan filter data Rekap Funnel</t>
         </is>
       </c>
       <c r="E747" s="56" t="inlineStr">
@@ -31747,19 +31747,19 @@
       </c>
       <c r="G747" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field filter mandatory - Klik button Filter Data</t>
+          <t>Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role) - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H747" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="748" ht="28" customHeight="1">
       <c r="A748" s="55" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="B748" s="56" t="inlineStr">
@@ -31774,7 +31774,7 @@
       </c>
       <c r="D748" s="56" t="inlineStr">
         <is>
-          <t>Mengunduh data Rekap Funnel</t>
+          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E748" s="56" t="inlineStr">
@@ -31789,19 +31789,19 @@
       </c>
       <c r="G748" s="56" t="inlineStr">
         <is>
-          <t>Klik button Download Excel</t>
+          <t>Mengosongkan field filter mandatory - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H748" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file Excel data Rekap Funnel.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="749" ht="14" customHeight="1">
       <c r="A749" s="55" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="B749" s="56" t="inlineStr">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="C749" s="56" t="inlineStr">
         <is>
-          <t>Regional Funnel</t>
+          <t>Rekap Funnel</t>
         </is>
       </c>
       <c r="D749" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Regional Funnel</t>
+          <t>Mengunduh data Rekap Funnel</t>
         </is>
       </c>
       <c r="E749" s="56" t="inlineStr">
@@ -31826,24 +31826,24 @@
       </c>
       <c r="F749" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G749" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Funding - Klik sub menu Regional Funnel</t>
+          <t>Klik button Download Excel</t>
         </is>
       </c>
       <c r="H749" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Regional Funnel.</t>
+          <t>Berhasil mendownload file Excel data Rekap Funnel.</t>
         </is>
       </c>
     </row>
     <row r="750" ht="14" customHeight="1">
       <c r="A750" s="55" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="B750" s="56" t="inlineStr">
@@ -31858,7 +31858,7 @@
       </c>
       <c r="D750" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Regional Funnel</t>
+          <t>Membuka halaman Regional Funnel</t>
         </is>
       </c>
       <c r="E750" s="56" t="inlineStr">
@@ -31868,24 +31868,24 @@
       </c>
       <c r="F750" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G750" s="56" t="inlineStr">
         <is>
-          <t>Mengisi semua field filter mandatory - Klik button Submit</t>
+          <t>Klik menu Report Funding - Klik sub menu Regional Funnel</t>
         </is>
       </c>
       <c r="H750" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+          <t>Berhasil menampilkan halaman Regional Funnel.</t>
         </is>
       </c>
     </row>
     <row r="751" ht="14" customHeight="1">
       <c r="A751" s="55" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="B751" s="56" t="inlineStr">
@@ -31900,7 +31900,7 @@
       </c>
       <c r="D751" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
+          <t>Melakukan filter data Regional Funnel</t>
         </is>
       </c>
       <c r="E751" s="56" t="inlineStr">
@@ -31915,19 +31915,19 @@
       </c>
       <c r="G751" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field filter mandatory - Klik button Submit</t>
+          <t>Mengisi semua field filter mandatory - Klik button Submit</t>
         </is>
       </c>
       <c r="H751" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="752" ht="14" customHeight="1">
       <c r="A752" s="55" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="B752" s="56" t="inlineStr">
@@ -31942,7 +31942,7 @@
       </c>
       <c r="D752" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Regional Funnel dengan keyword valid</t>
+          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E752" s="56" t="inlineStr">
@@ -31957,19 +31957,19 @@
       </c>
       <c r="G752" s="56" t="inlineStr">
         <is>
-          <t>Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Mengosongkan field filter mandatory - Klik button Submit</t>
         </is>
       </c>
       <c r="H752" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="753" ht="14" customHeight="1">
       <c r="A753" s="55" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="B753" s="56" t="inlineStr">
@@ -31984,7 +31984,7 @@
       </c>
       <c r="D753" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Regional Funnel dengan keyword tidak valid</t>
+          <t>Mencari data Regional Funnel dengan keyword valid</t>
         </is>
       </c>
       <c r="E753" s="56" t="inlineStr">
@@ -31999,19 +31999,19 @@
       </c>
       <c r="G753" s="56" t="inlineStr">
         <is>
-          <t>Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
         </is>
       </c>
       <c r="H753" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil menampilkan data yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="754" ht="14" customHeight="1">
       <c r="A754" s="55" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="B754" s="56" t="inlineStr">
@@ -32026,7 +32026,7 @@
       </c>
       <c r="D754" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data prospek berdasarkan kantor cabang</t>
+          <t>Mencari data Regional Funnel dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E754" s="56" t="inlineStr">
@@ -32041,19 +32041,19 @@
       </c>
       <c r="G754" s="56" t="inlineStr">
         <is>
-          <t>Klik salah satu daftar kantor cabang pada tabel</t>
+          <t>Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
         </is>
       </c>
       <c r="H754" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data prospek pada kantor cabang yang dipilih.</t>
+          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="755" ht="14" customHeight="1">
       <c r="A755" s="55" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="B755" s="56" t="inlineStr">
@@ -32063,12 +32063,12 @@
       </c>
       <c r="C755" s="56" t="inlineStr">
         <is>
-          <t>Pengaturan Funnel</t>
+          <t>Regional Funnel</t>
         </is>
       </c>
       <c r="D755" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Pengaturan Funnel Funding</t>
+          <t>Menampilkan data prospek berdasarkan kantor cabang</t>
         </is>
       </c>
       <c r="E755" s="56" t="inlineStr">
@@ -32078,24 +32078,24 @@
       </c>
       <c r="F755" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G755" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Funding - Klik sub menu Pengaturan Funnel</t>
+          <t>Klik salah satu daftar kantor cabang pada tabel</t>
         </is>
       </c>
       <c r="H755" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Pengaturan Funnel Funding.</t>
+          <t>Berhasil menampilkan data prospek pada kantor cabang yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="756" ht="14" customHeight="1">
       <c r="A756" s="55" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="B756" s="56" t="inlineStr">
@@ -32110,7 +32110,7 @@
       </c>
       <c r="D756" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data Pengaturan Funnel Funding berdasarkan section</t>
+          <t>Membuka halaman Pengaturan Funnel Funding</t>
         </is>
       </c>
       <c r="E756" s="56" t="inlineStr">
@@ -32120,24 +32120,24 @@
       </c>
       <c r="F756" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G756" s="56" t="inlineStr">
         <is>
-          <t>Klik salah satu daftar section pada tabel</t>
+          <t>Klik menu Report Funding - Klik sub menu Pengaturan Funnel</t>
         </is>
       </c>
       <c r="H756" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pengaturan funnel Funding.</t>
+          <t>Berhasil menampilkan halaman Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
     <row r="757" ht="14" customHeight="1">
       <c r="A757" s="55" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="B757" s="56" t="inlineStr">
@@ -32152,7 +32152,7 @@
       </c>
       <c r="D757" s="56" t="inlineStr">
         <is>
-          <t>Mengubah data Pengaturan Funnel Funding</t>
+          <t>Menampilkan data Pengaturan Funnel Funding berdasarkan section</t>
         </is>
       </c>
       <c r="E757" s="56" t="inlineStr">
@@ -32162,24 +32162,24 @@
       </c>
       <c r="F757" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G757" s="56" t="inlineStr">
         <is>
-          <t>Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel - Klik button Submit</t>
+          <t>Klik salah satu daftar section pada tabel</t>
         </is>
       </c>
       <c r="H757" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
+          <t>Berhasil menampilkan data pengaturan funnel Funding.</t>
         </is>
       </c>
     </row>
     <row r="758" ht="14" customHeight="1">
       <c r="A758" s="55" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="B758" s="56" t="inlineStr">
@@ -32194,7 +32194,7 @@
       </c>
       <c r="D758" s="56" t="inlineStr">
         <is>
-          <t>Mengubah data Pengaturan Funnel Funding tanpa mengisi field mandatory</t>
+          <t>Mengubah data Pengaturan Funnel Funding</t>
         </is>
       </c>
       <c r="E758" s="56" t="inlineStr">
@@ -32209,19 +32209,19 @@
       </c>
       <c r="G758" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field mandatory Performance Percentage - Klik button Submit</t>
+          <t>Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel - Klik button Submit</t>
         </is>
       </c>
       <c r="H758" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+          <t>Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
     <row r="759" ht="14" customHeight="1">
       <c r="A759" s="55" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="B759" s="56" t="inlineStr">
@@ -32236,7 +32236,7 @@
       </c>
       <c r="D759" s="56" t="inlineStr">
         <is>
-          <t>Menambahkan Condition pada Performance Indicator</t>
+          <t>Mengubah data Pengaturan Funnel Funding tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E759" s="56" t="inlineStr">
@@ -32246,24 +32246,24 @@
       </c>
       <c r="F759" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G759" s="56" t="inlineStr">
         <is>
-          <t>Klik button Add Condition pada bagian Performance Indicator - Mengisi semua field mandatory pada condition baru - Klik button Submit</t>
+          <t>Mengosongkan field mandatory Performance Percentage - Klik button Submit</t>
         </is>
       </c>
       <c r="H759" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menyimpan condition baru pada Performance Indicator.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
     <row r="760" ht="14" customHeight="1">
       <c r="A760" s="55" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="B760" s="56" t="inlineStr">
@@ -32278,7 +32278,7 @@
       </c>
       <c r="D760" s="56" t="inlineStr">
         <is>
-          <t>Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory</t>
+          <t>Menambahkan Condition pada Performance Indicator</t>
         </is>
       </c>
       <c r="E760" s="56" t="inlineStr">
@@ -32293,19 +32293,19 @@
       </c>
       <c r="G760" s="56" t="inlineStr">
         <is>
-          <t>Klik button Add Condition pada bagian Performance Indicator - Mengosongkan field mandatory pada condition baru - Klik button Submit</t>
+          <t>Klik button Add Condition pada bagian Performance Indicator - Mengisi semua field mandatory pada condition baru - Klik button Submit</t>
         </is>
       </c>
       <c r="H760" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+          <t>Berhasil menyimpan condition baru pada Performance Indicator.</t>
         </is>
       </c>
     </row>
     <row r="761" ht="14" customHeight="1">
       <c r="A761" s="55" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="B761" s="56" t="inlineStr">
@@ -32320,7 +32320,7 @@
       </c>
       <c r="D761" s="56" t="inlineStr">
         <is>
-          <t>Menghapus Condition pada Performance Indicator</t>
+          <t>Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E761" s="56" t="inlineStr">
@@ -32335,19 +32335,19 @@
       </c>
       <c r="G761" s="56" t="inlineStr">
         <is>
-          <t>Klik button Remove pada salah satu condition di Performance Indicator - Klik button Submit</t>
+          <t>Klik button Add Condition pada bagian Performance Indicator - Mengosongkan field mandatory pada condition baru - Klik button Submit</t>
         </is>
       </c>
       <c r="H761" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
     <row r="762" ht="14" customHeight="1">
       <c r="A762" s="55" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>63.7</t>
         </is>
       </c>
       <c r="B762" s="56" t="inlineStr">
@@ -32357,12 +32357,12 @@
       </c>
       <c r="C762" s="56" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D762" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Daily Sales Agenda</t>
+          <t>Menghapus Condition pada Performance Indicator</t>
         </is>
       </c>
       <c r="E762" s="56" t="inlineStr">
@@ -32372,24 +32372,24 @@
       </c>
       <c r="F762" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G762" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Funding - Klik sub menu Daily Sales Agenda</t>
+          <t>Klik button Remove pada salah satu condition di Performance Indicator - Klik button Submit</t>
         </is>
       </c>
       <c r="H762" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Daily Sales Agenda.</t>
+          <t>Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
     <row r="763" ht="14" customHeight="1">
       <c r="A763" s="55" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="B763" s="56" t="inlineStr">
@@ -32404,7 +32404,7 @@
       </c>
       <c r="D763" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Daily Sales Agenda</t>
+          <t>Membuka halaman Daily Sales Agenda</t>
         </is>
       </c>
       <c r="E763" s="56" t="inlineStr">
@@ -32414,24 +32414,24 @@
       </c>
       <c r="F763" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G763" s="56" t="inlineStr">
         <is>
-          <t>Mengisi semua field filter mandatory - Klik button Filter Data</t>
+          <t>Klik menu Report Funding - Klik sub menu Daily Sales Agenda</t>
         </is>
       </c>
       <c r="H763" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+          <t>Berhasil menampilkan halaman Daily Sales Agenda.</t>
         </is>
       </c>
     </row>
     <row r="764" ht="14" customHeight="1">
       <c r="A764" s="55" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="B764" s="56" t="inlineStr">
@@ -32446,7 +32446,7 @@
       </c>
       <c r="D764" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
+          <t>Melakukan filter data Daily Sales Agenda</t>
         </is>
       </c>
       <c r="E764" s="56" t="inlineStr">
@@ -32461,19 +32461,19 @@
       </c>
       <c r="G764" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field filter mandatory - Klik button Filter Data</t>
+          <t>Mengisi semua field filter mandatory - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H764" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="765" ht="14" customHeight="1">
       <c r="A765" s="55" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="B765" s="56" t="inlineStr">
@@ -32488,7 +32488,7 @@
       </c>
       <c r="D765" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Masuk</t>
+          <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E765" s="56" t="inlineStr">
@@ -32503,19 +32503,19 @@
       </c>
       <c r="G765" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk</t>
+          <t>Mengosongkan field filter mandatory - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H765" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pada tab Prospek Masuk.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="766" ht="14" customHeight="1">
       <c r="A766" s="55" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="B766" s="56" t="inlineStr">
@@ -32530,7 +32530,7 @@
       </c>
       <c r="D766" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Masuk dengan keyword valid</t>
+          <t>Menampilkan data tab Prospek Masuk</t>
         </is>
       </c>
       <c r="E766" s="56" t="inlineStr">
@@ -32540,24 +32540,24 @@
       </c>
       <c r="F766" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G766" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Klik tab Prospek Masuk</t>
         </is>
       </c>
       <c r="H766" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan data pada tab Prospek Masuk.</t>
         </is>
       </c>
     </row>
     <row r="767" ht="28" customHeight="1">
       <c r="A767" s="55" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="B767" s="56" t="inlineStr">
@@ -32572,34 +32572,34 @@
       </c>
       <c r="D767" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
+          <t>Mencari data Prospek Masuk dengan keyword valid</t>
         </is>
       </c>
       <c r="E767" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F767" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G767" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Klik tab Prospek Masuk - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
         </is>
       </c>
       <c r="H767" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil menampilkan data yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="768" ht="14" customHeight="1">
       <c r="A768" s="55" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="B768" s="56" t="inlineStr">
@@ -32614,12 +32614,12 @@
       </c>
       <c r="D768" s="56" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Masuk</t>
+          <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E768" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F768" s="55" t="inlineStr">
@@ -32629,19 +32629,19 @@
       </c>
       <c r="G768" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk - Klik salah satu nama prospek pada tabel</t>
+          <t>Klik tab Prospek Masuk - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
         </is>
       </c>
       <c r="H768" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman detail prospek.</t>
+          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="769" ht="14" customHeight="1">
       <c r="A769" s="55" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="B769" s="56" t="inlineStr">
@@ -32656,7 +32656,7 @@
       </c>
       <c r="D769" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data tab Prospek Masuk</t>
+          <t>Melihat detail Prospek Masuk</t>
         </is>
       </c>
       <c r="E769" s="56" t="inlineStr">
@@ -32666,24 +32666,24 @@
       </c>
       <c r="F769" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G769" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk - Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Klik tab Prospek Masuk - Klik salah satu nama prospek pada tabel</t>
         </is>
       </c>
       <c r="H769" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
     <row r="770" ht="14" customHeight="1">
       <c r="A770" s="55" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="B770" s="56" t="inlineStr">
@@ -32698,7 +32698,7 @@
       </c>
       <c r="D770" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Closing</t>
+          <t>Mengekspor data tab Prospek Masuk</t>
         </is>
       </c>
       <c r="E770" s="56" t="inlineStr">
@@ -32708,24 +32708,24 @@
       </c>
       <c r="F770" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G770" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing</t>
+          <t>Klik tab Prospek Masuk - Klik button Export - Klik icon download pada panel Download Export</t>
         </is>
       </c>
       <c r="H770" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pada tab Prospek Closing.</t>
+          <t>Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
     <row r="771" ht="14" customHeight="1">
       <c r="A771" s="55" t="inlineStr">
         <is>
-          <t>64.10</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="B771" s="56" t="inlineStr">
@@ -32740,7 +32740,7 @@
       </c>
       <c r="D771" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Closing dengan keyword valid</t>
+          <t>Menampilkan data tab Prospek Closing</t>
         </is>
       </c>
       <c r="E771" s="56" t="inlineStr">
@@ -32750,24 +32750,24 @@
       </c>
       <c r="F771" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G771" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Klik tab Prospek Closing</t>
         </is>
       </c>
       <c r="H771" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan data pada tab Prospek Closing.</t>
         </is>
       </c>
     </row>
     <row r="772" ht="14" customHeight="1">
       <c r="A772" s="55" t="inlineStr">
         <is>
-          <t>64.11</t>
+          <t>64.10</t>
         </is>
       </c>
       <c r="B772" s="56" t="inlineStr">
@@ -32782,34 +32782,34 @@
       </c>
       <c r="D772" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
+          <t>Mencari data Prospek Closing dengan keyword valid</t>
         </is>
       </c>
       <c r="E772" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F772" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G772" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Klik tab Prospek Closing - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
         </is>
       </c>
       <c r="H772" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil menampilkan data yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="773" ht="14" customHeight="1">
       <c r="A773" s="55" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.11</t>
         </is>
       </c>
       <c r="B773" s="56" t="inlineStr">
@@ -32824,12 +32824,12 @@
       </c>
       <c r="D773" s="56" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Closing</t>
+          <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E773" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F773" s="55" t="inlineStr">
@@ -32839,19 +32839,19 @@
       </c>
       <c r="G773" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing - Klik salah satu nama prospek pada tabel</t>
+          <t>Klik tab Prospek Closing - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
         </is>
       </c>
       <c r="H773" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman detail prospek.</t>
+          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="774" ht="14" customHeight="1">
       <c r="A774" s="55" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="B774" s="56" t="inlineStr">
@@ -32866,7 +32866,7 @@
       </c>
       <c r="D774" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data tab Prospek Closing</t>
+          <t>Melihat detail Prospek Closing</t>
         </is>
       </c>
       <c r="E774" s="56" t="inlineStr">
@@ -32876,24 +32876,24 @@
       </c>
       <c r="F774" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G774" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing - Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Klik tab Prospek Closing - Klik salah satu nama prospek pada tabel</t>
         </is>
       </c>
       <c r="H774" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
     <row r="775" ht="14" customHeight="1">
       <c r="A775" s="55" t="inlineStr">
         <is>
-          <t>64.14</t>
+          <t>64.13</t>
         </is>
       </c>
       <c r="B775" s="56" t="inlineStr">
@@ -32908,7 +32908,7 @@
       </c>
       <c r="D775" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Referal</t>
+          <t>Mengekspor data tab Prospek Closing</t>
         </is>
       </c>
       <c r="E775" s="56" t="inlineStr">
@@ -32918,24 +32918,24 @@
       </c>
       <c r="F775" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G775" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal</t>
+          <t>Klik tab Prospek Closing - Klik button Export - Klik icon download pada panel Download Export</t>
         </is>
       </c>
       <c r="H775" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pada tab Prospek Referal.</t>
+          <t>Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
     <row r="776" ht="14" customHeight="1">
       <c r="A776" s="55" t="inlineStr">
         <is>
-          <t>64.15</t>
+          <t>64.14</t>
         </is>
       </c>
       <c r="B776" s="56" t="inlineStr">
@@ -32950,7 +32950,7 @@
       </c>
       <c r="D776" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Referal dengan keyword valid</t>
+          <t>Menampilkan data tab Prospek Referal</t>
         </is>
       </c>
       <c r="E776" s="56" t="inlineStr">
@@ -32960,24 +32960,24 @@
       </c>
       <c r="F776" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G776" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Klik tab Prospek Referal</t>
         </is>
       </c>
       <c r="H776" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan data pada tab Prospek Referal.</t>
         </is>
       </c>
     </row>
     <row r="777" ht="14" customHeight="1">
       <c r="A777" s="55" t="inlineStr">
         <is>
-          <t>64.16</t>
+          <t>64.15</t>
         </is>
       </c>
       <c r="B777" s="56" t="inlineStr">
@@ -32992,34 +32992,34 @@
       </c>
       <c r="D777" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Referal dengan keyword tidak valid</t>
+          <t>Mencari data Prospek Referal dengan keyword valid</t>
         </is>
       </c>
       <c r="E777" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F777" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G777" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Klik tab Prospek Referal - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
         </is>
       </c>
       <c r="H777" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil menampilkan data yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="778" ht="14" customHeight="1">
       <c r="A778" s="55" t="inlineStr">
         <is>
-          <t>64.17</t>
+          <t>64.16</t>
         </is>
       </c>
       <c r="B778" s="56" t="inlineStr">
@@ -33034,12 +33034,12 @@
       </c>
       <c r="D778" s="56" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Referal</t>
+          <t>Mencari data Prospek Referal dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E778" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F778" s="55" t="inlineStr">
@@ -33049,19 +33049,19 @@
       </c>
       <c r="G778" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal - Klik salah satu nama prospek pada tabel</t>
+          <t>Klik tab Prospek Referal - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
         </is>
       </c>
       <c r="H778" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman detail prospek.</t>
+          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="779" ht="28" customHeight="1">
       <c r="A779" s="55" t="inlineStr">
         <is>
-          <t>64.18</t>
+          <t>64.17</t>
         </is>
       </c>
       <c r="B779" s="56" t="inlineStr">
@@ -33076,7 +33076,7 @@
       </c>
       <c r="D779" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data tab Prospek Referal</t>
+          <t>Melihat detail Prospek Referal</t>
         </is>
       </c>
       <c r="E779" s="56" t="inlineStr">
@@ -33086,24 +33086,24 @@
       </c>
       <c r="F779" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G779" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal - Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Klik tab Prospek Referal - Klik salah satu nama prospek pada tabel</t>
         </is>
       </c>
       <c r="H779" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
     <row r="780" ht="14" customHeight="1">
       <c r="A780" s="55" t="inlineStr">
         <is>
-          <t>64.19</t>
+          <t>64.18</t>
         </is>
       </c>
       <c r="B780" s="56" t="inlineStr">
@@ -33118,7 +33118,7 @@
       </c>
       <c r="D780" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Referal Closing</t>
+          <t>Mengekspor data tab Prospek Referal</t>
         </is>
       </c>
       <c r="E780" s="56" t="inlineStr">
@@ -33128,24 +33128,24 @@
       </c>
       <c r="F780" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G780" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal Closing</t>
+          <t>Klik tab Prospek Referal - Klik button Export - Klik icon download pada panel Download Export</t>
         </is>
       </c>
       <c r="H780" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
+          <t>Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
     <row r="781" ht="28" customHeight="1">
       <c r="A781" s="55" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>64.19</t>
         </is>
       </c>
       <c r="B781" s="56" t="inlineStr">
@@ -33160,7 +33160,7 @@
       </c>
       <c r="D781" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
+          <t>Menampilkan data tab Prospek Referal Closing</t>
         </is>
       </c>
       <c r="E781" s="56" t="inlineStr">
@@ -33170,24 +33170,24 @@
       </c>
       <c r="F781" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G781" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal Closing - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Klik tab Prospek Referal Closing</t>
         </is>
       </c>
       <c r="H781" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
         </is>
       </c>
     </row>
     <row r="782" ht="14" customHeight="1">
       <c r="A782" s="55" t="inlineStr">
         <is>
-          <t>64.21</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="B782" s="56" t="inlineStr">
@@ -33202,34 +33202,34 @@
       </c>
       <c r="D782" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Referal Closing dengan keyword tidak valid</t>
+          <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
         </is>
       </c>
       <c r="E782" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F782" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G782" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal Closing - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Klik tab Prospek Referal Closing - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
         </is>
       </c>
       <c r="H782" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil menampilkan data yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="783" ht="14" customHeight="1">
       <c r="A783" s="55" t="inlineStr">
         <is>
-          <t>64.22</t>
+          <t>64.21</t>
         </is>
       </c>
       <c r="B783" s="56" t="inlineStr">
@@ -33244,12 +33244,12 @@
       </c>
       <c r="D783" s="56" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Referal Closing</t>
+          <t>Mencari data Prospek Referal Closing dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E783" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F783" s="55" t="inlineStr">
@@ -33259,19 +33259,19 @@
       </c>
       <c r="G783" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal Closing - Klik salah satu nama prospek pada tabel</t>
+          <t>Klik tab Prospek Referal Closing - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
         </is>
       </c>
       <c r="H783" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman detail prospek.</t>
+          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="784" ht="14" customHeight="1">
       <c r="A784" s="55" t="inlineStr">
         <is>
-          <t>64.23</t>
+          <t>64.22</t>
         </is>
       </c>
       <c r="B784" s="56" t="inlineStr">
@@ -33286,7 +33286,7 @@
       </c>
       <c r="D784" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data tab Prospek Referal Closing</t>
+          <t>Melihat detail Prospek Referal Closing</t>
         </is>
       </c>
       <c r="E784" s="56" t="inlineStr">
@@ -33296,39 +33296,39 @@
       </c>
       <c r="F784" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G784" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal Closing - Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Klik tab Prospek Referal Closing - Klik salah satu nama prospek pada tabel</t>
         </is>
       </c>
       <c r="H784" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
     <row r="785" ht="14" customHeight="1">
       <c r="A785" s="55" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>64.23</t>
         </is>
       </c>
       <c r="B785" s="56" t="inlineStr">
         <is>
-          <t>Report Lending</t>
+          <t>Report Funding</t>
         </is>
       </c>
       <c r="C785" s="56" t="inlineStr">
         <is>
-          <t>Personal Funnel</t>
+          <t>Daily Sales Agenda</t>
         </is>
       </c>
       <c r="D785" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Personal Funnel</t>
+          <t>Mengekspor data tab Prospek Referal Closing</t>
         </is>
       </c>
       <c r="E785" s="56" t="inlineStr">
@@ -33338,24 +33338,24 @@
       </c>
       <c r="F785" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G785" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Lending - Klik sub menu Personal Funnel</t>
+          <t>Klik tab Prospek Referal Closing - Klik button Export - Klik icon download pada panel Download Export</t>
         </is>
       </c>
       <c r="H785" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Personal Funnel.</t>
+          <t>Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
     <row r="786" ht="14" customHeight="1">
       <c r="A786" s="55" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="B786" s="56" t="inlineStr">
@@ -33370,7 +33370,7 @@
       </c>
       <c r="D786" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Personal Funnel</t>
+          <t>Membuka halaman Personal Funnel</t>
         </is>
       </c>
       <c r="E786" s="56" t="inlineStr">
@@ -33385,19 +33385,19 @@
       </c>
       <c r="G786" s="56" t="inlineStr">
         <is>
-          <t>Mengisi semua field filter mandatory - Klik button Submit</t>
+          <t>Klik menu Report Lending - Klik sub menu Personal Funnel</t>
         </is>
       </c>
       <c r="H786" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+          <t>Berhasil menampilkan halaman Personal Funnel.</t>
         </is>
       </c>
     </row>
     <row r="787" ht="14" customHeight="1">
       <c r="A787" s="55" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="B787" s="56" t="inlineStr">
@@ -33412,7 +33412,7 @@
       </c>
       <c r="D787" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
+          <t>Melakukan filter data Personal Funnel</t>
         </is>
       </c>
       <c r="E787" s="56" t="inlineStr">
@@ -33427,19 +33427,19 @@
       </c>
       <c r="G787" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field filter mandatory - Klik button Submit</t>
+          <t>Mengisi semua field filter mandatory - Klik button Submit</t>
         </is>
       </c>
       <c r="H787" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="788" ht="14" customHeight="1">
       <c r="A788" s="55" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="B788" s="56" t="inlineStr">
@@ -33454,7 +33454,7 @@
       </c>
       <c r="D788" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data Personal Funnel</t>
+          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E788" s="56" t="inlineStr">
@@ -33464,24 +33464,24 @@
       </c>
       <c r="F788" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G788" s="56" t="inlineStr">
         <is>
-          <t>Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Mengosongkan field filter mandatory - Klik button Submit</t>
         </is>
       </c>
       <c r="H788" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="789" ht="14" customHeight="1">
       <c r="A789" s="55" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="B789" s="56" t="inlineStr">
@@ -33491,12 +33491,12 @@
       </c>
       <c r="C789" s="56" t="inlineStr">
         <is>
-          <t>Rekap Funnel</t>
+          <t>Personal Funnel</t>
         </is>
       </c>
       <c r="D789" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Rekap Funnel</t>
+          <t>Mengekspor data Personal Funnel</t>
         </is>
       </c>
       <c r="E789" s="56" t="inlineStr">
@@ -33511,19 +33511,19 @@
       </c>
       <c r="G789" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Lending - Klik sub menu Rekap Funnel</t>
+          <t>Klik button Export - Klik icon download pada panel Download Export</t>
         </is>
       </c>
       <c r="H789" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Rekap Funnel.</t>
+          <t>Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
     <row r="790" ht="14" customHeight="1">
       <c r="A790" s="55" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="B790" s="56" t="inlineStr">
@@ -33538,7 +33538,7 @@
       </c>
       <c r="D790" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data Rekap Funnel</t>
+          <t>Membuka halaman Rekap Funnel</t>
         </is>
       </c>
       <c r="E790" s="56" t="inlineStr">
@@ -33548,24 +33548,24 @@
       </c>
       <c r="F790" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G790" s="56" t="inlineStr">
         <is>
-          <t>Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun) - Klik button Filter Data</t>
+          <t>Klik menu Report Lending - Klik sub menu Rekap Funnel</t>
         </is>
       </c>
       <c r="H790" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
+          <t>Berhasil menampilkan halaman Rekap Funnel.</t>
         </is>
       </c>
     </row>
     <row r="791" ht="14" customHeight="1">
       <c r="A791" s="55" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="B791" s="56" t="inlineStr">
@@ -33580,7 +33580,7 @@
       </c>
       <c r="D791" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Rekap Funnel</t>
+          <t>Menampilkan data Rekap Funnel</t>
         </is>
       </c>
       <c r="E791" s="56" t="inlineStr">
@@ -33595,19 +33595,19 @@
       </c>
       <c r="G791" s="56" t="inlineStr">
         <is>
-          <t>Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role) - Klik button Filter Data</t>
+          <t>Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun) - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H791" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
+          <t>Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
         </is>
       </c>
     </row>
     <row r="792" ht="14" customHeight="1">
       <c r="A792" s="55" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="B792" s="56" t="inlineStr">
@@ -33622,7 +33622,7 @@
       </c>
       <c r="D792" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
+          <t>Melakukan filter data Rekap Funnel</t>
         </is>
       </c>
       <c r="E792" s="56" t="inlineStr">
@@ -33637,19 +33637,19 @@
       </c>
       <c r="G792" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field filter mandatory - Klik button Filter Data</t>
+          <t>Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role) - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H792" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="793" ht="14" customHeight="1">
       <c r="A793" s="55" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="B793" s="56" t="inlineStr">
@@ -33664,7 +33664,7 @@
       </c>
       <c r="D793" s="56" t="inlineStr">
         <is>
-          <t>Mengunduh data Rekap Funnel</t>
+          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E793" s="56" t="inlineStr">
@@ -33679,19 +33679,19 @@
       </c>
       <c r="G793" s="56" t="inlineStr">
         <is>
-          <t>Klik button Download Excel</t>
+          <t>Mengosongkan field filter mandatory - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H793" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file Excel data Rekap Funnel.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="794" ht="14" customHeight="1">
       <c r="A794" s="55" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="B794" s="56" t="inlineStr">
@@ -33701,12 +33701,12 @@
       </c>
       <c r="C794" s="56" t="inlineStr">
         <is>
-          <t>Regional Funnel</t>
+          <t>Rekap Funnel</t>
         </is>
       </c>
       <c r="D794" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Regional Funnel</t>
+          <t>Mengunduh data Rekap Funnel</t>
         </is>
       </c>
       <c r="E794" s="56" t="inlineStr">
@@ -33721,19 +33721,19 @@
       </c>
       <c r="G794" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Lending - Klik sub menu Regional Funnel</t>
+          <t>Klik button Download Excel</t>
         </is>
       </c>
       <c r="H794" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Regional Funnel.</t>
+          <t>Berhasil mendownload file Excel data Rekap Funnel.</t>
         </is>
       </c>
     </row>
     <row r="795" ht="14" customHeight="1">
       <c r="A795" s="55" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="B795" s="56" t="inlineStr">
@@ -33748,7 +33748,7 @@
       </c>
       <c r="D795" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Regional Funnel</t>
+          <t>Membuka halaman Regional Funnel</t>
         </is>
       </c>
       <c r="E795" s="56" t="inlineStr">
@@ -33763,19 +33763,19 @@
       </c>
       <c r="G795" s="56" t="inlineStr">
         <is>
-          <t>Mengisi semua field filter mandatory - Klik button Submit</t>
+          <t>Klik menu Report Lending - Klik sub menu Regional Funnel</t>
         </is>
       </c>
       <c r="H795" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+          <t>Berhasil menampilkan halaman Regional Funnel.</t>
         </is>
       </c>
     </row>
     <row r="796" ht="14" customHeight="1">
       <c r="A796" s="55" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="B796" s="56" t="inlineStr">
@@ -33790,7 +33790,7 @@
       </c>
       <c r="D796" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
+          <t>Melakukan filter data Regional Funnel</t>
         </is>
       </c>
       <c r="E796" s="56" t="inlineStr">
@@ -33805,19 +33805,19 @@
       </c>
       <c r="G796" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field filter mandatory - Klik button Submit</t>
+          <t>Mengisi semua field filter mandatory - Klik button Submit</t>
         </is>
       </c>
       <c r="H796" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="797" ht="14" customHeight="1">
       <c r="A797" s="55" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="B797" s="56" t="inlineStr">
@@ -33827,12 +33827,12 @@
       </c>
       <c r="C797" s="56" t="inlineStr">
         <is>
-          <t>Pengaturan Funnel</t>
+          <t>Regional Funnel</t>
         </is>
       </c>
       <c r="D797" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Pengaturan Funnel Lending</t>
+          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E797" s="56" t="inlineStr">
@@ -33842,24 +33842,24 @@
       </c>
       <c r="F797" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G797" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Lending - Klik sub menu Pengaturan Funnel</t>
+          <t>Mengosongkan field filter mandatory - Klik button Submit</t>
         </is>
       </c>
       <c r="H797" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Pengaturan Funnel Lending.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="798" ht="14" customHeight="1">
       <c r="A798" s="55" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="B798" s="56" t="inlineStr">
@@ -33874,7 +33874,7 @@
       </c>
       <c r="D798" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data Pengaturan Funnel Lending berdasarkan section</t>
+          <t>Membuka halaman Pengaturan Funnel Lending</t>
         </is>
       </c>
       <c r="E798" s="56" t="inlineStr">
@@ -33884,24 +33884,24 @@
       </c>
       <c r="F798" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G798" s="56" t="inlineStr">
         <is>
-          <t>Klik salah satu daftar section pada tabel</t>
+          <t>Klik menu Report Lending - Klik sub menu Pengaturan Funnel</t>
         </is>
       </c>
       <c r="H798" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pengaturan funnel Lending.</t>
+          <t>Berhasil menampilkan halaman Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
     <row r="799" ht="14" customHeight="1">
       <c r="A799" s="55" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="B799" s="56" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="D799" s="56" t="inlineStr">
         <is>
-          <t>Mengubah data Pengaturan Funnel Lending</t>
+          <t>Menampilkan data Pengaturan Funnel Lending berdasarkan section</t>
         </is>
       </c>
       <c r="E799" s="56" t="inlineStr">
@@ -33926,24 +33926,24 @@
       </c>
       <c r="F799" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G799" s="56" t="inlineStr">
         <is>
-          <t>Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel - Klik button Submit</t>
+          <t>Klik salah satu daftar section pada tabel</t>
         </is>
       </c>
       <c r="H799" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
+          <t>Berhasil menampilkan data pengaturan funnel Lending.</t>
         </is>
       </c>
     </row>
     <row r="800" ht="14" customHeight="1">
       <c r="A800" s="55" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="B800" s="56" t="inlineStr">
@@ -33958,7 +33958,7 @@
       </c>
       <c r="D800" s="56" t="inlineStr">
         <is>
-          <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
+          <t>Mengubah data Pengaturan Funnel Lending</t>
         </is>
       </c>
       <c r="E800" s="56" t="inlineStr">
@@ -33973,19 +33973,19 @@
       </c>
       <c r="G800" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field mandatory Performance Percentage - Klik button Submit</t>
+          <t>Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel - Klik button Submit</t>
         </is>
       </c>
       <c r="H800" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+          <t>Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
     <row r="801" ht="14" customHeight="1">
       <c r="A801" s="55" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="B801" s="56" t="inlineStr">
@@ -34000,7 +34000,7 @@
       </c>
       <c r="D801" s="56" t="inlineStr">
         <is>
-          <t>Menambahkan Condition pada Performance Indicator</t>
+          <t>Mengubah data Pengaturan Funnel Lending tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E801" s="56" t="inlineStr">
@@ -34010,24 +34010,24 @@
       </c>
       <c r="F801" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G801" s="56" t="inlineStr">
         <is>
-          <t>Klik button Add Condition pada bagian Performance Indicator - Mengisi semua field mandatory pada condition baru - Klik button Submit</t>
+          <t>Mengosongkan field mandatory Performance Percentage - Klik button Submit</t>
         </is>
       </c>
       <c r="H801" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menyimpan condition baru pada Performance Indicator.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
     <row r="802" ht="14" customHeight="1">
       <c r="A802" s="55" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="B802" s="56" t="inlineStr">
@@ -34042,7 +34042,7 @@
       </c>
       <c r="D802" s="56" t="inlineStr">
         <is>
-          <t>Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory</t>
+          <t>Menambahkan Condition pada Performance Indicator</t>
         </is>
       </c>
       <c r="E802" s="56" t="inlineStr">
@@ -34057,19 +34057,19 @@
       </c>
       <c r="G802" s="56" t="inlineStr">
         <is>
-          <t>Klik button Add Condition pada bagian Performance Indicator - Mengosongkan field mandatory pada condition baru - Klik button Submit</t>
+          <t>Klik button Add Condition pada bagian Performance Indicator - Mengisi semua field mandatory pada condition baru - Klik button Submit</t>
         </is>
       </c>
       <c r="H802" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+          <t>Berhasil menyimpan condition baru pada Performance Indicator.</t>
         </is>
       </c>
     </row>
     <row r="803" ht="14" customHeight="1">
       <c r="A803" s="55" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="B803" s="56" t="inlineStr">
@@ -34084,7 +34084,7 @@
       </c>
       <c r="D803" s="56" t="inlineStr">
         <is>
-          <t>Menghapus Condition pada Performance Indicator</t>
+          <t>Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E803" s="56" t="inlineStr">
@@ -34099,19 +34099,19 @@
       </c>
       <c r="G803" s="56" t="inlineStr">
         <is>
-          <t>Klik button Remove pada salah satu condition di Performance Indicator - Klik button Submit</t>
+          <t>Klik button Add Condition pada bagian Performance Indicator - Mengosongkan field mandatory pada condition baru - Klik button Submit</t>
         </is>
       </c>
       <c r="H803" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
     <row r="804" ht="14" customHeight="1">
       <c r="A804" s="55" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="B804" s="56" t="inlineStr">
@@ -34121,12 +34121,12 @@
       </c>
       <c r="C804" s="56" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D804" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Daily Sales Agenda</t>
+          <t>Menghapus Condition pada Performance Indicator</t>
         </is>
       </c>
       <c r="E804" s="56" t="inlineStr">
@@ -34136,24 +34136,24 @@
       </c>
       <c r="F804" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G804" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Lending - Klik sub menu Daily Sales Agenda</t>
+          <t>Klik button Remove pada salah satu condition di Performance Indicator - Klik button Submit</t>
         </is>
       </c>
       <c r="H804" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Daily Sales Agenda.</t>
+          <t>Berhasil menyimpan perubahan data Pengaturan Funnel Lending.</t>
         </is>
       </c>
     </row>
     <row r="805" ht="14" customHeight="1">
       <c r="A805" s="55" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="B805" s="56" t="inlineStr">
@@ -34168,7 +34168,7 @@
       </c>
       <c r="D805" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Daily Sales Agenda</t>
+          <t>Membuka halaman Daily Sales Agenda</t>
         </is>
       </c>
       <c r="E805" s="56" t="inlineStr">
@@ -34178,24 +34178,24 @@
       </c>
       <c r="F805" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G805" s="56" t="inlineStr">
         <is>
-          <t>Mengisi semua field filter mandatory - Klik button Filter Data</t>
+          <t>Klik menu Report Lending - Klik sub menu Daily Sales Agenda</t>
         </is>
       </c>
       <c r="H805" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+          <t>Berhasil menampilkan halaman Daily Sales Agenda.</t>
         </is>
       </c>
     </row>
     <row r="806" ht="14" customHeight="1">
       <c r="A806" s="55" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="B806" s="56" t="inlineStr">
@@ -34210,7 +34210,7 @@
       </c>
       <c r="D806" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
+          <t>Melakukan filter data Daily Sales Agenda</t>
         </is>
       </c>
       <c r="E806" s="56" t="inlineStr">
@@ -34225,19 +34225,19 @@
       </c>
       <c r="G806" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field filter mandatory - Klik button Filter Data</t>
+          <t>Mengisi semua field filter mandatory - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H806" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="807" ht="14" customHeight="1">
       <c r="A807" s="55" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="B807" s="56" t="inlineStr">
@@ -34252,7 +34252,7 @@
       </c>
       <c r="D807" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Masuk</t>
+          <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E807" s="56" t="inlineStr">
@@ -34267,19 +34267,19 @@
       </c>
       <c r="G807" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk</t>
+          <t>Mengosongkan field filter mandatory - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H807" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pada tab Prospek Masuk.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="808" ht="14" customHeight="1">
       <c r="A808" s="55" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="B808" s="56" t="inlineStr">
@@ -34294,7 +34294,7 @@
       </c>
       <c r="D808" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Masuk dengan keyword valid</t>
+          <t>Menampilkan data tab Prospek Masuk</t>
         </is>
       </c>
       <c r="E808" s="56" t="inlineStr">
@@ -34304,24 +34304,24 @@
       </c>
       <c r="F808" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G808" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Klik tab Prospek Masuk</t>
         </is>
       </c>
       <c r="H808" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan data pada tab Prospek Masuk.</t>
         </is>
       </c>
     </row>
     <row r="809" ht="14" customHeight="1">
       <c r="A809" s="55" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="B809" s="56" t="inlineStr">
@@ -34336,34 +34336,34 @@
       </c>
       <c r="D809" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
+          <t>Mencari data Prospek Masuk dengan keyword valid</t>
         </is>
       </c>
       <c r="E809" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F809" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G809" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Klik tab Prospek Masuk - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
         </is>
       </c>
       <c r="H809" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil menampilkan data yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="810" ht="42" customHeight="1">
       <c r="A810" s="55" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="B810" s="56" t="inlineStr">
@@ -34378,12 +34378,12 @@
       </c>
       <c r="D810" s="56" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Masuk</t>
+          <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E810" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F810" s="55" t="inlineStr">
@@ -34393,19 +34393,19 @@
       </c>
       <c r="G810" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk - Klik salah satu nama prospek pada tabel</t>
+          <t>Klik tab Prospek Masuk - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
         </is>
       </c>
       <c r="H810" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman detail prospek.</t>
+          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="811" ht="28" customHeight="1">
       <c r="A811" s="55" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="B811" s="56" t="inlineStr">
@@ -34420,7 +34420,7 @@
       </c>
       <c r="D811" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data tab Prospek Masuk</t>
+          <t>Melihat detail Prospek Masuk</t>
         </is>
       </c>
       <c r="E811" s="56" t="inlineStr">
@@ -34430,24 +34430,24 @@
       </c>
       <c r="F811" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G811" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk - Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Klik tab Prospek Masuk - Klik salah satu nama prospek pada tabel</t>
         </is>
       </c>
       <c r="H811" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
     <row r="812" ht="42" customHeight="1">
       <c r="A812" s="55" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="B812" s="56" t="inlineStr">
@@ -34462,7 +34462,7 @@
       </c>
       <c r="D812" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Closing</t>
+          <t>Mengekspor data tab Prospek Masuk</t>
         </is>
       </c>
       <c r="E812" s="56" t="inlineStr">
@@ -34472,24 +34472,24 @@
       </c>
       <c r="F812" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G812" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing</t>
+          <t>Klik tab Prospek Masuk - Klik button Export - Klik icon download pada panel Download Export</t>
         </is>
       </c>
       <c r="H812" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pada tab Prospek Closing.</t>
+          <t>Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
     <row r="813" ht="28" customHeight="1">
       <c r="A813" s="55" t="inlineStr">
         <is>
-          <t>69.10</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="B813" s="56" t="inlineStr">
@@ -34504,7 +34504,7 @@
       </c>
       <c r="D813" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Closing dengan keyword valid</t>
+          <t>Menampilkan data tab Prospek Closing</t>
         </is>
       </c>
       <c r="E813" s="56" t="inlineStr">
@@ -34514,24 +34514,24 @@
       </c>
       <c r="F813" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G813" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Klik tab Prospek Closing</t>
         </is>
       </c>
       <c r="H813" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan data pada tab Prospek Closing.</t>
         </is>
       </c>
     </row>
     <row r="814" ht="28" customHeight="1">
       <c r="A814" s="55" t="inlineStr">
         <is>
-          <t>69.11</t>
+          <t>69.10</t>
         </is>
       </c>
       <c r="B814" s="56" t="inlineStr">
@@ -34546,34 +34546,34 @@
       </c>
       <c r="D814" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
+          <t>Mencari data Prospek Closing dengan keyword valid</t>
         </is>
       </c>
       <c r="E814" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F814" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G814" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Klik tab Prospek Closing - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
         </is>
       </c>
       <c r="H814" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil menampilkan data yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="815" ht="56" customHeight="1">
       <c r="A815" s="55" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>69.11</t>
         </is>
       </c>
       <c r="B815" s="56" t="inlineStr">
@@ -34588,12 +34588,12 @@
       </c>
       <c r="D815" s="56" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Closing</t>
+          <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E815" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F815" s="55" t="inlineStr">
@@ -34603,19 +34603,19 @@
       </c>
       <c r="G815" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing - Klik salah satu nama prospek pada tabel</t>
+          <t>Klik tab Prospek Closing - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
         </is>
       </c>
       <c r="H815" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman detail prospek.</t>
+          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="816" ht="56" customHeight="1">
       <c r="A816" s="55" t="inlineStr">
         <is>
-          <t>69.13</t>
+          <t>69.12</t>
         </is>
       </c>
       <c r="B816" s="56" t="inlineStr">
@@ -34630,7 +34630,7 @@
       </c>
       <c r="D816" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data tab Prospek Closing</t>
+          <t>Melihat detail Prospek Closing</t>
         </is>
       </c>
       <c r="E816" s="56" t="inlineStr">
@@ -34640,24 +34640,24 @@
       </c>
       <c r="F816" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G816" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing - Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Klik tab Prospek Closing - Klik salah satu nama prospek pada tabel</t>
         </is>
       </c>
       <c r="H816" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
     <row r="817" ht="28" customHeight="1">
       <c r="A817" s="55" t="inlineStr">
         <is>
-          <t>69.14</t>
+          <t>69.13</t>
         </is>
       </c>
       <c r="B817" s="56" t="inlineStr">
@@ -34672,7 +34672,7 @@
       </c>
       <c r="D817" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Referal</t>
+          <t>Mengekspor data tab Prospek Closing</t>
         </is>
       </c>
       <c r="E817" s="56" t="inlineStr">
@@ -34682,24 +34682,24 @@
       </c>
       <c r="F817" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G817" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal</t>
+          <t>Klik tab Prospek Closing - Klik button Export - Klik icon download pada panel Download Export</t>
         </is>
       </c>
       <c r="H817" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pada tab Prospek Referal.</t>
+          <t>Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
     <row r="818" ht="28" customHeight="1">
       <c r="A818" s="55" t="inlineStr">
         <is>
-          <t>69.15</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="B818" s="56" t="inlineStr">
@@ -34714,7 +34714,7 @@
       </c>
       <c r="D818" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Referal dengan keyword valid</t>
+          <t>Menampilkan data tab Prospek Referal</t>
         </is>
       </c>
       <c r="E818" s="56" t="inlineStr">
@@ -34724,24 +34724,24 @@
       </c>
       <c r="F818" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G818" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Klik tab Prospek Referal</t>
         </is>
       </c>
       <c r="H818" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan data pada tab Prospek Referal.</t>
         </is>
       </c>
     </row>
     <row r="819" ht="42" customHeight="1">
       <c r="A819" s="55" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>69.15</t>
         </is>
       </c>
       <c r="B819" s="56" t="inlineStr">
@@ -34756,34 +34756,34 @@
       </c>
       <c r="D819" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Referal dengan keyword tidak valid</t>
+          <t>Mencari data Prospek Referal dengan keyword valid</t>
         </is>
       </c>
       <c r="E819" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F819" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G819" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Klik tab Prospek Referal - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
         </is>
       </c>
       <c r="H819" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil menampilkan data yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="820" ht="14" customHeight="1">
       <c r="A820" s="55" t="inlineStr">
         <is>
-          <t>69.17</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="B820" s="56" t="inlineStr">
@@ -34798,12 +34798,12 @@
       </c>
       <c r="D820" s="56" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Referal</t>
+          <t>Mencari data Prospek Referal dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E820" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F820" s="55" t="inlineStr">
@@ -34813,19 +34813,19 @@
       </c>
       <c r="G820" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal - Klik salah satu nama prospek pada tabel</t>
+          <t>Klik tab Prospek Referal - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
         </is>
       </c>
       <c r="H820" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman detail prospek.</t>
+          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="821" ht="56" customHeight="1">
       <c r="A821" s="55" t="inlineStr">
         <is>
-          <t>69.18</t>
+          <t>69.17</t>
         </is>
       </c>
       <c r="B821" s="56" t="inlineStr">
@@ -34840,7 +34840,7 @@
       </c>
       <c r="D821" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data tab Prospek Referal</t>
+          <t>Melihat detail Prospek Referal</t>
         </is>
       </c>
       <c r="E821" s="56" t="inlineStr">
@@ -34850,24 +34850,24 @@
       </c>
       <c r="F821" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G821" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal - Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Klik tab Prospek Referal - Klik salah satu nama prospek pada tabel</t>
         </is>
       </c>
       <c r="H821" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
     <row r="822" ht="56" customHeight="1">
       <c r="A822" s="55" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>69.18</t>
         </is>
       </c>
       <c r="B822" s="56" t="inlineStr">
@@ -34882,7 +34882,7 @@
       </c>
       <c r="D822" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Referal Closing</t>
+          <t>Mengekspor data tab Prospek Referal</t>
         </is>
       </c>
       <c r="E822" s="56" t="inlineStr">
@@ -34892,24 +34892,24 @@
       </c>
       <c r="F822" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G822" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal Closing</t>
+          <t>Klik tab Prospek Referal - Klik button Export - Klik icon download pada panel Download Export</t>
         </is>
       </c>
       <c r="H822" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
+          <t>Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
     <row r="823" ht="56" customHeight="1">
       <c r="A823" s="55" t="inlineStr">
         <is>
-          <t>69.20</t>
+          <t>69.19</t>
         </is>
       </c>
       <c r="B823" s="56" t="inlineStr">
@@ -34924,7 +34924,7 @@
       </c>
       <c r="D823" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
+          <t>Menampilkan data tab Prospek Referal Closing</t>
         </is>
       </c>
       <c r="E823" s="56" t="inlineStr">
@@ -34934,24 +34934,24 @@
       </c>
       <c r="F823" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G823" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal Closing - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Klik tab Prospek Referal Closing</t>
         </is>
       </c>
       <c r="H823" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
         </is>
       </c>
     </row>
     <row r="824" ht="14" customHeight="1">
       <c r="A824" s="55" t="inlineStr">
         <is>
-          <t>69.21</t>
+          <t>69.20</t>
         </is>
       </c>
       <c r="B824" s="56" t="inlineStr">
@@ -34966,34 +34966,34 @@
       </c>
       <c r="D824" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Referal Closing dengan keyword tidak valid</t>
+          <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
         </is>
       </c>
       <c r="E824" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F824" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G824" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal Closing - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Klik tab Prospek Referal Closing - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
         </is>
       </c>
       <c r="H824" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil menampilkan data yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="825" ht="14" customHeight="1">
       <c r="A825" s="55" t="inlineStr">
         <is>
-          <t>69.22</t>
+          <t>69.21</t>
         </is>
       </c>
       <c r="B825" s="56" t="inlineStr">
@@ -35008,12 +35008,12 @@
       </c>
       <c r="D825" s="56" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Referal Closing</t>
+          <t>Mencari data Prospek Referal Closing dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E825" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F825" s="55" t="inlineStr">
@@ -35023,19 +35023,19 @@
       </c>
       <c r="G825" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal Closing - Klik salah satu nama prospek pada tabel</t>
+          <t>Klik tab Prospek Referal Closing - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
         </is>
       </c>
       <c r="H825" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman detail prospek.</t>
+          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="826" ht="14" customHeight="1">
       <c r="A826" s="55" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>69.22</t>
         </is>
       </c>
       <c r="B826" s="56" t="inlineStr">
@@ -35050,7 +35050,7 @@
       </c>
       <c r="D826" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data tab Prospek Referal Closing</t>
+          <t>Melihat detail Prospek Referal Closing</t>
         </is>
       </c>
       <c r="E826" s="56" t="inlineStr">
@@ -35060,39 +35060,39 @@
       </c>
       <c r="F826" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G826" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal Closing - Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Klik tab Prospek Referal Closing - Klik salah satu nama prospek pada tabel</t>
         </is>
       </c>
       <c r="H826" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
     <row r="827" ht="42" customHeight="1">
       <c r="A827" s="55" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="B827" s="56" t="inlineStr">
         <is>
-          <t>Re-Assign dan Approval</t>
+          <t>Report Lending</t>
         </is>
       </c>
       <c r="C827" s="56" t="inlineStr">
         <is>
-          <t>Approval non Banking</t>
+          <t>Daily Sales Agenda</t>
         </is>
       </c>
       <c r="D827" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Approval non Banking</t>
+          <t>Mengekspor data tab Prospek Referal Closing</t>
         </is>
       </c>
       <c r="E827" s="56" t="inlineStr">
@@ -35107,19 +35107,19 @@
       </c>
       <c r="G827" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Re-Assign &amp; Approval - Klik submenu Approval non banking</t>
+          <t>Klik tab Prospek Referal Closing - Klik button Export - Klik icon download pada panel Download Export</t>
         </is>
       </c>
       <c r="H827" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman Approval non banking</t>
+          <t>Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
     <row r="828" ht="14" customHeight="1">
       <c r="A828" s="55" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="B828" s="56" t="inlineStr">
@@ -35134,7 +35134,7 @@
       </c>
       <c r="D828" s="56" t="inlineStr">
         <is>
-          <t>Filter data</t>
+          <t>Membuka halaman Approval non Banking</t>
         </is>
       </c>
       <c r="E828" s="56" t="inlineStr">
@@ -35144,24 +35144,24 @@
       </c>
       <c r="F828" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G828" s="56" t="inlineStr">
         <is>
-          <t>Pilih sales - Pilih produk - Pilih bulan - Pilih tahun - Klik button Submit</t>
+          <t>Klik menu Re-Assign &amp; Approval - Klik submenu Approval non banking</t>
         </is>
       </c>
       <c r="H828" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data approval non banking sesuai dengan filter data yang di pilih</t>
+          <t>Menampilkan halaman Approval non banking</t>
         </is>
       </c>
     </row>
     <row r="829" ht="56" customHeight="1">
       <c r="A829" s="55" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="B829" s="56" t="inlineStr">
@@ -35176,7 +35176,7 @@
       </c>
       <c r="D829" s="56" t="inlineStr">
         <is>
-          <t>Mencari data</t>
+          <t>Filter data</t>
         </is>
       </c>
       <c r="E829" s="56" t="inlineStr">
@@ -35186,24 +35186,24 @@
       </c>
       <c r="F829" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G829" s="56" t="inlineStr">
         <is>
-          <t>Input keyword pada field search - Klik icon search yang ada di sebelah field search</t>
+          <t>Pilih sales - Pilih produk - Pilih bulan - Pilih tahun - Klik button Submit</t>
         </is>
       </c>
       <c r="H829" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai dengan keyword yang di cari</t>
+          <t>Menampilkan data approval non banking sesuai dengan filter data yang di pilih</t>
         </is>
       </c>
     </row>
     <row r="830" ht="28" customHeight="1">
       <c r="A830" s="55" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="B830" s="56" t="inlineStr">
@@ -35218,7 +35218,7 @@
       </c>
       <c r="D830" s="56" t="inlineStr">
         <is>
-          <t>Melihat Detail data Approval non banking</t>
+          <t>Mencari data</t>
         </is>
       </c>
       <c r="E830" s="56" t="inlineStr">
@@ -35233,19 +35233,19 @@
       </c>
       <c r="G830" s="56" t="inlineStr">
         <is>
-          <t>Klik titik tiga - Klik Detail</t>
+          <t>Input keyword pada field search - Klik icon search yang ada di sebelah field search</t>
         </is>
       </c>
       <c r="H830" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman detail data approval non banking</t>
+          <t>Berhasil menampilkan data sesuai dengan keyword yang di cari</t>
         </is>
       </c>
     </row>
     <row r="831" ht="42" customHeight="1">
       <c r="A831" s="55" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="B831" s="56" t="inlineStr">
@@ -35260,7 +35260,7 @@
       </c>
       <c r="D831" s="56" t="inlineStr">
         <is>
-          <t>Menyetujui Prospek</t>
+          <t>Melihat Detail data Approval non banking</t>
         </is>
       </c>
       <c r="E831" s="56" t="inlineStr">
@@ -35270,24 +35270,24 @@
       </c>
       <c r="F831" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G831" s="56" t="inlineStr">
         <is>
-          <t>Klik titik tiga - Klik Setujui - Input Realisasi - Input Remark - Klik button Setujui</t>
+          <t>Klik titik tiga - Klik Detail</t>
         </is>
       </c>
       <c r="H831" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menyetujui prospek, menampilkan popup 'Sukses menyetujui prospek'</t>
+          <t>Menampilkan halaman detail data approval non banking</t>
         </is>
       </c>
     </row>
     <row r="832" ht="28" customHeight="1">
       <c r="A832" s="55" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="B832" s="56" t="inlineStr">
@@ -35302,7 +35302,7 @@
       </c>
       <c r="D832" s="56" t="inlineStr">
         <is>
-          <t>Batal menyetujui Prospek</t>
+          <t>Menyetujui Prospek</t>
         </is>
       </c>
       <c r="E832" s="56" t="inlineStr">
@@ -35317,19 +35317,19 @@
       </c>
       <c r="G832" s="56" t="inlineStr">
         <is>
-          <t>Klik button Batalkan pada modal approve</t>
+          <t>Klik titik tiga - Klik Setujui - Input Realisasi - Input Remark - Klik button Setujui</t>
         </is>
       </c>
       <c r="H832" s="56" t="inlineStr">
         <is>
-          <t>Modal approve tertutup dan tetap di halaman approval non banking</t>
+          <t>Berhasil menyetujui prospek, menampilkan popup 'Sukses menyetujui prospek'</t>
         </is>
       </c>
     </row>
     <row r="833" ht="14" customHeight="1">
       <c r="A833" s="55" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="B833" s="56" t="inlineStr">
@@ -35344,34 +35344,34 @@
       </c>
       <c r="D833" s="56" t="inlineStr">
         <is>
-          <t>Tidak menginput nilai realisasi pada modal approve</t>
+          <t>Batal menyetujui Prospek</t>
         </is>
       </c>
       <c r="E833" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F833" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G833" s="56" t="inlineStr">
         <is>
-          <t>Kosongkan nilai realisasi - Input remark - Klik button Setujui</t>
+          <t>Klik button Batalkan pada modal approve</t>
         </is>
       </c>
       <c r="H833" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan alert 'Realisasi dibutuhkan!'</t>
+          <t>Modal approve tertutup dan tetap di halaman approval non banking</t>
         </is>
       </c>
     </row>
     <row r="834" ht="14" customHeight="1">
       <c r="A834" s="55" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="B834" s="56" t="inlineStr">
@@ -35386,7 +35386,7 @@
       </c>
       <c r="D834" s="56" t="inlineStr">
         <is>
-          <t>Tidak menginput remark pada modal approve</t>
+          <t>Tidak menginput nilai realisasi pada modal approve</t>
         </is>
       </c>
       <c r="E834" s="56" t="inlineStr">
@@ -35401,19 +35401,19 @@
       </c>
       <c r="G834" s="56" t="inlineStr">
         <is>
-          <t>Kosongkan remark</t>
+          <t>Kosongkan nilai realisasi - Input remark - Klik button Setujui</t>
         </is>
       </c>
       <c r="H834" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan alert 'Remark dibutuhkan!'</t>
+          <t>Menampilkan alert 'Realisasi dibutuhkan!'</t>
         </is>
       </c>
     </row>
     <row r="835" ht="14" customHeight="1">
       <c r="A835" s="55" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="B835" s="56" t="inlineStr">
@@ -35428,7 +35428,7 @@
       </c>
       <c r="D835" s="56" t="inlineStr">
         <is>
-          <t>Menginput huruf pada field realisasi</t>
+          <t>Tidak menginput remark pada modal approve</t>
         </is>
       </c>
       <c r="E835" s="56" t="inlineStr">
@@ -35438,24 +35438,24 @@
       </c>
       <c r="F835" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G835" s="56" t="inlineStr">
         <is>
-          <t>Input huruf pada field realisasi kemudian pindah ke filed lain</t>
+          <t>Kosongkan remark</t>
         </is>
       </c>
       <c r="H835" s="56" t="inlineStr">
         <is>
-          <t>Sistem menghapus input non-numerik secara otomatis saat field kehilangan fokus. Field Realiasi menjadi kosong</t>
+          <t>Menampilkan alert 'Remark dibutuhkan!'</t>
         </is>
       </c>
     </row>
     <row r="836" ht="42" customHeight="1">
       <c r="A836" s="55" t="inlineStr">
         <is>
-          <t>70.10</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="B836" s="56" t="inlineStr">
@@ -35470,12 +35470,12 @@
       </c>
       <c r="D836" s="56" t="inlineStr">
         <is>
-          <t>Menolak Prospek</t>
+          <t>Menginput huruf pada field realisasi</t>
         </is>
       </c>
       <c r="E836" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F836" s="55" t="inlineStr">
@@ -35485,19 +35485,19 @@
       </c>
       <c r="G836" s="56" t="inlineStr">
         <is>
-          <t>Klik titik tiga - Klik Tolak - Input Remark - Klik button Tolak</t>
+          <t>Input huruf pada field realisasi kemudian pindah ke filed lain</t>
         </is>
       </c>
       <c r="H836" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menolak prospek, menampilkan popup 'Sukses menolak prospek'</t>
+          <t>Sistem menghapus input non-numerik secara otomatis saat field kehilangan fokus. Field Realiasi menjadi kosong</t>
         </is>
       </c>
     </row>
     <row r="837" ht="28" customHeight="1">
       <c r="A837" s="55" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>70.10</t>
         </is>
       </c>
       <c r="B837" s="56" t="inlineStr">
@@ -35512,7 +35512,7 @@
       </c>
       <c r="D837" s="56" t="inlineStr">
         <is>
-          <t>Batal menolak prospek</t>
+          <t>Menolak Prospek</t>
         </is>
       </c>
       <c r="E837" s="56" t="inlineStr">
@@ -35527,19 +35527,19 @@
       </c>
       <c r="G837" s="56" t="inlineStr">
         <is>
-          <t>Klik button Batalkan pada moal tolak prospek</t>
+          <t>Klik titik tiga - Klik Tolak - Input Remark - Klik button Tolak</t>
         </is>
       </c>
       <c r="H837" s="56" t="inlineStr">
         <is>
-          <t>Modal tolak prospek tertutup dan tetap berada di halaman approval non banking</t>
+          <t>Berhasil menolak prospek, menampilkan popup 'Sukses menolak prospek'</t>
         </is>
       </c>
     </row>
     <row r="838" ht="28" customHeight="1">
       <c r="A838" s="55" t="inlineStr">
         <is>
-          <t>70.12</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="B838" s="56" t="inlineStr">
@@ -35554,7 +35554,7 @@
       </c>
       <c r="D838" s="56" t="inlineStr">
         <is>
-          <t>Tidak menginput remark pada modal tolak prospek</t>
+          <t>Batal menolak prospek</t>
         </is>
       </c>
       <c r="E838" s="56" t="inlineStr">
@@ -35564,24 +35564,24 @@
       </c>
       <c r="F838" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G838" s="56" t="inlineStr">
         <is>
-          <t>Kosongkan remark - Klik button Tolak</t>
+          <t>Klik button Batalkan pada moal tolak prospek</t>
         </is>
       </c>
       <c r="H838" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan alert 'Remark dibutuhkan!'</t>
+          <t>Modal tolak prospek tertutup dan tetap berada di halaman approval non banking</t>
         </is>
       </c>
     </row>
     <row r="839" ht="70" customHeight="1">
       <c r="A839" s="55" t="inlineStr">
         <is>
-          <t>70.13</t>
+          <t>70.12</t>
         </is>
       </c>
       <c r="B839" s="56" t="inlineStr">
@@ -35596,7 +35596,7 @@
       </c>
       <c r="D839" s="56" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Tidak menginput remark pada modal tolak prospek</t>
         </is>
       </c>
       <c r="E839" s="56" t="inlineStr">
@@ -35606,24 +35606,24 @@
       </c>
       <c r="F839" s="55" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G839" s="56" t="inlineStr">
         <is>
-          <t>Klik pagination (10/halaman) - Pilih berapa data yang ingin ditampilkan</t>
+          <t>Kosongkan remark - Klik button Tolak</t>
         </is>
       </c>
       <c r="H839" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+          <t>Menampilkan alert 'Remark dibutuhkan!'</t>
         </is>
       </c>
     </row>
     <row r="840" ht="28" customHeight="1">
       <c r="A840" s="55" t="inlineStr">
         <is>
-          <t>70.14</t>
+          <t>70.13</t>
         </is>
       </c>
       <c r="B840" s="56" t="inlineStr">
@@ -35638,7 +35638,7 @@
       </c>
       <c r="D840" s="56" t="inlineStr">
         <is>
-          <t>Pindah Halaman</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E840" s="56" t="inlineStr">
@@ -35653,19 +35653,19 @@
       </c>
       <c r="G840" s="56" t="inlineStr">
         <is>
-          <t>Input angka halaman di field pindah halaman - Klik Enter pada keyboard</t>
+          <t>Klik pagination (10/halaman) - Pilih berapa data yang ingin ditampilkan</t>
         </is>
       </c>
       <c r="H840" s="56" t="inlineStr">
         <is>
-          <t>Berhasil berpindah ke halaman yang dituju.</t>
+          <t>Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="841" ht="84" customHeight="1">
       <c r="A841" s="55" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>70.14</t>
         </is>
       </c>
       <c r="B841" s="56" t="inlineStr">
@@ -35680,7 +35680,7 @@
       </c>
       <c r="D841" s="56" t="inlineStr">
         <is>
-          <t>Filter kolom</t>
+          <t>Pindah Halaman</t>
         </is>
       </c>
       <c r="E841" s="56" t="inlineStr">
@@ -35690,24 +35690,24 @@
       </c>
       <c r="F841" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G841" s="56" t="inlineStr">
         <is>
-          <t>Klik icon filter kolom - Checklist/unchecklist kolom</t>
+          <t>Input angka halaman di field pindah halaman - Klik Enter pada keyboard</t>
         </is>
       </c>
       <c r="H841" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tabel sesuai dengan kolom yang di ceklis</t>
+          <t>Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
     <row r="842" ht="28" customHeight="1">
       <c r="A842" s="55" t="inlineStr">
         <is>
-          <t>70.16</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="B842" s="56" t="inlineStr">
@@ -35722,7 +35722,7 @@
       </c>
       <c r="D842" s="56" t="inlineStr">
         <is>
-          <t>Reset ke Default pada filter kolom</t>
+          <t>Filter kolom</t>
         </is>
       </c>
       <c r="E842" s="56" t="inlineStr">
@@ -35737,19 +35737,19 @@
       </c>
       <c r="G842" s="56" t="inlineStr">
         <is>
-          <t>Klik Reset ke Default</t>
+          <t>Klik icon filter kolom - Checklist/unchecklist kolom</t>
         </is>
       </c>
       <c r="H842" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data tabel dengan kolom default</t>
+          <t>Menampilkan data tabel sesuai dengan kolom yang di ceklis</t>
         </is>
       </c>
     </row>
     <row r="843" ht="28" customHeight="1">
       <c r="A843" s="55" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>70.16</t>
         </is>
       </c>
       <c r="B843" s="56" t="inlineStr">
@@ -35764,7 +35764,7 @@
       </c>
       <c r="D843" s="56" t="inlineStr">
         <is>
-          <t>Filter data</t>
+          <t>Reset ke Default pada filter kolom</t>
         </is>
       </c>
       <c r="E843" s="56" t="inlineStr">
@@ -35779,19 +35779,19 @@
       </c>
       <c r="G843" s="56" t="inlineStr">
         <is>
-          <t>Pilih sales - Pilih produk - Pilih bulan - Pilih tahun - Klik button Submit</t>
+          <t>Klik Reset ke Default</t>
         </is>
       </c>
       <c r="H843" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data approval non banking sesuai dengan filter data yang di pilih</t>
+          <t>Berhasil menampilkan data tabel dengan kolom default</t>
         </is>
       </c>
     </row>
     <row r="844" ht="28" customHeight="1">
       <c r="A844" s="55" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>70.17</t>
         </is>
       </c>
       <c r="B844" s="56" t="inlineStr">
@@ -35806,7 +35806,7 @@
       </c>
       <c r="D844" s="56" t="inlineStr">
         <is>
-          <t>Mencari data</t>
+          <t>Filter data</t>
         </is>
       </c>
       <c r="E844" s="56" t="inlineStr">
@@ -35816,24 +35816,24 @@
       </c>
       <c r="F844" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G844" s="56" t="inlineStr">
         <is>
-          <t>Input keyword pada field search - Klik icon search yang ada di sebelah field search</t>
+          <t>Pilih sales - Pilih produk - Pilih bulan - Pilih tahun - Klik button Submit</t>
         </is>
       </c>
       <c r="H844" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai dengan keyword yang di cari</t>
+          <t>Menampilkan data approval non banking sesuai dengan filter data yang di pilih</t>
         </is>
       </c>
     </row>
     <row r="845" ht="42" customHeight="1">
       <c r="A845" s="55" t="inlineStr">
         <is>
-          <t>70.19</t>
+          <t>70.18</t>
         </is>
       </c>
       <c r="B845" s="56" t="inlineStr">
@@ -35848,7 +35848,7 @@
       </c>
       <c r="D845" s="56" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Mencari data</t>
         </is>
       </c>
       <c r="E845" s="56" t="inlineStr">
@@ -35858,24 +35858,24 @@
       </c>
       <c r="F845" s="55" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G845" s="56" t="inlineStr">
         <is>
-          <t>Klik pagination (10/halaman) - Pilih berapa data yang ingin ditampilkan</t>
+          <t>Input keyword pada field search - Klik icon search yang ada di sebelah field search</t>
         </is>
       </c>
       <c r="H845" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+          <t>Berhasil menampilkan data sesuai dengan keyword yang di cari</t>
         </is>
       </c>
     </row>
     <row r="846" ht="28" customHeight="1">
       <c r="A846" s="55" t="inlineStr">
         <is>
-          <t>70.20</t>
+          <t>70.19</t>
         </is>
       </c>
       <c r="B846" s="56" t="inlineStr">
@@ -35890,7 +35890,7 @@
       </c>
       <c r="D846" s="56" t="inlineStr">
         <is>
-          <t>Pindah Halaman</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E846" s="56" t="inlineStr">
@@ -35905,19 +35905,19 @@
       </c>
       <c r="G846" s="56" t="inlineStr">
         <is>
-          <t>Input angka halaman di field pindah halaman - Klik Enter pada keyboard</t>
+          <t>Klik pagination (10/halaman) - Pilih berapa data yang ingin ditampilkan</t>
         </is>
       </c>
       <c r="H846" s="56" t="inlineStr">
         <is>
-          <t>Berhasil berpindah ke halaman yang dituju.</t>
+          <t>Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="847" ht="14" customHeight="1">
       <c r="A847" s="55" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>70.20</t>
         </is>
       </c>
       <c r="B847" s="56" t="inlineStr">
@@ -35932,7 +35932,7 @@
       </c>
       <c r="D847" s="56" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Pindah Halaman</t>
         </is>
       </c>
       <c r="E847" s="56" t="inlineStr">
@@ -35947,19 +35947,19 @@
       </c>
       <c r="G847" s="56" t="inlineStr">
         <is>
-          <t>Klik pagination (10/halaman) - Pilih berapa data yang ingin ditampilkan</t>
+          <t>Input angka halaman di field pindah halaman - Klik Enter pada keyboard</t>
         </is>
       </c>
       <c r="H847" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
+          <t>Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
     <row r="848" ht="14" customHeight="1">
       <c r="A848" s="55" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="B848" s="56" t="inlineStr">
@@ -35974,7 +35974,7 @@
       </c>
       <c r="D848" s="56" t="inlineStr">
         <is>
-          <t>Pindah Halaman</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E848" s="56" t="inlineStr">
@@ -35989,19 +35989,19 @@
       </c>
       <c r="G848" s="56" t="inlineStr">
         <is>
-          <t>Input angka halaman di field pindah halaman - Klik Enter pada keyboard</t>
+          <t>Klik pagination (10/halaman) - Pilih berapa data yang ingin ditampilkan</t>
         </is>
       </c>
       <c r="H848" s="56" t="inlineStr">
         <is>
-          <t>Berhasil berpindah ke halaman yang dituju.</t>
+          <t>Berhasil menampilkan data sesuai jumlah data per halaman yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="849" ht="42" customHeight="1">
       <c r="A849" s="55" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="B849" s="56" t="inlineStr">
@@ -36011,12 +36011,12 @@
       </c>
       <c r="C849" s="56" t="inlineStr">
         <is>
-          <t>Re-Assign Prospek</t>
+          <t>Approval non Banking</t>
         </is>
       </c>
       <c r="D849" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Re-Assign Prospek</t>
+          <t>Pindah Halaman</t>
         </is>
       </c>
       <c r="E849" s="56" t="inlineStr">
@@ -36026,24 +36026,24 @@
       </c>
       <c r="F849" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G849" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Re-Assign &amp; Approval - Klik submenu Re-Assign Prospek</t>
+          <t>Input angka halaman di field pindah halaman - Klik Enter pada keyboard</t>
         </is>
       </c>
       <c r="H849" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman Re-Assign Prospek</t>
+          <t>Berhasil berpindah ke halaman yang dituju.</t>
         </is>
       </c>
     </row>
     <row r="850" ht="28" customHeight="1">
       <c r="A850" s="55" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="B850" s="56" t="inlineStr">
@@ -36058,7 +36058,7 @@
       </c>
       <c r="D850" s="56" t="inlineStr">
         <is>
-          <t>Melakukan Re-Assign Prospek</t>
+          <t>Membuka halaman Re-Assign Prospek</t>
         </is>
       </c>
       <c r="E850" s="56" t="inlineStr">
@@ -36073,19 +36073,19 @@
       </c>
       <c r="G850" s="56" t="inlineStr">
         <is>
-          <t>Pilih prospek dengan klik checkbox - Klik button Re-Assign () data - Klik button Yes - Pilih kantor wilayah - Pilih kantor cabang - Pilih kantor cabang pembantu - Pilih sales - Klik button Submit</t>
+          <t>Klik menu Re-Assign &amp; Approval - Klik submenu Re-Assign Prospek</t>
         </is>
       </c>
       <c r="H850" s="56" t="inlineStr">
         <is>
-          <t>Berhasil melakukan re-assign prospek ke sales yang di pilih dan menampilkan popup 'Berhasil melakukan Re-assign Prospek' kemudian data tersebut sudah tidak ada pada tabel re-assign prospek</t>
+          <t>Menampilkan halaman Re-Assign Prospek</t>
         </is>
       </c>
     </row>
     <row r="851" ht="28" customHeight="1">
       <c r="A851" s="55" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="B851" s="56" t="inlineStr">
@@ -36100,7 +36100,7 @@
       </c>
       <c r="D851" s="56" t="inlineStr">
         <is>
-          <t>Validasi count checklist data</t>
+          <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
       <c r="E851" s="56" t="inlineStr">
@@ -36110,24 +36110,24 @@
       </c>
       <c r="F851" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G851" s="56" t="inlineStr">
         <is>
-          <t>Cek informasi yang ada pada button Reassign () data</t>
+          <t>Pilih prospek dengan klik checkbox - Klik button Re-Assign () data - Klik button Yes - Pilih kantor wilayah - Pilih kantor cabang - Pilih kantor cabang pembantu - Pilih sales - Klik button Submit</t>
         </is>
       </c>
       <c r="H851" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan count angka yang sesuai dengan data yang di checklist</t>
+          <t>Berhasil melakukan re-assign prospek ke sales yang di pilih dan menampilkan popup 'Berhasil melakukan Re-assign Prospek' kemudian data tersebut sudah tidak ada pada tabel re-assign prospek</t>
         </is>
       </c>
     </row>
     <row r="852" ht="28" customHeight="1">
       <c r="A852" s="55" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="B852" s="56" t="inlineStr">
@@ -36142,7 +36142,7 @@
       </c>
       <c r="D852" s="56" t="inlineStr">
         <is>
-          <t>Validasi data yang sudah dii pilih</t>
+          <t>Validasi count checklist data</t>
         </is>
       </c>
       <c r="E852" s="56" t="inlineStr">
@@ -36157,19 +36157,19 @@
       </c>
       <c r="G852" s="56" t="inlineStr">
         <is>
-          <t>Cek pada halaman pindah kelolaan, data tabel nya berisi prospek yang di pilih</t>
+          <t>Cek informasi yang ada pada button Reassign () data</t>
         </is>
       </c>
       <c r="H852" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tabel prospek yang di pilih saja</t>
+          <t>Menampilkan count angka yang sesuai dengan data yang di checklist</t>
         </is>
       </c>
     </row>
     <row r="853" ht="28" customHeight="1">
       <c r="A853" s="55" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="B853" s="56" t="inlineStr">
@@ -36184,34 +36184,34 @@
       </c>
       <c r="D853" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field inputan mandatory pada reassign prospek</t>
+          <t>Validasi data yang sudah dii pilih</t>
         </is>
       </c>
       <c r="E853" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F853" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G853" s="56" t="inlineStr">
         <is>
-          <t>Kosongkan salah satu atau semua field mandatory - Klik button Submit</t>
+          <t>Cek pada halaman pindah kelolaan, data tabel nya berisi prospek yang di pilih</t>
         </is>
       </c>
       <c r="H853" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan alert pada setiap field mandatory bahwa field tersebut dibutuhkan / wajib diisi</t>
+          <t>Menampilkan data tabel prospek yang di pilih saja</t>
         </is>
       </c>
     </row>
     <row r="854" ht="28" customHeight="1">
       <c r="A854" s="55" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="B854" s="56" t="inlineStr">
@@ -36226,12 +36226,12 @@
       </c>
       <c r="D854" s="56" t="inlineStr">
         <is>
-          <t>Membatalkan Re-Assign Prospek</t>
+          <t>Mengosongkan field inputan mandatory pada reassign prospek</t>
         </is>
       </c>
       <c r="E854" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F854" s="55" t="inlineStr">
@@ -36241,19 +36241,19 @@
       </c>
       <c r="G854" s="56" t="inlineStr">
         <is>
-          <t>Klik button Batalkan pada halaman pindah kelolaan</t>
+          <t>Kosongkan salah satu atau semua field mandatory - Klik button Submit</t>
         </is>
       </c>
       <c r="H854" s="56" t="inlineStr">
         <is>
-          <t>Kembali ke halaman utama Re-assign Prospek</t>
+          <t>Menampilkan alert pada setiap field mandatory bahwa field tersebut dibutuhkan / wajib diisi</t>
         </is>
       </c>
     </row>
     <row r="855" ht="28" customHeight="1">
       <c r="A855" s="55" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="B855" s="56" t="inlineStr">
@@ -36268,7 +36268,7 @@
       </c>
       <c r="D855" s="56" t="inlineStr">
         <is>
-          <t>Validasi data prospek yang di re-assign</t>
+          <t>Membatalkan Re-Assign Prospek</t>
         </is>
       </c>
       <c r="E855" s="56" t="inlineStr">
@@ -36283,19 +36283,19 @@
       </c>
       <c r="G855" s="56" t="inlineStr">
         <is>
-          <t>Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek - Klik menu Lead Qualification - Klik submenu Aktifitas - Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
+          <t>Klik button Batalkan pada halaman pindah kelolaan</t>
         </is>
       </c>
       <c r="H855" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data prospek yang sebelumnya di re-assign dan pada detail prospek menampilkan informasi ex. "Re-prospek dari Lead ID: 11370987"</t>
+          <t>Kembali ke halaman utama Re-assign Prospek</t>
         </is>
       </c>
     </row>
     <row r="856" ht="28" customHeight="1">
       <c r="A856" s="55" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="B856" s="56" t="inlineStr">
@@ -36310,7 +36310,7 @@
       </c>
       <c r="D856" s="56" t="inlineStr">
         <is>
-          <t>Melakukan Re-assign prospek semua data</t>
+          <t>Validasi data prospek yang di re-assign</t>
         </is>
       </c>
       <c r="E856" s="56" t="inlineStr">
@@ -36325,19 +36325,19 @@
       </c>
       <c r="G856" s="56" t="inlineStr">
         <is>
-          <t>Klik button Reassign semua data - Klik button Yes - Pilih kantor wilayah - Pilih kantor cabang - Pilih kantor cabang pembantu - Pilih sales - Klik button Submit</t>
+          <t>Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek - Klik menu Lead Qualification - Klik submenu Aktifitas - Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
       <c r="H856" s="56" t="inlineStr">
         <is>
-          <t>Berhasil melakukan re-assign prospek ke sales yang di pilih dan menampilkan popup 'Berhasil melakukan Re-assign Prospek' kemudian data tabel sudah kosong / tidak ada data re-assign prospek</t>
+          <t>Berhasil menampilkan data prospek yang sebelumnya di re-assign dan pada detail prospek menampilkan informasi ex. "Re-prospek dari Lead ID: 11370987"</t>
         </is>
       </c>
     </row>
     <row r="857" ht="28" customHeight="1">
       <c r="A857" s="55" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="B857" s="56" t="inlineStr">
@@ -36352,7 +36352,7 @@
       </c>
       <c r="D857" s="56" t="inlineStr">
         <is>
-          <t>Validasi semua data</t>
+          <t>Melakukan Re-assign prospek semua data</t>
         </is>
       </c>
       <c r="E857" s="56" t="inlineStr">
@@ -36362,24 +36362,24 @@
       </c>
       <c r="F857" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G857" s="56" t="inlineStr">
         <is>
-          <t>Cek pada halaman pindah kelolaan, data tabel nya berisi semua prospek</t>
+          <t>Klik button Reassign semua data - Klik button Yes - Pilih kantor wilayah - Pilih kantor cabang - Pilih kantor cabang pembantu - Pilih sales - Klik button Submit</t>
         </is>
       </c>
       <c r="H857" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tabel yang berisi semua prospek</t>
+          <t>Berhasil melakukan re-assign prospek ke sales yang di pilih dan menampilkan popup 'Berhasil melakukan Re-assign Prospek' kemudian data tabel sudah kosong / tidak ada data re-assign prospek</t>
         </is>
       </c>
     </row>
     <row r="858" ht="28" customHeight="1">
       <c r="A858" s="55" t="inlineStr">
         <is>
-          <t>71.10</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="B858" s="56" t="inlineStr">
@@ -36394,7 +36394,7 @@
       </c>
       <c r="D858" s="56" t="inlineStr">
         <is>
-          <t>Membatalkan Re-Assign Prospek</t>
+          <t>Validasi semua data</t>
         </is>
       </c>
       <c r="E858" s="56" t="inlineStr">
@@ -36404,24 +36404,24 @@
       </c>
       <c r="F858" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G858" s="56" t="inlineStr">
         <is>
-          <t>Klik button Batalkan pada halaman pindah kelolaan</t>
+          <t>Cek pada halaman pindah kelolaan, data tabel nya berisi semua prospek</t>
         </is>
       </c>
       <c r="H858" s="56" t="inlineStr">
         <is>
-          <t>Kembali ke halaman utama Re-assign Prospek</t>
+          <t>Menampilkan data tabel yang berisi semua prospek</t>
         </is>
       </c>
     </row>
     <row r="859" ht="28" customHeight="1">
       <c r="A859" s="55" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>71.10</t>
         </is>
       </c>
       <c r="B859" s="56" t="inlineStr">
@@ -36436,7 +36436,7 @@
       </c>
       <c r="D859" s="56" t="inlineStr">
         <is>
-          <t>Validasi semua data prospek yang di re-assign</t>
+          <t>Membatalkan Re-Assign Prospek</t>
         </is>
       </c>
       <c r="E859" s="56" t="inlineStr">
@@ -36446,24 +36446,24 @@
       </c>
       <c r="F859" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G859" s="56" t="inlineStr">
         <is>
-          <t>Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek - Klik menu Lead Qualification - Klik submenu Aktifitas - Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
+          <t>Klik button Batalkan pada halaman pindah kelolaan</t>
         </is>
       </c>
       <c r="H859" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data prospek yang sebelumnya di re-assign dan pada detail prospek menampilkan informasi ex. "Re-prospek dari Lead ID: 11370987"</t>
+          <t>Kembali ke halaman utama Re-assign Prospek</t>
         </is>
       </c>
     </row>
     <row r="860" ht="28" customHeight="1">
       <c r="A860" s="55" t="inlineStr">
         <is>
-          <t>71.12</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="B860" s="56" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="D860" s="56" t="inlineStr">
         <is>
-          <t>Melakukan Re-Assign Prospek</t>
+          <t>Validasi semua data prospek yang di re-assign</t>
         </is>
       </c>
       <c r="E860" s="56" t="inlineStr">
@@ -36488,24 +36488,24 @@
       </c>
       <c r="F860" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G860" s="56" t="inlineStr">
         <is>
-          <t>Pilih prospek dengan klik checkbox - Klik button Re-Assign () data - Klik button Yes - Pilih kantor wilayah - Pilih kantor cabang - Pilih kantor cabang pembantu - Pilih sales - Klik button Submit</t>
+          <t>Login menggunakan user yang sebelumnya sudah dipilih ketika re-assign prospek - Klik menu Lead Qualification - Klik submenu Aktifitas - Cek data yang sebelum nya di re-assign pada tabel dan pada detail prospek</t>
         </is>
       </c>
       <c r="H860" s="56" t="inlineStr">
         <is>
-          <t>Berhasil melakukan re-assign prospek ke sales yang di pilih dan menampilkan popup 'Berhasil melakukan Re-assign Prospek' kemudian data tersebut sudah tidak ada pada tabel re-assign prospek</t>
+          <t>Berhasil menampilkan data prospek yang sebelumnya di re-assign dan pada detail prospek menampilkan informasi ex. "Re-prospek dari Lead ID: 11370987"</t>
         </is>
       </c>
     </row>
     <row r="861" ht="28" customHeight="1">
       <c r="A861" s="55" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.12</t>
         </is>
       </c>
       <c r="B861" s="56" t="inlineStr">
@@ -36515,12 +36515,12 @@
       </c>
       <c r="C861" s="56" t="inlineStr">
         <is>
-          <t>Re-Assign Management</t>
+          <t>Re-Assign Prospek</t>
         </is>
       </c>
       <c r="D861" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Re-Assign Management</t>
+          <t>Melakukan Re-Assign Prospek</t>
         </is>
       </c>
       <c r="E861" s="56" t="inlineStr">
@@ -36535,19 +36535,19 @@
       </c>
       <c r="G861" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Re-Assign &amp; Approval - Klik submenu Re-Assign Management</t>
+          <t>Pilih prospek dengan klik checkbox - Klik button Re-Assign () data - Klik button Yes - Pilih kantor wilayah - Pilih kantor cabang - Pilih kantor cabang pembantu - Pilih sales - Klik button Submit</t>
         </is>
       </c>
       <c r="H861" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman Re-Assign Management</t>
+          <t>Berhasil melakukan re-assign prospek ke sales yang di pilih dan menampilkan popup 'Berhasil melakukan Re-assign Prospek' kemudian data tersebut sudah tidak ada pada tabel re-assign prospek</t>
         </is>
       </c>
     </row>
     <row r="862" ht="28" customHeight="1">
       <c r="A862" s="55" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="B862" s="56" t="inlineStr">
@@ -36562,7 +36562,7 @@
       </c>
       <c r="D862" s="56" t="inlineStr">
         <is>
-          <t>Mencari data prospek pada halaman Re-Assign Management</t>
+          <t>Membuka halaman Re-Assign Management</t>
         </is>
       </c>
       <c r="E862" s="56" t="inlineStr">
@@ -36577,19 +36577,19 @@
       </c>
       <c r="G862" s="56" t="inlineStr">
         <is>
-          <t>Input nama nasabah pada field search - Klik icon search atau klik Enter</t>
+          <t>Klik menu Re-Assign &amp; Approval - Klik submenu Re-Assign Management</t>
         </is>
       </c>
       <c r="H862" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data prospek Re-Assign Management sesuai dengan nama yang di cari</t>
+          <t>Menampilkan halaman Re-Assign Management</t>
         </is>
       </c>
     </row>
     <row r="863" ht="28" customHeight="1">
       <c r="A863" s="55" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="B863" s="56" t="inlineStr">
@@ -36604,7 +36604,7 @@
       </c>
       <c r="D863" s="56" t="inlineStr">
         <is>
-          <t>Mencari data prospek yang tidak ada pada halaman Re-Assign Management</t>
+          <t>Mencari data prospek pada halaman Re-Assign Management</t>
         </is>
       </c>
       <c r="E863" s="56" t="inlineStr">
@@ -36619,19 +36619,19 @@
       </c>
       <c r="G863" s="56" t="inlineStr">
         <is>
-          <t>Input nama nasabah yang datanya tidak ada - Klik icon search atau klik Enter</t>
+          <t>Input nama nasabah pada field search - Klik icon search atau klik Enter</t>
         </is>
       </c>
       <c r="H863" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan tabel kosong dengan keterangan no data</t>
+          <t>Menampilkan data prospek Re-Assign Management sesuai dengan nama yang di cari</t>
         </is>
       </c>
     </row>
     <row r="864" ht="28" customHeight="1">
       <c r="A864" s="55" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="B864" s="56" t="inlineStr">
@@ -36646,7 +36646,7 @@
       </c>
       <c r="D864" s="56" t="inlineStr">
         <is>
-          <t>Validasi jumlah data yang di pilih untuk reassign</t>
+          <t>Mencari data prospek yang tidak ada pada halaman Re-Assign Management</t>
         </is>
       </c>
       <c r="E864" s="56" t="inlineStr">
@@ -36661,19 +36661,19 @@
       </c>
       <c r="G864" s="56" t="inlineStr">
         <is>
-          <t>cek jumlah data yang muncul pada button Reassign () data</t>
+          <t>Input nama nasabah yang datanya tidak ada - Klik icon search atau klik Enter</t>
         </is>
       </c>
       <c r="H864" s="56" t="inlineStr">
         <is>
-          <t>Angka yang muncul pada button sesuai dengan jumlah data yang di pilih</t>
+          <t>Menampilkan tabel kosong dengan keterangan no data</t>
         </is>
       </c>
     </row>
     <row r="865" ht="28" customHeight="1">
       <c r="A865" s="55" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="B865" s="56" t="inlineStr">
@@ -36688,7 +36688,7 @@
       </c>
       <c r="D865" s="56" t="inlineStr">
         <is>
-          <t>Validasi data prospek yang di re-assign ke sales</t>
+          <t>Validasi jumlah data yang di pilih untuk reassign</t>
         </is>
       </c>
       <c r="E865" s="56" t="inlineStr">
@@ -36703,34 +36703,34 @@
       </c>
       <c r="G865" s="56" t="inlineStr">
         <is>
-          <t>Login dengan akun sales yang sebelumnya sudah di pilih reassign management - Klik menu Lead Qualification - Klik submenu Aktifitas Referal - Cek data prospek yang sudah di reassign</t>
+          <t>cek jumlah data yang muncul pada button Reassign () data</t>
         </is>
       </c>
       <c r="H865" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data prospek yang sesuai dari reassign management</t>
+          <t>Angka yang muncul pada button sesuai dengan jumlah data yang di pilih</t>
         </is>
       </c>
     </row>
     <row r="866" ht="28" customHeight="1">
       <c r="A866" s="55" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="B866" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Re-Assign dan Approval</t>
         </is>
       </c>
       <c r="C866" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Re-Assign Management</t>
         </is>
       </c>
       <c r="D866" s="56" t="inlineStr">
         <is>
-          <t>Membuka menu riwayat export saya</t>
+          <t>Validasi data prospek yang di re-assign ke sales</t>
         </is>
       </c>
       <c r="E866" s="56" t="inlineStr">
@@ -36745,19 +36745,19 @@
       </c>
       <c r="G866" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Export Center, klik submenu Riwayat export</t>
+          <t>Login dengan akun sales yang sebelumnya sudah di pilih reassign management - Klik menu Lead Qualification - Klik submenu Aktifitas Referal - Cek data prospek yang sudah di reassign</t>
         </is>
       </c>
       <c r="H866" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman Riwayat export</t>
+          <t>Berhasil menampilkan data prospek yang sesuai dari reassign management</t>
         </is>
       </c>
     </row>
     <row r="867" ht="28" customHeight="1">
       <c r="A867" s="55" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="B867" s="56" t="inlineStr">
@@ -36772,7 +36772,7 @@
       </c>
       <c r="D867" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Membuka menu riwayat export saya</t>
         </is>
       </c>
       <c r="E867" s="56" t="inlineStr">
@@ -36782,24 +36782,24 @@
       </c>
       <c r="F867" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G867" s="56" t="inlineStr">
         <is>
-          <t>Klik button filter – pilih modul, export status, dan tentan tanggal request – kemudian klik terapkan filter</t>
+          <t>Klik menu Export Center, klik submenu Riwayat export</t>
         </is>
       </c>
       <c r="H867" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai filter yang dipilih</t>
+          <t>Menampilkan halaman Riwayat export</t>
         </is>
       </c>
     </row>
     <row r="868" ht="28" customHeight="1">
       <c r="A868" s="55" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="B868" s="56" t="inlineStr">
@@ -36814,7 +36814,7 @@
       </c>
       <c r="D868" s="56" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E868" s="56" t="inlineStr">
@@ -36824,24 +36824,24 @@
       </c>
       <c r="F868" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G868" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data dengan memilih status approval 'pending' dan status export 'Generate'</t>
+          <t>Klik button filter – pilih modul, export status, dan tentan tanggal request – kemudian klik terapkan filter</t>
         </is>
       </c>
       <c r="H868" s="56" t="inlineStr">
         <is>
-          <t>Berhasil Jumlah data pada card dan table sesuai</t>
+          <t>Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="869" ht="28" customHeight="1">
       <c r="A869" s="55" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="B869" s="56" t="inlineStr">
@@ -36856,7 +36856,7 @@
       </c>
       <c r="D869" s="56" t="inlineStr">
         <is>
-          <t>Validasi card disetujui dengan data table</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E869" s="56" t="inlineStr">
@@ -36871,7 +36871,7 @@
       </c>
       <c r="G869" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data status approval dengan memilih status 'Approved'</t>
+          <t>Melakukan filter data dengan memilih status approval 'pending' dan status export 'Generate'</t>
         </is>
       </c>
       <c r="H869" s="56" t="inlineStr">
@@ -36883,7 +36883,7 @@
     <row r="870" ht="28" customHeight="1">
       <c r="A870" s="55" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="B870" s="56" t="inlineStr">
@@ -36898,7 +36898,7 @@
       </c>
       <c r="D870" s="56" t="inlineStr">
         <is>
-          <t>Validasi card ditolak dengan data table</t>
+          <t>Validasi card disetujui dengan data table</t>
         </is>
       </c>
       <c r="E870" s="56" t="inlineStr">
@@ -36913,7 +36913,7 @@
       </c>
       <c r="G870" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data status approval dengan memilih status 'Rejected'</t>
+          <t>Melakukan filter data status approval dengan memilih status 'Approved'</t>
         </is>
       </c>
       <c r="H870" s="56" t="inlineStr">
@@ -36925,7 +36925,7 @@
     <row r="871" ht="28" customHeight="1">
       <c r="A871" s="55" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="B871" s="56" t="inlineStr">
@@ -36940,7 +36940,7 @@
       </c>
       <c r="D871" s="56" t="inlineStr">
         <is>
-          <t>Validasi card kadaluwarsa dengan data table</t>
+          <t>Validasi card ditolak dengan data table</t>
         </is>
       </c>
       <c r="E871" s="56" t="inlineStr">
@@ -36950,12 +36950,12 @@
       </c>
       <c r="F871" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G871" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data status approval dengan memilih status 'Expired'</t>
+          <t>Melakukan filter data status approval dengan memilih status 'Rejected'</t>
         </is>
       </c>
       <c r="H871" s="56" t="inlineStr">
@@ -36967,7 +36967,7 @@
     <row r="872" ht="70" customHeight="1">
       <c r="A872" s="55" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="B872" s="56" t="inlineStr">
@@ -36982,7 +36982,7 @@
       </c>
       <c r="D872" s="56" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Validasi card kadaluwarsa dengan data table</t>
         </is>
       </c>
       <c r="E872" s="56" t="inlineStr">
@@ -36992,24 +36992,24 @@
       </c>
       <c r="F872" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G872" s="56" t="inlineStr">
         <is>
-          <t>Input data pada kolom pencarian</t>
+          <t>Melakukan filter data status approval dengan memilih status 'Expired'</t>
         </is>
       </c>
       <c r="H872" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai kata kunci</t>
+          <t>Berhasil Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="873" ht="42" customHeight="1">
       <c r="A873" s="55" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="B873" s="56" t="inlineStr">
@@ -37024,12 +37024,12 @@
       </c>
       <c r="D873" s="56" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E873" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F873" s="55" t="inlineStr">
@@ -37039,19 +37039,19 @@
       </c>
       <c r="G873" s="56" t="inlineStr">
         <is>
-          <t>Input data yang belum terdaftar</t>
+          <t>Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H873" s="56" t="inlineStr">
         <is>
-          <t>Data tidak ditemukan</t>
+          <t>Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="874" ht="42" customHeight="1">
       <c r="A874" s="55" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="B874" s="56" t="inlineStr">
@@ -37066,12 +37066,12 @@
       </c>
       <c r="D874" s="56" t="inlineStr">
         <is>
-          <t>Mengunduh data yang sudah di approve</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E874" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F874" s="55" t="inlineStr">
@@ -37081,19 +37081,19 @@
       </c>
       <c r="G874" s="56" t="inlineStr">
         <is>
-          <t>Klik button download</t>
+          <t>Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H874" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mengunduh data</t>
+          <t>Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="875" ht="70" customHeight="1">
       <c r="A875" s="55" t="inlineStr">
         <is>
-          <t>73.10</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="B875" s="56" t="inlineStr">
@@ -37108,7 +37108,7 @@
       </c>
       <c r="D875" s="56" t="inlineStr">
         <is>
-          <t>Membuka dokumen hasil download</t>
+          <t>Mengunduh data yang sudah di approve</t>
         </is>
       </c>
       <c r="E875" s="56" t="inlineStr">
@@ -37123,19 +37123,19 @@
       </c>
       <c r="G875" s="56" t="inlineStr">
         <is>
-          <t>Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
+          <t>Klik button download</t>
         </is>
       </c>
       <c r="H875" s="56" t="inlineStr">
         <is>
-          <t>Berhasil membuka file hasil download</t>
+          <t>Berhasil mengunduh data</t>
         </is>
       </c>
     </row>
     <row r="876" ht="28" customHeight="1">
       <c r="A876" s="55" t="inlineStr">
         <is>
-          <t>73.11</t>
+          <t>73.10</t>
         </is>
       </c>
       <c r="B876" s="56" t="inlineStr">
@@ -37150,7 +37150,7 @@
       </c>
       <c r="D876" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Membuka dokumen hasil download</t>
         </is>
       </c>
       <c r="E876" s="56" t="inlineStr">
@@ -37160,24 +37160,24 @@
       </c>
       <c r="F876" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G876" s="56" t="inlineStr">
         <is>
-          <t>Klik button filter – pilih modul, export status, dan tentan tanggal request – kemudian klik terapkan filter</t>
+          <t>Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
         </is>
       </c>
       <c r="H876" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai filter yang dipilih</t>
+          <t>Berhasil membuka file hasil download</t>
         </is>
       </c>
     </row>
     <row r="877" ht="42" customHeight="1">
       <c r="A877" s="55" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>73.11</t>
         </is>
       </c>
       <c r="B877" s="56" t="inlineStr">
@@ -37192,7 +37192,7 @@
       </c>
       <c r="D877" s="56" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E877" s="56" t="inlineStr">
@@ -37202,24 +37202,24 @@
       </c>
       <c r="F877" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G877" s="56" t="inlineStr">
         <is>
-          <t>Input data pada kolom pencarian</t>
+          <t>Klik button filter – pilih modul, export status, dan tentan tanggal request – kemudian klik terapkan filter</t>
         </is>
       </c>
       <c r="H877" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai kata kunci</t>
+          <t>Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="878" ht="28" customHeight="1">
       <c r="A878" s="55" t="inlineStr">
         <is>
-          <t>73.13</t>
+          <t>73.12</t>
         </is>
       </c>
       <c r="B878" s="56" t="inlineStr">
@@ -37234,12 +37234,12 @@
       </c>
       <c r="D878" s="56" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E878" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F878" s="55" t="inlineStr">
@@ -37249,19 +37249,19 @@
       </c>
       <c r="G878" s="56" t="inlineStr">
         <is>
-          <t>Input data yang belum terdaftar</t>
+          <t>Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H878" s="56" t="inlineStr">
         <is>
-          <t>Data tidak ditemukan</t>
+          <t>Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="879" ht="28" customHeight="1">
       <c r="A879" s="55" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>73.13</t>
         </is>
       </c>
       <c r="B879" s="56" t="inlineStr">
@@ -37276,34 +37276,34 @@
       </c>
       <c r="D879" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E879" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F879" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G879" s="56" t="inlineStr">
         <is>
-          <t>Klik button filter – pilih modul, export status, dan tentan tanggal request – kemudian klik terapkan filter</t>
+          <t>Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H879" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai filter yang dipilih</t>
+          <t>Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="880" ht="28" customHeight="1">
       <c r="A880" s="55" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="B880" s="56" t="inlineStr">
@@ -37318,7 +37318,7 @@
       </c>
       <c r="D880" s="56" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Melakukan filter data</t>
         </is>
       </c>
       <c r="E880" s="56" t="inlineStr">
@@ -37328,24 +37328,24 @@
       </c>
       <c r="F880" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G880" s="56" t="inlineStr">
         <is>
-          <t>Input data pada kolom pencarian</t>
+          <t>Klik button filter – pilih modul, export status, dan tentan tanggal request – kemudian klik terapkan filter</t>
         </is>
       </c>
       <c r="H880" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai kata kunci</t>
+          <t>Menampilkan data sesuai filter yang dipilih</t>
         </is>
       </c>
     </row>
     <row r="881" ht="14" customHeight="1">
       <c r="A881" s="55" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.15</t>
         </is>
       </c>
       <c r="B881" s="56" t="inlineStr">
@@ -37360,12 +37360,12 @@
       </c>
       <c r="D881" s="56" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Mencari data pada kolom pencarian</t>
         </is>
       </c>
       <c r="E881" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F881" s="55" t="inlineStr">
@@ -37375,19 +37375,19 @@
       </c>
       <c r="G881" s="56" t="inlineStr">
         <is>
-          <t>Input data yang belum terdaftar</t>
+          <t>Input data pada kolom pencarian</t>
         </is>
       </c>
       <c r="H881" s="56" t="inlineStr">
         <is>
-          <t>Data tidak ditemukan</t>
+          <t>Menampilkan data sesuai kata kunci</t>
         </is>
       </c>
     </row>
     <row r="882" ht="42" customHeight="1">
       <c r="A882" s="55" t="inlineStr">
         <is>
-          <t>73.17</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="B882" s="56" t="inlineStr">
@@ -37402,12 +37402,12 @@
       </c>
       <c r="D882" s="56" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Mencari data kata kunci salah</t>
         </is>
       </c>
       <c r="E882" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F882" s="55" t="inlineStr">
@@ -37417,19 +37417,19 @@
       </c>
       <c r="G882" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data dengan memilih status approval 'pending' dan status export 'Generate'</t>
+          <t>Input data yang belum terdaftar</t>
         </is>
       </c>
       <c r="H882" s="56" t="inlineStr">
         <is>
-          <t>Berhasil Jumlah data pada card dan table sesuai</t>
+          <t>Data tidak ditemukan</t>
         </is>
       </c>
     </row>
     <row r="883" ht="42" customHeight="1">
       <c r="A883" s="55" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>73.17</t>
         </is>
       </c>
       <c r="B883" s="56" t="inlineStr">
@@ -37439,12 +37439,12 @@
       </c>
       <c r="C883" s="56" t="inlineStr">
         <is>
-          <t>Persetujuan Export</t>
+          <t>Riwayat export saya</t>
         </is>
       </c>
       <c r="D883" s="56" t="inlineStr">
         <is>
-          <t>Lakukan login menggunakan user monitoring</t>
+          <t>Validasi card menunggu approval dengan data table</t>
         </is>
       </c>
       <c r="E883" s="56" t="inlineStr">
@@ -37454,24 +37454,24 @@
       </c>
       <c r="F883" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G883" s="56" t="inlineStr">
         <is>
-          <t>Login menggunakan user monitoring</t>
+          <t>Melakukan filter data dengan memilih status approval 'pending' dan status export 'Generate'</t>
         </is>
       </c>
       <c r="H883" s="56" t="inlineStr">
         <is>
-          <t>Berhasil melakukan login</t>
+          <t>Berhasil Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
     <row r="884" ht="28" customHeight="1">
       <c r="A884" s="55" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="B884" s="56" t="inlineStr">
@@ -37486,7 +37486,7 @@
       </c>
       <c r="D884" s="56" t="inlineStr">
         <is>
-          <t>Membuka menu Persetujuan Export</t>
+          <t>Lakukan login menggunakan user monitoring</t>
         </is>
       </c>
       <c r="E884" s="56" t="inlineStr">
@@ -37496,24 +37496,24 @@
       </c>
       <c r="F884" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G884" s="56" t="inlineStr">
         <is>
-          <t>Klik menu exported data management, klik submenu persetujuan export</t>
+          <t>Login menggunakan user monitoring</t>
         </is>
       </c>
       <c r="H884" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman persetujuan export</t>
+          <t>Berhasil melakukan login</t>
         </is>
       </c>
     </row>
     <row r="885" ht="42" customHeight="1">
       <c r="A885" s="55" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="B885" s="56" t="inlineStr">
@@ -37528,7 +37528,7 @@
       </c>
       <c r="D885" s="56" t="inlineStr">
         <is>
-          <t>Melakukan approval data pengajuan export</t>
+          <t>Membuka menu Persetujuan Export</t>
         </is>
       </c>
       <c r="E885" s="56" t="inlineStr">
@@ -37543,19 +37543,19 @@
       </c>
       <c r="G885" s="56" t="inlineStr">
         <is>
-          <t>Klik icon titik tiga pada data pengajuan - Klik menu Setuju - Klik button YA pada popup konfirmasi</t>
+          <t>Klik menu exported data management, klik submenu persetujuan export</t>
         </is>
       </c>
       <c r="H885" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menyetujui data pengajuan export.</t>
+          <t>Menampilkan halaman persetujuan export</t>
         </is>
       </c>
     </row>
     <row r="886" ht="14" customHeight="1">
       <c r="A886" s="55" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="B886" s="56" t="inlineStr">
@@ -37570,7 +37570,7 @@
       </c>
       <c r="D886" s="56" t="inlineStr">
         <is>
-          <t>Melakukan reject data pengajuan export</t>
+          <t>Melakukan approval data pengajuan export</t>
         </is>
       </c>
       <c r="E886" s="56" t="inlineStr">
@@ -37585,19 +37585,19 @@
       </c>
       <c r="G886" s="56" t="inlineStr">
         <is>
-          <t>Klik icon (titik tiga) klik tolak, input alasan, klik submit</t>
+          <t>Klik icon titik tiga pada data pengajuan - Klik menu Setuju - Klik button YA pada popup konfirmasi</t>
         </is>
       </c>
       <c r="H886" s="56" t="inlineStr">
         <is>
-          <t>Berhasil melakukan reject data</t>
+          <t>Berhasil menyetujui data pengajuan export.</t>
         </is>
       </c>
     </row>
     <row r="887" ht="42" customHeight="1">
       <c r="A887" s="55" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="B887" s="56" t="inlineStr">
@@ -37607,12 +37607,12 @@
       </c>
       <c r="C887" s="56" t="inlineStr">
         <is>
-          <t>Management Export</t>
+          <t>Persetujuan Export</t>
         </is>
       </c>
       <c r="D887" s="56" t="inlineStr">
         <is>
-          <t>Membuka menu Management Export</t>
+          <t>Melakukan reject data pengajuan export</t>
         </is>
       </c>
       <c r="E887" s="56" t="inlineStr">
@@ -37627,19 +37627,19 @@
       </c>
       <c r="G887" s="56" t="inlineStr">
         <is>
-          <t>Klik menu exported data management, klik submenu management export</t>
+          <t>Klik icon (titik tiga) klik tolak, input alasan, klik submit</t>
         </is>
       </c>
       <c r="H887" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman management export</t>
+          <t>Berhasil melakukan reject data</t>
         </is>
       </c>
     </row>
     <row r="888" ht="42" customHeight="1">
       <c r="A888" s="55" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="B888" s="56" t="inlineStr">
@@ -37654,7 +37654,7 @@
       </c>
       <c r="D888" s="56" t="inlineStr">
         <is>
-          <t>Validasi card data file aktif dengan data table</t>
+          <t>Membuka menu Management Export</t>
         </is>
       </c>
       <c r="E888" s="56" t="inlineStr">
@@ -37664,24 +37664,24 @@
       </c>
       <c r="F888" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G888" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
+          <t>Klik menu exported data management, klik submenu management export</t>
         </is>
       </c>
       <c r="H888" s="56" t="inlineStr">
         <is>
-          <t>Jumlah data pada card dan table sesuai</t>
+          <t>Menampilkan halaman management export</t>
         </is>
       </c>
     </row>
     <row r="889" ht="28" customHeight="1">
       <c r="A889" s="55" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="B889" s="56" t="inlineStr">
@@ -37696,7 +37696,7 @@
       </c>
       <c r="D889" s="56" t="inlineStr">
         <is>
-          <t>Validasi card file kadaluwarsa dengan data table</t>
+          <t>Validasi card data file aktif dengan data table</t>
         </is>
       </c>
       <c r="E889" s="56" t="inlineStr">
@@ -37711,7 +37711,7 @@
       </c>
       <c r="G889" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
+          <t>Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
         </is>
       </c>
       <c r="H889" s="56" t="inlineStr">
@@ -37723,46 +37723,87 @@
     <row r="890" ht="42" customHeight="1">
       <c r="A890" s="55" t="inlineStr">
         <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="B890" s="56" t="inlineStr">
+        <is>
+          <t>Export data management</t>
+        </is>
+      </c>
+      <c r="C890" s="56" t="inlineStr">
+        <is>
+          <t>Management Export</t>
+        </is>
+      </c>
+      <c r="D890" s="56" t="inlineStr">
+        <is>
+          <t>Validasi card file kadaluwarsa dengan data table</t>
+        </is>
+      </c>
+      <c r="E890" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F890" s="55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G890" s="56" t="inlineStr">
+        <is>
+          <t>Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
+        </is>
+      </c>
+      <c r="H890" s="56" t="inlineStr">
+        <is>
+          <t>Jumlah data pada card dan table sesuai</t>
+        </is>
+      </c>
+    </row>
+    <row r="891" ht="14" customHeight="1">
+      <c r="A891" s="55" t="inlineStr">
+        <is>
           <t>75.4</t>
         </is>
       </c>
-      <c r="B890" s="56" t="inlineStr">
+      <c r="B891" s="56" t="inlineStr">
         <is>
           <t>Export data management</t>
         </is>
       </c>
-      <c r="C890" s="56" t="inlineStr">
+      <c r="C891" s="56" t="inlineStr">
         <is>
           <t>Management Export</t>
         </is>
       </c>
-      <c r="D890" s="56" t="inlineStr">
+      <c r="D891" s="56" t="inlineStr">
         <is>
           <t>Validasi card reject dengan data table</t>
         </is>
       </c>
-      <c r="E890" s="56" t="inlineStr">
-        <is>
-          <t>Positive Case</t>
-        </is>
-      </c>
-      <c r="F890" s="55" t="inlineStr">
+      <c r="E891" s="56" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F891" s="55" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G890" s="56" t="inlineStr">
+      <c r="G891" s="56" t="inlineStr">
         <is>
           <t>Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
         </is>
       </c>
-      <c r="H890" s="56" t="inlineStr">
+      <c r="H891" s="56" t="inlineStr">
         <is>
           <t>Jumlah data pada card dan table sesuai</t>
         </is>
       </c>
     </row>
-    <row r="891" ht="14" customHeight="1"/>
     <row r="892" ht="42" customHeight="1"/>
     <row r="893" ht="42" customHeight="1"/>
     <row r="894" ht="28" customHeight="1"/>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -3783,9 +3783,7 @@
       <c r="F79" s="55" t="inlineStr"/>
       <c r="G79" s="56" t="inlineStr">
         <is>
-          <t>1. Buka menu User Authority.
-2. Klik sub menu User.
-3. Periksa tampilan daftar data User.</t>
+          <t>Buka menu User Authority - Klik sub menu User - Periksa tampilan daftar data User</t>
         </is>
       </c>
       <c r="H79" s="56" t="inlineStr">
@@ -4197,9 +4195,7 @@
       <c r="F89" s="55" t="inlineStr"/>
       <c r="G89" s="56" t="inlineStr">
         <is>
-          <t>1. Buka menu User Authority.
-2. Klik sub menu Group Role.
-3. Periksa tampilan daftar data Group Role.</t>
+          <t>Buka menu User Authority - Klik sub menu Group Role - Periksa tampilan daftar data Group Role</t>
         </is>
       </c>
       <c r="H89" s="56" t="inlineStr">
@@ -4611,9 +4607,7 @@
       <c r="F99" s="55" t="inlineStr"/>
       <c r="G99" s="56" t="inlineStr">
         <is>
-          <t>1. Buka menu User Authority.
-2. Klik sub menu Tipe Karyawan.
-3. Periksa tampilan daftar data Tipe Karyawan.</t>
+          <t>Buka menu User Authority - Klik sub menu Tipe Karyawan - Periksa tampilan daftar data Tipe Karyawan</t>
         </is>
       </c>
       <c r="H99" s="56" t="inlineStr">
@@ -4983,9 +4977,7 @@
       <c r="F108" s="55" t="inlineStr"/>
       <c r="G108" s="56" t="inlineStr">
         <is>
-          <t>1. Buka menu User Authority.
-2. Klik sub menu Hak Akses Role.
-3. Periksa tampilan daftar data Hak Akses Role.</t>
+          <t>Buka menu User Authority - Klik sub menu Hak Akses Role - Periksa tampilan daftar data Hak Akses Role</t>
         </is>
       </c>
       <c r="H108" s="56" t="inlineStr">
@@ -5321,13 +5313,12 @@
       </c>
       <c r="G116" s="56" t="inlineStr">
         <is>
-          <t>1. Klik menu User Authority.
-2. Klik sub menu Keamanan Akun.</t>
+          <t>Klik menu User Authority - Klik sub menu Keamanan Akun</t>
         </is>
       </c>
       <c r="H116" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil Menampilkan daftar data Akun.</t>
+          <t>Berhasil Menampilkan daftar data Akun.</t>
         </is>
       </c>
     </row>
@@ -6204,13 +6195,12 @@
       </c>
       <c r="G137" s="56" t="inlineStr">
         <is>
-          <t>1. Pilih filter Status dan/atau Rentang Tanggal Permintaan.
-2. Klik button Filter.</t>
+          <t>Pilih filter Status dan/atau Rentang Tanggal Permintaan - Klik button Filter</t>
         </is>
       </c>
       <c r="H137" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil Melakukan filter data permintaan reset MFA.</t>
+          <t>Berhasil Melakukan filter data permintaan reset MFA.</t>
         </is>
       </c>
     </row>
@@ -6247,12 +6237,12 @@
       </c>
       <c r="G138" s="56" t="inlineStr">
         <is>
-          <t>1. Klik button Reset Filter.</t>
+          <t>Klik button Reset Filter</t>
         </is>
       </c>
       <c r="H138" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil Mereset filter data permintaan reset MFA.</t>
+          <t>Berhasil Mereset filter data permintaan reset MFA.</t>
         </is>
       </c>
     </row>
@@ -6667,13 +6657,12 @@
       </c>
       <c r="G148" s="56" t="inlineStr">
         <is>
-          <t>1. Pilih filter Status Sesi, Perangkat Terpercaya, dan/atau Rentang Tanggal Aktivitas Terakhir.
-2. Klik button Filter.</t>
+          <t>Pilih filter Status Sesi, Perangkat Terpercaya, dan/atau Rentang Tanggal Aktivitas Terakhir - Klik button Filter</t>
         </is>
       </c>
       <c r="H148" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil Melakukan filter data perangkat &amp; sesi.</t>
+          <t>Berhasil Melakukan filter data perangkat &amp; sesi.</t>
         </is>
       </c>
     </row>
@@ -6710,12 +6699,12 @@
       </c>
       <c r="G149" s="56" t="inlineStr">
         <is>
-          <t>1. Klik button Reset Filter.</t>
+          <t>Klik button Reset Filter</t>
         </is>
       </c>
       <c r="H149" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil Mereset filter data perangkat &amp; sesi.</t>
+          <t>Berhasil Mereset filter data perangkat &amp; sesi.</t>
         </is>
       </c>
     </row>
@@ -7172,13 +7161,12 @@
       </c>
       <c r="G160" s="56" t="inlineStr">
         <is>
-          <t>1. Klik menu Profile Nasabah &amp; Sales.
-2. Klik sub menu Profile Sales.</t>
+          <t>Klik menu Profile Nasabah &amp; Sales - Klik sub menu Profile Sales</t>
         </is>
       </c>
       <c r="H160" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil Menampilkan daftar data Sales.</t>
+          <t>Berhasil Menampilkan daftar data Sales.</t>
         </is>
       </c>
     </row>
@@ -7593,13 +7581,12 @@
       </c>
       <c r="G170" s="56" t="inlineStr">
         <is>
-          <t>1. Klik menu Profile Nasabah &amp; Sales.
-2. Klik sub menu Nasabah Perorangan.</t>
+          <t>Klik menu Profile Nasabah &amp; Sales - Klik sub menu Nasabah Perorangan</t>
         </is>
       </c>
       <c r="H170" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil Menampilkan daftar data Nasabah Perorangan.</t>
+          <t>Berhasil Menampilkan daftar data Nasabah Perorangan.</t>
         </is>
       </c>
     </row>
@@ -8140,13 +8127,12 @@
       </c>
       <c r="G183" s="56" t="inlineStr">
         <is>
-          <t>1. Pada tab Daftar Rekening, input keyword pada field Search.
-2. Klik button Search.</t>
+          <t>Pada tab Daftar Rekening, input keyword pada field Search - Klik button Search</t>
         </is>
       </c>
       <c r="H183" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil Mencari data pada tab Daftar Rekening dengan keyword valid.</t>
+          <t>Berhasil Mencari data pada tab Daftar Rekening dengan keyword valid.</t>
         </is>
       </c>
     </row>
@@ -8183,13 +8169,12 @@
       </c>
       <c r="G184" s="56" t="inlineStr">
         <is>
-          <t>1. Pada tab Daftar Rekening, input keyword yang tidak terdaftar pada field Search.
-2. Klik button Search.</t>
+          <t>Pada tab Daftar Rekening, input keyword yang tidak terdaftar pada field Search - Klik button Search</t>
         </is>
       </c>
       <c r="H184" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil Mencari data pada tab Daftar Rekening dengan keyword tidak valid.</t>
+          <t>Berhasil Mencari data pada tab Daftar Rekening dengan keyword tidak valid.</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8211,12 @@
       </c>
       <c r="G185" s="56" t="inlineStr">
         <is>
-          <t>1. Pada tab Daftar Rekening, klik salah satu Nomor Rekening pada tabel.</t>
+          <t>Pada tab Daftar Rekening, klik salah satu Nomor Rekening pada tabel</t>
         </is>
       </c>
       <c r="H185" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil Melihat detail load saldo rekening.</t>
+          <t>Berhasil Melihat detail load saldo rekening.</t>
         </is>
       </c>
     </row>
@@ -17279,12 +17264,12 @@
       </c>
       <c r="G403" s="56" t="inlineStr">
         <is>
-          <t>1. Klik salah satu card Kantor Wilayah.</t>
+          <t>Klik salah satu card Kantor Wilayah</t>
         </is>
       </c>
       <c r="H403" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil Melihat detail daftar absensi Kantor Wilayah.</t>
+          <t>Berhasil Melihat detail daftar absensi Kantor Wilayah.</t>
         </is>
       </c>
     </row>
@@ -19127,8 +19112,7 @@
       </c>
       <c r="G447" s="56" t="inlineStr">
         <is>
-          <t>1. Klik button Cancel Approval pada data yang berstatus Rejected.
-2. Klik Yes pada pop up konfirmasi.</t>
+          <t>Klik button Cancel Approval pada data yang berstatus Rejected - Klik Yes pada pop up konfirmasi</t>
         </is>
       </c>
       <c r="H447" s="56" t="inlineStr">
@@ -21312,14 +21296,12 @@
       </c>
       <c r="G499" s="56" t="inlineStr">
         <is>
-          <t>1. Klik checkbox pada salah satu data Personnel yang berstatus Tidak Aktif.
-2. Klik toggle Status pada data Personnel tersebut.</t>
+          <t>Klik checkbox pada salah satu data Personnel yang berstatus Tidak Aktif - Klik toggle Status pada data Personnel tersebut</t>
         </is>
       </c>
       <c r="H499" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil mencentang checkbox data Personnel.
-2. Berhasil menambahkan/mengaktifkan personnel ke Attendance Spot secara single.</t>
+          <t>Berhasil mencentang checkbox data Personnel. - Berhasil menambahkan/mengaktifkan personnel ke Attendance Spot secara single.</t>
         </is>
       </c>
     </row>
@@ -21356,14 +21338,12 @@
       </c>
       <c r="G500" s="56" t="inlineStr">
         <is>
-          <t>1. Klik checkbox pada salah satu data Personnel yang berstatus Aktif.
-2. Klik toggle Status pada data Personnel tersebut.</t>
+          <t>Klik checkbox pada salah satu data Personnel yang berstatus Aktif - Klik toggle Status pada data Personnel tersebut</t>
         </is>
       </c>
       <c r="H500" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil mencentang checkbox data Personnel.
-2. Berhasil menghapus/menonaktifkan personnel dari Attendance Spot secara single.</t>
+          <t>Berhasil mencentang checkbox data Personnel. - Berhasil menghapus/menonaktifkan personnel dari Attendance Spot secara single.</t>
         </is>
       </c>
     </row>
@@ -21400,14 +21380,12 @@
       </c>
       <c r="G501" s="56" t="inlineStr">
         <is>
-          <t>1. Klik beberapa checkbox data Personnel yang berstatus Tidak Aktif.
-2. Klik button Add Personnel.</t>
+          <t>Klik beberapa checkbox data Personnel yang berstatus Tidak Aktif - Klik button Add Personnel</t>
         </is>
       </c>
       <c r="H501" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil mencentang beberapa checkbox data Personnel.
-2. Berhasil menambahkan/mengaktifkan seluruh personnel yang dipilih ke Attendance Spot secara bulk.</t>
+          <t>Berhasil mencentang beberapa checkbox data Personnel. - Berhasil menambahkan/mengaktifkan seluruh personnel yang dipilih ke Attendance Spot secara bulk.</t>
         </is>
       </c>
     </row>
@@ -21444,14 +21422,12 @@
       </c>
       <c r="G502" s="56" t="inlineStr">
         <is>
-          <t>1. Klik beberapa checkbox data Personnel yang berstatus Aktif.
-2. Klik button Remove Personnel.</t>
+          <t>Klik beberapa checkbox data Personnel yang berstatus Aktif - Klik button Remove Personnel</t>
         </is>
       </c>
       <c r="H502" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil mencentang beberapa checkbox data Personnel.
-2. Berhasil menghapus/menonaktifkan seluruh personnel yang dipilih dari Attendance Spot secara bulk.</t>
+          <t>Berhasil mencentang beberapa checkbox data Personnel. - Berhasil menghapus/menonaktifkan seluruh personnel yang dipilih dari Attendance Spot secara bulk.</t>
         </is>
       </c>
     </row>
@@ -21992,14 +21968,12 @@
       </c>
       <c r="G515" s="56" t="inlineStr">
         <is>
-          <t>1. Pilih data pada salah satu dropdown filter (Kantor Wilayah, Kantor Cabang, dll).
-2. Klik button Filter.</t>
+          <t>Pilih data pada salah satu dropdown filter (Kantor Wilayah, Kantor Cabang, dll) - Klik button Filter</t>
         </is>
       </c>
       <c r="H515" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil memilih data filter.
-2. Berhasil menampilkan data Personnel sesuai filter yang dipilih.</t>
+          <t>Berhasil memilih data filter. - Berhasil menampilkan data Personnel sesuai filter yang dipilih.</t>
         </is>
       </c>
     </row>
@@ -22036,14 +22010,12 @@
       </c>
       <c r="G516" s="56" t="inlineStr">
         <is>
-          <t>1. Input keyword pada field Search di halaman Personnel.
-2. Klik button Search.</t>
+          <t>Input keyword pada field Search di halaman Personnel - Klik button Search</t>
         </is>
       </c>
       <c r="H516" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil menginput keyword.
-2. Berhasil menampilkan data Personnel sesuai keyword.</t>
+          <t>Berhasil menginput keyword. - Berhasil menampilkan data Personnel sesuai keyword.</t>
         </is>
       </c>
     </row>
@@ -22080,14 +22052,12 @@
       </c>
       <c r="G517" s="56" t="inlineStr">
         <is>
-          <t>1. Input keyword yang tidak terdaftar pada field Search di halaman Personnel.
-2. Klik button Search.</t>
+          <t>Input keyword yang tidak terdaftar pada field Search di halaman Personnel - Klik button Search</t>
         </is>
       </c>
       <c r="H517" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil menginput keyword.
-2. Berhasil menampilkan informasi data tidak ditemukan.</t>
+          <t>Berhasil menginput keyword. - Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
     </row>
@@ -22208,14 +22178,12 @@
       </c>
       <c r="G520" s="56" t="inlineStr">
         <is>
-          <t>1. Klik checkbox pada salah satu data Personnel yang sudah ter-assign.
-2. Klik icon Unassign (merah).</t>
+          <t>Klik checkbox pada salah satu data Personnel yang sudah ter-assign - Klik icon Unassign (merah)</t>
         </is>
       </c>
       <c r="H520" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil mencentang checkbox data Personnel.
-2. Berhasil menghapus (unassign) personnel tersebut dari Work Pattern.</t>
+          <t>Berhasil mencentang checkbox data Personnel. - Berhasil menghapus (unassign) personnel tersebut dari Work Pattern.</t>
         </is>
       </c>
     </row>
@@ -22252,14 +22220,12 @@
       </c>
       <c r="G521" s="56" t="inlineStr">
         <is>
-          <t>1. Klik beberapa checkbox data Personnel yang sudah ter-assign.
-2. Klik icon Unassign (merah).</t>
+          <t>Klik beberapa checkbox data Personnel yang sudah ter-assign - Klik icon Unassign (merah)</t>
         </is>
       </c>
       <c r="H521" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil mencentang beberapa checkbox data Personnel.
-2. Berhasil menghapus (unassign) seluruh personnel yang dipilih secara bulk dari Work Pattern.</t>
+          <t>Berhasil mencentang beberapa checkbox data Personnel. - Berhasil menghapus (unassign) seluruh personnel yang dipilih secara bulk dari Work Pattern.</t>
         </is>
       </c>
     </row>
@@ -22338,13 +22304,12 @@
       </c>
       <c r="G523" s="56" t="inlineStr">
         <is>
-          <t>1. Klik menu Setting Absent.
-2. Klik sub menu Holiday.</t>
+          <t>Klik menu Setting Absent - Klik sub menu Holiday</t>
         </is>
       </c>
       <c r="H523" s="56" t="inlineStr">
         <is>
-          <t>1. Berhasil Menampilkan daftar data Holiday.</t>
+          <t>Berhasil Menampilkan daftar data Holiday.</t>
         </is>
       </c>
     </row>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -42887,7 +42887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA222"/>
+  <dimension ref="A1:AA233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55592,6 +55592,424 @@
       <c r="Z222" s="49" t="n"/>
       <c r="AA222" s="49" t="n"/>
     </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="B223" s="46" t="inlineStr">
+        <is>
+          <t>Kunjungan</t>
+        </is>
+      </c>
+      <c r="C223" s="46" t="n"/>
+      <c r="D223" s="48" t="inlineStr">
+        <is>
+          <t>Membuka halaman Kunjungan</t>
+        </is>
+      </c>
+      <c r="E223" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F223" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G223" s="48" t="inlineStr">
+        <is>
+          <t>Buka menu Lainnya - Klik menu Kunjungan</t>
+        </is>
+      </c>
+      <c r="H223" s="48" t="inlineStr">
+        <is>
+          <t>Berhasil menampilkan halaman Kunjungan beserta informasi Periode, ringkasan Realisasi &amp; Target Visit, serta daftar riwayat kunjungan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="B224" s="46" t="inlineStr">
+        <is>
+          <t>Kunjungan</t>
+        </is>
+      </c>
+      <c r="C224" s="46" t="n"/>
+      <c r="D224" s="48" t="inlineStr">
+        <is>
+          <t>Melakukan filter periode tanggal kunjungan</t>
+        </is>
+      </c>
+      <c r="E224" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F224" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G224" s="48" t="inlineStr">
+        <is>
+          <t>Klik dropdown Periode - Pilih rentang tanggal pada kalender (Pilih rentang) - Klik button Simpan</t>
+        </is>
+      </c>
+      <c r="H224" s="48" t="inlineStr">
+        <is>
+          <t>Berhasil memfilter dan menampilkan daftar data kunjungan sesuai rentang periode tanggal yang dipilih.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="B225" s="46" t="inlineStr">
+        <is>
+          <t>Kunjungan</t>
+        </is>
+      </c>
+      <c r="C225" s="46" t="n"/>
+      <c r="D225" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail kunjungan</t>
+        </is>
+      </c>
+      <c r="E225" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F225" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G225" s="48" t="inlineStr">
+        <is>
+          <t>Klik salah satu card kunjungan pada daftar - Sistem menampilkan tab default Mulai Kunjungan - Klik tab Selesai Kunjungan</t>
+        </is>
+      </c>
+      <c r="H225" s="48" t="inlineStr">
+        <is>
+          <t>Berhasil menampilkan halaman Detail Kunjungan yang memuat peta lokasi, waktu, tipe kunjungan, dan nama nasabah pada tab Mulai Kunjungan maupun Selesai Kunjungan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="B226" s="46" t="inlineStr">
+        <is>
+          <t>Notifikasi</t>
+        </is>
+      </c>
+      <c r="C226" s="46" t="n"/>
+      <c r="D226" s="48" t="inlineStr">
+        <is>
+          <t>Membuka halaman Notifikasi</t>
+        </is>
+      </c>
+      <c r="E226" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F226" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G226" s="48" t="inlineStr">
+        <is>
+          <t>Buka aplikasi BTN Smart - Masuk ke Beranda - Klik icon Lonceng (Notifikasi)</t>
+        </is>
+      </c>
+      <c r="H226" s="48" t="inlineStr">
+        <is>
+          <t>Berhasil menampilkan halaman Notifikasi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="B227" s="46" t="inlineStr">
+        <is>
+          <t>Notifikasi</t>
+        </is>
+      </c>
+      <c r="C227" s="46" t="n"/>
+      <c r="D227" s="48" t="inlineStr">
+        <is>
+          <t>Mencari notifikasi dengan kata kunci valid</t>
+        </is>
+      </c>
+      <c r="E227" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F227" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G227" s="48" t="inlineStr">
+        <is>
+          <t>Masukkan kata kunci valid pada Search Bar</t>
+        </is>
+      </c>
+      <c r="H227" s="48" t="inlineStr">
+        <is>
+          <t>Berhasil menampilkan data notifikasi yang dicari.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="B228" s="46" t="inlineStr">
+        <is>
+          <t>Notifikasi</t>
+        </is>
+      </c>
+      <c r="C228" s="46" t="n"/>
+      <c r="D228" s="48" t="inlineStr">
+        <is>
+          <t>Mencari notifikasi dengan kata kunci tidak valid</t>
+        </is>
+      </c>
+      <c r="E228" s="46" t="inlineStr">
+        <is>
+          <t>Negative Case</t>
+        </is>
+      </c>
+      <c r="F228" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G228" s="48" t="inlineStr">
+        <is>
+          <t>Masukkan kata kunci tidak valid pada Search Bar</t>
+        </is>
+      </c>
+      <c r="H228" s="48" t="inlineStr">
+        <is>
+          <t>Berhasil menampilkan informasi data tidak ditemukan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="B229" s="46" t="inlineStr">
+        <is>
+          <t>Notifikasi</t>
+        </is>
+      </c>
+      <c r="C229" s="46" t="n"/>
+      <c r="D229" s="48" t="inlineStr">
+        <is>
+          <t>Melihat data notifikasi Belum Dibaca</t>
+        </is>
+      </c>
+      <c r="E229" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F229" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G229" s="48" t="inlineStr">
+        <is>
+          <t>Pada halaman Notifikasi, klik tab Belum Dibaca</t>
+        </is>
+      </c>
+      <c r="H229" s="48" t="inlineStr">
+        <is>
+          <t>Berhasil menampilkan data notifikasi belum dibaca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="B230" s="46" t="inlineStr">
+        <is>
+          <t>Notifikasi</t>
+        </is>
+      </c>
+      <c r="C230" s="46" t="n"/>
+      <c r="D230" s="48" t="inlineStr">
+        <is>
+          <t>Melihat data notifikasi Diarsipkan</t>
+        </is>
+      </c>
+      <c r="E230" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F230" s="46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G230" s="48" t="inlineStr">
+        <is>
+          <t>Pada halaman Notifikasi, klik tab Diarsipkan</t>
+        </is>
+      </c>
+      <c r="H230" s="48" t="inlineStr">
+        <is>
+          <t>Berhasil menampilkan data notifikasi diarsipkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="B231" s="46" t="inlineStr">
+        <is>
+          <t>Notifikasi</t>
+        </is>
+      </c>
+      <c r="C231" s="46" t="n"/>
+      <c r="D231" s="48" t="inlineStr">
+        <is>
+          <t>Melihat detail notifikasi</t>
+        </is>
+      </c>
+      <c r="E231" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F231" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G231" s="48" t="inlineStr">
+        <is>
+          <t>Pada halaman Notifikasi, klik salah satu notifikasi</t>
+        </is>
+      </c>
+      <c r="H231" s="48" t="inlineStr">
+        <is>
+          <t>Berhasil menampilkan detail notifikasi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="B232" s="46" t="inlineStr">
+        <is>
+          <t>Notifikasi</t>
+        </is>
+      </c>
+      <c r="C232" s="46" t="n"/>
+      <c r="D232" s="48" t="inlineStr">
+        <is>
+          <t>Mengarsipkan notifikasi</t>
+        </is>
+      </c>
+      <c r="E232" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F232" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G232" s="48" t="inlineStr">
+        <is>
+          <t>Pada halaman Detail Notifikasi, klik icon Arsipkan</t>
+        </is>
+      </c>
+      <c r="H232" s="48" t="inlineStr">
+        <is>
+          <t>Berhasil mengarsipkan notifikasi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="B233" s="46" t="inlineStr">
+        <is>
+          <t>Notifikasi</t>
+        </is>
+      </c>
+      <c r="C233" s="46" t="n"/>
+      <c r="D233" s="48" t="inlineStr">
+        <is>
+          <t>Membatalkan arsip notifikasi</t>
+        </is>
+      </c>
+      <c r="E233" s="46" t="inlineStr">
+        <is>
+          <t>Positive Case</t>
+        </is>
+      </c>
+      <c r="F233" s="46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G233" s="48" t="inlineStr">
+        <is>
+          <t>Pada detail notifikasi di tab Diarsipkan, klik icon Buka Arsip</t>
+        </is>
+      </c>
+      <c r="H233" s="48" t="inlineStr">
+        <is>
+          <t>Berhasil membatalkan arsip notifikasi.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -36727,17 +36727,17 @@
       </c>
       <c r="B867" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C867" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Riwayat Export</t>
         </is>
       </c>
       <c r="D867" s="56" t="inlineStr">
         <is>
-          <t>Membuka menu riwayat export saya</t>
+          <t>Membuka halaman Riwayat Export</t>
         </is>
       </c>
       <c r="E867" s="56" t="inlineStr">
@@ -36752,12 +36752,12 @@
       </c>
       <c r="G867" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Export Center, klik submenu Riwayat export</t>
+          <t>Klik menu Export Center - Klik submenu Riwayat Export</t>
         </is>
       </c>
       <c r="H867" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman Riwayat export</t>
+          <t>Berhasil menampilkan halaman Riwayat Export.</t>
         </is>
       </c>
     </row>
@@ -36769,17 +36769,17 @@
       </c>
       <c r="B868" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C868" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Riwayat Export</t>
         </is>
       </c>
       <c r="D868" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data riwayat export dengan kata kunci valid</t>
         </is>
       </c>
       <c r="E868" s="56" t="inlineStr">
@@ -36794,12 +36794,12 @@
       </c>
       <c r="G868" s="56" t="inlineStr">
         <is>
-          <t>Klik button filter – pilih modul, export status, dan tentan tanggal request – kemudian klik terapkan filter</t>
+          <t>Masukkan kata kunci valid pada Search Bar - Klik button Cari</t>
         </is>
       </c>
       <c r="H868" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai filter yang dipilih</t>
+          <t>Berhasil menampilkan data riwayat export yang dicari.</t>
         </is>
       </c>
     </row>
@@ -36811,37 +36811,37 @@
       </c>
       <c r="B869" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C869" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Riwayat Export</t>
         </is>
       </c>
       <c r="D869" s="56" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Mencari data riwayat export dengan kata kunci tidak valid</t>
         </is>
       </c>
       <c r="E869" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F869" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G869" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data dengan memilih status approval 'pending' dan status export 'Generate'</t>
+          <t>Masukkan kata kunci tidak valid pada Search Bar - Klik button Cari</t>
         </is>
       </c>
       <c r="H869" s="56" t="inlineStr">
         <is>
-          <t>Berhasil Jumlah data pada card dan table sesuai</t>
+          <t>Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
     </row>
@@ -36853,17 +36853,17 @@
       </c>
       <c r="B870" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C870" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Riwayat Export</t>
         </is>
       </c>
       <c r="D870" s="56" t="inlineStr">
         <is>
-          <t>Validasi card disetujui dengan data table</t>
+          <t>Melihat data riwayat export berdasarkan status</t>
         </is>
       </c>
       <c r="E870" s="56" t="inlineStr">
@@ -36873,17 +36873,17 @@
       </c>
       <c r="F870" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G870" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data status approval dengan memilih status 'Approved'</t>
+          <t>Pada halaman Riwayat Export, klik salah satu tab status</t>
         </is>
       </c>
       <c r="H870" s="56" t="inlineStr">
         <is>
-          <t>Berhasil Jumlah data pada card dan table sesuai</t>
+          <t>Berhasil menampilkan daftar data riwayat export sesuai status yang dipilih.</t>
         </is>
       </c>
     </row>
@@ -36895,17 +36895,17 @@
       </c>
       <c r="B871" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C871" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Riwayat Export</t>
         </is>
       </c>
       <c r="D871" s="56" t="inlineStr">
         <is>
-          <t>Validasi card ditolak dengan data table</t>
+          <t>Melakukan filter data riwayat export</t>
         </is>
       </c>
       <c r="E871" s="56" t="inlineStr">
@@ -36915,17 +36915,17 @@
       </c>
       <c r="F871" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G871" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data status approval dengan memilih status 'Rejected'</t>
+          <t>Klik button Filter - Pilih kriteria filter pada drawer - Klik button Terapkan Filter</t>
         </is>
       </c>
       <c r="H871" s="56" t="inlineStr">
         <is>
-          <t>Berhasil Jumlah data pada card dan table sesuai</t>
+          <t>Berhasil memfilter dan menampilkan data riwayat export sesuai kriteria filter.</t>
         </is>
       </c>
     </row>
@@ -36937,17 +36937,17 @@
       </c>
       <c r="B872" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C872" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Riwayat Export</t>
         </is>
       </c>
       <c r="D872" s="56" t="inlineStr">
         <is>
-          <t>Validasi card kadaluwarsa dengan data table</t>
+          <t>Mereset filter data riwayat export</t>
         </is>
       </c>
       <c r="E872" s="56" t="inlineStr">
@@ -36962,12 +36962,12 @@
       </c>
       <c r="G872" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data status approval dengan memilih status 'Expired'</t>
+          <t>Klik button Filter - Klik button Reset pada drawer Filter</t>
         </is>
       </c>
       <c r="H872" s="56" t="inlineStr">
         <is>
-          <t>Berhasil Jumlah data pada card dan table sesuai</t>
+          <t>Berhasil mereset filter dan menampilkan seluruh data riwayat export.</t>
         </is>
       </c>
     </row>
@@ -36979,17 +36979,17 @@
       </c>
       <c r="B873" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C873" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Riwayat Export</t>
         </is>
       </c>
       <c r="D873" s="56" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Melihat detail riwayat export</t>
         </is>
       </c>
       <c r="E873" s="56" t="inlineStr">
@@ -37004,12 +37004,12 @@
       </c>
       <c r="G873" s="56" t="inlineStr">
         <is>
-          <t>Input data pada kolom pencarian</t>
+          <t>Klik icon Aksi (...) pada salah satu baris data - Klik opsi Detail</t>
         </is>
       </c>
       <c r="H873" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai kata kunci</t>
+          <t>Berhasil menampilkan drawer Export Detail.</t>
         </is>
       </c>
     </row>
@@ -37021,22 +37021,22 @@
       </c>
       <c r="B874" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C874" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Riwayat Export</t>
         </is>
       </c>
       <c r="D874" s="56" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Mengunduh file data export yang tersedia</t>
         </is>
       </c>
       <c r="E874" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F874" s="55" t="inlineStr">
@@ -37046,34 +37046,34 @@
       </c>
       <c r="G874" s="56" t="inlineStr">
         <is>
-          <t>Input data yang belum terdaftar</t>
+          <t>Klik icon Aksi (...) pada baris data dengan status Tersedia - Klik opsi Download</t>
         </is>
       </c>
       <c r="H874" s="56" t="inlineStr">
         <is>
-          <t>Data tidak ditemukan</t>
+          <t>Berhasil mengunduh file data export.</t>
         </is>
       </c>
     </row>
     <row r="875" ht="70" customHeight="1">
       <c r="A875" s="55" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="B875" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C875" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Persetujuan Export</t>
         </is>
       </c>
       <c r="D875" s="56" t="inlineStr">
         <is>
-          <t>Mengunduh data yang sudah di approve</t>
+          <t>Membuka halaman Persetujuan Export</t>
         </is>
       </c>
       <c r="E875" s="56" t="inlineStr">
@@ -37088,34 +37088,34 @@
       </c>
       <c r="G875" s="56" t="inlineStr">
         <is>
-          <t>Klik button download</t>
+          <t>Klik menu Export Center - Klik submenu Persetujuan Export</t>
         </is>
       </c>
       <c r="H875" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mengunduh data</t>
+          <t>Berhasil menampilkan halaman Persetujuan Export.</t>
         </is>
       </c>
     </row>
     <row r="876" ht="28" customHeight="1">
       <c r="A876" s="55" t="inlineStr">
         <is>
-          <t>73.10</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="B876" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C876" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Persetujuan Export</t>
         </is>
       </c>
       <c r="D876" s="56" t="inlineStr">
         <is>
-          <t>Membuka dokumen hasil download</t>
+          <t>Mencari data persetujuan export dengan kata kunci valid</t>
         </is>
       </c>
       <c r="E876" s="56" t="inlineStr">
@@ -37125,44 +37125,44 @@
       </c>
       <c r="F876" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G876" s="56" t="inlineStr">
         <is>
-          <t>Extract file, kemudian masukan password yang terkirim pada email user yang mengajukan, input password maka file berhasil di extract, kemudian buka file</t>
+          <t>Masukkan kata kunci valid pada Search Bar - Klik button Cari</t>
         </is>
       </c>
       <c r="H876" s="56" t="inlineStr">
         <is>
-          <t>Berhasil membuka file hasil download</t>
+          <t>Berhasil menampilkan data persetujuan export yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="877" ht="42" customHeight="1">
       <c r="A877" s="55" t="inlineStr">
         <is>
-          <t>73.11</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="B877" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C877" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Persetujuan Export</t>
         </is>
       </c>
       <c r="D877" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mencari data persetujuan export dengan kata kunci tidak valid</t>
         </is>
       </c>
       <c r="E877" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F877" s="55" t="inlineStr">
@@ -37172,34 +37172,34 @@
       </c>
       <c r="G877" s="56" t="inlineStr">
         <is>
-          <t>Klik button filter – pilih modul, export status, dan tentan tanggal request – kemudian klik terapkan filter</t>
+          <t>Masukkan kata kunci tidak valid pada Search Bar - Klik button Cari</t>
         </is>
       </c>
       <c r="H877" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai filter yang dipilih</t>
+          <t>Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="878" ht="28" customHeight="1">
       <c r="A878" s="55" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="B878" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C878" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Persetujuan Export</t>
         </is>
       </c>
       <c r="D878" s="56" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Melihat data persetujuan export berdasarkan status</t>
         </is>
       </c>
       <c r="E878" s="56" t="inlineStr">
@@ -37209,81 +37209,81 @@
       </c>
       <c r="F878" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G878" s="56" t="inlineStr">
         <is>
-          <t>Input data pada kolom pencarian</t>
+          <t>Pada halaman Persetujuan Export, klik salah satu tab status</t>
         </is>
       </c>
       <c r="H878" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai kata kunci</t>
+          <t>Berhasil menampilkan daftar data persetujuan export sesuai status yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="879" ht="28" customHeight="1">
       <c r="A879" s="55" t="inlineStr">
         <is>
-          <t>73.13</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="B879" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C879" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Persetujuan Export</t>
         </is>
       </c>
       <c r="D879" s="56" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Melakukan filter data persetujuan export</t>
         </is>
       </c>
       <c r="E879" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F879" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G879" s="56" t="inlineStr">
         <is>
-          <t>Input data yang belum terdaftar</t>
+          <t>Klik button Filter - Pilih kriteria filter pada drawer - Klik button Terapkan Filter</t>
         </is>
       </c>
       <c r="H879" s="56" t="inlineStr">
         <is>
-          <t>Data tidak ditemukan</t>
+          <t>Berhasil memfilter dan menampilkan data persetujuan export sesuai kriteria filter.</t>
         </is>
       </c>
     </row>
     <row r="880" ht="28" customHeight="1">
       <c r="A880" s="55" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="B880" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C880" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Persetujuan Export</t>
         </is>
       </c>
       <c r="D880" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data</t>
+          <t>Mereset filter data persetujuan export</t>
         </is>
       </c>
       <c r="E880" s="56" t="inlineStr">
@@ -37298,34 +37298,34 @@
       </c>
       <c r="G880" s="56" t="inlineStr">
         <is>
-          <t>Klik button filter – pilih modul, export status, dan tentan tanggal request – kemudian klik terapkan filter</t>
+          <t>Klik button Filter - Klik button Reset pada drawer Filter</t>
         </is>
       </c>
       <c r="H880" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai filter yang dipilih</t>
+          <t>Berhasil mereset filter dan menampilkan seluruh data persetujuan export.</t>
         </is>
       </c>
     </row>
     <row r="881" ht="14" customHeight="1">
       <c r="A881" s="55" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="B881" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C881" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Persetujuan Export</t>
         </is>
       </c>
       <c r="D881" s="56" t="inlineStr">
         <is>
-          <t>Mencari data pada kolom pencarian</t>
+          <t>Melakukan approval data pengajuan export</t>
         </is>
       </c>
       <c r="E881" s="56" t="inlineStr">
@@ -37340,39 +37340,39 @@
       </c>
       <c r="G881" s="56" t="inlineStr">
         <is>
-          <t>Input data pada kolom pencarian</t>
+          <t>Klik icon Aksi (...) pada data status Menunggu - Pilih opsi Setujui - Klik button Setujui pada modal konfirmasi</t>
         </is>
       </c>
       <c r="H881" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data sesuai kata kunci</t>
+          <t>Berhasil menyetujui pengajuan export dan status berubah menjadi Disetujui.</t>
         </is>
       </c>
     </row>
     <row r="882" ht="42" customHeight="1">
       <c r="A882" s="55" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="B882" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C882" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Persetujuan Export</t>
         </is>
       </c>
       <c r="D882" s="56" t="inlineStr">
         <is>
-          <t>Mencari data kata kunci salah</t>
+          <t>Melakukan reject data pengajuan export</t>
         </is>
       </c>
       <c r="E882" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F882" s="55" t="inlineStr">
@@ -37382,34 +37382,34 @@
       </c>
       <c r="G882" s="56" t="inlineStr">
         <is>
-          <t>Input data yang belum terdaftar</t>
+          <t>Klik icon Aksi (...) pada data status Menunggu - Pilih opsi Tolak - Masukkan alasan pada field Alasan Penolakan - Klik button Tolak</t>
         </is>
       </c>
       <c r="H882" s="56" t="inlineStr">
         <is>
-          <t>Data tidak ditemukan</t>
+          <t>Berhasil menolak pengajuan export dan status berubah menjadi Ditolak.</t>
         </is>
       </c>
     </row>
     <row r="883" ht="42" customHeight="1">
       <c r="A883" s="55" t="inlineStr">
         <is>
-          <t>73.17</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="B883" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C883" s="56" t="inlineStr">
         <is>
-          <t>Riwayat export saya</t>
+          <t>Persetujuan Export</t>
         </is>
       </c>
       <c r="D883" s="56" t="inlineStr">
         <is>
-          <t>Validasi card menunggu approval dengan data table</t>
+          <t>Melihat detail pengajuan export</t>
         </is>
       </c>
       <c r="E883" s="56" t="inlineStr">
@@ -37419,39 +37419,39 @@
       </c>
       <c r="F883" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G883" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data dengan memilih status approval 'pending' dan status export 'Generate'</t>
+          <t>Klik icon Aksi (...) pada salah satu baris data - Klik opsi Detail</t>
         </is>
       </c>
       <c r="H883" s="56" t="inlineStr">
         <is>
-          <t>Berhasil Jumlah data pada card dan table sesuai</t>
+          <t>Berhasil menampilkan detail data pengajuan export.</t>
         </is>
       </c>
     </row>
     <row r="884" ht="28" customHeight="1">
       <c r="A884" s="55" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="B884" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C884" s="56" t="inlineStr">
         <is>
-          <t>Persetujuan Export</t>
+          <t>Aktivitas Export</t>
         </is>
       </c>
       <c r="D884" s="56" t="inlineStr">
         <is>
-          <t>Lakukan login menggunakan user monitoring</t>
+          <t>Membuka halaman Aktivitas Export</t>
         </is>
       </c>
       <c r="E884" s="56" t="inlineStr">
@@ -37461,39 +37461,39 @@
       </c>
       <c r="F884" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G884" s="56" t="inlineStr">
         <is>
-          <t>Login menggunakan user monitoring</t>
+          <t>Klik menu Export Center - Klik submenu Aktivitas Export</t>
         </is>
       </c>
       <c r="H884" s="56" t="inlineStr">
         <is>
-          <t>Berhasil melakukan login</t>
+          <t>Berhasil menampilkan halaman Aktivitas Export.</t>
         </is>
       </c>
     </row>
     <row r="885" ht="42" customHeight="1">
       <c r="A885" s="55" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="B885" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C885" s="56" t="inlineStr">
         <is>
-          <t>Persetujuan Export</t>
+          <t>Aktivitas Export</t>
         </is>
       </c>
       <c r="D885" s="56" t="inlineStr">
         <is>
-          <t>Membuka menu Persetujuan Export</t>
+          <t>Mencari data aktivitas export dengan kata kunci valid</t>
         </is>
       </c>
       <c r="E885" s="56" t="inlineStr">
@@ -37503,81 +37503,81 @@
       </c>
       <c r="F885" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G885" s="56" t="inlineStr">
         <is>
-          <t>Klik menu exported data management, klik submenu persetujuan export</t>
+          <t>Masukkan kata kunci valid pada Search Bar - Klik button Cari</t>
         </is>
       </c>
       <c r="H885" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman persetujuan export</t>
+          <t>Berhasil menampilkan data aktivitas export yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="886" ht="14" customHeight="1">
       <c r="A886" s="55" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="B886" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C886" s="56" t="inlineStr">
         <is>
-          <t>Persetujuan Export</t>
+          <t>Aktivitas Export</t>
         </is>
       </c>
       <c r="D886" s="56" t="inlineStr">
         <is>
-          <t>Melakukan approval data pengajuan export</t>
+          <t>Mencari data aktivitas export dengan kata kunci tidak valid</t>
         </is>
       </c>
       <c r="E886" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F886" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G886" s="56" t="inlineStr">
         <is>
-          <t>Klik icon titik tiga pada data pengajuan - Klik menu Setuju - Klik button YA pada popup konfirmasi</t>
+          <t>Masukkan kata kunci tidak valid pada Search Bar - Klik button Cari</t>
         </is>
       </c>
       <c r="H886" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menyetujui data pengajuan export.</t>
+          <t>Berhasil menampilkan informasi data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="887" ht="42" customHeight="1">
       <c r="A887" s="55" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="B887" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C887" s="56" t="inlineStr">
         <is>
-          <t>Persetujuan Export</t>
+          <t>Aktivitas Export</t>
         </is>
       </c>
       <c r="D887" s="56" t="inlineStr">
         <is>
-          <t>Melakukan reject data pengajuan export</t>
+          <t>Melihat data aktivitas export berdasarkan status</t>
         </is>
       </c>
       <c r="E887" s="56" t="inlineStr">
@@ -37587,39 +37587,39 @@
       </c>
       <c r="F887" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G887" s="56" t="inlineStr">
         <is>
-          <t>Klik icon (titik tiga) klik tolak, input alasan, klik submit</t>
+          <t>Pada halaman Aktivitas Export, klik salah satu tab status</t>
         </is>
       </c>
       <c r="H887" s="56" t="inlineStr">
         <is>
-          <t>Berhasil melakukan reject data</t>
+          <t>Berhasil menampilkan daftar data aktivitas export sesuai status yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="888" ht="42" customHeight="1">
       <c r="A888" s="55" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="B888" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C888" s="56" t="inlineStr">
         <is>
-          <t>Management Export</t>
+          <t>Aktivitas Export</t>
         </is>
       </c>
       <c r="D888" s="56" t="inlineStr">
         <is>
-          <t>Membuka menu Management Export</t>
+          <t>Melakukan filter data aktivitas export</t>
         </is>
       </c>
       <c r="E888" s="56" t="inlineStr">
@@ -37629,39 +37629,39 @@
       </c>
       <c r="F888" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G888" s="56" t="inlineStr">
         <is>
-          <t>Klik menu exported data management, klik submenu management export</t>
+          <t>Klik button Filter - Pilih kriteria filter pada drawer - Klik button Terapkan Filter</t>
         </is>
       </c>
       <c r="H888" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan halaman management export</t>
+          <t>Berhasil memfilter dan menampilkan data aktivitas export sesuai kriteria filter.</t>
         </is>
       </c>
     </row>
     <row r="889" ht="28" customHeight="1">
       <c r="A889" s="55" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="B889" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C889" s="56" t="inlineStr">
         <is>
-          <t>Management Export</t>
+          <t>Aktivitas Export</t>
         </is>
       </c>
       <c r="D889" s="56" t="inlineStr">
         <is>
-          <t>Validasi card data file aktif dengan data table</t>
+          <t>Mereset filter data aktivitas export</t>
         </is>
       </c>
       <c r="E889" s="56" t="inlineStr">
@@ -37676,34 +37676,34 @@
       </c>
       <c r="G889" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data dengan memilih status approvalnya “Approved” dan status exportnya “Generate” dengan tanggal sebelum hari berjalan</t>
+          <t>Klik button Filter - Klik button Reset pada drawer Filter</t>
         </is>
       </c>
       <c r="H889" s="56" t="inlineStr">
         <is>
-          <t>Jumlah data pada card dan table sesuai</t>
+          <t>Berhasil mereset filter dan menampilkan seluruh data aktivitas export.</t>
         </is>
       </c>
     </row>
     <row r="890" ht="42" customHeight="1">
       <c r="A890" s="55" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="B890" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C890" s="56" t="inlineStr">
         <is>
-          <t>Management Export</t>
+          <t>Aktivitas Export</t>
         </is>
       </c>
       <c r="D890" s="56" t="inlineStr">
         <is>
-          <t>Validasi card file kadaluwarsa dengan data table</t>
+          <t>Melihat detail aktivitas export</t>
         </is>
       </c>
       <c r="E890" s="56" t="inlineStr">
@@ -37713,39 +37713,39 @@
       </c>
       <c r="F890" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G890" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data dengan memilih status approvalnya “approve” dan status exportnya “generate” dengan tanggal sesudah hari berjalan</t>
+          <t>Klik icon Aksi (...) pada salah satu baris data - Klik opsi Detail</t>
         </is>
       </c>
       <c r="H890" s="56" t="inlineStr">
         <is>
-          <t>Jumlah data pada card dan table sesuai</t>
+          <t>Berhasil menampilkan detail data aktivitas export.</t>
         </is>
       </c>
     </row>
     <row r="891" ht="14" customHeight="1">
       <c r="A891" s="55" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="B891" s="56" t="inlineStr">
         <is>
-          <t>Export data management</t>
+          <t>Export Center</t>
         </is>
       </c>
       <c r="C891" s="56" t="inlineStr">
         <is>
-          <t>Management Export</t>
+          <t>Aktivitas Export</t>
         </is>
       </c>
       <c r="D891" s="56" t="inlineStr">
         <is>
-          <t>Validasi card reject dengan data table</t>
+          <t>Mengunduh file data export yang tersedia</t>
         </is>
       </c>
       <c r="E891" s="56" t="inlineStr">
@@ -37760,12 +37760,12 @@
       </c>
       <c r="G891" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data dengan memilih status approvalnya “reject” dan status exportnya “generate”</t>
+          <t>Klik icon Aksi (...) pada data dengan status Tersedia - Klik opsi Download</t>
         </is>
       </c>
       <c r="H891" s="56" t="inlineStr">
         <is>
-          <t>Jumlah data pada card dan table sesuai</t>
+          <t>Berhasil mengunduh file data export.</t>
         </is>
       </c>
     </row>

--- a/SIT/Test Case.xlsx
+++ b/SIT/Test Case.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z891"/>
+  <dimension ref="A1:Z899"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="12.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -31435,17 +31435,13 @@
       </c>
       <c r="B741" s="56" t="inlineStr">
         <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C741" s="56" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C741" s="56" t="n"/>
       <c r="D741" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Personal Funnel</t>
+          <t>Membuka halaman Kalender</t>
         </is>
       </c>
       <c r="E741" s="56" t="inlineStr">
@@ -31460,12 +31456,12 @@
       </c>
       <c r="G741" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Funding - Klik sub menu Personal Funnel</t>
+          <t>Masuk ke menu utama - Klik menu Kalender pada sidebar</t>
         </is>
       </c>
       <c r="H741" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Personal Funnel.</t>
+          <t>Berhasil menampilkan halaman Kalender beserta ringkasan status dan grid kalender.</t>
         </is>
       </c>
     </row>
@@ -31477,17 +31473,13 @@
       </c>
       <c r="B742" s="56" t="inlineStr">
         <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C742" s="56" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C742" s="56" t="n"/>
       <c r="D742" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Personal Funnel</t>
+          <t>Melakukan navigasi periode kalender</t>
         </is>
       </c>
       <c r="E742" s="56" t="inlineStr">
@@ -31502,12 +31494,12 @@
       </c>
       <c r="G742" s="56" t="inlineStr">
         <is>
-          <t>Mengisi semua field filter mandatory - Klik button Submit</t>
+          <t>Pada halaman Kalender, klik tombol navigasi panah (&lt; / &gt;) atau tombol Hari ini</t>
         </is>
       </c>
       <c r="H742" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+          <t>Berhasil mengubah tampilan periode kalender sesuai pilihan.</t>
         </is>
       </c>
     </row>
@@ -31519,17 +31511,13 @@
       </c>
       <c r="B743" s="56" t="inlineStr">
         <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C743" s="56" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C743" s="56" t="n"/>
       <c r="D743" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
+          <t>Mengubah mode tampilan kalender</t>
         </is>
       </c>
       <c r="E743" s="56" t="inlineStr">
@@ -31544,12 +31532,12 @@
       </c>
       <c r="G743" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field filter mandatory - Klik button Submit</t>
+          <t>Pada halaman Kalender, klik tombol mode tampilan (Bulan / Minggu / Hari / Daftar)</t>
         </is>
       </c>
       <c r="H743" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>Berhasil menampilkan kalender berdasarkan mode tampilan yang dipilih.</t>
         </is>
       </c>
     </row>
@@ -31561,17 +31549,13 @@
       </c>
       <c r="B744" s="56" t="inlineStr">
         <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C744" s="56" t="inlineStr">
-        <is>
-          <t>Personal Funnel</t>
-        </is>
-      </c>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C744" s="56" t="n"/>
       <c r="D744" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data Personal Funnel</t>
+          <t>Memfilter entri kalender berdasarkan kategori</t>
         </is>
       </c>
       <c r="E744" s="56" t="inlineStr">
@@ -31581,39 +31565,35 @@
       </c>
       <c r="F744" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G744" s="56" t="inlineStr">
         <is>
-          <t>Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Centang atau uncentang checkbox kategori entri (Task / Acara / Hari Libur / Time Off / Pola Kerja)</t>
         </is>
       </c>
       <c r="H744" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menampilkan entri kalender sesuai kategori yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="745" ht="14" customHeight="1">
       <c r="A745" s="55" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="B745" s="56" t="inlineStr">
         <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C745" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C745" s="56" t="n"/>
       <c r="D745" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Rekap Funnel</t>
+          <t>Menambahkan task baru</t>
         </is>
       </c>
       <c r="E745" s="56" t="inlineStr">
@@ -31628,34 +31608,30 @@
       </c>
       <c r="G745" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Funding - Klik sub menu Rekap Funnel</t>
+          <t>Klik tombol Tambah - Pilih Tambah Task - Lengkapi formulir task - Klik Buat Task</t>
         </is>
       </c>
       <c r="H745" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Rekap Funnel.</t>
+          <t>Berhasil menambahkan task baru ke dalam kalender.</t>
         </is>
       </c>
     </row>
     <row r="746" ht="28" customHeight="1">
       <c r="A746" s="55" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="B746" s="56" t="inlineStr">
         <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C746" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C746" s="56" t="n"/>
       <c r="D746" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data Rekap Funnel</t>
+          <t>Menambahkan acara baru</t>
         </is>
       </c>
       <c r="E746" s="56" t="inlineStr">
@@ -31665,39 +31641,35 @@
       </c>
       <c r="F746" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G746" s="56" t="inlineStr">
         <is>
-          <t>Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun) - Klik button Filter Data</t>
+          <t>Klik tombol Tambah - Pilih Tambah Acara - Lengkapi formulir event - Klik Buat Event</t>
         </is>
       </c>
       <c r="H746" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
+          <t>Berhasil menambahkan acara baru ke dalam kalender.</t>
         </is>
       </c>
     </row>
     <row r="747" ht="42" customHeight="1">
       <c r="A747" s="55" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="B747" s="56" t="inlineStr">
         <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C747" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C747" s="56" t="n"/>
       <c r="D747" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Rekap Funnel</t>
+          <t>Menambahkan label baru</t>
         </is>
       </c>
       <c r="E747" s="56" t="inlineStr">
@@ -31707,39 +31679,35 @@
       </c>
       <c r="F747" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G747" s="56" t="inlineStr">
         <is>
-          <t>Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role) - Klik button Filter Data</t>
+          <t>Klik tombol Kelola Label - Masukkan Nama label - Pilih warna label - Klik Tambah Label</t>
         </is>
       </c>
       <c r="H747" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
+          <t>Berhasil menambahkan label baru dan menampilkan notifikasi sukses.</t>
         </is>
       </c>
     </row>
     <row r="748" ht="28" customHeight="1">
       <c r="A748" s="55" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="B748" s="56" t="inlineStr">
         <is>
-          <t>Report Funding</t>
-        </is>
-      </c>
-      <c r="C748" s="56" t="inlineStr">
-        <is>
-          <t>Rekap Funnel</t>
-        </is>
-      </c>
+          <t>Kalender</t>
+        </is>
+      </c>
+      <c r="C748" s="56" t="n"/>
       <c r="D748" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
+          <t>Menghapus label</t>
         </is>
       </c>
       <c r="E748" s="56" t="inlineStr">
@@ -31749,24 +31717,24 @@
       </c>
       <c r="F748" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G748" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field filter mandatory - Klik button Filter Data</t>
+          <t>Pada daftar label, klik icon Hapus pada label yang dipilih - Konfirmasi Hapus</t>
         </is>
       </c>
       <c r="H748" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>Berhasil menghapus label dari sistem.</t>
         </is>
       </c>
     </row>
     <row r="749" ht="14" customHeight="1">
       <c r="A749" s="55" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="B749" s="56" t="inlineStr">
@@ -31776,12 +31744,12 @@
       </c>
       <c r="C749" s="56" t="inlineStr">
         <is>
-          <t>Rekap Funnel</t>
+          <t>Personal Funnel</t>
         </is>
       </c>
       <c r="D749" s="56" t="inlineStr">
         <is>
-          <t>Mengunduh data Rekap Funnel</t>
+          <t>Membuka halaman Personal Funnel</t>
         </is>
       </c>
       <c r="E749" s="56" t="inlineStr">
@@ -31791,24 +31759,24 @@
       </c>
       <c r="F749" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G749" s="56" t="inlineStr">
         <is>
-          <t>Klik button Download Excel</t>
+          <t>Klik menu Report Funding - Klik sub menu Personal Funnel</t>
         </is>
       </c>
       <c r="H749" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file Excel data Rekap Funnel.</t>
+          <t>Berhasil menampilkan halaman Personal Funnel.</t>
         </is>
       </c>
     </row>
     <row r="750" ht="14" customHeight="1">
       <c r="A750" s="55" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="B750" s="56" t="inlineStr">
@@ -31818,12 +31786,12 @@
       </c>
       <c r="C750" s="56" t="inlineStr">
         <is>
-          <t>Regional Funnel</t>
+          <t>Personal Funnel</t>
         </is>
       </c>
       <c r="D750" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Regional Funnel</t>
+          <t>Melakukan filter data Personal Funnel</t>
         </is>
       </c>
       <c r="E750" s="56" t="inlineStr">
@@ -31833,24 +31801,24 @@
       </c>
       <c r="F750" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G750" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Funding - Klik sub menu Regional Funnel</t>
+          <t>Mengisi semua field filter mandatory - Klik button Submit</t>
         </is>
       </c>
       <c r="H750" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Regional Funnel.</t>
+          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="751" ht="14" customHeight="1">
       <c r="A751" s="55" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="B751" s="56" t="inlineStr">
@@ -31860,12 +31828,12 @@
       </c>
       <c r="C751" s="56" t="inlineStr">
         <is>
-          <t>Regional Funnel</t>
+          <t>Personal Funnel</t>
         </is>
       </c>
       <c r="D751" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Regional Funnel</t>
+          <t>Melakukan filter data Personal Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E751" s="56" t="inlineStr">
@@ -31880,19 +31848,19 @@
       </c>
       <c r="G751" s="56" t="inlineStr">
         <is>
-          <t>Mengisi semua field filter mandatory - Klik button Submit</t>
+          <t>Mengosongkan field filter mandatory - Klik button Submit</t>
         </is>
       </c>
       <c r="H751" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="752" ht="14" customHeight="1">
       <c r="A752" s="55" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="B752" s="56" t="inlineStr">
@@ -31902,12 +31870,12 @@
       </c>
       <c r="C752" s="56" t="inlineStr">
         <is>
-          <t>Regional Funnel</t>
+          <t>Personal Funnel</t>
         </is>
       </c>
       <c r="D752" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
+          <t>Mengekspor data Personal Funnel</t>
         </is>
       </c>
       <c r="E752" s="56" t="inlineStr">
@@ -31917,24 +31885,24 @@
       </c>
       <c r="F752" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G752" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field filter mandatory - Klik button Submit</t>
+          <t>Klik button Export - Klik icon download pada panel Download Export</t>
         </is>
       </c>
       <c r="H752" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
     <row r="753" ht="14" customHeight="1">
       <c r="A753" s="55" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="B753" s="56" t="inlineStr">
@@ -31944,12 +31912,12 @@
       </c>
       <c r="C753" s="56" t="inlineStr">
         <is>
-          <t>Regional Funnel</t>
+          <t>Rekap Funnel</t>
         </is>
       </c>
       <c r="D753" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Regional Funnel dengan keyword valid</t>
+          <t>Membuka halaman Rekap Funnel</t>
         </is>
       </c>
       <c r="E753" s="56" t="inlineStr">
@@ -31959,24 +31927,24 @@
       </c>
       <c r="F753" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G753" s="56" t="inlineStr">
         <is>
-          <t>Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Klik menu Report Funding - Klik sub menu Rekap Funnel</t>
         </is>
       </c>
       <c r="H753" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan halaman Rekap Funnel.</t>
         </is>
       </c>
     </row>
     <row r="754" ht="14" customHeight="1">
       <c r="A754" s="55" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="B754" s="56" t="inlineStr">
@@ -31986,12 +31954,12 @@
       </c>
       <c r="C754" s="56" t="inlineStr">
         <is>
-          <t>Regional Funnel</t>
+          <t>Rekap Funnel</t>
         </is>
       </c>
       <c r="D754" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Regional Funnel dengan keyword tidak valid</t>
+          <t>Menampilkan data Rekap Funnel</t>
         </is>
       </c>
       <c r="E754" s="56" t="inlineStr">
@@ -32006,19 +31974,19 @@
       </c>
       <c r="G754" s="56" t="inlineStr">
         <is>
-          <t>Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Mengisi field filter mandatory (Kantor Wilayah, Unit Bisnis, Produk, Info Bulan, Info Tahun) - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H754" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil menampilkan daftar data Rekap Funnel di dalam tabel.</t>
         </is>
       </c>
     </row>
     <row r="755" ht="14" customHeight="1">
       <c r="A755" s="55" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="B755" s="56" t="inlineStr">
@@ -32028,12 +31996,12 @@
       </c>
       <c r="C755" s="56" t="inlineStr">
         <is>
-          <t>Regional Funnel</t>
+          <t>Rekap Funnel</t>
         </is>
       </c>
       <c r="D755" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data prospek berdasarkan kantor cabang</t>
+          <t>Melakukan filter data Rekap Funnel</t>
         </is>
       </c>
       <c r="E755" s="56" t="inlineStr">
@@ -32048,19 +32016,19 @@
       </c>
       <c r="G755" s="56" t="inlineStr">
         <is>
-          <t>Klik salah satu daftar kantor cabang pada tabel</t>
+          <t>Mengisi field filter mandatory beserta kriteria filter spesifik (seperti Kantor Cabang/Role) - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H755" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data prospek pada kantor cabang yang dipilih.</t>
+          <t>Berhasil menampilkan data Rekap Funnel yang sesuai dengan kriteria filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="756" ht="14" customHeight="1">
       <c r="A756" s="55" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="B756" s="56" t="inlineStr">
@@ -32070,12 +32038,12 @@
       </c>
       <c r="C756" s="56" t="inlineStr">
         <is>
-          <t>Pengaturan Funnel</t>
+          <t>Rekap Funnel</t>
         </is>
       </c>
       <c r="D756" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Pengaturan Funnel Funding</t>
+          <t>Melakukan filter data Rekap Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E756" s="56" t="inlineStr">
@@ -32085,24 +32053,24 @@
       </c>
       <c r="F756" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G756" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Funding - Klik sub menu Pengaturan Funnel</t>
+          <t>Mengosongkan field filter mandatory - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H756" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Pengaturan Funnel Funding.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="757" ht="14" customHeight="1">
       <c r="A757" s="55" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="B757" s="56" t="inlineStr">
@@ -32112,12 +32080,12 @@
       </c>
       <c r="C757" s="56" t="inlineStr">
         <is>
-          <t>Pengaturan Funnel</t>
+          <t>Rekap Funnel</t>
         </is>
       </c>
       <c r="D757" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data Pengaturan Funnel Funding berdasarkan section</t>
+          <t>Mengunduh data Rekap Funnel</t>
         </is>
       </c>
       <c r="E757" s="56" t="inlineStr">
@@ -32132,19 +32100,19 @@
       </c>
       <c r="G757" s="56" t="inlineStr">
         <is>
-          <t>Klik salah satu daftar section pada tabel</t>
+          <t>Klik button Download Excel</t>
         </is>
       </c>
       <c r="H757" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pengaturan funnel Funding.</t>
+          <t>Berhasil mendownload file Excel data Rekap Funnel.</t>
         </is>
       </c>
     </row>
     <row r="758" ht="14" customHeight="1">
       <c r="A758" s="55" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="B758" s="56" t="inlineStr">
@@ -32154,12 +32122,12 @@
       </c>
       <c r="C758" s="56" t="inlineStr">
         <is>
-          <t>Pengaturan Funnel</t>
+          <t>Regional Funnel</t>
         </is>
       </c>
       <c r="D758" s="56" t="inlineStr">
         <is>
-          <t>Mengubah data Pengaturan Funnel Funding</t>
+          <t>Membuka halaman Regional Funnel</t>
         </is>
       </c>
       <c r="E758" s="56" t="inlineStr">
@@ -32174,19 +32142,19 @@
       </c>
       <c r="G758" s="56" t="inlineStr">
         <is>
-          <t>Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel - Klik button Submit</t>
+          <t>Klik menu Report Funding - Klik sub menu Regional Funnel</t>
         </is>
       </c>
       <c r="H758" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
+          <t>Berhasil menampilkan halaman Regional Funnel.</t>
         </is>
       </c>
     </row>
     <row r="759" ht="14" customHeight="1">
       <c r="A759" s="55" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="B759" s="56" t="inlineStr">
@@ -32196,12 +32164,12 @@
       </c>
       <c r="C759" s="56" t="inlineStr">
         <is>
-          <t>Pengaturan Funnel</t>
+          <t>Regional Funnel</t>
         </is>
       </c>
       <c r="D759" s="56" t="inlineStr">
         <is>
-          <t>Mengubah data Pengaturan Funnel Funding tanpa mengisi field mandatory</t>
+          <t>Melakukan filter data Regional Funnel</t>
         </is>
       </c>
       <c r="E759" s="56" t="inlineStr">
@@ -32211,24 +32179,24 @@
       </c>
       <c r="F759" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G759" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field mandatory Performance Percentage - Klik button Submit</t>
+          <t>Mengisi semua field filter mandatory - Klik button Submit</t>
         </is>
       </c>
       <c r="H759" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="760" ht="14" customHeight="1">
       <c r="A760" s="55" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="B760" s="56" t="inlineStr">
@@ -32238,12 +32206,12 @@
       </c>
       <c r="C760" s="56" t="inlineStr">
         <is>
-          <t>Pengaturan Funnel</t>
+          <t>Regional Funnel</t>
         </is>
       </c>
       <c r="D760" s="56" t="inlineStr">
         <is>
-          <t>Menambahkan Condition pada Performance Indicator</t>
+          <t>Melakukan filter data Regional Funnel tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E760" s="56" t="inlineStr">
@@ -32258,19 +32226,19 @@
       </c>
       <c r="G760" s="56" t="inlineStr">
         <is>
-          <t>Klik button Add Condition pada bagian Performance Indicator - Mengisi semua field mandatory pada condition baru - Klik button Submit</t>
+          <t>Mengosongkan field filter mandatory - Klik button Submit</t>
         </is>
       </c>
       <c r="H760" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menyimpan condition baru pada Performance Indicator.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="761" ht="14" customHeight="1">
       <c r="A761" s="55" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="B761" s="56" t="inlineStr">
@@ -32280,12 +32248,12 @@
       </c>
       <c r="C761" s="56" t="inlineStr">
         <is>
-          <t>Pengaturan Funnel</t>
+          <t>Regional Funnel</t>
         </is>
       </c>
       <c r="D761" s="56" t="inlineStr">
         <is>
-          <t>Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory</t>
+          <t>Mencari data Regional Funnel dengan keyword valid</t>
         </is>
       </c>
       <c r="E761" s="56" t="inlineStr">
@@ -32300,19 +32268,19 @@
       </c>
       <c r="G761" s="56" t="inlineStr">
         <is>
-          <t>Klik button Add Condition pada bagian Performance Indicator - Mengosongkan field mandatory pada condition baru - Klik button Submit</t>
+          <t>Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
         </is>
       </c>
       <c r="H761" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
+          <t>Berhasil menampilkan data yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="762" ht="14" customHeight="1">
       <c r="A762" s="55" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="B762" s="56" t="inlineStr">
@@ -32322,12 +32290,12 @@
       </c>
       <c r="C762" s="56" t="inlineStr">
         <is>
-          <t>Pengaturan Funnel</t>
+          <t>Regional Funnel</t>
         </is>
       </c>
       <c r="D762" s="56" t="inlineStr">
         <is>
-          <t>Menghapus Condition pada Performance Indicator</t>
+          <t>Mencari data Regional Funnel dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E762" s="56" t="inlineStr">
@@ -32342,19 +32310,19 @@
       </c>
       <c r="G762" s="56" t="inlineStr">
         <is>
-          <t>Klik button Remove pada salah satu condition di Performance Indicator - Klik button Submit</t>
+          <t>Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
         </is>
       </c>
       <c r="H762" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
+          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="763" ht="14" customHeight="1">
       <c r="A763" s="55" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="B763" s="56" t="inlineStr">
@@ -32364,12 +32332,12 @@
       </c>
       <c r="C763" s="56" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Regional Funnel</t>
         </is>
       </c>
       <c r="D763" s="56" t="inlineStr">
         <is>
-          <t>Membuka halaman Daily Sales Agenda</t>
+          <t>Menampilkan data prospek berdasarkan kantor cabang</t>
         </is>
       </c>
       <c r="E763" s="56" t="inlineStr">
@@ -32379,24 +32347,24 @@
       </c>
       <c r="F763" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G763" s="56" t="inlineStr">
         <is>
-          <t>Klik menu Report Funding - Klik sub menu Daily Sales Agenda</t>
+          <t>Klik salah satu daftar kantor cabang pada tabel</t>
         </is>
       </c>
       <c r="H763" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman Daily Sales Agenda.</t>
+          <t>Berhasil menampilkan data prospek pada kantor cabang yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="764" ht="14" customHeight="1">
       <c r="A764" s="55" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="B764" s="56" t="inlineStr">
@@ -32406,12 +32374,12 @@
       </c>
       <c r="C764" s="56" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D764" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Daily Sales Agenda</t>
+          <t>Membuka halaman Pengaturan Funnel Funding</t>
         </is>
       </c>
       <c r="E764" s="56" t="inlineStr">
@@ -32421,24 +32389,24 @@
       </c>
       <c r="F764" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G764" s="56" t="inlineStr">
         <is>
-          <t>Mengisi semua field filter mandatory - Klik button Filter Data</t>
+          <t>Klik menu Report Funding - Klik sub menu Pengaturan Funnel</t>
         </is>
       </c>
       <c r="H764" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
+          <t>Berhasil menampilkan halaman Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
     <row r="765" ht="14" customHeight="1">
       <c r="A765" s="55" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="B765" s="56" t="inlineStr">
@@ -32448,12 +32416,12 @@
       </c>
       <c r="C765" s="56" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D765" s="56" t="inlineStr">
         <is>
-          <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
+          <t>Menampilkan data Pengaturan Funnel Funding berdasarkan section</t>
         </is>
       </c>
       <c r="E765" s="56" t="inlineStr">
@@ -32468,19 +32436,19 @@
       </c>
       <c r="G765" s="56" t="inlineStr">
         <is>
-          <t>Mengosongkan field filter mandatory - Klik button Filter Data</t>
+          <t>Klik salah satu daftar section pada tabel</t>
         </is>
       </c>
       <c r="H765" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
+          <t>Berhasil menampilkan data pengaturan funnel Funding.</t>
         </is>
       </c>
     </row>
     <row r="766" ht="14" customHeight="1">
       <c r="A766" s="55" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="B766" s="56" t="inlineStr">
@@ -32490,12 +32458,12 @@
       </c>
       <c r="C766" s="56" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D766" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Masuk</t>
+          <t>Mengubah data Pengaturan Funnel Funding</t>
         </is>
       </c>
       <c r="E766" s="56" t="inlineStr">
@@ -32505,24 +32473,24 @@
       </c>
       <c r="F766" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G766" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk</t>
+          <t>Mengisi semua field mandatory Performance Percentage pada setiap tahapan funnel - Klik button Submit</t>
         </is>
       </c>
       <c r="H766" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pada tab Prospek Masuk.</t>
+          <t>Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
     <row r="767" ht="28" customHeight="1">
       <c r="A767" s="55" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="B767" s="56" t="inlineStr">
@@ -32532,12 +32500,12 @@
       </c>
       <c r="C767" s="56" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D767" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Masuk dengan keyword valid</t>
+          <t>Mengubah data Pengaturan Funnel Funding tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E767" s="56" t="inlineStr">
@@ -32552,19 +32520,19 @@
       </c>
       <c r="G767" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Mengosongkan field mandatory Performance Percentage - Klik button Submit</t>
         </is>
       </c>
       <c r="H767" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
     <row r="768" ht="14" customHeight="1">
       <c r="A768" s="55" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="B768" s="56" t="inlineStr">
@@ -32574,17 +32542,17 @@
       </c>
       <c r="C768" s="56" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D768" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
+          <t>Menambahkan Condition pada Performance Indicator</t>
         </is>
       </c>
       <c r="E768" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F768" s="55" t="inlineStr">
@@ -32594,19 +32562,19 @@
       </c>
       <c r="G768" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Klik button Add Condition pada bagian Performance Indicator - Mengisi semua field mandatory pada condition baru - Klik button Submit</t>
         </is>
       </c>
       <c r="H768" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil menyimpan condition baru pada Performance Indicator.</t>
         </is>
       </c>
     </row>
     <row r="769" ht="14" customHeight="1">
       <c r="A769" s="55" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="B769" s="56" t="inlineStr">
@@ -32616,12 +32584,12 @@
       </c>
       <c r="C769" s="56" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D769" s="56" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Masuk</t>
+          <t>Menambahkan Condition pada Performance Indicator tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E769" s="56" t="inlineStr">
@@ -32636,19 +32604,19 @@
       </c>
       <c r="G769" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk - Klik salah satu nama prospek pada tabel</t>
+          <t>Klik button Add Condition pada bagian Performance Indicator - Mengosongkan field mandatory pada condition baru - Klik button Submit</t>
         </is>
       </c>
       <c r="H769" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman detail prospek.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field mandatory harus diisi.</t>
         </is>
       </c>
     </row>
     <row r="770" ht="14" customHeight="1">
       <c r="A770" s="55" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="B770" s="56" t="inlineStr">
@@ -32658,12 +32626,12 @@
       </c>
       <c r="C770" s="56" t="inlineStr">
         <is>
-          <t>Daily Sales Agenda</t>
+          <t>Pengaturan Funnel</t>
         </is>
       </c>
       <c r="D770" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data tab Prospek Masuk</t>
+          <t>Menghapus Condition pada Performance Indicator</t>
         </is>
       </c>
       <c r="E770" s="56" t="inlineStr">
@@ -32673,24 +32641,24 @@
       </c>
       <c r="F770" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G770" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Masuk - Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Klik button Remove pada salah satu condition di Performance Indicator - Klik button Submit</t>
         </is>
       </c>
       <c r="H770" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menyimpan perubahan data Pengaturan Funnel Funding.</t>
         </is>
       </c>
     </row>
     <row r="771" ht="14" customHeight="1">
       <c r="A771" s="55" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="B771" s="56" t="inlineStr">
@@ -32705,7 +32673,7 @@
       </c>
       <c r="D771" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Closing</t>
+          <t>Membuka halaman Daily Sales Agenda</t>
         </is>
       </c>
       <c r="E771" s="56" t="inlineStr">
@@ -32715,24 +32683,24 @@
       </c>
       <c r="F771" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G771" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing</t>
+          <t>Klik menu Report Funding - Klik sub menu Daily Sales Agenda</t>
         </is>
       </c>
       <c r="H771" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pada tab Prospek Closing.</t>
+          <t>Berhasil menampilkan halaman Daily Sales Agenda.</t>
         </is>
       </c>
     </row>
     <row r="772" ht="14" customHeight="1">
       <c r="A772" s="55" t="inlineStr">
         <is>
-          <t>64.10</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="B772" s="56" t="inlineStr">
@@ -32747,7 +32715,7 @@
       </c>
       <c r="D772" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Closing dengan keyword valid</t>
+          <t>Melakukan filter data Daily Sales Agenda</t>
         </is>
       </c>
       <c r="E772" s="56" t="inlineStr">
@@ -32757,24 +32725,24 @@
       </c>
       <c r="F772" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G772" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Mengisi semua field filter mandatory - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H772" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan data sesuai dengan filter yang dipilih.</t>
         </is>
       </c>
     </row>
     <row r="773" ht="14" customHeight="1">
       <c r="A773" s="55" t="inlineStr">
         <is>
-          <t>64.11</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="B773" s="56" t="inlineStr">
@@ -32789,12 +32757,12 @@
       </c>
       <c r="D773" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
+          <t>Melakukan filter data Daily Sales Agenda tanpa mengisi field mandatory</t>
         </is>
       </c>
       <c r="E773" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F773" s="55" t="inlineStr">
@@ -32804,19 +32772,19 @@
       </c>
       <c r="G773" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Mengosongkan field filter mandatory - Klik button Filter Data</t>
         </is>
       </c>
       <c r="H773" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil menampilkan pesan validasi bahwa field filter mandatory wajib diisi.</t>
         </is>
       </c>
     </row>
     <row r="774" ht="14" customHeight="1">
       <c r="A774" s="55" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="B774" s="56" t="inlineStr">
@@ -32831,7 +32799,7 @@
       </c>
       <c r="D774" s="56" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Closing</t>
+          <t>Menampilkan data tab Prospek Masuk</t>
         </is>
       </c>
       <c r="E774" s="56" t="inlineStr">
@@ -32846,19 +32814,19 @@
       </c>
       <c r="G774" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing - Klik salah satu nama prospek pada tabel</t>
+          <t>Klik tab Prospek Masuk</t>
         </is>
       </c>
       <c r="H774" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman detail prospek.</t>
+          <t>Berhasil menampilkan data pada tab Prospek Masuk.</t>
         </is>
       </c>
     </row>
     <row r="775" ht="14" customHeight="1">
       <c r="A775" s="55" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="B775" s="56" t="inlineStr">
@@ -32873,7 +32841,7 @@
       </c>
       <c r="D775" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data tab Prospek Closing</t>
+          <t>Mencari data Prospek Masuk dengan keyword valid</t>
         </is>
       </c>
       <c r="E775" s="56" t="inlineStr">
@@ -32888,19 +32856,19 @@
       </c>
       <c r="G775" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Closing - Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Klik tab Prospek Masuk - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
         </is>
       </c>
       <c r="H775" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menampilkan data yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="776" ht="14" customHeight="1">
       <c r="A776" s="55" t="inlineStr">
         <is>
-          <t>64.14</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="B776" s="56" t="inlineStr">
@@ -32915,12 +32883,12 @@
       </c>
       <c r="D776" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Referal</t>
+          <t>Mencari data Prospek Masuk dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E776" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F776" s="55" t="inlineStr">
@@ -32930,19 +32898,19 @@
       </c>
       <c r="G776" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal</t>
+          <t>Klik tab Prospek Masuk - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
         </is>
       </c>
       <c r="H776" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pada tab Prospek Referal.</t>
+          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="777" ht="14" customHeight="1">
       <c r="A777" s="55" t="inlineStr">
         <is>
-          <t>64.15</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="B777" s="56" t="inlineStr">
@@ -32957,7 +32925,7 @@
       </c>
       <c r="D777" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Referal dengan keyword valid</t>
+          <t>Melihat detail Prospek Masuk</t>
         </is>
       </c>
       <c r="E777" s="56" t="inlineStr">
@@ -32967,24 +32935,24 @@
       </c>
       <c r="F777" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G777" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Klik tab Prospek Masuk - Klik salah satu nama prospek pada tabel</t>
         </is>
       </c>
       <c r="H777" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
     <row r="778" ht="14" customHeight="1">
       <c r="A778" s="55" t="inlineStr">
         <is>
-          <t>64.16</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="B778" s="56" t="inlineStr">
@@ -32999,34 +32967,34 @@
       </c>
       <c r="D778" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Referal dengan keyword tidak valid</t>
+          <t>Mengekspor data tab Prospek Masuk</t>
         </is>
       </c>
       <c r="E778" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F778" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G778" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Klik tab Prospek Masuk - Klik button Export - Klik icon download pada panel Download Export</t>
         </is>
       </c>
       <c r="H778" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
     <row r="779" ht="28" customHeight="1">
       <c r="A779" s="55" t="inlineStr">
         <is>
-          <t>64.17</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="B779" s="56" t="inlineStr">
@@ -33041,7 +33009,7 @@
       </c>
       <c r="D779" s="56" t="inlineStr">
         <is>
-          <t>Melihat detail Prospek Referal</t>
+          <t>Menampilkan data tab Prospek Closing</t>
         </is>
       </c>
       <c r="E779" s="56" t="inlineStr">
@@ -33056,19 +33024,19 @@
       </c>
       <c r="G779" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal - Klik salah satu nama prospek pada tabel</t>
+          <t>Klik tab Prospek Closing</t>
         </is>
       </c>
       <c r="H779" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan halaman detail prospek.</t>
+          <t>Berhasil menampilkan data pada tab Prospek Closing.</t>
         </is>
       </c>
     </row>
     <row r="780" ht="14" customHeight="1">
       <c r="A780" s="55" t="inlineStr">
         <is>
-          <t>64.18</t>
+          <t>65.10</t>
         </is>
       </c>
       <c r="B780" s="56" t="inlineStr">
@@ -33083,7 +33051,7 @@
       </c>
       <c r="D780" s="56" t="inlineStr">
         <is>
-          <t>Mengekspor data tab Prospek Referal</t>
+          <t>Mencari data Prospek Closing dengan keyword valid</t>
         </is>
       </c>
       <c r="E780" s="56" t="inlineStr">
@@ -33098,19 +33066,19 @@
       </c>
       <c r="G780" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal - Klik button Export - Klik icon download pada panel Download Export</t>
+          <t>Klik tab Prospek Closing - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
         </is>
       </c>
       <c r="H780" s="56" t="inlineStr">
         <is>
-          <t>Berhasil mendownload file export.</t>
+          <t>Berhasil menampilkan data yang dicari.</t>
         </is>
       </c>
     </row>
     <row r="781" ht="28" customHeight="1">
       <c r="A781" s="55" t="inlineStr">
         <is>
-          <t>64.19</t>
+          <t>65.11</t>
         </is>
       </c>
       <c r="B781" s="56" t="inlineStr">
@@ -33125,12 +33093,12 @@
       </c>
       <c r="D781" s="56" t="inlineStr">
         <is>
-          <t>Menampilkan data tab Prospek Referal Closing</t>
+          <t>Mencari data Prospek Closing dengan keyword tidak valid</t>
         </is>
       </c>
       <c r="E781" s="56" t="inlineStr">
         <is>
-          <t>Positive Case</t>
+          <t>Negative Case</t>
         </is>
       </c>
       <c r="F781" s="55" t="inlineStr">
@@ -33140,19 +33108,19 @@
       </c>
       <c r="G781" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal Closing</t>
+          <t>Klik tab Prospek Closing - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
         </is>
       </c>
       <c r="H781" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data pada tab Prospek Referal Closing.</t>
+          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
         </is>
       </c>
     </row>
     <row r="782" ht="14" customHeight="1">
       <c r="A782" s="55" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>65.12</t>
         </is>
       </c>
       <c r="B782" s="56" t="inlineStr">
@@ -33167,7 +33135,7 @@
       </c>
       <c r="D782" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Referal Closing dengan keyword valid</t>
+          <t>Melihat detail Prospek Closing</t>
         </is>
       </c>
       <c r="E782" s="56" t="inlineStr">
@@ -33177,24 +33145,24 @@
       </c>
       <c r="F782" s="55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G782" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal Closing - Mengisi field Cari Data dengan keyword valid - Klik button Search</t>
+          <t>Klik tab Prospek Closing - Klik salah satu nama prospek pada tabel</t>
         </is>
       </c>
       <c r="H782" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan data yang dicari.</t>
+          <t>Berhasil menampilkan halaman detail prospek.</t>
         </is>
       </c>
     </row>
     <row r="783" ht="14" customHeight="1">
       <c r="A783" s="55" t="inlineStr">
         <is>
-          <t>64.21</t>
+          <t>65.13</t>
         </is>
       </c>
       <c r="B783" s="56" t="inlineStr">
@@ -33209,34 +33177,34 @@
       </c>
       <c r="D783" s="56" t="inlineStr">
         <is>
-          <t>Mencari data Prospek Referal Closing dengan keyword tidak valid</t>
+          <t>Mengekspor data tab Prospek Closing</t>
         </is>
       </c>
       <c r="E783" s="56" t="inlineStr">
         <is>
-          <t>Negative Case</t>
+          <t>Positive Case</t>
         </is>
       </c>
       <c r="F783" s="55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G783" s="56" t="inlineStr">
         <is>
-          <t>Klik tab Prospek Referal Closing - Mengisi field Cari Data dengan keyword tidak valid - Klik button Search</t>
+          <t>Klik tab Prospek Closing - Klik button Export - Klik icon download pada panel Download Export</t>
         </is>
       </c>
       <c r="H783" s="56" t="inlineStr">
         <is>
-          <t>Berhasil menampilkan informasi bahwa data tidak ditemukan.</t>
+          <t>Berhasil mendownload file export.</t>
         </is>
       </c>
     </row>
     <row r="784" ht="14" customHeight="1">
       <c r="A784" s="55" t="inlineStr">
         <is>
-          <t>64.22</t>
+          <t>65.14</t>
         </is>
       </c>
       <c r="B784" s="56" t="inlineStr">
@@ -33251,7 +33219,7 @@
       </c>
       <c r="D784" s="56